--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/GlobalMoSMT-2023/Shared Documents/General/2026/Goals Alignment 2026/Strategic Execution 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3237" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{748366EC-4437-42B7-8A5F-962600F38AC1}"/>
+  <xr:revisionPtr revIDLastSave="3302" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BCABF23-FFE1-4786-A3DA-C013F3078329}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Mastersheet" sheetId="5" state="hidden" r:id="rId1"/>
+    <sheet name="Mastersheet" sheetId="5" r:id="rId1"/>
     <sheet name="AOP Critical" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -366,7 +366,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="143">
   <si>
     <t>Strategic Imperatives</t>
   </si>
@@ -586,10 +586,11 @@
     <t>Increase contract penetration %</t>
   </si>
   <si>
-    <t>0.8% Gap VS AOP. YoY improvement by 0.7% excluding GRC, Win back campaign impact in Q4</t>
-  </si>
-  <si>
-    <t>Funnel focus actions driven across regions for same</t>
+    <t xml:space="preserve">-0.8% delta Vs AOP. Excluding GRC 0.7% YoY improvement.  LATAM renewals improved ITM Sep. </t>
+  </si>
+  <si>
+    <t>1) Funnel focus actions driven across regions for renewals.
+2) Contract Funnel tracked 90 days before expiry for timely renewals.</t>
   </si>
   <si>
     <t>Adjusted EBITA %</t>
@@ -604,12 +605,6 @@
     <t>AOP</t>
   </si>
   <si>
-    <t>EBIT lower by 1.4% vs AOP mainly impacted by increased in Mkt Sellex, which have wrong baseline.</t>
-  </si>
-  <si>
-    <t>During AOP26 wrong base considered of JuneFC 25, which was corretced and reflecting on June FC 26. (Action already closed)</t>
-  </si>
-  <si>
     <t>Adjusted EBITA KPI</t>
   </si>
   <si>
@@ -631,17 +626,18 @@
     <t>Inventory as a % MAT sales</t>
   </si>
   <si>
-    <t xml:space="preserve">Market inventory : 14 M above AOP .
-Growth : +3.8 M -Hudut  + Namibia tender  
-EU + 3.7  M above AOP driven delayed Demo liquidation  ,
-NAM progressing will with steady decline Month over month currently 0.8M above AOP , 
+    <t xml:space="preserve">Market inventory : 7.7 M above AOP .
+Growth : + 1M  Namibia tender  
+EU +1.2   M above AOP driven delayed Demo liquidation  ,
+NAM  0.5 M above AOP , 
 UIPE effect increased leading  to 10M increase in Mrkt inventory ( Aug reported at 31% against AOP 59% ) 
-UIPE @ AOP, inventory MAT would be 25.3% </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. NAR :AOP accelator program launched to improve OIT to rev conversion.
+</t>
+  </si>
+  <si>
+    <t>1. NAR :AOP accelator program launched to improve OIT to rev conversion.
 2. EU : Demo  liquidation plan aligned toward Q4 to maximise OIT in Q3.
-3. Growth: Hudut 41 system Q3 revnue conversion+ Namibia tender conversion </t>
+3. Growth:  Namibia tender conversion in Q4
+4. UIEP : COE team to analyse the difference and accurate capturing in AOP 2027</t>
   </si>
   <si>
     <t>Inventory as a % MAT sales KPI</t>
@@ -689,7 +685,7 @@
     <t>OIT Growth % (EQ)</t>
   </si>
   <si>
-    <t>EQ OIT YTD Aug lower by 1.5M, which is mainly coming by NAR -4.1M, EU -3.8M however Growth supported by over-drive +6.5M</t>
+    <t>EQ OIT YTD Sep lower by 0.2M, which is mainly coming by NAR -4.4M, EU -3.7M however Growth supported by over-drive +7.9M</t>
   </si>
   <si>
     <t>OIT (Equipment  + Service)</t>
@@ -704,17 +700,19 @@
     <t>Monthly Sales recognized (EQ)</t>
   </si>
   <si>
-    <t>Current OOH does not support the Q3 revenue plan for Europe and Growth.
-OOH is 35 which is   for 95.6 M (Q3 AOP).
-FY 80% OOH and need to be at 95% by Sep end to make FY AOP.</t>
-  </si>
-  <si>
-    <t>OIT to revnue accelarator program launched for NAR
-Drive Additinal B&amp;B OIT in NAM and EU to bridge revnue gap to AOP.
-Get supply chain geared up to deliver mexico tender ( 74 systems)</t>
+    <t xml:space="preserve">Current OOH does not support FY revnue plan. 
+OOH is 117 M agaist AOP of 141M .B&amp;B  24 M B&amp;B required to meet FY AOP.
+</t>
+  </si>
+  <si>
+    <t>Drive B&amp;B OIT 
+NAR : 5 M , EU: 8.5M , Growth : 7.6</t>
   </si>
   <si>
     <t>CSG % KPI</t>
+  </si>
+  <si>
+    <t>Growth</t>
   </si>
   <si>
     <t xml:space="preserve">Impact Index KPI </t>
@@ -1322,7 +1320,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="171">
+  <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1462,9 +1460,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1557,9 +1552,6 @@
     <xf numFmtId="166" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="8" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1569,6 +1561,12 @@
     <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -1811,6 +1809,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1859,35 +1860,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1908,35 +1881,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1999,6 +1944,83 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFDA9694"/>
         </patternFill>
       </fill>
@@ -2021,6 +2043,111 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2069,20 +2196,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
@@ -2091,118 +2204,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2231,6 +2232,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2280,13 +2288,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5198,7 +5199,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15.95">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
     </row>
@@ -5312,51 +5313,51 @@
         <f>IF('AOP Critical'!K6="","",'AOP Critical'!K6)</f>
         <v>T</v>
       </c>
-      <c r="K5" s="70">
+      <c r="K5" s="69">
         <f>IF('AOP Critical'!L6="","",'AOP Critical'!L6)</f>
         <v>0.08</v>
       </c>
-      <c r="L5" s="70">
+      <c r="L5" s="69">
         <f>IF('AOP Critical'!M6="","",'AOP Critical'!M6)</f>
         <v>0.08</v>
       </c>
-      <c r="M5" s="70">
+      <c r="M5" s="69">
         <f>IF('AOP Critical'!N6="","",'AOP Critical'!N6)</f>
         <v>0.08</v>
       </c>
-      <c r="N5" s="70">
+      <c r="N5" s="69">
         <f>IF('AOP Critical'!O6="","",'AOP Critical'!O6)</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="O5" s="70">
+      <c r="O5" s="69">
         <f>IF('AOP Critical'!P6="","",'AOP Critical'!P6)</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="P5" s="70">
+      <c r="P5" s="69">
         <f>IF('AOP Critical'!Q6="","",'AOP Critical'!Q6)</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="Q5" s="70">
+      <c r="Q5" s="69">
         <f>IF('AOP Critical'!R6="","",'AOP Critical'!R6)</f>
         <v>0.06</v>
       </c>
-      <c r="R5" s="70">
+      <c r="R5" s="69">
         <f>IF('AOP Critical'!S6="","",'AOP Critical'!S6)</f>
         <v>0.06</v>
       </c>
-      <c r="S5" s="70">
+      <c r="S5" s="69">
         <f>IF('AOP Critical'!T6="","",'AOP Critical'!T6)</f>
         <v>0.06</v>
       </c>
-      <c r="T5" s="70">
+      <c r="T5" s="69">
         <f>IF('AOP Critical'!U6="","",'AOP Critical'!U6)</f>
         <v>0.05</v>
       </c>
-      <c r="U5" s="70">
+      <c r="U5" s="69">
         <f>IF('AOP Critical'!V6="","",'AOP Critical'!V6)</f>
         <v>0.05</v>
       </c>
-      <c r="V5" s="70">
+      <c r="V5" s="69">
         <f>IF('AOP Critical'!W6="","",'AOP Critical'!W6)</f>
         <v>0.05</v>
       </c>
@@ -5398,51 +5399,51 @@
         <f>IF('AOP Critical'!K7="","",'AOP Critical'!K7)</f>
         <v>A</v>
       </c>
-      <c r="K6" s="69">
+      <c r="K6" s="68">
         <f>IF('AOP Critical'!L7="","",'AOP Critical'!L7)</f>
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="L6" s="69">
+      <c r="L6" s="68">
         <f>IF('AOP Critical'!M7="","",'AOP Critical'!M7)</f>
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="M6" s="69">
+      <c r="M6" s="68">
         <f>IF('AOP Critical'!N7="","",'AOP Critical'!N7)</f>
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="N6" s="69">
+      <c r="N6" s="68">
         <f>IF('AOP Critical'!O7="","",'AOP Critical'!O7)</f>
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="O6" s="69">
+      <c r="O6" s="68">
         <f>IF('AOP Critical'!P7="","",'AOP Critical'!P7)</f>
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="P6" s="69">
+      <c r="P6" s="68">
         <f>IF('AOP Critical'!Q7="","",'AOP Critical'!Q7)</f>
         <v>0.03</v>
       </c>
-      <c r="Q6" s="69">
+      <c r="Q6" s="68">
         <f>IF('AOP Critical'!R7="","",'AOP Critical'!R7)</f>
         <v>3.1E-2</v>
       </c>
-      <c r="R6" s="69">
+      <c r="R6" s="68">
         <f>IF('AOP Critical'!S7="","",'AOP Critical'!S7)</f>
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="S6" s="69">
+      <c r="S6" s="68">
         <f>IF('AOP Critical'!T7="","",'AOP Critical'!T7)</f>
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="T6" s="69" t="str">
+      <c r="T6" s="68" t="str">
         <f>IF('AOP Critical'!U7="","",'AOP Critical'!U7)</f>
         <v/>
       </c>
-      <c r="U6" s="69" t="str">
+      <c r="U6" s="68" t="str">
         <f>IF('AOP Critical'!V7="","",'AOP Critical'!V7)</f>
         <v/>
       </c>
-      <c r="V6" s="69" t="str">
+      <c r="V6" s="68" t="str">
         <f>IF('AOP Critical'!W7="","",'AOP Critical'!W7)</f>
         <v/>
       </c>
@@ -5484,51 +5485,51 @@
         <f>IF('AOP Critical'!K8="","",'AOP Critical'!K8)</f>
         <v>T</v>
       </c>
-      <c r="K7" s="71">
+      <c r="K7" s="70">
         <f>IF('AOP Critical'!L8="","",'AOP Critical'!L8)</f>
         <v>0.9</v>
       </c>
-      <c r="L7" s="71">
+      <c r="L7" s="70">
         <f>IF('AOP Critical'!M8="","",'AOP Critical'!M8)</f>
         <v>0.9</v>
       </c>
-      <c r="M7" s="71">
+      <c r="M7" s="70">
         <f>IF('AOP Critical'!N8="","",'AOP Critical'!N8)</f>
         <v>0.9</v>
       </c>
-      <c r="N7" s="71">
+      <c r="N7" s="70">
         <f>IF('AOP Critical'!O8="","",'AOP Critical'!O8)</f>
         <v>0.9</v>
       </c>
-      <c r="O7" s="71">
+      <c r="O7" s="70">
         <f>IF('AOP Critical'!P8="","",'AOP Critical'!P8)</f>
         <v>0.9</v>
       </c>
-      <c r="P7" s="71">
+      <c r="P7" s="70">
         <f>IF('AOP Critical'!Q8="","",'AOP Critical'!Q8)</f>
         <v>0.9</v>
       </c>
-      <c r="Q7" s="71">
+      <c r="Q7" s="70">
         <f>IF('AOP Critical'!R8="","",'AOP Critical'!R8)</f>
         <v>0.9</v>
       </c>
-      <c r="R7" s="71" t="str">
+      <c r="R7" s="70" t="str">
         <f>IF('AOP Critical'!S8="","",'AOP Critical'!S8)</f>
         <v/>
       </c>
-      <c r="S7" s="71" t="str">
+      <c r="S7" s="70" t="str">
         <f>IF('AOP Critical'!T8="","",'AOP Critical'!T8)</f>
         <v/>
       </c>
-      <c r="T7" s="71" t="str">
+      <c r="T7" s="70" t="str">
         <f>IF('AOP Critical'!U8="","",'AOP Critical'!U8)</f>
         <v/>
       </c>
-      <c r="U7" s="71" t="str">
+      <c r="U7" s="70" t="str">
         <f>IF('AOP Critical'!V8="","",'AOP Critical'!V8)</f>
         <v/>
       </c>
-      <c r="V7" s="71" t="str">
+      <c r="V7" s="70" t="str">
         <f>IF('AOP Critical'!W8="","",'AOP Critical'!W8)</f>
         <v/>
       </c>
@@ -5570,51 +5571,51 @@
         <f>IF('AOP Critical'!K9="","",'AOP Critical'!K9)</f>
         <v>A</v>
       </c>
-      <c r="K8" s="72">
+      <c r="K8" s="71">
         <f>IF('AOP Critical'!L9="","",'AOP Critical'!L9)</f>
         <v>1</v>
       </c>
-      <c r="L8" s="72">
+      <c r="L8" s="71">
         <f>IF('AOP Critical'!M9="","",'AOP Critical'!M9)</f>
         <v>0.75</v>
       </c>
-      <c r="M8" s="72">
+      <c r="M8" s="71">
         <f>IF('AOP Critical'!N9="","",'AOP Critical'!N9)</f>
         <v>0.4</v>
       </c>
-      <c r="N8" s="72">
+      <c r="N8" s="71">
         <f>IF('AOP Critical'!O9="","",'AOP Critical'!O9)</f>
         <v>0</v>
       </c>
-      <c r="O8" s="72">
+      <c r="O8" s="71">
         <f>IF('AOP Critical'!P9="","",'AOP Critical'!P9)</f>
         <v>0</v>
       </c>
-      <c r="P8" s="72">
+      <c r="P8" s="71">
         <f>IF('AOP Critical'!Q9="","",'AOP Critical'!Q9)</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="72">
+      <c r="Q8" s="71">
         <f>IF('AOP Critical'!R9="","",'AOP Critical'!R9)</f>
         <v>1</v>
       </c>
-      <c r="R8" s="72">
+      <c r="R8" s="71">
         <f>IF('AOP Critical'!S9="","",'AOP Critical'!S9)</f>
         <v>1</v>
       </c>
-      <c r="S8" s="72">
+      <c r="S8" s="71">
         <f>IF('AOP Critical'!T9="","",'AOP Critical'!T9)</f>
         <v>1</v>
       </c>
-      <c r="T8" s="72" t="str">
+      <c r="T8" s="71" t="str">
         <f>IF('AOP Critical'!U9="","",'AOP Critical'!U9)</f>
         <v/>
       </c>
-      <c r="U8" s="72" t="str">
+      <c r="U8" s="71" t="str">
         <f>IF('AOP Critical'!V9="","",'AOP Critical'!V9)</f>
         <v/>
       </c>
-      <c r="V8" s="72" t="str">
+      <c r="V8" s="71" t="str">
         <f>IF('AOP Critical'!W9="","",'AOP Critical'!W9)</f>
         <v/>
       </c>
@@ -5828,51 +5829,51 @@
         <f>IF('AOP Critical'!K41="","",'AOP Critical'!K41)</f>
         <v>T</v>
       </c>
-      <c r="K11" s="73">
+      <c r="K11" s="72">
         <f>IF('AOP Critical'!L41="","",'AOP Critical'!L41)</f>
         <v>1.9099999999999999E-2</v>
       </c>
-      <c r="L11" s="73">
+      <c r="L11" s="72">
         <f>IF('AOP Critical'!M41="","",'AOP Critical'!M41)</f>
         <v>4.07E-2</v>
       </c>
-      <c r="M11" s="73">
+      <c r="M11" s="72">
         <f>IF('AOP Critical'!N41="","",'AOP Critical'!N41)</f>
         <v>4.6199999999999998E-2</v>
       </c>
-      <c r="N11" s="73">
+      <c r="N11" s="72">
         <f>IF('AOP Critical'!O41="","",'AOP Critical'!O41)</f>
         <v>3.8600000000000002E-2</v>
       </c>
-      <c r="O11" s="73">
+      <c r="O11" s="72">
         <f>IF('AOP Critical'!P41="","",'AOP Critical'!P41)</f>
         <v>3.5299999999999998E-2</v>
       </c>
-      <c r="P11" s="73">
+      <c r="P11" s="72">
         <f>IF('AOP Critical'!Q41="","",'AOP Critical'!Q41)</f>
         <v>2.7099999999999999E-2</v>
       </c>
-      <c r="Q11" s="73">
+      <c r="Q11" s="72">
         <f>IF('AOP Critical'!R41="","",'AOP Critical'!R41)</f>
         <v>2.5100000000000001E-2</v>
       </c>
-      <c r="R11" s="73">
+      <c r="R11" s="72">
         <f>IF('AOP Critical'!S41="","",'AOP Critical'!S41)</f>
         <v>2.41E-2</v>
       </c>
-      <c r="S11" s="73">
+      <c r="S11" s="72">
         <f>IF('AOP Critical'!T41="","",'AOP Critical'!T41)</f>
         <v>3.1600000000000003E-2</v>
       </c>
-      <c r="T11" s="73">
+      <c r="T11" s="72">
         <f>IF('AOP Critical'!U41="","",'AOP Critical'!U41)</f>
         <v>3.1099999999999999E-2</v>
       </c>
-      <c r="U11" s="73">
+      <c r="U11" s="72">
         <f>IF('AOP Critical'!V41="","",'AOP Critical'!V41)</f>
         <v>3.5700000000000003E-2</v>
       </c>
-      <c r="V11" s="73">
+      <c r="V11" s="72">
         <f>IF('AOP Critical'!W41="","",'AOP Critical'!W41)</f>
         <v>3.32E-2</v>
       </c>
@@ -5914,51 +5915,51 @@
         <f>IF('AOP Critical'!K42="","",'AOP Critical'!K42)</f>
         <v>A</v>
       </c>
-      <c r="K12" s="73">
+      <c r="K12" s="72">
         <f>IF('AOP Critical'!L42="","",'AOP Critical'!L42)</f>
         <v>9.1999999999999998E-3</v>
       </c>
-      <c r="L12" s="73">
+      <c r="L12" s="72">
         <f>IF('AOP Critical'!M42="","",'AOP Critical'!M42)</f>
         <v>1.5800000000000002E-2</v>
       </c>
-      <c r="M12" s="73">
+      <c r="M12" s="72">
         <f>IF('AOP Critical'!N42="","",'AOP Critical'!N42)</f>
         <v>1.7600000000000001E-2</v>
       </c>
-      <c r="N12" s="73">
+      <c r="N12" s="72">
         <f>IF('AOP Critical'!O42="","",'AOP Critical'!O42)</f>
         <v>1.5800000000000002E-2</v>
       </c>
-      <c r="O12" s="73">
+      <c r="O12" s="72">
         <f>IF('AOP Critical'!P42="","",'AOP Critical'!P42)</f>
         <v>8.6E-3</v>
       </c>
-      <c r="P12" s="73">
+      <c r="P12" s="72">
         <f>IF('AOP Critical'!Q42="","",'AOP Critical'!Q42)</f>
         <v>1.2699999999999999E-2</v>
       </c>
-      <c r="Q12" s="73">
+      <c r="Q12" s="72">
         <f>IF('AOP Critical'!R42="","",'AOP Critical'!R42)</f>
         <v>1.3299999999999999E-2</v>
       </c>
-      <c r="R12" s="73">
+      <c r="R12" s="72">
         <f>IF('AOP Critical'!S42="","",'AOP Critical'!S42)</f>
         <v>1.3899999999999999E-2</v>
       </c>
-      <c r="S12" s="73">
+      <c r="S12" s="72">
         <f>IF('AOP Critical'!T42="","",'AOP Critical'!T42)</f>
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="T12" s="73" t="str">
+      <c r="T12" s="72" t="str">
         <f>IF('AOP Critical'!U42="","",'AOP Critical'!U42)</f>
         <v/>
       </c>
-      <c r="U12" s="73" t="str">
+      <c r="U12" s="72" t="str">
         <f>IF('AOP Critical'!V42="","",'AOP Critical'!V42)</f>
         <v/>
       </c>
-      <c r="V12" s="73" t="str">
+      <c r="V12" s="72" t="str">
         <f>IF('AOP Critical'!W42="","",'AOP Critical'!W42)</f>
         <v/>
       </c>
@@ -6077,51 +6078,51 @@
         <f>IF('AOP Critical'!K12="","",'AOP Critical'!K12)</f>
         <v>T</v>
       </c>
-      <c r="K15" s="71">
+      <c r="K15" s="70">
         <f>IF('AOP Critical'!L12="","",'AOP Critical'!L12)</f>
         <v>0.69</v>
       </c>
-      <c r="L15" s="71">
+      <c r="L15" s="70">
         <f>IF('AOP Critical'!M12="","",'AOP Critical'!M12)</f>
         <v>0.69</v>
       </c>
-      <c r="M15" s="71">
+      <c r="M15" s="70">
         <f>IF('AOP Critical'!N12="","",'AOP Critical'!N12)</f>
         <v>0.69</v>
       </c>
-      <c r="N15" s="71">
+      <c r="N15" s="70">
         <f>IF('AOP Critical'!O12="","",'AOP Critical'!O12)</f>
         <v>0.72</v>
       </c>
-      <c r="O15" s="71">
+      <c r="O15" s="70">
         <f>IF('AOP Critical'!P12="","",'AOP Critical'!P12)</f>
         <v>0.72</v>
       </c>
-      <c r="P15" s="71">
+      <c r="P15" s="70">
         <f>IF('AOP Critical'!Q12="","",'AOP Critical'!Q12)</f>
         <v>0.72</v>
       </c>
-      <c r="Q15" s="71">
+      <c r="Q15" s="70">
         <f>IF('AOP Critical'!R12="","",'AOP Critical'!R12)</f>
         <v>0.74</v>
       </c>
-      <c r="R15" s="71">
+      <c r="R15" s="70">
         <f>IF('AOP Critical'!S12="","",'AOP Critical'!S12)</f>
         <v>0.74</v>
       </c>
-      <c r="S15" s="71">
+      <c r="S15" s="70">
         <f>IF('AOP Critical'!T12="","",'AOP Critical'!T12)</f>
         <v>0.74</v>
       </c>
-      <c r="T15" s="71">
+      <c r="T15" s="70">
         <f>IF('AOP Critical'!U12="","",'AOP Critical'!U12)</f>
         <v>0.79</v>
       </c>
-      <c r="U15" s="71">
+      <c r="U15" s="70">
         <f>IF('AOP Critical'!V12="","",'AOP Critical'!V12)</f>
         <v>0.79</v>
       </c>
-      <c r="V15" s="71">
+      <c r="V15" s="70">
         <f>IF('AOP Critical'!W12="","",'AOP Critical'!W12)</f>
         <v>0.79</v>
       </c>
@@ -6167,51 +6168,51 @@
         <f>IF('AOP Critical'!K13="","",'AOP Critical'!K13)</f>
         <v>A</v>
       </c>
-      <c r="K16" s="71">
+      <c r="K16" s="70">
         <f>IF('AOP Critical'!L13="","",'AOP Critical'!L13)</f>
         <v>0.83</v>
       </c>
-      <c r="L16" s="71">
+      <c r="L16" s="70">
         <f>IF('AOP Critical'!M13="","",'AOP Critical'!M13)</f>
         <v>0.82</v>
       </c>
-      <c r="M16" s="71">
+      <c r="M16" s="70">
         <f>IF('AOP Critical'!N13="","",'AOP Critical'!N13)</f>
         <v>0.81</v>
       </c>
-      <c r="N16" s="71">
+      <c r="N16" s="70">
         <f>IF('AOP Critical'!O13="","",'AOP Critical'!O13)</f>
         <v>0.6</v>
       </c>
-      <c r="O16" s="71">
+      <c r="O16" s="70">
         <f>IF('AOP Critical'!P13="","",'AOP Critical'!P13)</f>
         <v>0.87</v>
       </c>
-      <c r="P16" s="71">
+      <c r="P16" s="70">
         <f>IF('AOP Critical'!Q13="","",'AOP Critical'!Q13)</f>
         <v>0.77</v>
       </c>
-      <c r="Q16" s="71">
+      <c r="Q16" s="70">
         <f>IF('AOP Critical'!R13="","",'AOP Critical'!R13)</f>
         <v>0.75</v>
       </c>
-      <c r="R16" s="71">
+      <c r="R16" s="70">
         <f>IF('AOP Critical'!S13="","",'AOP Critical'!S13)</f>
         <v>0.81</v>
       </c>
-      <c r="S16" s="71" t="str">
+      <c r="S16" s="70">
         <f>IF('AOP Critical'!T13="","",'AOP Critical'!T13)</f>
-        <v/>
-      </c>
-      <c r="T16" s="71" t="str">
+        <v>0.89</v>
+      </c>
+      <c r="T16" s="70" t="str">
         <f>IF('AOP Critical'!U13="","",'AOP Critical'!U13)</f>
         <v/>
       </c>
-      <c r="U16" s="71" t="str">
+      <c r="U16" s="70" t="str">
         <f>IF('AOP Critical'!V13="","",'AOP Critical'!V13)</f>
         <v/>
       </c>
-      <c r="V16" s="71" t="str">
+      <c r="V16" s="70" t="str">
         <f>IF('AOP Critical'!W13="","",'AOP Critical'!W13)</f>
         <v/>
       </c>
@@ -6257,51 +6258,51 @@
         <f>IF('AOP Critical'!K14="","",'AOP Critical'!K14)</f>
         <v>T</v>
       </c>
-      <c r="K17" s="72">
+      <c r="K17" s="71">
         <f>IF('AOP Critical'!L14="","",'AOP Critical'!L14)</f>
         <v>0.54249999999999998</v>
       </c>
-      <c r="L17" s="72">
+      <c r="L17" s="71">
         <f>IF('AOP Critical'!M14="","",'AOP Critical'!M14)</f>
         <v>0.54399999999999993</v>
       </c>
-      <c r="M17" s="72">
+      <c r="M17" s="71">
         <f>IF('AOP Critical'!N14="","",'AOP Critical'!N14)</f>
         <v>0.54549999999999987</v>
       </c>
-      <c r="N17" s="72">
+      <c r="N17" s="71">
         <f>IF('AOP Critical'!O14="","",'AOP Critical'!O14)</f>
         <v>0.54699999999999982</v>
       </c>
-      <c r="O17" s="72">
+      <c r="O17" s="71">
         <f>IF('AOP Critical'!P14="","",'AOP Critical'!P14)</f>
         <v>0.54849999999999977</v>
       </c>
-      <c r="P17" s="72">
+      <c r="P17" s="71">
         <f>IF('AOP Critical'!Q14="","",'AOP Critical'!Q14)</f>
         <v>0.54999999999999971</v>
       </c>
-      <c r="Q17" s="72">
+      <c r="Q17" s="71">
         <f>IF('AOP Critical'!R14="","",'AOP Critical'!R14)</f>
         <v>0.55149999999999966</v>
       </c>
-      <c r="R17" s="72">
+      <c r="R17" s="71">
         <f>IF('AOP Critical'!S14="","",'AOP Critical'!S14)</f>
         <v>0.54510000000000003</v>
       </c>
-      <c r="S17" s="72">
+      <c r="S17" s="71">
         <f>IF('AOP Critical'!T14="","",'AOP Critical'!T14)</f>
         <v>0.54610000000000003</v>
       </c>
-      <c r="T17" s="72" t="str">
+      <c r="T17" s="71" t="str">
         <f>IF('AOP Critical'!U14="","",'AOP Critical'!U14)</f>
         <v/>
       </c>
-      <c r="U17" s="72" t="str">
+      <c r="U17" s="71" t="str">
         <f>IF('AOP Critical'!V14="","",'AOP Critical'!V14)</f>
         <v/>
       </c>
-      <c r="V17" s="72" t="str">
+      <c r="V17" s="71" t="str">
         <f>IF('AOP Critical'!W14="","",'AOP Critical'!W14)</f>
         <v/>
       </c>
@@ -6347,51 +6348,51 @@
         <f>IF('AOP Critical'!K15="","",'AOP Critical'!K15)</f>
         <v>A</v>
       </c>
-      <c r="K18" s="72">
+      <c r="K18" s="71">
         <f>IF('AOP Critical'!L15="","",'AOP Critical'!L15)</f>
         <v>0.51780000000000004</v>
       </c>
-      <c r="L18" s="72">
+      <c r="L18" s="71">
         <f>IF('AOP Critical'!M15="","",'AOP Critical'!M15)</f>
         <v>0.54100000000000004</v>
       </c>
-      <c r="M18" s="72">
+      <c r="M18" s="71">
         <f>IF('AOP Critical'!N15="","",'AOP Critical'!N15)</f>
         <v>0.54100000000000004</v>
       </c>
-      <c r="N18" s="72">
+      <c r="N18" s="71">
         <f>IF('AOP Critical'!O15="","",'AOP Critical'!O15)</f>
         <v>0.53969999999999996</v>
       </c>
-      <c r="O18" s="72">
+      <c r="O18" s="71">
         <f>IF('AOP Critical'!P15="","",'AOP Critical'!P15)</f>
         <v>0.54100000000000004</v>
       </c>
-      <c r="P18" s="72">
+      <c r="P18" s="71">
         <f>IF('AOP Critical'!Q15="","",'AOP Critical'!Q15)</f>
         <v>0.53800000000000003</v>
       </c>
-      <c r="Q18" s="72">
+      <c r="Q18" s="71">
         <f>IF('AOP Critical'!R15="","",'AOP Critical'!R15)</f>
         <v>0.53600000000000003</v>
       </c>
-      <c r="R18" s="72">
+      <c r="R18" s="71">
         <f>IF('AOP Critical'!S15="","",'AOP Critical'!S15)</f>
         <v>0.5363</v>
       </c>
-      <c r="S18" s="72">
+      <c r="S18" s="71">
         <f>IF('AOP Critical'!T15="","",'AOP Critical'!T15)</f>
         <v>0.53749999999999998</v>
       </c>
-      <c r="T18" s="72" t="str">
+      <c r="T18" s="71" t="str">
         <f>IF('AOP Critical'!U15="","",'AOP Critical'!U15)</f>
         <v/>
       </c>
-      <c r="U18" s="72" t="str">
+      <c r="U18" s="71" t="str">
         <f>IF('AOP Critical'!V15="","",'AOP Critical'!V15)</f>
         <v/>
       </c>
-      <c r="V18" s="72" t="str">
+      <c r="V18" s="71" t="str">
         <f>IF('AOP Critical'!W15="","",'AOP Critical'!W15)</f>
         <v/>
       </c>
@@ -6437,51 +6438,51 @@
         <f>IF('AOP Critical'!K49="","",'AOP Critical'!K49)</f>
         <v>T</v>
       </c>
-      <c r="K19" s="73">
+      <c r="K19" s="72">
         <f>IF('AOP Critical'!L49="","",'AOP Critical'!L49)</f>
         <v>0.73199999999999998</v>
       </c>
-      <c r="L19" s="73">
+      <c r="L19" s="72">
         <f>IF('AOP Critical'!M49="","",'AOP Critical'!M49)</f>
         <v>0.72749999999999992</v>
       </c>
-      <c r="M19" s="73">
+      <c r="M19" s="72">
         <f>IF('AOP Critical'!N49="","",'AOP Critical'!N49)</f>
         <v>0.7287499999999999</v>
       </c>
-      <c r="N19" s="73">
+      <c r="N19" s="72">
         <f>IF('AOP Critical'!O49="","",'AOP Critical'!O49)</f>
         <v>0.72999999999999987</v>
       </c>
-      <c r="O19" s="73">
+      <c r="O19" s="72">
         <f>IF('AOP Critical'!P49="","",'AOP Critical'!P49)</f>
         <v>0.73124999999999984</v>
       </c>
-      <c r="P19" s="73">
+      <c r="P19" s="72">
         <f>IF('AOP Critical'!Q49="","",'AOP Critical'!Q49)</f>
         <v>0.73249999999999982</v>
       </c>
-      <c r="Q19" s="73">
+      <c r="Q19" s="72">
         <f>IF('AOP Critical'!R49="","",'AOP Critical'!R49)</f>
         <v>0.73374999999999979</v>
       </c>
-      <c r="R19" s="73">
+      <c r="R19" s="72">
         <f>IF('AOP Critical'!S49="","",'AOP Critical'!S49)</f>
         <v>0.73499999999999976</v>
       </c>
-      <c r="S19" s="73">
+      <c r="S19" s="72">
         <f>IF('AOP Critical'!T49="","",'AOP Critical'!T49)</f>
         <v>0.73624999999999974</v>
       </c>
-      <c r="T19" s="73">
+      <c r="T19" s="72">
         <f>IF('AOP Critical'!U49="","",'AOP Critical'!U49)</f>
         <v>0.73749999999999971</v>
       </c>
-      <c r="U19" s="73">
+      <c r="U19" s="72">
         <f>IF('AOP Critical'!V49="","",'AOP Critical'!V49)</f>
         <v>0.73874999999999968</v>
       </c>
-      <c r="V19" s="73">
+      <c r="V19" s="72">
         <f>IF('AOP Critical'!W49="","",'AOP Critical'!W49)</f>
         <v>0.73999999999999966</v>
       </c>
@@ -6527,51 +6528,51 @@
         <f>IF('AOP Critical'!K50="","",'AOP Critical'!K50)</f>
         <v>A</v>
       </c>
-      <c r="K20" s="73">
+      <c r="K20" s="72">
         <f>IF('AOP Critical'!L50="","",'AOP Critical'!L50)</f>
         <v>0.69299999999999995</v>
       </c>
-      <c r="L20" s="73">
+      <c r="L20" s="72">
         <f>IF('AOP Critical'!M50="","",'AOP Critical'!M50)</f>
         <v>0.71099999999999997</v>
       </c>
-      <c r="M20" s="73">
+      <c r="M20" s="72">
         <f>IF('AOP Critical'!N50="","",'AOP Critical'!N50)</f>
         <v>0.72499999999999998</v>
       </c>
-      <c r="N20" s="73">
+      <c r="N20" s="72">
         <f>IF('AOP Critical'!O50="","",'AOP Critical'!O50)</f>
         <v>0.72299999999999998</v>
       </c>
-      <c r="O20" s="73">
+      <c r="O20" s="72">
         <f>IF('AOP Critical'!P50="","",'AOP Critical'!P50)</f>
         <v>0.73599999999999999</v>
       </c>
-      <c r="P20" s="73">
+      <c r="P20" s="72">
         <f>IF('AOP Critical'!Q50="","",'AOP Critical'!Q50)</f>
         <v>0.74150000000000005</v>
       </c>
-      <c r="Q20" s="73">
+      <c r="Q20" s="72">
         <f>IF('AOP Critical'!R50="","",'AOP Critical'!R50)</f>
         <v>0.74099999999999999</v>
       </c>
-      <c r="R20" s="73">
+      <c r="R20" s="72">
         <f>IF('AOP Critical'!S50="","",'AOP Critical'!S50)</f>
         <v>0.74450000000000005</v>
       </c>
-      <c r="S20" s="73">
+      <c r="S20" s="72">
         <f>IF('AOP Critical'!T50="","",'AOP Critical'!T50)</f>
         <v>0.74770000000000003</v>
       </c>
-      <c r="T20" s="73" t="str">
+      <c r="T20" s="72" t="str">
         <f>IF('AOP Critical'!U50="","",'AOP Critical'!U50)</f>
         <v/>
       </c>
-      <c r="U20" s="73" t="str">
+      <c r="U20" s="72" t="str">
         <f>IF('AOP Critical'!V50="","",'AOP Critical'!V50)</f>
         <v/>
       </c>
-      <c r="V20" s="73" t="str">
+      <c r="V20" s="72" t="str">
         <f>IF('AOP Critical'!W50="","",'AOP Critical'!W50)</f>
         <v/>
       </c>
@@ -6690,51 +6691,51 @@
         <f>IF('AOP Critical'!K16="","",'AOP Critical'!K16)</f>
         <v>T</v>
       </c>
-      <c r="K23" s="72">
+      <c r="K23" s="71">
         <f>IF('AOP Critical'!L16="","",'AOP Critical'!L16)</f>
         <v>0.11774014693384624</v>
       </c>
-      <c r="L23" s="72">
+      <c r="L23" s="71">
         <f>IF('AOP Critical'!M16="","",'AOP Critical'!M16)</f>
         <v>7.6823633140503819E-2</v>
       </c>
-      <c r="M23" s="72">
+      <c r="M23" s="71">
         <f>IF('AOP Critical'!N16="","",'AOP Critical'!N16)</f>
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="N23" s="72">
+      <c r="N23" s="71">
         <f>IF('AOP Critical'!O16="","",'AOP Critical'!O16)</f>
         <v>9.9962463776604421E-2</v>
       </c>
-      <c r="O23" s="72">
+      <c r="O23" s="71">
         <f>IF('AOP Critical'!P16="","",'AOP Critical'!P16)</f>
         <v>0.1038498729590533</v>
       </c>
-      <c r="P23" s="72">
+      <c r="P23" s="71">
         <f>IF('AOP Critical'!Q16="","",'AOP Critical'!Q16)</f>
         <v>0.11814554963094943</v>
       </c>
-      <c r="Q23" s="72">
+      <c r="Q23" s="71">
         <f>IF('AOP Critical'!R16="","",'AOP Critical'!R16)</f>
         <v>0.13344842106998206</v>
       </c>
-      <c r="R23" s="72">
+      <c r="R23" s="71">
         <f>IF('AOP Critical'!S16="","",'AOP Critical'!S16)</f>
         <v>0.13972119594175969</v>
       </c>
-      <c r="S23" s="72" t="str">
+      <c r="S23" s="71">
         <f>IF('AOP Critical'!T16="","",'AOP Critical'!T16)</f>
-        <v/>
-      </c>
-      <c r="T23" s="72" t="str">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="T23" s="71" t="str">
         <f>IF('AOP Critical'!U16="","",'AOP Critical'!U16)</f>
         <v/>
       </c>
-      <c r="U23" s="72" t="str">
+      <c r="U23" s="71" t="str">
         <f>IF('AOP Critical'!V16="","",'AOP Critical'!V16)</f>
         <v/>
       </c>
-      <c r="V23" s="72" t="str">
+      <c r="V23" s="71" t="str">
         <f>IF('AOP Critical'!W16="","",'AOP Critical'!W16)</f>
         <v/>
       </c>
@@ -6780,51 +6781,51 @@
         <f>IF('AOP Critical'!K17="","",'AOP Critical'!K17)</f>
         <v>A</v>
       </c>
-      <c r="K24" s="72">
+      <c r="K24" s="71">
         <f>IF('AOP Critical'!L17="","",'AOP Critical'!L17)</f>
         <v>-4.253311543933095E-2</v>
       </c>
-      <c r="L24" s="72">
+      <c r="L24" s="71">
         <f>IF('AOP Critical'!M17="","",'AOP Critical'!M17)</f>
         <v>7.8013174622509063E-2</v>
       </c>
-      <c r="M24" s="72">
+      <c r="M24" s="71">
         <f>IF('AOP Critical'!N17="","",'AOP Critical'!N17)</f>
         <v>0.14699999999999999</v>
       </c>
-      <c r="N24" s="72">
+      <c r="N24" s="71">
         <f>IF('AOP Critical'!O17="","",'AOP Critical'!O17)</f>
         <v>0.13678322320362704</v>
       </c>
-      <c r="O24" s="72">
+      <c r="O24" s="71">
         <f>IF('AOP Critical'!P17="","",'AOP Critical'!P17)</f>
         <v>0.14558303908159406</v>
       </c>
-      <c r="P24" s="72">
+      <c r="P24" s="71">
         <f>IF('AOP Critical'!Q17="","",'AOP Critical'!Q17)</f>
         <v>0.12590494186157489</v>
       </c>
-      <c r="Q24" s="72">
+      <c r="Q24" s="71">
         <f>IF('AOP Critical'!R17="","",'AOP Critical'!R17)</f>
         <v>0.10712720377087674</v>
       </c>
-      <c r="R24" s="72">
+      <c r="R24" s="71">
         <f>IF('AOP Critical'!S17="","",'AOP Critical'!S17)</f>
         <v>0.12649723977955013</v>
       </c>
-      <c r="S24" s="72" t="str">
+      <c r="S24" s="71">
         <f>IF('AOP Critical'!T17="","",'AOP Critical'!T17)</f>
-        <v/>
-      </c>
-      <c r="T24" s="72" t="str">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="T24" s="71" t="str">
         <f>IF('AOP Critical'!U17="","",'AOP Critical'!U17)</f>
         <v/>
       </c>
-      <c r="U24" s="72" t="str">
+      <c r="U24" s="71" t="str">
         <f>IF('AOP Critical'!V17="","",'AOP Critical'!V17)</f>
         <v/>
       </c>
-      <c r="V24" s="72" t="str">
+      <c r="V24" s="71" t="str">
         <f>IF('AOP Critical'!W17="","",'AOP Critical'!W17)</f>
         <v/>
       </c>
@@ -6870,51 +6871,51 @@
         <f>IF('AOP Critical'!K18="","",'AOP Critical'!K18)</f>
         <v>T</v>
       </c>
-      <c r="K25" s="75">
+      <c r="K25" s="74">
         <f>IF('AOP Critical'!L18="","",'AOP Critical'!L18)</f>
-        <v>0.254</v>
-      </c>
-      <c r="L25" s="75">
+        <v>0.224</v>
+      </c>
+      <c r="L25" s="74">
         <f>IF('AOP Critical'!M18="","",'AOP Critical'!M18)</f>
-        <v>0.44800000000000001</v>
-      </c>
-      <c r="M25" s="75">
+        <v>0.35800000000000004</v>
+      </c>
+      <c r="M25" s="74">
         <f>IF('AOP Critical'!N18="","",'AOP Critical'!N18)</f>
-        <v>0.96700000000000008</v>
-      </c>
-      <c r="N25" s="75">
+        <v>0.79700000000000004</v>
+      </c>
+      <c r="N25" s="74">
         <f>IF('AOP Critical'!O18="","",'AOP Critical'!O18)</f>
-        <v>1.331</v>
-      </c>
-      <c r="O25" s="75">
+        <v>1.0409999999999999</v>
+      </c>
+      <c r="O25" s="74">
         <f>IF('AOP Critical'!P18="","",'AOP Critical'!P18)</f>
-        <v>1.595</v>
-      </c>
-      <c r="P25" s="75">
+        <v>1.155</v>
+      </c>
+      <c r="P25" s="74">
         <f>IF('AOP Critical'!Q18="","",'AOP Critical'!Q18)</f>
-        <v>2.1840000000000002</v>
-      </c>
-      <c r="Q25" s="75">
+        <v>1.6040000000000001</v>
+      </c>
+      <c r="Q25" s="74">
         <f>IF('AOP Critical'!R18="","",'AOP Critical'!R18)</f>
-        <v>3.0979999999999999</v>
-      </c>
-      <c r="R25" s="75">
+        <v>2.4180000000000001</v>
+      </c>
+      <c r="R25" s="74">
         <f>IF('AOP Critical'!S18="","",'AOP Critical'!S18)</f>
-        <v>3.7</v>
-      </c>
-      <c r="S25" s="75">
+        <v>2.93</v>
+      </c>
+      <c r="S25" s="74">
         <f>IF('AOP Critical'!T18="","",'AOP Critical'!T18)</f>
-        <v>4.5439999999999996</v>
-      </c>
-      <c r="T25" s="75" t="str">
+        <v>3.7040000000000002</v>
+      </c>
+      <c r="T25" s="74" t="str">
         <f>IF('AOP Critical'!U18="","",'AOP Critical'!U18)</f>
         <v/>
       </c>
-      <c r="U25" s="75" t="str">
+      <c r="U25" s="74" t="str">
         <f>IF('AOP Critical'!V18="","",'AOP Critical'!V18)</f>
         <v/>
       </c>
-      <c r="V25" s="75" t="str">
+      <c r="V25" s="74" t="str">
         <f>IF('AOP Critical'!W18="","",'AOP Critical'!W18)</f>
         <v/>
       </c>
@@ -6960,51 +6961,51 @@
         <f>IF('AOP Critical'!K19="","",'AOP Critical'!K19)</f>
         <v>A</v>
       </c>
-      <c r="K26" s="75">
+      <c r="K26" s="74">
         <f>IF('AOP Critical'!L19="","",'AOP Critical'!L19)</f>
-        <v>0.28899999999999998</v>
-      </c>
-      <c r="L26" s="75">
+        <v>0.2598381666666667</v>
+      </c>
+      <c r="L26" s="74">
         <f>IF('AOP Critical'!M19="","",'AOP Critical'!M19)</f>
-        <v>0.46800000000000003</v>
-      </c>
-      <c r="M26" s="75">
+        <v>0.3838381666666667</v>
+      </c>
+      <c r="M26" s="74">
         <f>IF('AOP Critical'!N19="","",'AOP Critical'!N19)</f>
-        <v>1.2749999999999999</v>
-      </c>
-      <c r="N26" s="75">
+        <v>1.1128381666666667</v>
+      </c>
+      <c r="N26" s="74">
         <f>IF('AOP Critical'!O19="","",'AOP Critical'!O19)</f>
-        <v>1.5509999999999999</v>
-      </c>
-      <c r="O26" s="75">
+        <v>1.3223861666666668</v>
+      </c>
+      <c r="O26" s="74">
         <f>IF('AOP Critical'!P19="","",'AOP Critical'!P19)</f>
-        <v>1.9910000000000001</v>
-      </c>
-      <c r="P26" s="75">
+        <v>1.6513861666666667</v>
+      </c>
+      <c r="P26" s="74">
         <f>IF('AOP Critical'!Q19="","",'AOP Critical'!Q19)</f>
-        <v>2.5489999999999999</v>
-      </c>
-      <c r="Q26" s="75">
+        <v>2.1303861666666668</v>
+      </c>
+      <c r="Q26" s="74">
         <f>IF('AOP Critical'!R19="","",'AOP Critical'!R19)</f>
-        <v>3.0990000000000002</v>
-      </c>
-      <c r="R26" s="75">
+        <v>2.6433861666666667</v>
+      </c>
+      <c r="R26" s="74">
         <f>IF('AOP Critical'!S19="","",'AOP Critical'!S19)</f>
-        <v>3.895</v>
-      </c>
-      <c r="S26" s="75">
+        <v>3.3972231666666666</v>
+      </c>
+      <c r="S26" s="74">
         <f>IF('AOP Critical'!T19="","",'AOP Critical'!T19)</f>
-        <v>5.0119999999999996</v>
-      </c>
-      <c r="T26" s="75" t="str">
+        <v>4.5205241666666662</v>
+      </c>
+      <c r="T26" s="74" t="str">
         <f>IF('AOP Critical'!U19="","",'AOP Critical'!U19)</f>
         <v/>
       </c>
-      <c r="U26" s="75" t="str">
+      <c r="U26" s="74" t="str">
         <f>IF('AOP Critical'!V19="","",'AOP Critical'!V19)</f>
         <v/>
       </c>
-      <c r="V26" s="75" t="str">
+      <c r="V26" s="74" t="str">
         <f>IF('AOP Critical'!W19="","",'AOP Critical'!W19)</f>
         <v/>
       </c>
@@ -7050,51 +7051,51 @@
         <f>IF('AOP Critical'!K20="","",'AOP Critical'!K20)</f>
         <v>T</v>
       </c>
-      <c r="K27" s="71">
+      <c r="K27" s="70">
         <f>IF('AOP Critical'!L20="","",'AOP Critical'!L20)</f>
         <v>0.28399999999999997</v>
       </c>
-      <c r="L27" s="71">
+      <c r="L27" s="70">
         <f>IF('AOP Critical'!M20="","",'AOP Critical'!M20)</f>
         <v>0.28260000000000002</v>
       </c>
-      <c r="M27" s="71">
+      <c r="M27" s="70">
         <f>IF('AOP Critical'!N20="","",'AOP Critical'!N20)</f>
         <v>0.28999999999999998</v>
       </c>
-      <c r="N27" s="71">
+      <c r="N27" s="70">
         <f>IF('AOP Critical'!O20="","",'AOP Critical'!O20)</f>
         <v>0.28999999999999998</v>
       </c>
-      <c r="O27" s="71">
+      <c r="O27" s="70">
         <f>IF('AOP Critical'!P20="","",'AOP Critical'!P20)</f>
         <v>0.27</v>
       </c>
-      <c r="P27" s="71">
+      <c r="P27" s="70">
         <f>IF('AOP Critical'!Q20="","",'AOP Critical'!Q20)</f>
         <v>0.26</v>
       </c>
-      <c r="Q27" s="71">
+      <c r="Q27" s="70">
         <f>IF('AOP Critical'!R20="","",'AOP Critical'!R20)</f>
         <v>0.24</v>
       </c>
-      <c r="R27" s="71">
+      <c r="R27" s="70">
         <f>IF('AOP Critical'!S20="","",'AOP Critical'!S20)</f>
         <v>0.23</v>
       </c>
-      <c r="S27" s="71" t="str">
+      <c r="S27" s="70">
         <f>IF('AOP Critical'!T20="","",'AOP Critical'!T20)</f>
-        <v/>
-      </c>
-      <c r="T27" s="71" t="str">
+        <v>0.25</v>
+      </c>
+      <c r="T27" s="70" t="str">
         <f>IF('AOP Critical'!U20="","",'AOP Critical'!U20)</f>
         <v/>
       </c>
-      <c r="U27" s="71" t="str">
+      <c r="U27" s="70" t="str">
         <f>IF('AOP Critical'!V20="","",'AOP Critical'!V20)</f>
         <v/>
       </c>
-      <c r="V27" s="71" t="str">
+      <c r="V27" s="70" t="str">
         <f>IF('AOP Critical'!W20="","",'AOP Critical'!W20)</f>
         <v/>
       </c>
@@ -7140,51 +7141,51 @@
         <f>IF('AOP Critical'!K21="","",'AOP Critical'!K21)</f>
         <v>A</v>
       </c>
-      <c r="K28" s="71">
+      <c r="K28" s="70">
         <f>IF('AOP Critical'!L21="","",'AOP Critical'!L21)</f>
         <v>0.27400000000000002</v>
       </c>
-      <c r="L28" s="71">
+      <c r="L28" s="70">
         <f>IF('AOP Critical'!M21="","",'AOP Critical'!M21)</f>
         <v>0.29899999999999999</v>
       </c>
-      <c r="M28" s="71">
+      <c r="M28" s="70">
         <f>IF('AOP Critical'!N21="","",'AOP Critical'!N21)</f>
         <v>0.28999999999999998</v>
       </c>
-      <c r="N28" s="71">
+      <c r="N28" s="70">
         <f>IF('AOP Critical'!O21="","",'AOP Critical'!O21)</f>
         <v>0.3</v>
       </c>
-      <c r="O28" s="71">
+      <c r="O28" s="70">
         <f>IF('AOP Critical'!P21="","",'AOP Critical'!P21)</f>
         <v>0.31</v>
       </c>
-      <c r="P28" s="71">
+      <c r="P28" s="70">
         <f>IF('AOP Critical'!Q21="","",'AOP Critical'!Q21)</f>
         <v>0.28999999999999998</v>
       </c>
-      <c r="Q28" s="71">
+      <c r="Q28" s="70">
         <f>IF('AOP Critical'!R21="","",'AOP Critical'!R21)</f>
         <v>0.3</v>
       </c>
-      <c r="R28" s="71">
+      <c r="R28" s="70">
         <f>IF('AOP Critical'!S21="","",'AOP Critical'!S21)</f>
         <v>0.3</v>
       </c>
-      <c r="S28" s="71" t="str">
+      <c r="S28" s="70">
         <f>IF('AOP Critical'!T21="","",'AOP Critical'!T21)</f>
-        <v/>
-      </c>
-      <c r="T28" s="71" t="str">
+        <v>0.27</v>
+      </c>
+      <c r="T28" s="70" t="str">
         <f>IF('AOP Critical'!U21="","",'AOP Critical'!U21)</f>
         <v/>
       </c>
-      <c r="U28" s="71" t="str">
+      <c r="U28" s="70" t="str">
         <f>IF('AOP Critical'!V21="","",'AOP Critical'!V21)</f>
         <v/>
       </c>
-      <c r="V28" s="71" t="str">
+      <c r="V28" s="70" t="str">
         <f>IF('AOP Critical'!W21="","",'AOP Critical'!W21)</f>
         <v/>
       </c>
@@ -7230,51 +7231,51 @@
         <f>IF('AOP Critical'!K51="","",'AOP Critical'!K51)</f>
         <v>T</v>
       </c>
-      <c r="K29" s="72">
+      <c r="K29" s="71">
         <f>IF('AOP Critical'!L51="","",'AOP Critical'!L51)</f>
         <v>0.34700072985878605</v>
       </c>
-      <c r="L29" s="72">
+      <c r="L29" s="71">
         <f>IF('AOP Critical'!M51="","",'AOP Critical'!M51)</f>
         <v>0.32854527661902383</v>
       </c>
-      <c r="M29" s="72">
+      <c r="M29" s="71">
         <f>IF('AOP Critical'!N51="","",'AOP Critical'!N51)</f>
         <v>0.30191652751587683</v>
       </c>
-      <c r="N29" s="72">
+      <c r="N29" s="71">
         <f>IF('AOP Critical'!O51="","",'AOP Critical'!O51)</f>
         <v>0.32233175889748933</v>
       </c>
-      <c r="O29" s="72">
+      <c r="O29" s="71">
         <f>IF('AOP Critical'!P51="","",'AOP Critical'!P51)</f>
         <v>0.32732965712929335</v>
       </c>
-      <c r="P29" s="72">
+      <c r="P29" s="71">
         <f>IF('AOP Critical'!Q51="","",'AOP Critical'!Q51)</f>
         <v>0.31564073493651035</v>
       </c>
-      <c r="Q29" s="72">
+      <c r="Q29" s="71">
         <f>IF('AOP Critical'!R51="","",'AOP Critical'!R51)</f>
         <v>0.33096935042775388</v>
       </c>
-      <c r="R29" s="72">
+      <c r="R29" s="71">
         <f>IF('AOP Critical'!S51="","",'AOP Critical'!S51)</f>
         <v>0.33943248102419393</v>
       </c>
-      <c r="S29" s="72" t="str">
+      <c r="S29" s="71">
         <f>IF('AOP Critical'!T51="","",'AOP Critical'!T51)</f>
-        <v/>
-      </c>
-      <c r="T29" s="72" t="str">
+        <v>0.33082830926903184</v>
+      </c>
+      <c r="T29" s="71" t="str">
         <f>IF('AOP Critical'!U51="","",'AOP Critical'!U51)</f>
         <v/>
       </c>
-      <c r="U29" s="72" t="str">
+      <c r="U29" s="71" t="str">
         <f>IF('AOP Critical'!V51="","",'AOP Critical'!V51)</f>
         <v/>
       </c>
-      <c r="V29" s="72" t="str">
+      <c r="V29" s="71" t="str">
         <f>IF('AOP Critical'!W51="","",'AOP Critical'!W51)</f>
         <v/>
       </c>
@@ -7320,51 +7321,51 @@
         <f>IF('AOP Critical'!K52="","",'AOP Critical'!K52)</f>
         <v>A</v>
       </c>
-      <c r="K30" s="72">
+      <c r="K30" s="71">
         <f>IF('AOP Critical'!L52="","",'AOP Critical'!L52)</f>
         <v>0.36591770011686803</v>
       </c>
-      <c r="L30" s="72">
+      <c r="L30" s="71">
         <f>IF('AOP Critical'!M52="","",'AOP Critical'!M52)</f>
         <v>0.43346514302305739</v>
       </c>
-      <c r="M30" s="72">
+      <c r="M30" s="71">
         <f>IF('AOP Critical'!N52="","",'AOP Critical'!N52)</f>
         <v>0.41319844449711768</v>
       </c>
-      <c r="N30" s="72">
+      <c r="N30" s="71">
         <f>IF('AOP Critical'!O52="","",'AOP Critical'!O52)</f>
         <v>0.41195005974326776</v>
       </c>
-      <c r="O30" s="72">
+      <c r="O30" s="71">
         <f>IF('AOP Critical'!P52="","",'AOP Critical'!P52)</f>
         <v>0.40747704161607318</v>
       </c>
-      <c r="P30" s="72">
+      <c r="P30" s="71">
         <f>IF('AOP Critical'!Q52="","",'AOP Critical'!Q52)</f>
         <v>0.36849551470072495</v>
       </c>
-      <c r="Q30" s="72">
+      <c r="Q30" s="71">
         <f>IF('AOP Critical'!R52="","",'AOP Critical'!R52)</f>
         <v>0.35573521911109235</v>
       </c>
-      <c r="R30" s="72">
+      <c r="R30" s="71">
         <f>IF('AOP Critical'!S52="","",'AOP Critical'!S52)</f>
         <v>0.36691053201149237</v>
       </c>
-      <c r="S30" s="72" t="str">
+      <c r="S30" s="71">
         <f>IF('AOP Critical'!T52="","",'AOP Critical'!T52)</f>
-        <v/>
-      </c>
-      <c r="T30" s="72" t="str">
+        <v>0.36899999999999999</v>
+      </c>
+      <c r="T30" s="71" t="str">
         <f>IF('AOP Critical'!U52="","",'AOP Critical'!U52)</f>
         <v/>
       </c>
-      <c r="U30" s="72" t="str">
+      <c r="U30" s="71" t="str">
         <f>IF('AOP Critical'!V52="","",'AOP Critical'!V52)</f>
         <v/>
       </c>
-      <c r="V30" s="72" t="str">
+      <c r="V30" s="71" t="str">
         <f>IF('AOP Critical'!W52="","",'AOP Critical'!W52)</f>
         <v/>
       </c>
@@ -7483,51 +7484,51 @@
         <f>IF('AOP Critical'!K26="","",'AOP Critical'!K26)</f>
         <v>T</v>
       </c>
-      <c r="K33" s="71">
+      <c r="K33" s="70">
         <f>IF('AOP Critical'!L26="","",'AOP Critical'!L26)</f>
         <v>0.34</v>
       </c>
-      <c r="L33" s="71">
+      <c r="L33" s="70">
         <f>IF('AOP Critical'!M26="","",'AOP Critical'!M26)</f>
         <v>0.34</v>
       </c>
-      <c r="M33" s="71">
+      <c r="M33" s="70">
         <f>IF('AOP Critical'!N26="","",'AOP Critical'!N26)</f>
         <v>0.34</v>
       </c>
-      <c r="N33" s="71">
+      <c r="N33" s="70">
         <f>IF('AOP Critical'!O26="","",'AOP Critical'!O26)</f>
         <v>0.34</v>
       </c>
-      <c r="O33" s="71">
+      <c r="O33" s="70">
         <f>IF('AOP Critical'!P26="","",'AOP Critical'!P26)</f>
         <v>0.34</v>
       </c>
-      <c r="P33" s="71">
+      <c r="P33" s="70">
         <f>IF('AOP Critical'!Q26="","",'AOP Critical'!Q26)</f>
         <v>0.34</v>
       </c>
-      <c r="Q33" s="71">
+      <c r="Q33" s="70">
         <f>IF('AOP Critical'!R26="","",'AOP Critical'!R26)</f>
         <v>0.34</v>
       </c>
-      <c r="R33" s="71">
+      <c r="R33" s="70">
         <f>IF('AOP Critical'!S26="","",'AOP Critical'!S26)</f>
         <v>0.34</v>
       </c>
-      <c r="S33" s="71">
+      <c r="S33" s="70">
         <f>IF('AOP Critical'!T26="","",'AOP Critical'!T26)</f>
         <v>0.34</v>
       </c>
-      <c r="T33" s="71" t="str">
+      <c r="T33" s="70" t="str">
         <f>IF('AOP Critical'!U26="","",'AOP Critical'!U26)</f>
         <v/>
       </c>
-      <c r="U33" s="71" t="str">
+      <c r="U33" s="70" t="str">
         <f>IF('AOP Critical'!V26="","",'AOP Critical'!V26)</f>
         <v/>
       </c>
-      <c r="V33" s="71" t="str">
+      <c r="V33" s="70" t="str">
         <f>IF('AOP Critical'!W26="","",'AOP Critical'!W26)</f>
         <v/>
       </c>
@@ -7573,51 +7574,51 @@
         <f>IF('AOP Critical'!K27="","",'AOP Critical'!K27)</f>
         <v>A</v>
       </c>
-      <c r="K34" s="71">
+      <c r="K34" s="70">
         <f>IF('AOP Critical'!L27="","",'AOP Critical'!L27)</f>
         <v>0.318</v>
       </c>
-      <c r="L34" s="71">
+      <c r="L34" s="70">
         <f>IF('AOP Critical'!M27="","",'AOP Critical'!M27)</f>
         <v>0.35799999999999998</v>
       </c>
-      <c r="M34" s="71">
+      <c r="M34" s="70">
         <f>IF('AOP Critical'!N27="","",'AOP Critical'!N27)</f>
         <v>0.41499999999999998</v>
       </c>
-      <c r="N34" s="71">
+      <c r="N34" s="70">
         <f>IF('AOP Critical'!O27="","",'AOP Critical'!O27)</f>
         <v>0.40500000000000003</v>
       </c>
-      <c r="O34" s="71">
+      <c r="O34" s="70">
         <f>IF('AOP Critical'!P27="","",'AOP Critical'!P27)</f>
         <v>0.371</v>
       </c>
-      <c r="P34" s="71">
+      <c r="P34" s="70">
         <f>IF('AOP Critical'!Q27="","",'AOP Critical'!Q27)</f>
         <v>0.41899999999999998</v>
       </c>
-      <c r="Q34" s="71">
+      <c r="Q34" s="70">
         <f>IF('AOP Critical'!R27="","",'AOP Critical'!R27)</f>
         <v>0.39900000000000002</v>
       </c>
-      <c r="R34" s="71">
+      <c r="R34" s="70">
         <f>IF('AOP Critical'!S27="","",'AOP Critical'!S27)</f>
-        <v>0.35</v>
-      </c>
-      <c r="S34" s="71">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="S34" s="70">
         <f>IF('AOP Critical'!T27="","",'AOP Critical'!T27)</f>
-        <v>0.35</v>
-      </c>
-      <c r="T34" s="71" t="str">
+        <v>0.42299999999999999</v>
+      </c>
+      <c r="T34" s="70" t="str">
         <f>IF('AOP Critical'!U27="","",'AOP Critical'!U27)</f>
         <v/>
       </c>
-      <c r="U34" s="71" t="str">
+      <c r="U34" s="70" t="str">
         <f>IF('AOP Critical'!V27="","",'AOP Critical'!V27)</f>
         <v/>
       </c>
-      <c r="V34" s="71" t="str">
+      <c r="V34" s="70" t="str">
         <f>IF('AOP Critical'!W27="","",'AOP Critical'!W27)</f>
         <v/>
       </c>
@@ -7663,51 +7664,51 @@
         <f>IF('AOP Critical'!K22="","",'AOP Critical'!K22)</f>
         <v>T</v>
       </c>
-      <c r="K35" s="71">
+      <c r="K35" s="70">
         <f>IF('AOP Critical'!L22="","",'AOP Critical'!L22)</f>
         <v>0.9</v>
       </c>
-      <c r="L35" s="71">
+      <c r="L35" s="70">
         <f>IF('AOP Critical'!M22="","",'AOP Critical'!M22)</f>
         <v>0.9</v>
       </c>
-      <c r="M35" s="71">
+      <c r="M35" s="70">
         <f>IF('AOP Critical'!N22="","",'AOP Critical'!N22)</f>
         <v>0.9</v>
       </c>
-      <c r="N35" s="71">
+      <c r="N35" s="70">
         <f>IF('AOP Critical'!O22="","",'AOP Critical'!O22)</f>
         <v>0.9</v>
       </c>
-      <c r="O35" s="71">
+      <c r="O35" s="70">
         <f>IF('AOP Critical'!P22="","",'AOP Critical'!P22)</f>
         <v>0.9</v>
       </c>
-      <c r="P35" s="71">
+      <c r="P35" s="70">
         <f>IF('AOP Critical'!Q22="","",'AOP Critical'!Q22)</f>
         <v>0.9</v>
       </c>
-      <c r="Q35" s="71">
+      <c r="Q35" s="70">
         <f>IF('AOP Critical'!R22="","",'AOP Critical'!R22)</f>
         <v>0.9</v>
       </c>
-      <c r="R35" s="71">
+      <c r="R35" s="70">
         <f>IF('AOP Critical'!S22="","",'AOP Critical'!S22)</f>
         <v>0.9</v>
       </c>
-      <c r="S35" s="71">
+      <c r="S35" s="70">
         <f>IF('AOP Critical'!T22="","",'AOP Critical'!T22)</f>
         <v>0.9</v>
       </c>
-      <c r="T35" s="71">
+      <c r="T35" s="70">
         <f>IF('AOP Critical'!U22="","",'AOP Critical'!U22)</f>
         <v>0.9</v>
       </c>
-      <c r="U35" s="71">
+      <c r="U35" s="70">
         <f>IF('AOP Critical'!V22="","",'AOP Critical'!V22)</f>
         <v>0.9</v>
       </c>
-      <c r="V35" s="71">
+      <c r="V35" s="70">
         <f>IF('AOP Critical'!W22="","",'AOP Critical'!W22)</f>
         <v>0.9</v>
       </c>
@@ -7753,51 +7754,51 @@
         <f>IF('AOP Critical'!K23="","",'AOP Critical'!K23)</f>
         <v>A</v>
       </c>
-      <c r="K36" s="71">
+      <c r="K36" s="70">
         <f>IF('AOP Critical'!L23="","",'AOP Critical'!L23)</f>
         <v>0.81</v>
       </c>
-      <c r="L36" s="71">
+      <c r="L36" s="70">
         <f>IF('AOP Critical'!M23="","",'AOP Critical'!M23)</f>
         <v>0.78</v>
       </c>
-      <c r="M36" s="71">
+      <c r="M36" s="70">
         <f>IF('AOP Critical'!N23="","",'AOP Critical'!N23)</f>
         <v>0.8</v>
       </c>
-      <c r="N36" s="71">
+      <c r="N36" s="70">
         <f>IF('AOP Critical'!O23="","",'AOP Critical'!O23)</f>
         <v>0.82</v>
       </c>
-      <c r="O36" s="71">
+      <c r="O36" s="70">
         <f>IF('AOP Critical'!P23="","",'AOP Critical'!P23)</f>
         <v>0.79500000000000004</v>
       </c>
-      <c r="P36" s="71">
+      <c r="P36" s="70">
         <f>IF('AOP Critical'!Q23="","",'AOP Critical'!Q23)</f>
         <v>0.86</v>
       </c>
-      <c r="Q36" s="71">
+      <c r="Q36" s="70">
         <f>IF('AOP Critical'!R23="","",'AOP Critical'!R23)</f>
         <v>0.88</v>
       </c>
-      <c r="R36" s="71">
+      <c r="R36" s="70">
         <f>IF('AOP Critical'!S23="","",'AOP Critical'!S23)</f>
         <v>0.94</v>
       </c>
-      <c r="S36" s="71" t="str">
+      <c r="S36" s="70">
         <f>IF('AOP Critical'!T23="","",'AOP Critical'!T23)</f>
-        <v/>
-      </c>
-      <c r="T36" s="71" t="str">
+        <v>0.91</v>
+      </c>
+      <c r="T36" s="70" t="str">
         <f>IF('AOP Critical'!U23="","",'AOP Critical'!U23)</f>
         <v/>
       </c>
-      <c r="U36" s="71" t="str">
+      <c r="U36" s="70" t="str">
         <f>IF('AOP Critical'!V23="","",'AOP Critical'!V23)</f>
         <v/>
       </c>
-      <c r="V36" s="71" t="str">
+      <c r="V36" s="70" t="str">
         <f>IF('AOP Critical'!W23="","",'AOP Critical'!W23)</f>
         <v/>
       </c>
@@ -7843,51 +7844,51 @@
         <f>IF('AOP Critical'!K43="","",'AOP Critical'!K43)</f>
         <v>T</v>
       </c>
-      <c r="K37" s="72" t="str">
+      <c r="K37" s="71" t="str">
         <f>IF('AOP Critical'!L43="","",'AOP Critical'!L43)</f>
         <v/>
       </c>
-      <c r="L37" s="72" t="str">
+      <c r="L37" s="71" t="str">
         <f>IF('AOP Critical'!M43="","",'AOP Critical'!M43)</f>
         <v/>
       </c>
-      <c r="M37" s="72">
+      <c r="M37" s="71">
         <f>IF('AOP Critical'!N43="","",'AOP Critical'!N43)</f>
         <v>0.05</v>
       </c>
-      <c r="N37" s="72" t="str">
+      <c r="N37" s="71" t="str">
         <f>IF('AOP Critical'!O43="","",'AOP Critical'!O43)</f>
         <v/>
       </c>
-      <c r="O37" s="72" t="str">
+      <c r="O37" s="71" t="str">
         <f>IF('AOP Critical'!P43="","",'AOP Critical'!P43)</f>
         <v/>
       </c>
-      <c r="P37" s="72">
+      <c r="P37" s="71">
         <f>IF('AOP Critical'!Q43="","",'AOP Critical'!Q43)</f>
         <v>5.5E-2</v>
       </c>
-      <c r="Q37" s="72" t="str">
+      <c r="Q37" s="71" t="str">
         <f>IF('AOP Critical'!R43="","",'AOP Critical'!R43)</f>
         <v/>
       </c>
-      <c r="R37" s="72" t="str">
+      <c r="R37" s="71" t="str">
         <f>IF('AOP Critical'!S43="","",'AOP Critical'!S43)</f>
         <v/>
       </c>
-      <c r="S37" s="72" t="str">
+      <c r="S37" s="71" t="str">
         <f>IF('AOP Critical'!T43="","",'AOP Critical'!T43)</f>
         <v/>
       </c>
-      <c r="T37" s="72" t="str">
+      <c r="T37" s="71" t="str">
         <f>IF('AOP Critical'!U43="","",'AOP Critical'!U43)</f>
         <v/>
       </c>
-      <c r="U37" s="72" t="str">
+      <c r="U37" s="71" t="str">
         <f>IF('AOP Critical'!V43="","",'AOP Critical'!V43)</f>
         <v/>
       </c>
-      <c r="V37" s="72" t="str">
+      <c r="V37" s="71" t="str">
         <f>IF('AOP Critical'!W43="","",'AOP Critical'!W43)</f>
         <v/>
       </c>
@@ -8023,51 +8024,51 @@
         <f>IF('AOP Critical'!K45="","",'AOP Critical'!K45)</f>
         <v>T</v>
       </c>
-      <c r="K39" s="72">
+      <c r="K39" s="71">
         <f>IF('AOP Critical'!L45="","",'AOP Critical'!L45)</f>
         <v>0.4</v>
       </c>
-      <c r="L39" s="72">
+      <c r="L39" s="71">
         <f>IF('AOP Critical'!M45="","",'AOP Critical'!M45)</f>
         <v>0.4</v>
       </c>
-      <c r="M39" s="72">
+      <c r="M39" s="71">
         <f>IF('AOP Critical'!N45="","",'AOP Critical'!N45)</f>
         <v>0.4</v>
       </c>
-      <c r="N39" s="72">
+      <c r="N39" s="71">
         <f>IF('AOP Critical'!O45="","",'AOP Critical'!O45)</f>
         <v>0.4</v>
       </c>
-      <c r="O39" s="72">
+      <c r="O39" s="71">
         <f>IF('AOP Critical'!P45="","",'AOP Critical'!P45)</f>
         <v>0.4</v>
       </c>
-      <c r="P39" s="72">
+      <c r="P39" s="71">
         <f>IF('AOP Critical'!Q45="","",'AOP Critical'!Q45)</f>
         <v>0.4</v>
       </c>
-      <c r="Q39" s="72">
+      <c r="Q39" s="71">
         <f>IF('AOP Critical'!R45="","",'AOP Critical'!R45)</f>
         <v>0.4</v>
       </c>
-      <c r="R39" s="72" t="str">
+      <c r="R39" s="71">
         <f>IF('AOP Critical'!S45="","",'AOP Critical'!S45)</f>
-        <v/>
-      </c>
-      <c r="S39" s="72" t="str">
+        <v>0.4</v>
+      </c>
+      <c r="S39" s="71">
         <f>IF('AOP Critical'!T45="","",'AOP Critical'!T45)</f>
-        <v/>
-      </c>
-      <c r="T39" s="72" t="str">
+        <v>0.4</v>
+      </c>
+      <c r="T39" s="71" t="str">
         <f>IF('AOP Critical'!U45="","",'AOP Critical'!U45)</f>
         <v/>
       </c>
-      <c r="U39" s="72" t="str">
+      <c r="U39" s="71" t="str">
         <f>IF('AOP Critical'!V45="","",'AOP Critical'!V45)</f>
         <v/>
       </c>
-      <c r="V39" s="72" t="str">
+      <c r="V39" s="71" t="str">
         <f>IF('AOP Critical'!W45="","",'AOP Critical'!W45)</f>
         <v/>
       </c>
@@ -8113,51 +8114,51 @@
         <f>IF('AOP Critical'!K46="","",'AOP Critical'!K46)</f>
         <v>A</v>
       </c>
-      <c r="K40" s="72">
+      <c r="K40" s="71">
         <f>IF('AOP Critical'!L46="","",'AOP Critical'!L46)</f>
         <v>0.66</v>
       </c>
-      <c r="L40" s="72">
+      <c r="L40" s="71">
         <f>IF('AOP Critical'!M46="","",'AOP Critical'!M46)</f>
         <v>0.34</v>
       </c>
-      <c r="M40" s="72">
+      <c r="M40" s="71">
         <f>IF('AOP Critical'!N46="","",'AOP Critical'!N46)</f>
         <v>0.41</v>
       </c>
-      <c r="N40" s="72">
+      <c r="N40" s="71">
         <f>IF('AOP Critical'!O46="","",'AOP Critical'!O46)</f>
         <v>0.39</v>
       </c>
-      <c r="O40" s="72">
+      <c r="O40" s="71">
         <f>IF('AOP Critical'!P46="","",'AOP Critical'!P46)</f>
         <v>0.40799999999999997</v>
       </c>
-      <c r="P40" s="72">
+      <c r="P40" s="71">
         <f>IF('AOP Critical'!Q46="","",'AOP Critical'!Q46)</f>
         <v>0.43</v>
       </c>
-      <c r="Q40" s="72">
+      <c r="Q40" s="71">
         <f>IF('AOP Critical'!R46="","",'AOP Critical'!R46)</f>
         <v>0.56000000000000005</v>
       </c>
-      <c r="R40" s="72">
+      <c r="R40" s="71">
         <f>IF('AOP Critical'!S46="","",'AOP Critical'!S46)</f>
         <v>0.39</v>
       </c>
-      <c r="S40" s="72">
+      <c r="S40" s="71">
         <f>IF('AOP Critical'!T46="","",'AOP Critical'!T46)</f>
         <v>0.37</v>
       </c>
-      <c r="T40" s="72" t="str">
+      <c r="T40" s="71" t="str">
         <f>IF('AOP Critical'!U46="","",'AOP Critical'!U46)</f>
         <v/>
       </c>
-      <c r="U40" s="72" t="str">
+      <c r="U40" s="71" t="str">
         <f>IF('AOP Critical'!V46="","",'AOP Critical'!V46)</f>
         <v/>
       </c>
-      <c r="V40" s="72" t="str">
+      <c r="V40" s="71" t="str">
         <f>IF('AOP Critical'!W46="","",'AOP Critical'!W46)</f>
         <v/>
       </c>
@@ -8325,9 +8326,9 @@
         <f>IF('AOP Critical'!S48="","",'AOP Critical'!S48)</f>
         <v>51.9</v>
       </c>
-      <c r="S42" t="str">
+      <c r="S42">
         <f>IF('AOP Critical'!T48="","",'AOP Critical'!T48)</f>
-        <v/>
+        <v>55.8</v>
       </c>
       <c r="T42" t="str">
         <f>IF('AOP Critical'!U48="","",'AOP Critical'!U48)</f>
@@ -8456,51 +8457,51 @@
         <f>IF('AOP Critical'!K28="","",'AOP Critical'!K28)</f>
         <v>T</v>
       </c>
-      <c r="K45" s="72" vm="1">
+      <c r="K45" s="71" vm="1">
         <f>IF('AOP Critical'!L28="","",'AOP Critical'!L28)</f>
         <v>3.6951550944796852E-2</v>
       </c>
-      <c r="L45" s="72" vm="3">
+      <c r="L45" s="71" vm="3">
         <f>IF('AOP Critical'!M28="","",'AOP Critical'!M28)</f>
         <v>0.43621586155644376</v>
       </c>
-      <c r="M45" s="72" vm="6">
+      <c r="M45" s="71" vm="6">
         <f>IF('AOP Critical'!N28="","",'AOP Critical'!N28)</f>
         <v>6.9838696752701823E-2</v>
       </c>
-      <c r="N45" s="72" vm="10">
+      <c r="N45" s="71" vm="10">
         <f>IF('AOP Critical'!O28="","",'AOP Critical'!O28)</f>
         <v>0.21843539773619547</v>
       </c>
-      <c r="O45" s="72" vm="12">
+      <c r="O45" s="71" vm="12">
         <f>IF('AOP Critical'!P28="","",'AOP Critical'!P28)</f>
         <v>0.20239261325941293</v>
       </c>
-      <c r="P45" s="72" vm="14">
+      <c r="P45" s="71" vm="14">
         <f>IF('AOP Critical'!Q28="","",'AOP Critical'!Q28)</f>
         <v>0.29754592225545773</v>
       </c>
-      <c r="Q45" s="72" vm="18">
+      <c r="Q45" s="71" vm="18">
         <f>IF('AOP Critical'!R28="","",'AOP Critical'!R28)</f>
         <v>0.26300517799117751</v>
       </c>
-      <c r="R45" s="72" vm="22">
+      <c r="R45" s="71" vm="22">
         <f>IF('AOP Critical'!S28="","",'AOP Critical'!S28)</f>
         <v>0.30756202137510114</v>
       </c>
-      <c r="S45" s="72" t="str">
+      <c r="S45" s="71">
         <f>IF('AOP Critical'!T28="","",'AOP Critical'!T28)</f>
-        <v/>
-      </c>
-      <c r="T45" s="72" t="str">
+        <v>0.38100000000000001</v>
+      </c>
+      <c r="T45" s="71" t="str">
         <f>IF('AOP Critical'!U28="","",'AOP Critical'!U28)</f>
         <v/>
       </c>
-      <c r="U45" s="72" t="str">
+      <c r="U45" s="71" t="str">
         <f>IF('AOP Critical'!V28="","",'AOP Critical'!V28)</f>
         <v/>
       </c>
-      <c r="V45" s="72" t="str">
+      <c r="V45" s="71" t="str">
         <f>IF('AOP Critical'!W28="","",'AOP Critical'!W28)</f>
         <v/>
       </c>
@@ -8546,51 +8547,51 @@
         <f>IF('AOP Critical'!K29="","",'AOP Critical'!K29)</f>
         <v>A</v>
       </c>
-      <c r="K46" s="72" vm="2">
+      <c r="K46" s="71" vm="2">
         <f>IF('AOP Critical'!L29="","",'AOP Critical'!L29)</f>
         <v>-0.21537837470975407</v>
       </c>
-      <c r="L46" s="72">
+      <c r="L46" s="71">
         <f>IF('AOP Critical'!M29="","",'AOP Critical'!M29)</f>
         <v>0.27400000000000002</v>
       </c>
-      <c r="M46" s="72" vm="7">
+      <c r="M46" s="71" vm="7">
         <f>IF('AOP Critical'!N29="","",'AOP Critical'!N29)</f>
         <v>0.17956999989031885</v>
       </c>
-      <c r="N46" s="72" vm="11">
+      <c r="N46" s="71" vm="11">
         <f>IF('AOP Critical'!O29="","",'AOP Critical'!O29)</f>
         <v>0.24020098639758425</v>
       </c>
-      <c r="O46" s="72" vm="13">
+      <c r="O46" s="71" vm="13">
         <f>IF('AOP Critical'!P29="","",'AOP Critical'!P29)</f>
         <v>0.12891206138967748</v>
       </c>
-      <c r="P46" s="72" vm="15">
+      <c r="P46" s="71" vm="15">
         <f>IF('AOP Critical'!Q29="","",'AOP Critical'!Q29)</f>
         <v>0.37665227402645685</v>
       </c>
-      <c r="Q46" s="72" vm="19">
+      <c r="Q46" s="71" vm="19">
         <f>IF('AOP Critical'!R29="","",'AOP Critical'!R29)</f>
         <v>0.26390638821134749</v>
       </c>
-      <c r="R46" s="72" vm="23">
+      <c r="R46" s="71" vm="23">
         <f>IF('AOP Critical'!S29="","",'AOP Critical'!S29)</f>
         <v>0.28426058124592513</v>
       </c>
-      <c r="S46" s="72" t="str">
+      <c r="S46" s="71">
         <f>IF('AOP Critical'!T29="","",'AOP Critical'!T29)</f>
-        <v/>
-      </c>
-      <c r="T46" s="72" t="str">
+        <v>0.378</v>
+      </c>
+      <c r="T46" s="71" t="str">
         <f>IF('AOP Critical'!U29="","",'AOP Critical'!U29)</f>
         <v/>
       </c>
-      <c r="U46" s="72" t="str">
+      <c r="U46" s="71" t="str">
         <f>IF('AOP Critical'!V29="","",'AOP Critical'!V29)</f>
         <v/>
       </c>
-      <c r="V46" s="72" t="str">
+      <c r="V46" s="71" t="str">
         <f>IF('AOP Critical'!W29="","",'AOP Critical'!W29)</f>
         <v/>
       </c>
@@ -8636,48 +8637,48 @@
         <f>IF('AOP Critical'!K30="","",'AOP Critical'!K30)</f>
         <v>T</v>
       </c>
-      <c r="K47" s="72"/>
-      <c r="L47" s="72" vm="4">
+      <c r="K47" s="71"/>
+      <c r="L47" s="71" vm="4">
         <f>IF('AOP Critical'!M30="","",'AOP Critical'!M30)</f>
         <v>9.8925321866648819E-2</v>
       </c>
-      <c r="M47" s="72" vm="8">
+      <c r="M47" s="71" vm="8">
         <f>IF('AOP Critical'!N30="","",'AOP Critical'!N30)</f>
         <v>0.11712228373869382</v>
       </c>
-      <c r="N47" s="72">
+      <c r="N47" s="71">
         <f>IF('AOP Critical'!O30="","",'AOP Critical'!O30)</f>
         <v>0.15809999999999999</v>
       </c>
-      <c r="O47" s="72">
+      <c r="O47" s="71">
         <f>IF('AOP Critical'!P30="","",'AOP Critical'!P30)</f>
         <v>0.151</v>
       </c>
-      <c r="P47" s="72" vm="16">
+      <c r="P47" s="71" vm="16">
         <f>IF('AOP Critical'!Q30="","",'AOP Critical'!Q30)</f>
         <v>0.12551463489599346</v>
       </c>
-      <c r="Q47" s="72" vm="20">
+      <c r="Q47" s="71" vm="20">
         <f>IF('AOP Critical'!R30="","",'AOP Critical'!R30)</f>
         <v>0.10280225768958351</v>
       </c>
-      <c r="R47" s="72">
+      <c r="R47" s="71">
         <f>IF('AOP Critical'!S30="","",'AOP Critical'!S30)</f>
         <v>0.13500000000000001</v>
       </c>
-      <c r="S47" s="72" t="str">
+      <c r="S47" s="71">
         <f>IF('AOP Critical'!T30="","",'AOP Critical'!T30)</f>
-        <v/>
-      </c>
-      <c r="T47" s="72" t="str">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="T47" s="71" t="str">
         <f>IF('AOP Critical'!U30="","",'AOP Critical'!U30)</f>
         <v/>
       </c>
-      <c r="U47" s="72" t="str">
+      <c r="U47" s="71" t="str">
         <f>IF('AOP Critical'!V30="","",'AOP Critical'!V30)</f>
         <v/>
       </c>
-      <c r="V47" s="72" t="str">
+      <c r="V47" s="71" t="str">
         <f>IF('AOP Critical'!W30="","",'AOP Critical'!W30)</f>
         <v/>
       </c>
@@ -8719,51 +8720,51 @@
         <f>IF('AOP Critical'!K31="","",'AOP Critical'!K31)</f>
         <v>A</v>
       </c>
-      <c r="K48" s="72">
+      <c r="K48" s="71">
         <f>IF('AOP Critical'!L31="","",'AOP Critical'!L31)</f>
         <v>0.32500000000000001</v>
       </c>
-      <c r="L48" s="72" vm="5">
+      <c r="L48" s="71" vm="5">
         <f>IF('AOP Critical'!M31="","",'AOP Critical'!M31)</f>
         <v>0.19016698273293486</v>
       </c>
-      <c r="M48" s="72" vm="9">
+      <c r="M48" s="71" vm="9">
         <f>IF('AOP Critical'!N31="","",'AOP Critical'!N31)</f>
         <v>0.14313042982821633</v>
       </c>
-      <c r="N48" s="72">
+      <c r="N48" s="71">
         <f>IF('AOP Critical'!O31="","",'AOP Critical'!O31)</f>
         <v>0.2399</v>
       </c>
-      <c r="O48" s="72">
+      <c r="O48" s="71">
         <f>IF('AOP Critical'!P31="","",'AOP Critical'!P31)</f>
         <v>0.20599999999999999</v>
       </c>
-      <c r="P48" s="72" vm="17">
+      <c r="P48" s="71" vm="17">
         <f>IF('AOP Critical'!Q31="","",'AOP Critical'!Q31)</f>
         <v>0.15714973912715791</v>
       </c>
-      <c r="Q48" s="72" vm="21">
+      <c r="Q48" s="71" vm="21">
         <f>IF('AOP Critical'!R31="","",'AOP Critical'!R31)</f>
         <v>0.10382365349216505</v>
       </c>
-      <c r="R48" s="72">
+      <c r="R48" s="71">
         <f>IF('AOP Critical'!S31="","",'AOP Critical'!S31)</f>
         <v>0.151</v>
       </c>
-      <c r="S48" s="72" t="str">
+      <c r="S48" s="71">
         <f>IF('AOP Critical'!T31="","",'AOP Critical'!T31)</f>
-        <v/>
-      </c>
-      <c r="T48" s="72" t="str">
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="T48" s="71" t="str">
         <f>IF('AOP Critical'!U31="","",'AOP Critical'!U31)</f>
         <v/>
       </c>
-      <c r="U48" s="72" t="str">
+      <c r="U48" s="71" t="str">
         <f>IF('AOP Critical'!V31="","",'AOP Critical'!V31)</f>
         <v/>
       </c>
-      <c r="V48" s="72" t="str">
+      <c r="V48" s="71" t="str">
         <f>IF('AOP Critical'!W31="","",'AOP Critical'!W31)</f>
         <v/>
       </c>
@@ -8809,51 +8810,51 @@
         <f>IF('AOP Critical'!K32="","",'AOP Critical'!K32)</f>
         <v>T</v>
       </c>
-      <c r="K49" s="74">
+      <c r="K49" s="73">
         <f>IF('AOP Critical'!L32="","",'AOP Critical'!L32)</f>
         <v>8.6903037999999988</v>
       </c>
-      <c r="L49" s="74">
+      <c r="L49" s="73">
         <f>IF('AOP Critical'!M32="","",'AOP Critical'!M32)</f>
         <v>14.05</v>
       </c>
-      <c r="M49" s="74">
+      <c r="M49" s="73">
         <f>IF('AOP Critical'!N32="","",'AOP Critical'!N32)</f>
         <v>24.179069699999999</v>
       </c>
-      <c r="N49" s="74">
+      <c r="N49" s="73">
         <f>IF('AOP Critical'!O32="","",'AOP Critical'!O32)</f>
         <v>33.551317699999998</v>
       </c>
-      <c r="O49" s="74">
+      <c r="O49" s="73">
         <f>IF('AOP Critical'!P32="","",'AOP Critical'!P32)</f>
         <v>41.442849800000005</v>
       </c>
-      <c r="P49" s="74">
+      <c r="P49" s="73">
         <f>IF('AOP Critical'!Q32="","",'AOP Critical'!Q32)</f>
         <v>60.823965100000009</v>
       </c>
-      <c r="Q49" s="74">
+      <c r="Q49" s="73">
         <f>IF('AOP Critical'!R32="","",'AOP Critical'!R32)</f>
         <v>72.599999999999994</v>
       </c>
-      <c r="R49" s="74">
+      <c r="R49" s="73">
         <f>IF('AOP Critical'!S32="","",'AOP Critical'!S32)</f>
         <v>82.449704499999996</v>
       </c>
-      <c r="S49" s="74" t="str">
+      <c r="S49" s="73">
         <f>IF('AOP Critical'!T32="","",'AOP Critical'!T32)</f>
-        <v/>
-      </c>
-      <c r="T49" s="74" t="str">
+        <v>97.4</v>
+      </c>
+      <c r="T49" s="73" t="str">
         <f>IF('AOP Critical'!U32="","",'AOP Critical'!U32)</f>
         <v/>
       </c>
-      <c r="U49" s="74" t="str">
+      <c r="U49" s="73" t="str">
         <f>IF('AOP Critical'!V32="","",'AOP Critical'!V32)</f>
         <v/>
       </c>
-      <c r="V49" s="74" t="str">
+      <c r="V49" s="73" t="str">
         <f>IF('AOP Critical'!W32="","",'AOP Critical'!W32)</f>
         <v/>
       </c>
@@ -8899,51 +8900,51 @@
         <f>IF('AOP Critical'!K33="","",'AOP Critical'!K33)</f>
         <v>A</v>
       </c>
-      <c r="K50" s="74">
+      <c r="K50" s="73">
         <f>IF('AOP Critical'!L33="","",'AOP Critical'!L33)</f>
         <v>4.05</v>
       </c>
-      <c r="L50" s="74">
+      <c r="L50" s="73">
         <f>IF('AOP Critical'!M33="","",'AOP Critical'!M33)</f>
         <v>9.7989724000000002</v>
       </c>
-      <c r="M50" s="74">
+      <c r="M50" s="73">
         <f>IF('AOP Critical'!N33="","",'AOP Critical'!N33)</f>
         <v>25.313448100000002</v>
       </c>
-      <c r="N50" s="74">
+      <c r="N50" s="73">
         <f>IF('AOP Critical'!O33="","",'AOP Critical'!O33)</f>
         <v>31.452557499999998</v>
       </c>
-      <c r="O50" s="74">
+      <c r="O50" s="73">
         <f>IF('AOP Critical'!P33="","",'AOP Critical'!P33)</f>
         <v>41.128122899999994</v>
       </c>
-      <c r="P50" s="74">
+      <c r="P50" s="73">
         <f>IF('AOP Critical'!Q33="","",'AOP Critical'!Q33)</f>
         <v>55.164574999999999</v>
       </c>
-      <c r="Q50" s="74">
+      <c r="Q50" s="73">
         <f>IF('AOP Critical'!R33="","",'AOP Critical'!R33)</f>
         <v>61.940289700000001</v>
       </c>
-      <c r="R50" s="74">
+      <c r="R50" s="73">
         <f>IF('AOP Critical'!S33="","",'AOP Critical'!S33)</f>
         <v>72.779408199999978</v>
       </c>
-      <c r="S50" s="74" t="str">
+      <c r="S50" s="73">
         <f>IF('AOP Critical'!T33="","",'AOP Critical'!T33)</f>
-        <v/>
-      </c>
-      <c r="T50" s="74" t="str">
+        <v>91.2</v>
+      </c>
+      <c r="T50" s="73" t="str">
         <f>IF('AOP Critical'!U33="","",'AOP Critical'!U33)</f>
         <v/>
       </c>
-      <c r="U50" s="74" t="str">
+      <c r="U50" s="73" t="str">
         <f>IF('AOP Critical'!V33="","",'AOP Critical'!V33)</f>
         <v/>
       </c>
-      <c r="V50" s="74" t="str">
+      <c r="V50" s="73" t="str">
         <f>IF('AOP Critical'!W33="","",'AOP Critical'!W33)</f>
         <v/>
       </c>
@@ -8989,51 +8990,51 @@
         <f>IF('AOP Critical'!K24="","",'AOP Critical'!K24)</f>
         <v>T</v>
       </c>
-      <c r="K51" s="72" t="str">
+      <c r="K51" s="71" t="str">
         <f>IF('AOP Critical'!L24="","",'AOP Critical'!L24)</f>
         <v/>
       </c>
-      <c r="L51" s="72" t="str">
+      <c r="L51" s="71" t="str">
         <f>IF('AOP Critical'!M24="","",'AOP Critical'!M24)</f>
         <v/>
       </c>
-      <c r="M51" s="72">
+      <c r="M51" s="71">
         <f>IF('AOP Critical'!N24="","",'AOP Critical'!N24)</f>
         <v>0.104</v>
       </c>
-      <c r="N51" s="72" t="str">
+      <c r="N51" s="71" t="str">
         <f>IF('AOP Critical'!O24="","",'AOP Critical'!O24)</f>
         <v>QTR</v>
       </c>
-      <c r="O51" s="72" t="str">
+      <c r="O51" s="71" t="str">
         <f>IF('AOP Critical'!P24="","",'AOP Critical'!P24)</f>
         <v>QTR</v>
       </c>
-      <c r="P51" s="72">
+      <c r="P51" s="71">
         <f>IF('AOP Critical'!Q24="","",'AOP Critical'!Q24)</f>
         <v>0.11799999999999999</v>
       </c>
-      <c r="Q51" s="72" t="str">
+      <c r="Q51" s="71" t="str">
         <f>IF('AOP Critical'!R24="","",'AOP Critical'!R24)</f>
         <v>QTR</v>
       </c>
-      <c r="R51" s="72" t="str">
+      <c r="R51" s="71" t="str">
         <f>IF('AOP Critical'!S24="","",'AOP Critical'!S24)</f>
         <v>QTR</v>
       </c>
-      <c r="S51" s="72" t="str">
+      <c r="S51" s="71" t="str">
         <f>IF('AOP Critical'!T24="","",'AOP Critical'!T24)</f>
         <v/>
       </c>
-      <c r="T51" s="72" t="str">
+      <c r="T51" s="71" t="str">
         <f>IF('AOP Critical'!U24="","",'AOP Critical'!U24)</f>
         <v>QTR</v>
       </c>
-      <c r="U51" s="72" t="str">
+      <c r="U51" s="71" t="str">
         <f>IF('AOP Critical'!V24="","",'AOP Critical'!V24)</f>
         <v>QTR</v>
       </c>
-      <c r="V51" s="72" t="str">
+      <c r="V51" s="71" t="str">
         <f>IF('AOP Critical'!W24="","",'AOP Critical'!W24)</f>
         <v/>
       </c>
@@ -9227,51 +9228,51 @@
         <f>IF('AOP Critical'!K34="","",'AOP Critical'!K34)</f>
         <v>T</v>
       </c>
-      <c r="K56" s="71" t="str">
+      <c r="K56" s="70" t="str">
         <f>IF('AOP Critical'!L34="","",'AOP Critical'!L34)</f>
         <v/>
       </c>
-      <c r="L56" s="71" t="str">
+      <c r="L56" s="70" t="str">
         <f>IF('AOP Critical'!M34="","",'AOP Critical'!M34)</f>
         <v/>
       </c>
-      <c r="M56" s="71">
+      <c r="M56" s="70">
         <f>IF('AOP Critical'!N34="","",'AOP Critical'!N34)</f>
         <v>0.9</v>
       </c>
-      <c r="N56" s="71" t="str">
+      <c r="N56" s="70" t="str">
         <f>IF('AOP Critical'!O34="","",'AOP Critical'!O34)</f>
         <v/>
       </c>
-      <c r="O56" s="71" t="str">
+      <c r="O56" s="70" t="str">
         <f>IF('AOP Critical'!P34="","",'AOP Critical'!P34)</f>
         <v/>
       </c>
-      <c r="P56" s="71">
+      <c r="P56" s="70">
         <f>IF('AOP Critical'!Q34="","",'AOP Critical'!Q34)</f>
         <v>0.9</v>
       </c>
-      <c r="Q56" s="71" t="str">
+      <c r="Q56" s="70" t="str">
         <f>IF('AOP Critical'!R34="","",'AOP Critical'!R34)</f>
         <v/>
       </c>
-      <c r="R56" s="71" t="str">
+      <c r="R56" s="70" t="str">
         <f>IF('AOP Critical'!S34="","",'AOP Critical'!S34)</f>
         <v/>
       </c>
-      <c r="S56" s="71">
+      <c r="S56" s="70">
         <f>IF('AOP Critical'!T34="","",'AOP Critical'!T34)</f>
         <v>0.9</v>
       </c>
-      <c r="T56" s="71" t="str">
+      <c r="T56" s="70" t="str">
         <f>IF('AOP Critical'!U34="","",'AOP Critical'!U34)</f>
         <v/>
       </c>
-      <c r="U56" s="71" t="str">
+      <c r="U56" s="70" t="str">
         <f>IF('AOP Critical'!V34="","",'AOP Critical'!V34)</f>
         <v/>
       </c>
-      <c r="V56" s="71">
+      <c r="V56" s="70">
         <f>IF('AOP Critical'!W34="","",'AOP Critical'!W34)</f>
         <v>0.9</v>
       </c>
@@ -9302,51 +9303,51 @@
         <f>IF('AOP Critical'!K35="","",'AOP Critical'!K35)</f>
         <v>A</v>
       </c>
-      <c r="K57" s="71" t="str">
+      <c r="K57" s="70" t="str">
         <f>IF('AOP Critical'!L35="","",'AOP Critical'!L35)</f>
         <v>QTR</v>
       </c>
-      <c r="L57" s="71" t="str">
+      <c r="L57" s="70" t="str">
         <f>IF('AOP Critical'!M35="","",'AOP Critical'!M35)</f>
         <v>QTR</v>
       </c>
-      <c r="M57" s="71">
+      <c r="M57" s="70">
         <f>IF('AOP Critical'!N35="","",'AOP Critical'!N35)</f>
         <v>1</v>
       </c>
-      <c r="N57" s="71" t="str">
+      <c r="N57" s="70" t="str">
         <f>IF('AOP Critical'!O35="","",'AOP Critical'!O35)</f>
         <v>QTR</v>
       </c>
-      <c r="O57" s="71" t="str">
+      <c r="O57" s="70" t="str">
         <f>IF('AOP Critical'!P35="","",'AOP Critical'!P35)</f>
         <v>QTR</v>
       </c>
-      <c r="P57" s="71">
+      <c r="P57" s="70">
         <f>IF('AOP Critical'!Q35="","",'AOP Critical'!Q35)</f>
         <v>0.96199999999999997</v>
       </c>
-      <c r="Q57" s="71" t="str">
+      <c r="Q57" s="70" t="str">
         <f>IF('AOP Critical'!R35="","",'AOP Critical'!R35)</f>
         <v>QTR</v>
       </c>
-      <c r="R57" s="71" t="str">
+      <c r="R57" s="70" t="str">
         <f>IF('AOP Critical'!S35="","",'AOP Critical'!S35)</f>
         <v>QTR</v>
       </c>
-      <c r="S57" s="71" t="str">
+      <c r="S57" s="70">
         <f>IF('AOP Critical'!T35="","",'AOP Critical'!T35)</f>
-        <v/>
-      </c>
-      <c r="T57" s="71" t="str">
+        <v>0.91300000000000003</v>
+      </c>
+      <c r="T57" s="70" t="str">
         <f>IF('AOP Critical'!U35="","",'AOP Critical'!U35)</f>
         <v/>
       </c>
-      <c r="U57" s="71" t="str">
+      <c r="U57" s="70" t="str">
         <f>IF('AOP Critical'!V35="","",'AOP Critical'!V35)</f>
         <v/>
       </c>
-      <c r="V57" s="71" t="str">
+      <c r="V57" s="70" t="str">
         <f>IF('AOP Critical'!W35="","",'AOP Critical'!W35)</f>
         <v/>
       </c>
@@ -9377,51 +9378,51 @@
         <f>IF('AOP Critical'!K36="","",'AOP Critical'!K36)</f>
         <v>T</v>
       </c>
-      <c r="K58" s="71" t="str">
+      <c r="K58" s="70" t="str">
         <f>IF('AOP Critical'!L36="","",'AOP Critical'!L36)</f>
         <v/>
       </c>
-      <c r="L58" s="71" t="str">
+      <c r="L58" s="70" t="str">
         <f>IF('AOP Critical'!M36="","",'AOP Critical'!M36)</f>
         <v/>
       </c>
-      <c r="M58" s="71" t="str">
+      <c r="M58" s="70" t="str">
         <f>IF('AOP Critical'!N36="","",'AOP Critical'!N36)</f>
         <v/>
       </c>
-      <c r="N58" s="71">
+      <c r="N58" s="70">
         <f>IF('AOP Critical'!O36="","",'AOP Critical'!O36)</f>
         <v>0.83</v>
       </c>
-      <c r="O58" s="71" t="str">
+      <c r="O58" s="70" t="str">
         <f>IF('AOP Critical'!P36="","",'AOP Critical'!P36)</f>
         <v/>
       </c>
-      <c r="P58" s="71">
+      <c r="P58" s="70">
         <f>IF('AOP Critical'!Q36="","",'AOP Critical'!Q36)</f>
         <v>0.83</v>
       </c>
-      <c r="Q58" s="71" t="str">
+      <c r="Q58" s="70" t="str">
         <f>IF('AOP Critical'!R36="","",'AOP Critical'!R36)</f>
         <v/>
       </c>
-      <c r="R58" s="71" t="str">
+      <c r="R58" s="70" t="str">
         <f>IF('AOP Critical'!S36="","",'AOP Critical'!S36)</f>
         <v/>
       </c>
-      <c r="S58" s="71" t="str">
+      <c r="S58" s="70" t="str">
         <f>IF('AOP Critical'!T36="","",'AOP Critical'!T36)</f>
         <v/>
       </c>
-      <c r="T58" s="71" t="str">
+      <c r="T58" s="70" t="str">
         <f>IF('AOP Critical'!U36="","",'AOP Critical'!U36)</f>
         <v/>
       </c>
-      <c r="U58" s="71" t="str">
+      <c r="U58" s="70" t="str">
         <f>IF('AOP Critical'!V36="","",'AOP Critical'!V36)</f>
         <v/>
       </c>
-      <c r="V58" s="71" t="str">
+      <c r="V58" s="70" t="str">
         <f>IF('AOP Critical'!W36="","",'AOP Critical'!W36)</f>
         <v/>
       </c>
@@ -9452,51 +9453,51 @@
         <f>IF('AOP Critical'!K37="","",'AOP Critical'!K37)</f>
         <v>A</v>
       </c>
-      <c r="K59" s="71" t="str">
+      <c r="K59" s="70" t="str">
         <f>IF('AOP Critical'!L37="","",'AOP Critical'!L37)</f>
         <v>HY</v>
       </c>
-      <c r="L59" s="71" t="str">
+      <c r="L59" s="70" t="str">
         <f>IF('AOP Critical'!M37="","",'AOP Critical'!M37)</f>
         <v>HY</v>
       </c>
-      <c r="M59" s="71" t="str">
+      <c r="M59" s="70" t="str">
         <f>IF('AOP Critical'!N37="","",'AOP Critical'!N37)</f>
         <v>HY</v>
       </c>
-      <c r="N59" s="71">
+      <c r="N59" s="70">
         <f>IF('AOP Critical'!O37="","",'AOP Critical'!O37)</f>
         <v>0.79</v>
       </c>
-      <c r="O59" s="71" t="str">
+      <c r="O59" s="70" t="str">
         <f>IF('AOP Critical'!P37="","",'AOP Critical'!P37)</f>
         <v>HY</v>
       </c>
-      <c r="P59" s="71">
+      <c r="P59" s="70">
         <f>IF('AOP Critical'!Q37="","",'AOP Critical'!Q37)</f>
         <v>0.79</v>
       </c>
-      <c r="Q59" s="71" t="str">
+      <c r="Q59" s="70" t="str">
         <f>IF('AOP Critical'!R37="","",'AOP Critical'!R37)</f>
         <v>HY</v>
       </c>
-      <c r="R59" s="71" t="str">
+      <c r="R59" s="70" t="str">
         <f>IF('AOP Critical'!S37="","",'AOP Critical'!S37)</f>
         <v/>
       </c>
-      <c r="S59" s="71" t="str">
+      <c r="S59" s="70" t="str">
         <f>IF('AOP Critical'!T37="","",'AOP Critical'!T37)</f>
         <v/>
       </c>
-      <c r="T59" s="71" t="str">
+      <c r="T59" s="70" t="str">
         <f>IF('AOP Critical'!U37="","",'AOP Critical'!U37)</f>
         <v/>
       </c>
-      <c r="U59" s="71" t="str">
+      <c r="U59" s="70" t="str">
         <f>IF('AOP Critical'!V37="","",'AOP Critical'!V37)</f>
         <v/>
       </c>
-      <c r="V59" s="71" t="str">
+      <c r="V59" s="70" t="str">
         <f>IF('AOP Critical'!W37="","",'AOP Critical'!W37)</f>
         <v/>
       </c>
@@ -9625,7 +9626,7 @@
       <c r="AA4" s="112"/>
     </row>
     <row r="5" spans="1:27" ht="27" customHeight="1">
-      <c r="A5" s="88" t="s">
+      <c r="A5" s="86" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="35" t="s">
@@ -9642,7 +9643,7 @@
       </c>
       <c r="F5" s="116"/>
       <c r="G5" s="116"/>
-      <c r="H5" s="89" t="s">
+      <c r="H5" s="87" t="s">
         <v>8</v>
       </c>
       <c r="I5" s="35" t="s">
@@ -9793,33 +9794,33 @@
       <c r="L7" s="17">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="M7" s="52">
+      <c r="M7" s="51">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="N7" s="52">
+      <c r="N7" s="51">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="O7" s="52">
+      <c r="O7" s="51">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="P7" s="52">
+      <c r="P7" s="51">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="Q7" s="52">
+      <c r="Q7" s="51">
         <v>0.03</v>
       </c>
-      <c r="R7" s="52">
+      <c r="R7" s="51">
         <v>3.1E-2</v>
       </c>
-      <c r="S7" s="52">
+      <c r="S7" s="51">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="T7" s="52">
+      <c r="T7" s="51">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="U7" s="52"/>
-      <c r="V7" s="52"/>
-      <c r="W7" s="52"/>
+      <c r="U7" s="51"/>
+      <c r="V7" s="51"/>
+      <c r="W7" s="51"/>
       <c r="X7" s="94"/>
       <c r="Y7" s="96"/>
       <c r="Z7" s="96"/>
@@ -9907,33 +9908,33 @@
       <c r="L9" s="19">
         <v>1</v>
       </c>
-      <c r="M9" s="54">
+      <c r="M9" s="53">
         <v>0.75</v>
       </c>
-      <c r="N9" s="54">
+      <c r="N9" s="53">
         <v>0.4</v>
       </c>
-      <c r="O9" s="77">
+      <c r="O9" s="76">
         <v>0</v>
       </c>
-      <c r="P9" s="54">
+      <c r="P9" s="53">
         <v>0</v>
       </c>
-      <c r="Q9" s="54">
+      <c r="Q9" s="53">
         <v>0</v>
       </c>
-      <c r="R9" s="54">
+      <c r="R9" s="53">
         <v>1</v>
       </c>
-      <c r="S9" s="54">
+      <c r="S9" s="53">
         <v>1</v>
       </c>
-      <c r="T9" s="54">
+      <c r="T9" s="53">
         <v>1</v>
       </c>
-      <c r="U9" s="54"/>
-      <c r="V9" s="54"/>
-      <c r="W9" s="54"/>
+      <c r="U9" s="53"/>
+      <c r="V9" s="53"/>
+      <c r="W9" s="53"/>
       <c r="X9" s="94"/>
       <c r="Y9" s="96"/>
       <c r="Z9" s="115"/>
@@ -10019,7 +10020,7 @@
       <c r="L11" s="9">
         <v>2</v>
       </c>
-      <c r="M11" s="55">
+      <c r="M11" s="54">
         <v>1</v>
       </c>
       <c r="N11" s="9">
@@ -10162,7 +10163,9 @@
       <c r="S13" s="19">
         <v>0.81</v>
       </c>
-      <c r="T13" s="19"/>
+      <c r="T13" s="19">
+        <v>0.89</v>
+      </c>
       <c r="U13" s="19"/>
       <c r="V13" s="19"/>
       <c r="W13" s="29"/>
@@ -10171,7 +10174,7 @@
       <c r="Z13" s="96"/>
       <c r="AA13" s="124"/>
     </row>
-    <row r="14" spans="1:27">
+    <row r="14" spans="1:27" ht="15">
       <c r="A14" s="109"/>
       <c r="B14" s="93" t="s">
         <v>68</v>
@@ -10229,10 +10232,10 @@
       <c r="U14" s="38"/>
       <c r="V14" s="38"/>
       <c r="W14" s="38"/>
-      <c r="X14" s="94" t="s">
+      <c r="X14" s="171" t="s">
         <v>71</v>
       </c>
-      <c r="Y14" s="152" t="s">
+      <c r="Y14" s="97" t="s">
         <v>72</v>
       </c>
       <c r="Z14" s="152"/>
@@ -10255,7 +10258,7 @@
       <c r="L15" s="17">
         <v>0.51780000000000004</v>
       </c>
-      <c r="M15" s="52">
+      <c r="M15" s="51">
         <v>0.54100000000000004</v>
       </c>
       <c r="N15" s="17">
@@ -10270,13 +10273,13 @@
       <c r="Q15" s="17">
         <v>0.53800000000000003</v>
       </c>
-      <c r="R15" s="79">
+      <c r="R15" s="78">
         <v>0.53600000000000003</v>
       </c>
-      <c r="S15" s="79">
+      <c r="S15" s="78">
         <v>0.5363</v>
       </c>
-      <c r="T15" s="79">
+      <c r="T15" s="78">
         <v>0.53749999999999998</v>
       </c>
       <c r="U15" s="32"/>
@@ -10335,25 +10338,23 @@
       <c r="Q16" s="38">
         <v>0.11814554963094943</v>
       </c>
-      <c r="R16" s="83">
+      <c r="R16" s="82">
         <v>0.13344842106998206</v>
       </c>
-      <c r="S16" s="83">
+      <c r="S16" s="82">
         <v>0.13972119594175969</v>
       </c>
-      <c r="T16" s="25"/>
+      <c r="T16" s="82">
+        <v>0.13600000000000001</v>
+      </c>
       <c r="U16" s="25"/>
       <c r="V16" s="25"/>
       <c r="W16" s="26"/>
-      <c r="X16" s="94" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y16" s="95" t="s">
-        <v>78</v>
-      </c>
+      <c r="X16" s="94"/>
+      <c r="Y16" s="95"/>
       <c r="Z16" s="115"/>
       <c r="AA16" s="123" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -10373,7 +10374,7 @@
       <c r="L17" s="17">
         <v>-4.253311543933095E-2</v>
       </c>
-      <c r="M17" s="52">
+      <c r="M17" s="51">
         <v>7.8013174622509063E-2</v>
       </c>
       <c r="N17" s="17">
@@ -10394,7 +10395,9 @@
       <c r="S17" s="17">
         <v>0.12649723977955013</v>
       </c>
-      <c r="T17" s="19"/>
+      <c r="T17" s="17">
+        <v>0.14699999999999999</v>
+      </c>
       <c r="U17" s="19"/>
       <c r="V17" s="19"/>
       <c r="W17" s="29"/>
@@ -10406,13 +10409,13 @@
     <row r="18" spans="1:27">
       <c r="A18" s="109"/>
       <c r="B18" s="93" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C18" s="93" t="s">
         <v>74</v>
       </c>
       <c r="D18" s="93" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E18" s="108" t="s">
         <v>76</v>
@@ -10423,7 +10426,7 @@
         <v>32</v>
       </c>
       <c r="I18" s="108" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J18" s="107" t="s">
         <v>52</v>
@@ -10432,38 +10435,37 @@
         <v>53</v>
       </c>
       <c r="L18" s="48">
-        <v>0.254</v>
+        <v>0.224</v>
       </c>
       <c r="M18" s="48">
-        <v>0.44800000000000001</v>
+        <v>0.35800000000000004</v>
       </c>
       <c r="N18" s="48">
-        <f>0.254+0.194+0.519</f>
-        <v>0.96700000000000008</v>
+        <v>0.79700000000000004</v>
       </c>
       <c r="O18" s="48">
-        <v>1.331</v>
+        <v>1.0409999999999999</v>
       </c>
       <c r="P18" s="48">
-        <v>1.595</v>
+        <v>1.155</v>
       </c>
       <c r="Q18" s="48">
-        <v>2.1840000000000002</v>
+        <v>1.6040000000000001</v>
       </c>
       <c r="R18" s="48">
-        <v>3.0979999999999999</v>
+        <v>2.4180000000000001</v>
       </c>
       <c r="S18" s="48">
-        <v>3.7</v>
+        <v>2.93</v>
       </c>
       <c r="T18" s="48">
-        <v>4.5439999999999996</v>
+        <v>3.7040000000000002</v>
       </c>
       <c r="U18" s="48"/>
       <c r="V18" s="48"/>
       <c r="W18" s="48"/>
       <c r="X18" s="157" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="Y18" s="157"/>
       <c r="Z18" s="154">
@@ -10485,36 +10487,36 @@
       <c r="K19" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="L19" s="49">
-        <v>0.28899999999999998</v>
-      </c>
-      <c r="M19" s="9">
-        <v>0.46800000000000003</v>
-      </c>
-      <c r="N19" s="49">
-        <v>1.2749999999999999</v>
-      </c>
-      <c r="O19" s="49">
-        <v>1.5509999999999999</v>
-      </c>
-      <c r="P19" s="49">
-        <v>1.9910000000000001</v>
-      </c>
-      <c r="Q19" s="49">
-        <v>2.5489999999999999</v>
-      </c>
-      <c r="R19" s="86">
-        <v>3.0990000000000002</v>
-      </c>
-      <c r="S19" s="86">
-        <v>3.895</v>
-      </c>
-      <c r="T19" s="86">
-        <v>5.0119999999999996</v>
+      <c r="L19" s="88">
+        <v>0.2598381666666667</v>
+      </c>
+      <c r="M19" s="88">
+        <v>0.3838381666666667</v>
+      </c>
+      <c r="N19" s="88">
+        <v>1.1128381666666667</v>
+      </c>
+      <c r="O19" s="88">
+        <v>1.3223861666666668</v>
+      </c>
+      <c r="P19" s="88">
+        <v>1.6513861666666667</v>
+      </c>
+      <c r="Q19" s="88">
+        <v>2.1303861666666668</v>
+      </c>
+      <c r="R19" s="89">
+        <v>2.6433861666666667</v>
+      </c>
+      <c r="S19" s="89">
+        <v>3.3972231666666666</v>
+      </c>
+      <c r="T19" s="89">
+        <v>4.5205241666666662</v>
       </c>
       <c r="U19" s="47"/>
       <c r="V19" s="47"/>
-      <c r="W19" s="50"/>
+      <c r="W19" s="49"/>
       <c r="X19" s="157"/>
       <c r="Y19" s="157"/>
       <c r="Z19" s="155"/>
@@ -10523,13 +10525,13 @@
     <row r="20" spans="1:27" ht="24" customHeight="1">
       <c r="A20" s="109"/>
       <c r="B20" s="93" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C20" s="93" t="s">
         <v>65</v>
       </c>
       <c r="D20" s="90" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E20" s="108" t="s">
         <v>76</v>
@@ -10572,19 +10574,21 @@
       <c r="S20" s="18">
         <v>0.23</v>
       </c>
-      <c r="T20" s="18"/>
+      <c r="T20" s="18">
+        <v>0.25</v>
+      </c>
       <c r="U20" s="18"/>
       <c r="V20" s="18"/>
       <c r="W20" s="28"/>
       <c r="X20" s="99" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="Y20" s="101" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="Z20" s="153"/>
       <c r="AA20" s="125" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="32.1" customHeight="1" thickBot="1">
@@ -10625,7 +10629,9 @@
       <c r="S21" s="30">
         <v>0.3</v>
       </c>
-      <c r="T21" s="30"/>
+      <c r="T21" s="30">
+        <v>0.27</v>
+      </c>
       <c r="U21" s="30"/>
       <c r="V21" s="30"/>
       <c r="W21" s="31"/>
@@ -10639,13 +10645,13 @@
         <v>26</v>
       </c>
       <c r="B22" s="93" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" s="122" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" s="93" t="s">
         <v>89</v>
-      </c>
-      <c r="C22" s="122" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22" s="93" t="s">
-        <v>91</v>
       </c>
       <c r="E22" s="108">
         <v>90</v>
@@ -10721,10 +10727,10 @@
       <c r="K23" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="L23" s="56">
+      <c r="L23" s="55">
         <v>0.81</v>
       </c>
-      <c r="M23" s="56">
+      <c r="M23" s="55">
         <v>0.78</v>
       </c>
       <c r="N23" s="19">
@@ -10745,7 +10751,9 @@
       <c r="S23" s="30">
         <v>0.94</v>
       </c>
-      <c r="T23" s="30"/>
+      <c r="T23" s="30">
+        <v>0.91</v>
+      </c>
       <c r="U23" s="30"/>
       <c r="V23" s="30"/>
       <c r="W23" s="31"/>
@@ -10759,22 +10767,22 @@
         <v>27</v>
       </c>
       <c r="B24" s="93" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="122" t="s">
+        <v>91</v>
+      </c>
+      <c r="D24" s="90" t="s">
         <v>92</v>
       </c>
-      <c r="C24" s="122" t="s">
+      <c r="E24" s="108" t="s">
         <v>93</v>
       </c>
-      <c r="D24" s="90" t="s">
-        <v>94</v>
-      </c>
-      <c r="E24" s="108" t="s">
-        <v>95</v>
-      </c>
       <c r="F24" s="108" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G24" s="108" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H24" s="111" t="s">
         <v>32</v>
@@ -10794,33 +10802,33 @@
         <v>0.104</v>
       </c>
       <c r="O24" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="P24" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q24" s="38">
         <v>0.11799999999999999</v>
       </c>
       <c r="R24" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="S24" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="T24" s="36"/>
       <c r="U24" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="V24" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="W24" s="39"/>
       <c r="X24" s="137"/>
       <c r="Y24" s="152"/>
       <c r="Z24" s="119"/>
       <c r="AA24" s="123" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="15" thickBot="1">
@@ -10838,37 +10846,37 @@
         <v>55</v>
       </c>
       <c r="L25" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M25" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="N25" s="52">
+        <v>94</v>
+      </c>
+      <c r="N25" s="51">
         <v>0.115</v>
       </c>
       <c r="O25" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="P25" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q25" s="17">
         <v>0.121</v>
       </c>
       <c r="R25" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="S25" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="T25" s="57"/>
+        <v>94</v>
+      </c>
+      <c r="T25" s="56"/>
       <c r="U25" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="V25" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="W25" s="57"/>
+        <v>94</v>
+      </c>
+      <c r="W25" s="56"/>
       <c r="X25" s="106"/>
       <c r="Y25" s="113"/>
       <c r="Z25" s="153"/>
@@ -10877,13 +10885,13 @@
     <row r="26" spans="1:27" ht="14.45" customHeight="1">
       <c r="A26" s="167"/>
       <c r="B26" s="91" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C26" s="160" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D26" s="90" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E26" s="108">
         <v>34</v>
@@ -10936,7 +10944,7 @@
       <c r="Y26" s="96"/>
       <c r="Z26" s="115"/>
       <c r="AA26" s="123" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:27" ht="14.45" customHeight="1" thickBot="1">
@@ -10953,10 +10961,10 @@
       <c r="K27" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="L27" s="80">
+      <c r="L27" s="79">
         <v>0.318</v>
       </c>
-      <c r="M27" s="52">
+      <c r="M27" s="51">
         <v>0.35799999999999998</v>
       </c>
       <c r="N27" s="17">
@@ -10974,11 +10982,11 @@
       <c r="R27" s="17">
         <v>0.39900000000000002</v>
       </c>
-      <c r="S27" s="19">
-        <v>0.35</v>
-      </c>
-      <c r="T27" s="19">
-        <v>0.35</v>
+      <c r="S27" s="17">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="T27" s="17">
+        <v>0.42299999999999999</v>
       </c>
       <c r="U27" s="19"/>
       <c r="V27" s="19"/>
@@ -10991,13 +10999,13 @@
     <row r="28" spans="1:27" ht="14.45" customHeight="1">
       <c r="A28" s="167"/>
       <c r="B28" s="90" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C28" s="93" t="s">
         <v>74</v>
       </c>
       <c r="D28" s="90" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E28" s="108" t="s">
         <v>76</v>
@@ -11034,23 +11042,25 @@
       <c r="Q28" s="38" vm="14">
         <v>0.29754592225545773</v>
       </c>
-      <c r="R28" s="83" vm="18">
+      <c r="R28" s="82" vm="18">
         <v>0.26300517799117751</v>
       </c>
-      <c r="S28" s="83" vm="22">
+      <c r="S28" s="82" vm="22">
         <v>0.30756202137510114</v>
       </c>
-      <c r="T28" s="25"/>
+      <c r="T28" s="82">
+        <v>0.38100000000000001</v>
+      </c>
       <c r="U28" s="25"/>
       <c r="V28" s="25"/>
       <c r="W28" s="26"/>
       <c r="X28" s="103" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Y28" s="97"/>
       <c r="Z28" s="119"/>
       <c r="AA28" s="128" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:27" ht="15" thickBot="1">
@@ -11070,7 +11080,7 @@
       <c r="L29" s="17" vm="2">
         <v>-0.21537837470975407</v>
       </c>
-      <c r="M29" s="51">
+      <c r="M29" s="50">
         <v>0.27400000000000002</v>
       </c>
       <c r="N29" s="17" vm="7">
@@ -11091,7 +11101,9 @@
       <c r="S29" s="17" vm="23">
         <v>0.28426058124592513</v>
       </c>
-      <c r="T29" s="19"/>
+      <c r="T29" s="17">
+        <v>0.378</v>
+      </c>
       <c r="U29" s="19"/>
       <c r="V29" s="19"/>
       <c r="W29" s="29"/>
@@ -11107,7 +11119,7 @@
         <v>74</v>
       </c>
       <c r="D30" s="90" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E30" s="108" t="s">
         <v>76</v>
@@ -11144,13 +11156,15 @@
       <c r="Q30" s="38" vm="16">
         <v>0.12551463489599346</v>
       </c>
-      <c r="R30" s="83" vm="20">
+      <c r="R30" s="82" vm="20">
         <v>0.10280225768958351</v>
       </c>
-      <c r="S30" s="83">
+      <c r="S30" s="82">
         <v>0.13500000000000001</v>
       </c>
-      <c r="T30" s="25"/>
+      <c r="T30" s="82">
+        <v>0.11600000000000001</v>
+      </c>
       <c r="U30" s="25"/>
       <c r="V30" s="25"/>
       <c r="W30" s="26"/>
@@ -11176,7 +11190,7 @@
       <c r="L31" s="17">
         <v>0.32500000000000001</v>
       </c>
-      <c r="M31" s="52" vm="5">
+      <c r="M31" s="51" vm="5">
         <v>0.19016698273293486</v>
       </c>
       <c r="N31" s="17" vm="9">
@@ -11191,13 +11205,15 @@
       <c r="Q31" s="17" vm="17">
         <v>0.15714973912715791</v>
       </c>
-      <c r="R31" s="84" vm="21">
+      <c r="R31" s="83" vm="21">
         <v>0.10382365349216505</v>
       </c>
-      <c r="S31" s="84">
+      <c r="S31" s="83">
         <v>0.151</v>
       </c>
-      <c r="T31" s="45"/>
+      <c r="T31" s="83">
+        <v>0.17799999999999999</v>
+      </c>
       <c r="U31" s="45"/>
       <c r="V31" s="45"/>
       <c r="W31" s="46"/>
@@ -11209,13 +11225,13 @@
     <row r="32" spans="1:27" ht="14.45" customHeight="1">
       <c r="A32" s="167"/>
       <c r="B32" s="93" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C32" s="122" t="s">
         <v>65</v>
       </c>
       <c r="D32" s="90" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E32" s="108" t="s">
         <v>76</v>
@@ -11226,7 +11242,7 @@
         <v>32</v>
       </c>
       <c r="I32" s="108" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J32" s="107" t="s">
         <v>52</v>
@@ -11243,34 +11259,36 @@
       <c r="N32" s="42">
         <v>24.179069699999999</v>
       </c>
-      <c r="O32" s="66">
+      <c r="O32" s="65">
         <v>33.551317699999998</v>
       </c>
       <c r="P32" s="42">
         <v>41.442849800000005</v>
       </c>
-      <c r="Q32" s="81">
+      <c r="Q32" s="80">
         <v>60.823965100000009</v>
       </c>
       <c r="R32" s="8">
         <v>72.599999999999994</v>
       </c>
-      <c r="S32" s="87">
+      <c r="S32" s="85">
         <v>82.449704499999996</v>
       </c>
-      <c r="T32" s="8"/>
+      <c r="T32" s="8">
+        <v>97.4</v>
+      </c>
       <c r="U32" s="8"/>
       <c r="V32" s="8"/>
       <c r="W32" s="34"/>
       <c r="X32" s="169" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="Y32" s="97" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="Z32" s="119"/>
       <c r="AA32" s="123" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:29" ht="15.6" customHeight="1" thickBot="1">
@@ -11290,28 +11308,30 @@
       <c r="L33" s="43">
         <v>4.05</v>
       </c>
-      <c r="M33" s="53">
+      <c r="M33" s="52">
         <v>9.7989724000000002</v>
       </c>
       <c r="N33" s="43">
         <v>25.313448100000002</v>
       </c>
-      <c r="O33" s="67">
+      <c r="O33" s="66">
         <v>31.452557499999998</v>
       </c>
       <c r="P33" s="43">
         <v>41.128122899999994</v>
       </c>
-      <c r="Q33" s="82">
+      <c r="Q33" s="81">
         <v>55.164574999999999</v>
       </c>
-      <c r="R33" s="85">
+      <c r="R33" s="84">
         <v>61.940289700000001</v>
       </c>
-      <c r="S33" s="85">
+      <c r="S33" s="84">
         <v>72.779408199999978</v>
       </c>
-      <c r="T33" s="32"/>
+      <c r="T33" s="32">
+        <v>91.2</v>
+      </c>
       <c r="U33" s="32"/>
       <c r="V33" s="32"/>
       <c r="W33" s="33"/>
@@ -11328,7 +11348,7 @@
         <v>29</v>
       </c>
       <c r="C34" s="93" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D34" s="90" t="s">
         <v>31</v>
@@ -11371,10 +11391,12 @@
         <v>0.9</v>
       </c>
       <c r="X34" s="94"/>
-      <c r="Y34" s="96"/>
+      <c r="Y34" s="96" t="s">
+        <v>109</v>
+      </c>
       <c r="Z34" s="115"/>
       <c r="AA34" s="123" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -11392,30 +11414,32 @@
         <v>55</v>
       </c>
       <c r="L35" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M35" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N35" s="19">
         <v>1</v>
       </c>
       <c r="O35" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="P35" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q35" s="19">
         <v>0.96199999999999997</v>
       </c>
       <c r="R35" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="S35" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="T35" s="19"/>
+        <v>94</v>
+      </c>
+      <c r="T35" s="19">
+        <v>0.91300000000000003</v>
+      </c>
       <c r="U35" s="19"/>
       <c r="V35" s="19"/>
       <c r="W35" s="29"/>
@@ -11430,7 +11454,7 @@
         <v>35</v>
       </c>
       <c r="C36" s="93" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D36" s="90" t="s">
         <v>37</v>
@@ -11469,14 +11493,14 @@
       <c r="V36" s="18"/>
       <c r="W36" s="28"/>
       <c r="X36" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y36" s="95" t="s">
         <v>113</v>
-      </c>
-      <c r="Y36" s="95" t="s">
-        <v>114</v>
       </c>
       <c r="Z36" s="115"/>
       <c r="AA36" s="123" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -11494,31 +11518,31 @@
         <v>55</v>
       </c>
       <c r="L37" s="22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M37" s="22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N37" s="22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O37" s="19">
         <v>0.79</v>
       </c>
       <c r="P37" s="22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q37" s="19">
         <v>0.79</v>
       </c>
       <c r="R37" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="S37" s="58"/>
-      <c r="T37" s="58"/>
-      <c r="U37" s="58"/>
-      <c r="V37" s="58"/>
-      <c r="W37" s="59"/>
+        <v>115</v>
+      </c>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="57"/>
+      <c r="V37" s="57"/>
+      <c r="W37" s="58"/>
       <c r="X37" s="137"/>
       <c r="Y37" s="97"/>
       <c r="Z37" s="119"/>
@@ -11555,10 +11579,10 @@
     </row>
     <row r="39" spans="1:29" s="5" customFormat="1" ht="23.45">
       <c r="A39" s="141" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B39" s="141"/>
-      <c r="C39" s="60"/>
+      <c r="C39" s="59"/>
       <c r="D39"/>
       <c r="E39"/>
       <c r="F39"/>
@@ -11589,7 +11613,7 @@
         <v>0</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>3</v>
@@ -11598,13 +11622,13 @@
         <v>4</v>
       </c>
       <c r="E40" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="F40" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F40" s="10" t="s">
+      <c r="G40" s="10" t="s">
         <v>120</v>
-      </c>
-      <c r="G40" s="10" t="s">
-        <v>121</v>
       </c>
       <c r="H40" s="10" t="s">
         <v>8</v>
@@ -11625,7 +11649,7 @@
         <v>13</v>
       </c>
       <c r="N40" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O40" s="10" t="s">
         <v>15</v>
@@ -11634,7 +11658,7 @@
         <v>16</v>
       </c>
       <c r="Q40" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R40" s="10" t="s">
         <v>18</v>
@@ -11654,7 +11678,7 @@
       <c r="W40" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="X40" s="62" t="s">
+      <c r="X40" s="61" t="s">
         <v>43</v>
       </c>
       <c r="Y40" s="10" t="s">
@@ -11672,22 +11696,22 @@
         <v>47</v>
       </c>
       <c r="B41" s="145" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C41" s="146" t="s">
         <v>49</v>
       </c>
       <c r="D41" s="147" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E41" s="140" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F41" s="140" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G41" s="140" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H41" s="159" t="s">
         <v>51</v>
@@ -11698,50 +11722,50 @@
       <c r="J41" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="K41" s="63" t="s">
+      <c r="K41" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="L41" s="78">
+      <c r="L41" s="77">
         <v>1.9099999999999999E-2</v>
       </c>
-      <c r="M41" s="78">
+      <c r="M41" s="77">
         <v>4.07E-2</v>
       </c>
-      <c r="N41" s="78">
+      <c r="N41" s="77">
         <v>4.6199999999999998E-2</v>
       </c>
-      <c r="O41" s="78">
+      <c r="O41" s="77">
         <v>3.8600000000000002E-2</v>
       </c>
-      <c r="P41" s="78">
+      <c r="P41" s="77">
         <v>3.5299999999999998E-2</v>
       </c>
-      <c r="Q41" s="64">
+      <c r="Q41" s="63">
         <v>2.7099999999999999E-2</v>
       </c>
-      <c r="R41" s="64">
+      <c r="R41" s="63">
         <v>2.5100000000000001E-2</v>
       </c>
-      <c r="S41" s="64">
+      <c r="S41" s="63">
         <v>2.41E-2</v>
       </c>
-      <c r="T41" s="64">
+      <c r="T41" s="63">
         <v>3.1600000000000003E-2</v>
       </c>
-      <c r="U41" s="64">
+      <c r="U41" s="63">
         <v>3.1099999999999999E-2</v>
       </c>
-      <c r="V41" s="64">
+      <c r="V41" s="63">
         <v>3.5700000000000003E-2</v>
       </c>
-      <c r="W41" s="65">
+      <c r="W41" s="64">
         <v>3.32E-2</v>
       </c>
       <c r="X41" s="136"/>
       <c r="Y41" s="131"/>
       <c r="Z41" s="131"/>
       <c r="AA41" s="124" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AC41" s="12"/>
     </row>
@@ -11759,36 +11783,36 @@
       <c r="K42" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="L42" s="57">
+      <c r="L42" s="56">
         <v>9.1999999999999998E-3</v>
       </c>
-      <c r="M42" s="57">
+      <c r="M42" s="56">
         <v>1.5800000000000002E-2</v>
       </c>
-      <c r="N42" s="57">
+      <c r="N42" s="56">
         <v>1.7600000000000001E-2</v>
       </c>
-      <c r="O42" s="57">
+      <c r="O42" s="56">
         <v>1.5800000000000002E-2</v>
       </c>
-      <c r="P42" s="57">
+      <c r="P42" s="56">
         <v>8.6E-3</v>
       </c>
-      <c r="Q42" s="57">
+      <c r="Q42" s="56">
         <v>1.2699999999999999E-2</v>
       </c>
-      <c r="R42" s="57">
+      <c r="R42" s="56">
         <v>1.3299999999999999E-2</v>
       </c>
-      <c r="S42" s="57">
+      <c r="S42" s="56">
         <v>1.3899999999999999E-2</v>
       </c>
-      <c r="T42" s="57">
+      <c r="T42" s="56">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="U42" s="57"/>
-      <c r="V42" s="57"/>
-      <c r="W42" s="61"/>
+      <c r="U42" s="56"/>
+      <c r="V42" s="56"/>
+      <c r="W42" s="60"/>
       <c r="X42" s="136"/>
       <c r="Y42" s="131"/>
       <c r="Z42" s="131"/>
@@ -11799,22 +11823,22 @@
         <v>26</v>
       </c>
       <c r="B43" s="91" t="s">
+        <v>125</v>
+      </c>
+      <c r="C43" s="92" t="s">
+        <v>91</v>
+      </c>
+      <c r="D43" s="90" t="s">
         <v>126</v>
       </c>
-      <c r="C43" s="92" t="s">
+      <c r="E43" s="108" t="s">
         <v>93</v>
       </c>
-      <c r="D43" s="90" t="s">
-        <v>127</v>
-      </c>
-      <c r="E43" s="108" t="s">
-        <v>95</v>
-      </c>
       <c r="F43" s="108" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G43" s="108" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H43" s="111" t="s">
         <v>32</v>
@@ -11845,14 +11869,14 @@
       <c r="V43" s="36"/>
       <c r="W43" s="39"/>
       <c r="X43" s="130" t="s">
+        <v>127</v>
+      </c>
+      <c r="Y43" s="132" t="s">
         <v>128</v>
-      </c>
-      <c r="Y43" s="132" t="s">
-        <v>129</v>
       </c>
       <c r="Z43" s="133"/>
       <c r="AA43" s="134" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="44" spans="1:29">
@@ -11870,37 +11894,37 @@
         <v>55</v>
       </c>
       <c r="L44" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M44" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N44" s="17">
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="O44" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="P44" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q44" s="17">
         <v>0.04</v>
       </c>
       <c r="R44" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="S44" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="T44" s="57"/>
+        <v>94</v>
+      </c>
+      <c r="T44" s="56"/>
       <c r="U44" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="V44" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="W44" s="57"/>
+        <v>94</v>
+      </c>
+      <c r="W44" s="56"/>
       <c r="X44" s="130"/>
       <c r="Y44" s="132"/>
       <c r="Z44" s="133"/>
@@ -11909,22 +11933,22 @@
     <row r="45" spans="1:29">
       <c r="A45" s="144"/>
       <c r="B45" s="91" t="s">
+        <v>130</v>
+      </c>
+      <c r="C45" s="92" t="s">
+        <v>91</v>
+      </c>
+      <c r="D45" s="90" t="s">
         <v>131</v>
       </c>
-      <c r="C45" s="92" t="s">
+      <c r="E45" s="108" t="s">
         <v>93</v>
       </c>
-      <c r="D45" s="90" t="s">
-        <v>132</v>
-      </c>
-      <c r="E45" s="108" t="s">
-        <v>95</v>
-      </c>
       <c r="F45" s="108" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G45" s="108" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H45" s="111" t="s">
         <v>32</v>
@@ -11959,20 +11983,24 @@
       <c r="R45" s="36">
         <v>0.4</v>
       </c>
-      <c r="S45" s="36"/>
-      <c r="T45" s="36"/>
+      <c r="S45" s="36">
+        <v>0.4</v>
+      </c>
+      <c r="T45" s="36">
+        <v>0.4</v>
+      </c>
       <c r="U45" s="36"/>
       <c r="V45" s="36"/>
       <c r="W45" s="39"/>
       <c r="X45" s="130"/>
       <c r="Y45" s="132" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Z45" s="135">
         <v>46188</v>
       </c>
       <c r="AA45" s="126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="46" spans="1:29" ht="16.5" customHeight="1">
@@ -12027,28 +12055,28 @@
     <row r="47" spans="1:29">
       <c r="A47" s="144"/>
       <c r="B47" s="91" t="s">
+        <v>133</v>
+      </c>
+      <c r="C47" s="92" t="s">
+        <v>88</v>
+      </c>
+      <c r="D47" s="90" t="s">
         <v>134</v>
       </c>
-      <c r="C47" s="92" t="s">
-        <v>90</v>
-      </c>
-      <c r="D47" s="90" t="s">
-        <v>135</v>
-      </c>
       <c r="E47" s="108" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F47" s="108" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G47" s="108" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H47" s="111" t="s">
         <v>32</v>
       </c>
       <c r="I47" s="108" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J47" s="127" t="s">
         <v>52</v>
@@ -12096,7 +12124,7 @@
       <c r="Y47" s="133"/>
       <c r="Z47" s="133"/>
       <c r="AA47" s="90" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="48" spans="1:29" ht="20.45" customHeight="1">
@@ -12138,7 +12166,9 @@
       <c r="S48" s="9">
         <v>51.9</v>
       </c>
-      <c r="T48" s="9"/>
+      <c r="T48" s="9">
+        <v>55.8</v>
+      </c>
       <c r="U48" s="9"/>
       <c r="V48" s="9"/>
       <c r="W48" s="27"/>
@@ -12149,25 +12179,25 @@
     </row>
     <row r="49" spans="1:27">
       <c r="A49" s="143" t="s">
+        <v>136</v>
+      </c>
+      <c r="B49" s="150" t="s">
         <v>137</v>
-      </c>
-      <c r="B49" s="150" t="s">
-        <v>138</v>
       </c>
       <c r="C49" s="92" t="s">
         <v>69</v>
       </c>
       <c r="D49" s="90" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E49" s="108">
         <v>74</v>
       </c>
       <c r="F49" s="108" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G49" s="108" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H49" s="111" t="s">
         <v>32</v>
@@ -12221,7 +12251,7 @@
       <c r="Y49" s="132"/>
       <c r="Z49" s="133"/>
       <c r="AA49" s="126" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="50" spans="1:27">
@@ -12267,7 +12297,7 @@
       </c>
       <c r="U50" s="17"/>
       <c r="V50" s="17"/>
-      <c r="W50" s="76"/>
+      <c r="W50" s="75"/>
       <c r="X50" s="130"/>
       <c r="Y50" s="132"/>
       <c r="Z50" s="133"/>
@@ -12278,22 +12308,22 @@
         <v>25</v>
       </c>
       <c r="B51" s="91" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C51" s="92" t="s">
         <v>74</v>
       </c>
       <c r="D51" s="90" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E51" s="108">
         <v>33.1</v>
       </c>
       <c r="F51" s="108" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G51" s="108" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H51" s="111" t="s">
         <v>32</v>
@@ -12331,7 +12361,9 @@
       <c r="S51" s="38">
         <v>0.33943248102419393</v>
       </c>
-      <c r="T51" s="36"/>
+      <c r="T51" s="38">
+        <v>0.33082830926903184</v>
+      </c>
       <c r="U51" s="36"/>
       <c r="V51" s="36"/>
       <c r="W51" s="39"/>
@@ -12339,7 +12371,7 @@
       <c r="Y51" s="133"/>
       <c r="Z51" s="133"/>
       <c r="AA51" s="93" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="52" spans="1:27" ht="15" thickBot="1">
@@ -12371,16 +12403,18 @@
       <c r="P52" s="17">
         <v>0.40747704161607318</v>
       </c>
-      <c r="Q52" s="79">
+      <c r="Q52" s="78">
         <v>0.36849551470072495</v>
       </c>
-      <c r="R52" s="79">
+      <c r="R52" s="78">
         <v>0.35573521911109235</v>
       </c>
-      <c r="S52" s="79">
+      <c r="S52" s="78">
         <v>0.36691053201149237</v>
       </c>
-      <c r="T52" s="30"/>
+      <c r="T52" s="78">
+        <v>0.36899999999999999</v>
+      </c>
       <c r="U52" s="30"/>
       <c r="V52" s="30"/>
       <c r="W52" s="31"/>
@@ -12716,34 +12750,34 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L27">
-    <cfRule type="expression" dxfId="66" priority="78">
+    <cfRule type="expression" dxfId="66" priority="81" stopIfTrue="1">
+      <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&gt;=L26)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="65" priority="80">
+      <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&lt;L26)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="79">
+      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&lt;=L26)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="63" priority="78">
       <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&gt;L26)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="79">
-      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&lt;=L26)</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L7:W7 L9:W9 L11:W11 L13:W13 L15:W15 L17:W17 L19:W19 L21:W21 L23:W23 M27:W27 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37">
+    <cfRule type="expression" dxfId="62" priority="249">
+      <formula xml:space="preserve"> AND(OR($H6="Higher the better", $H6="Higher the Better"), L7&gt;= L6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="80">
-      <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&lt;L26)</formula>
+    <cfRule type="expression" dxfId="61" priority="74">
+      <formula>AND(OR($H6="Lower the better", $H6="Lower the better"), L7&gt; L6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="81" stopIfTrue="1">
-      <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&gt;=L26)</formula>
+    <cfRule type="expression" dxfId="60" priority="247">
+      <formula>AND(OR($H6="Lower the better", $H6= "Lower the Better"), L7 &lt;= L6)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="59" priority="248">
+      <formula>AND(OR($H6="Higher the better", $H6="Higher the Better"), L7 &lt; L6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L7:W7 L9:W9 L11:W11 L13:W13 L17:W17 L19:W19 L21:W21 L23:W23 M27:W27 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37 L15:W15">
-    <cfRule type="expression" dxfId="62" priority="74">
-      <formula>AND(OR($H6="Lower the better", $H6="Lower the better"), L7&gt; L6)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="61" priority="247">
-      <formula>AND(OR($H6="Lower the better", $H6= "Lower the Better"), L7 &lt;= L6)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="60" priority="248">
-      <formula>AND(OR($H6="Higher the better", $H6="Higher the Better"), L7 &lt; L6)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="59" priority="249">
-      <formula xml:space="preserve"> AND(OR($H6="Higher the better", $H6="Higher the Better"), L7&gt;= L6)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L7:W7 L9:W9 L11:W11 L13:W13 L17:W17 L19:W19 L21:W21 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37 L15:W15 L23:W27">
+  <conditionalFormatting sqref="L23:W27 L7:W7 L9:W9 L11:W11 L13:W13 L15:W15 L17:W17 L19:W19 L21:W21 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37">
     <cfRule type="containsBlanks" dxfId="58" priority="245">
       <formula>LEN(TRIM(L7))=0</formula>
     </cfRule>
@@ -12757,185 +12791,185 @@
     <cfRule type="containsBlanks" dxfId="56" priority="173">
       <formula>LEN(TRIM(L46))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="175">
+    <cfRule type="expression" dxfId="55" priority="177">
+      <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&lt;L45)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="54" priority="175">
       <formula>AND(OR($H45="Lower the better", $H45="Lower the Better"), L46&gt;L45)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="176">
+    <cfRule type="expression" dxfId="53" priority="176">
       <formula>AND(OR($H45="Lower the better", $H45="Lower the Better"), L46&lt;=L45)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="53" priority="177">
-      <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&lt;L45)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="52" priority="178" stopIfTrue="1">
       <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&gt;=L45)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L52:W52">
-    <cfRule type="containsBlanks" dxfId="51" priority="104">
+    <cfRule type="expression" dxfId="51" priority="107">
+      <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&lt;L51)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="50" priority="106">
+      <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&lt;=L51)</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="49" priority="104">
       <formula>LEN(TRIM(L52))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="105">
+    <cfRule type="expression" dxfId="48" priority="105">
       <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&gt;L51)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="49" priority="106">
-      <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&lt;=L51)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="107">
-      <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&lt;L51)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="47" priority="108" stopIfTrue="1">
       <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&gt;=L51)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25 T25 W25 L42:W42">
-    <cfRule type="containsBlanks" dxfId="46" priority="67">
+    <cfRule type="expression" dxfId="46" priority="71" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&gt;=L24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="45" priority="70">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&lt;L24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="68">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&gt;L24)</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="43" priority="67">
       <formula>LEN(TRIM(L25))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="68">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&gt;L24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="44" priority="69">
+    <cfRule type="expression" dxfId="42" priority="69">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&lt;=L24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="43" priority="70">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&lt;L24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="71" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&gt;=L24)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25">
-    <cfRule type="containsBlanks" dxfId="41" priority="16">
-      <formula>LEN(TRIM(N25))=0</formula>
+    <cfRule type="expression" dxfId="41" priority="18">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="40" priority="17">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&gt;N24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="18">
+    <cfRule type="containsBlanks" dxfId="39" priority="16">
+      <formula>LEN(TRIM(N25))=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="25" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="22">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&gt;N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="24">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="35" priority="21">
+      <formula>LEN(TRIM(N25))=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="20" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="23">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="19">
+    <cfRule type="expression" dxfId="32" priority="19">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="37" priority="20" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="36" priority="21">
-      <formula>LEN(TRIM(N25))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="35" priority="22">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&gt;N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="23">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="24">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="25" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N44">
-    <cfRule type="containsBlanks" dxfId="31" priority="62">
+    <cfRule type="expression" dxfId="31" priority="65">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&lt;N43)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="66" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&gt;=N43)</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="29" priority="62">
       <formula>LEN(TRIM(N44))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="63">
+    <cfRule type="expression" dxfId="28" priority="63">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&gt;N43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="64">
+    <cfRule type="expression" dxfId="27" priority="64">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&lt;=N43)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="65">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&lt;N43)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="66" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&gt;=N43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q25">
-    <cfRule type="containsBlanks" dxfId="26" priority="26">
-      <formula>LEN(TRIM(Q25))=0</formula>
+    <cfRule type="expression" dxfId="26" priority="30" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&gt;=Q24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="27">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&gt;Q24)</formula>
+    <cfRule type="expression" dxfId="25" priority="29">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&lt;Q24)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="24" priority="28">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&lt;=Q24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="29">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&lt;Q24)</formula>
+    <cfRule type="expression" dxfId="23" priority="27">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&gt;Q24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="30" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&gt;=Q24)</formula>
+    <cfRule type="containsBlanks" dxfId="22" priority="26">
+      <formula>LEN(TRIM(Q25))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q37">
-    <cfRule type="expression" dxfId="21" priority="6">
-      <formula>AND(OR($H36="Lower the better", $H36="Lower the better"), Q37&gt; Q36)</formula>
+    <cfRule type="expression" dxfId="21" priority="10">
+      <formula xml:space="preserve"> AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37&gt;= Q36)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="20" priority="7">
-      <formula>LEN(TRIM(Q37))=0</formula>
+    <cfRule type="expression" dxfId="20" priority="9">
+      <formula>AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37 &lt; Q36)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="8">
       <formula>AND(OR($H36="Lower the better", $H36= "Lower the Better"), Q37 &lt;= Q36)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="9">
-      <formula>AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37 &lt; Q36)</formula>
+    <cfRule type="expression" dxfId="18" priority="6">
+      <formula>AND(OR($H36="Lower the better", $H36="Lower the better"), Q37&gt; Q36)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="10">
-      <formula xml:space="preserve"> AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37&gt;= Q36)</formula>
+    <cfRule type="containsBlanks" dxfId="17" priority="7">
+      <formula>LEN(TRIM(Q37))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q44">
-    <cfRule type="containsBlanks" dxfId="16" priority="11">
-      <formula>LEN(TRIM(Q44))=0</formula>
+    <cfRule type="expression" dxfId="16" priority="15" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&gt;=Q43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="12">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&gt;Q43)</formula>
+    <cfRule type="expression" dxfId="15" priority="14">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&lt;Q43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="13">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&lt;=Q43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="14">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&lt;Q43)</formula>
+    <cfRule type="expression" dxfId="13" priority="12">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&gt;Q43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="15" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&gt;=Q43)</formula>
+    <cfRule type="containsBlanks" dxfId="12" priority="11">
+      <formula>LEN(TRIM(Q44))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T44">
-    <cfRule type="containsBlanks" dxfId="11" priority="52">
-      <formula>LEN(TRIM(T44))=0</formula>
+    <cfRule type="expression" dxfId="11" priority="56" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&gt;=T43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="53">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&gt;T43)</formula>
+    <cfRule type="expression" dxfId="10" priority="55">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&lt;T43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="9" priority="54">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&lt;=T43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="55">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&lt;T43)</formula>
+    <cfRule type="expression" dxfId="8" priority="53">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&gt;T43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="56" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&gt;=T43)</formula>
+    <cfRule type="containsBlanks" dxfId="7" priority="52">
+      <formula>LEN(TRIM(T44))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W44">
-    <cfRule type="containsBlanks" dxfId="6" priority="47">
+    <cfRule type="expression" dxfId="6" priority="48">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&gt;W43)</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="5" priority="47">
       <formula>LEN(TRIM(W44))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="48">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&gt;W43)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="49">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&lt;=W43)</formula>
+    <cfRule type="expression" dxfId="4" priority="51" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&gt;=W43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="3" priority="50">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&lt;W43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="51" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&gt;=W43)</formula>
+    <cfRule type="expression" dxfId="2" priority="49">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&lt;=W43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA47">
@@ -12948,7 +12982,7 @@
       <formula>LEN(TRIM(AA51))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J41:J52 J6:J37" xr:uid="{61C2D6F6-6FCD-4E8F-B96B-259C330F7837}">
       <formula1>"Monthly, Quarterly, Half yearly"</formula1>
     </dataValidation>
@@ -12986,26 +13020,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -13143,20 +13163,34 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00689E59-8A26-4E67-9A3E-2052C2F0E5F2}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CFCB212-7126-4863-80E7-8646D7325D33}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -13182,7 +13182,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00689E59-8A26-4E67-9A3E-2052C2F0E5F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77641BCA-A8DE-46A1-A07C-49ABD030EF3E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/GlobalMoSMT-2023/Shared Documents/General/2026/Goals Alignment 2026/Strategic Execution 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3302" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BCABF23-FFE1-4786-A3DA-C013F3078329}"/>
+  <xr:revisionPtr revIDLastSave="3303" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A93ABE6-18DF-497E-AC52-532E61417EF1}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="1030" windowWidth="9600" windowHeight="5450" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
   </bookViews>
   <sheets>
     <sheet name="Mastersheet" sheetId="5" r:id="rId1"/>
     <sheet name="AOP Critical" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -586,13 +586,6 @@
     <t>Increase contract penetration %</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.8% delta Vs AOP. Excluding GRC 0.7% YoY improvement.  LATAM renewals improved ITM Sep. </t>
-  </si>
-  <si>
-    <t>1) Funnel focus actions driven across regions for renewals.
-2) Contract Funnel tracked 90 days before expiry for timely renewals.</t>
-  </si>
-  <si>
     <t>Adjusted EBITA %</t>
   </si>
   <si>
@@ -617,13 +610,200 @@
     <t>Mn</t>
   </si>
   <si>
+    <t>Inventory MAT sales</t>
+  </si>
+  <si>
+    <t>Inventory as a % MAT sales</t>
+  </si>
+  <si>
+    <t>Inventory as a % MAT sales KPI</t>
+  </si>
+  <si>
+    <t>NPI Schedule Adherence</t>
+  </si>
+  <si>
+    <t>Shivaraj G</t>
+  </si>
+  <si>
+    <t>Dhruv  Schedule Adherence</t>
+  </si>
+  <si>
+    <t>Implied Market Share Gain</t>
+  </si>
+  <si>
+    <t>Sarika P</t>
+  </si>
+  <si>
+    <t>Implied Market Share Gain (ITQ)</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>QTR</t>
+  </si>
+  <si>
+    <t>Win Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Win Rate </t>
+  </si>
+  <si>
+    <t>(Philips OIT) / (Philips OIT + lost SFDC + not pursuing SFDC)</t>
+  </si>
+  <si>
+    <t>Implied Market Share Gain KPI</t>
+  </si>
+  <si>
+    <t>Order Intake Growth</t>
+  </si>
+  <si>
+    <t>OIT Growth % (EQ)</t>
+  </si>
+  <si>
+    <t>OIT (Equipment  + Service)</t>
+  </si>
+  <si>
+    <t>OIT Growth % (CS)</t>
+  </si>
+  <si>
+    <t>Comparable Sales</t>
+  </si>
+  <si>
+    <t>Monthly Sales recognized (EQ)</t>
+  </si>
+  <si>
+    <t>CSG % KPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impact Index KPI </t>
+  </si>
+  <si>
+    <t>Lakshmi M</t>
+  </si>
+  <si>
+    <t>EES scores are out! It is a balanced story. We are better than H1 2025 but slightly worse than H2 2025</t>
+  </si>
+  <si>
+    <t>CS has hit it out of the park.Quality dipped from 100% but still highest, Marketing is holding but at low scores. R&amp;D has dropped some big numbers.</t>
+  </si>
+  <si>
+    <t>Employee Engagement KPI</t>
+  </si>
+  <si>
+    <t>HY</t>
+  </si>
+  <si>
+    <t>MoS Value Levers 2026 - 2028:</t>
+  </si>
+  <si>
+    <t>Value Levers</t>
+  </si>
+  <si>
+    <t>AOP
+ 2026</t>
+  </si>
+  <si>
+    <t>AOP
+ 2027</t>
+  </si>
+  <si>
+    <t>AOP
+ 2028</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
+  <si>
+    <t>Cost Of Non-Quality as % of Sales</t>
+  </si>
+  <si>
+    <t>Cost of FCO, Warranty, Obsolescence, Scrap and Rework.</t>
+  </si>
+  <si>
+    <t>Competitive Roadmap</t>
+  </si>
+  <si>
+    <t>Roadmap MS% delivery (NPI OIT)</t>
+  </si>
+  <si>
+    <t>Zenition 10 &amp; 30 OIT below Q2 AOP due NPIs and price pressure from GE &amp; Siemens</t>
+  </si>
+  <si>
+    <t>Focus on Philips IB opportunity through mapping and targeted promotions to improve win rate</t>
+  </si>
+  <si>
+    <t>(MS% delivered by roadmap)
+/ (MS% ambition) 
+over 5 year horizon</t>
+  </si>
+  <si>
+    <t>Vitality index</t>
+  </si>
+  <si>
+    <t>% of sales from MoS Innovation &lt; 3 years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Improve Z10 &amp; Z30 competitiveness (sales training to counter competition) and bundling service at POS address price gap
+</t>
+  </si>
+  <si>
+    <t>I2M Value Creation</t>
+  </si>
+  <si>
+    <t>Development progress (per year, per quarter, %) X Incremental IGM</t>
+  </si>
+  <si>
+    <t>Development progress 
+(per year, per quarter, %) X Incremental IGM,( from business cases, M€ )</t>
+  </si>
+  <si>
+    <t>Cusotomer Focus</t>
+  </si>
+  <si>
+    <t>Services - Time To System Up (TTSU)</t>
+  </si>
+  <si>
+    <t>% of system down cases back up &lt;48hrs</t>
+  </si>
+  <si>
+    <t>Time To System Up &lt; 48h</t>
+  </si>
+  <si>
+    <t>Profitability - Margin Expansion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Driving profitability via margin expansion  </t>
+  </si>
+  <si>
+    <t>Focus on optimizing FCP, pricing, and product mix to drive margin expansion</t>
+  </si>
+  <si>
     <t>YTD Sept Productivity no's on track.Good Realization from E&amp;E savings of Pune and also a gap reduction of R&amp;D Budget YTD.</t>
   </si>
   <si>
-    <t>Inventory MAT sales</t>
-  </si>
-  <si>
-    <t>Inventory as a % MAT sales</t>
+    <t>EQ OIT YTD Sep lower by 0.2M, which is mainly coming by NAR -4.4M, EU -3.7M however Growth supported by over-drive +7.9M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current OOH does not support FY revnue plan. 
+OOH is 117 M agaist AOP of 141M .B&amp;B  24 M B&amp;B required to meet FY AOP.
+</t>
+  </si>
+  <si>
+    <t>Growth</t>
+  </si>
+  <si>
+    <t>Drive B&amp;B OIT 
+NAR : 5 M , EU: 8.5M , Growth : 7.6</t>
+  </si>
+  <si>
+    <t>1. NAR :AOP accelator program launched to improve OIT to rev conversion.
+2. EU : Demo  liquidation plan aligned toward Q4 to maximise OIT in Q3.
+3. Growth:  Namibia tender conversion in Q4
+4. UIEP : COE team to analyse the difference and accurate capturing in AOP 2027</t>
   </si>
   <si>
     <t xml:space="preserve">Market inventory : 7.7 M above AOP .
@@ -634,191 +814,11 @@
 </t>
   </si>
   <si>
-    <t>1. NAR :AOP accelator program launched to improve OIT to rev conversion.
-2. EU : Demo  liquidation plan aligned toward Q4 to maximise OIT in Q3.
-3. Growth:  Namibia tender conversion in Q4
-4. UIEP : COE team to analyse the difference and accurate capturing in AOP 2027</t>
-  </si>
-  <si>
-    <t>Inventory as a % MAT sales KPI</t>
-  </si>
-  <si>
-    <t>NPI Schedule Adherence</t>
-  </si>
-  <si>
-    <t>Shivaraj G</t>
-  </si>
-  <si>
-    <t>Dhruv  Schedule Adherence</t>
-  </si>
-  <si>
-    <t>Implied Market Share Gain</t>
-  </si>
-  <si>
-    <t>Sarika P</t>
-  </si>
-  <si>
-    <t>Implied Market Share Gain (ITQ)</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>QTR</t>
-  </si>
-  <si>
-    <t>Win Rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Win Rate </t>
-  </si>
-  <si>
-    <t>(Philips OIT) / (Philips OIT + lost SFDC + not pursuing SFDC)</t>
-  </si>
-  <si>
-    <t>Implied Market Share Gain KPI</t>
-  </si>
-  <si>
-    <t>Order Intake Growth</t>
-  </si>
-  <si>
-    <t>OIT Growth % (EQ)</t>
-  </si>
-  <si>
-    <t>EQ OIT YTD Sep lower by 0.2M, which is mainly coming by NAR -4.4M, EU -3.7M however Growth supported by over-drive +7.9M</t>
-  </si>
-  <si>
-    <t>OIT (Equipment  + Service)</t>
-  </si>
-  <si>
-    <t>OIT Growth % (CS)</t>
-  </si>
-  <si>
-    <t>Comparable Sales</t>
-  </si>
-  <si>
-    <t>Monthly Sales recognized (EQ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current OOH does not support FY revnue plan. 
-OOH is 117 M agaist AOP of 141M .B&amp;B  24 M B&amp;B required to meet FY AOP.
-</t>
-  </si>
-  <si>
-    <t>Drive B&amp;B OIT 
-NAR : 5 M , EU: 8.5M , Growth : 7.6</t>
-  </si>
-  <si>
-    <t>CSG % KPI</t>
-  </si>
-  <si>
-    <t>Growth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Impact Index KPI </t>
-  </si>
-  <si>
-    <t>Lakshmi M</t>
-  </si>
-  <si>
-    <t>EES scores are out! It is a balanced story. We are better than H1 2025 but slightly worse than H2 2025</t>
-  </si>
-  <si>
-    <t>CS has hit it out of the park.Quality dipped from 100% but still highest, Marketing is holding but at low scores. R&amp;D has dropped some big numbers.</t>
-  </si>
-  <si>
-    <t>Employee Engagement KPI</t>
-  </si>
-  <si>
-    <t>HY</t>
-  </si>
-  <si>
-    <t>MoS Value Levers 2026 - 2028:</t>
-  </si>
-  <si>
-    <t>Value Levers</t>
-  </si>
-  <si>
-    <t>AOP
- 2026</t>
-  </si>
-  <si>
-    <t>AOP
- 2027</t>
-  </si>
-  <si>
-    <t>AOP
- 2028</t>
-  </si>
-  <si>
-    <t>Mar</t>
-  </si>
-  <si>
-    <t>June</t>
-  </si>
-  <si>
-    <t>Cost Of Non-Quality as % of Sales</t>
-  </si>
-  <si>
-    <t>Cost of FCO, Warranty, Obsolescence, Scrap and Rework.</t>
-  </si>
-  <si>
-    <t>Competitive Roadmap</t>
-  </si>
-  <si>
-    <t>Roadmap MS% delivery (NPI OIT)</t>
-  </si>
-  <si>
-    <t>Zenition 10 &amp; 30 OIT below Q2 AOP due NPIs and price pressure from GE &amp; Siemens</t>
-  </si>
-  <si>
-    <t>Focus on Philips IB opportunity through mapping and targeted promotions to improve win rate</t>
-  </si>
-  <si>
-    <t>(MS% delivered by roadmap)
-/ (MS% ambition) 
-over 5 year horizon</t>
-  </si>
-  <si>
-    <t>Vitality index</t>
-  </si>
-  <si>
-    <t>% of sales from MoS Innovation &lt; 3 years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Improve Z10 &amp; Z30 competitiveness (sales training to counter competition) and bundling service at POS address price gap
-</t>
-  </si>
-  <si>
-    <t>I2M Value Creation</t>
-  </si>
-  <si>
-    <t>Development progress (per year, per quarter, %) X Incremental IGM</t>
-  </si>
-  <si>
-    <t>Development progress 
-(per year, per quarter, %) X Incremental IGM,( from business cases, M€ )</t>
-  </si>
-  <si>
-    <t>Cusotomer Focus</t>
-  </si>
-  <si>
-    <t>Services - Time To System Up (TTSU)</t>
-  </si>
-  <si>
-    <t>% of system down cases back up &lt;48hrs</t>
-  </si>
-  <si>
-    <t>Time To System Up &lt; 48h</t>
-  </si>
-  <si>
-    <t>Profitability - Margin Expansion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Driving profitability via margin expansion  </t>
-  </si>
-  <si>
-    <t>Focus on optimizing FCP, pricing, and product mix to drive margin expansion</t>
+    <t xml:space="preserve">-0.8% delta Vs AOP. Excluding GRC 0.7% YoY improvement.  LATAM renewals improved ITM Sep. </t>
+  </si>
+  <si>
+    <t>1) Funnel focus actions driven across regions for renewals.
+2) Contract Funnel tracked 90 days before expiry for timely renewals.</t>
   </si>
 </sst>
 </file>
@@ -832,7 +832,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1561,12 +1561,6 @@
     <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -1809,6 +1803,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1860,7 +1860,35 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1881,7 +1909,35 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1944,83 +2000,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFDA9694"/>
         </patternFill>
       </fill>
@@ -2043,111 +2022,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2196,6 +2070,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
@@ -2204,6 +2092,118 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2232,6 +2232,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2281,13 +2288,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4630,6 +4630,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BD41CE00-E924-4733-B76A-3C4E09FA89B8}" name="Customer_Focus" displayName="Customer_Focus" ref="A14:V20" totalsRowShown="0">
   <autoFilter ref="A14:V20" xr:uid="{BD41CE00-E924-4733-B76A-3C4E09FA89B8}"/>
@@ -5186,29 +5190,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247AD843-49A7-417E-9F24-86908363EFA2}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:V59"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.5703125" customWidth="1"/>
-    <col min="5" max="6" width="10.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" customWidth="1"/>
+    <col min="3" max="3" width="55.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.54296875" customWidth="1"/>
+    <col min="5" max="6" width="10.453125" customWidth="1"/>
+    <col min="7" max="7" width="13.81640625" customWidth="1"/>
+    <col min="9" max="9" width="11.54296875" customWidth="1"/>
+    <col min="10" max="10" width="13.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="15.95">
+    <row r="1" spans="1:22" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -5276,7 +5280,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5" t="str">
         <f>IF('AOP Critical'!B6="","",'AOP Critical'!B6)</f>
         <v>Complaint Closure</v>
@@ -5362,7 +5366,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" t="str">
         <f>IF('AOP Critical'!B6="","",'AOP Critical'!B6)</f>
         <v>Complaint Closure</v>
@@ -5448,7 +5452,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" t="str">
         <f>IF('AOP Critical'!B8="","",'AOP Critical'!B8)</f>
         <v>% of CAPA investgation</v>
@@ -5534,7 +5538,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" t="str">
         <f>IF('AOP Critical'!B8="","",'AOP Critical'!B8)</f>
         <v>% of CAPA investgation</v>
@@ -5620,7 +5624,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
         <f>IF('AOP Critical'!B10="","",'AOP Critical'!B10)</f>
         <v xml:space="preserve"># of Corrections &amp; Removals </v>
@@ -5706,7 +5710,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
         <f>IF('AOP Critical'!B10="","",'AOP Critical'!B10)</f>
         <v xml:space="preserve"># of Corrections &amp; Removals </v>
@@ -5792,7 +5796,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11" t="str">
         <f>IF('AOP Critical'!B41="","",'AOP Critical'!B41)</f>
         <v>Cost Of Non-Quality as % of Sales</v>
@@ -5878,7 +5882,7 @@
         <v>3.32E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
         <f>IF('AOP Critical'!B41="","",'AOP Critical'!B41)</f>
         <v>Cost Of Non-Quality as % of Sales</v>
@@ -5964,12 +5968,12 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -6037,7 +6041,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15" t="str">
         <f>IF('AOP Critical'!B12="","",'AOP Critical'!B12)</f>
         <v>Ontime In Full</v>
@@ -6127,7 +6131,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" t="str">
         <f>IF('AOP Critical'!B12="","",'AOP Critical'!B12)</f>
         <v>Ontime In Full</v>
@@ -6217,7 +6221,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" t="str">
         <f>IF('AOP Critical'!B14="","",'AOP Critical'!B14)</f>
         <v>Contract Penetration</v>
@@ -6307,7 +6311,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A18" t="str">
         <f>IF('AOP Critical'!B14="","",'AOP Critical'!B14)</f>
         <v>Contract Penetration</v>
@@ -6397,7 +6401,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19" t="str">
         <f>IF('AOP Critical'!B49="","",'AOP Critical'!B49)</f>
         <v>Services - Time To System Up (TTSU)</v>
@@ -6487,7 +6491,7 @@
         <v>0.73999999999999966</v>
       </c>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A20" t="str">
         <f>IF('AOP Critical'!B49="","",'AOP Critical'!B49)</f>
         <v>Services - Time To System Up (TTSU)</v>
@@ -6577,12 +6581,12 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>2</v>
       </c>
@@ -6650,7 +6654,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:22">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A23" t="str">
         <f>IF('AOP Critical'!B16="","",'AOP Critical'!B16)</f>
         <v>Adjusted EBITA %</v>
@@ -6740,7 +6744,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A24" t="str">
         <f>IF('AOP Critical'!B16="","",'AOP Critical'!B16)</f>
         <v>Adjusted EBITA %</v>
@@ -6830,7 +6834,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A25" t="str">
         <f>IF('AOP Critical'!B18="","",'AOP Critical'!B18)</f>
         <v>Productivity</v>
@@ -6905,7 +6909,7 @@
       </c>
       <c r="S25" s="74">
         <f>IF('AOP Critical'!T18="","",'AOP Critical'!T18)</f>
-        <v>3.7040000000000002</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="T25" s="74" t="str">
         <f>IF('AOP Critical'!U18="","",'AOP Critical'!U18)</f>
@@ -6920,7 +6924,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A26" t="str">
         <f>IF('AOP Critical'!B18="","",'AOP Critical'!B18)</f>
         <v>Productivity</v>
@@ -7010,7 +7014,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A27" t="str">
         <f>IF('AOP Critical'!B20="","",'AOP Critical'!B20)</f>
         <v>Inventory MAT sales</v>
@@ -7100,7 +7104,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A28" t="str">
         <f>IF('AOP Critical'!B20="","",'AOP Critical'!B20)</f>
         <v>Inventory MAT sales</v>
@@ -7190,7 +7194,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A29" t="str">
         <f>IF('AOP Critical'!B51="","",'AOP Critical'!B51)</f>
         <v>Profitability - Margin Expansion</v>
@@ -7280,7 +7284,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:22">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A30" t="str">
         <f>IF('AOP Critical'!B51="","",'AOP Critical'!B51)</f>
         <v>Profitability - Margin Expansion</v>
@@ -7370,12 +7374,12 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>2</v>
       </c>
@@ -7443,7 +7447,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:22">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A33" t="str">
         <f>IF('AOP Critical'!B26="","",'AOP Critical'!B26)</f>
         <v xml:space="preserve">Win Rate </v>
@@ -7533,7 +7537,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:22">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A34" t="str">
         <f>IF('AOP Critical'!B26="","",'AOP Critical'!B26)</f>
         <v xml:space="preserve">Win Rate </v>
@@ -7623,7 +7627,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:22">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A35" t="str">
         <f>IF('AOP Critical'!B22="","",'AOP Critical'!B22)</f>
         <v>NPI Schedule Adherence</v>
@@ -7713,7 +7717,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A36" t="str">
         <f>IF('AOP Critical'!B22="","",'AOP Critical'!B22)</f>
         <v>NPI Schedule Adherence</v>
@@ -7803,7 +7807,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:22">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A37" t="str">
         <f>IF('AOP Critical'!B43="","",'AOP Critical'!B43)</f>
         <v>Competitive Roadmap</v>
@@ -7893,7 +7897,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:22">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A38" t="str">
         <f>IF('AOP Critical'!B43="","",'AOP Critical'!B43)</f>
         <v>Competitive Roadmap</v>
@@ -7983,7 +7987,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:22">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A39" t="str">
         <f>IF('AOP Critical'!B45="","",'AOP Critical'!B45)</f>
         <v>Vitality index</v>
@@ -8073,7 +8077,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:22">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A40" t="str">
         <f>IF('AOP Critical'!B45="","",'AOP Critical'!B45)</f>
         <v>Vitality index</v>
@@ -8163,7 +8167,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:22">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A41" t="str">
         <f>IF('AOP Critical'!B47="","",'AOP Critical'!B47)</f>
         <v>I2M Value Creation</v>
@@ -8253,7 +8257,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:22">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A42" t="str">
         <f>IF('AOP Critical'!B47="","",'AOP Critical'!B47)</f>
         <v>I2M Value Creation</v>
@@ -8343,12 +8347,12 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:22">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="1:22">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>2</v>
       </c>
@@ -8416,7 +8420,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="1:22">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A45" t="str">
         <f>IF('AOP Critical'!D28="","",'AOP Critical'!D28)</f>
         <v>OIT Growth % (EQ)</v>
@@ -8506,7 +8510,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:22">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A46" t="str">
         <f>IF('AOP Critical'!D28="","",'AOP Critical'!D28)</f>
         <v>OIT Growth % (EQ)</v>
@@ -8596,7 +8600,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:22">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A47" t="str">
         <f>IF('AOP Critical'!D30="","",'AOP Critical'!D30)</f>
         <v>OIT Growth % (CS)</v>
@@ -8683,7 +8687,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:22">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A48" t="str">
         <f>IF('AOP Critical'!D30="","",'AOP Critical'!D30)</f>
         <v>OIT Growth % (CS)</v>
@@ -8769,7 +8773,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:22">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A49" t="str">
         <f>IF('AOP Critical'!B32="","",'AOP Critical'!B32)</f>
         <v>Comparable Sales</v>
@@ -8859,7 +8863,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:22">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A50" t="str">
         <f>IF('AOP Critical'!B32="","",'AOP Critical'!B32)</f>
         <v>Comparable Sales</v>
@@ -8949,7 +8953,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:22">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A51" t="str">
         <f>IF('AOP Critical'!B24="","",'AOP Critical'!B24)</f>
         <v>Implied Market Share Gain</v>
@@ -9039,7 +9043,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:22">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A52" t="str">
         <f>IF('AOP Critical'!B24="","",'AOP Critical'!B24)</f>
         <v>Implied Market Share Gain</v>
@@ -9129,12 +9133,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:22">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A54" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:22">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>2</v>
       </c>
@@ -9202,7 +9206,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:22">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>29</v>
       </c>
@@ -9277,7 +9281,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="57" spans="1:22">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>29</v>
       </c>
@@ -9352,7 +9356,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:22">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>35</v>
       </c>
@@ -9427,7 +9431,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:22">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>35</v>
       </c>
@@ -9523,33 +9527,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{632542D1-52E6-4116-B536-B17D5839DF19}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AC66"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.5703125" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="26.85546875" customWidth="1"/>
-    <col min="5" max="5" width="5.140625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="1.85546875" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="2.7109375" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" customWidth="1"/>
-    <col min="12" max="12" width="5.5703125" customWidth="1"/>
-    <col min="13" max="13" width="6.85546875" customWidth="1"/>
-    <col min="14" max="14" width="6.28515625" customWidth="1"/>
-    <col min="15" max="15" width="7.28515625" customWidth="1"/>
-    <col min="16" max="22" width="6.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.54296875" customWidth="1"/>
+    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="26.81640625" customWidth="1"/>
+    <col min="5" max="5" width="5.1796875" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="4.54296875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="1.81640625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="2.7265625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="5.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.7265625" customWidth="1"/>
+    <col min="12" max="12" width="5.54296875" customWidth="1"/>
+    <col min="13" max="13" width="6.81640625" customWidth="1"/>
+    <col min="14" max="14" width="6.26953125" customWidth="1"/>
+    <col min="15" max="15" width="7.26953125" customWidth="1"/>
+    <col min="16" max="22" width="6.1796875" customWidth="1"/>
     <col min="23" max="23" width="6" customWidth="1"/>
-    <col min="24" max="24" width="58.85546875" style="20" customWidth="1"/>
-    <col min="25" max="25" width="68.140625" customWidth="1"/>
-    <col min="26" max="26" width="17.7109375" customWidth="1"/>
+    <col min="24" max="24" width="58.81640625" style="20" customWidth="1"/>
+    <col min="25" max="25" width="68.1796875" customWidth="1"/>
+    <col min="26" max="26" width="17.7265625" customWidth="1"/>
     <col min="27" max="27" width="57" style="13" customWidth="1"/>
-    <col min="28" max="46" width="8.5703125" customWidth="1"/>
+    <col min="28" max="46" width="8.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
         <v>39</v>
       </c>
@@ -9560,7 +9564,7 @@
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="B2" s="6"/>
       <c r="C2" s="7"/>
       <c r="E2" s="6"/>
@@ -9569,11 +9573,11 @@
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
     </row>
-    <row r="3" spans="1:27" s="5" customFormat="1" ht="23.45">
-      <c r="A3" s="110" t="s">
+    <row r="3" spans="1:27" s="5" customFormat="1" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="108" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="110"/>
+      <c r="B3" s="108"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -9593,39 +9597,39 @@
       <c r="X3" s="21"/>
       <c r="AA3" s="14"/>
     </row>
-    <row r="4" spans="1:27" s="5" customFormat="1">
-      <c r="A4" s="112" t="str">
+    <row r="4" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="110" t="str">
         <f ca="1">"Current Month-Year " &amp; ":" &amp; TEXT(TODAY(),"YYYY-MM")</f>
         <v>Current Month-Year :2026-10</v>
       </c>
-      <c r="B4" s="112"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="112"/>
-      <c r="L4" s="112"/>
-      <c r="M4" s="112"/>
-      <c r="N4" s="112"/>
-      <c r="O4" s="112"/>
-      <c r="P4" s="112"/>
-      <c r="Q4" s="112"/>
-      <c r="R4" s="112"/>
-      <c r="S4" s="112"/>
-      <c r="T4" s="112"/>
-      <c r="U4" s="112"/>
-      <c r="V4" s="112"/>
-      <c r="W4" s="112"/>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="112"/>
-      <c r="Z4" s="112"/>
-      <c r="AA4" s="112"/>
+      <c r="B4" s="110"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110"/>
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110"/>
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110"/>
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110"/>
+      <c r="V4" s="110"/>
+      <c r="W4" s="110"/>
+      <c r="X4" s="110"/>
+      <c r="Y4" s="110"/>
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
     </row>
-    <row r="5" spans="1:27" ht="27" customHeight="1">
+    <row r="5" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="86" t="s">
         <v>0</v>
       </c>
@@ -9638,11 +9642,11 @@
       <c r="D5" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="116" t="s">
+      <c r="E5" s="114" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="114"/>
       <c r="H5" s="87" t="s">
         <v>8</v>
       </c>
@@ -9704,31 +9708,31 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:27">
-      <c r="A6" s="109" t="s">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A6" s="107" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="91" t="s">
+      <c r="B6" s="89" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="92" t="s">
+      <c r="C6" s="90" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="108">
+      <c r="E6" s="106">
         <v>10</v>
       </c>
-      <c r="F6" s="108"/>
-      <c r="G6" s="108"/>
-      <c r="H6" s="111" t="s">
+      <c r="F6" s="106"/>
+      <c r="G6" s="106"/>
+      <c r="H6" s="109" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="108" t="s">
+      <c r="I6" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="107" t="s">
+      <c r="J6" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K6" s="23" t="s">
@@ -9770,24 +9774,24 @@
       <c r="W6" s="28">
         <v>0.05</v>
       </c>
-      <c r="X6" s="106"/>
-      <c r="Y6" s="113"/>
-      <c r="Z6" s="113"/>
-      <c r="AA6" s="123" t="s">
+      <c r="X6" s="104"/>
+      <c r="Y6" s="111"/>
+      <c r="Z6" s="111"/>
+      <c r="AA6" s="121" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:27">
-      <c r="A7" s="109"/>
-      <c r="B7" s="91"/>
-      <c r="C7" s="92"/>
-      <c r="D7" s="90"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="108"/>
-      <c r="G7" s="108"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="108"/>
-      <c r="J7" s="107"/>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A7" s="107"/>
+      <c r="B7" s="89"/>
+      <c r="C7" s="90"/>
+      <c r="D7" s="88"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="106"/>
+      <c r="G7" s="106"/>
+      <c r="H7" s="109"/>
+      <c r="I7" s="106"/>
+      <c r="J7" s="105"/>
       <c r="K7" s="23" t="s">
         <v>55</v>
       </c>
@@ -9821,34 +9825,34 @@
       <c r="U7" s="51"/>
       <c r="V7" s="51"/>
       <c r="W7" s="51"/>
-      <c r="X7" s="94"/>
-      <c r="Y7" s="96"/>
-      <c r="Z7" s="96"/>
-      <c r="AA7" s="124"/>
+      <c r="X7" s="92"/>
+      <c r="Y7" s="94"/>
+      <c r="Z7" s="94"/>
+      <c r="AA7" s="122"/>
     </row>
-    <row r="8" spans="1:27">
-      <c r="A8" s="109"/>
-      <c r="B8" s="91" t="s">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A8" s="107"/>
+      <c r="B8" s="89" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="92" t="s">
+      <c r="C8" s="90" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="90" t="s">
+      <c r="D8" s="88" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="108">
+      <c r="E8" s="106">
         <v>90</v>
       </c>
-      <c r="F8" s="108"/>
-      <c r="G8" s="108"/>
-      <c r="H8" s="111" t="s">
+      <c r="F8" s="106"/>
+      <c r="G8" s="106"/>
+      <c r="H8" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="108" t="s">
+      <c r="I8" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="107" t="s">
+      <c r="J8" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K8" s="23" t="s">
@@ -9880,28 +9884,28 @@
       <c r="U8" s="18"/>
       <c r="V8" s="18"/>
       <c r="W8" s="28"/>
-      <c r="X8" s="94"/>
-      <c r="Y8" s="95" t="s">
+      <c r="X8" s="92"/>
+      <c r="Y8" s="93" t="s">
         <v>58</v>
       </c>
-      <c r="Z8" s="114">
+      <c r="Z8" s="112">
         <v>46231</v>
       </c>
-      <c r="AA8" s="123" t="s">
+      <c r="AA8" s="121" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:27">
-      <c r="A9" s="109"/>
-      <c r="B9" s="91"/>
-      <c r="C9" s="92"/>
-      <c r="D9" s="90"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108"/>
-      <c r="G9" s="108"/>
-      <c r="H9" s="111"/>
-      <c r="I9" s="108"/>
-      <c r="J9" s="107"/>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A9" s="107"/>
+      <c r="B9" s="89"/>
+      <c r="C9" s="90"/>
+      <c r="D9" s="88"/>
+      <c r="E9" s="106"/>
+      <c r="F9" s="106"/>
+      <c r="G9" s="106"/>
+      <c r="H9" s="109"/>
+      <c r="I9" s="106"/>
+      <c r="J9" s="105"/>
       <c r="K9" s="23" t="s">
         <v>55</v>
       </c>
@@ -9935,34 +9939,34 @@
       <c r="U9" s="53"/>
       <c r="V9" s="53"/>
       <c r="W9" s="53"/>
-      <c r="X9" s="94"/>
-      <c r="Y9" s="96"/>
-      <c r="Z9" s="115"/>
-      <c r="AA9" s="124"/>
+      <c r="X9" s="92"/>
+      <c r="Y9" s="94"/>
+      <c r="Z9" s="113"/>
+      <c r="AA9" s="122"/>
     </row>
-    <row r="10" spans="1:27">
-      <c r="A10" s="109"/>
-      <c r="B10" s="91" t="s">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A10" s="107"/>
+      <c r="B10" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="92" t="s">
+      <c r="C10" s="90" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="90" t="s">
+      <c r="D10" s="88" t="s">
         <v>61</v>
       </c>
-      <c r="E10" s="108">
+      <c r="E10" s="106">
         <v>1</v>
       </c>
-      <c r="F10" s="108"/>
-      <c r="G10" s="108"/>
-      <c r="H10" s="111" t="s">
+      <c r="F10" s="106"/>
+      <c r="G10" s="106"/>
+      <c r="H10" s="109" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="108" t="s">
+      <c r="I10" s="106" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="107" t="s">
+      <c r="J10" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K10" s="23" t="s">
@@ -9996,24 +10000,24 @@
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
       <c r="W10" s="34"/>
-      <c r="X10" s="94"/>
-      <c r="Y10" s="163"/>
-      <c r="Z10" s="117"/>
-      <c r="AA10" s="123" t="s">
+      <c r="X10" s="92"/>
+      <c r="Y10" s="161"/>
+      <c r="Z10" s="115"/>
+      <c r="AA10" s="121" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="15" thickBot="1">
-      <c r="A11" s="109"/>
-      <c r="B11" s="91"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="90"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="111"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="107"/>
+    <row r="11" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="107"/>
+      <c r="B11" s="89"/>
+      <c r="C11" s="90"/>
+      <c r="D11" s="88"/>
+      <c r="E11" s="106"/>
+      <c r="F11" s="106"/>
+      <c r="G11" s="106"/>
+      <c r="H11" s="109"/>
+      <c r="I11" s="106"/>
+      <c r="J11" s="105"/>
       <c r="K11" s="23" t="s">
         <v>55</v>
       </c>
@@ -10047,36 +10051,36 @@
       <c r="U11" s="32"/>
       <c r="V11" s="32"/>
       <c r="W11" s="33"/>
-      <c r="X11" s="94"/>
-      <c r="Y11" s="164"/>
-      <c r="Z11" s="118"/>
-      <c r="AA11" s="124"/>
+      <c r="X11" s="92"/>
+      <c r="Y11" s="162"/>
+      <c r="Z11" s="116"/>
+      <c r="AA11" s="122"/>
     </row>
-    <row r="12" spans="1:27">
-      <c r="A12" s="109" t="s">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A12" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="93" t="s">
+      <c r="B12" s="91" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="93" t="s">
+      <c r="C12" s="91" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="90" t="s">
+      <c r="D12" s="88" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="108">
+      <c r="E12" s="106">
         <v>84</v>
       </c>
-      <c r="F12" s="108"/>
-      <c r="G12" s="108"/>
-      <c r="H12" s="111" t="s">
+      <c r="F12" s="106"/>
+      <c r="G12" s="106"/>
+      <c r="H12" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="108" t="s">
+      <c r="I12" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="107" t="s">
+      <c r="J12" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K12" s="23" t="s">
@@ -10118,24 +10122,24 @@
       <c r="W12" s="26">
         <v>0.79</v>
       </c>
-      <c r="X12" s="94"/>
-      <c r="Y12" s="95"/>
-      <c r="Z12" s="96"/>
-      <c r="AA12" s="123" t="s">
+      <c r="X12" s="92"/>
+      <c r="Y12" s="93"/>
+      <c r="Z12" s="94"/>
+      <c r="AA12" s="121" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:27">
-      <c r="A13" s="109"/>
-      <c r="B13" s="93"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="90"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="108"/>
-      <c r="G13" s="108"/>
-      <c r="H13" s="111"/>
-      <c r="I13" s="108"/>
-      <c r="J13" s="107"/>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A13" s="107"/>
+      <c r="B13" s="91"/>
+      <c r="C13" s="91"/>
+      <c r="D13" s="88"/>
+      <c r="E13" s="106"/>
+      <c r="F13" s="106"/>
+      <c r="G13" s="106"/>
+      <c r="H13" s="109"/>
+      <c r="I13" s="106"/>
+      <c r="J13" s="105"/>
       <c r="K13" s="23" t="s">
         <v>55</v>
       </c>
@@ -10169,34 +10173,34 @@
       <c r="U13" s="19"/>
       <c r="V13" s="19"/>
       <c r="W13" s="29"/>
-      <c r="X13" s="94"/>
-      <c r="Y13" s="96"/>
-      <c r="Z13" s="96"/>
-      <c r="AA13" s="124"/>
+      <c r="X13" s="92"/>
+      <c r="Y13" s="94"/>
+      <c r="Z13" s="94"/>
+      <c r="AA13" s="122"/>
     </row>
-    <row r="14" spans="1:27" ht="15">
-      <c r="A14" s="109"/>
-      <c r="B14" s="93" t="s">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A14" s="107"/>
+      <c r="B14" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="122" t="s">
+      <c r="C14" s="120" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="90" t="s">
+      <c r="D14" s="88" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="108">
+      <c r="E14" s="106">
         <v>54.6</v>
       </c>
-      <c r="F14" s="108"/>
-      <c r="G14" s="108"/>
-      <c r="H14" s="111" t="s">
+      <c r="F14" s="106"/>
+      <c r="G14" s="106"/>
+      <c r="H14" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="108" t="s">
+      <c r="I14" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J14" s="107" t="s">
+      <c r="J14" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K14" s="23" t="s">
@@ -10233,25 +10237,25 @@
       <c r="V14" s="38"/>
       <c r="W14" s="38"/>
       <c r="X14" s="171" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y14" s="97" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z14" s="152"/>
-      <c r="AA14" s="151"/>
+        <v>141</v>
+      </c>
+      <c r="Y14" s="95" t="s">
+        <v>142</v>
+      </c>
+      <c r="Z14" s="150"/>
+      <c r="AA14" s="149"/>
     </row>
-    <row r="15" spans="1:27" ht="15" thickBot="1">
-      <c r="A15" s="109"/>
-      <c r="B15" s="93"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="90"/>
-      <c r="E15" s="108"/>
-      <c r="F15" s="108"/>
-      <c r="G15" s="108"/>
-      <c r="H15" s="111"/>
-      <c r="I15" s="108"/>
-      <c r="J15" s="107"/>
+    <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="107"/>
+      <c r="B15" s="91"/>
+      <c r="C15" s="120"/>
+      <c r="D15" s="88"/>
+      <c r="E15" s="106"/>
+      <c r="F15" s="106"/>
+      <c r="G15" s="106"/>
+      <c r="H15" s="109"/>
+      <c r="I15" s="106"/>
+      <c r="J15" s="105"/>
       <c r="K15" s="23" t="s">
         <v>55</v>
       </c>
@@ -10285,36 +10289,36 @@
       <c r="U15" s="32"/>
       <c r="V15" s="32"/>
       <c r="W15" s="33"/>
-      <c r="X15" s="94"/>
-      <c r="Y15" s="113"/>
-      <c r="Z15" s="113"/>
-      <c r="AA15" s="131"/>
+      <c r="X15" s="92"/>
+      <c r="Y15" s="111"/>
+      <c r="Z15" s="111"/>
+      <c r="AA15" s="129"/>
     </row>
-    <row r="16" spans="1:27">
-      <c r="A16" s="109" t="s">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A16" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="93" t="s">
+      <c r="B16" s="91" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="91" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" s="88" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="93" t="s">
+      <c r="E16" s="106" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="90" t="s">
-        <v>75</v>
-      </c>
-      <c r="E16" s="108" t="s">
-        <v>76</v>
-      </c>
-      <c r="F16" s="108"/>
-      <c r="G16" s="108"/>
-      <c r="H16" s="111" t="s">
+      <c r="F16" s="106"/>
+      <c r="G16" s="106"/>
+      <c r="H16" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I16" s="108" t="s">
+      <c r="I16" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="107" t="s">
+      <c r="J16" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K16" s="23" t="s">
@@ -10350,24 +10354,24 @@
       <c r="U16" s="25"/>
       <c r="V16" s="25"/>
       <c r="W16" s="26"/>
-      <c r="X16" s="94"/>
-      <c r="Y16" s="95"/>
-      <c r="Z16" s="115"/>
-      <c r="AA16" s="123" t="s">
-        <v>77</v>
+      <c r="X16" s="92"/>
+      <c r="Y16" s="93"/>
+      <c r="Z16" s="113"/>
+      <c r="AA16" s="121" t="s">
+        <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:27">
-      <c r="A17" s="109"/>
-      <c r="B17" s="93"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="90"/>
-      <c r="E17" s="108"/>
-      <c r="F17" s="108"/>
-      <c r="G17" s="108"/>
-      <c r="H17" s="111"/>
-      <c r="I17" s="108"/>
-      <c r="J17" s="107"/>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A17" s="107"/>
+      <c r="B17" s="91"/>
+      <c r="C17" s="91"/>
+      <c r="D17" s="88"/>
+      <c r="E17" s="106"/>
+      <c r="F17" s="106"/>
+      <c r="G17" s="106"/>
+      <c r="H17" s="109"/>
+      <c r="I17" s="106"/>
+      <c r="J17" s="105"/>
       <c r="K17" s="23" t="s">
         <v>55</v>
       </c>
@@ -10401,34 +10405,34 @@
       <c r="U17" s="19"/>
       <c r="V17" s="19"/>
       <c r="W17" s="29"/>
-      <c r="X17" s="94"/>
-      <c r="Y17" s="96"/>
-      <c r="Z17" s="115"/>
-      <c r="AA17" s="124"/>
+      <c r="X17" s="92"/>
+      <c r="Y17" s="94"/>
+      <c r="Z17" s="113"/>
+      <c r="AA17" s="122"/>
     </row>
-    <row r="18" spans="1:27">
-      <c r="A18" s="109"/>
-      <c r="B18" s="93" t="s">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A18" s="107"/>
+      <c r="B18" s="91" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="91" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" s="91" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" s="106" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" s="106"/>
+      <c r="G18" s="106"/>
+      <c r="H18" s="109" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="106" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="93" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" s="93" t="s">
-        <v>79</v>
-      </c>
-      <c r="E18" s="108" t="s">
-        <v>76</v>
-      </c>
-      <c r="F18" s="108"/>
-      <c r="G18" s="108"/>
-      <c r="H18" s="111" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="108" t="s">
-        <v>80</v>
-      </c>
-      <c r="J18" s="107" t="s">
+      <c r="J18" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K18" s="23" t="s">
@@ -10459,92 +10463,92 @@
         <v>2.93</v>
       </c>
       <c r="T18" s="48">
-        <v>3.7040000000000002</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="U18" s="48"/>
       <c r="V18" s="48"/>
       <c r="W18" s="48"/>
-      <c r="X18" s="157" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y18" s="157"/>
-      <c r="Z18" s="154">
+      <c r="X18" s="155" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y18" s="155"/>
+      <c r="Z18" s="152">
         <v>46108</v>
       </c>
-      <c r="AA18" s="156"/>
+      <c r="AA18" s="154"/>
     </row>
-    <row r="19" spans="1:27" ht="18.600000000000001" customHeight="1">
-      <c r="A19" s="109"/>
-      <c r="B19" s="93"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="93"/>
-      <c r="E19" s="108"/>
-      <c r="F19" s="108"/>
-      <c r="G19" s="108"/>
-      <c r="H19" s="111"/>
-      <c r="I19" s="108"/>
-      <c r="J19" s="107"/>
+    <row r="19" spans="1:27" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="107"/>
+      <c r="B19" s="91"/>
+      <c r="C19" s="91"/>
+      <c r="D19" s="91"/>
+      <c r="E19" s="106"/>
+      <c r="F19" s="106"/>
+      <c r="G19" s="106"/>
+      <c r="H19" s="109"/>
+      <c r="I19" s="106"/>
+      <c r="J19" s="105"/>
       <c r="K19" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="L19" s="88">
+      <c r="L19" s="169">
         <v>0.2598381666666667</v>
       </c>
-      <c r="M19" s="88">
+      <c r="M19" s="169">
         <v>0.3838381666666667</v>
       </c>
-      <c r="N19" s="88">
+      <c r="N19" s="169">
         <v>1.1128381666666667</v>
       </c>
-      <c r="O19" s="88">
+      <c r="O19" s="169">
         <v>1.3223861666666668</v>
       </c>
-      <c r="P19" s="88">
+      <c r="P19" s="169">
         <v>1.6513861666666667</v>
       </c>
-      <c r="Q19" s="88">
+      <c r="Q19" s="169">
         <v>2.1303861666666668</v>
       </c>
-      <c r="R19" s="89">
+      <c r="R19" s="170">
         <v>2.6433861666666667</v>
       </c>
-      <c r="S19" s="89">
+      <c r="S19" s="170">
         <v>3.3972231666666666</v>
       </c>
-      <c r="T19" s="89">
+      <c r="T19" s="170">
         <v>4.5205241666666662</v>
       </c>
       <c r="U19" s="47"/>
       <c r="V19" s="47"/>
       <c r="W19" s="49"/>
-      <c r="X19" s="157"/>
-      <c r="Y19" s="157"/>
-      <c r="Z19" s="155"/>
-      <c r="AA19" s="156"/>
+      <c r="X19" s="155"/>
+      <c r="Y19" s="155"/>
+      <c r="Z19" s="153"/>
+      <c r="AA19" s="154"/>
     </row>
-    <row r="20" spans="1:27" ht="24" customHeight="1">
-      <c r="A20" s="109"/>
-      <c r="B20" s="93" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" s="93" t="s">
+    <row r="20" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="107"/>
+      <c r="B20" s="91" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="91" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="90" t="s">
-        <v>83</v>
-      </c>
-      <c r="E20" s="108" t="s">
-        <v>76</v>
-      </c>
-      <c r="F20" s="108"/>
-      <c r="G20" s="108"/>
-      <c r="H20" s="111" t="s">
+      <c r="D20" s="88" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="106" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" s="106"/>
+      <c r="G20" s="106"/>
+      <c r="H20" s="109" t="s">
         <v>51</v>
       </c>
-      <c r="I20" s="108" t="s">
+      <c r="I20" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="107" t="s">
+      <c r="J20" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K20" s="23" t="s">
@@ -10580,28 +10584,28 @@
       <c r="U20" s="18"/>
       <c r="V20" s="18"/>
       <c r="W20" s="28"/>
-      <c r="X20" s="99" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y20" s="101" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z20" s="153"/>
-      <c r="AA20" s="125" t="s">
-        <v>86</v>
+      <c r="X20" s="97" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y20" s="99" t="s">
+        <v>139</v>
+      </c>
+      <c r="Z20" s="151"/>
+      <c r="AA20" s="123" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="32.1" customHeight="1" thickBot="1">
-      <c r="A21" s="109"/>
-      <c r="B21" s="93"/>
-      <c r="C21" s="93"/>
-      <c r="D21" s="90"/>
-      <c r="E21" s="108"/>
-      <c r="F21" s="108"/>
-      <c r="G21" s="108"/>
-      <c r="H21" s="111"/>
-      <c r="I21" s="108"/>
-      <c r="J21" s="107"/>
+    <row r="21" spans="1:27" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="107"/>
+      <c r="B21" s="91"/>
+      <c r="C21" s="91"/>
+      <c r="D21" s="88"/>
+      <c r="E21" s="106"/>
+      <c r="F21" s="106"/>
+      <c r="G21" s="106"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="106"/>
+      <c r="J21" s="105"/>
       <c r="K21" s="23" t="s">
         <v>55</v>
       </c>
@@ -10635,36 +10639,36 @@
       <c r="U21" s="30"/>
       <c r="V21" s="30"/>
       <c r="W21" s="31"/>
-      <c r="X21" s="100"/>
-      <c r="Y21" s="102"/>
-      <c r="Z21" s="119"/>
-      <c r="AA21" s="125"/>
+      <c r="X21" s="98"/>
+      <c r="Y21" s="100"/>
+      <c r="Z21" s="117"/>
+      <c r="AA21" s="123"/>
     </row>
-    <row r="22" spans="1:27" ht="15.95" customHeight="1">
-      <c r="A22" s="109" t="s">
+    <row r="22" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="107" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="93" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" s="122" t="s">
-        <v>88</v>
-      </c>
-      <c r="D22" s="93" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" s="108">
+      <c r="B22" s="91" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" s="120" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22" s="106">
         <v>90</v>
       </c>
-      <c r="F22" s="108"/>
-      <c r="G22" s="108"/>
-      <c r="H22" s="111" t="s">
+      <c r="F22" s="106"/>
+      <c r="G22" s="106"/>
+      <c r="H22" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="108" t="s">
+      <c r="I22" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J22" s="107" t="s">
+      <c r="J22" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K22" s="23" t="s">
@@ -10706,24 +10710,24 @@
       <c r="W22" s="28">
         <v>0.9</v>
       </c>
-      <c r="X22" s="105"/>
-      <c r="Y22" s="95"/>
-      <c r="Z22" s="114">
+      <c r="X22" s="103"/>
+      <c r="Y22" s="93"/>
+      <c r="Z22" s="112">
         <v>46257</v>
       </c>
-      <c r="AA22" s="161"/>
+      <c r="AA22" s="159"/>
     </row>
-    <row r="23" spans="1:27" ht="17.100000000000001" customHeight="1" thickBot="1">
-      <c r="A23" s="168"/>
-      <c r="B23" s="93"/>
-      <c r="C23" s="122"/>
-      <c r="D23" s="93"/>
-      <c r="E23" s="108"/>
-      <c r="F23" s="108"/>
-      <c r="G23" s="108"/>
-      <c r="H23" s="111"/>
-      <c r="I23" s="108"/>
-      <c r="J23" s="107"/>
+    <row r="23" spans="1:27" ht="17.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="166"/>
+      <c r="B23" s="91"/>
+      <c r="C23" s="120"/>
+      <c r="D23" s="91"/>
+      <c r="E23" s="106"/>
+      <c r="F23" s="106"/>
+      <c r="G23" s="106"/>
+      <c r="H23" s="109"/>
+      <c r="I23" s="106"/>
+      <c r="J23" s="105"/>
       <c r="K23" s="23" t="s">
         <v>55</v>
       </c>
@@ -10757,40 +10761,40 @@
       <c r="U23" s="30"/>
       <c r="V23" s="30"/>
       <c r="W23" s="31"/>
-      <c r="X23" s="106"/>
-      <c r="Y23" s="96"/>
-      <c r="Z23" s="115"/>
-      <c r="AA23" s="162"/>
+      <c r="X23" s="104"/>
+      <c r="Y23" s="94"/>
+      <c r="Z23" s="113"/>
+      <c r="AA23" s="160"/>
     </row>
-    <row r="24" spans="1:27" ht="17.45" customHeight="1">
-      <c r="A24" s="143" t="s">
+    <row r="24" spans="1:27" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="141" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="93" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" s="122" t="s">
-        <v>91</v>
-      </c>
-      <c r="D24" s="90" t="s">
-        <v>92</v>
-      </c>
-      <c r="E24" s="108" t="s">
-        <v>93</v>
-      </c>
-      <c r="F24" s="108" t="s">
-        <v>93</v>
-      </c>
-      <c r="G24" s="108" t="s">
-        <v>93</v>
-      </c>
-      <c r="H24" s="111" t="s">
+      <c r="B24" s="91" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="120" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="88" t="s">
+        <v>87</v>
+      </c>
+      <c r="E24" s="106" t="s">
+        <v>88</v>
+      </c>
+      <c r="F24" s="106" t="s">
+        <v>88</v>
+      </c>
+      <c r="G24" s="106" t="s">
+        <v>88</v>
+      </c>
+      <c r="H24" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="108" t="s">
+      <c r="I24" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J24" s="120" t="s">
+      <c r="J24" s="118" t="s">
         <v>34</v>
       </c>
       <c r="K24" s="23" t="s">
@@ -10802,109 +10806,109 @@
         <v>0.104</v>
       </c>
       <c r="O24" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="P24" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="Q24" s="38">
         <v>0.11799999999999999</v>
       </c>
       <c r="R24" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="S24" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="T24" s="36"/>
       <c r="U24" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="V24" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="W24" s="39"/>
-      <c r="X24" s="137"/>
-      <c r="Y24" s="152"/>
-      <c r="Z24" s="119"/>
-      <c r="AA24" s="123" t="s">
-        <v>95</v>
+      <c r="X24" s="135"/>
+      <c r="Y24" s="150"/>
+      <c r="Z24" s="117"/>
+      <c r="AA24" s="121" t="s">
+        <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="15" thickBot="1">
-      <c r="A25" s="167"/>
-      <c r="B25" s="93"/>
-      <c r="C25" s="122"/>
-      <c r="D25" s="90"/>
-      <c r="E25" s="108"/>
-      <c r="F25" s="108"/>
-      <c r="G25" s="108"/>
-      <c r="H25" s="111"/>
-      <c r="I25" s="108"/>
-      <c r="J25" s="120"/>
+    <row r="25" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="165"/>
+      <c r="B25" s="91"/>
+      <c r="C25" s="120"/>
+      <c r="D25" s="88"/>
+      <c r="E25" s="106"/>
+      <c r="F25" s="106"/>
+      <c r="G25" s="106"/>
+      <c r="H25" s="109"/>
+      <c r="I25" s="106"/>
+      <c r="J25" s="118"/>
       <c r="K25" s="23" t="s">
         <v>55</v>
       </c>
       <c r="L25" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M25" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="N25" s="51">
         <v>0.115</v>
       </c>
       <c r="O25" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="P25" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="Q25" s="17">
         <v>0.121</v>
       </c>
       <c r="R25" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="S25" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="T25" s="56"/>
       <c r="U25" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="V25" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="W25" s="56"/>
-      <c r="X25" s="106"/>
-      <c r="Y25" s="113"/>
-      <c r="Z25" s="153"/>
-      <c r="AA25" s="124"/>
+      <c r="X25" s="104"/>
+      <c r="Y25" s="111"/>
+      <c r="Z25" s="151"/>
+      <c r="AA25" s="122"/>
     </row>
-    <row r="26" spans="1:27" ht="14.45" customHeight="1">
-      <c r="A26" s="167"/>
-      <c r="B26" s="91" t="s">
-        <v>96</v>
-      </c>
-      <c r="C26" s="160" t="s">
+    <row r="26" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="165"/>
+      <c r="B26" s="89" t="s">
         <v>91</v>
       </c>
-      <c r="D26" s="90" t="s">
-        <v>97</v>
-      </c>
-      <c r="E26" s="108">
+      <c r="C26" s="158" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" s="88" t="s">
+        <v>92</v>
+      </c>
+      <c r="E26" s="106">
         <v>34</v>
       </c>
-      <c r="F26" s="158"/>
-      <c r="G26" s="158"/>
-      <c r="H26" s="111" t="s">
+      <c r="F26" s="156"/>
+      <c r="G26" s="156"/>
+      <c r="H26" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I26" s="108" t="s">
+      <c r="I26" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J26" s="107" t="s">
+      <c r="J26" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K26" s="23" t="s">
@@ -10940,24 +10944,24 @@
       <c r="U26" s="25"/>
       <c r="V26" s="25"/>
       <c r="W26" s="26"/>
-      <c r="X26" s="94"/>
-      <c r="Y26" s="96"/>
-      <c r="Z26" s="115"/>
-      <c r="AA26" s="123" t="s">
-        <v>98</v>
+      <c r="X26" s="92"/>
+      <c r="Y26" s="94"/>
+      <c r="Z26" s="113"/>
+      <c r="AA26" s="121" t="s">
+        <v>93</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="14.45" customHeight="1" thickBot="1">
-      <c r="A27" s="167"/>
-      <c r="B27" s="91"/>
-      <c r="C27" s="160"/>
-      <c r="D27" s="90"/>
-      <c r="E27" s="108"/>
-      <c r="F27" s="158"/>
-      <c r="G27" s="158"/>
-      <c r="H27" s="111"/>
-      <c r="I27" s="108"/>
-      <c r="J27" s="107"/>
+    <row r="27" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="165"/>
+      <c r="B27" s="89"/>
+      <c r="C27" s="158"/>
+      <c r="D27" s="88"/>
+      <c r="E27" s="106"/>
+      <c r="F27" s="156"/>
+      <c r="G27" s="156"/>
+      <c r="H27" s="109"/>
+      <c r="I27" s="106"/>
+      <c r="J27" s="105"/>
       <c r="K27" s="23" t="s">
         <v>55</v>
       </c>
@@ -10991,34 +10995,34 @@
       <c r="U27" s="19"/>
       <c r="V27" s="19"/>
       <c r="W27" s="29"/>
-      <c r="X27" s="94"/>
-      <c r="Y27" s="96"/>
-      <c r="Z27" s="115"/>
-      <c r="AA27" s="124"/>
+      <c r="X27" s="92"/>
+      <c r="Y27" s="94"/>
+      <c r="Z27" s="113"/>
+      <c r="AA27" s="122"/>
     </row>
-    <row r="28" spans="1:27" ht="14.45" customHeight="1">
-      <c r="A28" s="167"/>
-      <c r="B28" s="90" t="s">
-        <v>99</v>
-      </c>
-      <c r="C28" s="93" t="s">
+    <row r="28" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="165"/>
+      <c r="B28" s="88" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="91" t="s">
+        <v>72</v>
+      </c>
+      <c r="D28" s="88" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" s="106" t="s">
         <v>74</v>
       </c>
-      <c r="D28" s="90" t="s">
-        <v>100</v>
-      </c>
-      <c r="E28" s="108" t="s">
-        <v>76</v>
-      </c>
-      <c r="F28" s="108"/>
-      <c r="G28" s="108"/>
-      <c r="H28" s="111" t="s">
+      <c r="F28" s="106"/>
+      <c r="G28" s="106"/>
+      <c r="H28" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I28" s="108" t="s">
+      <c r="I28" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J28" s="107" t="s">
+      <c r="J28" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K28" s="23" t="s">
@@ -11054,26 +11058,26 @@
       <c r="U28" s="25"/>
       <c r="V28" s="25"/>
       <c r="W28" s="26"/>
-      <c r="X28" s="103" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y28" s="97"/>
-      <c r="Z28" s="119"/>
-      <c r="AA28" s="128" t="s">
-        <v>102</v>
+      <c r="X28" s="101" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y28" s="95"/>
+      <c r="Z28" s="117"/>
+      <c r="AA28" s="126" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="15" thickBot="1">
-      <c r="A29" s="167"/>
-      <c r="B29" s="90"/>
-      <c r="C29" s="93"/>
-      <c r="D29" s="90"/>
-      <c r="E29" s="108"/>
-      <c r="F29" s="108"/>
-      <c r="G29" s="108"/>
-      <c r="H29" s="111"/>
-      <c r="I29" s="108"/>
-      <c r="J29" s="107"/>
+    <row r="29" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="165"/>
+      <c r="B29" s="88"/>
+      <c r="C29" s="91"/>
+      <c r="D29" s="88"/>
+      <c r="E29" s="106"/>
+      <c r="F29" s="106"/>
+      <c r="G29" s="106"/>
+      <c r="H29" s="109"/>
+      <c r="I29" s="106"/>
+      <c r="J29" s="105"/>
       <c r="K29" s="23" t="s">
         <v>55</v>
       </c>
@@ -11107,32 +11111,32 @@
       <c r="U29" s="19"/>
       <c r="V29" s="19"/>
       <c r="W29" s="29"/>
-      <c r="X29" s="104"/>
-      <c r="Y29" s="98"/>
-      <c r="Z29" s="153"/>
-      <c r="AA29" s="129"/>
+      <c r="X29" s="102"/>
+      <c r="Y29" s="96"/>
+      <c r="Z29" s="151"/>
+      <c r="AA29" s="127"/>
     </row>
-    <row r="30" spans="1:27" ht="14.45" customHeight="1">
-      <c r="A30" s="167"/>
-      <c r="B30" s="90"/>
-      <c r="C30" s="93" t="s">
+    <row r="30" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="165"/>
+      <c r="B30" s="88"/>
+      <c r="C30" s="91" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" s="88" t="s">
+        <v>97</v>
+      </c>
+      <c r="E30" s="106" t="s">
         <v>74</v>
       </c>
-      <c r="D30" s="90" t="s">
-        <v>103</v>
-      </c>
-      <c r="E30" s="108" t="s">
-        <v>76</v>
-      </c>
-      <c r="F30" s="108"/>
-      <c r="G30" s="108"/>
-      <c r="H30" s="111" t="s">
+      <c r="F30" s="106"/>
+      <c r="G30" s="106"/>
+      <c r="H30" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I30" s="108" t="s">
+      <c r="I30" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J30" s="107" t="s">
+      <c r="J30" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K30" s="23" t="s">
@@ -11168,22 +11172,22 @@
       <c r="U30" s="25"/>
       <c r="V30" s="25"/>
       <c r="W30" s="26"/>
-      <c r="X30" s="103"/>
-      <c r="Y30" s="152"/>
-      <c r="Z30" s="119"/>
-      <c r="AA30" s="165"/>
+      <c r="X30" s="101"/>
+      <c r="Y30" s="150"/>
+      <c r="Z30" s="117"/>
+      <c r="AA30" s="163"/>
     </row>
-    <row r="31" spans="1:27">
-      <c r="A31" s="167"/>
-      <c r="B31" s="90"/>
-      <c r="C31" s="93"/>
-      <c r="D31" s="90"/>
-      <c r="E31" s="108"/>
-      <c r="F31" s="108"/>
-      <c r="G31" s="108"/>
-      <c r="H31" s="111"/>
-      <c r="I31" s="108"/>
-      <c r="J31" s="107"/>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A31" s="165"/>
+      <c r="B31" s="88"/>
+      <c r="C31" s="91"/>
+      <c r="D31" s="88"/>
+      <c r="E31" s="106"/>
+      <c r="F31" s="106"/>
+      <c r="G31" s="106"/>
+      <c r="H31" s="109"/>
+      <c r="I31" s="106"/>
+      <c r="J31" s="105"/>
       <c r="K31" s="23" t="s">
         <v>55</v>
       </c>
@@ -11217,34 +11221,34 @@
       <c r="U31" s="45"/>
       <c r="V31" s="45"/>
       <c r="W31" s="46"/>
-      <c r="X31" s="104"/>
-      <c r="Y31" s="113"/>
-      <c r="Z31" s="153"/>
-      <c r="AA31" s="166"/>
+      <c r="X31" s="102"/>
+      <c r="Y31" s="111"/>
+      <c r="Z31" s="151"/>
+      <c r="AA31" s="164"/>
     </row>
-    <row r="32" spans="1:27" ht="14.45" customHeight="1">
-      <c r="A32" s="167"/>
-      <c r="B32" s="93" t="s">
-        <v>104</v>
-      </c>
-      <c r="C32" s="122" t="s">
+    <row r="32" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="165"/>
+      <c r="B32" s="91" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="90" t="s">
-        <v>105</v>
-      </c>
-      <c r="E32" s="108" t="s">
-        <v>76</v>
-      </c>
-      <c r="F32" s="108"/>
-      <c r="G32" s="108"/>
-      <c r="H32" s="111" t="s">
+      <c r="D32" s="88" t="s">
+        <v>99</v>
+      </c>
+      <c r="E32" s="106" t="s">
+        <v>74</v>
+      </c>
+      <c r="F32" s="106"/>
+      <c r="G32" s="106"/>
+      <c r="H32" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I32" s="108" t="s">
-        <v>80</v>
-      </c>
-      <c r="J32" s="107" t="s">
+      <c r="I32" s="106" t="s">
+        <v>78</v>
+      </c>
+      <c r="J32" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K32" s="23" t="s">
@@ -11280,28 +11284,28 @@
       <c r="U32" s="8"/>
       <c r="V32" s="8"/>
       <c r="W32" s="34"/>
-      <c r="X32" s="169" t="s">
-        <v>106</v>
-      </c>
-      <c r="Y32" s="97" t="s">
-        <v>107</v>
-      </c>
-      <c r="Z32" s="119"/>
-      <c r="AA32" s="123" t="s">
-        <v>108</v>
+      <c r="X32" s="167" t="s">
+        <v>136</v>
+      </c>
+      <c r="Y32" s="95" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z32" s="117"/>
+      <c r="AA32" s="121" t="s">
+        <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A33" s="167"/>
-      <c r="B33" s="93"/>
-      <c r="C33" s="122"/>
-      <c r="D33" s="90"/>
-      <c r="E33" s="108"/>
-      <c r="F33" s="108"/>
-      <c r="G33" s="108"/>
-      <c r="H33" s="111"/>
-      <c r="I33" s="108"/>
-      <c r="J33" s="107"/>
+    <row r="33" spans="1:29" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="165"/>
+      <c r="B33" s="91"/>
+      <c r="C33" s="120"/>
+      <c r="D33" s="88"/>
+      <c r="E33" s="106"/>
+      <c r="F33" s="106"/>
+      <c r="G33" s="106"/>
+      <c r="H33" s="109"/>
+      <c r="I33" s="106"/>
+      <c r="J33" s="105"/>
       <c r="K33" s="23" t="s">
         <v>55</v>
       </c>
@@ -11335,36 +11339,36 @@
       <c r="U33" s="32"/>
       <c r="V33" s="32"/>
       <c r="W33" s="33"/>
-      <c r="X33" s="170"/>
-      <c r="Y33" s="98"/>
-      <c r="Z33" s="153"/>
-      <c r="AA33" s="124"/>
+      <c r="X33" s="168"/>
+      <c r="Y33" s="96"/>
+      <c r="Z33" s="151"/>
+      <c r="AA33" s="122"/>
     </row>
-    <row r="34" spans="1:29">
-      <c r="A34" s="109" t="s">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A34" s="107" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="148" t="s">
+      <c r="B34" s="146" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="93" t="s">
-        <v>88</v>
-      </c>
-      <c r="D34" s="90" t="s">
+      <c r="C34" s="91" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" s="88" t="s">
         <v>31</v>
       </c>
-      <c r="E34" s="108">
+      <c r="E34" s="106">
         <v>90</v>
       </c>
-      <c r="F34" s="108"/>
-      <c r="G34" s="108"/>
-      <c r="H34" s="111" t="s">
+      <c r="F34" s="106"/>
+      <c r="G34" s="106"/>
+      <c r="H34" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I34" s="108" t="s">
+      <c r="I34" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J34" s="120" t="s">
+      <c r="J34" s="118" t="s">
         <v>34</v>
       </c>
       <c r="K34" s="23" t="s">
@@ -11390,52 +11394,52 @@
       <c r="W34" s="26">
         <v>0.9</v>
       </c>
-      <c r="X34" s="94"/>
-      <c r="Y34" s="96" t="s">
-        <v>109</v>
-      </c>
-      <c r="Z34" s="115"/>
-      <c r="AA34" s="123" t="s">
-        <v>110</v>
+      <c r="X34" s="92"/>
+      <c r="Y34" s="94" t="s">
+        <v>137</v>
+      </c>
+      <c r="Z34" s="113"/>
+      <c r="AA34" s="121" t="s">
+        <v>101</v>
       </c>
     </row>
-    <row r="35" spans="1:29">
-      <c r="A35" s="109"/>
-      <c r="B35" s="148"/>
-      <c r="C35" s="93"/>
-      <c r="D35" s="90"/>
-      <c r="E35" s="108"/>
-      <c r="F35" s="108"/>
-      <c r="G35" s="108"/>
-      <c r="H35" s="111"/>
-      <c r="I35" s="108"/>
-      <c r="J35" s="120"/>
+    <row r="35" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A35" s="107"/>
+      <c r="B35" s="146"/>
+      <c r="C35" s="91"/>
+      <c r="D35" s="88"/>
+      <c r="E35" s="106"/>
+      <c r="F35" s="106"/>
+      <c r="G35" s="106"/>
+      <c r="H35" s="109"/>
+      <c r="I35" s="106"/>
+      <c r="J35" s="118"/>
       <c r="K35" s="23" t="s">
         <v>55</v>
       </c>
       <c r="L35" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M35" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="N35" s="19">
         <v>1</v>
       </c>
       <c r="O35" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="P35" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="Q35" s="19">
         <v>0.96199999999999997</v>
       </c>
       <c r="R35" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="S35" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="T35" s="19">
         <v>0.91300000000000003</v>
@@ -11443,34 +11447,34 @@
       <c r="U35" s="19"/>
       <c r="V35" s="19"/>
       <c r="W35" s="29"/>
-      <c r="X35" s="94"/>
-      <c r="Y35" s="96"/>
-      <c r="Z35" s="115"/>
-      <c r="AA35" s="124"/>
+      <c r="X35" s="92"/>
+      <c r="Y35" s="94"/>
+      <c r="Z35" s="113"/>
+      <c r="AA35" s="122"/>
     </row>
-    <row r="36" spans="1:29">
-      <c r="A36" s="109"/>
-      <c r="B36" s="148" t="s">
+    <row r="36" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A36" s="107"/>
+      <c r="B36" s="146" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="93" t="s">
-        <v>111</v>
-      </c>
-      <c r="D36" s="90" t="s">
+      <c r="C36" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="D36" s="88" t="s">
         <v>37</v>
       </c>
-      <c r="E36" s="108">
+      <c r="E36" s="106">
         <v>83</v>
       </c>
-      <c r="F36" s="108"/>
-      <c r="G36" s="108"/>
-      <c r="H36" s="111" t="s">
+      <c r="F36" s="106"/>
+      <c r="G36" s="106"/>
+      <c r="H36" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I36" s="108" t="s">
+      <c r="I36" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J36" s="121" t="s">
+      <c r="J36" s="119" t="s">
         <v>38</v>
       </c>
       <c r="K36" s="23" t="s">
@@ -11492,96 +11496,96 @@
       <c r="U36" s="18"/>
       <c r="V36" s="18"/>
       <c r="W36" s="28"/>
-      <c r="X36" s="94" t="s">
-        <v>112</v>
-      </c>
-      <c r="Y36" s="95" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z36" s="115"/>
-      <c r="AA36" s="123" t="s">
-        <v>114</v>
+      <c r="X36" s="92" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y36" s="93" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z36" s="113"/>
+      <c r="AA36" s="121" t="s">
+        <v>105</v>
       </c>
     </row>
-    <row r="37" spans="1:29">
-      <c r="A37" s="109"/>
-      <c r="B37" s="148"/>
-      <c r="C37" s="93"/>
-      <c r="D37" s="90"/>
-      <c r="E37" s="108"/>
-      <c r="F37" s="108"/>
-      <c r="G37" s="108"/>
-      <c r="H37" s="111"/>
-      <c r="I37" s="108"/>
-      <c r="J37" s="121"/>
+    <row r="37" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A37" s="107"/>
+      <c r="B37" s="146"/>
+      <c r="C37" s="91"/>
+      <c r="D37" s="88"/>
+      <c r="E37" s="106"/>
+      <c r="F37" s="106"/>
+      <c r="G37" s="106"/>
+      <c r="H37" s="109"/>
+      <c r="I37" s="106"/>
+      <c r="J37" s="119"/>
       <c r="K37" s="23" t="s">
         <v>55</v>
       </c>
       <c r="L37" s="22" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="M37" s="22" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="N37" s="22" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="O37" s="19">
         <v>0.79</v>
       </c>
       <c r="P37" s="22" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="Q37" s="19">
         <v>0.79</v>
       </c>
       <c r="R37" s="22" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="S37" s="57"/>
       <c r="T37" s="57"/>
       <c r="U37" s="57"/>
       <c r="V37" s="57"/>
       <c r="W37" s="58"/>
-      <c r="X37" s="137"/>
-      <c r="Y37" s="97"/>
-      <c r="Z37" s="119"/>
-      <c r="AA37" s="125"/>
+      <c r="X37" s="135"/>
+      <c r="Y37" s="95"/>
+      <c r="Z37" s="117"/>
+      <c r="AA37" s="123"/>
     </row>
-    <row r="38" spans="1:29" s="5" customFormat="1">
-      <c r="A38" s="138"/>
-      <c r="B38" s="138"/>
-      <c r="C38" s="138"/>
-      <c r="D38" s="138"/>
-      <c r="E38" s="138"/>
-      <c r="F38" s="138"/>
-      <c r="G38" s="138"/>
-      <c r="H38" s="138"/>
-      <c r="I38" s="138"/>
-      <c r="J38" s="138"/>
-      <c r="K38" s="138"/>
-      <c r="L38" s="138"/>
-      <c r="M38" s="138"/>
-      <c r="N38" s="138"/>
-      <c r="O38" s="138"/>
-      <c r="P38" s="139"/>
-      <c r="Q38" s="139"/>
-      <c r="R38" s="139"/>
-      <c r="S38" s="139"/>
-      <c r="T38" s="139"/>
-      <c r="U38" s="139"/>
-      <c r="V38" s="139"/>
-      <c r="W38" s="139"/>
-      <c r="X38" s="139"/>
-      <c r="Y38" s="139"/>
-      <c r="Z38" s="139"/>
-      <c r="AA38" s="139"/>
+    <row r="38" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="136"/>
+      <c r="B38" s="136"/>
+      <c r="C38" s="136"/>
+      <c r="D38" s="136"/>
+      <c r="E38" s="136"/>
+      <c r="F38" s="136"/>
+      <c r="G38" s="136"/>
+      <c r="H38" s="136"/>
+      <c r="I38" s="136"/>
+      <c r="J38" s="136"/>
+      <c r="K38" s="136"/>
+      <c r="L38" s="136"/>
+      <c r="M38" s="136"/>
+      <c r="N38" s="136"/>
+      <c r="O38" s="136"/>
+      <c r="P38" s="137"/>
+      <c r="Q38" s="137"/>
+      <c r="R38" s="137"/>
+      <c r="S38" s="137"/>
+      <c r="T38" s="137"/>
+      <c r="U38" s="137"/>
+      <c r="V38" s="137"/>
+      <c r="W38" s="137"/>
+      <c r="X38" s="137"/>
+      <c r="Y38" s="137"/>
+      <c r="Z38" s="137"/>
+      <c r="AA38" s="137"/>
     </row>
-    <row r="39" spans="1:29" s="5" customFormat="1" ht="23.45">
-      <c r="A39" s="141" t="s">
-        <v>116</v>
-      </c>
-      <c r="B39" s="141"/>
+    <row r="39" spans="1:29" s="5" customFormat="1" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="139" t="s">
+        <v>107</v>
+      </c>
+      <c r="B39" s="139"/>
       <c r="C39" s="59"/>
       <c r="D39"/>
       <c r="E39"/>
@@ -11608,12 +11612,12 @@
       <c r="Z39"/>
       <c r="AA39" s="13"/>
     </row>
-    <row r="40" spans="1:29" ht="27.6" customHeight="1">
+    <row r="40" spans="1:29" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="44" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>3</v>
@@ -11622,13 +11626,13 @@
         <v>4</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="H40" s="10" t="s">
         <v>8</v>
@@ -11649,7 +11653,7 @@
         <v>13</v>
       </c>
       <c r="N40" s="10" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="O40" s="10" t="s">
         <v>15</v>
@@ -11658,7 +11662,7 @@
         <v>16</v>
       </c>
       <c r="Q40" s="10" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="R40" s="10" t="s">
         <v>18</v>
@@ -11691,35 +11695,35 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:29">
-      <c r="A41" s="142" t="s">
+    <row r="41" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A41" s="140" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="145" t="s">
-        <v>123</v>
-      </c>
-      <c r="C41" s="146" t="s">
+      <c r="B41" s="143" t="s">
+        <v>114</v>
+      </c>
+      <c r="C41" s="144" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="147" t="s">
-        <v>124</v>
-      </c>
-      <c r="E41" s="140" t="s">
-        <v>93</v>
-      </c>
-      <c r="F41" s="140" t="s">
-        <v>93</v>
-      </c>
-      <c r="G41" s="140" t="s">
-        <v>93</v>
-      </c>
-      <c r="H41" s="159" t="s">
+      <c r="D41" s="145" t="s">
+        <v>115</v>
+      </c>
+      <c r="E41" s="138" t="s">
+        <v>88</v>
+      </c>
+      <c r="F41" s="138" t="s">
+        <v>88</v>
+      </c>
+      <c r="G41" s="138" t="s">
+        <v>88</v>
+      </c>
+      <c r="H41" s="157" t="s">
         <v>51</v>
       </c>
-      <c r="I41" s="140" t="s">
+      <c r="I41" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="J41" s="149" t="s">
+      <c r="J41" s="147" t="s">
         <v>52</v>
       </c>
       <c r="K41" s="62" t="s">
@@ -11761,25 +11765,25 @@
       <c r="W41" s="64">
         <v>3.32E-2</v>
       </c>
-      <c r="X41" s="136"/>
-      <c r="Y41" s="131"/>
-      <c r="Z41" s="131"/>
-      <c r="AA41" s="124" t="s">
-        <v>123</v>
+      <c r="X41" s="134"/>
+      <c r="Y41" s="129"/>
+      <c r="Z41" s="129"/>
+      <c r="AA41" s="122" t="s">
+        <v>114</v>
       </c>
       <c r="AC41" s="12"/>
     </row>
-    <row r="42" spans="1:29" ht="23.1" customHeight="1">
-      <c r="A42" s="143"/>
-      <c r="B42" s="91"/>
-      <c r="C42" s="92"/>
-      <c r="D42" s="90"/>
-      <c r="E42" s="108"/>
-      <c r="F42" s="108"/>
-      <c r="G42" s="108"/>
-      <c r="H42" s="111"/>
-      <c r="I42" s="108"/>
-      <c r="J42" s="127"/>
+    <row r="42" spans="1:29" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="141"/>
+      <c r="B42" s="89"/>
+      <c r="C42" s="90"/>
+      <c r="D42" s="88"/>
+      <c r="E42" s="106"/>
+      <c r="F42" s="106"/>
+      <c r="G42" s="106"/>
+      <c r="H42" s="109"/>
+      <c r="I42" s="106"/>
+      <c r="J42" s="125"/>
       <c r="K42" s="23" t="s">
         <v>55</v>
       </c>
@@ -11813,40 +11817,40 @@
       <c r="U42" s="56"/>
       <c r="V42" s="56"/>
       <c r="W42" s="60"/>
-      <c r="X42" s="136"/>
-      <c r="Y42" s="131"/>
-      <c r="Z42" s="131"/>
-      <c r="AA42" s="126"/>
+      <c r="X42" s="134"/>
+      <c r="Y42" s="129"/>
+      <c r="Z42" s="129"/>
+      <c r="AA42" s="124"/>
     </row>
-    <row r="43" spans="1:29">
-      <c r="A43" s="144" t="s">
+    <row r="43" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A43" s="142" t="s">
         <v>26</v>
       </c>
-      <c r="B43" s="91" t="s">
-        <v>125</v>
-      </c>
-      <c r="C43" s="92" t="s">
-        <v>91</v>
-      </c>
-      <c r="D43" s="90" t="s">
-        <v>126</v>
-      </c>
-      <c r="E43" s="108" t="s">
-        <v>93</v>
-      </c>
-      <c r="F43" s="108" t="s">
-        <v>93</v>
-      </c>
-      <c r="G43" s="108" t="s">
-        <v>93</v>
-      </c>
-      <c r="H43" s="111" t="s">
+      <c r="B43" s="89" t="s">
+        <v>116</v>
+      </c>
+      <c r="C43" s="90" t="s">
+        <v>86</v>
+      </c>
+      <c r="D43" s="88" t="s">
+        <v>117</v>
+      </c>
+      <c r="E43" s="106" t="s">
+        <v>88</v>
+      </c>
+      <c r="F43" s="106" t="s">
+        <v>88</v>
+      </c>
+      <c r="G43" s="106" t="s">
+        <v>88</v>
+      </c>
+      <c r="H43" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I43" s="108" t="s">
+      <c r="I43" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J43" s="120" t="s">
+      <c r="J43" s="118" t="s">
         <v>34</v>
       </c>
       <c r="K43" s="23" t="s">
@@ -11868,95 +11872,95 @@
       <c r="U43" s="36"/>
       <c r="V43" s="36"/>
       <c r="W43" s="39"/>
-      <c r="X43" s="130" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y43" s="132" t="s">
-        <v>128</v>
-      </c>
-      <c r="Z43" s="133"/>
-      <c r="AA43" s="134" t="s">
-        <v>129</v>
+      <c r="X43" s="128" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y43" s="130" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z43" s="131"/>
+      <c r="AA43" s="132" t="s">
+        <v>120</v>
       </c>
     </row>
-    <row r="44" spans="1:29">
-      <c r="A44" s="144"/>
-      <c r="B44" s="91"/>
-      <c r="C44" s="92"/>
-      <c r="D44" s="90"/>
-      <c r="E44" s="108"/>
-      <c r="F44" s="108"/>
-      <c r="G44" s="108"/>
-      <c r="H44" s="111"/>
-      <c r="I44" s="158"/>
-      <c r="J44" s="120"/>
+    <row r="44" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A44" s="142"/>
+      <c r="B44" s="89"/>
+      <c r="C44" s="90"/>
+      <c r="D44" s="88"/>
+      <c r="E44" s="106"/>
+      <c r="F44" s="106"/>
+      <c r="G44" s="106"/>
+      <c r="H44" s="109"/>
+      <c r="I44" s="156"/>
+      <c r="J44" s="118"/>
       <c r="K44" s="23" t="s">
         <v>55</v>
       </c>
       <c r="L44" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M44" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="N44" s="17">
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="O44" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="P44" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="Q44" s="17">
         <v>0.04</v>
       </c>
       <c r="R44" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="S44" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="T44" s="56"/>
       <c r="U44" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="V44" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="W44" s="56"/>
-      <c r="X44" s="130"/>
-      <c r="Y44" s="132"/>
-      <c r="Z44" s="133"/>
-      <c r="AA44" s="134"/>
+      <c r="X44" s="128"/>
+      <c r="Y44" s="130"/>
+      <c r="Z44" s="131"/>
+      <c r="AA44" s="132"/>
     </row>
-    <row r="45" spans="1:29">
-      <c r="A45" s="144"/>
-      <c r="B45" s="91" t="s">
-        <v>130</v>
-      </c>
-      <c r="C45" s="92" t="s">
-        <v>91</v>
-      </c>
-      <c r="D45" s="90" t="s">
-        <v>131</v>
-      </c>
-      <c r="E45" s="108" t="s">
-        <v>93</v>
-      </c>
-      <c r="F45" s="108" t="s">
-        <v>93</v>
-      </c>
-      <c r="G45" s="108" t="s">
-        <v>93</v>
-      </c>
-      <c r="H45" s="111" t="s">
+    <row r="45" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A45" s="142"/>
+      <c r="B45" s="89" t="s">
+        <v>121</v>
+      </c>
+      <c r="C45" s="90" t="s">
+        <v>86</v>
+      </c>
+      <c r="D45" s="88" t="s">
+        <v>122</v>
+      </c>
+      <c r="E45" s="106" t="s">
+        <v>88</v>
+      </c>
+      <c r="F45" s="106" t="s">
+        <v>88</v>
+      </c>
+      <c r="G45" s="106" t="s">
+        <v>88</v>
+      </c>
+      <c r="H45" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I45" s="108" t="s">
+      <c r="I45" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J45" s="127" t="s">
+      <c r="J45" s="125" t="s">
         <v>52</v>
       </c>
       <c r="K45" s="23" t="s">
@@ -11992,28 +11996,28 @@
       <c r="U45" s="36"/>
       <c r="V45" s="36"/>
       <c r="W45" s="39"/>
-      <c r="X45" s="130"/>
-      <c r="Y45" s="132" t="s">
-        <v>132</v>
-      </c>
-      <c r="Z45" s="135">
+      <c r="X45" s="128"/>
+      <c r="Y45" s="130" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z45" s="133">
         <v>46188</v>
       </c>
-      <c r="AA45" s="126" t="s">
-        <v>130</v>
+      <c r="AA45" s="124" t="s">
+        <v>121</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="16.5" customHeight="1">
-      <c r="A46" s="144"/>
-      <c r="B46" s="91"/>
-      <c r="C46" s="92"/>
-      <c r="D46" s="90"/>
-      <c r="E46" s="108"/>
-      <c r="F46" s="108"/>
-      <c r="G46" s="108"/>
-      <c r="H46" s="111"/>
-      <c r="I46" s="108"/>
-      <c r="J46" s="127"/>
+    <row r="46" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="142"/>
+      <c r="B46" s="89"/>
+      <c r="C46" s="90"/>
+      <c r="D46" s="88"/>
+      <c r="E46" s="106"/>
+      <c r="F46" s="106"/>
+      <c r="G46" s="106"/>
+      <c r="H46" s="109"/>
+      <c r="I46" s="106"/>
+      <c r="J46" s="125"/>
       <c r="K46" s="23" t="s">
         <v>55</v>
       </c>
@@ -12047,38 +12051,38 @@
       <c r="U46" s="19"/>
       <c r="V46" s="19"/>
       <c r="W46" s="29"/>
-      <c r="X46" s="130"/>
-      <c r="Y46" s="133"/>
-      <c r="Z46" s="133"/>
-      <c r="AA46" s="126"/>
+      <c r="X46" s="128"/>
+      <c r="Y46" s="131"/>
+      <c r="Z46" s="131"/>
+      <c r="AA46" s="124"/>
     </row>
-    <row r="47" spans="1:29">
-      <c r="A47" s="144"/>
-      <c r="B47" s="91" t="s">
-        <v>133</v>
-      </c>
-      <c r="C47" s="92" t="s">
+    <row r="47" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A47" s="142"/>
+      <c r="B47" s="89" t="s">
+        <v>124</v>
+      </c>
+      <c r="C47" s="90" t="s">
+        <v>83</v>
+      </c>
+      <c r="D47" s="88" t="s">
+        <v>125</v>
+      </c>
+      <c r="E47" s="106" t="s">
         <v>88</v>
       </c>
-      <c r="D47" s="90" t="s">
-        <v>134</v>
-      </c>
-      <c r="E47" s="108" t="s">
-        <v>93</v>
-      </c>
-      <c r="F47" s="108" t="s">
-        <v>93</v>
-      </c>
-      <c r="G47" s="108" t="s">
-        <v>93</v>
-      </c>
-      <c r="H47" s="111" t="s">
+      <c r="F47" s="106" t="s">
+        <v>88</v>
+      </c>
+      <c r="G47" s="106" t="s">
+        <v>88</v>
+      </c>
+      <c r="H47" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I47" s="108" t="s">
-        <v>80</v>
-      </c>
-      <c r="J47" s="127" t="s">
+      <c r="I47" s="106" t="s">
+        <v>78</v>
+      </c>
+      <c r="J47" s="125" t="s">
         <v>52</v>
       </c>
       <c r="K47" s="23" t="s">
@@ -12120,24 +12124,24 @@
       <c r="W47" s="40">
         <v>67</v>
       </c>
-      <c r="X47" s="130"/>
-      <c r="Y47" s="133"/>
-      <c r="Z47" s="133"/>
-      <c r="AA47" s="90" t="s">
-        <v>135</v>
+      <c r="X47" s="128"/>
+      <c r="Y47" s="131"/>
+      <c r="Z47" s="131"/>
+      <c r="AA47" s="88" t="s">
+        <v>126</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="20.45" customHeight="1">
-      <c r="A48" s="144"/>
-      <c r="B48" s="91"/>
-      <c r="C48" s="92"/>
-      <c r="D48" s="90"/>
-      <c r="E48" s="108"/>
-      <c r="F48" s="108"/>
-      <c r="G48" s="108"/>
-      <c r="H48" s="111"/>
-      <c r="I48" s="108"/>
-      <c r="J48" s="127"/>
+    <row r="48" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="142"/>
+      <c r="B48" s="89"/>
+      <c r="C48" s="90"/>
+      <c r="D48" s="88"/>
+      <c r="E48" s="106"/>
+      <c r="F48" s="106"/>
+      <c r="G48" s="106"/>
+      <c r="H48" s="109"/>
+      <c r="I48" s="106"/>
+      <c r="J48" s="125"/>
       <c r="K48" s="23" t="s">
         <v>55</v>
       </c>
@@ -12172,40 +12176,40 @@
       <c r="U48" s="9"/>
       <c r="V48" s="9"/>
       <c r="W48" s="27"/>
-      <c r="X48" s="130"/>
-      <c r="Y48" s="133"/>
-      <c r="Z48" s="133"/>
-      <c r="AA48" s="90"/>
+      <c r="X48" s="128"/>
+      <c r="Y48" s="131"/>
+      <c r="Z48" s="131"/>
+      <c r="AA48" s="88"/>
     </row>
-    <row r="49" spans="1:27">
-      <c r="A49" s="143" t="s">
-        <v>136</v>
-      </c>
-      <c r="B49" s="150" t="s">
-        <v>137</v>
-      </c>
-      <c r="C49" s="92" t="s">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A49" s="141" t="s">
+        <v>127</v>
+      </c>
+      <c r="B49" s="148" t="s">
+        <v>128</v>
+      </c>
+      <c r="C49" s="90" t="s">
         <v>69</v>
       </c>
-      <c r="D49" s="90" t="s">
-        <v>138</v>
-      </c>
-      <c r="E49" s="108">
+      <c r="D49" s="88" t="s">
+        <v>129</v>
+      </c>
+      <c r="E49" s="106">
         <v>74</v>
       </c>
-      <c r="F49" s="108" t="s">
-        <v>93</v>
-      </c>
-      <c r="G49" s="108" t="s">
-        <v>93</v>
-      </c>
-      <c r="H49" s="111" t="s">
+      <c r="F49" s="106" t="s">
+        <v>88</v>
+      </c>
+      <c r="G49" s="106" t="s">
+        <v>88</v>
+      </c>
+      <c r="H49" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I49" s="108" t="s">
+      <c r="I49" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J49" s="107" t="s">
+      <c r="J49" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K49" s="23" t="s">
@@ -12247,24 +12251,24 @@
       <c r="W49" s="41">
         <v>0.73999999999999966</v>
       </c>
-      <c r="X49" s="130"/>
-      <c r="Y49" s="132"/>
-      <c r="Z49" s="133"/>
-      <c r="AA49" s="126" t="s">
-        <v>139</v>
+      <c r="X49" s="128"/>
+      <c r="Y49" s="130"/>
+      <c r="Z49" s="131"/>
+      <c r="AA49" s="124" t="s">
+        <v>130</v>
       </c>
     </row>
-    <row r="50" spans="1:27">
-      <c r="A50" s="143"/>
-      <c r="B50" s="150"/>
-      <c r="C50" s="92"/>
-      <c r="D50" s="90"/>
-      <c r="E50" s="108"/>
-      <c r="F50" s="108"/>
-      <c r="G50" s="108"/>
-      <c r="H50" s="111"/>
-      <c r="I50" s="108"/>
-      <c r="J50" s="107"/>
+    <row r="50" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A50" s="141"/>
+      <c r="B50" s="148"/>
+      <c r="C50" s="90"/>
+      <c r="D50" s="88"/>
+      <c r="E50" s="106"/>
+      <c r="F50" s="106"/>
+      <c r="G50" s="106"/>
+      <c r="H50" s="109"/>
+      <c r="I50" s="106"/>
+      <c r="J50" s="105"/>
       <c r="K50" s="23" t="s">
         <v>55</v>
       </c>
@@ -12298,40 +12302,40 @@
       <c r="U50" s="17"/>
       <c r="V50" s="17"/>
       <c r="W50" s="75"/>
-      <c r="X50" s="130"/>
-      <c r="Y50" s="132"/>
-      <c r="Z50" s="133"/>
-      <c r="AA50" s="126"/>
+      <c r="X50" s="128"/>
+      <c r="Y50" s="130"/>
+      <c r="Z50" s="131"/>
+      <c r="AA50" s="124"/>
     </row>
-    <row r="51" spans="1:27">
-      <c r="A51" s="144" t="s">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A51" s="142" t="s">
         <v>25</v>
       </c>
-      <c r="B51" s="91" t="s">
-        <v>140</v>
-      </c>
-      <c r="C51" s="92" t="s">
-        <v>74</v>
-      </c>
-      <c r="D51" s="90" t="s">
-        <v>141</v>
-      </c>
-      <c r="E51" s="108">
+      <c r="B51" s="89" t="s">
+        <v>131</v>
+      </c>
+      <c r="C51" s="90" t="s">
+        <v>72</v>
+      </c>
+      <c r="D51" s="88" t="s">
+        <v>132</v>
+      </c>
+      <c r="E51" s="106">
         <v>33.1</v>
       </c>
-      <c r="F51" s="108" t="s">
-        <v>93</v>
-      </c>
-      <c r="G51" s="108" t="s">
-        <v>93</v>
-      </c>
-      <c r="H51" s="111" t="s">
+      <c r="F51" s="106" t="s">
+        <v>88</v>
+      </c>
+      <c r="G51" s="106" t="s">
+        <v>88</v>
+      </c>
+      <c r="H51" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I51" s="108" t="s">
+      <c r="I51" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J51" s="107" t="s">
+      <c r="J51" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K51" s="23" t="s">
@@ -12367,24 +12371,24 @@
       <c r="U51" s="36"/>
       <c r="V51" s="36"/>
       <c r="W51" s="39"/>
-      <c r="X51" s="130"/>
-      <c r="Y51" s="133"/>
-      <c r="Z51" s="133"/>
-      <c r="AA51" s="93" t="s">
-        <v>142</v>
+      <c r="X51" s="128"/>
+      <c r="Y51" s="131"/>
+      <c r="Z51" s="131"/>
+      <c r="AA51" s="91" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="15" thickBot="1">
-      <c r="A52" s="144"/>
-      <c r="B52" s="91"/>
-      <c r="C52" s="92"/>
-      <c r="D52" s="90"/>
-      <c r="E52" s="108"/>
-      <c r="F52" s="108"/>
-      <c r="G52" s="108"/>
-      <c r="H52" s="111"/>
-      <c r="I52" s="108"/>
-      <c r="J52" s="107"/>
+    <row r="52" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="142"/>
+      <c r="B52" s="89"/>
+      <c r="C52" s="90"/>
+      <c r="D52" s="88"/>
+      <c r="E52" s="106"/>
+      <c r="F52" s="106"/>
+      <c r="G52" s="106"/>
+      <c r="H52" s="109"/>
+      <c r="I52" s="106"/>
+      <c r="J52" s="105"/>
       <c r="K52" s="23" t="s">
         <v>55</v>
       </c>
@@ -12418,18 +12422,18 @@
       <c r="U52" s="30"/>
       <c r="V52" s="30"/>
       <c r="W52" s="31"/>
-      <c r="X52" s="130"/>
-      <c r="Y52" s="133"/>
-      <c r="Z52" s="133"/>
-      <c r="AA52" s="93"/>
+      <c r="X52" s="128"/>
+      <c r="Y52" s="131"/>
+      <c r="Z52" s="131"/>
+      <c r="AA52" s="91"/>
     </row>
-    <row r="54" spans="1:27" ht="14.45" customHeight="1"/>
-    <row r="56" spans="1:27" ht="14.45" customHeight="1"/>
-    <row r="58" spans="1:27" ht="14.45" customHeight="1"/>
-    <row r="60" spans="1:27" ht="14.45" customHeight="1"/>
-    <row r="62" spans="1:27" ht="14.45" customHeight="1"/>
-    <row r="64" spans="1:27" ht="14.45" customHeight="1"/>
-    <row r="66" ht="14.45" customHeight="1"/>
+    <row r="54" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="56" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="58" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="60" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="62" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="64" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="66" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="270">
     <mergeCell ref="A24:A33"/>
@@ -12750,34 +12754,34 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L27">
-    <cfRule type="expression" dxfId="66" priority="81" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="78">
+      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&gt;L26)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="65" priority="79">
+      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&lt;=L26)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="80">
+      <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&lt;L26)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="63" priority="81" stopIfTrue="1">
       <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&gt;=L26)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="80">
-      <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&lt;L26)</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L7:W7 L9:W9 L11:W11 L13:W13 L17:W17 L19:W19 L21:W21 L23:W23 M27:W27 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37 L15:W15">
+    <cfRule type="expression" dxfId="62" priority="74">
+      <formula>AND(OR($H6="Lower the better", $H6="Lower the better"), L7&gt; L6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="79">
-      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&lt;=L26)</formula>
+    <cfRule type="expression" dxfId="61" priority="247">
+      <formula>AND(OR($H6="Lower the better", $H6= "Lower the Better"), L7 &lt;= L6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="78">
-      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&gt;L26)</formula>
+    <cfRule type="expression" dxfId="60" priority="248">
+      <formula>AND(OR($H6="Higher the better", $H6="Higher the Better"), L7 &lt; L6)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="59" priority="249">
+      <formula xml:space="preserve"> AND(OR($H6="Higher the better", $H6="Higher the Better"), L7&gt;= L6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L7:W7 L9:W9 L11:W11 L13:W13 L15:W15 L17:W17 L19:W19 L21:W21 L23:W23 M27:W27 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37">
-    <cfRule type="expression" dxfId="62" priority="249">
-      <formula xml:space="preserve"> AND(OR($H6="Higher the better", $H6="Higher the Better"), L7&gt;= L6)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="61" priority="74">
-      <formula>AND(OR($H6="Lower the better", $H6="Lower the better"), L7&gt; L6)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="60" priority="247">
-      <formula>AND(OR($H6="Lower the better", $H6= "Lower the Better"), L7 &lt;= L6)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="59" priority="248">
-      <formula>AND(OR($H6="Higher the better", $H6="Higher the Better"), L7 &lt; L6)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L23:W27 L7:W7 L9:W9 L11:W11 L13:W13 L15:W15 L17:W17 L19:W19 L21:W21 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37">
+  <conditionalFormatting sqref="L7:W7 L9:W9 L11:W11 L13:W13 L17:W17 L19:W19 L21:W21 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37 L15:W15 L23:W27">
     <cfRule type="containsBlanks" dxfId="58" priority="245">
       <formula>LEN(TRIM(L7))=0</formula>
     </cfRule>
@@ -12791,185 +12795,185 @@
     <cfRule type="containsBlanks" dxfId="56" priority="173">
       <formula>LEN(TRIM(L46))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="177">
-      <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&lt;L45)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="54" priority="175">
+    <cfRule type="expression" dxfId="55" priority="175">
       <formula>AND(OR($H45="Lower the better", $H45="Lower the Better"), L46&gt;L45)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="176">
+    <cfRule type="expression" dxfId="54" priority="176">
       <formula>AND(OR($H45="Lower the better", $H45="Lower the Better"), L46&lt;=L45)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="53" priority="177">
+      <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&lt;L45)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="52" priority="178" stopIfTrue="1">
       <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&gt;=L45)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L52:W52">
-    <cfRule type="expression" dxfId="51" priority="107">
-      <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&lt;L51)</formula>
+    <cfRule type="containsBlanks" dxfId="51" priority="104">
+      <formula>LEN(TRIM(L52))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="106">
+    <cfRule type="expression" dxfId="50" priority="105">
+      <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&gt;L51)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="49" priority="106">
       <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&lt;=L51)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="49" priority="104">
-      <formula>LEN(TRIM(L52))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="105">
-      <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&gt;L51)</formula>
+    <cfRule type="expression" dxfId="48" priority="107">
+      <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&lt;L51)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="47" priority="108" stopIfTrue="1">
       <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&gt;=L51)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25 T25 W25 L42:W42">
-    <cfRule type="expression" dxfId="46" priority="71" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&gt;=L24)</formula>
+    <cfRule type="containsBlanks" dxfId="46" priority="67">
+      <formula>LEN(TRIM(L25))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="70">
+    <cfRule type="expression" dxfId="45" priority="68">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&gt;L24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="69">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&lt;=L24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="43" priority="70">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&lt;L24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="68">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&gt;L24)</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="43" priority="67">
-      <formula>LEN(TRIM(L25))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="69">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&lt;=L24)</formula>
+    <cfRule type="expression" dxfId="42" priority="71" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&gt;=L24)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25">
-    <cfRule type="expression" dxfId="41" priority="18">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
+    <cfRule type="containsBlanks" dxfId="41" priority="16">
+      <formula>LEN(TRIM(N25))=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="40" priority="17">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&gt;N24)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="39" priority="16">
+    <cfRule type="expression" dxfId="39" priority="18">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="19">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="20" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="36" priority="21">
       <formula>LEN(TRIM(N25))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="25" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="37" priority="22">
+    <cfRule type="expression" dxfId="35" priority="22">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&gt;N24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="24">
+    <cfRule type="expression" dxfId="34" priority="23">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="24">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="35" priority="21">
-      <formula>LEN(TRIM(N25))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="25" stopIfTrue="1">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="23">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="19">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N44">
-    <cfRule type="expression" dxfId="31" priority="65">
+    <cfRule type="containsBlanks" dxfId="31" priority="62">
+      <formula>LEN(TRIM(N44))=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="63">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&gt;N43)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="64">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&lt;=N43)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="65">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&lt;N43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="66" stopIfTrue="1">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&gt;=N43)</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="29" priority="62">
-      <formula>LEN(TRIM(N44))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="63">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&gt;N43)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="64">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&lt;=N43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q25">
-    <cfRule type="expression" dxfId="26" priority="30" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&gt;=Q24)</formula>
+    <cfRule type="containsBlanks" dxfId="26" priority="26">
+      <formula>LEN(TRIM(Q25))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="29">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&lt;Q24)</formula>
+    <cfRule type="expression" dxfId="25" priority="27">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&gt;Q24)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="24" priority="28">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&lt;=Q24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="27">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&gt;Q24)</formula>
+    <cfRule type="expression" dxfId="23" priority="29">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&lt;Q24)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="22" priority="26">
-      <formula>LEN(TRIM(Q25))=0</formula>
+    <cfRule type="expression" dxfId="22" priority="30" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&gt;=Q24)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q37">
-    <cfRule type="expression" dxfId="21" priority="10">
-      <formula xml:space="preserve"> AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37&gt;= Q36)</formula>
+    <cfRule type="expression" dxfId="21" priority="6">
+      <formula>AND(OR($H36="Lower the better", $H36="Lower the better"), Q37&gt; Q36)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="9">
-      <formula>AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37 &lt; Q36)</formula>
+    <cfRule type="containsBlanks" dxfId="20" priority="7">
+      <formula>LEN(TRIM(Q37))=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="8">
       <formula>AND(OR($H36="Lower the better", $H36= "Lower the Better"), Q37 &lt;= Q36)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="6">
-      <formula>AND(OR($H36="Lower the better", $H36="Lower the better"), Q37&gt; Q36)</formula>
+    <cfRule type="expression" dxfId="18" priority="9">
+      <formula>AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37 &lt; Q36)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="17" priority="7">
-      <formula>LEN(TRIM(Q37))=0</formula>
+    <cfRule type="expression" dxfId="17" priority="10">
+      <formula xml:space="preserve"> AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37&gt;= Q36)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q44">
-    <cfRule type="expression" dxfId="16" priority="15" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&gt;=Q43)</formula>
+    <cfRule type="containsBlanks" dxfId="16" priority="11">
+      <formula>LEN(TRIM(Q44))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="14">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&lt;Q43)</formula>
+    <cfRule type="expression" dxfId="15" priority="12">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&gt;Q43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="13">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&lt;=Q43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="12">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&gt;Q43)</formula>
+    <cfRule type="expression" dxfId="13" priority="14">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&lt;Q43)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="12" priority="11">
-      <formula>LEN(TRIM(Q44))=0</formula>
+    <cfRule type="expression" dxfId="12" priority="15" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&gt;=Q43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T44">
-    <cfRule type="expression" dxfId="11" priority="56" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&gt;=T43)</formula>
+    <cfRule type="containsBlanks" dxfId="11" priority="52">
+      <formula>LEN(TRIM(T44))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="55">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&lt;T43)</formula>
+    <cfRule type="expression" dxfId="10" priority="53">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&gt;T43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="9" priority="54">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&lt;=T43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="53">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&gt;T43)</formula>
+    <cfRule type="expression" dxfId="8" priority="55">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&lt;T43)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="7" priority="52">
-      <formula>LEN(TRIM(T44))=0</formula>
+    <cfRule type="expression" dxfId="7" priority="56" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&gt;=T43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W44">
-    <cfRule type="expression" dxfId="6" priority="48">
+    <cfRule type="containsBlanks" dxfId="6" priority="47">
+      <formula>LEN(TRIM(W44))=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="48">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&gt;W43)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="5" priority="47">
-      <formula>LEN(TRIM(W44))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="51" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&gt;=W43)</formula>
+    <cfRule type="expression" dxfId="4" priority="49">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&lt;=W43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="3" priority="50">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&lt;W43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="49">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&lt;=W43)</formula>
+    <cfRule type="expression" dxfId="2" priority="51" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&gt;=W43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA47">
@@ -12982,7 +12986,7 @@
       <formula>LEN(TRIM(AA51))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J41:J52 J6:J37" xr:uid="{61C2D6F6-6FCD-4E8F-B96B-259C330F7837}">
       <formula1>"Monthly, Quarterly, Half yearly"</formula1>
     </dataValidation>
@@ -13020,12 +13024,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -13163,34 +13181,41 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77641BCA-A8DE-46A1-A07C-49ABD030EF3E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="f5a961e1-edc1-4f62-8655-e8a46ef79e5c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="68108f69-118e-4385-83b3-00743b1bf54c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD78E28-5DE7-49AF-AEB8-FF19A745C15E}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -13215,7 +13215,7 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD78E28-5DE7-49AF-AEB8-FF19A745C15E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57B1DF09-E217-42CF-A426-07EED8851D07}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/GlobalMoSMT-2023/Shared Documents/General/2026/Goals Alignment 2026/Strategic Execution 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3303" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A93ABE6-18DF-497E-AC52-532E61417EF1}"/>
+  <xr:revisionPtr revIDLastSave="3308" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76C102A4-A0DE-48BA-9DAF-0B4AD92B8CB0}"/>
   <bookViews>
     <workbookView minimized="1" xWindow="0" yWindow="1030" windowWidth="9600" windowHeight="5450" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
   </bookViews>
@@ -814,11 +814,11 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">-0.8% delta Vs AOP. Excluding GRC 0.7% YoY improvement.  LATAM renewals improved ITM Sep. </t>
-  </si>
-  <si>
     <t>1) Funnel focus actions driven across regions for renewals.
 2) Contract Funnel tracked 90 days before expiry for timely renewals.</t>
+  </si>
+  <si>
+    <t>-0.8% delta Vs AOP. Excluding GRC 0.7% YoY improvement.  LATAM renewals improved ITM Sep. Expected turnaround is Q4 2026 (Dec)</t>
   </si>
 </sst>
 </file>
@@ -1378,9 +1378,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1811,6 +1808,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5203,7 +5203,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="16" x14ac:dyDescent="0.4">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
     </row>
@@ -5317,51 +5317,51 @@
         <f>IF('AOP Critical'!K6="","",'AOP Critical'!K6)</f>
         <v>T</v>
       </c>
-      <c r="K5" s="69">
+      <c r="K5" s="68">
         <f>IF('AOP Critical'!L6="","",'AOP Critical'!L6)</f>
         <v>0.08</v>
       </c>
-      <c r="L5" s="69">
+      <c r="L5" s="68">
         <f>IF('AOP Critical'!M6="","",'AOP Critical'!M6)</f>
         <v>0.08</v>
       </c>
-      <c r="M5" s="69">
+      <c r="M5" s="68">
         <f>IF('AOP Critical'!N6="","",'AOP Critical'!N6)</f>
         <v>0.08</v>
       </c>
-      <c r="N5" s="69">
+      <c r="N5" s="68">
         <f>IF('AOP Critical'!O6="","",'AOP Critical'!O6)</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="O5" s="69">
+      <c r="O5" s="68">
         <f>IF('AOP Critical'!P6="","",'AOP Critical'!P6)</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="P5" s="69">
+      <c r="P5" s="68">
         <f>IF('AOP Critical'!Q6="","",'AOP Critical'!Q6)</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="Q5" s="69">
+      <c r="Q5" s="68">
         <f>IF('AOP Critical'!R6="","",'AOP Critical'!R6)</f>
         <v>0.06</v>
       </c>
-      <c r="R5" s="69">
+      <c r="R5" s="68">
         <f>IF('AOP Critical'!S6="","",'AOP Critical'!S6)</f>
         <v>0.06</v>
       </c>
-      <c r="S5" s="69">
+      <c r="S5" s="68">
         <f>IF('AOP Critical'!T6="","",'AOP Critical'!T6)</f>
         <v>0.06</v>
       </c>
-      <c r="T5" s="69">
+      <c r="T5" s="68">
         <f>IF('AOP Critical'!U6="","",'AOP Critical'!U6)</f>
         <v>0.05</v>
       </c>
-      <c r="U5" s="69">
+      <c r="U5" s="68">
         <f>IF('AOP Critical'!V6="","",'AOP Critical'!V6)</f>
         <v>0.05</v>
       </c>
-      <c r="V5" s="69">
+      <c r="V5" s="68">
         <f>IF('AOP Critical'!W6="","",'AOP Critical'!W6)</f>
         <v>0.05</v>
       </c>
@@ -5403,51 +5403,51 @@
         <f>IF('AOP Critical'!K7="","",'AOP Critical'!K7)</f>
         <v>A</v>
       </c>
-      <c r="K6" s="68">
+      <c r="K6" s="67">
         <f>IF('AOP Critical'!L7="","",'AOP Critical'!L7)</f>
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="L6" s="68">
+      <c r="L6" s="67">
         <f>IF('AOP Critical'!M7="","",'AOP Critical'!M7)</f>
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="M6" s="68">
+      <c r="M6" s="67">
         <f>IF('AOP Critical'!N7="","",'AOP Critical'!N7)</f>
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="N6" s="68">
+      <c r="N6" s="67">
         <f>IF('AOP Critical'!O7="","",'AOP Critical'!O7)</f>
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="O6" s="68">
+      <c r="O6" s="67">
         <f>IF('AOP Critical'!P7="","",'AOP Critical'!P7)</f>
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="P6" s="68">
+      <c r="P6" s="67">
         <f>IF('AOP Critical'!Q7="","",'AOP Critical'!Q7)</f>
         <v>0.03</v>
       </c>
-      <c r="Q6" s="68">
+      <c r="Q6" s="67">
         <f>IF('AOP Critical'!R7="","",'AOP Critical'!R7)</f>
         <v>3.1E-2</v>
       </c>
-      <c r="R6" s="68">
+      <c r="R6" s="67">
         <f>IF('AOP Critical'!S7="","",'AOP Critical'!S7)</f>
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="S6" s="68">
+      <c r="S6" s="67">
         <f>IF('AOP Critical'!T7="","",'AOP Critical'!T7)</f>
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="T6" s="68" t="str">
+      <c r="T6" s="67" t="str">
         <f>IF('AOP Critical'!U7="","",'AOP Critical'!U7)</f>
         <v/>
       </c>
-      <c r="U6" s="68" t="str">
+      <c r="U6" s="67" t="str">
         <f>IF('AOP Critical'!V7="","",'AOP Critical'!V7)</f>
         <v/>
       </c>
-      <c r="V6" s="68" t="str">
+      <c r="V6" s="67" t="str">
         <f>IF('AOP Critical'!W7="","",'AOP Critical'!W7)</f>
         <v/>
       </c>
@@ -5489,51 +5489,51 @@
         <f>IF('AOP Critical'!K8="","",'AOP Critical'!K8)</f>
         <v>T</v>
       </c>
-      <c r="K7" s="70">
+      <c r="K7" s="69">
         <f>IF('AOP Critical'!L8="","",'AOP Critical'!L8)</f>
         <v>0.9</v>
       </c>
-      <c r="L7" s="70">
+      <c r="L7" s="69">
         <f>IF('AOP Critical'!M8="","",'AOP Critical'!M8)</f>
         <v>0.9</v>
       </c>
-      <c r="M7" s="70">
+      <c r="M7" s="69">
         <f>IF('AOP Critical'!N8="","",'AOP Critical'!N8)</f>
         <v>0.9</v>
       </c>
-      <c r="N7" s="70">
+      <c r="N7" s="69">
         <f>IF('AOP Critical'!O8="","",'AOP Critical'!O8)</f>
         <v>0.9</v>
       </c>
-      <c r="O7" s="70">
+      <c r="O7" s="69">
         <f>IF('AOP Critical'!P8="","",'AOP Critical'!P8)</f>
         <v>0.9</v>
       </c>
-      <c r="P7" s="70">
+      <c r="P7" s="69">
         <f>IF('AOP Critical'!Q8="","",'AOP Critical'!Q8)</f>
         <v>0.9</v>
       </c>
-      <c r="Q7" s="70">
+      <c r="Q7" s="69">
         <f>IF('AOP Critical'!R8="","",'AOP Critical'!R8)</f>
         <v>0.9</v>
       </c>
-      <c r="R7" s="70" t="str">
+      <c r="R7" s="69" t="str">
         <f>IF('AOP Critical'!S8="","",'AOP Critical'!S8)</f>
         <v/>
       </c>
-      <c r="S7" s="70" t="str">
+      <c r="S7" s="69" t="str">
         <f>IF('AOP Critical'!T8="","",'AOP Critical'!T8)</f>
         <v/>
       </c>
-      <c r="T7" s="70" t="str">
+      <c r="T7" s="69" t="str">
         <f>IF('AOP Critical'!U8="","",'AOP Critical'!U8)</f>
         <v/>
       </c>
-      <c r="U7" s="70" t="str">
+      <c r="U7" s="69" t="str">
         <f>IF('AOP Critical'!V8="","",'AOP Critical'!V8)</f>
         <v/>
       </c>
-      <c r="V7" s="70" t="str">
+      <c r="V7" s="69" t="str">
         <f>IF('AOP Critical'!W8="","",'AOP Critical'!W8)</f>
         <v/>
       </c>
@@ -5575,51 +5575,51 @@
         <f>IF('AOP Critical'!K9="","",'AOP Critical'!K9)</f>
         <v>A</v>
       </c>
-      <c r="K8" s="71">
+      <c r="K8" s="70">
         <f>IF('AOP Critical'!L9="","",'AOP Critical'!L9)</f>
         <v>1</v>
       </c>
-      <c r="L8" s="71">
+      <c r="L8" s="70">
         <f>IF('AOP Critical'!M9="","",'AOP Critical'!M9)</f>
         <v>0.75</v>
       </c>
-      <c r="M8" s="71">
+      <c r="M8" s="70">
         <f>IF('AOP Critical'!N9="","",'AOP Critical'!N9)</f>
         <v>0.4</v>
       </c>
-      <c r="N8" s="71">
+      <c r="N8" s="70">
         <f>IF('AOP Critical'!O9="","",'AOP Critical'!O9)</f>
         <v>0</v>
       </c>
-      <c r="O8" s="71">
+      <c r="O8" s="70">
         <f>IF('AOP Critical'!P9="","",'AOP Critical'!P9)</f>
         <v>0</v>
       </c>
-      <c r="P8" s="71">
+      <c r="P8" s="70">
         <f>IF('AOP Critical'!Q9="","",'AOP Critical'!Q9)</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="71">
+      <c r="Q8" s="70">
         <f>IF('AOP Critical'!R9="","",'AOP Critical'!R9)</f>
         <v>1</v>
       </c>
-      <c r="R8" s="71">
+      <c r="R8" s="70">
         <f>IF('AOP Critical'!S9="","",'AOP Critical'!S9)</f>
         <v>1</v>
       </c>
-      <c r="S8" s="71">
+      <c r="S8" s="70">
         <f>IF('AOP Critical'!T9="","",'AOP Critical'!T9)</f>
         <v>1</v>
       </c>
-      <c r="T8" s="71" t="str">
+      <c r="T8" s="70" t="str">
         <f>IF('AOP Critical'!U9="","",'AOP Critical'!U9)</f>
         <v/>
       </c>
-      <c r="U8" s="71" t="str">
+      <c r="U8" s="70" t="str">
         <f>IF('AOP Critical'!V9="","",'AOP Critical'!V9)</f>
         <v/>
       </c>
-      <c r="V8" s="71" t="str">
+      <c r="V8" s="70" t="str">
         <f>IF('AOP Critical'!W9="","",'AOP Critical'!W9)</f>
         <v/>
       </c>
@@ -5833,51 +5833,51 @@
         <f>IF('AOP Critical'!K41="","",'AOP Critical'!K41)</f>
         <v>T</v>
       </c>
-      <c r="K11" s="72">
+      <c r="K11" s="71">
         <f>IF('AOP Critical'!L41="","",'AOP Critical'!L41)</f>
         <v>1.9099999999999999E-2</v>
       </c>
-      <c r="L11" s="72">
+      <c r="L11" s="71">
         <f>IF('AOP Critical'!M41="","",'AOP Critical'!M41)</f>
         <v>4.07E-2</v>
       </c>
-      <c r="M11" s="72">
+      <c r="M11" s="71">
         <f>IF('AOP Critical'!N41="","",'AOP Critical'!N41)</f>
         <v>4.6199999999999998E-2</v>
       </c>
-      <c r="N11" s="72">
+      <c r="N11" s="71">
         <f>IF('AOP Critical'!O41="","",'AOP Critical'!O41)</f>
         <v>3.8600000000000002E-2</v>
       </c>
-      <c r="O11" s="72">
+      <c r="O11" s="71">
         <f>IF('AOP Critical'!P41="","",'AOP Critical'!P41)</f>
         <v>3.5299999999999998E-2</v>
       </c>
-      <c r="P11" s="72">
+      <c r="P11" s="71">
         <f>IF('AOP Critical'!Q41="","",'AOP Critical'!Q41)</f>
         <v>2.7099999999999999E-2</v>
       </c>
-      <c r="Q11" s="72">
+      <c r="Q11" s="71">
         <f>IF('AOP Critical'!R41="","",'AOP Critical'!R41)</f>
         <v>2.5100000000000001E-2</v>
       </c>
-      <c r="R11" s="72">
+      <c r="R11" s="71">
         <f>IF('AOP Critical'!S41="","",'AOP Critical'!S41)</f>
         <v>2.41E-2</v>
       </c>
-      <c r="S11" s="72">
+      <c r="S11" s="71">
         <f>IF('AOP Critical'!T41="","",'AOP Critical'!T41)</f>
         <v>3.1600000000000003E-2</v>
       </c>
-      <c r="T11" s="72">
+      <c r="T11" s="71">
         <f>IF('AOP Critical'!U41="","",'AOP Critical'!U41)</f>
         <v>3.1099999999999999E-2</v>
       </c>
-      <c r="U11" s="72">
+      <c r="U11" s="71">
         <f>IF('AOP Critical'!V41="","",'AOP Critical'!V41)</f>
         <v>3.5700000000000003E-2</v>
       </c>
-      <c r="V11" s="72">
+      <c r="V11" s="71">
         <f>IF('AOP Critical'!W41="","",'AOP Critical'!W41)</f>
         <v>3.32E-2</v>
       </c>
@@ -5919,51 +5919,51 @@
         <f>IF('AOP Critical'!K42="","",'AOP Critical'!K42)</f>
         <v>A</v>
       </c>
-      <c r="K12" s="72">
+      <c r="K12" s="71">
         <f>IF('AOP Critical'!L42="","",'AOP Critical'!L42)</f>
         <v>9.1999999999999998E-3</v>
       </c>
-      <c r="L12" s="72">
+      <c r="L12" s="71">
         <f>IF('AOP Critical'!M42="","",'AOP Critical'!M42)</f>
         <v>1.5800000000000002E-2</v>
       </c>
-      <c r="M12" s="72">
+      <c r="M12" s="71">
         <f>IF('AOP Critical'!N42="","",'AOP Critical'!N42)</f>
         <v>1.7600000000000001E-2</v>
       </c>
-      <c r="N12" s="72">
+      <c r="N12" s="71">
         <f>IF('AOP Critical'!O42="","",'AOP Critical'!O42)</f>
         <v>1.5800000000000002E-2</v>
       </c>
-      <c r="O12" s="72">
+      <c r="O12" s="71">
         <f>IF('AOP Critical'!P42="","",'AOP Critical'!P42)</f>
         <v>8.6E-3</v>
       </c>
-      <c r="P12" s="72">
+      <c r="P12" s="71">
         <f>IF('AOP Critical'!Q42="","",'AOP Critical'!Q42)</f>
         <v>1.2699999999999999E-2</v>
       </c>
-      <c r="Q12" s="72">
+      <c r="Q12" s="71">
         <f>IF('AOP Critical'!R42="","",'AOP Critical'!R42)</f>
         <v>1.3299999999999999E-2</v>
       </c>
-      <c r="R12" s="72">
+      <c r="R12" s="71">
         <f>IF('AOP Critical'!S42="","",'AOP Critical'!S42)</f>
         <v>1.3899999999999999E-2</v>
       </c>
-      <c r="S12" s="72">
+      <c r="S12" s="71">
         <f>IF('AOP Critical'!T42="","",'AOP Critical'!T42)</f>
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="T12" s="72" t="str">
+      <c r="T12" s="71" t="str">
         <f>IF('AOP Critical'!U42="","",'AOP Critical'!U42)</f>
         <v/>
       </c>
-      <c r="U12" s="72" t="str">
+      <c r="U12" s="71" t="str">
         <f>IF('AOP Critical'!V42="","",'AOP Critical'!V42)</f>
         <v/>
       </c>
-      <c r="V12" s="72" t="str">
+      <c r="V12" s="71" t="str">
         <f>IF('AOP Critical'!W42="","",'AOP Critical'!W42)</f>
         <v/>
       </c>
@@ -6082,51 +6082,51 @@
         <f>IF('AOP Critical'!K12="","",'AOP Critical'!K12)</f>
         <v>T</v>
       </c>
-      <c r="K15" s="70">
+      <c r="K15" s="69">
         <f>IF('AOP Critical'!L12="","",'AOP Critical'!L12)</f>
         <v>0.69</v>
       </c>
-      <c r="L15" s="70">
+      <c r="L15" s="69">
         <f>IF('AOP Critical'!M12="","",'AOP Critical'!M12)</f>
         <v>0.69</v>
       </c>
-      <c r="M15" s="70">
+      <c r="M15" s="69">
         <f>IF('AOP Critical'!N12="","",'AOP Critical'!N12)</f>
         <v>0.69</v>
       </c>
-      <c r="N15" s="70">
+      <c r="N15" s="69">
         <f>IF('AOP Critical'!O12="","",'AOP Critical'!O12)</f>
         <v>0.72</v>
       </c>
-      <c r="O15" s="70">
+      <c r="O15" s="69">
         <f>IF('AOP Critical'!P12="","",'AOP Critical'!P12)</f>
         <v>0.72</v>
       </c>
-      <c r="P15" s="70">
+      <c r="P15" s="69">
         <f>IF('AOP Critical'!Q12="","",'AOP Critical'!Q12)</f>
         <v>0.72</v>
       </c>
-      <c r="Q15" s="70">
+      <c r="Q15" s="69">
         <f>IF('AOP Critical'!R12="","",'AOP Critical'!R12)</f>
         <v>0.74</v>
       </c>
-      <c r="R15" s="70">
+      <c r="R15" s="69">
         <f>IF('AOP Critical'!S12="","",'AOP Critical'!S12)</f>
         <v>0.74</v>
       </c>
-      <c r="S15" s="70">
+      <c r="S15" s="69">
         <f>IF('AOP Critical'!T12="","",'AOP Critical'!T12)</f>
         <v>0.74</v>
       </c>
-      <c r="T15" s="70">
+      <c r="T15" s="69">
         <f>IF('AOP Critical'!U12="","",'AOP Critical'!U12)</f>
         <v>0.79</v>
       </c>
-      <c r="U15" s="70">
+      <c r="U15" s="69">
         <f>IF('AOP Critical'!V12="","",'AOP Critical'!V12)</f>
         <v>0.79</v>
       </c>
-      <c r="V15" s="70">
+      <c r="V15" s="69">
         <f>IF('AOP Critical'!W12="","",'AOP Critical'!W12)</f>
         <v>0.79</v>
       </c>
@@ -6172,51 +6172,51 @@
         <f>IF('AOP Critical'!K13="","",'AOP Critical'!K13)</f>
         <v>A</v>
       </c>
-      <c r="K16" s="70">
+      <c r="K16" s="69">
         <f>IF('AOP Critical'!L13="","",'AOP Critical'!L13)</f>
         <v>0.83</v>
       </c>
-      <c r="L16" s="70">
+      <c r="L16" s="69">
         <f>IF('AOP Critical'!M13="","",'AOP Critical'!M13)</f>
         <v>0.82</v>
       </c>
-      <c r="M16" s="70">
+      <c r="M16" s="69">
         <f>IF('AOP Critical'!N13="","",'AOP Critical'!N13)</f>
         <v>0.81</v>
       </c>
-      <c r="N16" s="70">
+      <c r="N16" s="69">
         <f>IF('AOP Critical'!O13="","",'AOP Critical'!O13)</f>
         <v>0.6</v>
       </c>
-      <c r="O16" s="70">
+      <c r="O16" s="69">
         <f>IF('AOP Critical'!P13="","",'AOP Critical'!P13)</f>
         <v>0.87</v>
       </c>
-      <c r="P16" s="70">
+      <c r="P16" s="69">
         <f>IF('AOP Critical'!Q13="","",'AOP Critical'!Q13)</f>
         <v>0.77</v>
       </c>
-      <c r="Q16" s="70">
+      <c r="Q16" s="69">
         <f>IF('AOP Critical'!R13="","",'AOP Critical'!R13)</f>
         <v>0.75</v>
       </c>
-      <c r="R16" s="70">
+      <c r="R16" s="69">
         <f>IF('AOP Critical'!S13="","",'AOP Critical'!S13)</f>
         <v>0.81</v>
       </c>
-      <c r="S16" s="70">
+      <c r="S16" s="69">
         <f>IF('AOP Critical'!T13="","",'AOP Critical'!T13)</f>
         <v>0.89</v>
       </c>
-      <c r="T16" s="70" t="str">
+      <c r="T16" s="69" t="str">
         <f>IF('AOP Critical'!U13="","",'AOP Critical'!U13)</f>
         <v/>
       </c>
-      <c r="U16" s="70" t="str">
+      <c r="U16" s="69" t="str">
         <f>IF('AOP Critical'!V13="","",'AOP Critical'!V13)</f>
         <v/>
       </c>
-      <c r="V16" s="70" t="str">
+      <c r="V16" s="69" t="str">
         <f>IF('AOP Critical'!W13="","",'AOP Critical'!W13)</f>
         <v/>
       </c>
@@ -6262,51 +6262,51 @@
         <f>IF('AOP Critical'!K14="","",'AOP Critical'!K14)</f>
         <v>T</v>
       </c>
-      <c r="K17" s="71">
+      <c r="K17" s="70">
         <f>IF('AOP Critical'!L14="","",'AOP Critical'!L14)</f>
         <v>0.54249999999999998</v>
       </c>
-      <c r="L17" s="71">
+      <c r="L17" s="70">
         <f>IF('AOP Critical'!M14="","",'AOP Critical'!M14)</f>
         <v>0.54399999999999993</v>
       </c>
-      <c r="M17" s="71">
+      <c r="M17" s="70">
         <f>IF('AOP Critical'!N14="","",'AOP Critical'!N14)</f>
         <v>0.54549999999999987</v>
       </c>
-      <c r="N17" s="71">
+      <c r="N17" s="70">
         <f>IF('AOP Critical'!O14="","",'AOP Critical'!O14)</f>
         <v>0.54699999999999982</v>
       </c>
-      <c r="O17" s="71">
+      <c r="O17" s="70">
         <f>IF('AOP Critical'!P14="","",'AOP Critical'!P14)</f>
         <v>0.54849999999999977</v>
       </c>
-      <c r="P17" s="71">
+      <c r="P17" s="70">
         <f>IF('AOP Critical'!Q14="","",'AOP Critical'!Q14)</f>
         <v>0.54999999999999971</v>
       </c>
-      <c r="Q17" s="71">
+      <c r="Q17" s="70">
         <f>IF('AOP Critical'!R14="","",'AOP Critical'!R14)</f>
         <v>0.55149999999999966</v>
       </c>
-      <c r="R17" s="71">
+      <c r="R17" s="70">
         <f>IF('AOP Critical'!S14="","",'AOP Critical'!S14)</f>
         <v>0.54510000000000003</v>
       </c>
-      <c r="S17" s="71">
+      <c r="S17" s="70">
         <f>IF('AOP Critical'!T14="","",'AOP Critical'!T14)</f>
         <v>0.54610000000000003</v>
       </c>
-      <c r="T17" s="71" t="str">
+      <c r="T17" s="70" t="str">
         <f>IF('AOP Critical'!U14="","",'AOP Critical'!U14)</f>
         <v/>
       </c>
-      <c r="U17" s="71" t="str">
+      <c r="U17" s="70" t="str">
         <f>IF('AOP Critical'!V14="","",'AOP Critical'!V14)</f>
         <v/>
       </c>
-      <c r="V17" s="71" t="str">
+      <c r="V17" s="70" t="str">
         <f>IF('AOP Critical'!W14="","",'AOP Critical'!W14)</f>
         <v/>
       </c>
@@ -6352,51 +6352,51 @@
         <f>IF('AOP Critical'!K15="","",'AOP Critical'!K15)</f>
         <v>A</v>
       </c>
-      <c r="K18" s="71">
+      <c r="K18" s="70">
         <f>IF('AOP Critical'!L15="","",'AOP Critical'!L15)</f>
         <v>0.51780000000000004</v>
       </c>
-      <c r="L18" s="71">
+      <c r="L18" s="70">
         <f>IF('AOP Critical'!M15="","",'AOP Critical'!M15)</f>
         <v>0.54100000000000004</v>
       </c>
-      <c r="M18" s="71">
+      <c r="M18" s="70">
         <f>IF('AOP Critical'!N15="","",'AOP Critical'!N15)</f>
         <v>0.54100000000000004</v>
       </c>
-      <c r="N18" s="71">
+      <c r="N18" s="70">
         <f>IF('AOP Critical'!O15="","",'AOP Critical'!O15)</f>
         <v>0.53969999999999996</v>
       </c>
-      <c r="O18" s="71">
+      <c r="O18" s="70">
         <f>IF('AOP Critical'!P15="","",'AOP Critical'!P15)</f>
         <v>0.54100000000000004</v>
       </c>
-      <c r="P18" s="71">
+      <c r="P18" s="70">
         <f>IF('AOP Critical'!Q15="","",'AOP Critical'!Q15)</f>
         <v>0.53800000000000003</v>
       </c>
-      <c r="Q18" s="71">
+      <c r="Q18" s="70">
         <f>IF('AOP Critical'!R15="","",'AOP Critical'!R15)</f>
         <v>0.53600000000000003</v>
       </c>
-      <c r="R18" s="71">
+      <c r="R18" s="70">
         <f>IF('AOP Critical'!S15="","",'AOP Critical'!S15)</f>
         <v>0.5363</v>
       </c>
-      <c r="S18" s="71">
+      <c r="S18" s="70">
         <f>IF('AOP Critical'!T15="","",'AOP Critical'!T15)</f>
         <v>0.53749999999999998</v>
       </c>
-      <c r="T18" s="71" t="str">
+      <c r="T18" s="70" t="str">
         <f>IF('AOP Critical'!U15="","",'AOP Critical'!U15)</f>
         <v/>
       </c>
-      <c r="U18" s="71" t="str">
+      <c r="U18" s="70" t="str">
         <f>IF('AOP Critical'!V15="","",'AOP Critical'!V15)</f>
         <v/>
       </c>
-      <c r="V18" s="71" t="str">
+      <c r="V18" s="70" t="str">
         <f>IF('AOP Critical'!W15="","",'AOP Critical'!W15)</f>
         <v/>
       </c>
@@ -6442,51 +6442,51 @@
         <f>IF('AOP Critical'!K49="","",'AOP Critical'!K49)</f>
         <v>T</v>
       </c>
-      <c r="K19" s="72">
+      <c r="K19" s="71">
         <f>IF('AOP Critical'!L49="","",'AOP Critical'!L49)</f>
         <v>0.73199999999999998</v>
       </c>
-      <c r="L19" s="72">
+      <c r="L19" s="71">
         <f>IF('AOP Critical'!M49="","",'AOP Critical'!M49)</f>
         <v>0.72749999999999992</v>
       </c>
-      <c r="M19" s="72">
+      <c r="M19" s="71">
         <f>IF('AOP Critical'!N49="","",'AOP Critical'!N49)</f>
         <v>0.7287499999999999</v>
       </c>
-      <c r="N19" s="72">
+      <c r="N19" s="71">
         <f>IF('AOP Critical'!O49="","",'AOP Critical'!O49)</f>
         <v>0.72999999999999987</v>
       </c>
-      <c r="O19" s="72">
+      <c r="O19" s="71">
         <f>IF('AOP Critical'!P49="","",'AOP Critical'!P49)</f>
         <v>0.73124999999999984</v>
       </c>
-      <c r="P19" s="72">
+      <c r="P19" s="71">
         <f>IF('AOP Critical'!Q49="","",'AOP Critical'!Q49)</f>
         <v>0.73249999999999982</v>
       </c>
-      <c r="Q19" s="72">
+      <c r="Q19" s="71">
         <f>IF('AOP Critical'!R49="","",'AOP Critical'!R49)</f>
         <v>0.73374999999999979</v>
       </c>
-      <c r="R19" s="72">
+      <c r="R19" s="71">
         <f>IF('AOP Critical'!S49="","",'AOP Critical'!S49)</f>
         <v>0.73499999999999976</v>
       </c>
-      <c r="S19" s="72">
+      <c r="S19" s="71">
         <f>IF('AOP Critical'!T49="","",'AOP Critical'!T49)</f>
         <v>0.73624999999999974</v>
       </c>
-      <c r="T19" s="72">
+      <c r="T19" s="71">
         <f>IF('AOP Critical'!U49="","",'AOP Critical'!U49)</f>
         <v>0.73749999999999971</v>
       </c>
-      <c r="U19" s="72">
+      <c r="U19" s="71">
         <f>IF('AOP Critical'!V49="","",'AOP Critical'!V49)</f>
         <v>0.73874999999999968</v>
       </c>
-      <c r="V19" s="72">
+      <c r="V19" s="71">
         <f>IF('AOP Critical'!W49="","",'AOP Critical'!W49)</f>
         <v>0.73999999999999966</v>
       </c>
@@ -6532,51 +6532,51 @@
         <f>IF('AOP Critical'!K50="","",'AOP Critical'!K50)</f>
         <v>A</v>
       </c>
-      <c r="K20" s="72">
+      <c r="K20" s="71">
         <f>IF('AOP Critical'!L50="","",'AOP Critical'!L50)</f>
         <v>0.69299999999999995</v>
       </c>
-      <c r="L20" s="72">
+      <c r="L20" s="71">
         <f>IF('AOP Critical'!M50="","",'AOP Critical'!M50)</f>
         <v>0.71099999999999997</v>
       </c>
-      <c r="M20" s="72">
+      <c r="M20" s="71">
         <f>IF('AOP Critical'!N50="","",'AOP Critical'!N50)</f>
         <v>0.72499999999999998</v>
       </c>
-      <c r="N20" s="72">
+      <c r="N20" s="71">
         <f>IF('AOP Critical'!O50="","",'AOP Critical'!O50)</f>
         <v>0.72299999999999998</v>
       </c>
-      <c r="O20" s="72">
+      <c r="O20" s="71">
         <f>IF('AOP Critical'!P50="","",'AOP Critical'!P50)</f>
         <v>0.73599999999999999</v>
       </c>
-      <c r="P20" s="72">
+      <c r="P20" s="71">
         <f>IF('AOP Critical'!Q50="","",'AOP Critical'!Q50)</f>
         <v>0.74150000000000005</v>
       </c>
-      <c r="Q20" s="72">
+      <c r="Q20" s="71">
         <f>IF('AOP Critical'!R50="","",'AOP Critical'!R50)</f>
         <v>0.74099999999999999</v>
       </c>
-      <c r="R20" s="72">
+      <c r="R20" s="71">
         <f>IF('AOP Critical'!S50="","",'AOP Critical'!S50)</f>
         <v>0.74450000000000005</v>
       </c>
-      <c r="S20" s="72">
+      <c r="S20" s="71">
         <f>IF('AOP Critical'!T50="","",'AOP Critical'!T50)</f>
         <v>0.74770000000000003</v>
       </c>
-      <c r="T20" s="72" t="str">
+      <c r="T20" s="71" t="str">
         <f>IF('AOP Critical'!U50="","",'AOP Critical'!U50)</f>
         <v/>
       </c>
-      <c r="U20" s="72" t="str">
+      <c r="U20" s="71" t="str">
         <f>IF('AOP Critical'!V50="","",'AOP Critical'!V50)</f>
         <v/>
       </c>
-      <c r="V20" s="72" t="str">
+      <c r="V20" s="71" t="str">
         <f>IF('AOP Critical'!W50="","",'AOP Critical'!W50)</f>
         <v/>
       </c>
@@ -6695,51 +6695,51 @@
         <f>IF('AOP Critical'!K16="","",'AOP Critical'!K16)</f>
         <v>T</v>
       </c>
-      <c r="K23" s="71">
+      <c r="K23" s="70">
         <f>IF('AOP Critical'!L16="","",'AOP Critical'!L16)</f>
         <v>0.11774014693384624</v>
       </c>
-      <c r="L23" s="71">
+      <c r="L23" s="70">
         <f>IF('AOP Critical'!M16="","",'AOP Critical'!M16)</f>
         <v>7.6823633140503819E-2</v>
       </c>
-      <c r="M23" s="71">
+      <c r="M23" s="70">
         <f>IF('AOP Critical'!N16="","",'AOP Critical'!N16)</f>
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="N23" s="71">
+      <c r="N23" s="70">
         <f>IF('AOP Critical'!O16="","",'AOP Critical'!O16)</f>
         <v>9.9962463776604421E-2</v>
       </c>
-      <c r="O23" s="71">
+      <c r="O23" s="70">
         <f>IF('AOP Critical'!P16="","",'AOP Critical'!P16)</f>
         <v>0.1038498729590533</v>
       </c>
-      <c r="P23" s="71">
+      <c r="P23" s="70">
         <f>IF('AOP Critical'!Q16="","",'AOP Critical'!Q16)</f>
         <v>0.11814554963094943</v>
       </c>
-      <c r="Q23" s="71">
+      <c r="Q23" s="70">
         <f>IF('AOP Critical'!R16="","",'AOP Critical'!R16)</f>
         <v>0.13344842106998206</v>
       </c>
-      <c r="R23" s="71">
+      <c r="R23" s="70">
         <f>IF('AOP Critical'!S16="","",'AOP Critical'!S16)</f>
         <v>0.13972119594175969</v>
       </c>
-      <c r="S23" s="71">
+      <c r="S23" s="70">
         <f>IF('AOP Critical'!T16="","",'AOP Critical'!T16)</f>
         <v>0.13600000000000001</v>
       </c>
-      <c r="T23" s="71" t="str">
+      <c r="T23" s="70" t="str">
         <f>IF('AOP Critical'!U16="","",'AOP Critical'!U16)</f>
         <v/>
       </c>
-      <c r="U23" s="71" t="str">
+      <c r="U23" s="70" t="str">
         <f>IF('AOP Critical'!V16="","",'AOP Critical'!V16)</f>
         <v/>
       </c>
-      <c r="V23" s="71" t="str">
+      <c r="V23" s="70" t="str">
         <f>IF('AOP Critical'!W16="","",'AOP Critical'!W16)</f>
         <v/>
       </c>
@@ -6785,51 +6785,51 @@
         <f>IF('AOP Critical'!K17="","",'AOP Critical'!K17)</f>
         <v>A</v>
       </c>
-      <c r="K24" s="71">
+      <c r="K24" s="70">
         <f>IF('AOP Critical'!L17="","",'AOP Critical'!L17)</f>
         <v>-4.253311543933095E-2</v>
       </c>
-      <c r="L24" s="71">
+      <c r="L24" s="70">
         <f>IF('AOP Critical'!M17="","",'AOP Critical'!M17)</f>
         <v>7.8013174622509063E-2</v>
       </c>
-      <c r="M24" s="71">
+      <c r="M24" s="70">
         <f>IF('AOP Critical'!N17="","",'AOP Critical'!N17)</f>
         <v>0.14699999999999999</v>
       </c>
-      <c r="N24" s="71">
+      <c r="N24" s="70">
         <f>IF('AOP Critical'!O17="","",'AOP Critical'!O17)</f>
         <v>0.13678322320362704</v>
       </c>
-      <c r="O24" s="71">
+      <c r="O24" s="70">
         <f>IF('AOP Critical'!P17="","",'AOP Critical'!P17)</f>
         <v>0.14558303908159406</v>
       </c>
-      <c r="P24" s="71">
+      <c r="P24" s="70">
         <f>IF('AOP Critical'!Q17="","",'AOP Critical'!Q17)</f>
         <v>0.12590494186157489</v>
       </c>
-      <c r="Q24" s="71">
+      <c r="Q24" s="70">
         <f>IF('AOP Critical'!R17="","",'AOP Critical'!R17)</f>
         <v>0.10712720377087674</v>
       </c>
-      <c r="R24" s="71">
+      <c r="R24" s="70">
         <f>IF('AOP Critical'!S17="","",'AOP Critical'!S17)</f>
         <v>0.12649723977955013</v>
       </c>
-      <c r="S24" s="71">
+      <c r="S24" s="70">
         <f>IF('AOP Critical'!T17="","",'AOP Critical'!T17)</f>
         <v>0.14699999999999999</v>
       </c>
-      <c r="T24" s="71" t="str">
+      <c r="T24" s="70" t="str">
         <f>IF('AOP Critical'!U17="","",'AOP Critical'!U17)</f>
         <v/>
       </c>
-      <c r="U24" s="71" t="str">
+      <c r="U24" s="70" t="str">
         <f>IF('AOP Critical'!V17="","",'AOP Critical'!V17)</f>
         <v/>
       </c>
-      <c r="V24" s="71" t="str">
+      <c r="V24" s="70" t="str">
         <f>IF('AOP Critical'!W17="","",'AOP Critical'!W17)</f>
         <v/>
       </c>
@@ -6875,51 +6875,51 @@
         <f>IF('AOP Critical'!K18="","",'AOP Critical'!K18)</f>
         <v>T</v>
       </c>
-      <c r="K25" s="74">
+      <c r="K25" s="73">
         <f>IF('AOP Critical'!L18="","",'AOP Critical'!L18)</f>
         <v>0.224</v>
       </c>
-      <c r="L25" s="74">
+      <c r="L25" s="73">
         <f>IF('AOP Critical'!M18="","",'AOP Critical'!M18)</f>
         <v>0.35800000000000004</v>
       </c>
-      <c r="M25" s="74">
+      <c r="M25" s="73">
         <f>IF('AOP Critical'!N18="","",'AOP Critical'!N18)</f>
         <v>0.79700000000000004</v>
       </c>
-      <c r="N25" s="74">
+      <c r="N25" s="73">
         <f>IF('AOP Critical'!O18="","",'AOP Critical'!O18)</f>
         <v>1.0409999999999999</v>
       </c>
-      <c r="O25" s="74">
+      <c r="O25" s="73">
         <f>IF('AOP Critical'!P18="","",'AOP Critical'!P18)</f>
         <v>1.155</v>
       </c>
-      <c r="P25" s="74">
+      <c r="P25" s="73">
         <f>IF('AOP Critical'!Q18="","",'AOP Critical'!Q18)</f>
         <v>1.6040000000000001</v>
       </c>
-      <c r="Q25" s="74">
+      <c r="Q25" s="73">
         <f>IF('AOP Critical'!R18="","",'AOP Critical'!R18)</f>
         <v>2.4180000000000001</v>
       </c>
-      <c r="R25" s="74">
+      <c r="R25" s="73">
         <f>IF('AOP Critical'!S18="","",'AOP Critical'!S18)</f>
         <v>2.93</v>
       </c>
-      <c r="S25" s="74">
+      <c r="S25" s="73">
         <f>IF('AOP Critical'!T18="","",'AOP Critical'!T18)</f>
         <v>4.2699999999999996</v>
       </c>
-      <c r="T25" s="74" t="str">
+      <c r="T25" s="73" t="str">
         <f>IF('AOP Critical'!U18="","",'AOP Critical'!U18)</f>
         <v/>
       </c>
-      <c r="U25" s="74" t="str">
+      <c r="U25" s="73" t="str">
         <f>IF('AOP Critical'!V18="","",'AOP Critical'!V18)</f>
         <v/>
       </c>
-      <c r="V25" s="74" t="str">
+      <c r="V25" s="73" t="str">
         <f>IF('AOP Critical'!W18="","",'AOP Critical'!W18)</f>
         <v/>
       </c>
@@ -6965,51 +6965,51 @@
         <f>IF('AOP Critical'!K19="","",'AOP Critical'!K19)</f>
         <v>A</v>
       </c>
-      <c r="K26" s="74">
+      <c r="K26" s="73">
         <f>IF('AOP Critical'!L19="","",'AOP Critical'!L19)</f>
         <v>0.2598381666666667</v>
       </c>
-      <c r="L26" s="74">
+      <c r="L26" s="73">
         <f>IF('AOP Critical'!M19="","",'AOP Critical'!M19)</f>
         <v>0.3838381666666667</v>
       </c>
-      <c r="M26" s="74">
+      <c r="M26" s="73">
         <f>IF('AOP Critical'!N19="","",'AOP Critical'!N19)</f>
         <v>1.1128381666666667</v>
       </c>
-      <c r="N26" s="74">
+      <c r="N26" s="73">
         <f>IF('AOP Critical'!O19="","",'AOP Critical'!O19)</f>
         <v>1.3223861666666668</v>
       </c>
-      <c r="O26" s="74">
+      <c r="O26" s="73">
         <f>IF('AOP Critical'!P19="","",'AOP Critical'!P19)</f>
         <v>1.6513861666666667</v>
       </c>
-      <c r="P26" s="74">
+      <c r="P26" s="73">
         <f>IF('AOP Critical'!Q19="","",'AOP Critical'!Q19)</f>
         <v>2.1303861666666668</v>
       </c>
-      <c r="Q26" s="74">
+      <c r="Q26" s="73">
         <f>IF('AOP Critical'!R19="","",'AOP Critical'!R19)</f>
         <v>2.6433861666666667</v>
       </c>
-      <c r="R26" s="74">
+      <c r="R26" s="73">
         <f>IF('AOP Critical'!S19="","",'AOP Critical'!S19)</f>
         <v>3.3972231666666666</v>
       </c>
-      <c r="S26" s="74">
+      <c r="S26" s="73">
         <f>IF('AOP Critical'!T19="","",'AOP Critical'!T19)</f>
         <v>4.5205241666666662</v>
       </c>
-      <c r="T26" s="74" t="str">
+      <c r="T26" s="73" t="str">
         <f>IF('AOP Critical'!U19="","",'AOP Critical'!U19)</f>
         <v/>
       </c>
-      <c r="U26" s="74" t="str">
+      <c r="U26" s="73" t="str">
         <f>IF('AOP Critical'!V19="","",'AOP Critical'!V19)</f>
         <v/>
       </c>
-      <c r="V26" s="74" t="str">
+      <c r="V26" s="73" t="str">
         <f>IF('AOP Critical'!W19="","",'AOP Critical'!W19)</f>
         <v/>
       </c>
@@ -7055,51 +7055,51 @@
         <f>IF('AOP Critical'!K20="","",'AOP Critical'!K20)</f>
         <v>T</v>
       </c>
-      <c r="K27" s="70">
+      <c r="K27" s="69">
         <f>IF('AOP Critical'!L20="","",'AOP Critical'!L20)</f>
         <v>0.28399999999999997</v>
       </c>
-      <c r="L27" s="70">
+      <c r="L27" s="69">
         <f>IF('AOP Critical'!M20="","",'AOP Critical'!M20)</f>
         <v>0.28260000000000002</v>
       </c>
-      <c r="M27" s="70">
+      <c r="M27" s="69">
         <f>IF('AOP Critical'!N20="","",'AOP Critical'!N20)</f>
         <v>0.28999999999999998</v>
       </c>
-      <c r="N27" s="70">
+      <c r="N27" s="69">
         <f>IF('AOP Critical'!O20="","",'AOP Critical'!O20)</f>
         <v>0.28999999999999998</v>
       </c>
-      <c r="O27" s="70">
+      <c r="O27" s="69">
         <f>IF('AOP Critical'!P20="","",'AOP Critical'!P20)</f>
         <v>0.27</v>
       </c>
-      <c r="P27" s="70">
+      <c r="P27" s="69">
         <f>IF('AOP Critical'!Q20="","",'AOP Critical'!Q20)</f>
         <v>0.26</v>
       </c>
-      <c r="Q27" s="70">
+      <c r="Q27" s="69">
         <f>IF('AOP Critical'!R20="","",'AOP Critical'!R20)</f>
         <v>0.24</v>
       </c>
-      <c r="R27" s="70">
+      <c r="R27" s="69">
         <f>IF('AOP Critical'!S20="","",'AOP Critical'!S20)</f>
         <v>0.23</v>
       </c>
-      <c r="S27" s="70">
+      <c r="S27" s="69">
         <f>IF('AOP Critical'!T20="","",'AOP Critical'!T20)</f>
         <v>0.25</v>
       </c>
-      <c r="T27" s="70" t="str">
+      <c r="T27" s="69" t="str">
         <f>IF('AOP Critical'!U20="","",'AOP Critical'!U20)</f>
         <v/>
       </c>
-      <c r="U27" s="70" t="str">
+      <c r="U27" s="69" t="str">
         <f>IF('AOP Critical'!V20="","",'AOP Critical'!V20)</f>
         <v/>
       </c>
-      <c r="V27" s="70" t="str">
+      <c r="V27" s="69" t="str">
         <f>IF('AOP Critical'!W20="","",'AOP Critical'!W20)</f>
         <v/>
       </c>
@@ -7145,51 +7145,51 @@
         <f>IF('AOP Critical'!K21="","",'AOP Critical'!K21)</f>
         <v>A</v>
       </c>
-      <c r="K28" s="70">
+      <c r="K28" s="69">
         <f>IF('AOP Critical'!L21="","",'AOP Critical'!L21)</f>
         <v>0.27400000000000002</v>
       </c>
-      <c r="L28" s="70">
+      <c r="L28" s="69">
         <f>IF('AOP Critical'!M21="","",'AOP Critical'!M21)</f>
         <v>0.29899999999999999</v>
       </c>
-      <c r="M28" s="70">
+      <c r="M28" s="69">
         <f>IF('AOP Critical'!N21="","",'AOP Critical'!N21)</f>
         <v>0.28999999999999998</v>
       </c>
-      <c r="N28" s="70">
+      <c r="N28" s="69">
         <f>IF('AOP Critical'!O21="","",'AOP Critical'!O21)</f>
         <v>0.3</v>
       </c>
-      <c r="O28" s="70">
+      <c r="O28" s="69">
         <f>IF('AOP Critical'!P21="","",'AOP Critical'!P21)</f>
         <v>0.31</v>
       </c>
-      <c r="P28" s="70">
+      <c r="P28" s="69">
         <f>IF('AOP Critical'!Q21="","",'AOP Critical'!Q21)</f>
         <v>0.28999999999999998</v>
       </c>
-      <c r="Q28" s="70">
+      <c r="Q28" s="69">
         <f>IF('AOP Critical'!R21="","",'AOP Critical'!R21)</f>
         <v>0.3</v>
       </c>
-      <c r="R28" s="70">
+      <c r="R28" s="69">
         <f>IF('AOP Critical'!S21="","",'AOP Critical'!S21)</f>
         <v>0.3</v>
       </c>
-      <c r="S28" s="70">
+      <c r="S28" s="69">
         <f>IF('AOP Critical'!T21="","",'AOP Critical'!T21)</f>
         <v>0.27</v>
       </c>
-      <c r="T28" s="70" t="str">
+      <c r="T28" s="69" t="str">
         <f>IF('AOP Critical'!U21="","",'AOP Critical'!U21)</f>
         <v/>
       </c>
-      <c r="U28" s="70" t="str">
+      <c r="U28" s="69" t="str">
         <f>IF('AOP Critical'!V21="","",'AOP Critical'!V21)</f>
         <v/>
       </c>
-      <c r="V28" s="70" t="str">
+      <c r="V28" s="69" t="str">
         <f>IF('AOP Critical'!W21="","",'AOP Critical'!W21)</f>
         <v/>
       </c>
@@ -7235,51 +7235,51 @@
         <f>IF('AOP Critical'!K51="","",'AOP Critical'!K51)</f>
         <v>T</v>
       </c>
-      <c r="K29" s="71">
+      <c r="K29" s="70">
         <f>IF('AOP Critical'!L51="","",'AOP Critical'!L51)</f>
         <v>0.34700072985878605</v>
       </c>
-      <c r="L29" s="71">
+      <c r="L29" s="70">
         <f>IF('AOP Critical'!M51="","",'AOP Critical'!M51)</f>
         <v>0.32854527661902383</v>
       </c>
-      <c r="M29" s="71">
+      <c r="M29" s="70">
         <f>IF('AOP Critical'!N51="","",'AOP Critical'!N51)</f>
         <v>0.30191652751587683</v>
       </c>
-      <c r="N29" s="71">
+      <c r="N29" s="70">
         <f>IF('AOP Critical'!O51="","",'AOP Critical'!O51)</f>
         <v>0.32233175889748933</v>
       </c>
-      <c r="O29" s="71">
+      <c r="O29" s="70">
         <f>IF('AOP Critical'!P51="","",'AOP Critical'!P51)</f>
         <v>0.32732965712929335</v>
       </c>
-      <c r="P29" s="71">
+      <c r="P29" s="70">
         <f>IF('AOP Critical'!Q51="","",'AOP Critical'!Q51)</f>
         <v>0.31564073493651035</v>
       </c>
-      <c r="Q29" s="71">
+      <c r="Q29" s="70">
         <f>IF('AOP Critical'!R51="","",'AOP Critical'!R51)</f>
         <v>0.33096935042775388</v>
       </c>
-      <c r="R29" s="71">
+      <c r="R29" s="70">
         <f>IF('AOP Critical'!S51="","",'AOP Critical'!S51)</f>
         <v>0.33943248102419393</v>
       </c>
-      <c r="S29" s="71">
+      <c r="S29" s="70">
         <f>IF('AOP Critical'!T51="","",'AOP Critical'!T51)</f>
         <v>0.33082830926903184</v>
       </c>
-      <c r="T29" s="71" t="str">
+      <c r="T29" s="70" t="str">
         <f>IF('AOP Critical'!U51="","",'AOP Critical'!U51)</f>
         <v/>
       </c>
-      <c r="U29" s="71" t="str">
+      <c r="U29" s="70" t="str">
         <f>IF('AOP Critical'!V51="","",'AOP Critical'!V51)</f>
         <v/>
       </c>
-      <c r="V29" s="71" t="str">
+      <c r="V29" s="70" t="str">
         <f>IF('AOP Critical'!W51="","",'AOP Critical'!W51)</f>
         <v/>
       </c>
@@ -7325,51 +7325,51 @@
         <f>IF('AOP Critical'!K52="","",'AOP Critical'!K52)</f>
         <v>A</v>
       </c>
-      <c r="K30" s="71">
+      <c r="K30" s="70">
         <f>IF('AOP Critical'!L52="","",'AOP Critical'!L52)</f>
         <v>0.36591770011686803</v>
       </c>
-      <c r="L30" s="71">
+      <c r="L30" s="70">
         <f>IF('AOP Critical'!M52="","",'AOP Critical'!M52)</f>
         <v>0.43346514302305739</v>
       </c>
-      <c r="M30" s="71">
+      <c r="M30" s="70">
         <f>IF('AOP Critical'!N52="","",'AOP Critical'!N52)</f>
         <v>0.41319844449711768</v>
       </c>
-      <c r="N30" s="71">
+      <c r="N30" s="70">
         <f>IF('AOP Critical'!O52="","",'AOP Critical'!O52)</f>
         <v>0.41195005974326776</v>
       </c>
-      <c r="O30" s="71">
+      <c r="O30" s="70">
         <f>IF('AOP Critical'!P52="","",'AOP Critical'!P52)</f>
         <v>0.40747704161607318</v>
       </c>
-      <c r="P30" s="71">
+      <c r="P30" s="70">
         <f>IF('AOP Critical'!Q52="","",'AOP Critical'!Q52)</f>
         <v>0.36849551470072495</v>
       </c>
-      <c r="Q30" s="71">
+      <c r="Q30" s="70">
         <f>IF('AOP Critical'!R52="","",'AOP Critical'!R52)</f>
         <v>0.35573521911109235</v>
       </c>
-      <c r="R30" s="71">
+      <c r="R30" s="70">
         <f>IF('AOP Critical'!S52="","",'AOP Critical'!S52)</f>
         <v>0.36691053201149237</v>
       </c>
-      <c r="S30" s="71">
+      <c r="S30" s="70">
         <f>IF('AOP Critical'!T52="","",'AOP Critical'!T52)</f>
         <v>0.36899999999999999</v>
       </c>
-      <c r="T30" s="71" t="str">
+      <c r="T30" s="70" t="str">
         <f>IF('AOP Critical'!U52="","",'AOP Critical'!U52)</f>
         <v/>
       </c>
-      <c r="U30" s="71" t="str">
+      <c r="U30" s="70" t="str">
         <f>IF('AOP Critical'!V52="","",'AOP Critical'!V52)</f>
         <v/>
       </c>
-      <c r="V30" s="71" t="str">
+      <c r="V30" s="70" t="str">
         <f>IF('AOP Critical'!W52="","",'AOP Critical'!W52)</f>
         <v/>
       </c>
@@ -7488,51 +7488,51 @@
         <f>IF('AOP Critical'!K26="","",'AOP Critical'!K26)</f>
         <v>T</v>
       </c>
-      <c r="K33" s="70">
+      <c r="K33" s="69">
         <f>IF('AOP Critical'!L26="","",'AOP Critical'!L26)</f>
         <v>0.34</v>
       </c>
-      <c r="L33" s="70">
+      <c r="L33" s="69">
         <f>IF('AOP Critical'!M26="","",'AOP Critical'!M26)</f>
         <v>0.34</v>
       </c>
-      <c r="M33" s="70">
+      <c r="M33" s="69">
         <f>IF('AOP Critical'!N26="","",'AOP Critical'!N26)</f>
         <v>0.34</v>
       </c>
-      <c r="N33" s="70">
+      <c r="N33" s="69">
         <f>IF('AOP Critical'!O26="","",'AOP Critical'!O26)</f>
         <v>0.34</v>
       </c>
-      <c r="O33" s="70">
+      <c r="O33" s="69">
         <f>IF('AOP Critical'!P26="","",'AOP Critical'!P26)</f>
         <v>0.34</v>
       </c>
-      <c r="P33" s="70">
+      <c r="P33" s="69">
         <f>IF('AOP Critical'!Q26="","",'AOP Critical'!Q26)</f>
         <v>0.34</v>
       </c>
-      <c r="Q33" s="70">
+      <c r="Q33" s="69">
         <f>IF('AOP Critical'!R26="","",'AOP Critical'!R26)</f>
         <v>0.34</v>
       </c>
-      <c r="R33" s="70">
+      <c r="R33" s="69">
         <f>IF('AOP Critical'!S26="","",'AOP Critical'!S26)</f>
         <v>0.34</v>
       </c>
-      <c r="S33" s="70">
+      <c r="S33" s="69">
         <f>IF('AOP Critical'!T26="","",'AOP Critical'!T26)</f>
         <v>0.34</v>
       </c>
-      <c r="T33" s="70" t="str">
+      <c r="T33" s="69" t="str">
         <f>IF('AOP Critical'!U26="","",'AOP Critical'!U26)</f>
         <v/>
       </c>
-      <c r="U33" s="70" t="str">
+      <c r="U33" s="69" t="str">
         <f>IF('AOP Critical'!V26="","",'AOP Critical'!V26)</f>
         <v/>
       </c>
-      <c r="V33" s="70" t="str">
+      <c r="V33" s="69" t="str">
         <f>IF('AOP Critical'!W26="","",'AOP Critical'!W26)</f>
         <v/>
       </c>
@@ -7578,51 +7578,51 @@
         <f>IF('AOP Critical'!K27="","",'AOP Critical'!K27)</f>
         <v>A</v>
       </c>
-      <c r="K34" s="70">
+      <c r="K34" s="69">
         <f>IF('AOP Critical'!L27="","",'AOP Critical'!L27)</f>
         <v>0.318</v>
       </c>
-      <c r="L34" s="70">
+      <c r="L34" s="69">
         <f>IF('AOP Critical'!M27="","",'AOP Critical'!M27)</f>
         <v>0.35799999999999998</v>
       </c>
-      <c r="M34" s="70">
+      <c r="M34" s="69">
         <f>IF('AOP Critical'!N27="","",'AOP Critical'!N27)</f>
         <v>0.41499999999999998</v>
       </c>
-      <c r="N34" s="70">
+      <c r="N34" s="69">
         <f>IF('AOP Critical'!O27="","",'AOP Critical'!O27)</f>
         <v>0.40500000000000003</v>
       </c>
-      <c r="O34" s="70">
+      <c r="O34" s="69">
         <f>IF('AOP Critical'!P27="","",'AOP Critical'!P27)</f>
         <v>0.371</v>
       </c>
-      <c r="P34" s="70">
+      <c r="P34" s="69">
         <f>IF('AOP Critical'!Q27="","",'AOP Critical'!Q27)</f>
         <v>0.41899999999999998</v>
       </c>
-      <c r="Q34" s="70">
+      <c r="Q34" s="69">
         <f>IF('AOP Critical'!R27="","",'AOP Critical'!R27)</f>
         <v>0.39900000000000002</v>
       </c>
-      <c r="R34" s="70">
+      <c r="R34" s="69">
         <f>IF('AOP Critical'!S27="","",'AOP Critical'!S27)</f>
         <v>0.41199999999999998</v>
       </c>
-      <c r="S34" s="70">
+      <c r="S34" s="69">
         <f>IF('AOP Critical'!T27="","",'AOP Critical'!T27)</f>
         <v>0.42299999999999999</v>
       </c>
-      <c r="T34" s="70" t="str">
+      <c r="T34" s="69" t="str">
         <f>IF('AOP Critical'!U27="","",'AOP Critical'!U27)</f>
         <v/>
       </c>
-      <c r="U34" s="70" t="str">
+      <c r="U34" s="69" t="str">
         <f>IF('AOP Critical'!V27="","",'AOP Critical'!V27)</f>
         <v/>
       </c>
-      <c r="V34" s="70" t="str">
+      <c r="V34" s="69" t="str">
         <f>IF('AOP Critical'!W27="","",'AOP Critical'!W27)</f>
         <v/>
       </c>
@@ -7668,51 +7668,51 @@
         <f>IF('AOP Critical'!K22="","",'AOP Critical'!K22)</f>
         <v>T</v>
       </c>
-      <c r="K35" s="70">
+      <c r="K35" s="69">
         <f>IF('AOP Critical'!L22="","",'AOP Critical'!L22)</f>
         <v>0.9</v>
       </c>
-      <c r="L35" s="70">
+      <c r="L35" s="69">
         <f>IF('AOP Critical'!M22="","",'AOP Critical'!M22)</f>
         <v>0.9</v>
       </c>
-      <c r="M35" s="70">
+      <c r="M35" s="69">
         <f>IF('AOP Critical'!N22="","",'AOP Critical'!N22)</f>
         <v>0.9</v>
       </c>
-      <c r="N35" s="70">
+      <c r="N35" s="69">
         <f>IF('AOP Critical'!O22="","",'AOP Critical'!O22)</f>
         <v>0.9</v>
       </c>
-      <c r="O35" s="70">
+      <c r="O35" s="69">
         <f>IF('AOP Critical'!P22="","",'AOP Critical'!P22)</f>
         <v>0.9</v>
       </c>
-      <c r="P35" s="70">
+      <c r="P35" s="69">
         <f>IF('AOP Critical'!Q22="","",'AOP Critical'!Q22)</f>
         <v>0.9</v>
       </c>
-      <c r="Q35" s="70">
+      <c r="Q35" s="69">
         <f>IF('AOP Critical'!R22="","",'AOP Critical'!R22)</f>
         <v>0.9</v>
       </c>
-      <c r="R35" s="70">
+      <c r="R35" s="69">
         <f>IF('AOP Critical'!S22="","",'AOP Critical'!S22)</f>
         <v>0.9</v>
       </c>
-      <c r="S35" s="70">
+      <c r="S35" s="69">
         <f>IF('AOP Critical'!T22="","",'AOP Critical'!T22)</f>
         <v>0.9</v>
       </c>
-      <c r="T35" s="70">
+      <c r="T35" s="69">
         <f>IF('AOP Critical'!U22="","",'AOP Critical'!U22)</f>
         <v>0.9</v>
       </c>
-      <c r="U35" s="70">
+      <c r="U35" s="69">
         <f>IF('AOP Critical'!V22="","",'AOP Critical'!V22)</f>
         <v>0.9</v>
       </c>
-      <c r="V35" s="70">
+      <c r="V35" s="69">
         <f>IF('AOP Critical'!W22="","",'AOP Critical'!W22)</f>
         <v>0.9</v>
       </c>
@@ -7758,51 +7758,51 @@
         <f>IF('AOP Critical'!K23="","",'AOP Critical'!K23)</f>
         <v>A</v>
       </c>
-      <c r="K36" s="70">
+      <c r="K36" s="69">
         <f>IF('AOP Critical'!L23="","",'AOP Critical'!L23)</f>
         <v>0.81</v>
       </c>
-      <c r="L36" s="70">
+      <c r="L36" s="69">
         <f>IF('AOP Critical'!M23="","",'AOP Critical'!M23)</f>
         <v>0.78</v>
       </c>
-      <c r="M36" s="70">
+      <c r="M36" s="69">
         <f>IF('AOP Critical'!N23="","",'AOP Critical'!N23)</f>
         <v>0.8</v>
       </c>
-      <c r="N36" s="70">
+      <c r="N36" s="69">
         <f>IF('AOP Critical'!O23="","",'AOP Critical'!O23)</f>
         <v>0.82</v>
       </c>
-      <c r="O36" s="70">
+      <c r="O36" s="69">
         <f>IF('AOP Critical'!P23="","",'AOP Critical'!P23)</f>
         <v>0.79500000000000004</v>
       </c>
-      <c r="P36" s="70">
+      <c r="P36" s="69">
         <f>IF('AOP Critical'!Q23="","",'AOP Critical'!Q23)</f>
         <v>0.86</v>
       </c>
-      <c r="Q36" s="70">
+      <c r="Q36" s="69">
         <f>IF('AOP Critical'!R23="","",'AOP Critical'!R23)</f>
         <v>0.88</v>
       </c>
-      <c r="R36" s="70">
+      <c r="R36" s="69">
         <f>IF('AOP Critical'!S23="","",'AOP Critical'!S23)</f>
         <v>0.94</v>
       </c>
-      <c r="S36" s="70">
+      <c r="S36" s="69">
         <f>IF('AOP Critical'!T23="","",'AOP Critical'!T23)</f>
-        <v>0.91</v>
-      </c>
-      <c r="T36" s="70" t="str">
+        <v>0.94</v>
+      </c>
+      <c r="T36" s="69" t="str">
         <f>IF('AOP Critical'!U23="","",'AOP Critical'!U23)</f>
         <v/>
       </c>
-      <c r="U36" s="70" t="str">
+      <c r="U36" s="69" t="str">
         <f>IF('AOP Critical'!V23="","",'AOP Critical'!V23)</f>
         <v/>
       </c>
-      <c r="V36" s="70" t="str">
+      <c r="V36" s="69" t="str">
         <f>IF('AOP Critical'!W23="","",'AOP Critical'!W23)</f>
         <v/>
       </c>
@@ -7848,51 +7848,51 @@
         <f>IF('AOP Critical'!K43="","",'AOP Critical'!K43)</f>
         <v>T</v>
       </c>
-      <c r="K37" s="71" t="str">
+      <c r="K37" s="70" t="str">
         <f>IF('AOP Critical'!L43="","",'AOP Critical'!L43)</f>
         <v/>
       </c>
-      <c r="L37" s="71" t="str">
+      <c r="L37" s="70" t="str">
         <f>IF('AOP Critical'!M43="","",'AOP Critical'!M43)</f>
         <v/>
       </c>
-      <c r="M37" s="71">
+      <c r="M37" s="70">
         <f>IF('AOP Critical'!N43="","",'AOP Critical'!N43)</f>
         <v>0.05</v>
       </c>
-      <c r="N37" s="71" t="str">
+      <c r="N37" s="70" t="str">
         <f>IF('AOP Critical'!O43="","",'AOP Critical'!O43)</f>
         <v/>
       </c>
-      <c r="O37" s="71" t="str">
+      <c r="O37" s="70" t="str">
         <f>IF('AOP Critical'!P43="","",'AOP Critical'!P43)</f>
         <v/>
       </c>
-      <c r="P37" s="71">
+      <c r="P37" s="70">
         <f>IF('AOP Critical'!Q43="","",'AOP Critical'!Q43)</f>
         <v>5.5E-2</v>
       </c>
-      <c r="Q37" s="71" t="str">
+      <c r="Q37" s="70" t="str">
         <f>IF('AOP Critical'!R43="","",'AOP Critical'!R43)</f>
         <v/>
       </c>
-      <c r="R37" s="71" t="str">
+      <c r="R37" s="70" t="str">
         <f>IF('AOP Critical'!S43="","",'AOP Critical'!S43)</f>
         <v/>
       </c>
-      <c r="S37" s="71" t="str">
+      <c r="S37" s="70" t="str">
         <f>IF('AOP Critical'!T43="","",'AOP Critical'!T43)</f>
         <v/>
       </c>
-      <c r="T37" s="71" t="str">
+      <c r="T37" s="70" t="str">
         <f>IF('AOP Critical'!U43="","",'AOP Critical'!U43)</f>
         <v/>
       </c>
-      <c r="U37" s="71" t="str">
+      <c r="U37" s="70" t="str">
         <f>IF('AOP Critical'!V43="","",'AOP Critical'!V43)</f>
         <v/>
       </c>
-      <c r="V37" s="71" t="str">
+      <c r="V37" s="70" t="str">
         <f>IF('AOP Critical'!W43="","",'AOP Critical'!W43)</f>
         <v/>
       </c>
@@ -8028,51 +8028,51 @@
         <f>IF('AOP Critical'!K45="","",'AOP Critical'!K45)</f>
         <v>T</v>
       </c>
-      <c r="K39" s="71">
+      <c r="K39" s="70">
         <f>IF('AOP Critical'!L45="","",'AOP Critical'!L45)</f>
         <v>0.4</v>
       </c>
-      <c r="L39" s="71">
+      <c r="L39" s="70">
         <f>IF('AOP Critical'!M45="","",'AOP Critical'!M45)</f>
         <v>0.4</v>
       </c>
-      <c r="M39" s="71">
+      <c r="M39" s="70">
         <f>IF('AOP Critical'!N45="","",'AOP Critical'!N45)</f>
         <v>0.4</v>
       </c>
-      <c r="N39" s="71">
+      <c r="N39" s="70">
         <f>IF('AOP Critical'!O45="","",'AOP Critical'!O45)</f>
         <v>0.4</v>
       </c>
-      <c r="O39" s="71">
+      <c r="O39" s="70">
         <f>IF('AOP Critical'!P45="","",'AOP Critical'!P45)</f>
         <v>0.4</v>
       </c>
-      <c r="P39" s="71">
+      <c r="P39" s="70">
         <f>IF('AOP Critical'!Q45="","",'AOP Critical'!Q45)</f>
         <v>0.4</v>
       </c>
-      <c r="Q39" s="71">
+      <c r="Q39" s="70">
         <f>IF('AOP Critical'!R45="","",'AOP Critical'!R45)</f>
         <v>0.4</v>
       </c>
-      <c r="R39" s="71">
+      <c r="R39" s="70">
         <f>IF('AOP Critical'!S45="","",'AOP Critical'!S45)</f>
         <v>0.4</v>
       </c>
-      <c r="S39" s="71">
+      <c r="S39" s="70">
         <f>IF('AOP Critical'!T45="","",'AOP Critical'!T45)</f>
         <v>0.4</v>
       </c>
-      <c r="T39" s="71" t="str">
+      <c r="T39" s="70" t="str">
         <f>IF('AOP Critical'!U45="","",'AOP Critical'!U45)</f>
         <v/>
       </c>
-      <c r="U39" s="71" t="str">
+      <c r="U39" s="70" t="str">
         <f>IF('AOP Critical'!V45="","",'AOP Critical'!V45)</f>
         <v/>
       </c>
-      <c r="V39" s="71" t="str">
+      <c r="V39" s="70" t="str">
         <f>IF('AOP Critical'!W45="","",'AOP Critical'!W45)</f>
         <v/>
       </c>
@@ -8118,51 +8118,51 @@
         <f>IF('AOP Critical'!K46="","",'AOP Critical'!K46)</f>
         <v>A</v>
       </c>
-      <c r="K40" s="71">
+      <c r="K40" s="70">
         <f>IF('AOP Critical'!L46="","",'AOP Critical'!L46)</f>
         <v>0.66</v>
       </c>
-      <c r="L40" s="71">
+      <c r="L40" s="70">
         <f>IF('AOP Critical'!M46="","",'AOP Critical'!M46)</f>
         <v>0.34</v>
       </c>
-      <c r="M40" s="71">
+      <c r="M40" s="70">
         <f>IF('AOP Critical'!N46="","",'AOP Critical'!N46)</f>
         <v>0.41</v>
       </c>
-      <c r="N40" s="71">
+      <c r="N40" s="70">
         <f>IF('AOP Critical'!O46="","",'AOP Critical'!O46)</f>
         <v>0.39</v>
       </c>
-      <c r="O40" s="71">
+      <c r="O40" s="70">
         <f>IF('AOP Critical'!P46="","",'AOP Critical'!P46)</f>
         <v>0.40799999999999997</v>
       </c>
-      <c r="P40" s="71">
+      <c r="P40" s="70">
         <f>IF('AOP Critical'!Q46="","",'AOP Critical'!Q46)</f>
         <v>0.43</v>
       </c>
-      <c r="Q40" s="71">
+      <c r="Q40" s="70">
         <f>IF('AOP Critical'!R46="","",'AOP Critical'!R46)</f>
         <v>0.56000000000000005</v>
       </c>
-      <c r="R40" s="71">
+      <c r="R40" s="70">
         <f>IF('AOP Critical'!S46="","",'AOP Critical'!S46)</f>
         <v>0.39</v>
       </c>
-      <c r="S40" s="71">
+      <c r="S40" s="70">
         <f>IF('AOP Critical'!T46="","",'AOP Critical'!T46)</f>
         <v>0.37</v>
       </c>
-      <c r="T40" s="71" t="str">
+      <c r="T40" s="70" t="str">
         <f>IF('AOP Critical'!U46="","",'AOP Critical'!U46)</f>
         <v/>
       </c>
-      <c r="U40" s="71" t="str">
+      <c r="U40" s="70" t="str">
         <f>IF('AOP Critical'!V46="","",'AOP Critical'!V46)</f>
         <v/>
       </c>
-      <c r="V40" s="71" t="str">
+      <c r="V40" s="70" t="str">
         <f>IF('AOP Critical'!W46="","",'AOP Critical'!W46)</f>
         <v/>
       </c>
@@ -8461,51 +8461,51 @@
         <f>IF('AOP Critical'!K28="","",'AOP Critical'!K28)</f>
         <v>T</v>
       </c>
-      <c r="K45" s="71" vm="1">
+      <c r="K45" s="70" vm="1">
         <f>IF('AOP Critical'!L28="","",'AOP Critical'!L28)</f>
         <v>3.6951550944796852E-2</v>
       </c>
-      <c r="L45" s="71" vm="3">
+      <c r="L45" s="70" vm="3">
         <f>IF('AOP Critical'!M28="","",'AOP Critical'!M28)</f>
         <v>0.43621586155644376</v>
       </c>
-      <c r="M45" s="71" vm="6">
+      <c r="M45" s="70" vm="6">
         <f>IF('AOP Critical'!N28="","",'AOP Critical'!N28)</f>
         <v>6.9838696752701823E-2</v>
       </c>
-      <c r="N45" s="71" vm="10">
+      <c r="N45" s="70" vm="10">
         <f>IF('AOP Critical'!O28="","",'AOP Critical'!O28)</f>
         <v>0.21843539773619547</v>
       </c>
-      <c r="O45" s="71" vm="12">
+      <c r="O45" s="70" vm="12">
         <f>IF('AOP Critical'!P28="","",'AOP Critical'!P28)</f>
         <v>0.20239261325941293</v>
       </c>
-      <c r="P45" s="71" vm="14">
+      <c r="P45" s="70" vm="14">
         <f>IF('AOP Critical'!Q28="","",'AOP Critical'!Q28)</f>
         <v>0.29754592225545773</v>
       </c>
-      <c r="Q45" s="71" vm="18">
+      <c r="Q45" s="70" vm="18">
         <f>IF('AOP Critical'!R28="","",'AOP Critical'!R28)</f>
         <v>0.26300517799117751</v>
       </c>
-      <c r="R45" s="71" vm="22">
+      <c r="R45" s="70" vm="22">
         <f>IF('AOP Critical'!S28="","",'AOP Critical'!S28)</f>
         <v>0.30756202137510114</v>
       </c>
-      <c r="S45" s="71">
+      <c r="S45" s="70">
         <f>IF('AOP Critical'!T28="","",'AOP Critical'!T28)</f>
         <v>0.38100000000000001</v>
       </c>
-      <c r="T45" s="71" t="str">
+      <c r="T45" s="70" t="str">
         <f>IF('AOP Critical'!U28="","",'AOP Critical'!U28)</f>
         <v/>
       </c>
-      <c r="U45" s="71" t="str">
+      <c r="U45" s="70" t="str">
         <f>IF('AOP Critical'!V28="","",'AOP Critical'!V28)</f>
         <v/>
       </c>
-      <c r="V45" s="71" t="str">
+      <c r="V45" s="70" t="str">
         <f>IF('AOP Critical'!W28="","",'AOP Critical'!W28)</f>
         <v/>
       </c>
@@ -8551,51 +8551,51 @@
         <f>IF('AOP Critical'!K29="","",'AOP Critical'!K29)</f>
         <v>A</v>
       </c>
-      <c r="K46" s="71" vm="2">
+      <c r="K46" s="70" vm="2">
         <f>IF('AOP Critical'!L29="","",'AOP Critical'!L29)</f>
         <v>-0.21537837470975407</v>
       </c>
-      <c r="L46" s="71">
+      <c r="L46" s="70">
         <f>IF('AOP Critical'!M29="","",'AOP Critical'!M29)</f>
         <v>0.27400000000000002</v>
       </c>
-      <c r="M46" s="71" vm="7">
+      <c r="M46" s="70" vm="7">
         <f>IF('AOP Critical'!N29="","",'AOP Critical'!N29)</f>
         <v>0.17956999989031885</v>
       </c>
-      <c r="N46" s="71" vm="11">
+      <c r="N46" s="70" vm="11">
         <f>IF('AOP Critical'!O29="","",'AOP Critical'!O29)</f>
         <v>0.24020098639758425</v>
       </c>
-      <c r="O46" s="71" vm="13">
+      <c r="O46" s="70" vm="13">
         <f>IF('AOP Critical'!P29="","",'AOP Critical'!P29)</f>
         <v>0.12891206138967748</v>
       </c>
-      <c r="P46" s="71" vm="15">
+      <c r="P46" s="70" vm="15">
         <f>IF('AOP Critical'!Q29="","",'AOP Critical'!Q29)</f>
         <v>0.37665227402645685</v>
       </c>
-      <c r="Q46" s="71" vm="19">
+      <c r="Q46" s="70" vm="19">
         <f>IF('AOP Critical'!R29="","",'AOP Critical'!R29)</f>
         <v>0.26390638821134749</v>
       </c>
-      <c r="R46" s="71" vm="23">
+      <c r="R46" s="70" vm="23">
         <f>IF('AOP Critical'!S29="","",'AOP Critical'!S29)</f>
         <v>0.28426058124592513</v>
       </c>
-      <c r="S46" s="71">
+      <c r="S46" s="70">
         <f>IF('AOP Critical'!T29="","",'AOP Critical'!T29)</f>
         <v>0.378</v>
       </c>
-      <c r="T46" s="71" t="str">
+      <c r="T46" s="70" t="str">
         <f>IF('AOP Critical'!U29="","",'AOP Critical'!U29)</f>
         <v/>
       </c>
-      <c r="U46" s="71" t="str">
+      <c r="U46" s="70" t="str">
         <f>IF('AOP Critical'!V29="","",'AOP Critical'!V29)</f>
         <v/>
       </c>
-      <c r="V46" s="71" t="str">
+      <c r="V46" s="70" t="str">
         <f>IF('AOP Critical'!W29="","",'AOP Critical'!W29)</f>
         <v/>
       </c>
@@ -8641,48 +8641,48 @@
         <f>IF('AOP Critical'!K30="","",'AOP Critical'!K30)</f>
         <v>T</v>
       </c>
-      <c r="K47" s="71"/>
-      <c r="L47" s="71" vm="4">
+      <c r="K47" s="70"/>
+      <c r="L47" s="70" vm="4">
         <f>IF('AOP Critical'!M30="","",'AOP Critical'!M30)</f>
         <v>9.8925321866648819E-2</v>
       </c>
-      <c r="M47" s="71" vm="8">
+      <c r="M47" s="70" vm="8">
         <f>IF('AOP Critical'!N30="","",'AOP Critical'!N30)</f>
         <v>0.11712228373869382</v>
       </c>
-      <c r="N47" s="71">
+      <c r="N47" s="70">
         <f>IF('AOP Critical'!O30="","",'AOP Critical'!O30)</f>
         <v>0.15809999999999999</v>
       </c>
-      <c r="O47" s="71">
+      <c r="O47" s="70">
         <f>IF('AOP Critical'!P30="","",'AOP Critical'!P30)</f>
         <v>0.151</v>
       </c>
-      <c r="P47" s="71" vm="16">
+      <c r="P47" s="70" vm="16">
         <f>IF('AOP Critical'!Q30="","",'AOP Critical'!Q30)</f>
         <v>0.12551463489599346</v>
       </c>
-      <c r="Q47" s="71" vm="20">
+      <c r="Q47" s="70" vm="20">
         <f>IF('AOP Critical'!R30="","",'AOP Critical'!R30)</f>
         <v>0.10280225768958351</v>
       </c>
-      <c r="R47" s="71">
+      <c r="R47" s="70">
         <f>IF('AOP Critical'!S30="","",'AOP Critical'!S30)</f>
         <v>0.13500000000000001</v>
       </c>
-      <c r="S47" s="71">
+      <c r="S47" s="70">
         <f>IF('AOP Critical'!T30="","",'AOP Critical'!T30)</f>
         <v>0.11600000000000001</v>
       </c>
-      <c r="T47" s="71" t="str">
+      <c r="T47" s="70" t="str">
         <f>IF('AOP Critical'!U30="","",'AOP Critical'!U30)</f>
         <v/>
       </c>
-      <c r="U47" s="71" t="str">
+      <c r="U47" s="70" t="str">
         <f>IF('AOP Critical'!V30="","",'AOP Critical'!V30)</f>
         <v/>
       </c>
-      <c r="V47" s="71" t="str">
+      <c r="V47" s="70" t="str">
         <f>IF('AOP Critical'!W30="","",'AOP Critical'!W30)</f>
         <v/>
       </c>
@@ -8724,51 +8724,51 @@
         <f>IF('AOP Critical'!K31="","",'AOP Critical'!K31)</f>
         <v>A</v>
       </c>
-      <c r="K48" s="71">
+      <c r="K48" s="70">
         <f>IF('AOP Critical'!L31="","",'AOP Critical'!L31)</f>
         <v>0.32500000000000001</v>
       </c>
-      <c r="L48" s="71" vm="5">
+      <c r="L48" s="70" vm="5">
         <f>IF('AOP Critical'!M31="","",'AOP Critical'!M31)</f>
         <v>0.19016698273293486</v>
       </c>
-      <c r="M48" s="71" vm="9">
+      <c r="M48" s="70" vm="9">
         <f>IF('AOP Critical'!N31="","",'AOP Critical'!N31)</f>
         <v>0.14313042982821633</v>
       </c>
-      <c r="N48" s="71">
+      <c r="N48" s="70">
         <f>IF('AOP Critical'!O31="","",'AOP Critical'!O31)</f>
         <v>0.2399</v>
       </c>
-      <c r="O48" s="71">
+      <c r="O48" s="70">
         <f>IF('AOP Critical'!P31="","",'AOP Critical'!P31)</f>
         <v>0.20599999999999999</v>
       </c>
-      <c r="P48" s="71" vm="17">
+      <c r="P48" s="70" vm="17">
         <f>IF('AOP Critical'!Q31="","",'AOP Critical'!Q31)</f>
         <v>0.15714973912715791</v>
       </c>
-      <c r="Q48" s="71" vm="21">
+      <c r="Q48" s="70" vm="21">
         <f>IF('AOP Critical'!R31="","",'AOP Critical'!R31)</f>
         <v>0.10382365349216505</v>
       </c>
-      <c r="R48" s="71">
+      <c r="R48" s="70">
         <f>IF('AOP Critical'!S31="","",'AOP Critical'!S31)</f>
         <v>0.151</v>
       </c>
-      <c r="S48" s="71">
+      <c r="S48" s="70">
         <f>IF('AOP Critical'!T31="","",'AOP Critical'!T31)</f>
         <v>0.17799999999999999</v>
       </c>
-      <c r="T48" s="71" t="str">
+      <c r="T48" s="70" t="str">
         <f>IF('AOP Critical'!U31="","",'AOP Critical'!U31)</f>
         <v/>
       </c>
-      <c r="U48" s="71" t="str">
+      <c r="U48" s="70" t="str">
         <f>IF('AOP Critical'!V31="","",'AOP Critical'!V31)</f>
         <v/>
       </c>
-      <c r="V48" s="71" t="str">
+      <c r="V48" s="70" t="str">
         <f>IF('AOP Critical'!W31="","",'AOP Critical'!W31)</f>
         <v/>
       </c>
@@ -8814,51 +8814,51 @@
         <f>IF('AOP Critical'!K32="","",'AOP Critical'!K32)</f>
         <v>T</v>
       </c>
-      <c r="K49" s="73">
+      <c r="K49" s="72">
         <f>IF('AOP Critical'!L32="","",'AOP Critical'!L32)</f>
         <v>8.6903037999999988</v>
       </c>
-      <c r="L49" s="73">
+      <c r="L49" s="72">
         <f>IF('AOP Critical'!M32="","",'AOP Critical'!M32)</f>
         <v>14.05</v>
       </c>
-      <c r="M49" s="73">
+      <c r="M49" s="72">
         <f>IF('AOP Critical'!N32="","",'AOP Critical'!N32)</f>
         <v>24.179069699999999</v>
       </c>
-      <c r="N49" s="73">
+      <c r="N49" s="72">
         <f>IF('AOP Critical'!O32="","",'AOP Critical'!O32)</f>
         <v>33.551317699999998</v>
       </c>
-      <c r="O49" s="73">
+      <c r="O49" s="72">
         <f>IF('AOP Critical'!P32="","",'AOP Critical'!P32)</f>
         <v>41.442849800000005</v>
       </c>
-      <c r="P49" s="73">
+      <c r="P49" s="72">
         <f>IF('AOP Critical'!Q32="","",'AOP Critical'!Q32)</f>
         <v>60.823965100000009</v>
       </c>
-      <c r="Q49" s="73">
+      <c r="Q49" s="72">
         <f>IF('AOP Critical'!R32="","",'AOP Critical'!R32)</f>
         <v>72.599999999999994</v>
       </c>
-      <c r="R49" s="73">
+      <c r="R49" s="72">
         <f>IF('AOP Critical'!S32="","",'AOP Critical'!S32)</f>
         <v>82.449704499999996</v>
       </c>
-      <c r="S49" s="73">
+      <c r="S49" s="72">
         <f>IF('AOP Critical'!T32="","",'AOP Critical'!T32)</f>
         <v>97.4</v>
       </c>
-      <c r="T49" s="73" t="str">
+      <c r="T49" s="72" t="str">
         <f>IF('AOP Critical'!U32="","",'AOP Critical'!U32)</f>
         <v/>
       </c>
-      <c r="U49" s="73" t="str">
+      <c r="U49" s="72" t="str">
         <f>IF('AOP Critical'!V32="","",'AOP Critical'!V32)</f>
         <v/>
       </c>
-      <c r="V49" s="73" t="str">
+      <c r="V49" s="72" t="str">
         <f>IF('AOP Critical'!W32="","",'AOP Critical'!W32)</f>
         <v/>
       </c>
@@ -8904,51 +8904,51 @@
         <f>IF('AOP Critical'!K33="","",'AOP Critical'!K33)</f>
         <v>A</v>
       </c>
-      <c r="K50" s="73">
+      <c r="K50" s="72">
         <f>IF('AOP Critical'!L33="","",'AOP Critical'!L33)</f>
         <v>4.05</v>
       </c>
-      <c r="L50" s="73">
+      <c r="L50" s="72">
         <f>IF('AOP Critical'!M33="","",'AOP Critical'!M33)</f>
         <v>9.7989724000000002</v>
       </c>
-      <c r="M50" s="73">
+      <c r="M50" s="72">
         <f>IF('AOP Critical'!N33="","",'AOP Critical'!N33)</f>
         <v>25.313448100000002</v>
       </c>
-      <c r="N50" s="73">
+      <c r="N50" s="72">
         <f>IF('AOP Critical'!O33="","",'AOP Critical'!O33)</f>
         <v>31.452557499999998</v>
       </c>
-      <c r="O50" s="73">
+      <c r="O50" s="72">
         <f>IF('AOP Critical'!P33="","",'AOP Critical'!P33)</f>
         <v>41.128122899999994</v>
       </c>
-      <c r="P50" s="73">
+      <c r="P50" s="72">
         <f>IF('AOP Critical'!Q33="","",'AOP Critical'!Q33)</f>
         <v>55.164574999999999</v>
       </c>
-      <c r="Q50" s="73">
+      <c r="Q50" s="72">
         <f>IF('AOP Critical'!R33="","",'AOP Critical'!R33)</f>
         <v>61.940289700000001</v>
       </c>
-      <c r="R50" s="73">
+      <c r="R50" s="72">
         <f>IF('AOP Critical'!S33="","",'AOP Critical'!S33)</f>
         <v>72.779408199999978</v>
       </c>
-      <c r="S50" s="73">
+      <c r="S50" s="72">
         <f>IF('AOP Critical'!T33="","",'AOP Critical'!T33)</f>
         <v>91.2</v>
       </c>
-      <c r="T50" s="73" t="str">
+      <c r="T50" s="72" t="str">
         <f>IF('AOP Critical'!U33="","",'AOP Critical'!U33)</f>
         <v/>
       </c>
-      <c r="U50" s="73" t="str">
+      <c r="U50" s="72" t="str">
         <f>IF('AOP Critical'!V33="","",'AOP Critical'!V33)</f>
         <v/>
       </c>
-      <c r="V50" s="73" t="str">
+      <c r="V50" s="72" t="str">
         <f>IF('AOP Critical'!W33="","",'AOP Critical'!W33)</f>
         <v/>
       </c>
@@ -8994,51 +8994,51 @@
         <f>IF('AOP Critical'!K24="","",'AOP Critical'!K24)</f>
         <v>T</v>
       </c>
-      <c r="K51" s="71" t="str">
+      <c r="K51" s="70" t="str">
         <f>IF('AOP Critical'!L24="","",'AOP Critical'!L24)</f>
         <v/>
       </c>
-      <c r="L51" s="71" t="str">
+      <c r="L51" s="70" t="str">
         <f>IF('AOP Critical'!M24="","",'AOP Critical'!M24)</f>
         <v/>
       </c>
-      <c r="M51" s="71">
+      <c r="M51" s="70">
         <f>IF('AOP Critical'!N24="","",'AOP Critical'!N24)</f>
         <v>0.104</v>
       </c>
-      <c r="N51" s="71" t="str">
+      <c r="N51" s="70" t="str">
         <f>IF('AOP Critical'!O24="","",'AOP Critical'!O24)</f>
         <v>QTR</v>
       </c>
-      <c r="O51" s="71" t="str">
+      <c r="O51" s="70" t="str">
         <f>IF('AOP Critical'!P24="","",'AOP Critical'!P24)</f>
         <v>QTR</v>
       </c>
-      <c r="P51" s="71">
+      <c r="P51" s="70">
         <f>IF('AOP Critical'!Q24="","",'AOP Critical'!Q24)</f>
         <v>0.11799999999999999</v>
       </c>
-      <c r="Q51" s="71" t="str">
+      <c r="Q51" s="70" t="str">
         <f>IF('AOP Critical'!R24="","",'AOP Critical'!R24)</f>
         <v>QTR</v>
       </c>
-      <c r="R51" s="71" t="str">
+      <c r="R51" s="70" t="str">
         <f>IF('AOP Critical'!S24="","",'AOP Critical'!S24)</f>
         <v>QTR</v>
       </c>
-      <c r="S51" s="71" t="str">
+      <c r="S51" s="70" t="str">
         <f>IF('AOP Critical'!T24="","",'AOP Critical'!T24)</f>
         <v/>
       </c>
-      <c r="T51" s="71" t="str">
+      <c r="T51" s="70" t="str">
         <f>IF('AOP Critical'!U24="","",'AOP Critical'!U24)</f>
         <v>QTR</v>
       </c>
-      <c r="U51" s="71" t="str">
+      <c r="U51" s="70" t="str">
         <f>IF('AOP Critical'!V24="","",'AOP Critical'!V24)</f>
         <v>QTR</v>
       </c>
-      <c r="V51" s="71" t="str">
+      <c r="V51" s="70" t="str">
         <f>IF('AOP Critical'!W24="","",'AOP Critical'!W24)</f>
         <v/>
       </c>
@@ -9232,51 +9232,51 @@
         <f>IF('AOP Critical'!K34="","",'AOP Critical'!K34)</f>
         <v>T</v>
       </c>
-      <c r="K56" s="70" t="str">
+      <c r="K56" s="69" t="str">
         <f>IF('AOP Critical'!L34="","",'AOP Critical'!L34)</f>
         <v/>
       </c>
-      <c r="L56" s="70" t="str">
+      <c r="L56" s="69" t="str">
         <f>IF('AOP Critical'!M34="","",'AOP Critical'!M34)</f>
         <v/>
       </c>
-      <c r="M56" s="70">
+      <c r="M56" s="69">
         <f>IF('AOP Critical'!N34="","",'AOP Critical'!N34)</f>
         <v>0.9</v>
       </c>
-      <c r="N56" s="70" t="str">
+      <c r="N56" s="69" t="str">
         <f>IF('AOP Critical'!O34="","",'AOP Critical'!O34)</f>
         <v/>
       </c>
-      <c r="O56" s="70" t="str">
+      <c r="O56" s="69" t="str">
         <f>IF('AOP Critical'!P34="","",'AOP Critical'!P34)</f>
         <v/>
       </c>
-      <c r="P56" s="70">
+      <c r="P56" s="69">
         <f>IF('AOP Critical'!Q34="","",'AOP Critical'!Q34)</f>
         <v>0.9</v>
       </c>
-      <c r="Q56" s="70" t="str">
+      <c r="Q56" s="69" t="str">
         <f>IF('AOP Critical'!R34="","",'AOP Critical'!R34)</f>
         <v/>
       </c>
-      <c r="R56" s="70" t="str">
+      <c r="R56" s="69" t="str">
         <f>IF('AOP Critical'!S34="","",'AOP Critical'!S34)</f>
         <v/>
       </c>
-      <c r="S56" s="70">
+      <c r="S56" s="69">
         <f>IF('AOP Critical'!T34="","",'AOP Critical'!T34)</f>
         <v>0.9</v>
       </c>
-      <c r="T56" s="70" t="str">
+      <c r="T56" s="69" t="str">
         <f>IF('AOP Critical'!U34="","",'AOP Critical'!U34)</f>
         <v/>
       </c>
-      <c r="U56" s="70" t="str">
+      <c r="U56" s="69" t="str">
         <f>IF('AOP Critical'!V34="","",'AOP Critical'!V34)</f>
         <v/>
       </c>
-      <c r="V56" s="70">
+      <c r="V56" s="69">
         <f>IF('AOP Critical'!W34="","",'AOP Critical'!W34)</f>
         <v>0.9</v>
       </c>
@@ -9307,51 +9307,51 @@
         <f>IF('AOP Critical'!K35="","",'AOP Critical'!K35)</f>
         <v>A</v>
       </c>
-      <c r="K57" s="70" t="str">
+      <c r="K57" s="69" t="str">
         <f>IF('AOP Critical'!L35="","",'AOP Critical'!L35)</f>
         <v>QTR</v>
       </c>
-      <c r="L57" s="70" t="str">
+      <c r="L57" s="69" t="str">
         <f>IF('AOP Critical'!M35="","",'AOP Critical'!M35)</f>
         <v>QTR</v>
       </c>
-      <c r="M57" s="70">
+      <c r="M57" s="69">
         <f>IF('AOP Critical'!N35="","",'AOP Critical'!N35)</f>
         <v>1</v>
       </c>
-      <c r="N57" s="70" t="str">
+      <c r="N57" s="69" t="str">
         <f>IF('AOP Critical'!O35="","",'AOP Critical'!O35)</f>
         <v>QTR</v>
       </c>
-      <c r="O57" s="70" t="str">
+      <c r="O57" s="69" t="str">
         <f>IF('AOP Critical'!P35="","",'AOP Critical'!P35)</f>
         <v>QTR</v>
       </c>
-      <c r="P57" s="70">
+      <c r="P57" s="69">
         <f>IF('AOP Critical'!Q35="","",'AOP Critical'!Q35)</f>
         <v>0.96199999999999997</v>
       </c>
-      <c r="Q57" s="70" t="str">
+      <c r="Q57" s="69" t="str">
         <f>IF('AOP Critical'!R35="","",'AOP Critical'!R35)</f>
         <v>QTR</v>
       </c>
-      <c r="R57" s="70" t="str">
+      <c r="R57" s="69" t="str">
         <f>IF('AOP Critical'!S35="","",'AOP Critical'!S35)</f>
         <v>QTR</v>
       </c>
-      <c r="S57" s="70">
+      <c r="S57" s="69">
         <f>IF('AOP Critical'!T35="","",'AOP Critical'!T35)</f>
         <v>0.91300000000000003</v>
       </c>
-      <c r="T57" s="70" t="str">
+      <c r="T57" s="69" t="str">
         <f>IF('AOP Critical'!U35="","",'AOP Critical'!U35)</f>
         <v/>
       </c>
-      <c r="U57" s="70" t="str">
+      <c r="U57" s="69" t="str">
         <f>IF('AOP Critical'!V35="","",'AOP Critical'!V35)</f>
         <v/>
       </c>
-      <c r="V57" s="70" t="str">
+      <c r="V57" s="69" t="str">
         <f>IF('AOP Critical'!W35="","",'AOP Critical'!W35)</f>
         <v/>
       </c>
@@ -9382,51 +9382,51 @@
         <f>IF('AOP Critical'!K36="","",'AOP Critical'!K36)</f>
         <v>T</v>
       </c>
-      <c r="K58" s="70" t="str">
+      <c r="K58" s="69" t="str">
         <f>IF('AOP Critical'!L36="","",'AOP Critical'!L36)</f>
         <v/>
       </c>
-      <c r="L58" s="70" t="str">
+      <c r="L58" s="69" t="str">
         <f>IF('AOP Critical'!M36="","",'AOP Critical'!M36)</f>
         <v/>
       </c>
-      <c r="M58" s="70" t="str">
+      <c r="M58" s="69" t="str">
         <f>IF('AOP Critical'!N36="","",'AOP Critical'!N36)</f>
         <v/>
       </c>
-      <c r="N58" s="70">
+      <c r="N58" s="69">
         <f>IF('AOP Critical'!O36="","",'AOP Critical'!O36)</f>
         <v>0.83</v>
       </c>
-      <c r="O58" s="70" t="str">
+      <c r="O58" s="69" t="str">
         <f>IF('AOP Critical'!P36="","",'AOP Critical'!P36)</f>
         <v/>
       </c>
-      <c r="P58" s="70">
+      <c r="P58" s="69">
         <f>IF('AOP Critical'!Q36="","",'AOP Critical'!Q36)</f>
         <v>0.83</v>
       </c>
-      <c r="Q58" s="70" t="str">
+      <c r="Q58" s="69" t="str">
         <f>IF('AOP Critical'!R36="","",'AOP Critical'!R36)</f>
         <v/>
       </c>
-      <c r="R58" s="70" t="str">
+      <c r="R58" s="69" t="str">
         <f>IF('AOP Critical'!S36="","",'AOP Critical'!S36)</f>
         <v/>
       </c>
-      <c r="S58" s="70" t="str">
+      <c r="S58" s="69" t="str">
         <f>IF('AOP Critical'!T36="","",'AOP Critical'!T36)</f>
         <v/>
       </c>
-      <c r="T58" s="70" t="str">
+      <c r="T58" s="69" t="str">
         <f>IF('AOP Critical'!U36="","",'AOP Critical'!U36)</f>
         <v/>
       </c>
-      <c r="U58" s="70" t="str">
+      <c r="U58" s="69" t="str">
         <f>IF('AOP Critical'!V36="","",'AOP Critical'!V36)</f>
         <v/>
       </c>
-      <c r="V58" s="70" t="str">
+      <c r="V58" s="69" t="str">
         <f>IF('AOP Critical'!W36="","",'AOP Critical'!W36)</f>
         <v/>
       </c>
@@ -9457,51 +9457,51 @@
         <f>IF('AOP Critical'!K37="","",'AOP Critical'!K37)</f>
         <v>A</v>
       </c>
-      <c r="K59" s="70" t="str">
+      <c r="K59" s="69" t="str">
         <f>IF('AOP Critical'!L37="","",'AOP Critical'!L37)</f>
         <v>HY</v>
       </c>
-      <c r="L59" s="70" t="str">
+      <c r="L59" s="69" t="str">
         <f>IF('AOP Critical'!M37="","",'AOP Critical'!M37)</f>
         <v>HY</v>
       </c>
-      <c r="M59" s="70" t="str">
+      <c r="M59" s="69" t="str">
         <f>IF('AOP Critical'!N37="","",'AOP Critical'!N37)</f>
         <v>HY</v>
       </c>
-      <c r="N59" s="70">
+      <c r="N59" s="69">
         <f>IF('AOP Critical'!O37="","",'AOP Critical'!O37)</f>
         <v>0.79</v>
       </c>
-      <c r="O59" s="70" t="str">
+      <c r="O59" s="69" t="str">
         <f>IF('AOP Critical'!P37="","",'AOP Critical'!P37)</f>
         <v>HY</v>
       </c>
-      <c r="P59" s="70">
+      <c r="P59" s="69">
         <f>IF('AOP Critical'!Q37="","",'AOP Critical'!Q37)</f>
         <v>0.79</v>
       </c>
-      <c r="Q59" s="70" t="str">
+      <c r="Q59" s="69" t="str">
         <f>IF('AOP Critical'!R37="","",'AOP Critical'!R37)</f>
         <v>HY</v>
       </c>
-      <c r="R59" s="70" t="str">
+      <c r="R59" s="69" t="str">
         <f>IF('AOP Critical'!S37="","",'AOP Critical'!S37)</f>
         <v/>
       </c>
-      <c r="S59" s="70" t="str">
+      <c r="S59" s="69" t="str">
         <f>IF('AOP Critical'!T37="","",'AOP Critical'!T37)</f>
         <v/>
       </c>
-      <c r="T59" s="70" t="str">
+      <c r="T59" s="69" t="str">
         <f>IF('AOP Critical'!U37="","",'AOP Critical'!U37)</f>
         <v/>
       </c>
-      <c r="U59" s="70" t="str">
+      <c r="U59" s="69" t="str">
         <f>IF('AOP Critical'!V37="","",'AOP Critical'!V37)</f>
         <v/>
       </c>
-      <c r="V59" s="70" t="str">
+      <c r="V59" s="69" t="str">
         <f>IF('AOP Critical'!W37="","",'AOP Critical'!W37)</f>
         <v/>
       </c>
@@ -9574,10 +9574,10 @@
       <c r="I2" s="6"/>
     </row>
     <row r="3" spans="1:27" s="5" customFormat="1" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="108" t="s">
+      <c r="A3" s="107" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="108"/>
+      <c r="B3" s="107"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -9594,108 +9594,108 @@
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
       <c r="V3" s="2"/>
-      <c r="X3" s="21"/>
+      <c r="X3" s="171"/>
       <c r="AA3" s="14"/>
     </row>
     <row r="4" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="110" t="str">
+      <c r="A4" s="109" t="str">
         <f ca="1">"Current Month-Year " &amp; ":" &amp; TEXT(TODAY(),"YYYY-MM")</f>
         <v>Current Month-Year :2026-10</v>
       </c>
-      <c r="B4" s="110"/>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="110"/>
-      <c r="M4" s="110"/>
-      <c r="N4" s="110"/>
-      <c r="O4" s="110"/>
-      <c r="P4" s="110"/>
-      <c r="Q4" s="110"/>
-      <c r="R4" s="110"/>
-      <c r="S4" s="110"/>
-      <c r="T4" s="110"/>
-      <c r="U4" s="110"/>
-      <c r="V4" s="110"/>
-      <c r="W4" s="110"/>
-      <c r="X4" s="110"/>
-      <c r="Y4" s="110"/>
-      <c r="Z4" s="110"/>
-      <c r="AA4" s="110"/>
+      <c r="B4" s="109"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="109"/>
+      <c r="K4" s="109"/>
+      <c r="L4" s="109"/>
+      <c r="M4" s="109"/>
+      <c r="N4" s="109"/>
+      <c r="O4" s="109"/>
+      <c r="P4" s="109"/>
+      <c r="Q4" s="109"/>
+      <c r="R4" s="109"/>
+      <c r="S4" s="109"/>
+      <c r="T4" s="109"/>
+      <c r="U4" s="109"/>
+      <c r="V4" s="109"/>
+      <c r="W4" s="109"/>
+      <c r="X4" s="109"/>
+      <c r="Y4" s="109"/>
+      <c r="Z4" s="109"/>
+      <c r="AA4" s="109"/>
     </row>
     <row r="5" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="86" t="s">
+      <c r="A5" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="114" t="s">
+      <c r="E5" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="114"/>
-      <c r="G5" s="114"/>
-      <c r="H5" s="87" t="s">
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="35" t="s">
+      <c r="I5" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="35" t="s">
+      <c r="J5" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="35" t="s">
+      <c r="K5" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="L5" s="35" t="s">
+      <c r="L5" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="M5" s="35" t="s">
+      <c r="M5" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="N5" s="35" t="s">
+      <c r="N5" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="O5" s="35" t="s">
+      <c r="O5" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="P5" s="35" t="s">
+      <c r="P5" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="Q5" s="35" t="s">
+      <c r="Q5" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="R5" s="35" t="s">
+      <c r="R5" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="S5" s="35" t="s">
+      <c r="S5" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="T5" s="35" t="s">
+      <c r="T5" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="U5" s="35" t="s">
+      <c r="U5" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="V5" s="35" t="s">
+      <c r="V5" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="W5" s="35" t="s">
+      <c r="W5" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="X5" s="24" t="s">
+      <c r="X5" s="23" t="s">
         <v>43</v>
       </c>
       <c r="Y5" s="11" t="s">
@@ -9709,51 +9709,51 @@
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A6" s="107" t="s">
+      <c r="A6" s="106" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="89" t="s">
+      <c r="B6" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="90" t="s">
+      <c r="C6" s="89" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="88" t="s">
+      <c r="D6" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="106">
+      <c r="E6" s="105">
         <v>10</v>
       </c>
-      <c r="F6" s="106"/>
-      <c r="G6" s="106"/>
-      <c r="H6" s="109" t="s">
+      <c r="F6" s="105"/>
+      <c r="G6" s="105"/>
+      <c r="H6" s="108" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="106" t="s">
+      <c r="I6" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="105" t="s">
+      <c r="J6" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="K6" s="23" t="s">
+      <c r="K6" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L6" s="36">
+      <c r="L6" s="35">
         <v>0.08</v>
       </c>
-      <c r="M6" s="36">
+      <c r="M6" s="35">
         <v>0.08</v>
       </c>
-      <c r="N6" s="36">
+      <c r="N6" s="35">
         <v>0.08</v>
       </c>
-      <c r="O6" s="36">
+      <c r="O6" s="35">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="P6" s="36">
+      <c r="P6" s="35">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="Q6" s="36">
+      <c r="Q6" s="35">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="R6" s="18">
@@ -9771,223 +9771,223 @@
       <c r="V6" s="18">
         <v>0.05</v>
       </c>
-      <c r="W6" s="28">
+      <c r="W6" s="27">
         <v>0.05</v>
       </c>
-      <c r="X6" s="104"/>
-      <c r="Y6" s="111"/>
-      <c r="Z6" s="111"/>
-      <c r="AA6" s="121" t="s">
+      <c r="X6" s="103"/>
+      <c r="Y6" s="110"/>
+      <c r="Z6" s="110"/>
+      <c r="AA6" s="120" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A7" s="107"/>
-      <c r="B7" s="89"/>
-      <c r="C7" s="90"/>
-      <c r="D7" s="88"/>
-      <c r="E7" s="106"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="109"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="105"/>
-      <c r="K7" s="23" t="s">
+      <c r="A7" s="106"/>
+      <c r="B7" s="88"/>
+      <c r="C7" s="89"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="108"/>
+      <c r="I7" s="105"/>
+      <c r="J7" s="104"/>
+      <c r="K7" s="22" t="s">
         <v>55</v>
       </c>
       <c r="L7" s="17">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="M7" s="51">
+      <c r="M7" s="50">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="N7" s="51">
+      <c r="N7" s="50">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="O7" s="51">
+      <c r="O7" s="50">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="P7" s="51">
+      <c r="P7" s="50">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="Q7" s="51">
+      <c r="Q7" s="50">
         <v>0.03</v>
       </c>
-      <c r="R7" s="51">
+      <c r="R7" s="50">
         <v>3.1E-2</v>
       </c>
-      <c r="S7" s="51">
+      <c r="S7" s="50">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="T7" s="51">
+      <c r="T7" s="50">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="U7" s="51"/>
-      <c r="V7" s="51"/>
-      <c r="W7" s="51"/>
-      <c r="X7" s="92"/>
-      <c r="Y7" s="94"/>
-      <c r="Z7" s="94"/>
-      <c r="AA7" s="122"/>
+      <c r="U7" s="50"/>
+      <c r="V7" s="50"/>
+      <c r="W7" s="50"/>
+      <c r="X7" s="91"/>
+      <c r="Y7" s="93"/>
+      <c r="Z7" s="93"/>
+      <c r="AA7" s="121"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A8" s="107"/>
-      <c r="B8" s="89" t="s">
+      <c r="A8" s="106"/>
+      <c r="B8" s="88" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="90" t="s">
+      <c r="C8" s="89" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="88" t="s">
+      <c r="D8" s="87" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="106">
+      <c r="E8" s="105">
         <v>90</v>
       </c>
-      <c r="F8" s="106"/>
-      <c r="G8" s="106"/>
-      <c r="H8" s="109" t="s">
+      <c r="F8" s="105"/>
+      <c r="G8" s="105"/>
+      <c r="H8" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="106" t="s">
+      <c r="I8" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="105" t="s">
+      <c r="J8" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="K8" s="23" t="s">
+      <c r="K8" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L8" s="36">
+      <c r="L8" s="35">
         <v>0.9</v>
       </c>
-      <c r="M8" s="36">
+      <c r="M8" s="35">
         <v>0.9</v>
       </c>
-      <c r="N8" s="36">
+      <c r="N8" s="35">
         <v>0.9</v>
       </c>
-      <c r="O8" s="36">
+      <c r="O8" s="35">
         <v>0.9</v>
       </c>
-      <c r="P8" s="36">
+      <c r="P8" s="35">
         <v>0.9</v>
       </c>
-      <c r="Q8" s="36">
+      <c r="Q8" s="35">
         <v>0.9</v>
       </c>
-      <c r="R8" s="36">
+      <c r="R8" s="35">
         <v>0.9</v>
       </c>
       <c r="S8" s="18"/>
       <c r="T8" s="18"/>
       <c r="U8" s="18"/>
       <c r="V8" s="18"/>
-      <c r="W8" s="28"/>
-      <c r="X8" s="92"/>
-      <c r="Y8" s="93" t="s">
+      <c r="W8" s="27"/>
+      <c r="X8" s="91"/>
+      <c r="Y8" s="92" t="s">
         <v>58</v>
       </c>
-      <c r="Z8" s="112">
+      <c r="Z8" s="111">
         <v>46231</v>
       </c>
-      <c r="AA8" s="121" t="s">
+      <c r="AA8" s="120" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A9" s="107"/>
-      <c r="B9" s="89"/>
-      <c r="C9" s="90"/>
-      <c r="D9" s="88"/>
-      <c r="E9" s="106"/>
-      <c r="F9" s="106"/>
-      <c r="G9" s="106"/>
-      <c r="H9" s="109"/>
-      <c r="I9" s="106"/>
-      <c r="J9" s="105"/>
-      <c r="K9" s="23" t="s">
+      <c r="A9" s="106"/>
+      <c r="B9" s="88"/>
+      <c r="C9" s="89"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="108"/>
+      <c r="I9" s="105"/>
+      <c r="J9" s="104"/>
+      <c r="K9" s="22" t="s">
         <v>55</v>
       </c>
       <c r="L9" s="19">
         <v>1</v>
       </c>
-      <c r="M9" s="53">
+      <c r="M9" s="52">
         <v>0.75</v>
       </c>
-      <c r="N9" s="53">
+      <c r="N9" s="52">
         <v>0.4</v>
       </c>
-      <c r="O9" s="76">
+      <c r="O9" s="75">
         <v>0</v>
       </c>
-      <c r="P9" s="53">
+      <c r="P9" s="52">
         <v>0</v>
       </c>
-      <c r="Q9" s="53">
+      <c r="Q9" s="52">
         <v>0</v>
       </c>
-      <c r="R9" s="53">
+      <c r="R9" s="52">
         <v>1</v>
       </c>
-      <c r="S9" s="53">
+      <c r="S9" s="52">
         <v>1</v>
       </c>
-      <c r="T9" s="53">
+      <c r="T9" s="52">
         <v>1</v>
       </c>
-      <c r="U9" s="53"/>
-      <c r="V9" s="53"/>
-      <c r="W9" s="53"/>
-      <c r="X9" s="92"/>
-      <c r="Y9" s="94"/>
-      <c r="Z9" s="113"/>
-      <c r="AA9" s="122"/>
+      <c r="U9" s="52"/>
+      <c r="V9" s="52"/>
+      <c r="W9" s="52"/>
+      <c r="X9" s="91"/>
+      <c r="Y9" s="93"/>
+      <c r="Z9" s="112"/>
+      <c r="AA9" s="121"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A10" s="107"/>
-      <c r="B10" s="89" t="s">
+      <c r="A10" s="106"/>
+      <c r="B10" s="88" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="90" t="s">
+      <c r="C10" s="89" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="88" t="s">
+      <c r="D10" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="E10" s="106">
+      <c r="E10" s="105">
         <v>1</v>
       </c>
-      <c r="F10" s="106"/>
-      <c r="G10" s="106"/>
-      <c r="H10" s="109" t="s">
+      <c r="F10" s="105"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="108" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="106" t="s">
+      <c r="I10" s="105" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="105" t="s">
+      <c r="J10" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="K10" s="23" t="s">
+      <c r="K10" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L10" s="37">
+      <c r="L10" s="36">
         <v>1</v>
       </c>
-      <c r="M10" s="37">
+      <c r="M10" s="36">
         <v>1</v>
       </c>
-      <c r="N10" s="37">
+      <c r="N10" s="36">
         <v>1</v>
       </c>
-      <c r="O10" s="37">
+      <c r="O10" s="36">
         <v>1</v>
       </c>
-      <c r="P10" s="37">
+      <c r="P10" s="36">
         <v>1</v>
       </c>
-      <c r="Q10" s="37">
+      <c r="Q10" s="36">
         <v>1</v>
       </c>
       <c r="R10" s="8">
@@ -9999,32 +9999,32 @@
       <c r="T10" s="8"/>
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
-      <c r="W10" s="34"/>
-      <c r="X10" s="92"/>
-      <c r="Y10" s="161"/>
-      <c r="Z10" s="115"/>
-      <c r="AA10" s="121" t="s">
+      <c r="W10" s="33"/>
+      <c r="X10" s="91"/>
+      <c r="Y10" s="160"/>
+      <c r="Z10" s="114"/>
+      <c r="AA10" s="120" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="107"/>
-      <c r="B11" s="89"/>
-      <c r="C11" s="90"/>
-      <c r="D11" s="88"/>
-      <c r="E11" s="106"/>
-      <c r="F11" s="106"/>
-      <c r="G11" s="106"/>
-      <c r="H11" s="109"/>
-      <c r="I11" s="106"/>
-      <c r="J11" s="105"/>
-      <c r="K11" s="23" t="s">
+      <c r="A11" s="106"/>
+      <c r="B11" s="88"/>
+      <c r="C11" s="89"/>
+      <c r="D11" s="87"/>
+      <c r="E11" s="105"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="105"/>
+      <c r="H11" s="108"/>
+      <c r="I11" s="105"/>
+      <c r="J11" s="104"/>
+      <c r="K11" s="22" t="s">
         <v>55</v>
       </c>
       <c r="L11" s="9">
         <v>2</v>
       </c>
-      <c r="M11" s="54">
+      <c r="M11" s="53">
         <v>1</v>
       </c>
       <c r="N11" s="9">
@@ -10039,108 +10039,108 @@
       <c r="Q11" s="9">
         <v>0</v>
       </c>
-      <c r="R11" s="32">
+      <c r="R11" s="31">
         <v>0</v>
       </c>
-      <c r="S11" s="32">
+      <c r="S11" s="31">
         <v>0</v>
       </c>
-      <c r="T11" s="32">
+      <c r="T11" s="31">
         <v>0</v>
       </c>
-      <c r="U11" s="32"/>
-      <c r="V11" s="32"/>
-      <c r="W11" s="33"/>
-      <c r="X11" s="92"/>
-      <c r="Y11" s="162"/>
-      <c r="Z11" s="116"/>
-      <c r="AA11" s="122"/>
+      <c r="U11" s="31"/>
+      <c r="V11" s="31"/>
+      <c r="W11" s="32"/>
+      <c r="X11" s="91"/>
+      <c r="Y11" s="161"/>
+      <c r="Z11" s="115"/>
+      <c r="AA11" s="121"/>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A12" s="107" t="s">
+      <c r="A12" s="106" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="91" t="s">
+      <c r="B12" s="90" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="91" t="s">
+      <c r="C12" s="90" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="88" t="s">
+      <c r="D12" s="87" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="106">
+      <c r="E12" s="105">
         <v>84</v>
       </c>
-      <c r="F12" s="106"/>
-      <c r="G12" s="106"/>
-      <c r="H12" s="109" t="s">
+      <c r="F12" s="105"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="106" t="s">
+      <c r="I12" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="105" t="s">
+      <c r="J12" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="K12" s="23" t="s">
+      <c r="K12" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L12" s="36">
+      <c r="L12" s="35">
         <v>0.69</v>
       </c>
-      <c r="M12" s="36">
+      <c r="M12" s="35">
         <v>0.69</v>
       </c>
-      <c r="N12" s="36">
+      <c r="N12" s="35">
         <v>0.69</v>
       </c>
-      <c r="O12" s="36">
+      <c r="O12" s="35">
         <v>0.72</v>
       </c>
-      <c r="P12" s="36">
+      <c r="P12" s="35">
         <v>0.72</v>
       </c>
-      <c r="Q12" s="36">
+      <c r="Q12" s="35">
         <v>0.72</v>
       </c>
-      <c r="R12" s="25">
+      <c r="R12" s="24">
         <v>0.74</v>
       </c>
-      <c r="S12" s="25">
+      <c r="S12" s="24">
         <v>0.74</v>
       </c>
-      <c r="T12" s="25">
+      <c r="T12" s="24">
         <v>0.74</v>
       </c>
-      <c r="U12" s="25">
+      <c r="U12" s="24">
         <v>0.79</v>
       </c>
-      <c r="V12" s="25">
+      <c r="V12" s="24">
         <v>0.79</v>
       </c>
-      <c r="W12" s="26">
+      <c r="W12" s="25">
         <v>0.79</v>
       </c>
-      <c r="X12" s="92"/>
-      <c r="Y12" s="93"/>
-      <c r="Z12" s="94"/>
-      <c r="AA12" s="121" t="s">
+      <c r="X12" s="91"/>
+      <c r="Y12" s="92"/>
+      <c r="Z12" s="93"/>
+      <c r="AA12" s="120" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A13" s="107"/>
-      <c r="B13" s="91"/>
-      <c r="C13" s="91"/>
-      <c r="D13" s="88"/>
-      <c r="E13" s="106"/>
-      <c r="F13" s="106"/>
-      <c r="G13" s="106"/>
-      <c r="H13" s="109"/>
-      <c r="I13" s="106"/>
-      <c r="J13" s="105"/>
-      <c r="K13" s="23" t="s">
+      <c r="A13" s="106"/>
+      <c r="B13" s="90"/>
+      <c r="C13" s="90"/>
+      <c r="D13" s="87"/>
+      <c r="E13" s="105"/>
+      <c r="F13" s="105"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="108"/>
+      <c r="I13" s="105"/>
+      <c r="J13" s="104"/>
+      <c r="K13" s="22" t="s">
         <v>55</v>
       </c>
       <c r="L13" s="19">
@@ -10172,97 +10172,97 @@
       </c>
       <c r="U13" s="19"/>
       <c r="V13" s="19"/>
-      <c r="W13" s="29"/>
-      <c r="X13" s="92"/>
-      <c r="Y13" s="94"/>
-      <c r="Z13" s="94"/>
-      <c r="AA13" s="122"/>
+      <c r="W13" s="28"/>
+      <c r="X13" s="91"/>
+      <c r="Y13" s="93"/>
+      <c r="Z13" s="93"/>
+      <c r="AA13" s="121"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A14" s="107"/>
-      <c r="B14" s="91" t="s">
+      <c r="A14" s="106"/>
+      <c r="B14" s="90" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="120" t="s">
+      <c r="C14" s="119" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="88" t="s">
+      <c r="D14" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="106">
+      <c r="E14" s="105">
         <v>54.6</v>
       </c>
-      <c r="F14" s="106"/>
-      <c r="G14" s="106"/>
-      <c r="H14" s="109" t="s">
+      <c r="F14" s="105"/>
+      <c r="G14" s="105"/>
+      <c r="H14" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="106" t="s">
+      <c r="I14" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="J14" s="105" t="s">
+      <c r="J14" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="K14" s="23" t="s">
+      <c r="K14" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L14" s="38">
+      <c r="L14" s="37">
         <v>0.54249999999999998</v>
       </c>
-      <c r="M14" s="38">
+      <c r="M14" s="37">
         <v>0.54399999999999993</v>
       </c>
-      <c r="N14" s="38">
+      <c r="N14" s="37">
         <v>0.54549999999999987</v>
       </c>
-      <c r="O14" s="38">
+      <c r="O14" s="37">
         <v>0.54699999999999982</v>
       </c>
-      <c r="P14" s="38">
+      <c r="P14" s="37">
         <v>0.54849999999999977</v>
       </c>
-      <c r="Q14" s="38">
+      <c r="Q14" s="37">
         <v>0.54999999999999971</v>
       </c>
-      <c r="R14" s="38">
+      <c r="R14" s="37">
         <v>0.55149999999999966</v>
       </c>
-      <c r="S14" s="38">
+      <c r="S14" s="37">
         <v>0.54510000000000003</v>
       </c>
-      <c r="T14" s="38">
+      <c r="T14" s="37">
         <v>0.54610000000000003</v>
       </c>
-      <c r="U14" s="38"/>
-      <c r="V14" s="38"/>
-      <c r="W14" s="38"/>
-      <c r="X14" s="171" t="s">
+      <c r="U14" s="37"/>
+      <c r="V14" s="37"/>
+      <c r="W14" s="37"/>
+      <c r="X14" s="170" t="s">
+        <v>142</v>
+      </c>
+      <c r="Y14" s="94" t="s">
         <v>141</v>
       </c>
-      <c r="Y14" s="95" t="s">
-        <v>142</v>
-      </c>
-      <c r="Z14" s="150"/>
-      <c r="AA14" s="149"/>
+      <c r="Z14" s="149"/>
+      <c r="AA14" s="148"/>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="107"/>
-      <c r="B15" s="91"/>
-      <c r="C15" s="120"/>
-      <c r="D15" s="88"/>
-      <c r="E15" s="106"/>
-      <c r="F15" s="106"/>
-      <c r="G15" s="106"/>
-      <c r="H15" s="109"/>
-      <c r="I15" s="106"/>
-      <c r="J15" s="105"/>
-      <c r="K15" s="23" t="s">
+      <c r="A15" s="106"/>
+      <c r="B15" s="90"/>
+      <c r="C15" s="119"/>
+      <c r="D15" s="87"/>
+      <c r="E15" s="105"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="105"/>
+      <c r="H15" s="108"/>
+      <c r="I15" s="105"/>
+      <c r="J15" s="104"/>
+      <c r="K15" s="22" t="s">
         <v>55</v>
       </c>
       <c r="L15" s="17">
         <v>0.51780000000000004</v>
       </c>
-      <c r="M15" s="51">
+      <c r="M15" s="50">
         <v>0.54100000000000004</v>
       </c>
       <c r="N15" s="17">
@@ -10277,108 +10277,108 @@
       <c r="Q15" s="17">
         <v>0.53800000000000003</v>
       </c>
-      <c r="R15" s="78">
+      <c r="R15" s="77">
         <v>0.53600000000000003</v>
       </c>
-      <c r="S15" s="78">
+      <c r="S15" s="77">
         <v>0.5363</v>
       </c>
-      <c r="T15" s="78">
+      <c r="T15" s="77">
         <v>0.53749999999999998</v>
       </c>
-      <c r="U15" s="32"/>
-      <c r="V15" s="32"/>
-      <c r="W15" s="33"/>
-      <c r="X15" s="92"/>
-      <c r="Y15" s="111"/>
-      <c r="Z15" s="111"/>
-      <c r="AA15" s="129"/>
+      <c r="U15" s="31"/>
+      <c r="V15" s="31"/>
+      <c r="W15" s="32"/>
+      <c r="X15" s="91"/>
+      <c r="Y15" s="110"/>
+      <c r="Z15" s="110"/>
+      <c r="AA15" s="128"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A16" s="107" t="s">
+      <c r="A16" s="106" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="91" t="s">
+      <c r="B16" s="90" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="91" t="s">
+      <c r="C16" s="90" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="88" t="s">
+      <c r="D16" s="87" t="s">
         <v>73</v>
       </c>
-      <c r="E16" s="106" t="s">
+      <c r="E16" s="105" t="s">
         <v>74</v>
       </c>
-      <c r="F16" s="106"/>
-      <c r="G16" s="106"/>
-      <c r="H16" s="109" t="s">
+      <c r="F16" s="105"/>
+      <c r="G16" s="105"/>
+      <c r="H16" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="I16" s="106" t="s">
+      <c r="I16" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="105" t="s">
+      <c r="J16" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="K16" s="23" t="s">
+      <c r="K16" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L16" s="38">
+      <c r="L16" s="37">
         <v>0.11774014693384624</v>
       </c>
-      <c r="M16" s="38">
+      <c r="M16" s="37">
         <v>7.6823633140503819E-2</v>
       </c>
-      <c r="N16" s="38">
+      <c r="N16" s="37">
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="O16" s="38">
+      <c r="O16" s="37">
         <v>9.9962463776604421E-2</v>
       </c>
-      <c r="P16" s="38">
+      <c r="P16" s="37">
         <v>0.1038498729590533</v>
       </c>
-      <c r="Q16" s="38">
+      <c r="Q16" s="37">
         <v>0.11814554963094943</v>
       </c>
-      <c r="R16" s="82">
+      <c r="R16" s="81">
         <v>0.13344842106998206</v>
       </c>
-      <c r="S16" s="82">
+      <c r="S16" s="81">
         <v>0.13972119594175969</v>
       </c>
-      <c r="T16" s="82">
+      <c r="T16" s="81">
         <v>0.13600000000000001</v>
       </c>
-      <c r="U16" s="25"/>
-      <c r="V16" s="25"/>
-      <c r="W16" s="26"/>
-      <c r="X16" s="92"/>
-      <c r="Y16" s="93"/>
-      <c r="Z16" s="113"/>
-      <c r="AA16" s="121" t="s">
+      <c r="U16" s="24"/>
+      <c r="V16" s="24"/>
+      <c r="W16" s="25"/>
+      <c r="X16" s="91"/>
+      <c r="Y16" s="92"/>
+      <c r="Z16" s="112"/>
+      <c r="AA16" s="120" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A17" s="107"/>
-      <c r="B17" s="91"/>
-      <c r="C17" s="91"/>
-      <c r="D17" s="88"/>
-      <c r="E17" s="106"/>
-      <c r="F17" s="106"/>
-      <c r="G17" s="106"/>
-      <c r="H17" s="109"/>
-      <c r="I17" s="106"/>
-      <c r="J17" s="105"/>
-      <c r="K17" s="23" t="s">
+      <c r="A17" s="106"/>
+      <c r="B17" s="90"/>
+      <c r="C17" s="90"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="105"/>
+      <c r="F17" s="105"/>
+      <c r="G17" s="105"/>
+      <c r="H17" s="108"/>
+      <c r="I17" s="105"/>
+      <c r="J17" s="104"/>
+      <c r="K17" s="22" t="s">
         <v>55</v>
       </c>
       <c r="L17" s="17">
         <v>-4.253311543933095E-2</v>
       </c>
-      <c r="M17" s="51">
+      <c r="M17" s="50">
         <v>7.8013174622509063E-2</v>
       </c>
       <c r="N17" s="17">
@@ -10404,172 +10404,172 @@
       </c>
       <c r="U17" s="19"/>
       <c r="V17" s="19"/>
-      <c r="W17" s="29"/>
-      <c r="X17" s="92"/>
-      <c r="Y17" s="94"/>
-      <c r="Z17" s="113"/>
-      <c r="AA17" s="122"/>
+      <c r="W17" s="28"/>
+      <c r="X17" s="91"/>
+      <c r="Y17" s="93"/>
+      <c r="Z17" s="112"/>
+      <c r="AA17" s="121"/>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A18" s="107"/>
-      <c r="B18" s="91" t="s">
+      <c r="A18" s="106"/>
+      <c r="B18" s="90" t="s">
         <v>76</v>
       </c>
-      <c r="C18" s="91" t="s">
+      <c r="C18" s="90" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="91" t="s">
+      <c r="D18" s="90" t="s">
         <v>77</v>
       </c>
-      <c r="E18" s="106" t="s">
+      <c r="E18" s="105" t="s">
         <v>74</v>
       </c>
-      <c r="F18" s="106"/>
-      <c r="G18" s="106"/>
-      <c r="H18" s="109" t="s">
+      <c r="F18" s="105"/>
+      <c r="G18" s="105"/>
+      <c r="H18" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="I18" s="106" t="s">
+      <c r="I18" s="105" t="s">
         <v>78</v>
       </c>
-      <c r="J18" s="105" t="s">
+      <c r="J18" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="K18" s="23" t="s">
+      <c r="K18" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L18" s="48">
+      <c r="L18" s="47">
         <v>0.224</v>
       </c>
-      <c r="M18" s="48">
+      <c r="M18" s="47">
         <v>0.35800000000000004</v>
       </c>
-      <c r="N18" s="48">
+      <c r="N18" s="47">
         <v>0.79700000000000004</v>
       </c>
-      <c r="O18" s="48">
+      <c r="O18" s="47">
         <v>1.0409999999999999</v>
       </c>
-      <c r="P18" s="48">
+      <c r="P18" s="47">
         <v>1.155</v>
       </c>
-      <c r="Q18" s="48">
+      <c r="Q18" s="47">
         <v>1.6040000000000001</v>
       </c>
-      <c r="R18" s="48">
+      <c r="R18" s="47">
         <v>2.4180000000000001</v>
       </c>
-      <c r="S18" s="48">
+      <c r="S18" s="47">
         <v>2.93</v>
       </c>
-      <c r="T18" s="48">
+      <c r="T18" s="47">
         <v>4.2699999999999996</v>
       </c>
-      <c r="U18" s="48"/>
-      <c r="V18" s="48"/>
-      <c r="W18" s="48"/>
-      <c r="X18" s="155" t="s">
+      <c r="U18" s="47"/>
+      <c r="V18" s="47"/>
+      <c r="W18" s="47"/>
+      <c r="X18" s="154" t="s">
         <v>134</v>
       </c>
-      <c r="Y18" s="155"/>
-      <c r="Z18" s="152">
+      <c r="Y18" s="154"/>
+      <c r="Z18" s="151">
         <v>46108</v>
       </c>
-      <c r="AA18" s="154"/>
+      <c r="AA18" s="153"/>
     </row>
     <row r="19" spans="1:27" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="107"/>
-      <c r="B19" s="91"/>
-      <c r="C19" s="91"/>
-      <c r="D19" s="91"/>
-      <c r="E19" s="106"/>
-      <c r="F19" s="106"/>
-      <c r="G19" s="106"/>
-      <c r="H19" s="109"/>
-      <c r="I19" s="106"/>
-      <c r="J19" s="105"/>
-      <c r="K19" s="23" t="s">
+      <c r="A19" s="106"/>
+      <c r="B19" s="90"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="90"/>
+      <c r="E19" s="105"/>
+      <c r="F19" s="105"/>
+      <c r="G19" s="105"/>
+      <c r="H19" s="108"/>
+      <c r="I19" s="105"/>
+      <c r="J19" s="104"/>
+      <c r="K19" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="L19" s="169">
+      <c r="L19" s="168">
         <v>0.2598381666666667</v>
       </c>
-      <c r="M19" s="169">
+      <c r="M19" s="168">
         <v>0.3838381666666667</v>
       </c>
-      <c r="N19" s="169">
+      <c r="N19" s="168">
         <v>1.1128381666666667</v>
       </c>
-      <c r="O19" s="169">
+      <c r="O19" s="168">
         <v>1.3223861666666668</v>
       </c>
-      <c r="P19" s="169">
+      <c r="P19" s="168">
         <v>1.6513861666666667</v>
       </c>
-      <c r="Q19" s="169">
+      <c r="Q19" s="168">
         <v>2.1303861666666668</v>
       </c>
-      <c r="R19" s="170">
+      <c r="R19" s="169">
         <v>2.6433861666666667</v>
       </c>
-      <c r="S19" s="170">
+      <c r="S19" s="169">
         <v>3.3972231666666666</v>
       </c>
-      <c r="T19" s="170">
+      <c r="T19" s="169">
         <v>4.5205241666666662</v>
       </c>
-      <c r="U19" s="47"/>
-      <c r="V19" s="47"/>
-      <c r="W19" s="49"/>
-      <c r="X19" s="155"/>
-      <c r="Y19" s="155"/>
-      <c r="Z19" s="153"/>
-      <c r="AA19" s="154"/>
+      <c r="U19" s="46"/>
+      <c r="V19" s="46"/>
+      <c r="W19" s="48"/>
+      <c r="X19" s="154"/>
+      <c r="Y19" s="154"/>
+      <c r="Z19" s="152"/>
+      <c r="AA19" s="153"/>
     </row>
     <row r="20" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="107"/>
-      <c r="B20" s="91" t="s">
+      <c r="A20" s="106"/>
+      <c r="B20" s="90" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="91" t="s">
+      <c r="C20" s="90" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="88" t="s">
+      <c r="D20" s="87" t="s">
         <v>80</v>
       </c>
-      <c r="E20" s="106" t="s">
+      <c r="E20" s="105" t="s">
         <v>74</v>
       </c>
-      <c r="F20" s="106"/>
-      <c r="G20" s="106"/>
-      <c r="H20" s="109" t="s">
+      <c r="F20" s="105"/>
+      <c r="G20" s="105"/>
+      <c r="H20" s="108" t="s">
         <v>51</v>
       </c>
-      <c r="I20" s="106" t="s">
+      <c r="I20" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="105" t="s">
+      <c r="J20" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="K20" s="23" t="s">
+      <c r="K20" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L20" s="36">
+      <c r="L20" s="35">
         <v>0.28399999999999997</v>
       </c>
-      <c r="M20" s="36">
+      <c r="M20" s="35">
         <v>0.28260000000000002</v>
       </c>
-      <c r="N20" s="36">
+      <c r="N20" s="35">
         <v>0.28999999999999998</v>
       </c>
-      <c r="O20" s="36">
+      <c r="O20" s="35">
         <v>0.28999999999999998</v>
       </c>
-      <c r="P20" s="36">
+      <c r="P20" s="35">
         <v>0.27</v>
       </c>
-      <c r="Q20" s="36">
+      <c r="Q20" s="35">
         <v>0.26</v>
       </c>
       <c r="R20" s="18">
@@ -10583,30 +10583,30 @@
       </c>
       <c r="U20" s="18"/>
       <c r="V20" s="18"/>
-      <c r="W20" s="28"/>
-      <c r="X20" s="97" t="s">
+      <c r="W20" s="27"/>
+      <c r="X20" s="96" t="s">
         <v>140</v>
       </c>
-      <c r="Y20" s="99" t="s">
+      <c r="Y20" s="98" t="s">
         <v>139</v>
       </c>
-      <c r="Z20" s="151"/>
-      <c r="AA20" s="123" t="s">
+      <c r="Z20" s="150"/>
+      <c r="AA20" s="122" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="107"/>
-      <c r="B21" s="91"/>
-      <c r="C21" s="91"/>
-      <c r="D21" s="88"/>
-      <c r="E21" s="106"/>
-      <c r="F21" s="106"/>
-      <c r="G21" s="106"/>
-      <c r="H21" s="109"/>
-      <c r="I21" s="106"/>
-      <c r="J21" s="105"/>
-      <c r="K21" s="23" t="s">
+      <c r="A21" s="106"/>
+      <c r="B21" s="90"/>
+      <c r="C21" s="90"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="105"/>
+      <c r="F21" s="105"/>
+      <c r="G21" s="105"/>
+      <c r="H21" s="108"/>
+      <c r="I21" s="105"/>
+      <c r="J21" s="104"/>
+      <c r="K21" s="22" t="s">
         <v>55</v>
       </c>
       <c r="L21" s="19">
@@ -10627,69 +10627,69 @@
       <c r="Q21" s="19">
         <v>0.28999999999999998</v>
       </c>
-      <c r="R21" s="30">
+      <c r="R21" s="29">
         <v>0.3</v>
       </c>
-      <c r="S21" s="30">
+      <c r="S21" s="29">
         <v>0.3</v>
       </c>
-      <c r="T21" s="30">
+      <c r="T21" s="29">
         <v>0.27</v>
       </c>
-      <c r="U21" s="30"/>
-      <c r="V21" s="30"/>
-      <c r="W21" s="31"/>
-      <c r="X21" s="98"/>
-      <c r="Y21" s="100"/>
-      <c r="Z21" s="117"/>
-      <c r="AA21" s="123"/>
+      <c r="U21" s="29"/>
+      <c r="V21" s="29"/>
+      <c r="W21" s="30"/>
+      <c r="X21" s="97"/>
+      <c r="Y21" s="99"/>
+      <c r="Z21" s="116"/>
+      <c r="AA21" s="122"/>
     </row>
     <row r="22" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="107" t="s">
+      <c r="A22" s="106" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="91" t="s">
+      <c r="B22" s="90" t="s">
         <v>82</v>
       </c>
-      <c r="C22" s="120" t="s">
+      <c r="C22" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="D22" s="91" t="s">
+      <c r="D22" s="90" t="s">
         <v>84</v>
       </c>
-      <c r="E22" s="106">
+      <c r="E22" s="105">
         <v>90</v>
       </c>
-      <c r="F22" s="106"/>
-      <c r="G22" s="106"/>
-      <c r="H22" s="109" t="s">
+      <c r="F22" s="105"/>
+      <c r="G22" s="105"/>
+      <c r="H22" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="106" t="s">
+      <c r="I22" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="J22" s="105" t="s">
+      <c r="J22" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="K22" s="23" t="s">
+      <c r="K22" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L22" s="36">
+      <c r="L22" s="35">
         <v>0.9</v>
       </c>
-      <c r="M22" s="36">
+      <c r="M22" s="35">
         <v>0.9</v>
       </c>
-      <c r="N22" s="36">
+      <c r="N22" s="35">
         <v>0.9</v>
       </c>
-      <c r="O22" s="36">
+      <c r="O22" s="35">
         <v>0.9</v>
       </c>
-      <c r="P22" s="36">
+      <c r="P22" s="35">
         <v>0.9</v>
       </c>
-      <c r="Q22" s="36">
+      <c r="Q22" s="35">
         <v>0.9</v>
       </c>
       <c r="R22" s="18">
@@ -10707,34 +10707,34 @@
       <c r="V22" s="18">
         <v>0.9</v>
       </c>
-      <c r="W22" s="28">
+      <c r="W22" s="27">
         <v>0.9</v>
       </c>
-      <c r="X22" s="103"/>
-      <c r="Y22" s="93"/>
-      <c r="Z22" s="112">
+      <c r="X22" s="102"/>
+      <c r="Y22" s="92"/>
+      <c r="Z22" s="111">
         <v>46257</v>
       </c>
-      <c r="AA22" s="159"/>
+      <c r="AA22" s="158"/>
     </row>
     <row r="23" spans="1:27" ht="17.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="166"/>
-      <c r="B23" s="91"/>
-      <c r="C23" s="120"/>
-      <c r="D23" s="91"/>
-      <c r="E23" s="106"/>
-      <c r="F23" s="106"/>
-      <c r="G23" s="106"/>
-      <c r="H23" s="109"/>
-      <c r="I23" s="106"/>
-      <c r="J23" s="105"/>
-      <c r="K23" s="23" t="s">
+      <c r="A23" s="165"/>
+      <c r="B23" s="90"/>
+      <c r="C23" s="119"/>
+      <c r="D23" s="90"/>
+      <c r="E23" s="105"/>
+      <c r="F23" s="105"/>
+      <c r="G23" s="105"/>
+      <c r="H23" s="108"/>
+      <c r="I23" s="105"/>
+      <c r="J23" s="104"/>
+      <c r="K23" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="L23" s="55">
+      <c r="L23" s="54">
         <v>0.81</v>
       </c>
-      <c r="M23" s="55">
+      <c r="M23" s="54">
         <v>0.78</v>
       </c>
       <c r="N23" s="19">
@@ -10749,226 +10749,226 @@
       <c r="Q23" s="19">
         <v>0.86</v>
       </c>
-      <c r="R23" s="30">
+      <c r="R23" s="29">
         <v>0.88</v>
       </c>
-      <c r="S23" s="30">
+      <c r="S23" s="29">
         <v>0.94</v>
       </c>
-      <c r="T23" s="30">
-        <v>0.91</v>
-      </c>
-      <c r="U23" s="30"/>
-      <c r="V23" s="30"/>
-      <c r="W23" s="31"/>
-      <c r="X23" s="104"/>
-      <c r="Y23" s="94"/>
-      <c r="Z23" s="113"/>
-      <c r="AA23" s="160"/>
+      <c r="T23" s="29">
+        <v>0.94</v>
+      </c>
+      <c r="U23" s="29"/>
+      <c r="V23" s="29"/>
+      <c r="W23" s="30"/>
+      <c r="X23" s="103"/>
+      <c r="Y23" s="93"/>
+      <c r="Z23" s="112"/>
+      <c r="AA23" s="159"/>
     </row>
     <row r="24" spans="1:27" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="141" t="s">
+      <c r="A24" s="140" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="91" t="s">
+      <c r="B24" s="90" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="120" t="s">
+      <c r="C24" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="D24" s="88" t="s">
+      <c r="D24" s="87" t="s">
         <v>87</v>
       </c>
-      <c r="E24" s="106" t="s">
+      <c r="E24" s="105" t="s">
         <v>88</v>
       </c>
-      <c r="F24" s="106" t="s">
+      <c r="F24" s="105" t="s">
         <v>88</v>
       </c>
-      <c r="G24" s="106" t="s">
+      <c r="G24" s="105" t="s">
         <v>88</v>
       </c>
-      <c r="H24" s="109" t="s">
+      <c r="H24" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="106" t="s">
+      <c r="I24" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="J24" s="118" t="s">
+      <c r="J24" s="117" t="s">
         <v>34</v>
       </c>
-      <c r="K24" s="23" t="s">
+      <c r="K24" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L24" s="36"/>
-      <c r="M24" s="36"/>
-      <c r="N24" s="38">
+      <c r="L24" s="35"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="37">
         <v>0.104</v>
       </c>
-      <c r="O24" s="22" t="s">
+      <c r="O24" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="P24" s="22" t="s">
+      <c r="P24" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="Q24" s="38">
+      <c r="Q24" s="37">
         <v>0.11799999999999999</v>
       </c>
-      <c r="R24" s="22" t="s">
+      <c r="R24" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="S24" s="22" t="s">
+      <c r="S24" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="T24" s="36"/>
-      <c r="U24" s="22" t="s">
+      <c r="T24" s="35"/>
+      <c r="U24" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="V24" s="22" t="s">
+      <c r="V24" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="W24" s="39"/>
-      <c r="X24" s="135"/>
-      <c r="Y24" s="150"/>
-      <c r="Z24" s="117"/>
-      <c r="AA24" s="121" t="s">
+      <c r="W24" s="38"/>
+      <c r="X24" s="134"/>
+      <c r="Y24" s="149"/>
+      <c r="Z24" s="116"/>
+      <c r="AA24" s="120" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="165"/>
-      <c r="B25" s="91"/>
-      <c r="C25" s="120"/>
-      <c r="D25" s="88"/>
-      <c r="E25" s="106"/>
-      <c r="F25" s="106"/>
-      <c r="G25" s="106"/>
-      <c r="H25" s="109"/>
-      <c r="I25" s="106"/>
-      <c r="J25" s="118"/>
-      <c r="K25" s="23" t="s">
+      <c r="A25" s="164"/>
+      <c r="B25" s="90"/>
+      <c r="C25" s="119"/>
+      <c r="D25" s="87"/>
+      <c r="E25" s="105"/>
+      <c r="F25" s="105"/>
+      <c r="G25" s="105"/>
+      <c r="H25" s="108"/>
+      <c r="I25" s="105"/>
+      <c r="J25" s="117"/>
+      <c r="K25" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="L25" s="22" t="s">
+      <c r="L25" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="M25" s="22" t="s">
+      <c r="M25" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="N25" s="51">
+      <c r="N25" s="50">
         <v>0.115</v>
       </c>
-      <c r="O25" s="22" t="s">
+      <c r="O25" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="P25" s="22" t="s">
+      <c r="P25" s="21" t="s">
         <v>89</v>
       </c>
       <c r="Q25" s="17">
         <v>0.121</v>
       </c>
-      <c r="R25" s="22" t="s">
+      <c r="R25" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="S25" s="22" t="s">
+      <c r="S25" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="T25" s="56"/>
-      <c r="U25" s="22" t="s">
+      <c r="T25" s="55"/>
+      <c r="U25" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="V25" s="22" t="s">
+      <c r="V25" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="W25" s="56"/>
-      <c r="X25" s="104"/>
-      <c r="Y25" s="111"/>
-      <c r="Z25" s="151"/>
-      <c r="AA25" s="122"/>
+      <c r="W25" s="55"/>
+      <c r="X25" s="103"/>
+      <c r="Y25" s="110"/>
+      <c r="Z25" s="150"/>
+      <c r="AA25" s="121"/>
     </row>
     <row r="26" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="165"/>
-      <c r="B26" s="89" t="s">
+      <c r="A26" s="164"/>
+      <c r="B26" s="88" t="s">
         <v>91</v>
       </c>
-      <c r="C26" s="158" t="s">
+      <c r="C26" s="157" t="s">
         <v>86</v>
       </c>
-      <c r="D26" s="88" t="s">
+      <c r="D26" s="87" t="s">
         <v>92</v>
       </c>
-      <c r="E26" s="106">
+      <c r="E26" s="105">
         <v>34</v>
       </c>
-      <c r="F26" s="156"/>
-      <c r="G26" s="156"/>
-      <c r="H26" s="109" t="s">
+      <c r="F26" s="155"/>
+      <c r="G26" s="155"/>
+      <c r="H26" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="I26" s="106" t="s">
+      <c r="I26" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="J26" s="105" t="s">
+      <c r="J26" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="K26" s="23" t="s">
+      <c r="K26" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L26" s="36">
+      <c r="L26" s="35">
         <v>0.34</v>
       </c>
-      <c r="M26" s="36">
+      <c r="M26" s="35">
         <v>0.34</v>
       </c>
-      <c r="N26" s="36">
+      <c r="N26" s="35">
         <v>0.34</v>
       </c>
-      <c r="O26" s="36">
+      <c r="O26" s="35">
         <v>0.34</v>
       </c>
-      <c r="P26" s="36">
+      <c r="P26" s="35">
         <v>0.34</v>
       </c>
-      <c r="Q26" s="36">
+      <c r="Q26" s="35">
         <v>0.34</v>
       </c>
-      <c r="R26" s="36">
+      <c r="R26" s="35">
         <v>0.34</v>
       </c>
-      <c r="S26" s="25">
+      <c r="S26" s="24">
         <v>0.34</v>
       </c>
-      <c r="T26" s="25">
+      <c r="T26" s="24">
         <v>0.34</v>
       </c>
-      <c r="U26" s="25"/>
-      <c r="V26" s="25"/>
-      <c r="W26" s="26"/>
-      <c r="X26" s="92"/>
-      <c r="Y26" s="94"/>
-      <c r="Z26" s="113"/>
-      <c r="AA26" s="121" t="s">
+      <c r="U26" s="24"/>
+      <c r="V26" s="24"/>
+      <c r="W26" s="25"/>
+      <c r="X26" s="91"/>
+      <c r="Y26" s="93"/>
+      <c r="Z26" s="112"/>
+      <c r="AA26" s="120" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="165"/>
-      <c r="B27" s="89"/>
-      <c r="C27" s="158"/>
-      <c r="D27" s="88"/>
-      <c r="E27" s="106"/>
-      <c r="F27" s="156"/>
-      <c r="G27" s="156"/>
-      <c r="H27" s="109"/>
-      <c r="I27" s="106"/>
-      <c r="J27" s="105"/>
-      <c r="K27" s="23" t="s">
+      <c r="A27" s="164"/>
+      <c r="B27" s="88"/>
+      <c r="C27" s="157"/>
+      <c r="D27" s="87"/>
+      <c r="E27" s="105"/>
+      <c r="F27" s="155"/>
+      <c r="G27" s="155"/>
+      <c r="H27" s="108"/>
+      <c r="I27" s="105"/>
+      <c r="J27" s="104"/>
+      <c r="K27" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="L27" s="79">
+      <c r="L27" s="78">
         <v>0.318</v>
       </c>
-      <c r="M27" s="51">
+      <c r="M27" s="50">
         <v>0.35799999999999998</v>
       </c>
       <c r="N27" s="17">
@@ -10994,97 +10994,97 @@
       </c>
       <c r="U27" s="19"/>
       <c r="V27" s="19"/>
-      <c r="W27" s="29"/>
-      <c r="X27" s="92"/>
-      <c r="Y27" s="94"/>
-      <c r="Z27" s="113"/>
-      <c r="AA27" s="122"/>
+      <c r="W27" s="28"/>
+      <c r="X27" s="91"/>
+      <c r="Y27" s="93"/>
+      <c r="Z27" s="112"/>
+      <c r="AA27" s="121"/>
     </row>
     <row r="28" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="165"/>
-      <c r="B28" s="88" t="s">
+      <c r="A28" s="164"/>
+      <c r="B28" s="87" t="s">
         <v>94</v>
       </c>
-      <c r="C28" s="91" t="s">
+      <c r="C28" s="90" t="s">
         <v>72</v>
       </c>
-      <c r="D28" s="88" t="s">
+      <c r="D28" s="87" t="s">
         <v>95</v>
       </c>
-      <c r="E28" s="106" t="s">
+      <c r="E28" s="105" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="106"/>
-      <c r="G28" s="106"/>
-      <c r="H28" s="109" t="s">
+      <c r="F28" s="105"/>
+      <c r="G28" s="105"/>
+      <c r="H28" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="I28" s="106" t="s">
+      <c r="I28" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="J28" s="105" t="s">
+      <c r="J28" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="K28" s="23" t="s">
+      <c r="K28" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L28" s="38" vm="1">
+      <c r="L28" s="37" vm="1">
         <v>3.6951550944796852E-2</v>
       </c>
-      <c r="M28" s="38" vm="3">
+      <c r="M28" s="37" vm="3">
         <v>0.43621586155644376</v>
       </c>
-      <c r="N28" s="38" vm="6">
+      <c r="N28" s="37" vm="6">
         <v>6.9838696752701823E-2</v>
       </c>
-      <c r="O28" s="38" vm="10">
+      <c r="O28" s="37" vm="10">
         <v>0.21843539773619547</v>
       </c>
-      <c r="P28" s="38" vm="12">
+      <c r="P28" s="37" vm="12">
         <v>0.20239261325941293</v>
       </c>
-      <c r="Q28" s="38" vm="14">
+      <c r="Q28" s="37" vm="14">
         <v>0.29754592225545773</v>
       </c>
-      <c r="R28" s="82" vm="18">
+      <c r="R28" s="81" vm="18">
         <v>0.26300517799117751</v>
       </c>
-      <c r="S28" s="82" vm="22">
+      <c r="S28" s="81" vm="22">
         <v>0.30756202137510114</v>
       </c>
-      <c r="T28" s="82">
+      <c r="T28" s="81">
         <v>0.38100000000000001</v>
       </c>
-      <c r="U28" s="25"/>
-      <c r="V28" s="25"/>
-      <c r="W28" s="26"/>
-      <c r="X28" s="101" t="s">
+      <c r="U28" s="24"/>
+      <c r="V28" s="24"/>
+      <c r="W28" s="25"/>
+      <c r="X28" s="100" t="s">
         <v>135</v>
       </c>
-      <c r="Y28" s="95"/>
-      <c r="Z28" s="117"/>
-      <c r="AA28" s="126" t="s">
+      <c r="Y28" s="94"/>
+      <c r="Z28" s="116"/>
+      <c r="AA28" s="125" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="165"/>
-      <c r="B29" s="88"/>
-      <c r="C29" s="91"/>
-      <c r="D29" s="88"/>
-      <c r="E29" s="106"/>
-      <c r="F29" s="106"/>
-      <c r="G29" s="106"/>
-      <c r="H29" s="109"/>
-      <c r="I29" s="106"/>
-      <c r="J29" s="105"/>
-      <c r="K29" s="23" t="s">
+      <c r="A29" s="164"/>
+      <c r="B29" s="87"/>
+      <c r="C29" s="90"/>
+      <c r="D29" s="87"/>
+      <c r="E29" s="105"/>
+      <c r="F29" s="105"/>
+      <c r="G29" s="105"/>
+      <c r="H29" s="108"/>
+      <c r="I29" s="105"/>
+      <c r="J29" s="104"/>
+      <c r="K29" s="22" t="s">
         <v>55</v>
       </c>
       <c r="L29" s="17" vm="2">
         <v>-0.21537837470975407</v>
       </c>
-      <c r="M29" s="50">
+      <c r="M29" s="49">
         <v>0.27400000000000002</v>
       </c>
       <c r="N29" s="17" vm="7">
@@ -11110,91 +11110,91 @@
       </c>
       <c r="U29" s="19"/>
       <c r="V29" s="19"/>
-      <c r="W29" s="29"/>
-      <c r="X29" s="102"/>
-      <c r="Y29" s="96"/>
-      <c r="Z29" s="151"/>
-      <c r="AA29" s="127"/>
+      <c r="W29" s="28"/>
+      <c r="X29" s="101"/>
+      <c r="Y29" s="95"/>
+      <c r="Z29" s="150"/>
+      <c r="AA29" s="126"/>
     </row>
     <row r="30" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="165"/>
-      <c r="B30" s="88"/>
-      <c r="C30" s="91" t="s">
+      <c r="A30" s="164"/>
+      <c r="B30" s="87"/>
+      <c r="C30" s="90" t="s">
         <v>72</v>
       </c>
-      <c r="D30" s="88" t="s">
+      <c r="D30" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="E30" s="106" t="s">
+      <c r="E30" s="105" t="s">
         <v>74</v>
       </c>
-      <c r="F30" s="106"/>
-      <c r="G30" s="106"/>
-      <c r="H30" s="109" t="s">
+      <c r="F30" s="105"/>
+      <c r="G30" s="105"/>
+      <c r="H30" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="I30" s="106" t="s">
+      <c r="I30" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="J30" s="105" t="s">
+      <c r="J30" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="K30" s="23" t="s">
+      <c r="K30" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L30" s="38">
+      <c r="L30" s="37">
         <v>0.35899999999999999</v>
       </c>
-      <c r="M30" s="38" vm="4">
+      <c r="M30" s="37" vm="4">
         <v>9.8925321866648819E-2</v>
       </c>
-      <c r="N30" s="38" vm="8">
+      <c r="N30" s="37" vm="8">
         <v>0.11712228373869382</v>
       </c>
-      <c r="O30" s="38">
+      <c r="O30" s="37">
         <v>0.15809999999999999</v>
       </c>
-      <c r="P30" s="38">
+      <c r="P30" s="37">
         <v>0.151</v>
       </c>
-      <c r="Q30" s="38" vm="16">
+      <c r="Q30" s="37" vm="16">
         <v>0.12551463489599346</v>
       </c>
-      <c r="R30" s="82" vm="20">
+      <c r="R30" s="81" vm="20">
         <v>0.10280225768958351</v>
       </c>
-      <c r="S30" s="82">
+      <c r="S30" s="81">
         <v>0.13500000000000001</v>
       </c>
-      <c r="T30" s="82">
+      <c r="T30" s="81">
         <v>0.11600000000000001</v>
       </c>
-      <c r="U30" s="25"/>
-      <c r="V30" s="25"/>
-      <c r="W30" s="26"/>
-      <c r="X30" s="101"/>
-      <c r="Y30" s="150"/>
-      <c r="Z30" s="117"/>
-      <c r="AA30" s="163"/>
+      <c r="U30" s="24"/>
+      <c r="V30" s="24"/>
+      <c r="W30" s="25"/>
+      <c r="X30" s="100"/>
+      <c r="Y30" s="149"/>
+      <c r="Z30" s="116"/>
+      <c r="AA30" s="162"/>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A31" s="165"/>
-      <c r="B31" s="88"/>
-      <c r="C31" s="91"/>
-      <c r="D31" s="88"/>
-      <c r="E31" s="106"/>
-      <c r="F31" s="106"/>
-      <c r="G31" s="106"/>
-      <c r="H31" s="109"/>
-      <c r="I31" s="106"/>
-      <c r="J31" s="105"/>
-      <c r="K31" s="23" t="s">
+      <c r="A31" s="164"/>
+      <c r="B31" s="87"/>
+      <c r="C31" s="90"/>
+      <c r="D31" s="87"/>
+      <c r="E31" s="105"/>
+      <c r="F31" s="105"/>
+      <c r="G31" s="105"/>
+      <c r="H31" s="108"/>
+      <c r="I31" s="105"/>
+      <c r="J31" s="104"/>
+      <c r="K31" s="22" t="s">
         <v>55</v>
       </c>
       <c r="L31" s="17">
         <v>0.32500000000000001</v>
       </c>
-      <c r="M31" s="51" vm="5">
+      <c r="M31" s="50" vm="5">
         <v>0.19016698273293486</v>
       </c>
       <c r="N31" s="17" vm="9">
@@ -11209,73 +11209,73 @@
       <c r="Q31" s="17" vm="17">
         <v>0.15714973912715791</v>
       </c>
-      <c r="R31" s="83" vm="21">
+      <c r="R31" s="82" vm="21">
         <v>0.10382365349216505</v>
       </c>
-      <c r="S31" s="83">
+      <c r="S31" s="82">
         <v>0.151</v>
       </c>
-      <c r="T31" s="83">
+      <c r="T31" s="82">
         <v>0.17799999999999999</v>
       </c>
-      <c r="U31" s="45"/>
-      <c r="V31" s="45"/>
-      <c r="W31" s="46"/>
-      <c r="X31" s="102"/>
-      <c r="Y31" s="111"/>
-      <c r="Z31" s="151"/>
-      <c r="AA31" s="164"/>
+      <c r="U31" s="44"/>
+      <c r="V31" s="44"/>
+      <c r="W31" s="45"/>
+      <c r="X31" s="101"/>
+      <c r="Y31" s="110"/>
+      <c r="Z31" s="150"/>
+      <c r="AA31" s="163"/>
     </row>
     <row r="32" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="165"/>
-      <c r="B32" s="91" t="s">
+      <c r="A32" s="164"/>
+      <c r="B32" s="90" t="s">
         <v>98</v>
       </c>
-      <c r="C32" s="120" t="s">
+      <c r="C32" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="88" t="s">
+      <c r="D32" s="87" t="s">
         <v>99</v>
       </c>
-      <c r="E32" s="106" t="s">
+      <c r="E32" s="105" t="s">
         <v>74</v>
       </c>
-      <c r="F32" s="106"/>
-      <c r="G32" s="106"/>
-      <c r="H32" s="109" t="s">
+      <c r="F32" s="105"/>
+      <c r="G32" s="105"/>
+      <c r="H32" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="I32" s="106" t="s">
+      <c r="I32" s="105" t="s">
         <v>78</v>
       </c>
-      <c r="J32" s="105" t="s">
+      <c r="J32" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="K32" s="23" t="s">
+      <c r="K32" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L32" s="42">
+      <c r="L32" s="41">
         <v>8.6903037999999988</v>
       </c>
-      <c r="M32" s="42">
+      <c r="M32" s="41">
         <v>14.05</v>
       </c>
-      <c r="N32" s="42">
+      <c r="N32" s="41">
         <v>24.179069699999999</v>
       </c>
-      <c r="O32" s="65">
+      <c r="O32" s="64">
         <v>33.551317699999998</v>
       </c>
-      <c r="P32" s="42">
+      <c r="P32" s="41">
         <v>41.442849800000005</v>
       </c>
-      <c r="Q32" s="80">
+      <c r="Q32" s="79">
         <v>60.823965100000009</v>
       </c>
       <c r="R32" s="8">
         <v>72.599999999999994</v>
       </c>
-      <c r="S32" s="85">
+      <c r="S32" s="84">
         <v>82.449704499999996</v>
       </c>
       <c r="T32" s="8">
@@ -11283,162 +11283,162 @@
       </c>
       <c r="U32" s="8"/>
       <c r="V32" s="8"/>
-      <c r="W32" s="34"/>
-      <c r="X32" s="167" t="s">
+      <c r="W32" s="33"/>
+      <c r="X32" s="166" t="s">
         <v>136</v>
       </c>
-      <c r="Y32" s="95" t="s">
+      <c r="Y32" s="94" t="s">
         <v>138</v>
       </c>
-      <c r="Z32" s="117"/>
-      <c r="AA32" s="121" t="s">
+      <c r="Z32" s="116"/>
+      <c r="AA32" s="120" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:29" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="165"/>
-      <c r="B33" s="91"/>
-      <c r="C33" s="120"/>
-      <c r="D33" s="88"/>
-      <c r="E33" s="106"/>
-      <c r="F33" s="106"/>
-      <c r="G33" s="106"/>
-      <c r="H33" s="109"/>
-      <c r="I33" s="106"/>
-      <c r="J33" s="105"/>
-      <c r="K33" s="23" t="s">
+      <c r="A33" s="164"/>
+      <c r="B33" s="90"/>
+      <c r="C33" s="119"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="105"/>
+      <c r="F33" s="105"/>
+      <c r="G33" s="105"/>
+      <c r="H33" s="108"/>
+      <c r="I33" s="105"/>
+      <c r="J33" s="104"/>
+      <c r="K33" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="L33" s="43">
+      <c r="L33" s="42">
         <v>4.05</v>
       </c>
-      <c r="M33" s="52">
+      <c r="M33" s="51">
         <v>9.7989724000000002</v>
       </c>
-      <c r="N33" s="43">
+      <c r="N33" s="42">
         <v>25.313448100000002</v>
       </c>
-      <c r="O33" s="66">
+      <c r="O33" s="65">
         <v>31.452557499999998</v>
       </c>
-      <c r="P33" s="43">
+      <c r="P33" s="42">
         <v>41.128122899999994</v>
       </c>
-      <c r="Q33" s="81">
+      <c r="Q33" s="80">
         <v>55.164574999999999</v>
       </c>
-      <c r="R33" s="84">
+      <c r="R33" s="83">
         <v>61.940289700000001</v>
       </c>
-      <c r="S33" s="84">
+      <c r="S33" s="83">
         <v>72.779408199999978</v>
       </c>
-      <c r="T33" s="32">
+      <c r="T33" s="31">
         <v>91.2</v>
       </c>
-      <c r="U33" s="32"/>
-      <c r="V33" s="32"/>
-      <c r="W33" s="33"/>
-      <c r="X33" s="168"/>
-      <c r="Y33" s="96"/>
-      <c r="Z33" s="151"/>
-      <c r="AA33" s="122"/>
+      <c r="U33" s="31"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="32"/>
+      <c r="X33" s="167"/>
+      <c r="Y33" s="95"/>
+      <c r="Z33" s="150"/>
+      <c r="AA33" s="121"/>
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A34" s="107" t="s">
+      <c r="A34" s="106" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="146" t="s">
+      <c r="B34" s="145" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="90" t="s">
         <v>83</v>
       </c>
-      <c r="D34" s="88" t="s">
+      <c r="D34" s="87" t="s">
         <v>31</v>
       </c>
-      <c r="E34" s="106">
+      <c r="E34" s="105">
         <v>90</v>
       </c>
-      <c r="F34" s="106"/>
-      <c r="G34" s="106"/>
-      <c r="H34" s="109" t="s">
+      <c r="F34" s="105"/>
+      <c r="G34" s="105"/>
+      <c r="H34" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="I34" s="106" t="s">
+      <c r="I34" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="J34" s="118" t="s">
+      <c r="J34" s="117" t="s">
         <v>34</v>
       </c>
-      <c r="K34" s="23" t="s">
+      <c r="K34" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L34" s="36"/>
-      <c r="M34" s="36"/>
-      <c r="N34" s="36">
+      <c r="L34" s="35"/>
+      <c r="M34" s="35"/>
+      <c r="N34" s="35">
         <v>0.9</v>
       </c>
-      <c r="O34" s="36"/>
-      <c r="P34" s="36"/>
-      <c r="Q34" s="36">
+      <c r="O34" s="35"/>
+      <c r="P34" s="35"/>
+      <c r="Q34" s="35">
         <v>0.9</v>
       </c>
-      <c r="R34" s="25"/>
-      <c r="S34" s="25"/>
-      <c r="T34" s="25">
+      <c r="R34" s="24"/>
+      <c r="S34" s="24"/>
+      <c r="T34" s="24">
         <v>0.9</v>
       </c>
-      <c r="U34" s="25"/>
-      <c r="V34" s="25"/>
-      <c r="W34" s="26">
+      <c r="U34" s="24"/>
+      <c r="V34" s="24"/>
+      <c r="W34" s="25">
         <v>0.9</v>
       </c>
-      <c r="X34" s="92"/>
-      <c r="Y34" s="94" t="s">
+      <c r="X34" s="91"/>
+      <c r="Y34" s="93" t="s">
         <v>137</v>
       </c>
-      <c r="Z34" s="113"/>
-      <c r="AA34" s="121" t="s">
+      <c r="Z34" s="112"/>
+      <c r="AA34" s="120" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A35" s="107"/>
-      <c r="B35" s="146"/>
-      <c r="C35" s="91"/>
-      <c r="D35" s="88"/>
-      <c r="E35" s="106"/>
-      <c r="F35" s="106"/>
-      <c r="G35" s="106"/>
-      <c r="H35" s="109"/>
-      <c r="I35" s="106"/>
-      <c r="J35" s="118"/>
-      <c r="K35" s="23" t="s">
+      <c r="A35" s="106"/>
+      <c r="B35" s="145"/>
+      <c r="C35" s="90"/>
+      <c r="D35" s="87"/>
+      <c r="E35" s="105"/>
+      <c r="F35" s="105"/>
+      <c r="G35" s="105"/>
+      <c r="H35" s="108"/>
+      <c r="I35" s="105"/>
+      <c r="J35" s="117"/>
+      <c r="K35" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="L35" s="22" t="s">
+      <c r="L35" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="M35" s="22" t="s">
+      <c r="M35" s="21" t="s">
         <v>89</v>
       </c>
       <c r="N35" s="19">
         <v>1</v>
       </c>
-      <c r="O35" s="22" t="s">
+      <c r="O35" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="P35" s="22" t="s">
+      <c r="P35" s="21" t="s">
         <v>89</v>
       </c>
       <c r="Q35" s="19">
         <v>0.96199999999999997</v>
       </c>
-      <c r="R35" s="22" t="s">
+      <c r="R35" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="S35" s="22" t="s">
+      <c r="S35" s="21" t="s">
         <v>89</v>
       </c>
       <c r="T35" s="19">
@@ -11446,48 +11446,48 @@
       </c>
       <c r="U35" s="19"/>
       <c r="V35" s="19"/>
-      <c r="W35" s="29"/>
-      <c r="X35" s="92"/>
-      <c r="Y35" s="94"/>
-      <c r="Z35" s="113"/>
-      <c r="AA35" s="122"/>
+      <c r="W35" s="28"/>
+      <c r="X35" s="91"/>
+      <c r="Y35" s="93"/>
+      <c r="Z35" s="112"/>
+      <c r="AA35" s="121"/>
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A36" s="107"/>
-      <c r="B36" s="146" t="s">
+      <c r="A36" s="106"/>
+      <c r="B36" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="91" t="s">
+      <c r="C36" s="90" t="s">
         <v>102</v>
       </c>
-      <c r="D36" s="88" t="s">
+      <c r="D36" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="E36" s="106">
+      <c r="E36" s="105">
         <v>83</v>
       </c>
-      <c r="F36" s="106"/>
-      <c r="G36" s="106"/>
-      <c r="H36" s="109" t="s">
+      <c r="F36" s="105"/>
+      <c r="G36" s="105"/>
+      <c r="H36" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="I36" s="106" t="s">
+      <c r="I36" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="J36" s="119" t="s">
+      <c r="J36" s="118" t="s">
         <v>38</v>
       </c>
-      <c r="K36" s="23" t="s">
+      <c r="K36" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L36" s="36"/>
-      <c r="M36" s="36"/>
-      <c r="N36" s="36"/>
-      <c r="O36" s="36">
+      <c r="L36" s="35"/>
+      <c r="M36" s="35"/>
+      <c r="N36" s="35"/>
+      <c r="O36" s="35">
         <v>0.83</v>
       </c>
-      <c r="P36" s="36"/>
-      <c r="Q36" s="36">
+      <c r="P36" s="35"/>
+      <c r="Q36" s="35">
         <v>0.83</v>
       </c>
       <c r="R36" s="18"/>
@@ -11495,98 +11495,98 @@
       <c r="T36" s="18"/>
       <c r="U36" s="18"/>
       <c r="V36" s="18"/>
-      <c r="W36" s="28"/>
-      <c r="X36" s="92" t="s">
+      <c r="W36" s="27"/>
+      <c r="X36" s="91" t="s">
         <v>103</v>
       </c>
-      <c r="Y36" s="93" t="s">
+      <c r="Y36" s="92" t="s">
         <v>104</v>
       </c>
-      <c r="Z36" s="113"/>
-      <c r="AA36" s="121" t="s">
+      <c r="Z36" s="112"/>
+      <c r="AA36" s="120" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A37" s="107"/>
-      <c r="B37" s="146"/>
-      <c r="C37" s="91"/>
-      <c r="D37" s="88"/>
-      <c r="E37" s="106"/>
-      <c r="F37" s="106"/>
-      <c r="G37" s="106"/>
-      <c r="H37" s="109"/>
-      <c r="I37" s="106"/>
-      <c r="J37" s="119"/>
-      <c r="K37" s="23" t="s">
+      <c r="A37" s="106"/>
+      <c r="B37" s="145"/>
+      <c r="C37" s="90"/>
+      <c r="D37" s="87"/>
+      <c r="E37" s="105"/>
+      <c r="F37" s="105"/>
+      <c r="G37" s="105"/>
+      <c r="H37" s="108"/>
+      <c r="I37" s="105"/>
+      <c r="J37" s="118"/>
+      <c r="K37" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="L37" s="22" t="s">
+      <c r="L37" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="M37" s="22" t="s">
+      <c r="M37" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="N37" s="22" t="s">
+      <c r="N37" s="21" t="s">
         <v>106</v>
       </c>
       <c r="O37" s="19">
         <v>0.79</v>
       </c>
-      <c r="P37" s="22" t="s">
+      <c r="P37" s="21" t="s">
         <v>106</v>
       </c>
       <c r="Q37" s="19">
         <v>0.79</v>
       </c>
-      <c r="R37" s="22" t="s">
+      <c r="R37" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="S37" s="57"/>
-      <c r="T37" s="57"/>
-      <c r="U37" s="57"/>
-      <c r="V37" s="57"/>
-      <c r="W37" s="58"/>
-      <c r="X37" s="135"/>
-      <c r="Y37" s="95"/>
-      <c r="Z37" s="117"/>
-      <c r="AA37" s="123"/>
+      <c r="S37" s="56"/>
+      <c r="T37" s="56"/>
+      <c r="U37" s="56"/>
+      <c r="V37" s="56"/>
+      <c r="W37" s="57"/>
+      <c r="X37" s="134"/>
+      <c r="Y37" s="94"/>
+      <c r="Z37" s="116"/>
+      <c r="AA37" s="122"/>
     </row>
     <row r="38" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="136"/>
-      <c r="B38" s="136"/>
-      <c r="C38" s="136"/>
-      <c r="D38" s="136"/>
-      <c r="E38" s="136"/>
-      <c r="F38" s="136"/>
-      <c r="G38" s="136"/>
-      <c r="H38" s="136"/>
-      <c r="I38" s="136"/>
-      <c r="J38" s="136"/>
-      <c r="K38" s="136"/>
-      <c r="L38" s="136"/>
-      <c r="M38" s="136"/>
-      <c r="N38" s="136"/>
-      <c r="O38" s="136"/>
-      <c r="P38" s="137"/>
-      <c r="Q38" s="137"/>
-      <c r="R38" s="137"/>
-      <c r="S38" s="137"/>
-      <c r="T38" s="137"/>
-      <c r="U38" s="137"/>
-      <c r="V38" s="137"/>
-      <c r="W38" s="137"/>
-      <c r="X38" s="137"/>
-      <c r="Y38" s="137"/>
-      <c r="Z38" s="137"/>
-      <c r="AA38" s="137"/>
+      <c r="A38" s="135"/>
+      <c r="B38" s="135"/>
+      <c r="C38" s="135"/>
+      <c r="D38" s="135"/>
+      <c r="E38" s="135"/>
+      <c r="F38" s="135"/>
+      <c r="G38" s="135"/>
+      <c r="H38" s="135"/>
+      <c r="I38" s="135"/>
+      <c r="J38" s="135"/>
+      <c r="K38" s="135"/>
+      <c r="L38" s="135"/>
+      <c r="M38" s="135"/>
+      <c r="N38" s="135"/>
+      <c r="O38" s="135"/>
+      <c r="P38" s="136"/>
+      <c r="Q38" s="136"/>
+      <c r="R38" s="136"/>
+      <c r="S38" s="136"/>
+      <c r="T38" s="136"/>
+      <c r="U38" s="136"/>
+      <c r="V38" s="136"/>
+      <c r="W38" s="136"/>
+      <c r="X38" s="136"/>
+      <c r="Y38" s="136"/>
+      <c r="Z38" s="136"/>
+      <c r="AA38" s="136"/>
     </row>
     <row r="39" spans="1:29" s="5" customFormat="1" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="139" t="s">
+      <c r="A39" s="138" t="s">
         <v>107</v>
       </c>
-      <c r="B39" s="139"/>
-      <c r="C39" s="59"/>
+      <c r="B39" s="138"/>
+      <c r="C39" s="58"/>
       <c r="D39"/>
       <c r="E39"/>
       <c r="F39"/>
@@ -11613,7 +11613,7 @@
       <c r="AA39" s="13"/>
     </row>
     <row r="40" spans="1:29" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="44" t="s">
+      <c r="A40" s="43" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="10" t="s">
@@ -11643,7 +11643,7 @@
       <c r="J40" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="K40" s="35" t="s">
+      <c r="K40" s="34" t="s">
         <v>11</v>
       </c>
       <c r="L40" s="10" t="s">
@@ -11682,7 +11682,7 @@
       <c r="W40" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="X40" s="61" t="s">
+      <c r="X40" s="60" t="s">
         <v>43</v>
       </c>
       <c r="Y40" s="10" t="s">
@@ -11696,329 +11696,329 @@
       </c>
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A41" s="140" t="s">
+      <c r="A41" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="143" t="s">
+      <c r="B41" s="142" t="s">
         <v>114</v>
       </c>
-      <c r="C41" s="144" t="s">
+      <c r="C41" s="143" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="145" t="s">
+      <c r="D41" s="144" t="s">
         <v>115</v>
       </c>
-      <c r="E41" s="138" t="s">
+      <c r="E41" s="137" t="s">
         <v>88</v>
       </c>
-      <c r="F41" s="138" t="s">
+      <c r="F41" s="137" t="s">
         <v>88</v>
       </c>
-      <c r="G41" s="138" t="s">
+      <c r="G41" s="137" t="s">
         <v>88</v>
       </c>
-      <c r="H41" s="157" t="s">
+      <c r="H41" s="156" t="s">
         <v>51</v>
       </c>
-      <c r="I41" s="138" t="s">
+      <c r="I41" s="137" t="s">
         <v>33</v>
       </c>
-      <c r="J41" s="147" t="s">
+      <c r="J41" s="146" t="s">
         <v>52</v>
       </c>
-      <c r="K41" s="62" t="s">
+      <c r="K41" s="61" t="s">
         <v>53</v>
       </c>
-      <c r="L41" s="77">
+      <c r="L41" s="76">
         <v>1.9099999999999999E-2</v>
       </c>
-      <c r="M41" s="77">
+      <c r="M41" s="76">
         <v>4.07E-2</v>
       </c>
-      <c r="N41" s="77">
+      <c r="N41" s="76">
         <v>4.6199999999999998E-2</v>
       </c>
-      <c r="O41" s="77">
+      <c r="O41" s="76">
         <v>3.8600000000000002E-2</v>
       </c>
-      <c r="P41" s="77">
+      <c r="P41" s="76">
         <v>3.5299999999999998E-2</v>
       </c>
-      <c r="Q41" s="63">
+      <c r="Q41" s="62">
         <v>2.7099999999999999E-2</v>
       </c>
-      <c r="R41" s="63">
+      <c r="R41" s="62">
         <v>2.5100000000000001E-2</v>
       </c>
-      <c r="S41" s="63">
+      <c r="S41" s="62">
         <v>2.41E-2</v>
       </c>
-      <c r="T41" s="63">
+      <c r="T41" s="62">
         <v>3.1600000000000003E-2</v>
       </c>
-      <c r="U41" s="63">
+      <c r="U41" s="62">
         <v>3.1099999999999999E-2</v>
       </c>
-      <c r="V41" s="63">
+      <c r="V41" s="62">
         <v>3.5700000000000003E-2</v>
       </c>
-      <c r="W41" s="64">
+      <c r="W41" s="63">
         <v>3.32E-2</v>
       </c>
-      <c r="X41" s="134"/>
-      <c r="Y41" s="129"/>
-      <c r="Z41" s="129"/>
-      <c r="AA41" s="122" t="s">
+      <c r="X41" s="133"/>
+      <c r="Y41" s="128"/>
+      <c r="Z41" s="128"/>
+      <c r="AA41" s="121" t="s">
         <v>114</v>
       </c>
       <c r="AC41" s="12"/>
     </row>
     <row r="42" spans="1:29" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="141"/>
-      <c r="B42" s="89"/>
-      <c r="C42" s="90"/>
-      <c r="D42" s="88"/>
-      <c r="E42" s="106"/>
-      <c r="F42" s="106"/>
-      <c r="G42" s="106"/>
-      <c r="H42" s="109"/>
-      <c r="I42" s="106"/>
-      <c r="J42" s="125"/>
-      <c r="K42" s="23" t="s">
+      <c r="A42" s="140"/>
+      <c r="B42" s="88"/>
+      <c r="C42" s="89"/>
+      <c r="D42" s="87"/>
+      <c r="E42" s="105"/>
+      <c r="F42" s="105"/>
+      <c r="G42" s="105"/>
+      <c r="H42" s="108"/>
+      <c r="I42" s="105"/>
+      <c r="J42" s="124"/>
+      <c r="K42" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="L42" s="56">
+      <c r="L42" s="55">
         <v>9.1999999999999998E-3</v>
       </c>
-      <c r="M42" s="56">
+      <c r="M42" s="55">
         <v>1.5800000000000002E-2</v>
       </c>
-      <c r="N42" s="56">
+      <c r="N42" s="55">
         <v>1.7600000000000001E-2</v>
       </c>
-      <c r="O42" s="56">
+      <c r="O42" s="55">
         <v>1.5800000000000002E-2</v>
       </c>
-      <c r="P42" s="56">
+      <c r="P42" s="55">
         <v>8.6E-3</v>
       </c>
-      <c r="Q42" s="56">
+      <c r="Q42" s="55">
         <v>1.2699999999999999E-2</v>
       </c>
-      <c r="R42" s="56">
+      <c r="R42" s="55">
         <v>1.3299999999999999E-2</v>
       </c>
-      <c r="S42" s="56">
+      <c r="S42" s="55">
         <v>1.3899999999999999E-2</v>
       </c>
-      <c r="T42" s="56">
+      <c r="T42" s="55">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="U42" s="56"/>
-      <c r="V42" s="56"/>
-      <c r="W42" s="60"/>
-      <c r="X42" s="134"/>
-      <c r="Y42" s="129"/>
-      <c r="Z42" s="129"/>
-      <c r="AA42" s="124"/>
+      <c r="U42" s="55"/>
+      <c r="V42" s="55"/>
+      <c r="W42" s="59"/>
+      <c r="X42" s="133"/>
+      <c r="Y42" s="128"/>
+      <c r="Z42" s="128"/>
+      <c r="AA42" s="123"/>
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A43" s="142" t="s">
+      <c r="A43" s="141" t="s">
         <v>26</v>
       </c>
-      <c r="B43" s="89" t="s">
+      <c r="B43" s="88" t="s">
         <v>116</v>
       </c>
-      <c r="C43" s="90" t="s">
+      <c r="C43" s="89" t="s">
         <v>86</v>
       </c>
-      <c r="D43" s="88" t="s">
+      <c r="D43" s="87" t="s">
         <v>117</v>
       </c>
-      <c r="E43" s="106" t="s">
+      <c r="E43" s="105" t="s">
         <v>88</v>
       </c>
-      <c r="F43" s="106" t="s">
+      <c r="F43" s="105" t="s">
         <v>88</v>
       </c>
-      <c r="G43" s="106" t="s">
+      <c r="G43" s="105" t="s">
         <v>88</v>
       </c>
-      <c r="H43" s="109" t="s">
+      <c r="H43" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="I43" s="106" t="s">
+      <c r="I43" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="J43" s="118" t="s">
+      <c r="J43" s="117" t="s">
         <v>34</v>
       </c>
-      <c r="K43" s="23" t="s">
+      <c r="K43" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L43" s="36"/>
-      <c r="M43" s="36"/>
-      <c r="N43" s="38">
+      <c r="L43" s="35"/>
+      <c r="M43" s="35"/>
+      <c r="N43" s="37">
         <v>0.05</v>
       </c>
-      <c r="O43" s="36"/>
-      <c r="P43" s="36"/>
-      <c r="Q43" s="38">
+      <c r="O43" s="35"/>
+      <c r="P43" s="35"/>
+      <c r="Q43" s="37">
         <v>5.5E-2</v>
       </c>
-      <c r="R43" s="36"/>
-      <c r="S43" s="36"/>
-      <c r="T43" s="36"/>
-      <c r="U43" s="36"/>
-      <c r="V43" s="36"/>
-      <c r="W43" s="39"/>
-      <c r="X43" s="128" t="s">
+      <c r="R43" s="35"/>
+      <c r="S43" s="35"/>
+      <c r="T43" s="35"/>
+      <c r="U43" s="35"/>
+      <c r="V43" s="35"/>
+      <c r="W43" s="38"/>
+      <c r="X43" s="127" t="s">
         <v>118</v>
       </c>
-      <c r="Y43" s="130" t="s">
+      <c r="Y43" s="129" t="s">
         <v>119</v>
       </c>
-      <c r="Z43" s="131"/>
-      <c r="AA43" s="132" t="s">
+      <c r="Z43" s="130"/>
+      <c r="AA43" s="131" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="44" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A44" s="142"/>
-      <c r="B44" s="89"/>
-      <c r="C44" s="90"/>
-      <c r="D44" s="88"/>
-      <c r="E44" s="106"/>
-      <c r="F44" s="106"/>
-      <c r="G44" s="106"/>
-      <c r="H44" s="109"/>
-      <c r="I44" s="156"/>
-      <c r="J44" s="118"/>
-      <c r="K44" s="23" t="s">
+      <c r="A44" s="141"/>
+      <c r="B44" s="88"/>
+      <c r="C44" s="89"/>
+      <c r="D44" s="87"/>
+      <c r="E44" s="105"/>
+      <c r="F44" s="105"/>
+      <c r="G44" s="105"/>
+      <c r="H44" s="108"/>
+      <c r="I44" s="155"/>
+      <c r="J44" s="117"/>
+      <c r="K44" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="L44" s="22" t="s">
+      <c r="L44" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="M44" s="22" t="s">
+      <c r="M44" s="21" t="s">
         <v>89</v>
       </c>
       <c r="N44" s="17">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="O44" s="22" t="s">
+      <c r="O44" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="P44" s="22" t="s">
+      <c r="P44" s="21" t="s">
         <v>89</v>
       </c>
       <c r="Q44" s="17">
         <v>0.04</v>
       </c>
-      <c r="R44" s="22" t="s">
+      <c r="R44" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="S44" s="22" t="s">
+      <c r="S44" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="T44" s="56"/>
-      <c r="U44" s="22" t="s">
+      <c r="T44" s="55"/>
+      <c r="U44" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="V44" s="22" t="s">
+      <c r="V44" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="W44" s="56"/>
-      <c r="X44" s="128"/>
-      <c r="Y44" s="130"/>
-      <c r="Z44" s="131"/>
-      <c r="AA44" s="132"/>
+      <c r="W44" s="55"/>
+      <c r="X44" s="127"/>
+      <c r="Y44" s="129"/>
+      <c r="Z44" s="130"/>
+      <c r="AA44" s="131"/>
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A45" s="142"/>
-      <c r="B45" s="89" t="s">
+      <c r="A45" s="141"/>
+      <c r="B45" s="88" t="s">
         <v>121</v>
       </c>
-      <c r="C45" s="90" t="s">
+      <c r="C45" s="89" t="s">
         <v>86</v>
       </c>
-      <c r="D45" s="88" t="s">
+      <c r="D45" s="87" t="s">
         <v>122</v>
       </c>
-      <c r="E45" s="106" t="s">
+      <c r="E45" s="105" t="s">
         <v>88</v>
       </c>
-      <c r="F45" s="106" t="s">
+      <c r="F45" s="105" t="s">
         <v>88</v>
       </c>
-      <c r="G45" s="106" t="s">
+      <c r="G45" s="105" t="s">
         <v>88</v>
       </c>
-      <c r="H45" s="109" t="s">
+      <c r="H45" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="I45" s="106" t="s">
+      <c r="I45" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="J45" s="125" t="s">
+      <c r="J45" s="124" t="s">
         <v>52</v>
       </c>
-      <c r="K45" s="23" t="s">
+      <c r="K45" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L45" s="36">
+      <c r="L45" s="35">
         <v>0.4</v>
       </c>
-      <c r="M45" s="36">
+      <c r="M45" s="35">
         <v>0.4</v>
       </c>
-      <c r="N45" s="36">
+      <c r="N45" s="35">
         <v>0.4</v>
       </c>
-      <c r="O45" s="36">
+      <c r="O45" s="35">
         <v>0.4</v>
       </c>
-      <c r="P45" s="36">
+      <c r="P45" s="35">
         <v>0.4</v>
       </c>
-      <c r="Q45" s="36">
+      <c r="Q45" s="35">
         <v>0.4</v>
       </c>
-      <c r="R45" s="36">
+      <c r="R45" s="35">
         <v>0.4</v>
       </c>
-      <c r="S45" s="36">
+      <c r="S45" s="35">
         <v>0.4</v>
       </c>
-      <c r="T45" s="36">
+      <c r="T45" s="35">
         <v>0.4</v>
       </c>
-      <c r="U45" s="36"/>
-      <c r="V45" s="36"/>
-      <c r="W45" s="39"/>
-      <c r="X45" s="128"/>
-      <c r="Y45" s="130" t="s">
+      <c r="U45" s="35"/>
+      <c r="V45" s="35"/>
+      <c r="W45" s="38"/>
+      <c r="X45" s="127"/>
+      <c r="Y45" s="129" t="s">
         <v>123</v>
       </c>
-      <c r="Z45" s="133">
+      <c r="Z45" s="132">
         <v>46188</v>
       </c>
-      <c r="AA45" s="124" t="s">
+      <c r="AA45" s="123" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="46" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="142"/>
-      <c r="B46" s="89"/>
-      <c r="C46" s="90"/>
-      <c r="D46" s="88"/>
-      <c r="E46" s="106"/>
-      <c r="F46" s="106"/>
-      <c r="G46" s="106"/>
-      <c r="H46" s="109"/>
-      <c r="I46" s="106"/>
-      <c r="J46" s="125"/>
-      <c r="K46" s="23" t="s">
+      <c r="A46" s="141"/>
+      <c r="B46" s="88"/>
+      <c r="C46" s="89"/>
+      <c r="D46" s="87"/>
+      <c r="E46" s="105"/>
+      <c r="F46" s="105"/>
+      <c r="G46" s="105"/>
+      <c r="H46" s="108"/>
+      <c r="I46" s="105"/>
+      <c r="J46" s="124"/>
+      <c r="K46" s="22" t="s">
         <v>55</v>
       </c>
       <c r="L46" s="19">
@@ -12050,99 +12050,99 @@
       </c>
       <c r="U46" s="19"/>
       <c r="V46" s="19"/>
-      <c r="W46" s="29"/>
-      <c r="X46" s="128"/>
-      <c r="Y46" s="131"/>
-      <c r="Z46" s="131"/>
-      <c r="AA46" s="124"/>
+      <c r="W46" s="28"/>
+      <c r="X46" s="127"/>
+      <c r="Y46" s="130"/>
+      <c r="Z46" s="130"/>
+      <c r="AA46" s="123"/>
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A47" s="142"/>
-      <c r="B47" s="89" t="s">
+      <c r="A47" s="141"/>
+      <c r="B47" s="88" t="s">
         <v>124</v>
       </c>
-      <c r="C47" s="90" t="s">
+      <c r="C47" s="89" t="s">
         <v>83</v>
       </c>
-      <c r="D47" s="88" t="s">
+      <c r="D47" s="87" t="s">
         <v>125</v>
       </c>
-      <c r="E47" s="106" t="s">
+      <c r="E47" s="105" t="s">
         <v>88</v>
       </c>
-      <c r="F47" s="106" t="s">
+      <c r="F47" s="105" t="s">
         <v>88</v>
       </c>
-      <c r="G47" s="106" t="s">
+      <c r="G47" s="105" t="s">
         <v>88</v>
       </c>
-      <c r="H47" s="109" t="s">
+      <c r="H47" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="I47" s="106" t="s">
+      <c r="I47" s="105" t="s">
         <v>78</v>
       </c>
-      <c r="J47" s="125" t="s">
+      <c r="J47" s="124" t="s">
         <v>52</v>
       </c>
-      <c r="K47" s="23" t="s">
+      <c r="K47" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L47" s="37">
+      <c r="L47" s="36">
         <v>5.5</v>
       </c>
-      <c r="M47" s="37">
+      <c r="M47" s="36">
         <v>11</v>
       </c>
-      <c r="N47" s="37">
+      <c r="N47" s="36">
         <v>16.5</v>
       </c>
-      <c r="O47" s="37">
+      <c r="O47" s="36">
         <v>22</v>
       </c>
-      <c r="P47" s="37">
+      <c r="P47" s="36">
         <v>27.5</v>
       </c>
-      <c r="Q47" s="37">
+      <c r="Q47" s="36">
         <v>33</v>
       </c>
-      <c r="R47" s="37">
+      <c r="R47" s="36">
         <v>38.5</v>
       </c>
-      <c r="S47" s="37">
+      <c r="S47" s="36">
         <v>44</v>
       </c>
-      <c r="T47" s="37">
+      <c r="T47" s="36">
         <v>49.5</v>
       </c>
-      <c r="U47" s="37">
+      <c r="U47" s="36">
         <v>55</v>
       </c>
-      <c r="V47" s="37">
+      <c r="V47" s="36">
         <v>60.5</v>
       </c>
-      <c r="W47" s="40">
+      <c r="W47" s="39">
         <v>67</v>
       </c>
-      <c r="X47" s="128"/>
-      <c r="Y47" s="131"/>
-      <c r="Z47" s="131"/>
-      <c r="AA47" s="88" t="s">
+      <c r="X47" s="127"/>
+      <c r="Y47" s="130"/>
+      <c r="Z47" s="130"/>
+      <c r="AA47" s="87" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="48" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="142"/>
-      <c r="B48" s="89"/>
-      <c r="C48" s="90"/>
-      <c r="D48" s="88"/>
-      <c r="E48" s="106"/>
-      <c r="F48" s="106"/>
-      <c r="G48" s="106"/>
-      <c r="H48" s="109"/>
-      <c r="I48" s="106"/>
-      <c r="J48" s="125"/>
-      <c r="K48" s="23" t="s">
+      <c r="A48" s="141"/>
+      <c r="B48" s="88"/>
+      <c r="C48" s="89"/>
+      <c r="D48" s="87"/>
+      <c r="E48" s="105"/>
+      <c r="F48" s="105"/>
+      <c r="G48" s="105"/>
+      <c r="H48" s="108"/>
+      <c r="I48" s="105"/>
+      <c r="J48" s="124"/>
+      <c r="K48" s="22" t="s">
         <v>55</v>
       </c>
       <c r="L48" s="9">
@@ -12175,101 +12175,101 @@
       </c>
       <c r="U48" s="9"/>
       <c r="V48" s="9"/>
-      <c r="W48" s="27"/>
-      <c r="X48" s="128"/>
-      <c r="Y48" s="131"/>
-      <c r="Z48" s="131"/>
-      <c r="AA48" s="88"/>
+      <c r="W48" s="26"/>
+      <c r="X48" s="127"/>
+      <c r="Y48" s="130"/>
+      <c r="Z48" s="130"/>
+      <c r="AA48" s="87"/>
     </row>
     <row r="49" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A49" s="141" t="s">
+      <c r="A49" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B49" s="148" t="s">
+      <c r="B49" s="147" t="s">
         <v>128</v>
       </c>
-      <c r="C49" s="90" t="s">
+      <c r="C49" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="D49" s="88" t="s">
+      <c r="D49" s="87" t="s">
         <v>129</v>
       </c>
-      <c r="E49" s="106">
+      <c r="E49" s="105">
         <v>74</v>
       </c>
-      <c r="F49" s="106" t="s">
+      <c r="F49" s="105" t="s">
         <v>88</v>
       </c>
-      <c r="G49" s="106" t="s">
+      <c r="G49" s="105" t="s">
         <v>88</v>
       </c>
-      <c r="H49" s="109" t="s">
+      <c r="H49" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="I49" s="106" t="s">
+      <c r="I49" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="J49" s="105" t="s">
+      <c r="J49" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="K49" s="23" t="s">
+      <c r="K49" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L49" s="38">
+      <c r="L49" s="37">
         <v>0.73199999999999998</v>
       </c>
-      <c r="M49" s="38">
+      <c r="M49" s="37">
         <v>0.72749999999999992</v>
       </c>
-      <c r="N49" s="38">
+      <c r="N49" s="37">
         <v>0.7287499999999999</v>
       </c>
-      <c r="O49" s="38">
+      <c r="O49" s="37">
         <v>0.72999999999999987</v>
       </c>
-      <c r="P49" s="38">
+      <c r="P49" s="37">
         <v>0.73124999999999984</v>
       </c>
-      <c r="Q49" s="38">
+      <c r="Q49" s="37">
         <v>0.73249999999999982</v>
       </c>
-      <c r="R49" s="38">
+      <c r="R49" s="37">
         <v>0.73374999999999979</v>
       </c>
-      <c r="S49" s="38">
+      <c r="S49" s="37">
         <v>0.73499999999999976</v>
       </c>
-      <c r="T49" s="38">
+      <c r="T49" s="37">
         <v>0.73624999999999974</v>
       </c>
-      <c r="U49" s="38">
+      <c r="U49" s="37">
         <v>0.73749999999999971</v>
       </c>
-      <c r="V49" s="38">
+      <c r="V49" s="37">
         <v>0.73874999999999968</v>
       </c>
-      <c r="W49" s="41">
+      <c r="W49" s="40">
         <v>0.73999999999999966</v>
       </c>
-      <c r="X49" s="128"/>
-      <c r="Y49" s="130"/>
-      <c r="Z49" s="131"/>
-      <c r="AA49" s="124" t="s">
+      <c r="X49" s="127"/>
+      <c r="Y49" s="129"/>
+      <c r="Z49" s="130"/>
+      <c r="AA49" s="123" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="50" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A50" s="141"/>
-      <c r="B50" s="148"/>
-      <c r="C50" s="90"/>
-      <c r="D50" s="88"/>
-      <c r="E50" s="106"/>
-      <c r="F50" s="106"/>
-      <c r="G50" s="106"/>
-      <c r="H50" s="109"/>
-      <c r="I50" s="106"/>
-      <c r="J50" s="105"/>
-      <c r="K50" s="23" t="s">
+      <c r="A50" s="140"/>
+      <c r="B50" s="147"/>
+      <c r="C50" s="89"/>
+      <c r="D50" s="87"/>
+      <c r="E50" s="105"/>
+      <c r="F50" s="105"/>
+      <c r="G50" s="105"/>
+      <c r="H50" s="108"/>
+      <c r="I50" s="105"/>
+      <c r="J50" s="104"/>
+      <c r="K50" s="22" t="s">
         <v>55</v>
       </c>
       <c r="L50" s="17">
@@ -12301,95 +12301,95 @@
       </c>
       <c r="U50" s="17"/>
       <c r="V50" s="17"/>
-      <c r="W50" s="75"/>
-      <c r="X50" s="128"/>
-      <c r="Y50" s="130"/>
-      <c r="Z50" s="131"/>
-      <c r="AA50" s="124"/>
+      <c r="W50" s="74"/>
+      <c r="X50" s="127"/>
+      <c r="Y50" s="129"/>
+      <c r="Z50" s="130"/>
+      <c r="AA50" s="123"/>
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A51" s="142" t="s">
+      <c r="A51" s="141" t="s">
         <v>25</v>
       </c>
-      <c r="B51" s="89" t="s">
+      <c r="B51" s="88" t="s">
         <v>131</v>
       </c>
-      <c r="C51" s="90" t="s">
+      <c r="C51" s="89" t="s">
         <v>72</v>
       </c>
-      <c r="D51" s="88" t="s">
+      <c r="D51" s="87" t="s">
         <v>132</v>
       </c>
-      <c r="E51" s="106">
+      <c r="E51" s="105">
         <v>33.1</v>
       </c>
-      <c r="F51" s="106" t="s">
+      <c r="F51" s="105" t="s">
         <v>88</v>
       </c>
-      <c r="G51" s="106" t="s">
+      <c r="G51" s="105" t="s">
         <v>88</v>
       </c>
-      <c r="H51" s="109" t="s">
+      <c r="H51" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="I51" s="106" t="s">
+      <c r="I51" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="J51" s="105" t="s">
+      <c r="J51" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="K51" s="23" t="s">
+      <c r="K51" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L51" s="38">
+      <c r="L51" s="37">
         <v>0.34700072985878605</v>
       </c>
-      <c r="M51" s="38">
+      <c r="M51" s="37">
         <v>0.32854527661902383</v>
       </c>
-      <c r="N51" s="38">
+      <c r="N51" s="37">
         <v>0.30191652751587683</v>
       </c>
-      <c r="O51" s="38">
+      <c r="O51" s="37">
         <v>0.32233175889748933</v>
       </c>
-      <c r="P51" s="38">
+      <c r="P51" s="37">
         <v>0.32732965712929335</v>
       </c>
-      <c r="Q51" s="38">
+      <c r="Q51" s="37">
         <v>0.31564073493651035</v>
       </c>
-      <c r="R51" s="38">
+      <c r="R51" s="37">
         <v>0.33096935042775388</v>
       </c>
-      <c r="S51" s="38">
+      <c r="S51" s="37">
         <v>0.33943248102419393</v>
       </c>
-      <c r="T51" s="38">
+      <c r="T51" s="37">
         <v>0.33082830926903184</v>
       </c>
-      <c r="U51" s="36"/>
-      <c r="V51" s="36"/>
-      <c r="W51" s="39"/>
-      <c r="X51" s="128"/>
-      <c r="Y51" s="131"/>
-      <c r="Z51" s="131"/>
-      <c r="AA51" s="91" t="s">
+      <c r="U51" s="35"/>
+      <c r="V51" s="35"/>
+      <c r="W51" s="38"/>
+      <c r="X51" s="127"/>
+      <c r="Y51" s="130"/>
+      <c r="Z51" s="130"/>
+      <c r="AA51" s="90" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="52" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="142"/>
-      <c r="B52" s="89"/>
-      <c r="C52" s="90"/>
-      <c r="D52" s="88"/>
-      <c r="E52" s="106"/>
-      <c r="F52" s="106"/>
-      <c r="G52" s="106"/>
-      <c r="H52" s="109"/>
-      <c r="I52" s="106"/>
-      <c r="J52" s="105"/>
-      <c r="K52" s="23" t="s">
+      <c r="A52" s="141"/>
+      <c r="B52" s="88"/>
+      <c r="C52" s="89"/>
+      <c r="D52" s="87"/>
+      <c r="E52" s="105"/>
+      <c r="F52" s="105"/>
+      <c r="G52" s="105"/>
+      <c r="H52" s="108"/>
+      <c r="I52" s="105"/>
+      <c r="J52" s="104"/>
+      <c r="K52" s="22" t="s">
         <v>55</v>
       </c>
       <c r="L52" s="17">
@@ -12407,25 +12407,25 @@
       <c r="P52" s="17">
         <v>0.40747704161607318</v>
       </c>
-      <c r="Q52" s="78">
+      <c r="Q52" s="77">
         <v>0.36849551470072495</v>
       </c>
-      <c r="R52" s="78">
+      <c r="R52" s="77">
         <v>0.35573521911109235</v>
       </c>
-      <c r="S52" s="78">
+      <c r="S52" s="77">
         <v>0.36691053201149237</v>
       </c>
-      <c r="T52" s="78">
+      <c r="T52" s="77">
         <v>0.36899999999999999</v>
       </c>
-      <c r="U52" s="30"/>
-      <c r="V52" s="30"/>
-      <c r="W52" s="31"/>
-      <c r="X52" s="128"/>
-      <c r="Y52" s="131"/>
-      <c r="Z52" s="131"/>
-      <c r="AA52" s="91"/>
+      <c r="U52" s="29"/>
+      <c r="V52" s="29"/>
+      <c r="W52" s="30"/>
+      <c r="X52" s="127"/>
+      <c r="Y52" s="130"/>
+      <c r="Z52" s="130"/>
+      <c r="AA52" s="90"/>
     </row>
     <row r="54" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="56" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -13215,7 +13215,7 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57B1DF09-E217-42CF-A426-07EED8851D07}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9ED71D40-7C0E-49D3-AC03-5381A9E7DC24}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -13215,7 +13215,7 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9ED71D40-7C0E-49D3-AC03-5381A9E7DC24}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AEEF6728-DD64-4985-9AAC-D753ED42B82F}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/GlobalMoSMT-2023/Shared Documents/General/2026/Goals Alignment 2026/Strategic Execution 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3308" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76C102A4-A0DE-48BA-9DAF-0B4AD92B8CB0}"/>
+  <xr:revisionPtr revIDLastSave="3310" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B9C3698-7C23-4896-8953-ED430E711542}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="1030" windowWidth="9600" windowHeight="5450" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
   </bookViews>
   <sheets>
     <sheet name="Mastersheet" sheetId="5" r:id="rId1"/>
@@ -366,7 +366,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="142">
   <si>
     <t>Strategic Imperatives</t>
   </si>
@@ -543,11 +543,6 @@
   </si>
   <si>
     <t>CAPA investigations ≤ 90 days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-The CAPA we are finishing in July. 
-</t>
   </si>
   <si>
     <t>CAPA investigations KPI</t>
@@ -826,11 +821,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="5">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="mmm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="mmm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -1318,7 +1313,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1329,14 +1324,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1366,7 +1361,7 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="8" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1426,7 +1421,7 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="8" fillId="7" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1435,13 +1430,13 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="7" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="7" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1462,13 +1457,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="15" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="15" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="16" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="16" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="9" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1505,21 +1500,21 @@
     <xf numFmtId="10" fontId="8" fillId="7" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="7" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="7" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="9" fillId="17" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1528,28 +1523,28 @@
     <xf numFmtId="10" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="7" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="7" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="7" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="7" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1558,32 +1553,245 @@
     <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1597,220 +1805,7 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1860,35 +1855,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1909,35 +1876,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2000,6 +1939,83 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFDA9694"/>
         </patternFill>
       </fill>
@@ -2022,6 +2038,111 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2070,20 +2191,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
@@ -2092,118 +2199,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2232,6 +2227,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2281,13 +2283,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4630,10 +4625,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BD41CE00-E924-4733-B76A-3C4E09FA89B8}" name="Customer_Focus" displayName="Customer_Focus" ref="A14:V20" totalsRowShown="0">
   <autoFilter ref="A14:V20" xr:uid="{BD41CE00-E924-4733-B76A-3C4E09FA89B8}"/>
@@ -9574,10 +9565,10 @@
       <c r="I2" s="6"/>
     </row>
     <row r="3" spans="1:27" s="5" customFormat="1" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="107" t="s">
+      <c r="A3" s="162" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="107"/>
+      <c r="B3" s="162"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -9594,40 +9585,40 @@
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
       <c r="V3" s="2"/>
-      <c r="X3" s="171"/>
+      <c r="X3" s="89"/>
       <c r="AA3" s="14"/>
     </row>
     <row r="4" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="109" t="str">
+      <c r="A4" s="163" t="str">
         <f ca="1">"Current Month-Year " &amp; ":" &amp; TEXT(TODAY(),"YYYY-MM")</f>
         <v>Current Month-Year :2026-10</v>
       </c>
-      <c r="B4" s="109"/>
-      <c r="C4" s="109"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="109"/>
-      <c r="L4" s="109"/>
-      <c r="M4" s="109"/>
-      <c r="N4" s="109"/>
-      <c r="O4" s="109"/>
-      <c r="P4" s="109"/>
-      <c r="Q4" s="109"/>
-      <c r="R4" s="109"/>
-      <c r="S4" s="109"/>
-      <c r="T4" s="109"/>
-      <c r="U4" s="109"/>
-      <c r="V4" s="109"/>
-      <c r="W4" s="109"/>
-      <c r="X4" s="109"/>
-      <c r="Y4" s="109"/>
-      <c r="Z4" s="109"/>
-      <c r="AA4" s="109"/>
+      <c r="B4" s="163"/>
+      <c r="C4" s="163"/>
+      <c r="D4" s="163"/>
+      <c r="E4" s="163"/>
+      <c r="F4" s="163"/>
+      <c r="G4" s="163"/>
+      <c r="H4" s="163"/>
+      <c r="I4" s="163"/>
+      <c r="J4" s="163"/>
+      <c r="K4" s="163"/>
+      <c r="L4" s="163"/>
+      <c r="M4" s="163"/>
+      <c r="N4" s="163"/>
+      <c r="O4" s="163"/>
+      <c r="P4" s="163"/>
+      <c r="Q4" s="163"/>
+      <c r="R4" s="163"/>
+      <c r="S4" s="163"/>
+      <c r="T4" s="163"/>
+      <c r="U4" s="163"/>
+      <c r="V4" s="163"/>
+      <c r="W4" s="163"/>
+      <c r="X4" s="163"/>
+      <c r="Y4" s="163"/>
+      <c r="Z4" s="163"/>
+      <c r="AA4" s="163"/>
     </row>
     <row r="5" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="85" t="s">
@@ -9642,11 +9633,11 @@
       <c r="D5" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="113" t="s">
+      <c r="E5" s="164" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
+      <c r="F5" s="164"/>
+      <c r="G5" s="164"/>
       <c r="H5" s="86" t="s">
         <v>8</v>
       </c>
@@ -9709,30 +9700,30 @@
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A6" s="106" t="s">
+      <c r="A6" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="88" t="s">
+      <c r="B6" s="125" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="89" t="s">
+      <c r="C6" s="137" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="87" t="s">
+      <c r="D6" s="105" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="105">
+      <c r="E6" s="104">
         <v>10</v>
       </c>
-      <c r="F6" s="105"/>
-      <c r="G6" s="105"/>
-      <c r="H6" s="108" t="s">
+      <c r="F6" s="104"/>
+      <c r="G6" s="104"/>
+      <c r="H6" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="105" t="s">
+      <c r="I6" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="104" t="s">
+      <c r="J6" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K6" s="22" t="s">
@@ -9774,24 +9765,24 @@
       <c r="W6" s="27">
         <v>0.05</v>
       </c>
-      <c r="X6" s="103"/>
-      <c r="Y6" s="110"/>
-      <c r="Z6" s="110"/>
-      <c r="AA6" s="120" t="s">
+      <c r="X6" s="110"/>
+      <c r="Y6" s="101"/>
+      <c r="Z6" s="101"/>
+      <c r="AA6" s="117" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A7" s="106"/>
-      <c r="B7" s="88"/>
-      <c r="C7" s="89"/>
-      <c r="D7" s="87"/>
-      <c r="E7" s="105"/>
-      <c r="F7" s="105"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="108"/>
-      <c r="I7" s="105"/>
-      <c r="J7" s="104"/>
+      <c r="A7" s="92"/>
+      <c r="B7" s="125"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="106"/>
       <c r="K7" s="22" t="s">
         <v>55</v>
       </c>
@@ -9825,34 +9816,34 @@
       <c r="U7" s="50"/>
       <c r="V7" s="50"/>
       <c r="W7" s="50"/>
-      <c r="X7" s="91"/>
-      <c r="Y7" s="93"/>
-      <c r="Z7" s="93"/>
-      <c r="AA7" s="121"/>
+      <c r="X7" s="111"/>
+      <c r="Y7" s="131"/>
+      <c r="Z7" s="131"/>
+      <c r="AA7" s="118"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A8" s="106"/>
-      <c r="B8" s="88" t="s">
+      <c r="A8" s="92"/>
+      <c r="B8" s="125" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="89" t="s">
+      <c r="C8" s="137" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="87" t="s">
+      <c r="D8" s="105" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="105">
+      <c r="E8" s="104">
         <v>90</v>
       </c>
-      <c r="F8" s="105"/>
-      <c r="G8" s="105"/>
-      <c r="H8" s="108" t="s">
+      <c r="F8" s="104"/>
+      <c r="G8" s="104"/>
+      <c r="H8" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="105" t="s">
+      <c r="I8" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="104" t="s">
+      <c r="J8" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K8" s="22" t="s">
@@ -9884,28 +9875,24 @@
       <c r="U8" s="18"/>
       <c r="V8" s="18"/>
       <c r="W8" s="27"/>
-      <c r="X8" s="91"/>
-      <c r="Y8" s="92" t="s">
+      <c r="X8" s="111"/>
+      <c r="Y8" s="130"/>
+      <c r="Z8" s="115"/>
+      <c r="AA8" s="117" t="s">
         <v>58</v>
-      </c>
-      <c r="Z8" s="111">
-        <v>46231</v>
-      </c>
-      <c r="AA8" s="120" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A9" s="106"/>
-      <c r="B9" s="88"/>
-      <c r="C9" s="89"/>
-      <c r="D9" s="87"/>
-      <c r="E9" s="105"/>
-      <c r="F9" s="105"/>
-      <c r="G9" s="105"/>
-      <c r="H9" s="108"/>
-      <c r="I9" s="105"/>
-      <c r="J9" s="104"/>
+      <c r="A9" s="92"/>
+      <c r="B9" s="125"/>
+      <c r="C9" s="137"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="104"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="103"/>
+      <c r="I9" s="104"/>
+      <c r="J9" s="106"/>
       <c r="K9" s="22" t="s">
         <v>55</v>
       </c>
@@ -9939,34 +9926,34 @@
       <c r="U9" s="52"/>
       <c r="V9" s="52"/>
       <c r="W9" s="52"/>
-      <c r="X9" s="91"/>
-      <c r="Y9" s="93"/>
-      <c r="Z9" s="112"/>
-      <c r="AA9" s="121"/>
+      <c r="X9" s="111"/>
+      <c r="Y9" s="131"/>
+      <c r="Z9" s="116"/>
+      <c r="AA9" s="118"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A10" s="106"/>
-      <c r="B10" s="88" t="s">
+      <c r="A10" s="92"/>
+      <c r="B10" s="125" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="137" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="105" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="89" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="87" t="s">
+      <c r="E10" s="104">
+        <v>1</v>
+      </c>
+      <c r="F10" s="104"/>
+      <c r="G10" s="104"/>
+      <c r="H10" s="103" t="s">
+        <v>51</v>
+      </c>
+      <c r="I10" s="104" t="s">
         <v>61</v>
       </c>
-      <c r="E10" s="105">
-        <v>1</v>
-      </c>
-      <c r="F10" s="105"/>
-      <c r="G10" s="105"/>
-      <c r="H10" s="108" t="s">
-        <v>51</v>
-      </c>
-      <c r="I10" s="105" t="s">
-        <v>62</v>
-      </c>
-      <c r="J10" s="104" t="s">
+      <c r="J10" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K10" s="22" t="s">
@@ -10000,24 +9987,24 @@
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
       <c r="W10" s="33"/>
-      <c r="X10" s="91"/>
-      <c r="Y10" s="160"/>
-      <c r="Z10" s="114"/>
-      <c r="AA10" s="120" t="s">
-        <v>63</v>
+      <c r="X10" s="111"/>
+      <c r="Y10" s="119"/>
+      <c r="Z10" s="165"/>
+      <c r="AA10" s="117" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="106"/>
-      <c r="B11" s="88"/>
-      <c r="C11" s="89"/>
-      <c r="D11" s="87"/>
-      <c r="E11" s="105"/>
-      <c r="F11" s="105"/>
-      <c r="G11" s="105"/>
-      <c r="H11" s="108"/>
-      <c r="I11" s="105"/>
-      <c r="J11" s="104"/>
+      <c r="A11" s="92"/>
+      <c r="B11" s="125"/>
+      <c r="C11" s="137"/>
+      <c r="D11" s="105"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="104"/>
+      <c r="H11" s="103"/>
+      <c r="I11" s="104"/>
+      <c r="J11" s="106"/>
       <c r="K11" s="22" t="s">
         <v>55</v>
       </c>
@@ -10051,36 +10038,36 @@
       <c r="U11" s="31"/>
       <c r="V11" s="31"/>
       <c r="W11" s="32"/>
-      <c r="X11" s="91"/>
-      <c r="Y11" s="161"/>
-      <c r="Z11" s="115"/>
-      <c r="AA11" s="121"/>
+      <c r="X11" s="111"/>
+      <c r="Y11" s="120"/>
+      <c r="Z11" s="166"/>
+      <c r="AA11" s="118"/>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A12" s="106" t="s">
+      <c r="A12" s="92" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="90" t="s">
+      <c r="B12" s="123" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="123" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="90" t="s">
+      <c r="D12" s="105" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="87" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12" s="105">
+      <c r="E12" s="104">
         <v>84</v>
       </c>
-      <c r="F12" s="105"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="108" t="s">
+      <c r="F12" s="104"/>
+      <c r="G12" s="104"/>
+      <c r="H12" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="105" t="s">
+      <c r="I12" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="104" t="s">
+      <c r="J12" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K12" s="22" t="s">
@@ -10122,24 +10109,24 @@
       <c r="W12" s="25">
         <v>0.79</v>
       </c>
-      <c r="X12" s="91"/>
-      <c r="Y12" s="92"/>
-      <c r="Z12" s="93"/>
-      <c r="AA12" s="120" t="s">
-        <v>67</v>
+      <c r="X12" s="111"/>
+      <c r="Y12" s="130"/>
+      <c r="Z12" s="131"/>
+      <c r="AA12" s="117" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A13" s="106"/>
-      <c r="B13" s="90"/>
-      <c r="C13" s="90"/>
-      <c r="D13" s="87"/>
-      <c r="E13" s="105"/>
-      <c r="F13" s="105"/>
-      <c r="G13" s="105"/>
-      <c r="H13" s="108"/>
-      <c r="I13" s="105"/>
-      <c r="J13" s="104"/>
+      <c r="A13" s="92"/>
+      <c r="B13" s="123"/>
+      <c r="C13" s="123"/>
+      <c r="D13" s="105"/>
+      <c r="E13" s="104"/>
+      <c r="F13" s="104"/>
+      <c r="G13" s="104"/>
+      <c r="H13" s="103"/>
+      <c r="I13" s="104"/>
+      <c r="J13" s="106"/>
       <c r="K13" s="22" t="s">
         <v>55</v>
       </c>
@@ -10173,34 +10160,34 @@
       <c r="U13" s="19"/>
       <c r="V13" s="19"/>
       <c r="W13" s="28"/>
-      <c r="X13" s="91"/>
-      <c r="Y13" s="93"/>
-      <c r="Z13" s="93"/>
-      <c r="AA13" s="121"/>
+      <c r="X13" s="111"/>
+      <c r="Y13" s="131"/>
+      <c r="Z13" s="131"/>
+      <c r="AA13" s="118"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A14" s="106"/>
-      <c r="B14" s="90" t="s">
+      <c r="A14" s="92"/>
+      <c r="B14" s="123" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="119" t="s">
+      <c r="D14" s="105" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="87" t="s">
-        <v>70</v>
-      </c>
-      <c r="E14" s="105">
+      <c r="E14" s="104">
         <v>54.6</v>
       </c>
-      <c r="F14" s="105"/>
-      <c r="G14" s="105"/>
-      <c r="H14" s="108" t="s">
+      <c r="F14" s="104"/>
+      <c r="G14" s="104"/>
+      <c r="H14" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="105" t="s">
+      <c r="I14" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J14" s="104" t="s">
+      <c r="J14" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K14" s="22" t="s">
@@ -10236,26 +10223,26 @@
       <c r="U14" s="37"/>
       <c r="V14" s="37"/>
       <c r="W14" s="37"/>
-      <c r="X14" s="170" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y14" s="94" t="s">
+      <c r="X14" s="129" t="s">
         <v>141</v>
       </c>
-      <c r="Z14" s="149"/>
-      <c r="AA14" s="148"/>
+      <c r="Y14" s="96" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z14" s="100"/>
+      <c r="AA14" s="127"/>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="106"/>
-      <c r="B15" s="90"/>
-      <c r="C15" s="119"/>
-      <c r="D15" s="87"/>
-      <c r="E15" s="105"/>
-      <c r="F15" s="105"/>
-      <c r="G15" s="105"/>
-      <c r="H15" s="108"/>
-      <c r="I15" s="105"/>
-      <c r="J15" s="104"/>
+      <c r="A15" s="92"/>
+      <c r="B15" s="123"/>
+      <c r="C15" s="124"/>
+      <c r="D15" s="105"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="104"/>
+      <c r="G15" s="104"/>
+      <c r="H15" s="103"/>
+      <c r="I15" s="104"/>
+      <c r="J15" s="106"/>
       <c r="K15" s="22" t="s">
         <v>55</v>
       </c>
@@ -10289,36 +10276,36 @@
       <c r="U15" s="31"/>
       <c r="V15" s="31"/>
       <c r="W15" s="32"/>
-      <c r="X15" s="91"/>
-      <c r="Y15" s="110"/>
-      <c r="Z15" s="110"/>
+      <c r="X15" s="111"/>
+      <c r="Y15" s="101"/>
+      <c r="Z15" s="101"/>
       <c r="AA15" s="128"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A16" s="106" t="s">
+      <c r="A16" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="90" t="s">
+      <c r="B16" s="123" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="123" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="90" t="s">
+      <c r="D16" s="105" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="87" t="s">
+      <c r="E16" s="104" t="s">
         <v>73</v>
       </c>
-      <c r="E16" s="105" t="s">
-        <v>74</v>
-      </c>
-      <c r="F16" s="105"/>
-      <c r="G16" s="105"/>
-      <c r="H16" s="108" t="s">
+      <c r="F16" s="104"/>
+      <c r="G16" s="104"/>
+      <c r="H16" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I16" s="105" t="s">
+      <c r="I16" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="104" t="s">
+      <c r="J16" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K16" s="22" t="s">
@@ -10354,24 +10341,24 @@
       <c r="U16" s="24"/>
       <c r="V16" s="24"/>
       <c r="W16" s="25"/>
-      <c r="X16" s="91"/>
-      <c r="Y16" s="92"/>
-      <c r="Z16" s="112"/>
-      <c r="AA16" s="120" t="s">
-        <v>75</v>
+      <c r="X16" s="111"/>
+      <c r="Y16" s="130"/>
+      <c r="Z16" s="116"/>
+      <c r="AA16" s="117" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A17" s="106"/>
-      <c r="B17" s="90"/>
-      <c r="C17" s="90"/>
-      <c r="D17" s="87"/>
-      <c r="E17" s="105"/>
-      <c r="F17" s="105"/>
-      <c r="G17" s="105"/>
-      <c r="H17" s="108"/>
-      <c r="I17" s="105"/>
-      <c r="J17" s="104"/>
+      <c r="A17" s="92"/>
+      <c r="B17" s="123"/>
+      <c r="C17" s="123"/>
+      <c r="D17" s="105"/>
+      <c r="E17" s="104"/>
+      <c r="F17" s="104"/>
+      <c r="G17" s="104"/>
+      <c r="H17" s="103"/>
+      <c r="I17" s="104"/>
+      <c r="J17" s="106"/>
       <c r="K17" s="22" t="s">
         <v>55</v>
       </c>
@@ -10405,34 +10392,34 @@
       <c r="U17" s="19"/>
       <c r="V17" s="19"/>
       <c r="W17" s="28"/>
-      <c r="X17" s="91"/>
-      <c r="Y17" s="93"/>
-      <c r="Z17" s="112"/>
-      <c r="AA17" s="121"/>
+      <c r="X17" s="111"/>
+      <c r="Y17" s="131"/>
+      <c r="Z17" s="116"/>
+      <c r="AA17" s="118"/>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A18" s="106"/>
-      <c r="B18" s="90" t="s">
+      <c r="A18" s="92"/>
+      <c r="B18" s="123" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="123" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="123" t="s">
         <v>76</v>
       </c>
-      <c r="C18" s="90" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" s="90" t="s">
+      <c r="E18" s="104" t="s">
+        <v>73</v>
+      </c>
+      <c r="F18" s="104"/>
+      <c r="G18" s="104"/>
+      <c r="H18" s="103" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="E18" s="105" t="s">
-        <v>74</v>
-      </c>
-      <c r="F18" s="105"/>
-      <c r="G18" s="105"/>
-      <c r="H18" s="108" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="105" t="s">
-        <v>78</v>
-      </c>
-      <c r="J18" s="104" t="s">
+      <c r="J18" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K18" s="22" t="s">
@@ -10468,87 +10455,87 @@
       <c r="U18" s="47"/>
       <c r="V18" s="47"/>
       <c r="W18" s="47"/>
-      <c r="X18" s="154" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y18" s="154"/>
-      <c r="Z18" s="151">
+      <c r="X18" s="135" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y18" s="135"/>
+      <c r="Z18" s="132">
         <v>46108</v>
       </c>
-      <c r="AA18" s="153"/>
+      <c r="AA18" s="134"/>
     </row>
     <row r="19" spans="1:27" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="106"/>
-      <c r="B19" s="90"/>
-      <c r="C19" s="90"/>
-      <c r="D19" s="90"/>
-      <c r="E19" s="105"/>
-      <c r="F19" s="105"/>
-      <c r="G19" s="105"/>
-      <c r="H19" s="108"/>
-      <c r="I19" s="105"/>
-      <c r="J19" s="104"/>
+      <c r="A19" s="92"/>
+      <c r="B19" s="123"/>
+      <c r="C19" s="123"/>
+      <c r="D19" s="123"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="104"/>
+      <c r="G19" s="104"/>
+      <c r="H19" s="103"/>
+      <c r="I19" s="104"/>
+      <c r="J19" s="106"/>
       <c r="K19" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="L19" s="168">
+      <c r="L19" s="87">
         <v>0.2598381666666667</v>
       </c>
-      <c r="M19" s="168">
+      <c r="M19" s="87">
         <v>0.3838381666666667</v>
       </c>
-      <c r="N19" s="168">
+      <c r="N19" s="87">
         <v>1.1128381666666667</v>
       </c>
-      <c r="O19" s="168">
+      <c r="O19" s="87">
         <v>1.3223861666666668</v>
       </c>
-      <c r="P19" s="168">
+      <c r="P19" s="87">
         <v>1.6513861666666667</v>
       </c>
-      <c r="Q19" s="168">
+      <c r="Q19" s="87">
         <v>2.1303861666666668</v>
       </c>
-      <c r="R19" s="169">
+      <c r="R19" s="88">
         <v>2.6433861666666667</v>
       </c>
-      <c r="S19" s="169">
+      <c r="S19" s="88">
         <v>3.3972231666666666</v>
       </c>
-      <c r="T19" s="169">
+      <c r="T19" s="88">
         <v>4.5205241666666662</v>
       </c>
       <c r="U19" s="46"/>
       <c r="V19" s="46"/>
       <c r="W19" s="48"/>
-      <c r="X19" s="154"/>
-      <c r="Y19" s="154"/>
-      <c r="Z19" s="152"/>
-      <c r="AA19" s="153"/>
+      <c r="X19" s="135"/>
+      <c r="Y19" s="135"/>
+      <c r="Z19" s="133"/>
+      <c r="AA19" s="134"/>
     </row>
     <row r="20" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="106"/>
-      <c r="B20" s="90" t="s">
+      <c r="A20" s="92"/>
+      <c r="B20" s="123" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="123" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="105" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="90" t="s">
-        <v>65</v>
-      </c>
-      <c r="D20" s="87" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" s="105" t="s">
-        <v>74</v>
-      </c>
-      <c r="F20" s="105"/>
-      <c r="G20" s="105"/>
-      <c r="H20" s="108" t="s">
+      <c r="E20" s="104" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" s="104"/>
+      <c r="G20" s="104"/>
+      <c r="H20" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="I20" s="105" t="s">
+      <c r="I20" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="104" t="s">
+      <c r="J20" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K20" s="22" t="s">
@@ -10584,28 +10571,28 @@
       <c r="U20" s="18"/>
       <c r="V20" s="18"/>
       <c r="W20" s="27"/>
-      <c r="X20" s="96" t="s">
-        <v>140</v>
-      </c>
-      <c r="Y20" s="98" t="s">
+      <c r="X20" s="167" t="s">
         <v>139</v>
       </c>
-      <c r="Z20" s="150"/>
-      <c r="AA20" s="122" t="s">
-        <v>81</v>
+      <c r="Y20" s="169" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z20" s="95"/>
+      <c r="AA20" s="153" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="106"/>
-      <c r="B21" s="90"/>
-      <c r="C21" s="90"/>
-      <c r="D21" s="87"/>
-      <c r="E21" s="105"/>
-      <c r="F21" s="105"/>
-      <c r="G21" s="105"/>
-      <c r="H21" s="108"/>
-      <c r="I21" s="105"/>
-      <c r="J21" s="104"/>
+      <c r="A21" s="92"/>
+      <c r="B21" s="123"/>
+      <c r="C21" s="123"/>
+      <c r="D21" s="105"/>
+      <c r="E21" s="104"/>
+      <c r="F21" s="104"/>
+      <c r="G21" s="104"/>
+      <c r="H21" s="103"/>
+      <c r="I21" s="104"/>
+      <c r="J21" s="106"/>
       <c r="K21" s="22" t="s">
         <v>55</v>
       </c>
@@ -10639,36 +10626,36 @@
       <c r="U21" s="29"/>
       <c r="V21" s="29"/>
       <c r="W21" s="30"/>
-      <c r="X21" s="97"/>
-      <c r="Y21" s="99"/>
-      <c r="Z21" s="116"/>
-      <c r="AA21" s="122"/>
+      <c r="X21" s="168"/>
+      <c r="Y21" s="170"/>
+      <c r="Z21" s="94"/>
+      <c r="AA21" s="153"/>
     </row>
     <row r="22" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="106" t="s">
+      <c r="A22" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="90" t="s">
+      <c r="B22" s="123" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" s="124" t="s">
         <v>82</v>
       </c>
-      <c r="C22" s="119" t="s">
+      <c r="D22" s="123" t="s">
         <v>83</v>
       </c>
-      <c r="D22" s="90" t="s">
-        <v>84</v>
-      </c>
-      <c r="E22" s="105">
+      <c r="E22" s="104">
         <v>90</v>
       </c>
-      <c r="F22" s="105"/>
-      <c r="G22" s="105"/>
-      <c r="H22" s="108" t="s">
+      <c r="F22" s="104"/>
+      <c r="G22" s="104"/>
+      <c r="H22" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="105" t="s">
+      <c r="I22" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J22" s="104" t="s">
+      <c r="J22" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K22" s="22" t="s">
@@ -10710,24 +10697,24 @@
       <c r="W22" s="27">
         <v>0.9</v>
       </c>
-      <c r="X22" s="102"/>
-      <c r="Y22" s="92"/>
-      <c r="Z22" s="111">
+      <c r="X22" s="171"/>
+      <c r="Y22" s="130"/>
+      <c r="Z22" s="115">
         <v>46257</v>
       </c>
-      <c r="AA22" s="158"/>
+      <c r="AA22" s="113"/>
     </row>
     <row r="23" spans="1:27" ht="17.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="165"/>
-      <c r="B23" s="90"/>
-      <c r="C23" s="119"/>
-      <c r="D23" s="90"/>
-      <c r="E23" s="105"/>
-      <c r="F23" s="105"/>
-      <c r="G23" s="105"/>
-      <c r="H23" s="108"/>
-      <c r="I23" s="105"/>
-      <c r="J23" s="104"/>
+      <c r="A23" s="93"/>
+      <c r="B23" s="123"/>
+      <c r="C23" s="124"/>
+      <c r="D23" s="123"/>
+      <c r="E23" s="104"/>
+      <c r="F23" s="104"/>
+      <c r="G23" s="104"/>
+      <c r="H23" s="103"/>
+      <c r="I23" s="104"/>
+      <c r="J23" s="106"/>
       <c r="K23" s="22" t="s">
         <v>55</v>
       </c>
@@ -10761,40 +10748,40 @@
       <c r="U23" s="29"/>
       <c r="V23" s="29"/>
       <c r="W23" s="30"/>
-      <c r="X23" s="103"/>
-      <c r="Y23" s="93"/>
-      <c r="Z23" s="112"/>
-      <c r="AA23" s="159"/>
+      <c r="X23" s="110"/>
+      <c r="Y23" s="131"/>
+      <c r="Z23" s="116"/>
+      <c r="AA23" s="114"/>
     </row>
     <row r="24" spans="1:27" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="140" t="s">
+      <c r="A24" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="90" t="s">
+      <c r="B24" s="123" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="124" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="119" t="s">
+      <c r="D24" s="105" t="s">
         <v>86</v>
       </c>
-      <c r="D24" s="87" t="s">
+      <c r="E24" s="104" t="s">
         <v>87</v>
       </c>
-      <c r="E24" s="105" t="s">
-        <v>88</v>
-      </c>
-      <c r="F24" s="105" t="s">
-        <v>88</v>
-      </c>
-      <c r="G24" s="105" t="s">
-        <v>88</v>
-      </c>
-      <c r="H24" s="108" t="s">
+      <c r="F24" s="104" t="s">
+        <v>87</v>
+      </c>
+      <c r="G24" s="104" t="s">
+        <v>87</v>
+      </c>
+      <c r="H24" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="105" t="s">
+      <c r="I24" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J24" s="117" t="s">
+      <c r="J24" s="102" t="s">
         <v>34</v>
       </c>
       <c r="K24" s="22" t="s">
@@ -10806,109 +10793,109 @@
         <v>0.104</v>
       </c>
       <c r="O24" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P24" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q24" s="37">
         <v>0.11799999999999999</v>
       </c>
       <c r="R24" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S24" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="T24" s="35"/>
       <c r="U24" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="V24" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="W24" s="38"/>
+      <c r="X24" s="109"/>
+      <c r="Y24" s="100"/>
+      <c r="Z24" s="94"/>
+      <c r="AA24" s="117" t="s">
         <v>89</v>
-      </c>
-      <c r="V24" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="W24" s="38"/>
-      <c r="X24" s="134"/>
-      <c r="Y24" s="149"/>
-      <c r="Z24" s="116"/>
-      <c r="AA24" s="120" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="164"/>
-      <c r="B25" s="90"/>
-      <c r="C25" s="119"/>
-      <c r="D25" s="87"/>
-      <c r="E25" s="105"/>
-      <c r="F25" s="105"/>
-      <c r="G25" s="105"/>
-      <c r="H25" s="108"/>
-      <c r="I25" s="105"/>
-      <c r="J25" s="117"/>
+      <c r="A25" s="91"/>
+      <c r="B25" s="123"/>
+      <c r="C25" s="124"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="104"/>
+      <c r="F25" s="104"/>
+      <c r="G25" s="104"/>
+      <c r="H25" s="103"/>
+      <c r="I25" s="104"/>
+      <c r="J25" s="102"/>
       <c r="K25" s="22" t="s">
         <v>55</v>
       </c>
       <c r="L25" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M25" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N25" s="50">
         <v>0.115</v>
       </c>
       <c r="O25" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P25" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q25" s="17">
         <v>0.121</v>
       </c>
       <c r="R25" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S25" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="T25" s="55"/>
       <c r="U25" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="V25" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="W25" s="55"/>
-      <c r="X25" s="103"/>
-      <c r="Y25" s="110"/>
-      <c r="Z25" s="150"/>
-      <c r="AA25" s="121"/>
+      <c r="X25" s="110"/>
+      <c r="Y25" s="101"/>
+      <c r="Z25" s="95"/>
+      <c r="AA25" s="118"/>
     </row>
     <row r="26" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="164"/>
-      <c r="B26" s="88" t="s">
+      <c r="A26" s="91"/>
+      <c r="B26" s="125" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="126" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="105" t="s">
         <v>91</v>
       </c>
-      <c r="C26" s="157" t="s">
-        <v>86</v>
-      </c>
-      <c r="D26" s="87" t="s">
-        <v>92</v>
-      </c>
-      <c r="E26" s="105">
+      <c r="E26" s="104">
         <v>34</v>
       </c>
-      <c r="F26" s="155"/>
-      <c r="G26" s="155"/>
-      <c r="H26" s="108" t="s">
+      <c r="F26" s="112"/>
+      <c r="G26" s="112"/>
+      <c r="H26" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I26" s="105" t="s">
+      <c r="I26" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J26" s="104" t="s">
+      <c r="J26" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K26" s="22" t="s">
@@ -10944,24 +10931,24 @@
       <c r="U26" s="24"/>
       <c r="V26" s="24"/>
       <c r="W26" s="25"/>
-      <c r="X26" s="91"/>
-      <c r="Y26" s="93"/>
-      <c r="Z26" s="112"/>
-      <c r="AA26" s="120" t="s">
-        <v>93</v>
+      <c r="X26" s="111"/>
+      <c r="Y26" s="131"/>
+      <c r="Z26" s="116"/>
+      <c r="AA26" s="117" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="164"/>
-      <c r="B27" s="88"/>
-      <c r="C27" s="157"/>
-      <c r="D27" s="87"/>
-      <c r="E27" s="105"/>
-      <c r="F27" s="155"/>
-      <c r="G27" s="155"/>
-      <c r="H27" s="108"/>
-      <c r="I27" s="105"/>
-      <c r="J27" s="104"/>
+      <c r="A27" s="91"/>
+      <c r="B27" s="125"/>
+      <c r="C27" s="126"/>
+      <c r="D27" s="105"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="112"/>
+      <c r="H27" s="103"/>
+      <c r="I27" s="104"/>
+      <c r="J27" s="106"/>
       <c r="K27" s="22" t="s">
         <v>55</v>
       </c>
@@ -10995,34 +10982,34 @@
       <c r="U27" s="19"/>
       <c r="V27" s="19"/>
       <c r="W27" s="28"/>
-      <c r="X27" s="91"/>
-      <c r="Y27" s="93"/>
-      <c r="Z27" s="112"/>
-      <c r="AA27" s="121"/>
+      <c r="X27" s="111"/>
+      <c r="Y27" s="131"/>
+      <c r="Z27" s="116"/>
+      <c r="AA27" s="118"/>
     </row>
     <row r="28" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="164"/>
-      <c r="B28" s="87" t="s">
+      <c r="A28" s="91"/>
+      <c r="B28" s="105" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" s="123" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" s="105" t="s">
         <v>94</v>
       </c>
-      <c r="C28" s="90" t="s">
-        <v>72</v>
-      </c>
-      <c r="D28" s="87" t="s">
-        <v>95</v>
-      </c>
-      <c r="E28" s="105" t="s">
-        <v>74</v>
-      </c>
-      <c r="F28" s="105"/>
-      <c r="G28" s="105"/>
-      <c r="H28" s="108" t="s">
+      <c r="E28" s="104" t="s">
+        <v>73</v>
+      </c>
+      <c r="F28" s="104"/>
+      <c r="G28" s="104"/>
+      <c r="H28" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I28" s="105" t="s">
+      <c r="I28" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J28" s="104" t="s">
+      <c r="J28" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K28" s="22" t="s">
@@ -11058,26 +11045,26 @@
       <c r="U28" s="24"/>
       <c r="V28" s="24"/>
       <c r="W28" s="25"/>
-      <c r="X28" s="100" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y28" s="94"/>
-      <c r="Z28" s="116"/>
-      <c r="AA28" s="125" t="s">
-        <v>96</v>
+      <c r="X28" s="159" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y28" s="96"/>
+      <c r="Z28" s="94"/>
+      <c r="AA28" s="154" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="164"/>
-      <c r="B29" s="87"/>
-      <c r="C29" s="90"/>
-      <c r="D29" s="87"/>
-      <c r="E29" s="105"/>
-      <c r="F29" s="105"/>
-      <c r="G29" s="105"/>
-      <c r="H29" s="108"/>
-      <c r="I29" s="105"/>
-      <c r="J29" s="104"/>
+      <c r="A29" s="91"/>
+      <c r="B29" s="105"/>
+      <c r="C29" s="123"/>
+      <c r="D29" s="105"/>
+      <c r="E29" s="104"/>
+      <c r="F29" s="104"/>
+      <c r="G29" s="104"/>
+      <c r="H29" s="103"/>
+      <c r="I29" s="104"/>
+      <c r="J29" s="106"/>
       <c r="K29" s="22" t="s">
         <v>55</v>
       </c>
@@ -11111,32 +11098,32 @@
       <c r="U29" s="19"/>
       <c r="V29" s="19"/>
       <c r="W29" s="28"/>
-      <c r="X29" s="101"/>
-      <c r="Y29" s="95"/>
-      <c r="Z29" s="150"/>
-      <c r="AA29" s="126"/>
+      <c r="X29" s="160"/>
+      <c r="Y29" s="97"/>
+      <c r="Z29" s="95"/>
+      <c r="AA29" s="155"/>
     </row>
     <row r="30" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="164"/>
-      <c r="B30" s="87"/>
-      <c r="C30" s="90" t="s">
-        <v>72</v>
-      </c>
-      <c r="D30" s="87" t="s">
-        <v>97</v>
-      </c>
-      <c r="E30" s="105" t="s">
-        <v>74</v>
-      </c>
-      <c r="F30" s="105"/>
-      <c r="G30" s="105"/>
-      <c r="H30" s="108" t="s">
+      <c r="A30" s="91"/>
+      <c r="B30" s="105"/>
+      <c r="C30" s="123" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" s="105" t="s">
+        <v>96</v>
+      </c>
+      <c r="E30" s="104" t="s">
+        <v>73</v>
+      </c>
+      <c r="F30" s="104"/>
+      <c r="G30" s="104"/>
+      <c r="H30" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I30" s="105" t="s">
+      <c r="I30" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J30" s="104" t="s">
+      <c r="J30" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K30" s="22" t="s">
@@ -11172,22 +11159,22 @@
       <c r="U30" s="24"/>
       <c r="V30" s="24"/>
       <c r="W30" s="25"/>
-      <c r="X30" s="100"/>
-      <c r="Y30" s="149"/>
-      <c r="Z30" s="116"/>
-      <c r="AA30" s="162"/>
+      <c r="X30" s="159"/>
+      <c r="Y30" s="100"/>
+      <c r="Z30" s="94"/>
+      <c r="AA30" s="107"/>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A31" s="164"/>
-      <c r="B31" s="87"/>
-      <c r="C31" s="90"/>
-      <c r="D31" s="87"/>
-      <c r="E31" s="105"/>
-      <c r="F31" s="105"/>
-      <c r="G31" s="105"/>
-      <c r="H31" s="108"/>
-      <c r="I31" s="105"/>
-      <c r="J31" s="104"/>
+      <c r="A31" s="91"/>
+      <c r="B31" s="105"/>
+      <c r="C31" s="123"/>
+      <c r="D31" s="105"/>
+      <c r="E31" s="104"/>
+      <c r="F31" s="104"/>
+      <c r="G31" s="104"/>
+      <c r="H31" s="103"/>
+      <c r="I31" s="104"/>
+      <c r="J31" s="106"/>
       <c r="K31" s="22" t="s">
         <v>55</v>
       </c>
@@ -11221,34 +11208,34 @@
       <c r="U31" s="44"/>
       <c r="V31" s="44"/>
       <c r="W31" s="45"/>
-      <c r="X31" s="101"/>
-      <c r="Y31" s="110"/>
-      <c r="Z31" s="150"/>
-      <c r="AA31" s="163"/>
+      <c r="X31" s="160"/>
+      <c r="Y31" s="101"/>
+      <c r="Z31" s="95"/>
+      <c r="AA31" s="108"/>
     </row>
     <row r="32" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="164"/>
-      <c r="B32" s="90" t="s">
+      <c r="A32" s="91"/>
+      <c r="B32" s="123" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" s="124" t="s">
+        <v>64</v>
+      </c>
+      <c r="D32" s="105" t="s">
         <v>98</v>
       </c>
-      <c r="C32" s="119" t="s">
-        <v>65</v>
-      </c>
-      <c r="D32" s="87" t="s">
-        <v>99</v>
-      </c>
-      <c r="E32" s="105" t="s">
-        <v>74</v>
-      </c>
-      <c r="F32" s="105"/>
-      <c r="G32" s="105"/>
-      <c r="H32" s="108" t="s">
+      <c r="E32" s="104" t="s">
+        <v>73</v>
+      </c>
+      <c r="F32" s="104"/>
+      <c r="G32" s="104"/>
+      <c r="H32" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I32" s="105" t="s">
-        <v>78</v>
-      </c>
-      <c r="J32" s="104" t="s">
+      <c r="I32" s="104" t="s">
+        <v>77</v>
+      </c>
+      <c r="J32" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K32" s="22" t="s">
@@ -11284,28 +11271,28 @@
       <c r="U32" s="8"/>
       <c r="V32" s="8"/>
       <c r="W32" s="33"/>
-      <c r="X32" s="166" t="s">
-        <v>136</v>
-      </c>
-      <c r="Y32" s="94" t="s">
-        <v>138</v>
-      </c>
-      <c r="Z32" s="116"/>
-      <c r="AA32" s="120" t="s">
-        <v>100</v>
+      <c r="X32" s="98" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y32" s="96" t="s">
+        <v>137</v>
+      </c>
+      <c r="Z32" s="94"/>
+      <c r="AA32" s="117" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:29" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="164"/>
-      <c r="B33" s="90"/>
-      <c r="C33" s="119"/>
-      <c r="D33" s="87"/>
-      <c r="E33" s="105"/>
-      <c r="F33" s="105"/>
-      <c r="G33" s="105"/>
-      <c r="H33" s="108"/>
-      <c r="I33" s="105"/>
-      <c r="J33" s="104"/>
+      <c r="A33" s="91"/>
+      <c r="B33" s="123"/>
+      <c r="C33" s="124"/>
+      <c r="D33" s="105"/>
+      <c r="E33" s="104"/>
+      <c r="F33" s="104"/>
+      <c r="G33" s="104"/>
+      <c r="H33" s="103"/>
+      <c r="I33" s="104"/>
+      <c r="J33" s="106"/>
       <c r="K33" s="22" t="s">
         <v>55</v>
       </c>
@@ -11339,36 +11326,36 @@
       <c r="U33" s="31"/>
       <c r="V33" s="31"/>
       <c r="W33" s="32"/>
-      <c r="X33" s="167"/>
-      <c r="Y33" s="95"/>
-      <c r="Z33" s="150"/>
-      <c r="AA33" s="121"/>
+      <c r="X33" s="99"/>
+      <c r="Y33" s="97"/>
+      <c r="Z33" s="95"/>
+      <c r="AA33" s="118"/>
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A34" s="106" t="s">
+      <c r="A34" s="92" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="145" t="s">
+      <c r="B34" s="144" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="90" t="s">
-        <v>83</v>
-      </c>
-      <c r="D34" s="87" t="s">
+      <c r="C34" s="123" t="s">
+        <v>82</v>
+      </c>
+      <c r="D34" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="E34" s="105">
+      <c r="E34" s="104">
         <v>90</v>
       </c>
-      <c r="F34" s="105"/>
-      <c r="G34" s="105"/>
-      <c r="H34" s="108" t="s">
+      <c r="F34" s="104"/>
+      <c r="G34" s="104"/>
+      <c r="H34" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I34" s="105" t="s">
+      <c r="I34" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J34" s="117" t="s">
+      <c r="J34" s="102" t="s">
         <v>34</v>
       </c>
       <c r="K34" s="22" t="s">
@@ -11394,52 +11381,52 @@
       <c r="W34" s="25">
         <v>0.9</v>
       </c>
-      <c r="X34" s="91"/>
-      <c r="Y34" s="93" t="s">
-        <v>137</v>
-      </c>
-      <c r="Z34" s="112"/>
-      <c r="AA34" s="120" t="s">
-        <v>101</v>
+      <c r="X34" s="111"/>
+      <c r="Y34" s="131" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z34" s="116"/>
+      <c r="AA34" s="117" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A35" s="106"/>
-      <c r="B35" s="145"/>
-      <c r="C35" s="90"/>
-      <c r="D35" s="87"/>
-      <c r="E35" s="105"/>
-      <c r="F35" s="105"/>
-      <c r="G35" s="105"/>
-      <c r="H35" s="108"/>
-      <c r="I35" s="105"/>
-      <c r="J35" s="117"/>
+      <c r="A35" s="92"/>
+      <c r="B35" s="144"/>
+      <c r="C35" s="123"/>
+      <c r="D35" s="105"/>
+      <c r="E35" s="104"/>
+      <c r="F35" s="104"/>
+      <c r="G35" s="104"/>
+      <c r="H35" s="103"/>
+      <c r="I35" s="104"/>
+      <c r="J35" s="102"/>
       <c r="K35" s="22" t="s">
         <v>55</v>
       </c>
       <c r="L35" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M35" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N35" s="19">
         <v>1</v>
       </c>
       <c r="O35" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P35" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q35" s="19">
         <v>0.96199999999999997</v>
       </c>
       <c r="R35" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S35" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="T35" s="19">
         <v>0.91300000000000003</v>
@@ -11447,34 +11434,34 @@
       <c r="U35" s="19"/>
       <c r="V35" s="19"/>
       <c r="W35" s="28"/>
-      <c r="X35" s="91"/>
-      <c r="Y35" s="93"/>
-      <c r="Z35" s="112"/>
-      <c r="AA35" s="121"/>
+      <c r="X35" s="111"/>
+      <c r="Y35" s="131"/>
+      <c r="Z35" s="116"/>
+      <c r="AA35" s="118"/>
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A36" s="106"/>
-      <c r="B36" s="145" t="s">
+      <c r="A36" s="92"/>
+      <c r="B36" s="144" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="90" t="s">
-        <v>102</v>
-      </c>
-      <c r="D36" s="87" t="s">
+      <c r="C36" s="123" t="s">
+        <v>101</v>
+      </c>
+      <c r="D36" s="105" t="s">
         <v>37</v>
       </c>
-      <c r="E36" s="105">
+      <c r="E36" s="104">
         <v>83</v>
       </c>
-      <c r="F36" s="105"/>
-      <c r="G36" s="105"/>
-      <c r="H36" s="108" t="s">
+      <c r="F36" s="104"/>
+      <c r="G36" s="104"/>
+      <c r="H36" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I36" s="105" t="s">
+      <c r="I36" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J36" s="118" t="s">
+      <c r="J36" s="161" t="s">
         <v>38</v>
       </c>
       <c r="K36" s="22" t="s">
@@ -11496,96 +11483,96 @@
       <c r="U36" s="18"/>
       <c r="V36" s="18"/>
       <c r="W36" s="27"/>
-      <c r="X36" s="91" t="s">
+      <c r="X36" s="111" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y36" s="130" t="s">
         <v>103</v>
       </c>
-      <c r="Y36" s="92" t="s">
+      <c r="Z36" s="116"/>
+      <c r="AA36" s="117" t="s">
         <v>104</v>
-      </c>
-      <c r="Z36" s="112"/>
-      <c r="AA36" s="120" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A37" s="106"/>
-      <c r="B37" s="145"/>
-      <c r="C37" s="90"/>
-      <c r="D37" s="87"/>
-      <c r="E37" s="105"/>
-      <c r="F37" s="105"/>
-      <c r="G37" s="105"/>
-      <c r="H37" s="108"/>
-      <c r="I37" s="105"/>
-      <c r="J37" s="118"/>
+      <c r="A37" s="92"/>
+      <c r="B37" s="144"/>
+      <c r="C37" s="123"/>
+      <c r="D37" s="105"/>
+      <c r="E37" s="104"/>
+      <c r="F37" s="104"/>
+      <c r="G37" s="104"/>
+      <c r="H37" s="103"/>
+      <c r="I37" s="104"/>
+      <c r="J37" s="161"/>
       <c r="K37" s="22" t="s">
         <v>55</v>
       </c>
       <c r="L37" s="21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M37" s="21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N37" s="21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O37" s="19">
         <v>0.79</v>
       </c>
       <c r="P37" s="21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q37" s="19">
         <v>0.79</v>
       </c>
       <c r="R37" s="21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="S37" s="56"/>
       <c r="T37" s="56"/>
       <c r="U37" s="56"/>
       <c r="V37" s="56"/>
       <c r="W37" s="57"/>
-      <c r="X37" s="134"/>
-      <c r="Y37" s="94"/>
-      <c r="Z37" s="116"/>
-      <c r="AA37" s="122"/>
+      <c r="X37" s="109"/>
+      <c r="Y37" s="96"/>
+      <c r="Z37" s="94"/>
+      <c r="AA37" s="153"/>
     </row>
     <row r="38" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="135"/>
-      <c r="B38" s="135"/>
-      <c r="C38" s="135"/>
-      <c r="D38" s="135"/>
-      <c r="E38" s="135"/>
-      <c r="F38" s="135"/>
-      <c r="G38" s="135"/>
-      <c r="H38" s="135"/>
-      <c r="I38" s="135"/>
-      <c r="J38" s="135"/>
-      <c r="K38" s="135"/>
-      <c r="L38" s="135"/>
-      <c r="M38" s="135"/>
-      <c r="N38" s="135"/>
-      <c r="O38" s="135"/>
-      <c r="P38" s="136"/>
-      <c r="Q38" s="136"/>
-      <c r="R38" s="136"/>
-      <c r="S38" s="136"/>
-      <c r="T38" s="136"/>
-      <c r="U38" s="136"/>
-      <c r="V38" s="136"/>
-      <c r="W38" s="136"/>
-      <c r="X38" s="136"/>
-      <c r="Y38" s="136"/>
-      <c r="Z38" s="136"/>
-      <c r="AA38" s="136"/>
+      <c r="A38" s="147"/>
+      <c r="B38" s="147"/>
+      <c r="C38" s="147"/>
+      <c r="D38" s="147"/>
+      <c r="E38" s="147"/>
+      <c r="F38" s="147"/>
+      <c r="G38" s="147"/>
+      <c r="H38" s="147"/>
+      <c r="I38" s="147"/>
+      <c r="J38" s="147"/>
+      <c r="K38" s="147"/>
+      <c r="L38" s="147"/>
+      <c r="M38" s="147"/>
+      <c r="N38" s="147"/>
+      <c r="O38" s="147"/>
+      <c r="P38" s="148"/>
+      <c r="Q38" s="148"/>
+      <c r="R38" s="148"/>
+      <c r="S38" s="148"/>
+      <c r="T38" s="148"/>
+      <c r="U38" s="148"/>
+      <c r="V38" s="148"/>
+      <c r="W38" s="148"/>
+      <c r="X38" s="148"/>
+      <c r="Y38" s="148"/>
+      <c r="Z38" s="148"/>
+      <c r="AA38" s="148"/>
     </row>
     <row r="39" spans="1:29" s="5" customFormat="1" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="138" t="s">
-        <v>107</v>
-      </c>
-      <c r="B39" s="138"/>
+      <c r="A39" s="149" t="s">
+        <v>106</v>
+      </c>
+      <c r="B39" s="149"/>
       <c r="C39" s="58"/>
       <c r="D39"/>
       <c r="E39"/>
@@ -11617,7 +11604,7 @@
         <v>0</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>3</v>
@@ -11626,13 +11613,13 @@
         <v>4</v>
       </c>
       <c r="E40" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="F40" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="F40" s="10" t="s">
+      <c r="G40" s="10" t="s">
         <v>110</v>
-      </c>
-      <c r="G40" s="10" t="s">
-        <v>111</v>
       </c>
       <c r="H40" s="10" t="s">
         <v>8</v>
@@ -11653,7 +11640,7 @@
         <v>13</v>
       </c>
       <c r="N40" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O40" s="10" t="s">
         <v>15</v>
@@ -11662,7 +11649,7 @@
         <v>16</v>
       </c>
       <c r="Q40" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R40" s="10" t="s">
         <v>18</v>
@@ -11696,34 +11683,34 @@
       </c>
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A41" s="139" t="s">
+      <c r="A41" s="150" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="142" t="s">
+      <c r="B41" s="151" t="s">
+        <v>113</v>
+      </c>
+      <c r="C41" s="152" t="s">
+        <v>49</v>
+      </c>
+      <c r="D41" s="143" t="s">
         <v>114</v>
       </c>
-      <c r="C41" s="143" t="s">
-        <v>49</v>
-      </c>
-      <c r="D41" s="144" t="s">
-        <v>115</v>
-      </c>
-      <c r="E41" s="137" t="s">
-        <v>88</v>
-      </c>
-      <c r="F41" s="137" t="s">
-        <v>88</v>
-      </c>
-      <c r="G41" s="137" t="s">
-        <v>88</v>
-      </c>
-      <c r="H41" s="156" t="s">
+      <c r="E41" s="121" t="s">
+        <v>87</v>
+      </c>
+      <c r="F41" s="121" t="s">
+        <v>87</v>
+      </c>
+      <c r="G41" s="121" t="s">
+        <v>87</v>
+      </c>
+      <c r="H41" s="122" t="s">
         <v>51</v>
       </c>
-      <c r="I41" s="137" t="s">
+      <c r="I41" s="121" t="s">
         <v>33</v>
       </c>
-      <c r="J41" s="146" t="s">
+      <c r="J41" s="138" t="s">
         <v>52</v>
       </c>
       <c r="K41" s="61" t="s">
@@ -11765,25 +11752,25 @@
       <c r="W41" s="63">
         <v>3.32E-2</v>
       </c>
-      <c r="X41" s="133"/>
+      <c r="X41" s="158"/>
       <c r="Y41" s="128"/>
       <c r="Z41" s="128"/>
-      <c r="AA41" s="121" t="s">
-        <v>114</v>
+      <c r="AA41" s="118" t="s">
+        <v>113</v>
       </c>
       <c r="AC41" s="12"/>
     </row>
     <row r="42" spans="1:29" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="140"/>
-      <c r="B42" s="88"/>
-      <c r="C42" s="89"/>
-      <c r="D42" s="87"/>
-      <c r="E42" s="105"/>
-      <c r="F42" s="105"/>
-      <c r="G42" s="105"/>
-      <c r="H42" s="108"/>
-      <c r="I42" s="105"/>
-      <c r="J42" s="124"/>
+      <c r="A42" s="90"/>
+      <c r="B42" s="125"/>
+      <c r="C42" s="137"/>
+      <c r="D42" s="105"/>
+      <c r="E42" s="104"/>
+      <c r="F42" s="104"/>
+      <c r="G42" s="104"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="104"/>
+      <c r="J42" s="139"/>
       <c r="K42" s="22" t="s">
         <v>55</v>
       </c>
@@ -11817,40 +11804,40 @@
       <c r="U42" s="55"/>
       <c r="V42" s="55"/>
       <c r="W42" s="59"/>
-      <c r="X42" s="133"/>
+      <c r="X42" s="158"/>
       <c r="Y42" s="128"/>
       <c r="Z42" s="128"/>
-      <c r="AA42" s="123"/>
+      <c r="AA42" s="145"/>
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A43" s="141" t="s">
+      <c r="A43" s="136" t="s">
         <v>26</v>
       </c>
-      <c r="B43" s="88" t="s">
+      <c r="B43" s="125" t="s">
+        <v>115</v>
+      </c>
+      <c r="C43" s="137" t="s">
+        <v>85</v>
+      </c>
+      <c r="D43" s="105" t="s">
         <v>116</v>
       </c>
-      <c r="C43" s="89" t="s">
-        <v>86</v>
-      </c>
-      <c r="D43" s="87" t="s">
-        <v>117</v>
-      </c>
-      <c r="E43" s="105" t="s">
-        <v>88</v>
-      </c>
-      <c r="F43" s="105" t="s">
-        <v>88</v>
-      </c>
-      <c r="G43" s="105" t="s">
-        <v>88</v>
-      </c>
-      <c r="H43" s="108" t="s">
+      <c r="E43" s="104" t="s">
+        <v>87</v>
+      </c>
+      <c r="F43" s="104" t="s">
+        <v>87</v>
+      </c>
+      <c r="G43" s="104" t="s">
+        <v>87</v>
+      </c>
+      <c r="H43" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I43" s="105" t="s">
+      <c r="I43" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J43" s="117" t="s">
+      <c r="J43" s="102" t="s">
         <v>34</v>
       </c>
       <c r="K43" s="22" t="s">
@@ -11872,95 +11859,95 @@
       <c r="U43" s="35"/>
       <c r="V43" s="35"/>
       <c r="W43" s="38"/>
-      <c r="X43" s="127" t="s">
+      <c r="X43" s="146" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y43" s="141" t="s">
         <v>118</v>
       </c>
-      <c r="Y43" s="129" t="s">
+      <c r="Z43" s="140"/>
+      <c r="AA43" s="156" t="s">
         <v>119</v>
-      </c>
-      <c r="Z43" s="130"/>
-      <c r="AA43" s="131" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="44" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A44" s="141"/>
-      <c r="B44" s="88"/>
-      <c r="C44" s="89"/>
-      <c r="D44" s="87"/>
-      <c r="E44" s="105"/>
-      <c r="F44" s="105"/>
-      <c r="G44" s="105"/>
-      <c r="H44" s="108"/>
-      <c r="I44" s="155"/>
-      <c r="J44" s="117"/>
+      <c r="A44" s="136"/>
+      <c r="B44" s="125"/>
+      <c r="C44" s="137"/>
+      <c r="D44" s="105"/>
+      <c r="E44" s="104"/>
+      <c r="F44" s="104"/>
+      <c r="G44" s="104"/>
+      <c r="H44" s="103"/>
+      <c r="I44" s="112"/>
+      <c r="J44" s="102"/>
       <c r="K44" s="22" t="s">
         <v>55</v>
       </c>
       <c r="L44" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M44" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N44" s="17">
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="O44" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P44" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q44" s="17">
         <v>0.04</v>
       </c>
       <c r="R44" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S44" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="T44" s="55"/>
       <c r="U44" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="V44" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="W44" s="55"/>
-      <c r="X44" s="127"/>
-      <c r="Y44" s="129"/>
-      <c r="Z44" s="130"/>
-      <c r="AA44" s="131"/>
+      <c r="X44" s="146"/>
+      <c r="Y44" s="141"/>
+      <c r="Z44" s="140"/>
+      <c r="AA44" s="156"/>
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A45" s="141"/>
-      <c r="B45" s="88" t="s">
+      <c r="A45" s="136"/>
+      <c r="B45" s="125" t="s">
+        <v>120</v>
+      </c>
+      <c r="C45" s="137" t="s">
+        <v>85</v>
+      </c>
+      <c r="D45" s="105" t="s">
         <v>121</v>
       </c>
-      <c r="C45" s="89" t="s">
-        <v>86</v>
-      </c>
-      <c r="D45" s="87" t="s">
-        <v>122</v>
-      </c>
-      <c r="E45" s="105" t="s">
-        <v>88</v>
-      </c>
-      <c r="F45" s="105" t="s">
-        <v>88</v>
-      </c>
-      <c r="G45" s="105" t="s">
-        <v>88</v>
-      </c>
-      <c r="H45" s="108" t="s">
+      <c r="E45" s="104" t="s">
+        <v>87</v>
+      </c>
+      <c r="F45" s="104" t="s">
+        <v>87</v>
+      </c>
+      <c r="G45" s="104" t="s">
+        <v>87</v>
+      </c>
+      <c r="H45" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I45" s="105" t="s">
+      <c r="I45" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J45" s="124" t="s">
+      <c r="J45" s="139" t="s">
         <v>52</v>
       </c>
       <c r="K45" s="22" t="s">
@@ -11996,28 +11983,28 @@
       <c r="U45" s="35"/>
       <c r="V45" s="35"/>
       <c r="W45" s="38"/>
-      <c r="X45" s="127"/>
-      <c r="Y45" s="129" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z45" s="132">
+      <c r="X45" s="146"/>
+      <c r="Y45" s="141" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z45" s="157">
         <v>46188</v>
       </c>
-      <c r="AA45" s="123" t="s">
-        <v>121</v>
+      <c r="AA45" s="145" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="141"/>
-      <c r="B46" s="88"/>
-      <c r="C46" s="89"/>
-      <c r="D46" s="87"/>
-      <c r="E46" s="105"/>
-      <c r="F46" s="105"/>
-      <c r="G46" s="105"/>
-      <c r="H46" s="108"/>
-      <c r="I46" s="105"/>
-      <c r="J46" s="124"/>
+      <c r="A46" s="136"/>
+      <c r="B46" s="125"/>
+      <c r="C46" s="137"/>
+      <c r="D46" s="105"/>
+      <c r="E46" s="104"/>
+      <c r="F46" s="104"/>
+      <c r="G46" s="104"/>
+      <c r="H46" s="103"/>
+      <c r="I46" s="104"/>
+      <c r="J46" s="139"/>
       <c r="K46" s="22" t="s">
         <v>55</v>
       </c>
@@ -12051,38 +12038,38 @@
       <c r="U46" s="19"/>
       <c r="V46" s="19"/>
       <c r="W46" s="28"/>
-      <c r="X46" s="127"/>
-      <c r="Y46" s="130"/>
-      <c r="Z46" s="130"/>
-      <c r="AA46" s="123"/>
+      <c r="X46" s="146"/>
+      <c r="Y46" s="140"/>
+      <c r="Z46" s="140"/>
+      <c r="AA46" s="145"/>
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A47" s="141"/>
-      <c r="B47" s="88" t="s">
+      <c r="A47" s="136"/>
+      <c r="B47" s="125" t="s">
+        <v>123</v>
+      </c>
+      <c r="C47" s="137" t="s">
+        <v>82</v>
+      </c>
+      <c r="D47" s="105" t="s">
         <v>124</v>
       </c>
-      <c r="C47" s="89" t="s">
-        <v>83</v>
-      </c>
-      <c r="D47" s="87" t="s">
-        <v>125</v>
-      </c>
-      <c r="E47" s="105" t="s">
-        <v>88</v>
-      </c>
-      <c r="F47" s="105" t="s">
-        <v>88</v>
-      </c>
-      <c r="G47" s="105" t="s">
-        <v>88</v>
-      </c>
-      <c r="H47" s="108" t="s">
+      <c r="E47" s="104" t="s">
+        <v>87</v>
+      </c>
+      <c r="F47" s="104" t="s">
+        <v>87</v>
+      </c>
+      <c r="G47" s="104" t="s">
+        <v>87</v>
+      </c>
+      <c r="H47" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I47" s="105" t="s">
-        <v>78</v>
-      </c>
-      <c r="J47" s="124" t="s">
+      <c r="I47" s="104" t="s">
+        <v>77</v>
+      </c>
+      <c r="J47" s="139" t="s">
         <v>52</v>
       </c>
       <c r="K47" s="22" t="s">
@@ -12124,24 +12111,24 @@
       <c r="W47" s="39">
         <v>67</v>
       </c>
-      <c r="X47" s="127"/>
-      <c r="Y47" s="130"/>
-      <c r="Z47" s="130"/>
-      <c r="AA47" s="87" t="s">
-        <v>126</v>
+      <c r="X47" s="146"/>
+      <c r="Y47" s="140"/>
+      <c r="Z47" s="140"/>
+      <c r="AA47" s="105" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="48" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="141"/>
-      <c r="B48" s="88"/>
-      <c r="C48" s="89"/>
-      <c r="D48" s="87"/>
-      <c r="E48" s="105"/>
-      <c r="F48" s="105"/>
-      <c r="G48" s="105"/>
-      <c r="H48" s="108"/>
-      <c r="I48" s="105"/>
-      <c r="J48" s="124"/>
+      <c r="A48" s="136"/>
+      <c r="B48" s="125"/>
+      <c r="C48" s="137"/>
+      <c r="D48" s="105"/>
+      <c r="E48" s="104"/>
+      <c r="F48" s="104"/>
+      <c r="G48" s="104"/>
+      <c r="H48" s="103"/>
+      <c r="I48" s="104"/>
+      <c r="J48" s="139"/>
       <c r="K48" s="22" t="s">
         <v>55</v>
       </c>
@@ -12176,40 +12163,40 @@
       <c r="U48" s="9"/>
       <c r="V48" s="9"/>
       <c r="W48" s="26"/>
-      <c r="X48" s="127"/>
-      <c r="Y48" s="130"/>
-      <c r="Z48" s="130"/>
-      <c r="AA48" s="87"/>
+      <c r="X48" s="146"/>
+      <c r="Y48" s="140"/>
+      <c r="Z48" s="140"/>
+      <c r="AA48" s="105"/>
     </row>
     <row r="49" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A49" s="140" t="s">
+      <c r="A49" s="90" t="s">
+        <v>126</v>
+      </c>
+      <c r="B49" s="142" t="s">
         <v>127</v>
       </c>
-      <c r="B49" s="147" t="s">
+      <c r="C49" s="137" t="s">
+        <v>68</v>
+      </c>
+      <c r="D49" s="105" t="s">
         <v>128</v>
       </c>
-      <c r="C49" s="89" t="s">
-        <v>69</v>
-      </c>
-      <c r="D49" s="87" t="s">
-        <v>129</v>
-      </c>
-      <c r="E49" s="105">
+      <c r="E49" s="104">
         <v>74</v>
       </c>
-      <c r="F49" s="105" t="s">
-        <v>88</v>
-      </c>
-      <c r="G49" s="105" t="s">
-        <v>88</v>
-      </c>
-      <c r="H49" s="108" t="s">
+      <c r="F49" s="104" t="s">
+        <v>87</v>
+      </c>
+      <c r="G49" s="104" t="s">
+        <v>87</v>
+      </c>
+      <c r="H49" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I49" s="105" t="s">
+      <c r="I49" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J49" s="104" t="s">
+      <c r="J49" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K49" s="22" t="s">
@@ -12251,24 +12238,24 @@
       <c r="W49" s="40">
         <v>0.73999999999999966</v>
       </c>
-      <c r="X49" s="127"/>
-      <c r="Y49" s="129"/>
-      <c r="Z49" s="130"/>
-      <c r="AA49" s="123" t="s">
-        <v>130</v>
+      <c r="X49" s="146"/>
+      <c r="Y49" s="141"/>
+      <c r="Z49" s="140"/>
+      <c r="AA49" s="145" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="50" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A50" s="140"/>
-      <c r="B50" s="147"/>
-      <c r="C50" s="89"/>
-      <c r="D50" s="87"/>
-      <c r="E50" s="105"/>
-      <c r="F50" s="105"/>
-      <c r="G50" s="105"/>
-      <c r="H50" s="108"/>
-      <c r="I50" s="105"/>
-      <c r="J50" s="104"/>
+      <c r="A50" s="90"/>
+      <c r="B50" s="142"/>
+      <c r="C50" s="137"/>
+      <c r="D50" s="105"/>
+      <c r="E50" s="104"/>
+      <c r="F50" s="104"/>
+      <c r="G50" s="104"/>
+      <c r="H50" s="103"/>
+      <c r="I50" s="104"/>
+      <c r="J50" s="106"/>
       <c r="K50" s="22" t="s">
         <v>55</v>
       </c>
@@ -12302,40 +12289,40 @@
       <c r="U50" s="17"/>
       <c r="V50" s="17"/>
       <c r="W50" s="74"/>
-      <c r="X50" s="127"/>
-      <c r="Y50" s="129"/>
-      <c r="Z50" s="130"/>
-      <c r="AA50" s="123"/>
+      <c r="X50" s="146"/>
+      <c r="Y50" s="141"/>
+      <c r="Z50" s="140"/>
+      <c r="AA50" s="145"/>
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A51" s="141" t="s">
+      <c r="A51" s="136" t="s">
         <v>25</v>
       </c>
-      <c r="B51" s="88" t="s">
+      <c r="B51" s="125" t="s">
+        <v>130</v>
+      </c>
+      <c r="C51" s="137" t="s">
+        <v>71</v>
+      </c>
+      <c r="D51" s="105" t="s">
         <v>131</v>
       </c>
-      <c r="C51" s="89" t="s">
-        <v>72</v>
-      </c>
-      <c r="D51" s="87" t="s">
-        <v>132</v>
-      </c>
-      <c r="E51" s="105">
+      <c r="E51" s="104">
         <v>33.1</v>
       </c>
-      <c r="F51" s="105" t="s">
-        <v>88</v>
-      </c>
-      <c r="G51" s="105" t="s">
-        <v>88</v>
-      </c>
-      <c r="H51" s="108" t="s">
+      <c r="F51" s="104" t="s">
+        <v>87</v>
+      </c>
+      <c r="G51" s="104" t="s">
+        <v>87</v>
+      </c>
+      <c r="H51" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I51" s="105" t="s">
+      <c r="I51" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J51" s="104" t="s">
+      <c r="J51" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K51" s="22" t="s">
@@ -12371,24 +12358,24 @@
       <c r="U51" s="35"/>
       <c r="V51" s="35"/>
       <c r="W51" s="38"/>
-      <c r="X51" s="127"/>
-      <c r="Y51" s="130"/>
-      <c r="Z51" s="130"/>
-      <c r="AA51" s="90" t="s">
-        <v>133</v>
+      <c r="X51" s="146"/>
+      <c r="Y51" s="140"/>
+      <c r="Z51" s="140"/>
+      <c r="AA51" s="123" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="52" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="141"/>
-      <c r="B52" s="88"/>
-      <c r="C52" s="89"/>
-      <c r="D52" s="87"/>
-      <c r="E52" s="105"/>
-      <c r="F52" s="105"/>
-      <c r="G52" s="105"/>
-      <c r="H52" s="108"/>
-      <c r="I52" s="105"/>
-      <c r="J52" s="104"/>
+      <c r="A52" s="136"/>
+      <c r="B52" s="125"/>
+      <c r="C52" s="137"/>
+      <c r="D52" s="105"/>
+      <c r="E52" s="104"/>
+      <c r="F52" s="104"/>
+      <c r="G52" s="104"/>
+      <c r="H52" s="103"/>
+      <c r="I52" s="104"/>
+      <c r="J52" s="106"/>
       <c r="K52" s="22" t="s">
         <v>55</v>
       </c>
@@ -12422,10 +12409,10 @@
       <c r="U52" s="29"/>
       <c r="V52" s="29"/>
       <c r="W52" s="30"/>
-      <c r="X52" s="127"/>
-      <c r="Y52" s="130"/>
-      <c r="Z52" s="130"/>
-      <c r="AA52" s="90"/>
+      <c r="X52" s="146"/>
+      <c r="Y52" s="140"/>
+      <c r="Z52" s="140"/>
+      <c r="AA52" s="123"/>
     </row>
     <row r="54" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="56" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -12436,28 +12423,230 @@
     <row r="66" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="270">
-    <mergeCell ref="A24:A33"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="Z32:Z33"/>
-    <mergeCell ref="Y32:Y33"/>
-    <mergeCell ref="X32:X33"/>
-    <mergeCell ref="Z24:Z25"/>
-    <mergeCell ref="Y24:Y25"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="Y30:Y31"/>
-    <mergeCell ref="Z28:Z29"/>
-    <mergeCell ref="Z30:Z31"/>
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="X16:X17"/>
+    <mergeCell ref="Y16:Y17"/>
+    <mergeCell ref="Y28:Y29"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="X20:X21"/>
+    <mergeCell ref="Y20:Y21"/>
+    <mergeCell ref="X28:X29"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="Y26:Y27"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="A4:AA4"/>
+    <mergeCell ref="Z6:Z7"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="X6:X7"/>
+    <mergeCell ref="A6:A11"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="Z10:Z11"/>
+    <mergeCell ref="Y6:Y7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="Z36:Z37"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="X34:X35"/>
+    <mergeCell ref="Y34:Y35"/>
+    <mergeCell ref="Z34:Z35"/>
+    <mergeCell ref="Y36:Y37"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="AA32:AA33"/>
+    <mergeCell ref="AA16:AA17"/>
+    <mergeCell ref="AA20:AA21"/>
+    <mergeCell ref="AA41:AA42"/>
+    <mergeCell ref="AA45:AA46"/>
+    <mergeCell ref="AA47:AA48"/>
+    <mergeCell ref="AA24:AA25"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="AA28:AA29"/>
+    <mergeCell ref="AA26:AA27"/>
+    <mergeCell ref="AA34:AA35"/>
+    <mergeCell ref="AA36:AA37"/>
+    <mergeCell ref="X47:X48"/>
+    <mergeCell ref="Y41:Y42"/>
+    <mergeCell ref="Z41:Z42"/>
+    <mergeCell ref="X45:X46"/>
+    <mergeCell ref="Y45:Y46"/>
+    <mergeCell ref="AA43:AA44"/>
+    <mergeCell ref="Z43:Z44"/>
+    <mergeCell ref="Z45:Z46"/>
+    <mergeCell ref="X41:X42"/>
+    <mergeCell ref="X36:X37"/>
+    <mergeCell ref="X30:X31"/>
+    <mergeCell ref="AA51:AA52"/>
+    <mergeCell ref="AA49:AA50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="J51:J52"/>
+    <mergeCell ref="X51:X52"/>
+    <mergeCell ref="Z51:Z52"/>
+    <mergeCell ref="X49:X50"/>
+    <mergeCell ref="A38:AA38"/>
+    <mergeCell ref="Z49:Z50"/>
+    <mergeCell ref="Y47:Y48"/>
+    <mergeCell ref="Z47:Z48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="X43:X44"/>
+    <mergeCell ref="Y43:Y44"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A48"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J45:J46"/>
+    <mergeCell ref="Y51:Y52"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="Y49:Y50"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="F51:F52"/>
+    <mergeCell ref="G51:G52"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="AA12:AA13"/>
+    <mergeCell ref="AA14:AA15"/>
+    <mergeCell ref="X14:X15"/>
+    <mergeCell ref="Y14:Y15"/>
+    <mergeCell ref="Z20:Z21"/>
+    <mergeCell ref="X12:X13"/>
+    <mergeCell ref="Y12:Y13"/>
+    <mergeCell ref="Z12:Z13"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="Z14:Z15"/>
+    <mergeCell ref="Z16:Z17"/>
+    <mergeCell ref="Z18:Z19"/>
+    <mergeCell ref="AA18:AA19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="X18:X19"/>
+    <mergeCell ref="Y18:Y19"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="E28:G29"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="E26:G27"/>
+    <mergeCell ref="E22:G23"/>
+    <mergeCell ref="AA22:AA23"/>
+    <mergeCell ref="Z22:Z23"/>
+    <mergeCell ref="Z26:Z27"/>
+    <mergeCell ref="AA6:AA7"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AA10:AA11"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="E6:G7"/>
+    <mergeCell ref="E8:G9"/>
+    <mergeCell ref="E10:G11"/>
+    <mergeCell ref="E12:G13"/>
+    <mergeCell ref="E14:G15"/>
+    <mergeCell ref="E16:G17"/>
+    <mergeCell ref="E18:G19"/>
+    <mergeCell ref="E20:G21"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="X10:X11"/>
+    <mergeCell ref="Y10:Y11"/>
     <mergeCell ref="AA30:AA31"/>
     <mergeCell ref="X24:X25"/>
     <mergeCell ref="E30:G31"/>
@@ -12482,230 +12671,28 @@
     <mergeCell ref="I36:I37"/>
     <mergeCell ref="J26:J27"/>
     <mergeCell ref="X26:X27"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="E26:G27"/>
-    <mergeCell ref="E22:G23"/>
-    <mergeCell ref="AA22:AA23"/>
-    <mergeCell ref="Z22:Z23"/>
-    <mergeCell ref="Z26:Z27"/>
-    <mergeCell ref="AA6:AA7"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AA10:AA11"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="E6:G7"/>
-    <mergeCell ref="E8:G9"/>
-    <mergeCell ref="E10:G11"/>
-    <mergeCell ref="E12:G13"/>
-    <mergeCell ref="E14:G15"/>
-    <mergeCell ref="E16:G17"/>
-    <mergeCell ref="E18:G19"/>
-    <mergeCell ref="E20:G21"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="X10:X11"/>
-    <mergeCell ref="Y10:Y11"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="E28:G29"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="I32:I33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="AA12:AA13"/>
-    <mergeCell ref="AA14:AA15"/>
-    <mergeCell ref="X14:X15"/>
-    <mergeCell ref="Y14:Y15"/>
-    <mergeCell ref="Z20:Z21"/>
-    <mergeCell ref="X12:X13"/>
-    <mergeCell ref="Y12:Y13"/>
-    <mergeCell ref="Z12:Z13"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="Z14:Z15"/>
-    <mergeCell ref="Z16:Z17"/>
-    <mergeCell ref="Z18:Z19"/>
-    <mergeCell ref="AA18:AA19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="X18:X19"/>
-    <mergeCell ref="Y18:Y19"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="F51:F52"/>
-    <mergeCell ref="G51:G52"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="J45:J46"/>
-    <mergeCell ref="Y51:Y52"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="Y49:Y50"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="AA51:AA52"/>
-    <mergeCell ref="AA49:AA50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="J51:J52"/>
-    <mergeCell ref="X51:X52"/>
-    <mergeCell ref="Z51:Z52"/>
-    <mergeCell ref="X49:X50"/>
-    <mergeCell ref="A38:AA38"/>
-    <mergeCell ref="Z49:Z50"/>
-    <mergeCell ref="Y47:Y48"/>
-    <mergeCell ref="Z47:Z48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="X43:X44"/>
-    <mergeCell ref="Y43:Y44"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A48"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="AA32:AA33"/>
-    <mergeCell ref="AA16:AA17"/>
-    <mergeCell ref="AA20:AA21"/>
-    <mergeCell ref="AA41:AA42"/>
-    <mergeCell ref="AA45:AA46"/>
-    <mergeCell ref="AA47:AA48"/>
-    <mergeCell ref="AA24:AA25"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="AA28:AA29"/>
-    <mergeCell ref="AA26:AA27"/>
-    <mergeCell ref="AA34:AA35"/>
-    <mergeCell ref="AA36:AA37"/>
-    <mergeCell ref="X47:X48"/>
-    <mergeCell ref="Y41:Y42"/>
-    <mergeCell ref="Z41:Z42"/>
-    <mergeCell ref="X45:X46"/>
-    <mergeCell ref="Y45:Y46"/>
-    <mergeCell ref="AA43:AA44"/>
-    <mergeCell ref="Z43:Z44"/>
-    <mergeCell ref="Z45:Z46"/>
-    <mergeCell ref="X41:X42"/>
-    <mergeCell ref="X36:X37"/>
-    <mergeCell ref="X30:X31"/>
-    <mergeCell ref="Z36:Z37"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="X34:X35"/>
-    <mergeCell ref="Y34:Y35"/>
-    <mergeCell ref="Z34:Z35"/>
-    <mergeCell ref="Y36:Y37"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A16:A21"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="A4:AA4"/>
-    <mergeCell ref="Z6:Z7"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="X6:X7"/>
-    <mergeCell ref="A6:A11"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="Z10:Z11"/>
-    <mergeCell ref="Y6:Y7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="X16:X17"/>
-    <mergeCell ref="Y16:Y17"/>
-    <mergeCell ref="Y28:Y29"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="X20:X21"/>
-    <mergeCell ref="Y20:Y21"/>
-    <mergeCell ref="X28:X29"/>
-    <mergeCell ref="X22:X23"/>
-    <mergeCell ref="Y22:Y23"/>
-    <mergeCell ref="Y26:Y27"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="A24:A33"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="Z32:Z33"/>
+    <mergeCell ref="Y32:Y33"/>
+    <mergeCell ref="X32:X33"/>
+    <mergeCell ref="Z24:Z25"/>
+    <mergeCell ref="Y24:Y25"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="Y30:Y31"/>
+    <mergeCell ref="Z28:Z29"/>
+    <mergeCell ref="Z30:Z31"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="B28:B31"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B6 H6:J6 C6:C12 B8 H8:J8 B10 H10:J10 B12 H12:J12 H14:J14 H16:J16 H20:J20 C22 H22:J22 H24:J24 D26:E26 H26:J26 C26:C27 H28:J28 H30:J30 H32:J32 H34:J34 H36:J36 D41:J41 C41:C43 D45:J45 C45:C52 D47:J47 D49:J49 D51:J51">
@@ -12754,34 +12741,34 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L27">
-    <cfRule type="expression" dxfId="66" priority="78">
+    <cfRule type="expression" dxfId="66" priority="81" stopIfTrue="1">
+      <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&gt;=L26)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="65" priority="80">
+      <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&lt;L26)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="79">
+      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&lt;=L26)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="63" priority="78">
       <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&gt;L26)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="79">
-      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&lt;=L26)</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L7:W7 L9:W9 L11:W11 L13:W13 L15:W15 L17:W17 L19:W19 L21:W21 L23:W23 M27:W27 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37">
+    <cfRule type="expression" dxfId="62" priority="249">
+      <formula xml:space="preserve"> AND(OR($H6="Higher the better", $H6="Higher the Better"), L7&gt;= L6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="80">
-      <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&lt;L26)</formula>
+    <cfRule type="expression" dxfId="61" priority="74">
+      <formula>AND(OR($H6="Lower the better", $H6="Lower the better"), L7&gt; L6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="81" stopIfTrue="1">
-      <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&gt;=L26)</formula>
+    <cfRule type="expression" dxfId="60" priority="247">
+      <formula>AND(OR($H6="Lower the better", $H6= "Lower the Better"), L7 &lt;= L6)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="59" priority="248">
+      <formula>AND(OR($H6="Higher the better", $H6="Higher the Better"), L7 &lt; L6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L7:W7 L9:W9 L11:W11 L13:W13 L17:W17 L19:W19 L21:W21 L23:W23 M27:W27 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37 L15:W15">
-    <cfRule type="expression" dxfId="62" priority="74">
-      <formula>AND(OR($H6="Lower the better", $H6="Lower the better"), L7&gt; L6)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="61" priority="247">
-      <formula>AND(OR($H6="Lower the better", $H6= "Lower the Better"), L7 &lt;= L6)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="60" priority="248">
-      <formula>AND(OR($H6="Higher the better", $H6="Higher the Better"), L7 &lt; L6)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="59" priority="249">
-      <formula xml:space="preserve"> AND(OR($H6="Higher the better", $H6="Higher the Better"), L7&gt;= L6)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L7:W7 L9:W9 L11:W11 L13:W13 L17:W17 L19:W19 L21:W21 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37 L15:W15 L23:W27">
+  <conditionalFormatting sqref="L23:W27 L7:W7 L9:W9 L11:W11 L13:W13 L15:W15 L17:W17 L19:W19 L21:W21 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37">
     <cfRule type="containsBlanks" dxfId="58" priority="245">
       <formula>LEN(TRIM(L7))=0</formula>
     </cfRule>
@@ -12795,185 +12782,185 @@
     <cfRule type="containsBlanks" dxfId="56" priority="173">
       <formula>LEN(TRIM(L46))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="175">
+    <cfRule type="expression" dxfId="55" priority="177">
+      <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&lt;L45)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="54" priority="175">
       <formula>AND(OR($H45="Lower the better", $H45="Lower the Better"), L46&gt;L45)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="176">
+    <cfRule type="expression" dxfId="53" priority="176">
       <formula>AND(OR($H45="Lower the better", $H45="Lower the Better"), L46&lt;=L45)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="53" priority="177">
-      <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&lt;L45)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="52" priority="178" stopIfTrue="1">
       <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&gt;=L45)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L52:W52">
-    <cfRule type="containsBlanks" dxfId="51" priority="104">
+    <cfRule type="expression" dxfId="51" priority="107">
+      <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&lt;L51)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="50" priority="106">
+      <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&lt;=L51)</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="49" priority="104">
       <formula>LEN(TRIM(L52))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="105">
+    <cfRule type="expression" dxfId="48" priority="105">
       <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&gt;L51)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="49" priority="106">
-      <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&lt;=L51)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="107">
-      <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&lt;L51)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="47" priority="108" stopIfTrue="1">
       <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&gt;=L51)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25 T25 W25 L42:W42">
-    <cfRule type="containsBlanks" dxfId="46" priority="67">
+    <cfRule type="expression" dxfId="46" priority="71" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&gt;=L24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="45" priority="70">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&lt;L24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="68">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&gt;L24)</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="43" priority="67">
       <formula>LEN(TRIM(L25))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="68">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&gt;L24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="44" priority="69">
+    <cfRule type="expression" dxfId="42" priority="69">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&lt;=L24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="43" priority="70">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&lt;L24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="71" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&gt;=L24)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25">
-    <cfRule type="containsBlanks" dxfId="41" priority="16">
-      <formula>LEN(TRIM(N25))=0</formula>
+    <cfRule type="expression" dxfId="41" priority="18">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="40" priority="17">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&gt;N24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="18">
+    <cfRule type="containsBlanks" dxfId="39" priority="16">
+      <formula>LEN(TRIM(N25))=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="25" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="22">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&gt;N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="24">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="35" priority="21">
+      <formula>LEN(TRIM(N25))=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="20" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="23">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="19">
+    <cfRule type="expression" dxfId="32" priority="19">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="37" priority="20" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="36" priority="21">
-      <formula>LEN(TRIM(N25))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="35" priority="22">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&gt;N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="23">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="24">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="25" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N44">
-    <cfRule type="containsBlanks" dxfId="31" priority="62">
+    <cfRule type="expression" dxfId="31" priority="65">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&lt;N43)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="66" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&gt;=N43)</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="29" priority="62">
       <formula>LEN(TRIM(N44))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="63">
+    <cfRule type="expression" dxfId="28" priority="63">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&gt;N43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="64">
+    <cfRule type="expression" dxfId="27" priority="64">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&lt;=N43)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="65">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&lt;N43)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="66" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&gt;=N43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q25">
-    <cfRule type="containsBlanks" dxfId="26" priority="26">
-      <formula>LEN(TRIM(Q25))=0</formula>
+    <cfRule type="expression" dxfId="26" priority="30" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&gt;=Q24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="27">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&gt;Q24)</formula>
+    <cfRule type="expression" dxfId="25" priority="29">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&lt;Q24)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="24" priority="28">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&lt;=Q24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="29">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&lt;Q24)</formula>
+    <cfRule type="expression" dxfId="23" priority="27">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&gt;Q24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="30" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&gt;=Q24)</formula>
+    <cfRule type="containsBlanks" dxfId="22" priority="26">
+      <formula>LEN(TRIM(Q25))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q37">
-    <cfRule type="expression" dxfId="21" priority="6">
-      <formula>AND(OR($H36="Lower the better", $H36="Lower the better"), Q37&gt; Q36)</formula>
+    <cfRule type="expression" dxfId="21" priority="10">
+      <formula xml:space="preserve"> AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37&gt;= Q36)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="20" priority="7">
-      <formula>LEN(TRIM(Q37))=0</formula>
+    <cfRule type="expression" dxfId="20" priority="9">
+      <formula>AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37 &lt; Q36)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="8">
       <formula>AND(OR($H36="Lower the better", $H36= "Lower the Better"), Q37 &lt;= Q36)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="9">
-      <formula>AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37 &lt; Q36)</formula>
+    <cfRule type="expression" dxfId="18" priority="6">
+      <formula>AND(OR($H36="Lower the better", $H36="Lower the better"), Q37&gt; Q36)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="10">
-      <formula xml:space="preserve"> AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37&gt;= Q36)</formula>
+    <cfRule type="containsBlanks" dxfId="17" priority="7">
+      <formula>LEN(TRIM(Q37))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q44">
-    <cfRule type="containsBlanks" dxfId="16" priority="11">
-      <formula>LEN(TRIM(Q44))=0</formula>
+    <cfRule type="expression" dxfId="16" priority="15" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&gt;=Q43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="12">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&gt;Q43)</formula>
+    <cfRule type="expression" dxfId="15" priority="14">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&lt;Q43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="13">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&lt;=Q43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="14">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&lt;Q43)</formula>
+    <cfRule type="expression" dxfId="13" priority="12">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&gt;Q43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="15" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&gt;=Q43)</formula>
+    <cfRule type="containsBlanks" dxfId="12" priority="11">
+      <formula>LEN(TRIM(Q44))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T44">
-    <cfRule type="containsBlanks" dxfId="11" priority="52">
-      <formula>LEN(TRIM(T44))=0</formula>
+    <cfRule type="expression" dxfId="11" priority="56" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&gt;=T43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="53">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&gt;T43)</formula>
+    <cfRule type="expression" dxfId="10" priority="55">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&lt;T43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="9" priority="54">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&lt;=T43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="55">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&lt;T43)</formula>
+    <cfRule type="expression" dxfId="8" priority="53">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&gt;T43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="56" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&gt;=T43)</formula>
+    <cfRule type="containsBlanks" dxfId="7" priority="52">
+      <formula>LEN(TRIM(T44))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W44">
-    <cfRule type="containsBlanks" dxfId="6" priority="47">
+    <cfRule type="expression" dxfId="6" priority="48">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&gt;W43)</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="5" priority="47">
       <formula>LEN(TRIM(W44))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="48">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&gt;W43)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="49">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&lt;=W43)</formula>
+    <cfRule type="expression" dxfId="4" priority="51" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&gt;=W43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="3" priority="50">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&lt;W43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="51" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&gt;=W43)</formula>
+    <cfRule type="expression" dxfId="2" priority="49">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&lt;=W43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA47">
@@ -13025,11 +13012,6 @@
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
@@ -13037,13 +13019,12 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -13181,7 +13162,21 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
@@ -13189,33 +13184,25 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="f5a961e1-edc1-4f62-8655-e8a46ef79e5c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="68108f69-118e-4385-83b3-00743b1bf54c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F9F019C-2529-47D7-9C19-168692A0A5B3}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AEEF6728-DD64-4985-9AAC-D753ED42B82F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="f5a961e1-edc1-4f62-8655-e8a46ef79e5c"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="68108f69-118e-4385-83b3-00743b1bf54c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/GlobalMoSMT-2023/Shared Documents/General/2026/Goals Alignment 2026/Strategic Execution 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3310" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B9C3698-7C23-4896-8953-ED430E711542}"/>
+  <xr:revisionPtr revIDLastSave="3320" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5A4BA57-CBB5-43E3-A661-F181EB486104}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
   </bookViews>
   <sheets>
     <sheet name="Mastersheet" sheetId="5" r:id="rId1"/>
@@ -366,7 +366,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="142">
   <si>
     <t>Strategic Imperatives</t>
   </si>
@@ -1562,251 +1562,251 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2441,8 +2441,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>712470</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>18415</xdr:rowOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>124248</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -9023,11 +9023,11 @@
       </c>
       <c r="T51" s="70" t="str">
         <f>IF('AOP Critical'!U24="","",'AOP Critical'!U24)</f>
-        <v>QTR</v>
+        <v/>
       </c>
       <c r="U51" s="70" t="str">
         <f>IF('AOP Critical'!V24="","",'AOP Critical'!V24)</f>
-        <v>QTR</v>
+        <v/>
       </c>
       <c r="V51" s="70" t="str">
         <f>IF('AOP Critical'!W24="","",'AOP Critical'!W24)</f>
@@ -9113,11 +9113,11 @@
       </c>
       <c r="T52" t="str">
         <f>IF('AOP Critical'!U25="","",'AOP Critical'!U25)</f>
-        <v>QTR</v>
+        <v/>
       </c>
       <c r="U52" t="str">
         <f>IF('AOP Critical'!V25="","",'AOP Critical'!V25)</f>
-        <v>QTR</v>
+        <v/>
       </c>
       <c r="V52" t="str">
         <f>IF('AOP Critical'!W25="","",'AOP Critical'!W25)</f>
@@ -9517,8 +9517,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{632542D1-52E6-4116-B536-B17D5839DF19}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AC66"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AC52"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="20.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.54296875" customWidth="1"/>
     <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
@@ -9531,11 +9531,12 @@
     <col min="9" max="9" width="5.26953125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6.7265625" customWidth="1"/>
-    <col min="12" max="12" width="5.54296875" customWidth="1"/>
-    <col min="13" max="13" width="6.81640625" customWidth="1"/>
+    <col min="12" max="12" width="5.54296875" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="6.81640625" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="6.26953125" customWidth="1"/>
-    <col min="15" max="15" width="7.26953125" customWidth="1"/>
-    <col min="16" max="22" width="6.1796875" customWidth="1"/>
+    <col min="15" max="15" width="7.26953125" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="6.1796875" hidden="1" customWidth="1"/>
+    <col min="17" max="22" width="6.1796875" customWidth="1"/>
     <col min="23" max="23" width="6" customWidth="1"/>
     <col min="24" max="24" width="58.81640625" style="20" customWidth="1"/>
     <col min="25" max="25" width="68.1796875" customWidth="1"/>
@@ -9544,7 +9545,7 @@
     <col min="28" max="46" width="8.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
         <v>39</v>
       </c>
@@ -9555,7 +9556,7 @@
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="6"/>
       <c r="C2" s="7"/>
       <c r="E2" s="6"/>
@@ -9564,11 +9565,11 @@
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
     </row>
-    <row r="3" spans="1:27" s="5" customFormat="1" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="162" t="s">
+    <row r="3" spans="1:27" s="5" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="110" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="162"/>
+      <c r="B3" s="110"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -9588,39 +9589,39 @@
       <c r="X3" s="89"/>
       <c r="AA3" s="14"/>
     </row>
-    <row r="4" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="163" t="str">
+    <row r="4" spans="1:27" s="5" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="112" t="str">
         <f ca="1">"Current Month-Year " &amp; ":" &amp; TEXT(TODAY(),"YYYY-MM")</f>
         <v>Current Month-Year :2026-10</v>
       </c>
-      <c r="B4" s="163"/>
-      <c r="C4" s="163"/>
-      <c r="D4" s="163"/>
-      <c r="E4" s="163"/>
-      <c r="F4" s="163"/>
-      <c r="G4" s="163"/>
-      <c r="H4" s="163"/>
-      <c r="I4" s="163"/>
-      <c r="J4" s="163"/>
-      <c r="K4" s="163"/>
-      <c r="L4" s="163"/>
-      <c r="M4" s="163"/>
-      <c r="N4" s="163"/>
-      <c r="O4" s="163"/>
-      <c r="P4" s="163"/>
-      <c r="Q4" s="163"/>
-      <c r="R4" s="163"/>
-      <c r="S4" s="163"/>
-      <c r="T4" s="163"/>
-      <c r="U4" s="163"/>
-      <c r="V4" s="163"/>
-      <c r="W4" s="163"/>
-      <c r="X4" s="163"/>
-      <c r="Y4" s="163"/>
-      <c r="Z4" s="163"/>
-      <c r="AA4" s="163"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="112"/>
+      <c r="L4" s="112"/>
+      <c r="M4" s="112"/>
+      <c r="N4" s="112"/>
+      <c r="O4" s="112"/>
+      <c r="P4" s="112"/>
+      <c r="Q4" s="112"/>
+      <c r="R4" s="112"/>
+      <c r="S4" s="112"/>
+      <c r="T4" s="112"/>
+      <c r="U4" s="112"/>
+      <c r="V4" s="112"/>
+      <c r="W4" s="112"/>
+      <c r="X4" s="112"/>
+      <c r="Y4" s="112"/>
+      <c r="Z4" s="112"/>
+      <c r="AA4" s="112"/>
     </row>
-    <row r="5" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:27" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="85" t="s">
         <v>0</v>
       </c>
@@ -9633,11 +9634,11 @@
       <c r="D5" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="164" t="s">
+      <c r="E5" s="116" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="164"/>
-      <c r="G5" s="164"/>
+      <c r="F5" s="116"/>
+      <c r="G5" s="116"/>
       <c r="H5" s="86" t="s">
         <v>8</v>
       </c>
@@ -9699,31 +9700,31 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A6" s="92" t="s">
+    <row r="6" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="109" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="125" t="s">
+      <c r="B6" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="137" t="s">
+      <c r="C6" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="105" t="s">
+      <c r="D6" s="90" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="104">
+      <c r="E6" s="108">
         <v>10</v>
       </c>
-      <c r="F6" s="104"/>
-      <c r="G6" s="104"/>
-      <c r="H6" s="103" t="s">
+      <c r="F6" s="108"/>
+      <c r="G6" s="108"/>
+      <c r="H6" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="104" t="s">
+      <c r="I6" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="106" t="s">
+      <c r="J6" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K6" s="22" t="s">
@@ -9765,24 +9766,24 @@
       <c r="W6" s="27">
         <v>0.05</v>
       </c>
-      <c r="X6" s="110"/>
-      <c r="Y6" s="101"/>
-      <c r="Z6" s="101"/>
-      <c r="AA6" s="117" t="s">
+      <c r="X6" s="106"/>
+      <c r="Y6" s="113"/>
+      <c r="Z6" s="113"/>
+      <c r="AA6" s="123" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A7" s="92"/>
-      <c r="B7" s="125"/>
-      <c r="C7" s="137"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="104"/>
-      <c r="F7" s="104"/>
-      <c r="G7" s="104"/>
-      <c r="H7" s="103"/>
-      <c r="I7" s="104"/>
-      <c r="J7" s="106"/>
+    <row r="7" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="109"/>
+      <c r="B7" s="91"/>
+      <c r="C7" s="92"/>
+      <c r="D7" s="90"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="108"/>
+      <c r="G7" s="108"/>
+      <c r="H7" s="111"/>
+      <c r="I7" s="108"/>
+      <c r="J7" s="107"/>
       <c r="K7" s="22" t="s">
         <v>55</v>
       </c>
@@ -9816,34 +9817,34 @@
       <c r="U7" s="50"/>
       <c r="V7" s="50"/>
       <c r="W7" s="50"/>
-      <c r="X7" s="111"/>
-      <c r="Y7" s="131"/>
-      <c r="Z7" s="131"/>
-      <c r="AA7" s="118"/>
+      <c r="X7" s="94"/>
+      <c r="Y7" s="96"/>
+      <c r="Z7" s="96"/>
+      <c r="AA7" s="124"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A8" s="92"/>
-      <c r="B8" s="125" t="s">
+    <row r="8" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="109"/>
+      <c r="B8" s="91" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="137" t="s">
+      <c r="C8" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="105" t="s">
+      <c r="D8" s="90" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="104">
+      <c r="E8" s="108">
         <v>90</v>
       </c>
-      <c r="F8" s="104"/>
-      <c r="G8" s="104"/>
-      <c r="H8" s="103" t="s">
+      <c r="F8" s="108"/>
+      <c r="G8" s="108"/>
+      <c r="H8" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="104" t="s">
+      <c r="I8" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="106" t="s">
+      <c r="J8" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K8" s="22" t="s">
@@ -9875,24 +9876,24 @@
       <c r="U8" s="18"/>
       <c r="V8" s="18"/>
       <c r="W8" s="27"/>
-      <c r="X8" s="111"/>
-      <c r="Y8" s="130"/>
-      <c r="Z8" s="115"/>
-      <c r="AA8" s="117" t="s">
+      <c r="X8" s="94"/>
+      <c r="Y8" s="95"/>
+      <c r="Z8" s="114"/>
+      <c r="AA8" s="123" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A9" s="92"/>
-      <c r="B9" s="125"/>
-      <c r="C9" s="137"/>
-      <c r="D9" s="105"/>
-      <c r="E9" s="104"/>
-      <c r="F9" s="104"/>
-      <c r="G9" s="104"/>
-      <c r="H9" s="103"/>
-      <c r="I9" s="104"/>
-      <c r="J9" s="106"/>
+    <row r="9" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="109"/>
+      <c r="B9" s="91"/>
+      <c r="C9" s="92"/>
+      <c r="D9" s="90"/>
+      <c r="E9" s="108"/>
+      <c r="F9" s="108"/>
+      <c r="G9" s="108"/>
+      <c r="H9" s="111"/>
+      <c r="I9" s="108"/>
+      <c r="J9" s="107"/>
       <c r="K9" s="22" t="s">
         <v>55</v>
       </c>
@@ -9926,34 +9927,34 @@
       <c r="U9" s="52"/>
       <c r="V9" s="52"/>
       <c r="W9" s="52"/>
-      <c r="X9" s="111"/>
-      <c r="Y9" s="131"/>
-      <c r="Z9" s="116"/>
-      <c r="AA9" s="118"/>
+      <c r="X9" s="94"/>
+      <c r="Y9" s="96"/>
+      <c r="Z9" s="115"/>
+      <c r="AA9" s="124"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A10" s="92"/>
-      <c r="B10" s="125" t="s">
+    <row r="10" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="109"/>
+      <c r="B10" s="91" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="137" t="s">
+      <c r="C10" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="105" t="s">
+      <c r="D10" s="90" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="104">
+      <c r="E10" s="108">
         <v>1</v>
       </c>
-      <c r="F10" s="104"/>
-      <c r="G10" s="104"/>
-      <c r="H10" s="103" t="s">
+      <c r="F10" s="108"/>
+      <c r="G10" s="108"/>
+      <c r="H10" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="104" t="s">
+      <c r="I10" s="108" t="s">
         <v>61</v>
       </c>
-      <c r="J10" s="106" t="s">
+      <c r="J10" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K10" s="22" t="s">
@@ -9987,24 +9988,24 @@
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
       <c r="W10" s="33"/>
-      <c r="X10" s="111"/>
-      <c r="Y10" s="119"/>
-      <c r="Z10" s="165"/>
-      <c r="AA10" s="117" t="s">
+      <c r="X10" s="94"/>
+      <c r="Y10" s="164"/>
+      <c r="Z10" s="117"/>
+      <c r="AA10" s="123" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="92"/>
-      <c r="B11" s="125"/>
-      <c r="C11" s="137"/>
-      <c r="D11" s="105"/>
-      <c r="E11" s="104"/>
-      <c r="F11" s="104"/>
-      <c r="G11" s="104"/>
-      <c r="H11" s="103"/>
-      <c r="I11" s="104"/>
-      <c r="J11" s="106"/>
+      <c r="A11" s="109"/>
+      <c r="B11" s="91"/>
+      <c r="C11" s="92"/>
+      <c r="D11" s="90"/>
+      <c r="E11" s="108"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="111"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="107"/>
       <c r="K11" s="22" t="s">
         <v>55</v>
       </c>
@@ -10038,36 +10039,36 @@
       <c r="U11" s="31"/>
       <c r="V11" s="31"/>
       <c r="W11" s="32"/>
-      <c r="X11" s="111"/>
-      <c r="Y11" s="120"/>
-      <c r="Z11" s="166"/>
-      <c r="AA11" s="118"/>
+      <c r="X11" s="94"/>
+      <c r="Y11" s="165"/>
+      <c r="Z11" s="118"/>
+      <c r="AA11" s="124"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A12" s="92" t="s">
+    <row r="12" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="109" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="123" t="s">
+      <c r="B12" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="123" t="s">
+      <c r="C12" s="93" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="105" t="s">
+      <c r="D12" s="90" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="104">
+      <c r="E12" s="108">
         <v>84</v>
       </c>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="103" t="s">
+      <c r="F12" s="108"/>
+      <c r="G12" s="108"/>
+      <c r="H12" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="104" t="s">
+      <c r="I12" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="106" t="s">
+      <c r="J12" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K12" s="22" t="s">
@@ -10109,24 +10110,24 @@
       <c r="W12" s="25">
         <v>0.79</v>
       </c>
-      <c r="X12" s="111"/>
-      <c r="Y12" s="130"/>
-      <c r="Z12" s="131"/>
-      <c r="AA12" s="117" t="s">
+      <c r="X12" s="94"/>
+      <c r="Y12" s="95"/>
+      <c r="Z12" s="96"/>
+      <c r="AA12" s="123" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A13" s="92"/>
-      <c r="B13" s="123"/>
-      <c r="C13" s="123"/>
-      <c r="D13" s="105"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="104"/>
-      <c r="G13" s="104"/>
-      <c r="H13" s="103"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="106"/>
+    <row r="13" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="109"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="90"/>
+      <c r="E13" s="108"/>
+      <c r="F13" s="108"/>
+      <c r="G13" s="108"/>
+      <c r="H13" s="111"/>
+      <c r="I13" s="108"/>
+      <c r="J13" s="107"/>
       <c r="K13" s="22" t="s">
         <v>55</v>
       </c>
@@ -10160,34 +10161,34 @@
       <c r="U13" s="19"/>
       <c r="V13" s="19"/>
       <c r="W13" s="28"/>
-      <c r="X13" s="111"/>
-      <c r="Y13" s="131"/>
-      <c r="Z13" s="131"/>
-      <c r="AA13" s="118"/>
+      <c r="X13" s="94"/>
+      <c r="Y13" s="96"/>
+      <c r="Z13" s="96"/>
+      <c r="AA13" s="124"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A14" s="92"/>
-      <c r="B14" s="123" t="s">
+    <row r="14" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="109"/>
+      <c r="B14" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="124" t="s">
+      <c r="C14" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="105" t="s">
+      <c r="D14" s="90" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="104">
+      <c r="E14" s="108">
         <v>54.6</v>
       </c>
-      <c r="F14" s="104"/>
-      <c r="G14" s="104"/>
-      <c r="H14" s="103" t="s">
+      <c r="F14" s="108"/>
+      <c r="G14" s="108"/>
+      <c r="H14" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="104" t="s">
+      <c r="I14" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J14" s="106" t="s">
+      <c r="J14" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K14" s="22" t="s">
@@ -10223,26 +10224,26 @@
       <c r="U14" s="37"/>
       <c r="V14" s="37"/>
       <c r="W14" s="37"/>
-      <c r="X14" s="129" t="s">
+      <c r="X14" s="152" t="s">
         <v>141</v>
       </c>
-      <c r="Y14" s="96" t="s">
+      <c r="Y14" s="97" t="s">
         <v>140</v>
       </c>
-      <c r="Z14" s="100"/>
-      <c r="AA14" s="127"/>
+      <c r="Z14" s="154"/>
+      <c r="AA14" s="151"/>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="92"/>
-      <c r="B15" s="123"/>
-      <c r="C15" s="124"/>
-      <c r="D15" s="105"/>
-      <c r="E15" s="104"/>
-      <c r="F15" s="104"/>
-      <c r="G15" s="104"/>
-      <c r="H15" s="103"/>
-      <c r="I15" s="104"/>
-      <c r="J15" s="106"/>
+      <c r="A15" s="109"/>
+      <c r="B15" s="93"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="90"/>
+      <c r="E15" s="108"/>
+      <c r="F15" s="108"/>
+      <c r="G15" s="108"/>
+      <c r="H15" s="111"/>
+      <c r="I15" s="108"/>
+      <c r="J15" s="107"/>
       <c r="K15" s="22" t="s">
         <v>55</v>
       </c>
@@ -10276,36 +10277,36 @@
       <c r="U15" s="31"/>
       <c r="V15" s="31"/>
       <c r="W15" s="32"/>
-      <c r="X15" s="111"/>
-      <c r="Y15" s="101"/>
-      <c r="Z15" s="101"/>
-      <c r="AA15" s="128"/>
+      <c r="X15" s="94"/>
+      <c r="Y15" s="113"/>
+      <c r="Z15" s="113"/>
+      <c r="AA15" s="131"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A16" s="92" t="s">
+    <row r="16" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="109" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="123" t="s">
+      <c r="B16" s="93" t="s">
         <v>70</v>
       </c>
-      <c r="C16" s="123" t="s">
+      <c r="C16" s="93" t="s">
         <v>71</v>
       </c>
-      <c r="D16" s="105" t="s">
+      <c r="D16" s="90" t="s">
         <v>72</v>
       </c>
-      <c r="E16" s="104" t="s">
+      <c r="E16" s="108" t="s">
         <v>73</v>
       </c>
-      <c r="F16" s="104"/>
-      <c r="G16" s="104"/>
-      <c r="H16" s="103" t="s">
+      <c r="F16" s="108"/>
+      <c r="G16" s="108"/>
+      <c r="H16" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I16" s="104" t="s">
+      <c r="I16" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="106" t="s">
+      <c r="J16" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K16" s="22" t="s">
@@ -10341,24 +10342,24 @@
       <c r="U16" s="24"/>
       <c r="V16" s="24"/>
       <c r="W16" s="25"/>
-      <c r="X16" s="111"/>
-      <c r="Y16" s="130"/>
-      <c r="Z16" s="116"/>
-      <c r="AA16" s="117" t="s">
+      <c r="X16" s="94"/>
+      <c r="Y16" s="95"/>
+      <c r="Z16" s="115"/>
+      <c r="AA16" s="123" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A17" s="92"/>
-      <c r="B17" s="123"/>
-      <c r="C17" s="123"/>
-      <c r="D17" s="105"/>
-      <c r="E17" s="104"/>
-      <c r="F17" s="104"/>
-      <c r="G17" s="104"/>
-      <c r="H17" s="103"/>
-      <c r="I17" s="104"/>
-      <c r="J17" s="106"/>
+    <row r="17" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="109"/>
+      <c r="B17" s="93"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="90"/>
+      <c r="E17" s="108"/>
+      <c r="F17" s="108"/>
+      <c r="G17" s="108"/>
+      <c r="H17" s="111"/>
+      <c r="I17" s="108"/>
+      <c r="J17" s="107"/>
       <c r="K17" s="22" t="s">
         <v>55</v>
       </c>
@@ -10392,34 +10393,34 @@
       <c r="U17" s="19"/>
       <c r="V17" s="19"/>
       <c r="W17" s="28"/>
-      <c r="X17" s="111"/>
-      <c r="Y17" s="131"/>
-      <c r="Z17" s="116"/>
-      <c r="AA17" s="118"/>
+      <c r="X17" s="94"/>
+      <c r="Y17" s="96"/>
+      <c r="Z17" s="115"/>
+      <c r="AA17" s="124"/>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A18" s="92"/>
-      <c r="B18" s="123" t="s">
+    <row r="18" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="109"/>
+      <c r="B18" s="93" t="s">
         <v>75</v>
       </c>
-      <c r="C18" s="123" t="s">
+      <c r="C18" s="93" t="s">
         <v>71</v>
       </c>
-      <c r="D18" s="123" t="s">
+      <c r="D18" s="93" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="104" t="s">
+      <c r="E18" s="108" t="s">
         <v>73</v>
       </c>
-      <c r="F18" s="104"/>
-      <c r="G18" s="104"/>
-      <c r="H18" s="103" t="s">
+      <c r="F18" s="108"/>
+      <c r="G18" s="108"/>
+      <c r="H18" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I18" s="104" t="s">
+      <c r="I18" s="108" t="s">
         <v>77</v>
       </c>
-      <c r="J18" s="106" t="s">
+      <c r="J18" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K18" s="22" t="s">
@@ -10455,26 +10456,26 @@
       <c r="U18" s="47"/>
       <c r="V18" s="47"/>
       <c r="W18" s="47"/>
-      <c r="X18" s="135" t="s">
+      <c r="X18" s="158" t="s">
         <v>133</v>
       </c>
-      <c r="Y18" s="135"/>
-      <c r="Z18" s="132">
+      <c r="Y18" s="158"/>
+      <c r="Z18" s="155">
         <v>46108</v>
       </c>
-      <c r="AA18" s="134"/>
+      <c r="AA18" s="157"/>
     </row>
-    <row r="19" spans="1:27" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="92"/>
-      <c r="B19" s="123"/>
-      <c r="C19" s="123"/>
-      <c r="D19" s="123"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="104"/>
-      <c r="G19" s="104"/>
-      <c r="H19" s="103"/>
-      <c r="I19" s="104"/>
-      <c r="J19" s="106"/>
+    <row r="19" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="109"/>
+      <c r="B19" s="93"/>
+      <c r="C19" s="93"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="108"/>
+      <c r="F19" s="108"/>
+      <c r="G19" s="108"/>
+      <c r="H19" s="111"/>
+      <c r="I19" s="108"/>
+      <c r="J19" s="107"/>
       <c r="K19" s="22" t="s">
         <v>55</v>
       </c>
@@ -10508,34 +10509,34 @@
       <c r="U19" s="46"/>
       <c r="V19" s="46"/>
       <c r="W19" s="48"/>
-      <c r="X19" s="135"/>
-      <c r="Y19" s="135"/>
-      <c r="Z19" s="133"/>
-      <c r="AA19" s="134"/>
+      <c r="X19" s="158"/>
+      <c r="Y19" s="158"/>
+      <c r="Z19" s="156"/>
+      <c r="AA19" s="157"/>
     </row>
-    <row r="20" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="92"/>
-      <c r="B20" s="123" t="s">
+    <row r="20" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="109"/>
+      <c r="B20" s="93" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="123" t="s">
+      <c r="C20" s="93" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="105" t="s">
+      <c r="D20" s="90" t="s">
         <v>79</v>
       </c>
-      <c r="E20" s="104" t="s">
+      <c r="E20" s="108" t="s">
         <v>73</v>
       </c>
-      <c r="F20" s="104"/>
-      <c r="G20" s="104"/>
-      <c r="H20" s="103" t="s">
+      <c r="F20" s="108"/>
+      <c r="G20" s="108"/>
+      <c r="H20" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="I20" s="104" t="s">
+      <c r="I20" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="106" t="s">
+      <c r="J20" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K20" s="22" t="s">
@@ -10571,28 +10572,28 @@
       <c r="U20" s="18"/>
       <c r="V20" s="18"/>
       <c r="W20" s="27"/>
-      <c r="X20" s="167" t="s">
+      <c r="X20" s="99" t="s">
         <v>139</v>
       </c>
-      <c r="Y20" s="169" t="s">
+      <c r="Y20" s="101" t="s">
         <v>138</v>
       </c>
-      <c r="Z20" s="95"/>
-      <c r="AA20" s="153" t="s">
+      <c r="Z20" s="153"/>
+      <c r="AA20" s="125" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="92"/>
-      <c r="B21" s="123"/>
-      <c r="C21" s="123"/>
-      <c r="D21" s="105"/>
-      <c r="E21" s="104"/>
-      <c r="F21" s="104"/>
-      <c r="G21" s="104"/>
-      <c r="H21" s="103"/>
-      <c r="I21" s="104"/>
-      <c r="J21" s="106"/>
+    <row r="21" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="109"/>
+      <c r="B21" s="93"/>
+      <c r="C21" s="93"/>
+      <c r="D21" s="90"/>
+      <c r="E21" s="108"/>
+      <c r="F21" s="108"/>
+      <c r="G21" s="108"/>
+      <c r="H21" s="111"/>
+      <c r="I21" s="108"/>
+      <c r="J21" s="107"/>
       <c r="K21" s="22" t="s">
         <v>55</v>
       </c>
@@ -10626,36 +10627,36 @@
       <c r="U21" s="29"/>
       <c r="V21" s="29"/>
       <c r="W21" s="30"/>
-      <c r="X21" s="168"/>
-      <c r="Y21" s="170"/>
-      <c r="Z21" s="94"/>
-      <c r="AA21" s="153"/>
+      <c r="X21" s="100"/>
+      <c r="Y21" s="102"/>
+      <c r="Z21" s="119"/>
+      <c r="AA21" s="125"/>
     </row>
-    <row r="22" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="92" t="s">
+    <row r="22" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="109" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="123" t="s">
+      <c r="B22" s="93" t="s">
         <v>81</v>
       </c>
-      <c r="C22" s="124" t="s">
+      <c r="C22" s="122" t="s">
         <v>82</v>
       </c>
-      <c r="D22" s="123" t="s">
+      <c r="D22" s="93" t="s">
         <v>83</v>
       </c>
-      <c r="E22" s="104">
+      <c r="E22" s="108">
         <v>90</v>
       </c>
-      <c r="F22" s="104"/>
-      <c r="G22" s="104"/>
-      <c r="H22" s="103" t="s">
+      <c r="F22" s="108"/>
+      <c r="G22" s="108"/>
+      <c r="H22" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="104" t="s">
+      <c r="I22" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J22" s="106" t="s">
+      <c r="J22" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K22" s="22" t="s">
@@ -10697,24 +10698,24 @@
       <c r="W22" s="27">
         <v>0.9</v>
       </c>
-      <c r="X22" s="171"/>
-      <c r="Y22" s="130"/>
-      <c r="Z22" s="115">
+      <c r="X22" s="105"/>
+      <c r="Y22" s="95"/>
+      <c r="Z22" s="114">
         <v>46257</v>
       </c>
-      <c r="AA22" s="113"/>
+      <c r="AA22" s="162"/>
     </row>
-    <row r="23" spans="1:27" ht="17.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="93"/>
-      <c r="B23" s="123"/>
-      <c r="C23" s="124"/>
-      <c r="D23" s="123"/>
-      <c r="E23" s="104"/>
-      <c r="F23" s="104"/>
-      <c r="G23" s="104"/>
-      <c r="H23" s="103"/>
-      <c r="I23" s="104"/>
-      <c r="J23" s="106"/>
+    <row r="23" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="169"/>
+      <c r="B23" s="93"/>
+      <c r="C23" s="122"/>
+      <c r="D23" s="93"/>
+      <c r="E23" s="108"/>
+      <c r="F23" s="108"/>
+      <c r="G23" s="108"/>
+      <c r="H23" s="111"/>
+      <c r="I23" s="108"/>
+      <c r="J23" s="107"/>
       <c r="K23" s="22" t="s">
         <v>55</v>
       </c>
@@ -10748,40 +10749,40 @@
       <c r="U23" s="29"/>
       <c r="V23" s="29"/>
       <c r="W23" s="30"/>
-      <c r="X23" s="110"/>
-      <c r="Y23" s="131"/>
-      <c r="Z23" s="116"/>
-      <c r="AA23" s="114"/>
+      <c r="X23" s="106"/>
+      <c r="Y23" s="96"/>
+      <c r="Z23" s="115"/>
+      <c r="AA23" s="163"/>
     </row>
-    <row r="24" spans="1:27" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="90" t="s">
+    <row r="24" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="143" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="123" t="s">
+      <c r="B24" s="93" t="s">
         <v>84</v>
       </c>
-      <c r="C24" s="124" t="s">
+      <c r="C24" s="122" t="s">
         <v>85</v>
       </c>
-      <c r="D24" s="105" t="s">
+      <c r="D24" s="90" t="s">
         <v>86</v>
       </c>
-      <c r="E24" s="104" t="s">
+      <c r="E24" s="108" t="s">
         <v>87</v>
       </c>
-      <c r="F24" s="104" t="s">
+      <c r="F24" s="108" t="s">
         <v>87</v>
       </c>
-      <c r="G24" s="104" t="s">
+      <c r="G24" s="108" t="s">
         <v>87</v>
       </c>
-      <c r="H24" s="103" t="s">
+      <c r="H24" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="104" t="s">
+      <c r="I24" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J24" s="102" t="s">
+      <c r="J24" s="120" t="s">
         <v>34</v>
       </c>
       <c r="K24" s="22" t="s">
@@ -10808,31 +10809,27 @@
         <v>88</v>
       </c>
       <c r="T24" s="35"/>
-      <c r="U24" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="V24" s="21" t="s">
-        <v>88</v>
-      </c>
+      <c r="U24" s="21"/>
+      <c r="V24" s="21"/>
       <c r="W24" s="38"/>
-      <c r="X24" s="109"/>
-      <c r="Y24" s="100"/>
-      <c r="Z24" s="94"/>
-      <c r="AA24" s="117" t="s">
+      <c r="X24" s="137"/>
+      <c r="Y24" s="154"/>
+      <c r="Z24" s="119"/>
+      <c r="AA24" s="123" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="91"/>
-      <c r="B25" s="123"/>
-      <c r="C25" s="124"/>
-      <c r="D25" s="105"/>
-      <c r="E25" s="104"/>
-      <c r="F25" s="104"/>
-      <c r="G25" s="104"/>
-      <c r="H25" s="103"/>
-      <c r="I25" s="104"/>
-      <c r="J25" s="102"/>
+      <c r="A25" s="168"/>
+      <c r="B25" s="93"/>
+      <c r="C25" s="122"/>
+      <c r="D25" s="90"/>
+      <c r="E25" s="108"/>
+      <c r="F25" s="108"/>
+      <c r="G25" s="108"/>
+      <c r="H25" s="111"/>
+      <c r="I25" s="108"/>
+      <c r="J25" s="120"/>
       <c r="K25" s="22" t="s">
         <v>55</v>
       </c>
@@ -10861,41 +10858,37 @@
         <v>88</v>
       </c>
       <c r="T25" s="55"/>
-      <c r="U25" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="V25" s="21" t="s">
-        <v>88</v>
-      </c>
+      <c r="U25" s="21"/>
+      <c r="V25" s="21"/>
       <c r="W25" s="55"/>
-      <c r="X25" s="110"/>
-      <c r="Y25" s="101"/>
-      <c r="Z25" s="95"/>
-      <c r="AA25" s="118"/>
+      <c r="X25" s="106"/>
+      <c r="Y25" s="113"/>
+      <c r="Z25" s="153"/>
+      <c r="AA25" s="124"/>
     </row>
-    <row r="26" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="91"/>
-      <c r="B26" s="125" t="s">
+    <row r="26" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="168"/>
+      <c r="B26" s="91" t="s">
         <v>90</v>
       </c>
-      <c r="C26" s="126" t="s">
+      <c r="C26" s="161" t="s">
         <v>85</v>
       </c>
-      <c r="D26" s="105" t="s">
+      <c r="D26" s="90" t="s">
         <v>91</v>
       </c>
-      <c r="E26" s="104">
+      <c r="E26" s="108">
         <v>34</v>
       </c>
-      <c r="F26" s="112"/>
-      <c r="G26" s="112"/>
-      <c r="H26" s="103" t="s">
+      <c r="F26" s="159"/>
+      <c r="G26" s="159"/>
+      <c r="H26" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I26" s="104" t="s">
+      <c r="I26" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J26" s="106" t="s">
+      <c r="J26" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K26" s="22" t="s">
@@ -10931,24 +10924,24 @@
       <c r="U26" s="24"/>
       <c r="V26" s="24"/>
       <c r="W26" s="25"/>
-      <c r="X26" s="111"/>
-      <c r="Y26" s="131"/>
-      <c r="Z26" s="116"/>
-      <c r="AA26" s="117" t="s">
+      <c r="X26" s="94"/>
+      <c r="Y26" s="96"/>
+      <c r="Z26" s="115"/>
+      <c r="AA26" s="123" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="91"/>
-      <c r="B27" s="125"/>
-      <c r="C27" s="126"/>
-      <c r="D27" s="105"/>
-      <c r="E27" s="104"/>
-      <c r="F27" s="112"/>
-      <c r="G27" s="112"/>
-      <c r="H27" s="103"/>
-      <c r="I27" s="104"/>
-      <c r="J27" s="106"/>
+    <row r="27" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="168"/>
+      <c r="B27" s="91"/>
+      <c r="C27" s="161"/>
+      <c r="D27" s="90"/>
+      <c r="E27" s="108"/>
+      <c r="F27" s="159"/>
+      <c r="G27" s="159"/>
+      <c r="H27" s="111"/>
+      <c r="I27" s="108"/>
+      <c r="J27" s="107"/>
       <c r="K27" s="22" t="s">
         <v>55</v>
       </c>
@@ -10982,34 +10975,34 @@
       <c r="U27" s="19"/>
       <c r="V27" s="19"/>
       <c r="W27" s="28"/>
-      <c r="X27" s="111"/>
-      <c r="Y27" s="131"/>
-      <c r="Z27" s="116"/>
-      <c r="AA27" s="118"/>
+      <c r="X27" s="94"/>
+      <c r="Y27" s="96"/>
+      <c r="Z27" s="115"/>
+      <c r="AA27" s="124"/>
     </row>
-    <row r="28" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="91"/>
-      <c r="B28" s="105" t="s">
+    <row r="28" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="168"/>
+      <c r="B28" s="90" t="s">
         <v>93</v>
       </c>
-      <c r="C28" s="123" t="s">
+      <c r="C28" s="93" t="s">
         <v>71</v>
       </c>
-      <c r="D28" s="105" t="s">
+      <c r="D28" s="90" t="s">
         <v>94</v>
       </c>
-      <c r="E28" s="104" t="s">
+      <c r="E28" s="108" t="s">
         <v>73</v>
       </c>
-      <c r="F28" s="104"/>
-      <c r="G28" s="104"/>
-      <c r="H28" s="103" t="s">
+      <c r="F28" s="108"/>
+      <c r="G28" s="108"/>
+      <c r="H28" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I28" s="104" t="s">
+      <c r="I28" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J28" s="106" t="s">
+      <c r="J28" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K28" s="22" t="s">
@@ -11045,26 +11038,26 @@
       <c r="U28" s="24"/>
       <c r="V28" s="24"/>
       <c r="W28" s="25"/>
-      <c r="X28" s="159" t="s">
+      <c r="X28" s="103" t="s">
         <v>134</v>
       </c>
-      <c r="Y28" s="96"/>
-      <c r="Z28" s="94"/>
-      <c r="AA28" s="154" t="s">
+      <c r="Y28" s="97"/>
+      <c r="Z28" s="119"/>
+      <c r="AA28" s="128" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="91"/>
-      <c r="B29" s="105"/>
-      <c r="C29" s="123"/>
-      <c r="D29" s="105"/>
-      <c r="E29" s="104"/>
-      <c r="F29" s="104"/>
-      <c r="G29" s="104"/>
-      <c r="H29" s="103"/>
-      <c r="I29" s="104"/>
-      <c r="J29" s="106"/>
+      <c r="A29" s="168"/>
+      <c r="B29" s="90"/>
+      <c r="C29" s="93"/>
+      <c r="D29" s="90"/>
+      <c r="E29" s="108"/>
+      <c r="F29" s="108"/>
+      <c r="G29" s="108"/>
+      <c r="H29" s="111"/>
+      <c r="I29" s="108"/>
+      <c r="J29" s="107"/>
       <c r="K29" s="22" t="s">
         <v>55</v>
       </c>
@@ -11098,32 +11091,32 @@
       <c r="U29" s="19"/>
       <c r="V29" s="19"/>
       <c r="W29" s="28"/>
-      <c r="X29" s="160"/>
-      <c r="Y29" s="97"/>
-      <c r="Z29" s="95"/>
-      <c r="AA29" s="155"/>
+      <c r="X29" s="104"/>
+      <c r="Y29" s="98"/>
+      <c r="Z29" s="153"/>
+      <c r="AA29" s="129"/>
     </row>
-    <row r="30" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="91"/>
-      <c r="B30" s="105"/>
-      <c r="C30" s="123" t="s">
+    <row r="30" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="168"/>
+      <c r="B30" s="90"/>
+      <c r="C30" s="93" t="s">
         <v>71</v>
       </c>
-      <c r="D30" s="105" t="s">
+      <c r="D30" s="90" t="s">
         <v>96</v>
       </c>
-      <c r="E30" s="104" t="s">
+      <c r="E30" s="108" t="s">
         <v>73</v>
       </c>
-      <c r="F30" s="104"/>
-      <c r="G30" s="104"/>
-      <c r="H30" s="103" t="s">
+      <c r="F30" s="108"/>
+      <c r="G30" s="108"/>
+      <c r="H30" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I30" s="104" t="s">
+      <c r="I30" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J30" s="106" t="s">
+      <c r="J30" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K30" s="22" t="s">
@@ -11159,22 +11152,22 @@
       <c r="U30" s="24"/>
       <c r="V30" s="24"/>
       <c r="W30" s="25"/>
-      <c r="X30" s="159"/>
-      <c r="Y30" s="100"/>
-      <c r="Z30" s="94"/>
-      <c r="AA30" s="107"/>
+      <c r="X30" s="103"/>
+      <c r="Y30" s="154"/>
+      <c r="Z30" s="119"/>
+      <c r="AA30" s="166"/>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A31" s="91"/>
-      <c r="B31" s="105"/>
-      <c r="C31" s="123"/>
-      <c r="D31" s="105"/>
-      <c r="E31" s="104"/>
-      <c r="F31" s="104"/>
-      <c r="G31" s="104"/>
-      <c r="H31" s="103"/>
-      <c r="I31" s="104"/>
-      <c r="J31" s="106"/>
+    <row r="31" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="168"/>
+      <c r="B31" s="90"/>
+      <c r="C31" s="93"/>
+      <c r="D31" s="90"/>
+      <c r="E31" s="108"/>
+      <c r="F31" s="108"/>
+      <c r="G31" s="108"/>
+      <c r="H31" s="111"/>
+      <c r="I31" s="108"/>
+      <c r="J31" s="107"/>
       <c r="K31" s="22" t="s">
         <v>55</v>
       </c>
@@ -11208,34 +11201,34 @@
       <c r="U31" s="44"/>
       <c r="V31" s="44"/>
       <c r="W31" s="45"/>
-      <c r="X31" s="160"/>
-      <c r="Y31" s="101"/>
-      <c r="Z31" s="95"/>
-      <c r="AA31" s="108"/>
+      <c r="X31" s="104"/>
+      <c r="Y31" s="113"/>
+      <c r="Z31" s="153"/>
+      <c r="AA31" s="167"/>
     </row>
-    <row r="32" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="91"/>
-      <c r="B32" s="123" t="s">
+    <row r="32" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="168"/>
+      <c r="B32" s="93" t="s">
         <v>97</v>
       </c>
-      <c r="C32" s="124" t="s">
+      <c r="C32" s="122" t="s">
         <v>64</v>
       </c>
-      <c r="D32" s="105" t="s">
+      <c r="D32" s="90" t="s">
         <v>98</v>
       </c>
-      <c r="E32" s="104" t="s">
+      <c r="E32" s="108" t="s">
         <v>73</v>
       </c>
-      <c r="F32" s="104"/>
-      <c r="G32" s="104"/>
-      <c r="H32" s="103" t="s">
+      <c r="F32" s="108"/>
+      <c r="G32" s="108"/>
+      <c r="H32" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I32" s="104" t="s">
+      <c r="I32" s="108" t="s">
         <v>77</v>
       </c>
-      <c r="J32" s="106" t="s">
+      <c r="J32" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K32" s="22" t="s">
@@ -11271,28 +11264,28 @@
       <c r="U32" s="8"/>
       <c r="V32" s="8"/>
       <c r="W32" s="33"/>
-      <c r="X32" s="98" t="s">
+      <c r="X32" s="170" t="s">
         <v>135</v>
       </c>
-      <c r="Y32" s="96" t="s">
+      <c r="Y32" s="97" t="s">
         <v>137</v>
       </c>
-      <c r="Z32" s="94"/>
-      <c r="AA32" s="117" t="s">
+      <c r="Z32" s="119"/>
+      <c r="AA32" s="123" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="91"/>
-      <c r="B33" s="123"/>
-      <c r="C33" s="124"/>
-      <c r="D33" s="105"/>
-      <c r="E33" s="104"/>
-      <c r="F33" s="104"/>
-      <c r="G33" s="104"/>
-      <c r="H33" s="103"/>
-      <c r="I33" s="104"/>
-      <c r="J33" s="106"/>
+    <row r="33" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="168"/>
+      <c r="B33" s="93"/>
+      <c r="C33" s="122"/>
+      <c r="D33" s="90"/>
+      <c r="E33" s="108"/>
+      <c r="F33" s="108"/>
+      <c r="G33" s="108"/>
+      <c r="H33" s="111"/>
+      <c r="I33" s="108"/>
+      <c r="J33" s="107"/>
       <c r="K33" s="22" t="s">
         <v>55</v>
       </c>
@@ -11326,36 +11319,36 @@
       <c r="U33" s="31"/>
       <c r="V33" s="31"/>
       <c r="W33" s="32"/>
-      <c r="X33" s="99"/>
-      <c r="Y33" s="97"/>
-      <c r="Z33" s="95"/>
-      <c r="AA33" s="118"/>
+      <c r="X33" s="171"/>
+      <c r="Y33" s="98"/>
+      <c r="Z33" s="153"/>
+      <c r="AA33" s="124"/>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A34" s="92" t="s">
+    <row r="34" spans="1:29" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="109" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="144" t="s">
+      <c r="B34" s="148" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="123" t="s">
+      <c r="C34" s="93" t="s">
         <v>82</v>
       </c>
-      <c r="D34" s="105" t="s">
+      <c r="D34" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="E34" s="104">
+      <c r="E34" s="108">
         <v>90</v>
       </c>
-      <c r="F34" s="104"/>
-      <c r="G34" s="104"/>
-      <c r="H34" s="103" t="s">
+      <c r="F34" s="108"/>
+      <c r="G34" s="108"/>
+      <c r="H34" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I34" s="104" t="s">
+      <c r="I34" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J34" s="102" t="s">
+      <c r="J34" s="120" t="s">
         <v>34</v>
       </c>
       <c r="K34" s="22" t="s">
@@ -11381,26 +11374,26 @@
       <c r="W34" s="25">
         <v>0.9</v>
       </c>
-      <c r="X34" s="111"/>
-      <c r="Y34" s="131" t="s">
+      <c r="X34" s="94"/>
+      <c r="Y34" s="96" t="s">
         <v>136</v>
       </c>
-      <c r="Z34" s="116"/>
-      <c r="AA34" s="117" t="s">
+      <c r="Z34" s="115"/>
+      <c r="AA34" s="123" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A35" s="92"/>
-      <c r="B35" s="144"/>
-      <c r="C35" s="123"/>
-      <c r="D35" s="105"/>
-      <c r="E35" s="104"/>
-      <c r="F35" s="104"/>
-      <c r="G35" s="104"/>
-      <c r="H35" s="103"/>
-      <c r="I35" s="104"/>
-      <c r="J35" s="102"/>
+    <row r="35" spans="1:29" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="109"/>
+      <c r="B35" s="148"/>
+      <c r="C35" s="93"/>
+      <c r="D35" s="90"/>
+      <c r="E35" s="108"/>
+      <c r="F35" s="108"/>
+      <c r="G35" s="108"/>
+      <c r="H35" s="111"/>
+      <c r="I35" s="108"/>
+      <c r="J35" s="120"/>
       <c r="K35" s="22" t="s">
         <v>55</v>
       </c>
@@ -11434,34 +11427,34 @@
       <c r="U35" s="19"/>
       <c r="V35" s="19"/>
       <c r="W35" s="28"/>
-      <c r="X35" s="111"/>
-      <c r="Y35" s="131"/>
-      <c r="Z35" s="116"/>
-      <c r="AA35" s="118"/>
+      <c r="X35" s="94"/>
+      <c r="Y35" s="96"/>
+      <c r="Z35" s="115"/>
+      <c r="AA35" s="124"/>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A36" s="92"/>
-      <c r="B36" s="144" t="s">
+    <row r="36" spans="1:29" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="109"/>
+      <c r="B36" s="148" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="123" t="s">
+      <c r="C36" s="93" t="s">
         <v>101</v>
       </c>
-      <c r="D36" s="105" t="s">
+      <c r="D36" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="E36" s="104">
+      <c r="E36" s="108">
         <v>83</v>
       </c>
-      <c r="F36" s="104"/>
-      <c r="G36" s="104"/>
-      <c r="H36" s="103" t="s">
+      <c r="F36" s="108"/>
+      <c r="G36" s="108"/>
+      <c r="H36" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I36" s="104" t="s">
+      <c r="I36" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J36" s="161" t="s">
+      <c r="J36" s="121" t="s">
         <v>38</v>
       </c>
       <c r="K36" s="22" t="s">
@@ -11483,28 +11476,28 @@
       <c r="U36" s="18"/>
       <c r="V36" s="18"/>
       <c r="W36" s="27"/>
-      <c r="X36" s="111" t="s">
+      <c r="X36" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="Y36" s="130" t="s">
+      <c r="Y36" s="95" t="s">
         <v>103</v>
       </c>
-      <c r="Z36" s="116"/>
-      <c r="AA36" s="117" t="s">
+      <c r="Z36" s="115"/>
+      <c r="AA36" s="123" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A37" s="92"/>
-      <c r="B37" s="144"/>
-      <c r="C37" s="123"/>
-      <c r="D37" s="105"/>
-      <c r="E37" s="104"/>
-      <c r="F37" s="104"/>
-      <c r="G37" s="104"/>
-      <c r="H37" s="103"/>
-      <c r="I37" s="104"/>
-      <c r="J37" s="161"/>
+    <row r="37" spans="1:29" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A37" s="109"/>
+      <c r="B37" s="148"/>
+      <c r="C37" s="93"/>
+      <c r="D37" s="90"/>
+      <c r="E37" s="108"/>
+      <c r="F37" s="108"/>
+      <c r="G37" s="108"/>
+      <c r="H37" s="111"/>
+      <c r="I37" s="108"/>
+      <c r="J37" s="121"/>
       <c r="K37" s="22" t="s">
         <v>55</v>
       </c>
@@ -11534,45 +11527,45 @@
       <c r="U37" s="56"/>
       <c r="V37" s="56"/>
       <c r="W37" s="57"/>
-      <c r="X37" s="109"/>
-      <c r="Y37" s="96"/>
-      <c r="Z37" s="94"/>
-      <c r="AA37" s="153"/>
+      <c r="X37" s="137"/>
+      <c r="Y37" s="97"/>
+      <c r="Z37" s="119"/>
+      <c r="AA37" s="125"/>
     </row>
-    <row r="38" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="147"/>
-      <c r="B38" s="147"/>
-      <c r="C38" s="147"/>
-      <c r="D38" s="147"/>
-      <c r="E38" s="147"/>
-      <c r="F38" s="147"/>
-      <c r="G38" s="147"/>
-      <c r="H38" s="147"/>
-      <c r="I38" s="147"/>
-      <c r="J38" s="147"/>
-      <c r="K38" s="147"/>
-      <c r="L38" s="147"/>
-      <c r="M38" s="147"/>
-      <c r="N38" s="147"/>
-      <c r="O38" s="147"/>
-      <c r="P38" s="148"/>
-      <c r="Q38" s="148"/>
-      <c r="R38" s="148"/>
-      <c r="S38" s="148"/>
-      <c r="T38" s="148"/>
-      <c r="U38" s="148"/>
-      <c r="V38" s="148"/>
-      <c r="W38" s="148"/>
-      <c r="X38" s="148"/>
-      <c r="Y38" s="148"/>
-      <c r="Z38" s="148"/>
-      <c r="AA38" s="148"/>
+    <row r="38" spans="1:29" s="5" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="138"/>
+      <c r="B38" s="138"/>
+      <c r="C38" s="138"/>
+      <c r="D38" s="138"/>
+      <c r="E38" s="138"/>
+      <c r="F38" s="138"/>
+      <c r="G38" s="138"/>
+      <c r="H38" s="138"/>
+      <c r="I38" s="138"/>
+      <c r="J38" s="138"/>
+      <c r="K38" s="138"/>
+      <c r="L38" s="138"/>
+      <c r="M38" s="138"/>
+      <c r="N38" s="138"/>
+      <c r="O38" s="138"/>
+      <c r="P38" s="139"/>
+      <c r="Q38" s="139"/>
+      <c r="R38" s="139"/>
+      <c r="S38" s="139"/>
+      <c r="T38" s="139"/>
+      <c r="U38" s="139"/>
+      <c r="V38" s="139"/>
+      <c r="W38" s="139"/>
+      <c r="X38" s="139"/>
+      <c r="Y38" s="139"/>
+      <c r="Z38" s="139"/>
+      <c r="AA38" s="139"/>
     </row>
-    <row r="39" spans="1:29" s="5" customFormat="1" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="149" t="s">
+    <row r="39" spans="1:29" s="5" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="141" t="s">
         <v>106</v>
       </c>
-      <c r="B39" s="149"/>
+      <c r="B39" s="141"/>
       <c r="C39" s="58"/>
       <c r="D39"/>
       <c r="E39"/>
@@ -11599,7 +11592,7 @@
       <c r="Z39"/>
       <c r="AA39" s="13"/>
     </row>
-    <row r="40" spans="1:29" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="43" t="s">
         <v>0</v>
       </c>
@@ -11682,35 +11675,35 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A41" s="150" t="s">
+    <row r="41" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="142" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="151" t="s">
+      <c r="B41" s="145" t="s">
         <v>113</v>
       </c>
-      <c r="C41" s="152" t="s">
+      <c r="C41" s="146" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="143" t="s">
+      <c r="D41" s="147" t="s">
         <v>114</v>
       </c>
-      <c r="E41" s="121" t="s">
+      <c r="E41" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="F41" s="121" t="s">
+      <c r="F41" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="G41" s="121" t="s">
+      <c r="G41" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="H41" s="122" t="s">
+      <c r="H41" s="160" t="s">
         <v>51</v>
       </c>
-      <c r="I41" s="121" t="s">
+      <c r="I41" s="140" t="s">
         <v>33</v>
       </c>
-      <c r="J41" s="138" t="s">
+      <c r="J41" s="149" t="s">
         <v>52</v>
       </c>
       <c r="K41" s="61" t="s">
@@ -11752,25 +11745,25 @@
       <c r="W41" s="63">
         <v>3.32E-2</v>
       </c>
-      <c r="X41" s="158"/>
-      <c r="Y41" s="128"/>
-      <c r="Z41" s="128"/>
-      <c r="AA41" s="118" t="s">
+      <c r="X41" s="136"/>
+      <c r="Y41" s="131"/>
+      <c r="Z41" s="131"/>
+      <c r="AA41" s="124" t="s">
         <v>113</v>
       </c>
       <c r="AC41" s="12"/>
     </row>
-    <row r="42" spans="1:29" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="90"/>
-      <c r="B42" s="125"/>
-      <c r="C42" s="137"/>
-      <c r="D42" s="105"/>
-      <c r="E42" s="104"/>
-      <c r="F42" s="104"/>
-      <c r="G42" s="104"/>
-      <c r="H42" s="103"/>
-      <c r="I42" s="104"/>
-      <c r="J42" s="139"/>
+    <row r="42" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="143"/>
+      <c r="B42" s="91"/>
+      <c r="C42" s="92"/>
+      <c r="D42" s="90"/>
+      <c r="E42" s="108"/>
+      <c r="F42" s="108"/>
+      <c r="G42" s="108"/>
+      <c r="H42" s="111"/>
+      <c r="I42" s="108"/>
+      <c r="J42" s="127"/>
       <c r="K42" s="22" t="s">
         <v>55</v>
       </c>
@@ -11804,40 +11797,40 @@
       <c r="U42" s="55"/>
       <c r="V42" s="55"/>
       <c r="W42" s="59"/>
-      <c r="X42" s="158"/>
-      <c r="Y42" s="128"/>
-      <c r="Z42" s="128"/>
-      <c r="AA42" s="145"/>
+      <c r="X42" s="136"/>
+      <c r="Y42" s="131"/>
+      <c r="Z42" s="131"/>
+      <c r="AA42" s="126"/>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A43" s="136" t="s">
+    <row r="43" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="144" t="s">
         <v>26</v>
       </c>
-      <c r="B43" s="125" t="s">
+      <c r="B43" s="91" t="s">
         <v>115</v>
       </c>
-      <c r="C43" s="137" t="s">
+      <c r="C43" s="92" t="s">
         <v>85</v>
       </c>
-      <c r="D43" s="105" t="s">
+      <c r="D43" s="90" t="s">
         <v>116</v>
       </c>
-      <c r="E43" s="104" t="s">
+      <c r="E43" s="108" t="s">
         <v>87</v>
       </c>
-      <c r="F43" s="104" t="s">
+      <c r="F43" s="108" t="s">
         <v>87</v>
       </c>
-      <c r="G43" s="104" t="s">
+      <c r="G43" s="108" t="s">
         <v>87</v>
       </c>
-      <c r="H43" s="103" t="s">
+      <c r="H43" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I43" s="104" t="s">
+      <c r="I43" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J43" s="102" t="s">
+      <c r="J43" s="120" t="s">
         <v>34</v>
       </c>
       <c r="K43" s="22" t="s">
@@ -11859,28 +11852,28 @@
       <c r="U43" s="35"/>
       <c r="V43" s="35"/>
       <c r="W43" s="38"/>
-      <c r="X43" s="146" t="s">
+      <c r="X43" s="130" t="s">
         <v>117</v>
       </c>
-      <c r="Y43" s="141" t="s">
+      <c r="Y43" s="132" t="s">
         <v>118</v>
       </c>
-      <c r="Z43" s="140"/>
-      <c r="AA43" s="156" t="s">
+      <c r="Z43" s="133"/>
+      <c r="AA43" s="134" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A44" s="136"/>
-      <c r="B44" s="125"/>
-      <c r="C44" s="137"/>
-      <c r="D44" s="105"/>
-      <c r="E44" s="104"/>
-      <c r="F44" s="104"/>
-      <c r="G44" s="104"/>
-      <c r="H44" s="103"/>
-      <c r="I44" s="112"/>
-      <c r="J44" s="102"/>
+    <row r="44" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="144"/>
+      <c r="B44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="90"/>
+      <c r="E44" s="108"/>
+      <c r="F44" s="108"/>
+      <c r="G44" s="108"/>
+      <c r="H44" s="111"/>
+      <c r="I44" s="159"/>
+      <c r="J44" s="120"/>
       <c r="K44" s="22" t="s">
         <v>55</v>
       </c>
@@ -11916,38 +11909,38 @@
         <v>88</v>
       </c>
       <c r="W44" s="55"/>
-      <c r="X44" s="146"/>
-      <c r="Y44" s="141"/>
-      <c r="Z44" s="140"/>
-      <c r="AA44" s="156"/>
+      <c r="X44" s="130"/>
+      <c r="Y44" s="132"/>
+      <c r="Z44" s="133"/>
+      <c r="AA44" s="134"/>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A45" s="136"/>
-      <c r="B45" s="125" t="s">
+    <row r="45" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="144"/>
+      <c r="B45" s="91" t="s">
         <v>120</v>
       </c>
-      <c r="C45" s="137" t="s">
+      <c r="C45" s="92" t="s">
         <v>85</v>
       </c>
-      <c r="D45" s="105" t="s">
+      <c r="D45" s="90" t="s">
         <v>121</v>
       </c>
-      <c r="E45" s="104" t="s">
+      <c r="E45" s="108" t="s">
         <v>87</v>
       </c>
-      <c r="F45" s="104" t="s">
+      <c r="F45" s="108" t="s">
         <v>87</v>
       </c>
-      <c r="G45" s="104" t="s">
+      <c r="G45" s="108" t="s">
         <v>87</v>
       </c>
-      <c r="H45" s="103" t="s">
+      <c r="H45" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I45" s="104" t="s">
+      <c r="I45" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J45" s="139" t="s">
+      <c r="J45" s="127" t="s">
         <v>52</v>
       </c>
       <c r="K45" s="22" t="s">
@@ -11983,28 +11976,28 @@
       <c r="U45" s="35"/>
       <c r="V45" s="35"/>
       <c r="W45" s="38"/>
-      <c r="X45" s="146"/>
-      <c r="Y45" s="141" t="s">
+      <c r="X45" s="130"/>
+      <c r="Y45" s="132" t="s">
         <v>122</v>
       </c>
-      <c r="Z45" s="157">
+      <c r="Z45" s="135">
         <v>46188</v>
       </c>
-      <c r="AA45" s="145" t="s">
+      <c r="AA45" s="126" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="136"/>
-      <c r="B46" s="125"/>
-      <c r="C46" s="137"/>
-      <c r="D46" s="105"/>
-      <c r="E46" s="104"/>
-      <c r="F46" s="104"/>
-      <c r="G46" s="104"/>
-      <c r="H46" s="103"/>
-      <c r="I46" s="104"/>
-      <c r="J46" s="139"/>
+    <row r="46" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="144"/>
+      <c r="B46" s="91"/>
+      <c r="C46" s="92"/>
+      <c r="D46" s="90"/>
+      <c r="E46" s="108"/>
+      <c r="F46" s="108"/>
+      <c r="G46" s="108"/>
+      <c r="H46" s="111"/>
+      <c r="I46" s="108"/>
+      <c r="J46" s="127"/>
       <c r="K46" s="22" t="s">
         <v>55</v>
       </c>
@@ -12038,38 +12031,38 @@
       <c r="U46" s="19"/>
       <c r="V46" s="19"/>
       <c r="W46" s="28"/>
-      <c r="X46" s="146"/>
-      <c r="Y46" s="140"/>
-      <c r="Z46" s="140"/>
-      <c r="AA46" s="145"/>
+      <c r="X46" s="130"/>
+      <c r="Y46" s="133"/>
+      <c r="Z46" s="133"/>
+      <c r="AA46" s="126"/>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A47" s="136"/>
-      <c r="B47" s="125" t="s">
+    <row r="47" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="144"/>
+      <c r="B47" s="91" t="s">
         <v>123</v>
       </c>
-      <c r="C47" s="137" t="s">
+      <c r="C47" s="92" t="s">
         <v>82</v>
       </c>
-      <c r="D47" s="105" t="s">
+      <c r="D47" s="90" t="s">
         <v>124</v>
       </c>
-      <c r="E47" s="104" t="s">
+      <c r="E47" s="108" t="s">
         <v>87</v>
       </c>
-      <c r="F47" s="104" t="s">
+      <c r="F47" s="108" t="s">
         <v>87</v>
       </c>
-      <c r="G47" s="104" t="s">
+      <c r="G47" s="108" t="s">
         <v>87</v>
       </c>
-      <c r="H47" s="103" t="s">
+      <c r="H47" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I47" s="104" t="s">
+      <c r="I47" s="108" t="s">
         <v>77</v>
       </c>
-      <c r="J47" s="139" t="s">
+      <c r="J47" s="127" t="s">
         <v>52</v>
       </c>
       <c r="K47" s="22" t="s">
@@ -12111,24 +12104,24 @@
       <c r="W47" s="39">
         <v>67</v>
       </c>
-      <c r="X47" s="146"/>
-      <c r="Y47" s="140"/>
-      <c r="Z47" s="140"/>
-      <c r="AA47" s="105" t="s">
+      <c r="X47" s="130"/>
+      <c r="Y47" s="133"/>
+      <c r="Z47" s="133"/>
+      <c r="AA47" s="90" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="48" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="136"/>
-      <c r="B48" s="125"/>
-      <c r="C48" s="137"/>
-      <c r="D48" s="105"/>
-      <c r="E48" s="104"/>
-      <c r="F48" s="104"/>
-      <c r="G48" s="104"/>
-      <c r="H48" s="103"/>
-      <c r="I48" s="104"/>
-      <c r="J48" s="139"/>
+      <c r="A48" s="144"/>
+      <c r="B48" s="91"/>
+      <c r="C48" s="92"/>
+      <c r="D48" s="90"/>
+      <c r="E48" s="108"/>
+      <c r="F48" s="108"/>
+      <c r="G48" s="108"/>
+      <c r="H48" s="111"/>
+      <c r="I48" s="108"/>
+      <c r="J48" s="127"/>
       <c r="K48" s="22" t="s">
         <v>55</v>
       </c>
@@ -12163,40 +12156,40 @@
       <c r="U48" s="9"/>
       <c r="V48" s="9"/>
       <c r="W48" s="26"/>
-      <c r="X48" s="146"/>
-      <c r="Y48" s="140"/>
-      <c r="Z48" s="140"/>
-      <c r="AA48" s="105"/>
+      <c r="X48" s="130"/>
+      <c r="Y48" s="133"/>
+      <c r="Z48" s="133"/>
+      <c r="AA48" s="90"/>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A49" s="90" t="s">
+    <row r="49" spans="1:27" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="143" t="s">
         <v>126</v>
       </c>
-      <c r="B49" s="142" t="s">
+      <c r="B49" s="150" t="s">
         <v>127</v>
       </c>
-      <c r="C49" s="137" t="s">
+      <c r="C49" s="92" t="s">
         <v>68</v>
       </c>
-      <c r="D49" s="105" t="s">
+      <c r="D49" s="90" t="s">
         <v>128</v>
       </c>
-      <c r="E49" s="104">
+      <c r="E49" s="108">
         <v>74</v>
       </c>
-      <c r="F49" s="104" t="s">
+      <c r="F49" s="108" t="s">
         <v>87</v>
       </c>
-      <c r="G49" s="104" t="s">
+      <c r="G49" s="108" t="s">
         <v>87</v>
       </c>
-      <c r="H49" s="103" t="s">
+      <c r="H49" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I49" s="104" t="s">
+      <c r="I49" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J49" s="106" t="s">
+      <c r="J49" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K49" s="22" t="s">
@@ -12238,24 +12231,24 @@
       <c r="W49" s="40">
         <v>0.73999999999999966</v>
       </c>
-      <c r="X49" s="146"/>
-      <c r="Y49" s="141"/>
-      <c r="Z49" s="140"/>
-      <c r="AA49" s="145" t="s">
+      <c r="X49" s="130"/>
+      <c r="Y49" s="132"/>
+      <c r="Z49" s="133"/>
+      <c r="AA49" s="126" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A50" s="90"/>
-      <c r="B50" s="142"/>
-      <c r="C50" s="137"/>
-      <c r="D50" s="105"/>
-      <c r="E50" s="104"/>
-      <c r="F50" s="104"/>
-      <c r="G50" s="104"/>
-      <c r="H50" s="103"/>
-      <c r="I50" s="104"/>
-      <c r="J50" s="106"/>
+    <row r="50" spans="1:27" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="143"/>
+      <c r="B50" s="150"/>
+      <c r="C50" s="92"/>
+      <c r="D50" s="90"/>
+      <c r="E50" s="108"/>
+      <c r="F50" s="108"/>
+      <c r="G50" s="108"/>
+      <c r="H50" s="111"/>
+      <c r="I50" s="108"/>
+      <c r="J50" s="107"/>
       <c r="K50" s="22" t="s">
         <v>55</v>
       </c>
@@ -12289,40 +12282,40 @@
       <c r="U50" s="17"/>
       <c r="V50" s="17"/>
       <c r="W50" s="74"/>
-      <c r="X50" s="146"/>
-      <c r="Y50" s="141"/>
-      <c r="Z50" s="140"/>
-      <c r="AA50" s="145"/>
+      <c r="X50" s="130"/>
+      <c r="Y50" s="132"/>
+      <c r="Z50" s="133"/>
+      <c r="AA50" s="126"/>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A51" s="136" t="s">
+    <row r="51" spans="1:27" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="144" t="s">
         <v>25</v>
       </c>
-      <c r="B51" s="125" t="s">
+      <c r="B51" s="91" t="s">
         <v>130</v>
       </c>
-      <c r="C51" s="137" t="s">
+      <c r="C51" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="D51" s="105" t="s">
+      <c r="D51" s="90" t="s">
         <v>131</v>
       </c>
-      <c r="E51" s="104">
+      <c r="E51" s="108">
         <v>33.1</v>
       </c>
-      <c r="F51" s="104" t="s">
+      <c r="F51" s="108" t="s">
         <v>87</v>
       </c>
-      <c r="G51" s="104" t="s">
+      <c r="G51" s="108" t="s">
         <v>87</v>
       </c>
-      <c r="H51" s="103" t="s">
+      <c r="H51" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I51" s="104" t="s">
+      <c r="I51" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J51" s="106" t="s">
+      <c r="J51" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K51" s="22" t="s">
@@ -12358,24 +12351,24 @@
       <c r="U51" s="35"/>
       <c r="V51" s="35"/>
       <c r="W51" s="38"/>
-      <c r="X51" s="146"/>
-      <c r="Y51" s="140"/>
-      <c r="Z51" s="140"/>
-      <c r="AA51" s="123" t="s">
+      <c r="X51" s="130"/>
+      <c r="Y51" s="133"/>
+      <c r="Z51" s="133"/>
+      <c r="AA51" s="93" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="136"/>
-      <c r="B52" s="125"/>
-      <c r="C52" s="137"/>
-      <c r="D52" s="105"/>
-      <c r="E52" s="104"/>
-      <c r="F52" s="104"/>
-      <c r="G52" s="104"/>
-      <c r="H52" s="103"/>
-      <c r="I52" s="104"/>
-      <c r="J52" s="106"/>
+    <row r="52" spans="1:27" ht="20.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="144"/>
+      <c r="B52" s="91"/>
+      <c r="C52" s="92"/>
+      <c r="D52" s="90"/>
+      <c r="E52" s="108"/>
+      <c r="F52" s="108"/>
+      <c r="G52" s="108"/>
+      <c r="H52" s="111"/>
+      <c r="I52" s="108"/>
+      <c r="J52" s="107"/>
       <c r="K52" s="22" t="s">
         <v>55</v>
       </c>
@@ -12409,41 +12402,238 @@
       <c r="U52" s="29"/>
       <c r="V52" s="29"/>
       <c r="W52" s="30"/>
-      <c r="X52" s="146"/>
-      <c r="Y52" s="140"/>
-      <c r="Z52" s="140"/>
-      <c r="AA52" s="123"/>
+      <c r="X52" s="130"/>
+      <c r="Y52" s="133"/>
+      <c r="Z52" s="133"/>
+      <c r="AA52" s="93"/>
     </row>
-    <row r="54" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="56" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="58" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="60" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="62" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="64" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="66" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="270">
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="X16:X17"/>
-    <mergeCell ref="Y16:Y17"/>
-    <mergeCell ref="Y28:Y29"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="X20:X21"/>
-    <mergeCell ref="Y20:Y21"/>
-    <mergeCell ref="X28:X29"/>
-    <mergeCell ref="X22:X23"/>
-    <mergeCell ref="Y22:Y23"/>
-    <mergeCell ref="Y26:Y27"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="A24:A33"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="Z32:Z33"/>
+    <mergeCell ref="Y32:Y33"/>
+    <mergeCell ref="X32:X33"/>
+    <mergeCell ref="Z24:Z25"/>
+    <mergeCell ref="Y24:Y25"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="Y30:Y31"/>
+    <mergeCell ref="Z28:Z29"/>
+    <mergeCell ref="Z30:Z31"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="AA30:AA31"/>
+    <mergeCell ref="X24:X25"/>
+    <mergeCell ref="E30:G31"/>
+    <mergeCell ref="E32:G33"/>
+    <mergeCell ref="E34:G35"/>
+    <mergeCell ref="E36:G37"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="I34:I35"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="X26:X27"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="E26:G27"/>
+    <mergeCell ref="E22:G23"/>
+    <mergeCell ref="AA22:AA23"/>
+    <mergeCell ref="Z22:Z23"/>
+    <mergeCell ref="Z26:Z27"/>
+    <mergeCell ref="AA6:AA7"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AA10:AA11"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="E6:G7"/>
+    <mergeCell ref="E8:G9"/>
+    <mergeCell ref="E10:G11"/>
+    <mergeCell ref="E12:G13"/>
+    <mergeCell ref="E14:G15"/>
+    <mergeCell ref="E16:G17"/>
+    <mergeCell ref="E18:G19"/>
+    <mergeCell ref="E20:G21"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="X10:X11"/>
+    <mergeCell ref="Y10:Y11"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="E28:G29"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="AA12:AA13"/>
+    <mergeCell ref="AA14:AA15"/>
+    <mergeCell ref="X14:X15"/>
+    <mergeCell ref="Y14:Y15"/>
+    <mergeCell ref="Z20:Z21"/>
+    <mergeCell ref="X12:X13"/>
+    <mergeCell ref="Y12:Y13"/>
+    <mergeCell ref="Z12:Z13"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="Z14:Z15"/>
+    <mergeCell ref="Z16:Z17"/>
+    <mergeCell ref="Z18:Z19"/>
+    <mergeCell ref="AA18:AA19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="X18:X19"/>
+    <mergeCell ref="Y18:Y19"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="F51:F52"/>
+    <mergeCell ref="G51:G52"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J45:J46"/>
+    <mergeCell ref="Y51:Y52"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="Y49:Y50"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="AA51:AA52"/>
+    <mergeCell ref="AA49:AA50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="J51:J52"/>
+    <mergeCell ref="X51:X52"/>
+    <mergeCell ref="Z51:Z52"/>
+    <mergeCell ref="X49:X50"/>
+    <mergeCell ref="A38:AA38"/>
+    <mergeCell ref="Z49:Z50"/>
+    <mergeCell ref="Y47:Y48"/>
+    <mergeCell ref="Z47:Z48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="X43:X44"/>
+    <mergeCell ref="Y43:Y44"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A48"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="AA32:AA33"/>
+    <mergeCell ref="AA16:AA17"/>
+    <mergeCell ref="AA20:AA21"/>
+    <mergeCell ref="AA41:AA42"/>
+    <mergeCell ref="AA45:AA46"/>
+    <mergeCell ref="AA47:AA48"/>
+    <mergeCell ref="AA24:AA25"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="AA28:AA29"/>
+    <mergeCell ref="AA26:AA27"/>
+    <mergeCell ref="AA34:AA35"/>
+    <mergeCell ref="AA36:AA37"/>
+    <mergeCell ref="X47:X48"/>
+    <mergeCell ref="Y41:Y42"/>
+    <mergeCell ref="Z41:Z42"/>
+    <mergeCell ref="X45:X46"/>
+    <mergeCell ref="Y45:Y46"/>
+    <mergeCell ref="AA43:AA44"/>
+    <mergeCell ref="Z43:Z44"/>
+    <mergeCell ref="Z45:Z46"/>
+    <mergeCell ref="X41:X42"/>
+    <mergeCell ref="X36:X37"/>
+    <mergeCell ref="X30:X31"/>
+    <mergeCell ref="Z36:Z37"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="X34:X35"/>
+    <mergeCell ref="Y34:Y35"/>
+    <mergeCell ref="Z34:Z35"/>
+    <mergeCell ref="Y36:Y37"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="C18:C19"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A3:B3"/>
@@ -12468,231 +12658,27 @@
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="J8:J9"/>
-    <mergeCell ref="Z36:Z37"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="X34:X35"/>
-    <mergeCell ref="Y34:Y35"/>
-    <mergeCell ref="Z34:Z35"/>
-    <mergeCell ref="Y36:Y37"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="AA32:AA33"/>
-    <mergeCell ref="AA16:AA17"/>
-    <mergeCell ref="AA20:AA21"/>
-    <mergeCell ref="AA41:AA42"/>
-    <mergeCell ref="AA45:AA46"/>
-    <mergeCell ref="AA47:AA48"/>
-    <mergeCell ref="AA24:AA25"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="AA28:AA29"/>
-    <mergeCell ref="AA26:AA27"/>
-    <mergeCell ref="AA34:AA35"/>
-    <mergeCell ref="AA36:AA37"/>
-    <mergeCell ref="X47:X48"/>
-    <mergeCell ref="Y41:Y42"/>
-    <mergeCell ref="Z41:Z42"/>
-    <mergeCell ref="X45:X46"/>
-    <mergeCell ref="Y45:Y46"/>
-    <mergeCell ref="AA43:AA44"/>
-    <mergeCell ref="Z43:Z44"/>
-    <mergeCell ref="Z45:Z46"/>
-    <mergeCell ref="X41:X42"/>
-    <mergeCell ref="X36:X37"/>
-    <mergeCell ref="X30:X31"/>
-    <mergeCell ref="AA51:AA52"/>
-    <mergeCell ref="AA49:AA50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="J51:J52"/>
-    <mergeCell ref="X51:X52"/>
-    <mergeCell ref="Z51:Z52"/>
-    <mergeCell ref="X49:X50"/>
-    <mergeCell ref="A38:AA38"/>
-    <mergeCell ref="Z49:Z50"/>
-    <mergeCell ref="Y47:Y48"/>
-    <mergeCell ref="Z47:Z48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="X43:X44"/>
-    <mergeCell ref="Y43:Y44"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A48"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="J45:J46"/>
-    <mergeCell ref="Y51:Y52"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="Y49:Y50"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="F51:F52"/>
-    <mergeCell ref="G51:G52"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="AA12:AA13"/>
-    <mergeCell ref="AA14:AA15"/>
-    <mergeCell ref="X14:X15"/>
-    <mergeCell ref="Y14:Y15"/>
-    <mergeCell ref="Z20:Z21"/>
-    <mergeCell ref="X12:X13"/>
-    <mergeCell ref="Y12:Y13"/>
-    <mergeCell ref="Z12:Z13"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="Z14:Z15"/>
-    <mergeCell ref="Z16:Z17"/>
-    <mergeCell ref="Z18:Z19"/>
-    <mergeCell ref="AA18:AA19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="X18:X19"/>
-    <mergeCell ref="Y18:Y19"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="E28:G29"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="I32:I33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="E26:G27"/>
-    <mergeCell ref="E22:G23"/>
-    <mergeCell ref="AA22:AA23"/>
-    <mergeCell ref="Z22:Z23"/>
-    <mergeCell ref="Z26:Z27"/>
-    <mergeCell ref="AA6:AA7"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AA10:AA11"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="E6:G7"/>
-    <mergeCell ref="E8:G9"/>
-    <mergeCell ref="E10:G11"/>
-    <mergeCell ref="E12:G13"/>
-    <mergeCell ref="E14:G15"/>
-    <mergeCell ref="E16:G17"/>
-    <mergeCell ref="E18:G19"/>
-    <mergeCell ref="E20:G21"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="X10:X11"/>
-    <mergeCell ref="Y10:Y11"/>
-    <mergeCell ref="AA30:AA31"/>
-    <mergeCell ref="X24:X25"/>
-    <mergeCell ref="E30:G31"/>
-    <mergeCell ref="E32:G33"/>
-    <mergeCell ref="E34:G35"/>
-    <mergeCell ref="E36:G37"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="H32:H33"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="I34:I35"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="X26:X27"/>
-    <mergeCell ref="A24:A33"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="Z32:Z33"/>
-    <mergeCell ref="Y32:Y33"/>
-    <mergeCell ref="X32:X33"/>
-    <mergeCell ref="Z24:Z25"/>
-    <mergeCell ref="Y24:Y25"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="Y30:Y31"/>
-    <mergeCell ref="Z28:Z29"/>
-    <mergeCell ref="Z30:Z31"/>
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="X16:X17"/>
+    <mergeCell ref="Y16:Y17"/>
+    <mergeCell ref="Y28:Y29"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="X20:X21"/>
+    <mergeCell ref="Y20:Y21"/>
+    <mergeCell ref="X28:X29"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="Y26:Y27"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="I12:I13"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B6 H6:J6 C6:C12 B8 H8:J8 B10 H10:J10 B12 H12:J12 H14:J14 H16:J16 H20:J20 C22 H22:J22 H24:J24 D26:E26 H26:J26 C26:C27 H28:J28 H30:J30 H32:J32 H34:J34 H36:J36 D41:J41 C41:C43 D45:J45 C45:C52 D47:J47 D49:J49 D51:J51">
@@ -13011,20 +12997,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -13162,6 +13134,20 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -13169,11 +13155,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F096517C-598E-4E6D-B017-32F081EE1644}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13185,20 +13167,24 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F9F019C-2529-47D7-9C19-168692A0A5B3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="f5a961e1-edc1-4f62-8655-e8a46ef79e5c"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="68108f69-118e-4385-83b3-00743b1bf54c"/>
   </ds:schemaRefs>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/GlobalMoSMT-2023/Shared Documents/General/2026/Goals Alignment 2026/Strategic Execution 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3320" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5A4BA57-CBB5-43E3-A661-F181EB486104}"/>
+  <xr:revisionPtr revIDLastSave="3339" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{736A0B24-C905-4A14-9278-294C93D80D9F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
   </bookViews>
   <sheets>
     <sheet name="Mastersheet" sheetId="5" r:id="rId1"/>
     <sheet name="AOP Critical" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -366,7 +366,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="143">
   <si>
     <t>Strategic Imperatives</t>
   </si>
@@ -498,6 +498,9 @@
     <t>Q2</t>
   </si>
   <si>
+    <t>Q3</t>
+  </si>
+  <si>
     <t xml:space="preserve">If reported Red then
 state Cause  </t>
   </si>
@@ -581,6 +584,13 @@
     <t>Increase contract penetration %</t>
   </si>
   <si>
+    <t>-0.8% delta Vs AOP. Excluding GRC 0.7% YoY improvement.  LATAM renewals improved ITM Sep. Expected turnaround is Q4 2026 (Dec)</t>
+  </si>
+  <si>
+    <t>1) Funnel focus actions driven across regions for renewals.
+2) Contract Funnel tracked 90 days before expiry for timely renewals.</t>
+  </si>
+  <si>
     <t>Adjusted EBITA %</t>
   </si>
   <si>
@@ -605,200 +615,13 @@
     <t>Mn</t>
   </si>
   <si>
+    <t>YTD Sept Productivity no's on track.Good Realization from E&amp;E savings of Pune and also a gap reduction of R&amp;D Budget YTD.</t>
+  </si>
+  <si>
     <t>Inventory MAT sales</t>
   </si>
   <si>
     <t>Inventory as a % MAT sales</t>
-  </si>
-  <si>
-    <t>Inventory as a % MAT sales KPI</t>
-  </si>
-  <si>
-    <t>NPI Schedule Adherence</t>
-  </si>
-  <si>
-    <t>Shivaraj G</t>
-  </si>
-  <si>
-    <t>Dhruv  Schedule Adherence</t>
-  </si>
-  <si>
-    <t>Implied Market Share Gain</t>
-  </si>
-  <si>
-    <t>Sarika P</t>
-  </si>
-  <si>
-    <t>Implied Market Share Gain (ITQ)</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>QTR</t>
-  </si>
-  <si>
-    <t>Win Rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Win Rate </t>
-  </si>
-  <si>
-    <t>(Philips OIT) / (Philips OIT + lost SFDC + not pursuing SFDC)</t>
-  </si>
-  <si>
-    <t>Implied Market Share Gain KPI</t>
-  </si>
-  <si>
-    <t>Order Intake Growth</t>
-  </si>
-  <si>
-    <t>OIT Growth % (EQ)</t>
-  </si>
-  <si>
-    <t>OIT (Equipment  + Service)</t>
-  </si>
-  <si>
-    <t>OIT Growth % (CS)</t>
-  </si>
-  <si>
-    <t>Comparable Sales</t>
-  </si>
-  <si>
-    <t>Monthly Sales recognized (EQ)</t>
-  </si>
-  <si>
-    <t>CSG % KPI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Impact Index KPI </t>
-  </si>
-  <si>
-    <t>Lakshmi M</t>
-  </si>
-  <si>
-    <t>EES scores are out! It is a balanced story. We are better than H1 2025 but slightly worse than H2 2025</t>
-  </si>
-  <si>
-    <t>CS has hit it out of the park.Quality dipped from 100% but still highest, Marketing is holding but at low scores. R&amp;D has dropped some big numbers.</t>
-  </si>
-  <si>
-    <t>Employee Engagement KPI</t>
-  </si>
-  <si>
-    <t>HY</t>
-  </si>
-  <si>
-    <t>MoS Value Levers 2026 - 2028:</t>
-  </si>
-  <si>
-    <t>Value Levers</t>
-  </si>
-  <si>
-    <t>AOP
- 2026</t>
-  </si>
-  <si>
-    <t>AOP
- 2027</t>
-  </si>
-  <si>
-    <t>AOP
- 2028</t>
-  </si>
-  <si>
-    <t>Mar</t>
-  </si>
-  <si>
-    <t>June</t>
-  </si>
-  <si>
-    <t>Cost Of Non-Quality as % of Sales</t>
-  </si>
-  <si>
-    <t>Cost of FCO, Warranty, Obsolescence, Scrap and Rework.</t>
-  </si>
-  <si>
-    <t>Competitive Roadmap</t>
-  </si>
-  <si>
-    <t>Roadmap MS% delivery (NPI OIT)</t>
-  </si>
-  <si>
-    <t>Zenition 10 &amp; 30 OIT below Q2 AOP due NPIs and price pressure from GE &amp; Siemens</t>
-  </si>
-  <si>
-    <t>Focus on Philips IB opportunity through mapping and targeted promotions to improve win rate</t>
-  </si>
-  <si>
-    <t>(MS% delivered by roadmap)
-/ (MS% ambition) 
-over 5 year horizon</t>
-  </si>
-  <si>
-    <t>Vitality index</t>
-  </si>
-  <si>
-    <t>% of sales from MoS Innovation &lt; 3 years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Improve Z10 &amp; Z30 competitiveness (sales training to counter competition) and bundling service at POS address price gap
-</t>
-  </si>
-  <si>
-    <t>I2M Value Creation</t>
-  </si>
-  <si>
-    <t>Development progress (per year, per quarter, %) X Incremental IGM</t>
-  </si>
-  <si>
-    <t>Development progress 
-(per year, per quarter, %) X Incremental IGM,( from business cases, M€ )</t>
-  </si>
-  <si>
-    <t>Cusotomer Focus</t>
-  </si>
-  <si>
-    <t>Services - Time To System Up (TTSU)</t>
-  </si>
-  <si>
-    <t>% of system down cases back up &lt;48hrs</t>
-  </si>
-  <si>
-    <t>Time To System Up &lt; 48h</t>
-  </si>
-  <si>
-    <t>Profitability - Margin Expansion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Driving profitability via margin expansion  </t>
-  </si>
-  <si>
-    <t>Focus on optimizing FCP, pricing, and product mix to drive margin expansion</t>
-  </si>
-  <si>
-    <t>YTD Sept Productivity no's on track.Good Realization from E&amp;E savings of Pune and also a gap reduction of R&amp;D Budget YTD.</t>
-  </si>
-  <si>
-    <t>EQ OIT YTD Sep lower by 0.2M, which is mainly coming by NAR -4.4M, EU -3.7M however Growth supported by over-drive +7.9M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current OOH does not support FY revnue plan. 
-OOH is 117 M agaist AOP of 141M .B&amp;B  24 M B&amp;B required to meet FY AOP.
-</t>
-  </si>
-  <si>
-    <t>Growth</t>
-  </si>
-  <si>
-    <t>Drive B&amp;B OIT 
-NAR : 5 M , EU: 8.5M , Growth : 7.6</t>
-  </si>
-  <si>
-    <t>1. NAR :AOP accelator program launched to improve OIT to rev conversion.
-2. EU : Demo  liquidation plan aligned toward Q4 to maximise OIT in Q3.
-3. Growth:  Namibia tender conversion in Q4
-4. UIEP : COE team to analyse the difference and accurate capturing in AOP 2027</t>
   </si>
   <si>
     <t xml:space="preserve">Market inventory : 7.7 M above AOP .
@@ -809,11 +632,191 @@
 </t>
   </si>
   <si>
-    <t>1) Funnel focus actions driven across regions for renewals.
-2) Contract Funnel tracked 90 days before expiry for timely renewals.</t>
-  </si>
-  <si>
-    <t>-0.8% delta Vs AOP. Excluding GRC 0.7% YoY improvement.  LATAM renewals improved ITM Sep. Expected turnaround is Q4 2026 (Dec)</t>
+    <t>1. NAR :AOP accelator program launched to improve OIT to rev conversion.
+2. EU : Demo  liquidation plan aligned toward Q4 to maximise OIT in Q3.
+3. Growth:  Namibia tender conversion in Q4
+4. UIEP : COE team to analyse the difference and accurate capturing in AOP 2027</t>
+  </si>
+  <si>
+    <t>Inventory as a % MAT sales KPI</t>
+  </si>
+  <si>
+    <t>NPI Schedule Adherence</t>
+  </si>
+  <si>
+    <t>Shivaraj G</t>
+  </si>
+  <si>
+    <t>Dhruv  Schedule Adherence</t>
+  </si>
+  <si>
+    <t>Implied Market Share Gain</t>
+  </si>
+  <si>
+    <t>Sarika P</t>
+  </si>
+  <si>
+    <t>Implied Market Share Gain (ITQ)</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>QTR</t>
+  </si>
+  <si>
+    <t>Win Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Win Rate </t>
+  </si>
+  <si>
+    <t>(Philips OIT) / (Philips OIT + lost SFDC + not pursuing SFDC)</t>
+  </si>
+  <si>
+    <t>Implied Market Share Gain KPI</t>
+  </si>
+  <si>
+    <t>Order Intake Growth</t>
+  </si>
+  <si>
+    <t>OIT Growth % (EQ)</t>
+  </si>
+  <si>
+    <t>EQ OIT YTD Sep lower by 0.2M, which is mainly coming by NAR -4.4M, EU -3.7M however Growth supported by over-drive +7.9M</t>
+  </si>
+  <si>
+    <t>OIT (Equipment  + Service)</t>
+  </si>
+  <si>
+    <t>OIT Growth % (CS)</t>
+  </si>
+  <si>
+    <t>Comparable Sales</t>
+  </si>
+  <si>
+    <t>Monthly Sales recognized (EQ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current OOH does not support FY revnue plan. 
+OOH is 117 M agaist AOP of 141M .B&amp;B  24 M B&amp;B required to meet FY AOP.
+</t>
+  </si>
+  <si>
+    <t>Drive B&amp;B OIT 
+NAR : 5 M , EU: 8.5M , Growth : 7.6</t>
+  </si>
+  <si>
+    <t>CSG % KPI</t>
+  </si>
+  <si>
+    <t>Growth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impact Index KPI </t>
+  </si>
+  <si>
+    <t>Lakshmi M</t>
+  </si>
+  <si>
+    <t>EES scores are out! It is a balanced story. We are better than H1 2025 but slightly worse than H2 2025</t>
+  </si>
+  <si>
+    <t>CS has hit it out of the park.Quality dipped from 100% but still highest, Marketing is holding but at low scores. R&amp;D has dropped some big numbers.</t>
+  </si>
+  <si>
+    <t>Employee Engagement KPI</t>
+  </si>
+  <si>
+    <t>HY</t>
+  </si>
+  <si>
+    <t>MoS Value Levers 2026 - 2028:</t>
+  </si>
+  <si>
+    <t>Value Levers</t>
+  </si>
+  <si>
+    <t>AOP
+ 2026</t>
+  </si>
+  <si>
+    <t>AOP
+ 2027</t>
+  </si>
+  <si>
+    <t>AOP
+ 2028</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
+  <si>
+    <t>Cost Of Non-Quality as % of Sales</t>
+  </si>
+  <si>
+    <t>Cost of FCO, Warranty, Obsolescence, Scrap and Rework.</t>
+  </si>
+  <si>
+    <t>Competitive Roadmap</t>
+  </si>
+  <si>
+    <t>Roadmap MS% delivery (NPI OIT)</t>
+  </si>
+  <si>
+    <t>Zenition 10 &amp; 30 OIT below Q2 AOP due NPIs and price pressure from GE &amp; Siemens</t>
+  </si>
+  <si>
+    <t>Focus on Philips IB opportunity through mapping and targeted promotions to improve win rate</t>
+  </si>
+  <si>
+    <t>(MS% delivered by roadmap)
+/ (MS% ambition) 
+over 5 year horizon</t>
+  </si>
+  <si>
+    <t>Vitality index</t>
+  </si>
+  <si>
+    <t>% of sales from MoS Innovation &lt; 3 years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Improve Z10 &amp; Z30 competitiveness (sales training to counter competition) and bundling service at POS address price gap
+</t>
+  </si>
+  <si>
+    <t>I2M Value Creation</t>
+  </si>
+  <si>
+    <t>Development progress (per year, per quarter, %) X Incremental IGM</t>
+  </si>
+  <si>
+    <t>Development progress 
+(per year, per quarter, %) X Incremental IGM,( from business cases, M€ )</t>
+  </si>
+  <si>
+    <t>Cusotomer Focus</t>
+  </si>
+  <si>
+    <t>Services - Time To System Up (TTSU)</t>
+  </si>
+  <si>
+    <t>% of system down cases back up &lt;48hrs</t>
+  </si>
+  <si>
+    <t>Time To System Up &lt; 48h</t>
+  </si>
+  <si>
+    <t>Profitability - Margin Expansion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Driving profitability via margin expansion  </t>
+  </si>
+  <si>
+    <t>Focus on optimizing FCP, pricing, and product mix to drive margin expansion</t>
   </si>
 </sst>
 </file>
@@ -821,13 +824,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="mmm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="mmm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1313,7 +1316,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1324,14 +1327,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1361,84 +1364,84 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="7" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1457,13 +1460,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="15" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="15" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="16" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="16" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="9" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1500,21 +1503,21 @@
     <xf numFmtId="10" fontId="8" fillId="7" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="7" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="7" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="9" fillId="17" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1523,28 +1526,28 @@
     <xf numFmtId="10" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="7" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="7" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="7" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1553,10 +1556,10 @@
     <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1855,7 +1858,35 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1876,7 +1907,35 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1939,83 +1998,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFDA9694"/>
         </patternFill>
       </fill>
@@ -2038,111 +2020,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2191,6 +2068,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
@@ -2199,6 +2090,118 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2227,6 +2230,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2276,13 +2286,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5181,29 +5184,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247AD843-49A7-417E-9F24-86908363EFA2}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:V59"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="38.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.54296875" customWidth="1"/>
-    <col min="5" max="6" width="10.453125" customWidth="1"/>
-    <col min="7" max="7" width="13.81640625" customWidth="1"/>
-    <col min="9" max="9" width="11.54296875" customWidth="1"/>
-    <col min="10" max="10" width="13.81640625" customWidth="1"/>
+    <col min="3" max="3" width="55.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.5703125" customWidth="1"/>
+    <col min="5" max="6" width="10.42578125" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:22" ht="15.95">
       <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -5271,7 +5274,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22">
       <c r="A5" t="str">
         <f>IF('AOP Critical'!B6="","",'AOP Critical'!B6)</f>
         <v>Complaint Closure</v>
@@ -5357,7 +5360,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22">
       <c r="A6" t="str">
         <f>IF('AOP Critical'!B6="","",'AOP Critical'!B6)</f>
         <v>Complaint Closure</v>
@@ -5443,7 +5446,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22">
       <c r="A7" t="str">
         <f>IF('AOP Critical'!B8="","",'AOP Critical'!B8)</f>
         <v>% of CAPA investgation</v>
@@ -5529,7 +5532,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22">
       <c r="A8" t="str">
         <f>IF('AOP Critical'!B8="","",'AOP Critical'!B8)</f>
         <v>% of CAPA investgation</v>
@@ -5615,7 +5618,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22">
       <c r="A9" t="str">
         <f>IF('AOP Critical'!B10="","",'AOP Critical'!B10)</f>
         <v xml:space="preserve"># of Corrections &amp; Removals </v>
@@ -5684,9 +5687,9 @@
         <f>IF('AOP Critical'!S10="","",'AOP Critical'!S10)</f>
         <v>1</v>
       </c>
-      <c r="S9" t="str">
+      <c r="S9">
         <f>IF('AOP Critical'!T10="","",'AOP Critical'!T10)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T9" t="str">
         <f>IF('AOP Critical'!U10="","",'AOP Critical'!U10)</f>
@@ -5701,7 +5704,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22">
       <c r="A10" t="str">
         <f>IF('AOP Critical'!B10="","",'AOP Critical'!B10)</f>
         <v xml:space="preserve"># of Corrections &amp; Removals </v>
@@ -5787,7 +5790,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22">
       <c r="A11" t="str">
         <f>IF('AOP Critical'!B41="","",'AOP Critical'!B41)</f>
         <v>Cost Of Non-Quality as % of Sales</v>
@@ -5873,7 +5876,7 @@
         <v>3.32E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22">
       <c r="A12" t="str">
         <f>IF('AOP Critical'!B41="","",'AOP Critical'!B41)</f>
         <v>Cost Of Non-Quality as % of Sales</v>
@@ -5959,12 +5962,12 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22">
       <c r="A13" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -6032,7 +6035,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22">
       <c r="A15" t="str">
         <f>IF('AOP Critical'!B12="","",'AOP Critical'!B12)</f>
         <v>Ontime In Full</v>
@@ -6122,7 +6125,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22">
       <c r="A16" t="str">
         <f>IF('AOP Critical'!B12="","",'AOP Critical'!B12)</f>
         <v>Ontime In Full</v>
@@ -6212,7 +6215,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22">
       <c r="A17" t="str">
         <f>IF('AOP Critical'!B14="","",'AOP Critical'!B14)</f>
         <v>Contract Penetration</v>
@@ -6302,7 +6305,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22">
       <c r="A18" t="str">
         <f>IF('AOP Critical'!B14="","",'AOP Critical'!B14)</f>
         <v>Contract Penetration</v>
@@ -6392,7 +6395,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22">
       <c r="A19" t="str">
         <f>IF('AOP Critical'!B49="","",'AOP Critical'!B49)</f>
         <v>Services - Time To System Up (TTSU)</v>
@@ -6482,7 +6485,7 @@
         <v>0.73999999999999966</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22">
       <c r="A20" t="str">
         <f>IF('AOP Critical'!B49="","",'AOP Critical'!B49)</f>
         <v>Services - Time To System Up (TTSU)</v>
@@ -6572,12 +6575,12 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22">
       <c r="A21" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22">
       <c r="A22" t="s">
         <v>2</v>
       </c>
@@ -6645,7 +6648,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:22">
       <c r="A23" t="str">
         <f>IF('AOP Critical'!B16="","",'AOP Critical'!B16)</f>
         <v>Adjusted EBITA %</v>
@@ -6735,7 +6738,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:22">
       <c r="A24" t="str">
         <f>IF('AOP Critical'!B16="","",'AOP Critical'!B16)</f>
         <v>Adjusted EBITA %</v>
@@ -6825,7 +6828,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:22">
       <c r="A25" t="str">
         <f>IF('AOP Critical'!B18="","",'AOP Critical'!B18)</f>
         <v>Productivity</v>
@@ -6915,7 +6918,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:22">
       <c r="A26" t="str">
         <f>IF('AOP Critical'!B18="","",'AOP Critical'!B18)</f>
         <v>Productivity</v>
@@ -7005,7 +7008,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:22">
       <c r="A27" t="str">
         <f>IF('AOP Critical'!B20="","",'AOP Critical'!B20)</f>
         <v>Inventory MAT sales</v>
@@ -7095,7 +7098,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:22">
       <c r="A28" t="str">
         <f>IF('AOP Critical'!B20="","",'AOP Critical'!B20)</f>
         <v>Inventory MAT sales</v>
@@ -7185,7 +7188,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:22">
       <c r="A29" t="str">
         <f>IF('AOP Critical'!B51="","",'AOP Critical'!B51)</f>
         <v>Profitability - Margin Expansion</v>
@@ -7275,7 +7278,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:22">
       <c r="A30" t="str">
         <f>IF('AOP Critical'!B51="","",'AOP Critical'!B51)</f>
         <v>Profitability - Margin Expansion</v>
@@ -7365,12 +7368,12 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:22">
       <c r="A31" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:22">
       <c r="A32" t="s">
         <v>2</v>
       </c>
@@ -7438,7 +7441,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:22">
       <c r="A33" t="str">
         <f>IF('AOP Critical'!B26="","",'AOP Critical'!B26)</f>
         <v xml:space="preserve">Win Rate </v>
@@ -7528,7 +7531,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:22">
       <c r="A34" t="str">
         <f>IF('AOP Critical'!B26="","",'AOP Critical'!B26)</f>
         <v xml:space="preserve">Win Rate </v>
@@ -7618,7 +7621,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:22">
       <c r="A35" t="str">
         <f>IF('AOP Critical'!B22="","",'AOP Critical'!B22)</f>
         <v>NPI Schedule Adherence</v>
@@ -7708,7 +7711,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:22">
       <c r="A36" t="str">
         <f>IF('AOP Critical'!B22="","",'AOP Critical'!B22)</f>
         <v>NPI Schedule Adherence</v>
@@ -7798,7 +7801,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:22">
       <c r="A37" t="str">
         <f>IF('AOP Critical'!B43="","",'AOP Critical'!B43)</f>
         <v>Competitive Roadmap</v>
@@ -7888,7 +7891,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:22">
       <c r="A38" t="str">
         <f>IF('AOP Critical'!B43="","",'AOP Critical'!B43)</f>
         <v>Competitive Roadmap</v>
@@ -7978,7 +7981,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:22">
       <c r="A39" t="str">
         <f>IF('AOP Critical'!B45="","",'AOP Critical'!B45)</f>
         <v>Vitality index</v>
@@ -8068,7 +8071,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:22">
       <c r="A40" t="str">
         <f>IF('AOP Critical'!B45="","",'AOP Critical'!B45)</f>
         <v>Vitality index</v>
@@ -8158,7 +8161,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:22">
       <c r="A41" t="str">
         <f>IF('AOP Critical'!B47="","",'AOP Critical'!B47)</f>
         <v>I2M Value Creation</v>
@@ -8248,7 +8251,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:22">
       <c r="A42" t="str">
         <f>IF('AOP Critical'!B47="","",'AOP Critical'!B47)</f>
         <v>I2M Value Creation</v>
@@ -8338,12 +8341,12 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:22">
       <c r="A43" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:22">
       <c r="A44" t="s">
         <v>2</v>
       </c>
@@ -8411,7 +8414,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:22">
       <c r="A45" t="str">
         <f>IF('AOP Critical'!D28="","",'AOP Critical'!D28)</f>
         <v>OIT Growth % (EQ)</v>
@@ -8501,7 +8504,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:22">
       <c r="A46" t="str">
         <f>IF('AOP Critical'!D28="","",'AOP Critical'!D28)</f>
         <v>OIT Growth % (EQ)</v>
@@ -8591,7 +8594,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:22">
       <c r="A47" t="str">
         <f>IF('AOP Critical'!D30="","",'AOP Critical'!D30)</f>
         <v>OIT Growth % (CS)</v>
@@ -8678,7 +8681,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:22">
       <c r="A48" t="str">
         <f>IF('AOP Critical'!D30="","",'AOP Critical'!D30)</f>
         <v>OIT Growth % (CS)</v>
@@ -8764,7 +8767,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:22">
       <c r="A49" t="str">
         <f>IF('AOP Critical'!B32="","",'AOP Critical'!B32)</f>
         <v>Comparable Sales</v>
@@ -8854,7 +8857,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:22">
       <c r="A50" t="str">
         <f>IF('AOP Critical'!B32="","",'AOP Critical'!B32)</f>
         <v>Comparable Sales</v>
@@ -8944,7 +8947,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:22">
       <c r="A51" t="str">
         <f>IF('AOP Critical'!B24="","",'AOP Critical'!B24)</f>
         <v>Implied Market Share Gain</v>
@@ -9019,7 +9022,7 @@
       </c>
       <c r="S51" s="70" t="str">
         <f>IF('AOP Critical'!T24="","",'AOP Critical'!T24)</f>
-        <v/>
+        <v>QTR</v>
       </c>
       <c r="T51" s="70" t="str">
         <f>IF('AOP Critical'!U24="","",'AOP Critical'!U24)</f>
@@ -9034,7 +9037,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:22">
       <c r="A52" t="str">
         <f>IF('AOP Critical'!B24="","",'AOP Critical'!B24)</f>
         <v>Implied Market Share Gain</v>
@@ -9097,7 +9100,7 @@
       </c>
       <c r="P52">
         <f>IF('AOP Critical'!Q25="","",'AOP Critical'!Q25)</f>
-        <v>0.121</v>
+        <v>0.12</v>
       </c>
       <c r="Q52" t="str">
         <f>IF('AOP Critical'!R25="","",'AOP Critical'!R25)</f>
@@ -9109,7 +9112,7 @@
       </c>
       <c r="S52" t="str">
         <f>IF('AOP Critical'!T25="","",'AOP Critical'!T25)</f>
-        <v/>
+        <v>QTR</v>
       </c>
       <c r="T52" t="str">
         <f>IF('AOP Critical'!U25="","",'AOP Critical'!U25)</f>
@@ -9124,12 +9127,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:22">
       <c r="A54" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:22">
       <c r="A55" t="s">
         <v>2</v>
       </c>
@@ -9197,7 +9200,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:22">
       <c r="A56" t="s">
         <v>29</v>
       </c>
@@ -9272,7 +9275,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:22">
       <c r="A57" t="s">
         <v>29</v>
       </c>
@@ -9347,7 +9350,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:22">
       <c r="A58" t="s">
         <v>35</v>
       </c>
@@ -9422,7 +9425,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:22">
       <c r="A59" t="s">
         <v>35</v>
       </c>
@@ -9482,7 +9485,7 @@
       </c>
       <c r="S59" s="69" t="str">
         <f>IF('AOP Critical'!T37="","",'AOP Critical'!T37)</f>
-        <v/>
+        <v>HY</v>
       </c>
       <c r="T59" s="69" t="str">
         <f>IF('AOP Critical'!U37="","",'AOP Critical'!U37)</f>
@@ -9518,34 +9521,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{632542D1-52E6-4116-B536-B17D5839DF19}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AC52"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="20.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.45" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="25.54296875" customWidth="1"/>
-    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="26.81640625" customWidth="1"/>
-    <col min="5" max="5" width="5.1796875" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="4.54296875" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="1.81640625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="2.7265625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.7265625" customWidth="1"/>
-    <col min="12" max="12" width="5.54296875" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="6.81640625" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="6.26953125" customWidth="1"/>
-    <col min="15" max="15" width="7.26953125" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="6.1796875" hidden="1" customWidth="1"/>
-    <col min="17" max="22" width="6.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="1" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="26.85546875" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="1.85546875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="2.7109375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="6.85546875" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="6.28515625" customWidth="1"/>
+    <col min="15" max="15" width="7.28515625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="6.140625" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="6.140625" customWidth="1"/>
     <col min="23" max="23" width="6" customWidth="1"/>
-    <col min="24" max="24" width="58.81640625" style="20" customWidth="1"/>
-    <col min="25" max="25" width="68.1796875" customWidth="1"/>
-    <col min="26" max="26" width="17.7265625" customWidth="1"/>
+    <col min="24" max="24" width="58.85546875" style="20" customWidth="1"/>
+    <col min="25" max="25" width="68.140625" customWidth="1"/>
+    <col min="26" max="26" width="17.7109375" customWidth="1"/>
     <col min="27" max="27" width="57" style="13" customWidth="1"/>
-    <col min="28" max="46" width="8.54296875" customWidth="1"/>
+    <col min="28" max="46" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27" ht="20.45" customHeight="1">
       <c r="B1" s="3" t="s">
         <v>39</v>
       </c>
@@ -9556,7 +9560,7 @@
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
     </row>
-    <row r="2" spans="1:27" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27" ht="20.45" customHeight="1">
       <c r="B2" s="6"/>
       <c r="C2" s="7"/>
       <c r="E2" s="6"/>
@@ -9565,7 +9569,7 @@
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
     </row>
-    <row r="3" spans="1:27" s="5" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:27" s="5" customFormat="1" ht="20.45" customHeight="1">
       <c r="A3" s="110" t="s">
         <v>40</v>
       </c>
@@ -9589,7 +9593,7 @@
       <c r="X3" s="89"/>
       <c r="AA3" s="14"/>
     </row>
-    <row r="4" spans="1:27" s="5" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:27" s="5" customFormat="1" ht="20.45" customHeight="1">
       <c r="A4" s="112" t="str">
         <f ca="1">"Current Month-Year " &amp; ":" &amp; TEXT(TODAY(),"YYYY-MM")</f>
         <v>Current Month-Year :2026-10</v>
@@ -9621,7 +9625,7 @@
       <c r="Z4" s="112"/>
       <c r="AA4" s="112"/>
     </row>
-    <row r="5" spans="1:27" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:27" ht="20.45" customHeight="1">
       <c r="A5" s="85" t="s">
         <v>0</v>
       </c>
@@ -9676,7 +9680,7 @@
         <v>19</v>
       </c>
       <c r="T5" s="34" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="U5" s="34" t="s">
         <v>21</v>
@@ -9688,30 +9692,30 @@
         <v>23</v>
       </c>
       <c r="X5" s="23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Y5" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Z5" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AA5" s="15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:27" ht="14.45">
       <c r="A6" s="109" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B6" s="91" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C6" s="92" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D6" s="90" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E6" s="108">
         <v>10</v>
@@ -9719,16 +9723,16 @@
       <c r="F6" s="108"/>
       <c r="G6" s="108"/>
       <c r="H6" s="111" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I6" s="108" t="s">
         <v>33</v>
       </c>
       <c r="J6" s="107" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K6" s="22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L6" s="35">
         <v>0.08</v>
@@ -9770,10 +9774,10 @@
       <c r="Y6" s="113"/>
       <c r="Z6" s="113"/>
       <c r="AA6" s="123" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:27" ht="14.45">
       <c r="A7" s="109"/>
       <c r="B7" s="91"/>
       <c r="C7" s="92"/>
@@ -9785,7 +9789,7 @@
       <c r="I7" s="108"/>
       <c r="J7" s="107"/>
       <c r="K7" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L7" s="17">
         <v>3.7999999999999999E-2</v>
@@ -9822,16 +9826,16 @@
       <c r="Z7" s="96"/>
       <c r="AA7" s="124"/>
     </row>
-    <row r="8" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:27" ht="14.45">
       <c r="A8" s="109"/>
       <c r="B8" s="91" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C8" s="92" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" s="90" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E8" s="108">
         <v>90</v>
@@ -9845,10 +9849,10 @@
         <v>33</v>
       </c>
       <c r="J8" s="107" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K8" s="22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L8" s="35">
         <v>0.9</v>
@@ -9880,10 +9884,10 @@
       <c r="Y8" s="95"/>
       <c r="Z8" s="114"/>
       <c r="AA8" s="123" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:27" ht="14.45">
       <c r="A9" s="109"/>
       <c r="B9" s="91"/>
       <c r="C9" s="92"/>
@@ -9895,7 +9899,7 @@
       <c r="I9" s="108"/>
       <c r="J9" s="107"/>
       <c r="K9" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L9" s="19">
         <v>1</v>
@@ -9932,16 +9936,16 @@
       <c r="Z9" s="115"/>
       <c r="AA9" s="124"/>
     </row>
-    <row r="10" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:27" ht="14.45">
       <c r="A10" s="109"/>
       <c r="B10" s="91" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10" s="92" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D10" s="90" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E10" s="108">
         <v>1</v>
@@ -9949,16 +9953,16 @@
       <c r="F10" s="108"/>
       <c r="G10" s="108"/>
       <c r="H10" s="111" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I10" s="108" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J10" s="107" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K10" s="22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L10" s="36">
         <v>1</v>
@@ -9984,7 +9988,9 @@
       <c r="S10" s="8">
         <v>1</v>
       </c>
-      <c r="T10" s="8"/>
+      <c r="T10" s="8">
+        <v>1</v>
+      </c>
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
       <c r="W10" s="33"/>
@@ -9992,10 +9998,10 @@
       <c r="Y10" s="164"/>
       <c r="Z10" s="117"/>
       <c r="AA10" s="123" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:27" ht="15" thickBot="1">
       <c r="A11" s="109"/>
       <c r="B11" s="91"/>
       <c r="C11" s="92"/>
@@ -10007,7 +10013,7 @@
       <c r="I11" s="108"/>
       <c r="J11" s="107"/>
       <c r="K11" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L11" s="9">
         <v>2</v>
@@ -10044,18 +10050,18 @@
       <c r="Z11" s="118"/>
       <c r="AA11" s="124"/>
     </row>
-    <row r="12" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:27" ht="14.45">
       <c r="A12" s="109" t="s">
         <v>24</v>
       </c>
       <c r="B12" s="93" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C12" s="93" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D12" s="90" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E12" s="108">
         <v>84</v>
@@ -10069,10 +10075,10 @@
         <v>33</v>
       </c>
       <c r="J12" s="107" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K12" s="22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L12" s="35">
         <v>0.69</v>
@@ -10114,10 +10120,10 @@
       <c r="Y12" s="95"/>
       <c r="Z12" s="96"/>
       <c r="AA12" s="123" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:27" ht="14.45">
       <c r="A13" s="109"/>
       <c r="B13" s="93"/>
       <c r="C13" s="93"/>
@@ -10129,7 +10135,7 @@
       <c r="I13" s="108"/>
       <c r="J13" s="107"/>
       <c r="K13" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L13" s="19">
         <v>0.83</v>
@@ -10166,16 +10172,16 @@
       <c r="Z13" s="96"/>
       <c r="AA13" s="124"/>
     </row>
-    <row r="14" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:27" ht="14.45">
       <c r="A14" s="109"/>
       <c r="B14" s="93" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C14" s="122" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D14" s="90" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E14" s="108">
         <v>54.6</v>
@@ -10189,10 +10195,10 @@
         <v>33</v>
       </c>
       <c r="J14" s="107" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K14" s="22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L14" s="37">
         <v>0.54249999999999998</v>
@@ -10225,15 +10231,15 @@
       <c r="V14" s="37"/>
       <c r="W14" s="37"/>
       <c r="X14" s="152" t="s">
-        <v>141</v>
+        <v>71</v>
       </c>
       <c r="Y14" s="97" t="s">
-        <v>140</v>
+        <v>72</v>
       </c>
       <c r="Z14" s="154"/>
       <c r="AA14" s="151"/>
     </row>
-    <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:27" ht="15" thickBot="1">
       <c r="A15" s="109"/>
       <c r="B15" s="93"/>
       <c r="C15" s="122"/>
@@ -10245,7 +10251,7 @@
       <c r="I15" s="108"/>
       <c r="J15" s="107"/>
       <c r="K15" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L15" s="17">
         <v>0.51780000000000004</v>
@@ -10282,21 +10288,21 @@
       <c r="Z15" s="113"/>
       <c r="AA15" s="131"/>
     </row>
-    <row r="16" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:27" ht="14.45">
       <c r="A16" s="109" t="s">
         <v>25</v>
       </c>
       <c r="B16" s="93" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D16" s="90" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E16" s="108" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F16" s="108"/>
       <c r="G16" s="108"/>
@@ -10307,10 +10313,10 @@
         <v>33</v>
       </c>
       <c r="J16" s="107" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K16" s="22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L16" s="37">
         <v>0.11774014693384624</v>
@@ -10346,10 +10352,10 @@
       <c r="Y16" s="95"/>
       <c r="Z16" s="115"/>
       <c r="AA16" s="123" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:27" ht="14.45">
       <c r="A17" s="109"/>
       <c r="B17" s="93"/>
       <c r="C17" s="93"/>
@@ -10361,7 +10367,7 @@
       <c r="I17" s="108"/>
       <c r="J17" s="107"/>
       <c r="K17" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L17" s="17">
         <v>-4.253311543933095E-2</v>
@@ -10398,19 +10404,19 @@
       <c r="Z17" s="115"/>
       <c r="AA17" s="124"/>
     </row>
-    <row r="18" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:27" ht="14.45">
       <c r="A18" s="109"/>
       <c r="B18" s="93" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C18" s="93" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D18" s="93" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" s="108" t="s">
         <v>76</v>
-      </c>
-      <c r="E18" s="108" t="s">
-        <v>73</v>
       </c>
       <c r="F18" s="108"/>
       <c r="G18" s="108"/>
@@ -10418,13 +10424,13 @@
         <v>32</v>
       </c>
       <c r="I18" s="108" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J18" s="107" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K18" s="22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L18" s="47">
         <v>0.224</v>
@@ -10457,7 +10463,7 @@
       <c r="V18" s="47"/>
       <c r="W18" s="47"/>
       <c r="X18" s="158" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="Y18" s="158"/>
       <c r="Z18" s="155">
@@ -10465,7 +10471,7 @@
       </c>
       <c r="AA18" s="157"/>
     </row>
-    <row r="19" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:27" ht="14.45">
       <c r="A19" s="109"/>
       <c r="B19" s="93"/>
       <c r="C19" s="93"/>
@@ -10477,7 +10483,7 @@
       <c r="I19" s="108"/>
       <c r="J19" s="107"/>
       <c r="K19" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L19" s="87">
         <v>0.2598381666666667</v>
@@ -10514,33 +10520,33 @@
       <c r="Z19" s="156"/>
       <c r="AA19" s="157"/>
     </row>
-    <row r="20" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:27" ht="14.45">
       <c r="A20" s="109"/>
       <c r="B20" s="93" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C20" s="93" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D20" s="90" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E20" s="108" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F20" s="108"/>
       <c r="G20" s="108"/>
       <c r="H20" s="111" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I20" s="108" t="s">
         <v>33</v>
       </c>
       <c r="J20" s="107" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K20" s="22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L20" s="35">
         <v>0.28399999999999997</v>
@@ -10573,17 +10579,17 @@
       <c r="V20" s="18"/>
       <c r="W20" s="27"/>
       <c r="X20" s="99" t="s">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="Y20" s="101" t="s">
-        <v>138</v>
+        <v>85</v>
       </c>
       <c r="Z20" s="153"/>
       <c r="AA20" s="125" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:27" ht="15" thickBot="1">
       <c r="A21" s="109"/>
       <c r="B21" s="93"/>
       <c r="C21" s="93"/>
@@ -10595,7 +10601,7 @@
       <c r="I21" s="108"/>
       <c r="J21" s="107"/>
       <c r="K21" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L21" s="19">
         <v>0.27400000000000002</v>
@@ -10632,18 +10638,18 @@
       <c r="Z21" s="119"/>
       <c r="AA21" s="125"/>
     </row>
-    <row r="22" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:27" ht="14.45">
       <c r="A22" s="109" t="s">
         <v>26</v>
       </c>
       <c r="B22" s="93" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C22" s="122" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D22" s="93" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E22" s="108">
         <v>90</v>
@@ -10657,10 +10663,10 @@
         <v>33</v>
       </c>
       <c r="J22" s="107" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K22" s="22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L22" s="35">
         <v>0.9</v>
@@ -10705,7 +10711,7 @@
       </c>
       <c r="AA22" s="162"/>
     </row>
-    <row r="23" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:27" ht="15" thickBot="1">
       <c r="A23" s="169"/>
       <c r="B23" s="93"/>
       <c r="C23" s="122"/>
@@ -10717,7 +10723,7 @@
       <c r="I23" s="108"/>
       <c r="J23" s="107"/>
       <c r="K23" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L23" s="54">
         <v>0.81</v>
@@ -10725,25 +10731,25 @@
       <c r="M23" s="54">
         <v>0.78</v>
       </c>
-      <c r="N23" s="19">
+      <c r="N23" s="56">
         <v>0.8</v>
       </c>
-      <c r="O23" s="19">
+      <c r="O23" s="56">
         <v>0.82</v>
       </c>
-      <c r="P23" s="19">
+      <c r="P23" s="56">
         <v>0.79500000000000004</v>
       </c>
-      <c r="Q23" s="19">
+      <c r="Q23" s="56">
         <v>0.86</v>
       </c>
-      <c r="R23" s="29">
+      <c r="R23" s="56">
         <v>0.88</v>
       </c>
-      <c r="S23" s="29">
+      <c r="S23" s="56">
         <v>0.94</v>
       </c>
-      <c r="T23" s="29">
+      <c r="T23" s="56">
         <v>0.94</v>
       </c>
       <c r="U23" s="29"/>
@@ -10754,27 +10760,27 @@
       <c r="Z23" s="115"/>
       <c r="AA23" s="163"/>
     </row>
-    <row r="24" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:27" ht="14.45">
       <c r="A24" s="143" t="s">
         <v>27</v>
       </c>
       <c r="B24" s="93" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C24" s="122" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D24" s="90" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E24" s="108" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F24" s="108" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G24" s="108" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="H24" s="111" t="s">
         <v>32</v>
@@ -10786,7 +10792,7 @@
         <v>34</v>
       </c>
       <c r="K24" s="22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L24" s="35"/>
       <c r="M24" s="35"/>
@@ -10794,21 +10800,23 @@
         <v>0.104</v>
       </c>
       <c r="O24" s="21" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="P24" s="21" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q24" s="37">
         <v>0.11799999999999999</v>
       </c>
       <c r="R24" s="21" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="S24" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="T24" s="35"/>
+        <v>94</v>
+      </c>
+      <c r="T24" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="U24" s="21"/>
       <c r="V24" s="21"/>
       <c r="W24" s="38"/>
@@ -10816,10 +10824,10 @@
       <c r="Y24" s="154"/>
       <c r="Z24" s="119"/>
       <c r="AA24" s="123" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:27" ht="15" thickBot="1">
       <c r="A25" s="168"/>
       <c r="B25" s="93"/>
       <c r="C25" s="122"/>
@@ -10831,33 +10839,35 @@
       <c r="I25" s="108"/>
       <c r="J25" s="120"/>
       <c r="K25" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L25" s="21" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="M25" s="21" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="N25" s="50">
         <v>0.115</v>
       </c>
       <c r="O25" s="21" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="P25" s="21" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q25" s="17">
-        <v>0.121</v>
+        <v>0.12</v>
       </c>
       <c r="R25" s="21" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="S25" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="T25" s="55"/>
+        <v>94</v>
+      </c>
+      <c r="T25" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="U25" s="21"/>
       <c r="V25" s="21"/>
       <c r="W25" s="55"/>
@@ -10866,16 +10876,16 @@
       <c r="Z25" s="153"/>
       <c r="AA25" s="124"/>
     </row>
-    <row r="26" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:27" ht="14.45">
       <c r="A26" s="168"/>
       <c r="B26" s="91" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C26" s="161" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D26" s="90" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E26" s="108">
         <v>34</v>
@@ -10889,10 +10899,10 @@
         <v>33</v>
       </c>
       <c r="J26" s="107" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K26" s="22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L26" s="35">
         <v>0.34</v>
@@ -10900,25 +10910,25 @@
       <c r="M26" s="35">
         <v>0.34</v>
       </c>
-      <c r="N26" s="35">
+      <c r="N26" s="18">
         <v>0.34</v>
       </c>
-      <c r="O26" s="35">
+      <c r="O26" s="18">
         <v>0.34</v>
       </c>
-      <c r="P26" s="35">
+      <c r="P26" s="18">
         <v>0.34</v>
       </c>
-      <c r="Q26" s="35">
+      <c r="Q26" s="18">
         <v>0.34</v>
       </c>
-      <c r="R26" s="35">
+      <c r="R26" s="18">
         <v>0.34</v>
       </c>
-      <c r="S26" s="24">
+      <c r="S26" s="18">
         <v>0.34</v>
       </c>
-      <c r="T26" s="24">
+      <c r="T26" s="18">
         <v>0.34</v>
       </c>
       <c r="U26" s="24"/>
@@ -10928,10 +10938,10 @@
       <c r="Y26" s="96"/>
       <c r="Z26" s="115"/>
       <c r="AA26" s="123" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:27" ht="15" thickBot="1">
       <c r="A27" s="168"/>
       <c r="B27" s="91"/>
       <c r="C27" s="161"/>
@@ -10943,7 +10953,7 @@
       <c r="I27" s="108"/>
       <c r="J27" s="107"/>
       <c r="K27" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L27" s="78">
         <v>0.318</v>
@@ -10980,19 +10990,19 @@
       <c r="Z27" s="115"/>
       <c r="AA27" s="124"/>
     </row>
-    <row r="28" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:27" ht="14.45">
       <c r="A28" s="168"/>
       <c r="B28" s="90" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C28" s="93" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D28" s="90" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E28" s="108" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F28" s="108"/>
       <c r="G28" s="108"/>
@@ -11003,10 +11013,10 @@
         <v>33</v>
       </c>
       <c r="J28" s="107" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K28" s="22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L28" s="37" vm="1">
         <v>3.6951550944796852E-2</v>
@@ -11039,15 +11049,15 @@
       <c r="V28" s="24"/>
       <c r="W28" s="25"/>
       <c r="X28" s="103" t="s">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="Y28" s="97"/>
       <c r="Z28" s="119"/>
       <c r="AA28" s="128" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:27" ht="15" thickBot="1">
       <c r="A29" s="168"/>
       <c r="B29" s="90"/>
       <c r="C29" s="93"/>
@@ -11059,7 +11069,7 @@
       <c r="I29" s="108"/>
       <c r="J29" s="107"/>
       <c r="K29" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L29" s="17" vm="2">
         <v>-0.21537837470975407</v>
@@ -11096,17 +11106,17 @@
       <c r="Z29" s="153"/>
       <c r="AA29" s="129"/>
     </row>
-    <row r="30" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:27" ht="14.45">
       <c r="A30" s="168"/>
       <c r="B30" s="90"/>
       <c r="C30" s="93" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D30" s="90" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E30" s="108" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F30" s="108"/>
       <c r="G30" s="108"/>
@@ -11117,10 +11127,10 @@
         <v>33</v>
       </c>
       <c r="J30" s="107" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K30" s="22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L30" s="37">
         <v>0.35899999999999999</v>
@@ -11157,7 +11167,7 @@
       <c r="Z30" s="119"/>
       <c r="AA30" s="166"/>
     </row>
-    <row r="31" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:27" ht="14.45">
       <c r="A31" s="168"/>
       <c r="B31" s="90"/>
       <c r="C31" s="93"/>
@@ -11169,7 +11179,7 @@
       <c r="I31" s="108"/>
       <c r="J31" s="107"/>
       <c r="K31" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L31" s="17">
         <v>0.32500000000000001</v>
@@ -11206,19 +11216,19 @@
       <c r="Z31" s="153"/>
       <c r="AA31" s="167"/>
     </row>
-    <row r="32" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:27" ht="14.45">
       <c r="A32" s="168"/>
       <c r="B32" s="93" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C32" s="122" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D32" s="90" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="E32" s="108" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F32" s="108"/>
       <c r="G32" s="108"/>
@@ -11226,13 +11236,13 @@
         <v>32</v>
       </c>
       <c r="I32" s="108" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J32" s="107" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K32" s="22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L32" s="41">
         <v>8.6903037999999988</v>
@@ -11265,17 +11275,17 @@
       <c r="V32" s="8"/>
       <c r="W32" s="33"/>
       <c r="X32" s="170" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="Y32" s="97" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="Z32" s="119"/>
       <c r="AA32" s="123" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:29" ht="15" thickBot="1">
       <c r="A33" s="168"/>
       <c r="B33" s="93"/>
       <c r="C33" s="122"/>
@@ -11287,7 +11297,7 @@
       <c r="I33" s="108"/>
       <c r="J33" s="107"/>
       <c r="K33" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L33" s="42">
         <v>4.05</v>
@@ -11324,7 +11334,7 @@
       <c r="Z33" s="153"/>
       <c r="AA33" s="124"/>
     </row>
-    <row r="34" spans="1:29" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:29" ht="14.45">
       <c r="A34" s="109" t="s">
         <v>28</v>
       </c>
@@ -11332,7 +11342,7 @@
         <v>29</v>
       </c>
       <c r="C34" s="93" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D34" s="90" t="s">
         <v>31</v>
@@ -11352,7 +11362,7 @@
         <v>34</v>
       </c>
       <c r="K34" s="22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L34" s="35"/>
       <c r="M34" s="35"/>
@@ -11376,14 +11386,14 @@
       </c>
       <c r="X34" s="94"/>
       <c r="Y34" s="96" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="Z34" s="115"/>
       <c r="AA34" s="123" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:29" ht="14.45">
       <c r="A35" s="109"/>
       <c r="B35" s="148"/>
       <c r="C35" s="93"/>
@@ -11395,31 +11405,31 @@
       <c r="I35" s="108"/>
       <c r="J35" s="120"/>
       <c r="K35" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L35" s="21" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="M35" s="21" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="N35" s="19">
         <v>1</v>
       </c>
       <c r="O35" s="21" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="P35" s="21" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q35" s="19">
         <v>0.96199999999999997</v>
       </c>
       <c r="R35" s="21" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="S35" s="21" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="T35" s="19">
         <v>0.91300000000000003</v>
@@ -11432,13 +11442,13 @@
       <c r="Z35" s="115"/>
       <c r="AA35" s="124"/>
     </row>
-    <row r="36" spans="1:29" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:29" ht="14.45">
       <c r="A36" s="109"/>
       <c r="B36" s="148" t="s">
         <v>35</v>
       </c>
       <c r="C36" s="93" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D36" s="90" t="s">
         <v>37</v>
@@ -11458,7 +11468,7 @@
         <v>38</v>
       </c>
       <c r="K36" s="22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L36" s="35"/>
       <c r="M36" s="35"/>
@@ -11477,17 +11487,17 @@
       <c r="V36" s="18"/>
       <c r="W36" s="27"/>
       <c r="X36" s="94" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="Y36" s="95" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="Z36" s="115"/>
       <c r="AA36" s="123" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:29" ht="14.45">
       <c r="A37" s="109"/>
       <c r="B37" s="148"/>
       <c r="C37" s="93"/>
@@ -11499,31 +11509,33 @@
       <c r="I37" s="108"/>
       <c r="J37" s="121"/>
       <c r="K37" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L37" s="21" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="M37" s="21" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="N37" s="21" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="O37" s="19">
         <v>0.79</v>
       </c>
       <c r="P37" s="21" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="Q37" s="19">
         <v>0.79</v>
       </c>
       <c r="R37" s="21" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="S37" s="56"/>
-      <c r="T37" s="56"/>
+      <c r="T37" s="21" t="s">
+        <v>115</v>
+      </c>
       <c r="U37" s="56"/>
       <c r="V37" s="56"/>
       <c r="W37" s="57"/>
@@ -11532,7 +11544,7 @@
       <c r="Z37" s="119"/>
       <c r="AA37" s="125"/>
     </row>
-    <row r="38" spans="1:29" s="5" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:29" s="5" customFormat="1" ht="20.45" customHeight="1">
       <c r="A38" s="138"/>
       <c r="B38" s="138"/>
       <c r="C38" s="138"/>
@@ -11561,9 +11573,9 @@
       <c r="Z38" s="139"/>
       <c r="AA38" s="139"/>
     </row>
-    <row r="39" spans="1:29" s="5" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:29" s="5" customFormat="1" ht="20.45" customHeight="1">
       <c r="A39" s="141" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B39" s="141"/>
       <c r="C39" s="58"/>
@@ -11592,12 +11604,12 @@
       <c r="Z39"/>
       <c r="AA39" s="13"/>
     </row>
-    <row r="40" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:29" ht="20.45" customHeight="1">
       <c r="A40" s="43" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>3</v>
@@ -11606,13 +11618,13 @@
         <v>4</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H40" s="10" t="s">
         <v>8</v>
@@ -11633,7 +11645,7 @@
         <v>13</v>
       </c>
       <c r="N40" s="10" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="O40" s="10" t="s">
         <v>15</v>
@@ -11642,7 +11654,7 @@
         <v>16</v>
       </c>
       <c r="Q40" s="10" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="R40" s="10" t="s">
         <v>18</v>
@@ -11663,51 +11675,51 @@
         <v>23</v>
       </c>
       <c r="X40" s="60" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Y40" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Z40" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AA40" s="16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:29" ht="20.45" customHeight="1">
       <c r="A41" s="142" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B41" s="145" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C41" s="146" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D41" s="147" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E41" s="140" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F41" s="140" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G41" s="140" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="H41" s="160" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I41" s="140" t="s">
         <v>33</v>
       </c>
       <c r="J41" s="149" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K41" s="61" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L41" s="76">
         <v>1.9099999999999999E-2</v>
@@ -11749,11 +11761,11 @@
       <c r="Y41" s="131"/>
       <c r="Z41" s="131"/>
       <c r="AA41" s="124" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="AC41" s="12"/>
     </row>
-    <row r="42" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:29" ht="20.45" customHeight="1">
       <c r="A42" s="143"/>
       <c r="B42" s="91"/>
       <c r="C42" s="92"/>
@@ -11765,7 +11777,7 @@
       <c r="I42" s="108"/>
       <c r="J42" s="127"/>
       <c r="K42" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L42" s="55">
         <v>9.1999999999999998E-3</v>
@@ -11802,27 +11814,27 @@
       <c r="Z42" s="131"/>
       <c r="AA42" s="126"/>
     </row>
-    <row r="43" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:29" ht="20.45" customHeight="1">
       <c r="A43" s="144" t="s">
         <v>26</v>
       </c>
       <c r="B43" s="91" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C43" s="92" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D43" s="90" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="E43" s="108" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F43" s="108" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G43" s="108" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="H43" s="111" t="s">
         <v>32</v>
@@ -11834,7 +11846,7 @@
         <v>34</v>
       </c>
       <c r="K43" s="22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L43" s="35"/>
       <c r="M43" s="35"/>
@@ -11853,17 +11865,17 @@
       <c r="V43" s="35"/>
       <c r="W43" s="38"/>
       <c r="X43" s="130" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="Y43" s="132" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="Z43" s="133"/>
       <c r="AA43" s="134" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:29" ht="20.45" customHeight="1">
       <c r="A44" s="144"/>
       <c r="B44" s="91"/>
       <c r="C44" s="92"/>
@@ -11875,38 +11887,38 @@
       <c r="I44" s="159"/>
       <c r="J44" s="120"/>
       <c r="K44" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L44" s="21" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="M44" s="21" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="N44" s="17">
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="O44" s="21" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="P44" s="21" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q44" s="17">
         <v>0.04</v>
       </c>
       <c r="R44" s="21" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="S44" s="21" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="T44" s="55"/>
       <c r="U44" s="21" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="V44" s="21" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="W44" s="55"/>
       <c r="X44" s="130"/>
@@ -11914,25 +11926,25 @@
       <c r="Z44" s="133"/>
       <c r="AA44" s="134"/>
     </row>
-    <row r="45" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:29" ht="20.45" customHeight="1">
       <c r="A45" s="144"/>
       <c r="B45" s="91" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C45" s="92" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D45" s="90" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E45" s="108" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F45" s="108" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G45" s="108" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="H45" s="111" t="s">
         <v>32</v>
@@ -11941,10 +11953,10 @@
         <v>33</v>
       </c>
       <c r="J45" s="127" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K45" s="22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L45" s="35">
         <v>0.4</v>
@@ -11978,16 +11990,16 @@
       <c r="W45" s="38"/>
       <c r="X45" s="130"/>
       <c r="Y45" s="132" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="Z45" s="135">
         <v>46188</v>
       </c>
       <c r="AA45" s="126" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:29" ht="20.45" customHeight="1">
       <c r="A46" s="144"/>
       <c r="B46" s="91"/>
       <c r="C46" s="92"/>
@@ -11999,7 +12011,7 @@
       <c r="I46" s="108"/>
       <c r="J46" s="127"/>
       <c r="K46" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L46" s="19">
         <v>0.66</v>
@@ -12036,37 +12048,37 @@
       <c r="Z46" s="133"/>
       <c r="AA46" s="126"/>
     </row>
-    <row r="47" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:29" ht="20.45" customHeight="1">
       <c r="A47" s="144"/>
       <c r="B47" s="91" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C47" s="92" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D47" s="90" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="E47" s="108" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F47" s="108" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G47" s="108" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="H47" s="111" t="s">
         <v>32</v>
       </c>
       <c r="I47" s="108" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J47" s="127" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K47" s="22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L47" s="36">
         <v>5.5</v>
@@ -12108,10 +12120,10 @@
       <c r="Y47" s="133"/>
       <c r="Z47" s="133"/>
       <c r="AA47" s="90" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:29" ht="20.45" customHeight="1">
       <c r="A48" s="144"/>
       <c r="B48" s="91"/>
       <c r="C48" s="92"/>
@@ -12123,7 +12135,7 @@
       <c r="I48" s="108"/>
       <c r="J48" s="127"/>
       <c r="K48" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L48" s="9">
         <v>9</v>
@@ -12161,27 +12173,27 @@
       <c r="Z48" s="133"/>
       <c r="AA48" s="90"/>
     </row>
-    <row r="49" spans="1:27" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:27" ht="20.45" customHeight="1">
       <c r="A49" s="143" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B49" s="150" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="C49" s="92" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D49" s="90" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="E49" s="108">
         <v>74</v>
       </c>
       <c r="F49" s="108" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G49" s="108" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="H49" s="111" t="s">
         <v>32</v>
@@ -12190,10 +12202,10 @@
         <v>33</v>
       </c>
       <c r="J49" s="107" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K49" s="22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L49" s="37">
         <v>0.73199999999999998</v>
@@ -12235,10 +12247,10 @@
       <c r="Y49" s="132"/>
       <c r="Z49" s="133"/>
       <c r="AA49" s="126" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:27" ht="20.45" customHeight="1">
       <c r="A50" s="143"/>
       <c r="B50" s="150"/>
       <c r="C50" s="92"/>
@@ -12250,7 +12262,7 @@
       <c r="I50" s="108"/>
       <c r="J50" s="107"/>
       <c r="K50" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L50" s="17">
         <v>0.69299999999999995</v>
@@ -12287,27 +12299,27 @@
       <c r="Z50" s="133"/>
       <c r="AA50" s="126"/>
     </row>
-    <row r="51" spans="1:27" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:27" ht="20.45" customHeight="1">
       <c r="A51" s="144" t="s">
         <v>25</v>
       </c>
       <c r="B51" s="91" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C51" s="92" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D51" s="90" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="E51" s="108">
         <v>33.1</v>
       </c>
       <c r="F51" s="108" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G51" s="108" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="H51" s="111" t="s">
         <v>32</v>
@@ -12316,10 +12328,10 @@
         <v>33</v>
       </c>
       <c r="J51" s="107" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K51" s="22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L51" s="37">
         <v>0.34700072985878605</v>
@@ -12355,10 +12367,10 @@
       <c r="Y51" s="133"/>
       <c r="Z51" s="133"/>
       <c r="AA51" s="93" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="20.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:27" ht="20.45" customHeight="1" thickBot="1">
       <c r="A52" s="144"/>
       <c r="B52" s="91"/>
       <c r="C52" s="92"/>
@@ -12370,7 +12382,7 @@
       <c r="I52" s="108"/>
       <c r="J52" s="107"/>
       <c r="K52" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L52" s="17">
         <v>0.36591770011686803</v>
@@ -12727,34 +12739,34 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L27">
-    <cfRule type="expression" dxfId="66" priority="81" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="78">
+      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&gt;L26)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="65" priority="79">
+      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&lt;=L26)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="80">
+      <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&lt;L26)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="63" priority="81" stopIfTrue="1">
       <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&gt;=L26)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="80">
-      <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&lt;L26)</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L7:W7 L9:W9 L11:W11 L13:W13 L15:W15 L17:W17 L19:W19 L21:W21 L23:W23 M27:W27 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37 U37:W37">
+    <cfRule type="expression" dxfId="62" priority="74">
+      <formula>AND(OR($H6="Lower the better", $H6="Lower the better"), L7&gt; L6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="79">
-      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&lt;=L26)</formula>
+    <cfRule type="expression" dxfId="61" priority="247">
+      <formula>AND(OR($H6="Lower the better", $H6= "Lower the Better"), L7 &lt;= L6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="78">
-      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&gt;L26)</formula>
+    <cfRule type="expression" dxfId="60" priority="248">
+      <formula>AND(OR($H6="Higher the better", $H6="Higher the Better"), L7 &lt; L6)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="59" priority="249">
+      <formula xml:space="preserve"> AND(OR($H6="Higher the better", $H6="Higher the Better"), L7&gt;= L6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L7:W7 L9:W9 L11:W11 L13:W13 L15:W15 L17:W17 L19:W19 L21:W21 L23:W23 M27:W27 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37">
-    <cfRule type="expression" dxfId="62" priority="249">
-      <formula xml:space="preserve"> AND(OR($H6="Higher the better", $H6="Higher the Better"), L7&gt;= L6)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="61" priority="74">
-      <formula>AND(OR($H6="Lower the better", $H6="Lower the better"), L7&gt; L6)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="60" priority="247">
-      <formula>AND(OR($H6="Lower the better", $H6= "Lower the Better"), L7 &lt;= L6)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="59" priority="248">
-      <formula>AND(OR($H6="Higher the better", $H6="Higher the Better"), L7 &lt; L6)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L23:W27 L7:W7 L9:W9 L11:W11 L13:W13 L15:W15 L17:W17 L19:W19 L21:W21 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37">
+  <conditionalFormatting sqref="L7:W7 L9:W9 L11:W11 L13:W13 L15:W15 L17:W17 L19:W19 L21:W21 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37 L23:W27 U37:W37">
     <cfRule type="containsBlanks" dxfId="58" priority="245">
       <formula>LEN(TRIM(L7))=0</formula>
     </cfRule>
@@ -12768,185 +12780,185 @@
     <cfRule type="containsBlanks" dxfId="56" priority="173">
       <formula>LEN(TRIM(L46))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="177">
-      <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&lt;L45)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="54" priority="175">
+    <cfRule type="expression" dxfId="55" priority="175">
       <formula>AND(OR($H45="Lower the better", $H45="Lower the Better"), L46&gt;L45)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="176">
+    <cfRule type="expression" dxfId="54" priority="176">
       <formula>AND(OR($H45="Lower the better", $H45="Lower the Better"), L46&lt;=L45)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="53" priority="177">
+      <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&lt;L45)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="52" priority="178" stopIfTrue="1">
       <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&gt;=L45)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L52:W52">
-    <cfRule type="expression" dxfId="51" priority="107">
-      <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&lt;L51)</formula>
+    <cfRule type="containsBlanks" dxfId="51" priority="104">
+      <formula>LEN(TRIM(L52))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="106">
+    <cfRule type="expression" dxfId="50" priority="105">
+      <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&gt;L51)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="49" priority="106">
       <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&lt;=L51)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="49" priority="104">
-      <formula>LEN(TRIM(L52))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="105">
-      <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&gt;L51)</formula>
+    <cfRule type="expression" dxfId="48" priority="107">
+      <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&lt;L51)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="47" priority="108" stopIfTrue="1">
       <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&gt;=L51)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N25 T25 W25 L42:W42">
-    <cfRule type="expression" dxfId="46" priority="71" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&gt;=L24)</formula>
+  <conditionalFormatting sqref="N25 W25 L42:W42">
+    <cfRule type="containsBlanks" dxfId="46" priority="67">
+      <formula>LEN(TRIM(L25))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="70">
+    <cfRule type="expression" dxfId="45" priority="68">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&gt;L24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="69">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&lt;=L24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="43" priority="70">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&lt;L24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="68">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&gt;L24)</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="43" priority="67">
-      <formula>LEN(TRIM(L25))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="69">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&lt;=L24)</formula>
+    <cfRule type="expression" dxfId="42" priority="71" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&gt;=L24)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25">
-    <cfRule type="expression" dxfId="41" priority="18">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
+    <cfRule type="containsBlanks" dxfId="41" priority="16">
+      <formula>LEN(TRIM(N25))=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="40" priority="17">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&gt;N24)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="39" priority="16">
+    <cfRule type="expression" dxfId="39" priority="18">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="19">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="20" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="36" priority="21">
       <formula>LEN(TRIM(N25))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="25" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="37" priority="22">
+    <cfRule type="expression" dxfId="35" priority="22">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&gt;N24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="24">
+    <cfRule type="expression" dxfId="34" priority="23">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="24">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="35" priority="21">
-      <formula>LEN(TRIM(N25))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="25" stopIfTrue="1">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="23">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="19">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N44">
-    <cfRule type="expression" dxfId="31" priority="65">
+    <cfRule type="containsBlanks" dxfId="31" priority="62">
+      <formula>LEN(TRIM(N44))=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="63">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&gt;N43)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="64">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&lt;=N43)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="65">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&lt;N43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="66" stopIfTrue="1">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&gt;=N43)</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="29" priority="62">
-      <formula>LEN(TRIM(N44))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="63">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&gt;N43)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="64">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&lt;=N43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q25">
-    <cfRule type="expression" dxfId="26" priority="30" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&gt;=Q24)</formula>
+    <cfRule type="containsBlanks" dxfId="26" priority="26">
+      <formula>LEN(TRIM(Q25))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="29">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&lt;Q24)</formula>
+    <cfRule type="expression" dxfId="25" priority="27">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&gt;Q24)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="24" priority="28">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&lt;=Q24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="27">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&gt;Q24)</formula>
+    <cfRule type="expression" dxfId="23" priority="29">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&lt;Q24)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="22" priority="26">
-      <formula>LEN(TRIM(Q25))=0</formula>
+    <cfRule type="expression" dxfId="22" priority="30" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&gt;=Q24)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q37">
-    <cfRule type="expression" dxfId="21" priority="10">
-      <formula xml:space="preserve"> AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37&gt;= Q36)</formula>
+    <cfRule type="expression" dxfId="21" priority="6">
+      <formula>AND(OR($H36="Lower the better", $H36="Lower the better"), Q37&gt; Q36)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="9">
-      <formula>AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37 &lt; Q36)</formula>
+    <cfRule type="containsBlanks" dxfId="20" priority="7">
+      <formula>LEN(TRIM(Q37))=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="8">
       <formula>AND(OR($H36="Lower the better", $H36= "Lower the Better"), Q37 &lt;= Q36)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="6">
-      <formula>AND(OR($H36="Lower the better", $H36="Lower the better"), Q37&gt; Q36)</formula>
+    <cfRule type="expression" dxfId="18" priority="9">
+      <formula>AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37 &lt; Q36)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="17" priority="7">
-      <formula>LEN(TRIM(Q37))=0</formula>
+    <cfRule type="expression" dxfId="17" priority="10">
+      <formula xml:space="preserve"> AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37&gt;= Q36)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q44">
-    <cfRule type="expression" dxfId="16" priority="15" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&gt;=Q43)</formula>
+    <cfRule type="containsBlanks" dxfId="16" priority="11">
+      <formula>LEN(TRIM(Q44))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="14">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&lt;Q43)</formula>
+    <cfRule type="expression" dxfId="15" priority="12">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&gt;Q43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="13">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&lt;=Q43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="12">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&gt;Q43)</formula>
+    <cfRule type="expression" dxfId="13" priority="14">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&lt;Q43)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="12" priority="11">
-      <formula>LEN(TRIM(Q44))=0</formula>
+    <cfRule type="expression" dxfId="12" priority="15" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&gt;=Q43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T44">
-    <cfRule type="expression" dxfId="11" priority="56" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&gt;=T43)</formula>
+    <cfRule type="containsBlanks" dxfId="11" priority="52">
+      <formula>LEN(TRIM(T44))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="55">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&lt;T43)</formula>
+    <cfRule type="expression" dxfId="10" priority="53">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&gt;T43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="9" priority="54">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&lt;=T43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="53">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&gt;T43)</formula>
+    <cfRule type="expression" dxfId="8" priority="55">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&lt;T43)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="7" priority="52">
-      <formula>LEN(TRIM(T44))=0</formula>
+    <cfRule type="expression" dxfId="7" priority="56" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&gt;=T43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W44">
-    <cfRule type="expression" dxfId="6" priority="48">
+    <cfRule type="containsBlanks" dxfId="6" priority="47">
+      <formula>LEN(TRIM(W44))=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="48">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&gt;W43)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="5" priority="47">
-      <formula>LEN(TRIM(W44))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="51" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&gt;=W43)</formula>
+    <cfRule type="expression" dxfId="4" priority="49">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&lt;=W43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="3" priority="50">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&lt;W43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="49">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&lt;=W43)</formula>
+    <cfRule type="expression" dxfId="2" priority="51" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&gt;=W43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA47">
@@ -13155,40 +13167,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F096517C-598E-4E6D-B017-32F081EE1644}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{497B9C89-7047-44E4-9E7C-8AF16D1DE759}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="f5a961e1-edc1-4f62-8655-e8a46ef79e5c"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="68108f69-118e-4385-83b3-00743b1bf54c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/GlobalMoSMT-2023/Shared Documents/General/2026/Goals Alignment 2026/Strategic Execution 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3339" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{736A0B24-C905-4A14-9278-294C93D80D9F}"/>
+  <xr:revisionPtr revIDLastSave="3344" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A27AE65D-DBDE-4CC8-A71E-1E2190A0DEC8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
   </bookViews>
@@ -1565,32 +1565,236 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1604,212 +1808,8 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -5511,13 +5511,13 @@
         <f>IF('AOP Critical'!R8="","",'AOP Critical'!R8)</f>
         <v>0.9</v>
       </c>
-      <c r="R7" s="69" t="str">
+      <c r="R7" s="69">
         <f>IF('AOP Critical'!S8="","",'AOP Critical'!S8)</f>
-        <v/>
-      </c>
-      <c r="S7" s="69" t="str">
+        <v>0.9</v>
+      </c>
+      <c r="S7" s="69">
         <f>IF('AOP Critical'!T8="","",'AOP Critical'!T8)</f>
-        <v/>
+        <v>0.9</v>
       </c>
       <c r="T7" s="69" t="str">
         <f>IF('AOP Critical'!U8="","",'AOP Critical'!U8)</f>
@@ -9570,10 +9570,10 @@
       <c r="I2" s="6"/>
     </row>
     <row r="3" spans="1:27" s="5" customFormat="1" ht="20.45" customHeight="1">
-      <c r="A3" s="110" t="s">
+      <c r="A3" s="162" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="110"/>
+      <c r="B3" s="162"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -9594,36 +9594,36 @@
       <c r="AA3" s="14"/>
     </row>
     <row r="4" spans="1:27" s="5" customFormat="1" ht="20.45" customHeight="1">
-      <c r="A4" s="112" t="str">
+      <c r="A4" s="163" t="str">
         <f ca="1">"Current Month-Year " &amp; ":" &amp; TEXT(TODAY(),"YYYY-MM")</f>
         <v>Current Month-Year :2026-10</v>
       </c>
-      <c r="B4" s="112"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="112"/>
-      <c r="L4" s="112"/>
-      <c r="M4" s="112"/>
-      <c r="N4" s="112"/>
-      <c r="O4" s="112"/>
-      <c r="P4" s="112"/>
-      <c r="Q4" s="112"/>
-      <c r="R4" s="112"/>
-      <c r="S4" s="112"/>
-      <c r="T4" s="112"/>
-      <c r="U4" s="112"/>
-      <c r="V4" s="112"/>
-      <c r="W4" s="112"/>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="112"/>
-      <c r="Z4" s="112"/>
-      <c r="AA4" s="112"/>
+      <c r="B4" s="163"/>
+      <c r="C4" s="163"/>
+      <c r="D4" s="163"/>
+      <c r="E4" s="163"/>
+      <c r="F4" s="163"/>
+      <c r="G4" s="163"/>
+      <c r="H4" s="163"/>
+      <c r="I4" s="163"/>
+      <c r="J4" s="163"/>
+      <c r="K4" s="163"/>
+      <c r="L4" s="163"/>
+      <c r="M4" s="163"/>
+      <c r="N4" s="163"/>
+      <c r="O4" s="163"/>
+      <c r="P4" s="163"/>
+      <c r="Q4" s="163"/>
+      <c r="R4" s="163"/>
+      <c r="S4" s="163"/>
+      <c r="T4" s="163"/>
+      <c r="U4" s="163"/>
+      <c r="V4" s="163"/>
+      <c r="W4" s="163"/>
+      <c r="X4" s="163"/>
+      <c r="Y4" s="163"/>
+      <c r="Z4" s="163"/>
+      <c r="AA4" s="163"/>
     </row>
     <row r="5" spans="1:27" ht="20.45" customHeight="1">
       <c r="A5" s="85" t="s">
@@ -9638,11 +9638,11 @@
       <c r="D5" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="116" t="s">
+      <c r="E5" s="164" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
+      <c r="F5" s="164"/>
+      <c r="G5" s="164"/>
       <c r="H5" s="86" t="s">
         <v>8</v>
       </c>
@@ -9705,30 +9705,30 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="14.45">
-      <c r="A6" s="109" t="s">
+      <c r="A6" s="92" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="91" t="s">
+      <c r="B6" s="125" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="92" t="s">
+      <c r="C6" s="137" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="105" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="108">
+      <c r="E6" s="104">
         <v>10</v>
       </c>
-      <c r="F6" s="108"/>
-      <c r="G6" s="108"/>
-      <c r="H6" s="111" t="s">
+      <c r="F6" s="104"/>
+      <c r="G6" s="104"/>
+      <c r="H6" s="103" t="s">
         <v>52</v>
       </c>
-      <c r="I6" s="108" t="s">
+      <c r="I6" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="107" t="s">
+      <c r="J6" s="106" t="s">
         <v>53</v>
       </c>
       <c r="K6" s="22" t="s">
@@ -9770,24 +9770,24 @@
       <c r="W6" s="27">
         <v>0.05</v>
       </c>
-      <c r="X6" s="106"/>
-      <c r="Y6" s="113"/>
-      <c r="Z6" s="113"/>
-      <c r="AA6" s="123" t="s">
+      <c r="X6" s="110"/>
+      <c r="Y6" s="101"/>
+      <c r="Z6" s="101"/>
+      <c r="AA6" s="117" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="14.45">
-      <c r="A7" s="109"/>
-      <c r="B7" s="91"/>
-      <c r="C7" s="92"/>
-      <c r="D7" s="90"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="108"/>
-      <c r="G7" s="108"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="108"/>
-      <c r="J7" s="107"/>
+      <c r="A7" s="92"/>
+      <c r="B7" s="125"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="106"/>
       <c r="K7" s="22" t="s">
         <v>56</v>
       </c>
@@ -9821,34 +9821,34 @@
       <c r="U7" s="50"/>
       <c r="V7" s="50"/>
       <c r="W7" s="50"/>
-      <c r="X7" s="94"/>
-      <c r="Y7" s="96"/>
-      <c r="Z7" s="96"/>
-      <c r="AA7" s="124"/>
+      <c r="X7" s="111"/>
+      <c r="Y7" s="131"/>
+      <c r="Z7" s="131"/>
+      <c r="AA7" s="118"/>
     </row>
     <row r="8" spans="1:27" ht="14.45">
-      <c r="A8" s="109"/>
-      <c r="B8" s="91" t="s">
+      <c r="A8" s="92"/>
+      <c r="B8" s="125" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="92" t="s">
+      <c r="C8" s="137" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="90" t="s">
+      <c r="D8" s="105" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="108">
+      <c r="E8" s="104">
         <v>90</v>
       </c>
-      <c r="F8" s="108"/>
-      <c r="G8" s="108"/>
-      <c r="H8" s="111" t="s">
+      <c r="F8" s="104"/>
+      <c r="G8" s="104"/>
+      <c r="H8" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="108" t="s">
+      <c r="I8" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="107" t="s">
+      <c r="J8" s="106" t="s">
         <v>53</v>
       </c>
       <c r="K8" s="22" t="s">
@@ -9875,29 +9875,33 @@
       <c r="R8" s="35">
         <v>0.9</v>
       </c>
-      <c r="S8" s="18"/>
-      <c r="T8" s="18"/>
+      <c r="S8" s="35">
+        <v>0.9</v>
+      </c>
+      <c r="T8" s="35">
+        <v>0.9</v>
+      </c>
       <c r="U8" s="18"/>
       <c r="V8" s="18"/>
       <c r="W8" s="27"/>
-      <c r="X8" s="94"/>
-      <c r="Y8" s="95"/>
-      <c r="Z8" s="114"/>
-      <c r="AA8" s="123" t="s">
+      <c r="X8" s="111"/>
+      <c r="Y8" s="130"/>
+      <c r="Z8" s="115"/>
+      <c r="AA8" s="117" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="14.45">
-      <c r="A9" s="109"/>
-      <c r="B9" s="91"/>
-      <c r="C9" s="92"/>
-      <c r="D9" s="90"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108"/>
-      <c r="G9" s="108"/>
-      <c r="H9" s="111"/>
-      <c r="I9" s="108"/>
-      <c r="J9" s="107"/>
+      <c r="A9" s="92"/>
+      <c r="B9" s="125"/>
+      <c r="C9" s="137"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="104"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="103"/>
+      <c r="I9" s="104"/>
+      <c r="J9" s="106"/>
       <c r="K9" s="22" t="s">
         <v>56</v>
       </c>
@@ -9931,34 +9935,34 @@
       <c r="U9" s="52"/>
       <c r="V9" s="52"/>
       <c r="W9" s="52"/>
-      <c r="X9" s="94"/>
-      <c r="Y9" s="96"/>
-      <c r="Z9" s="115"/>
-      <c r="AA9" s="124"/>
+      <c r="X9" s="111"/>
+      <c r="Y9" s="131"/>
+      <c r="Z9" s="116"/>
+      <c r="AA9" s="118"/>
     </row>
     <row r="10" spans="1:27" ht="14.45">
-      <c r="A10" s="109"/>
-      <c r="B10" s="91" t="s">
+      <c r="A10" s="92"/>
+      <c r="B10" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="92" t="s">
+      <c r="C10" s="137" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="90" t="s">
+      <c r="D10" s="105" t="s">
         <v>61</v>
       </c>
-      <c r="E10" s="108">
+      <c r="E10" s="104">
         <v>1</v>
       </c>
-      <c r="F10" s="108"/>
-      <c r="G10" s="108"/>
-      <c r="H10" s="111" t="s">
+      <c r="F10" s="104"/>
+      <c r="G10" s="104"/>
+      <c r="H10" s="103" t="s">
         <v>52</v>
       </c>
-      <c r="I10" s="108" t="s">
+      <c r="I10" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="107" t="s">
+      <c r="J10" s="106" t="s">
         <v>53</v>
       </c>
       <c r="K10" s="22" t="s">
@@ -9994,24 +9998,24 @@
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
       <c r="W10" s="33"/>
-      <c r="X10" s="94"/>
-      <c r="Y10" s="164"/>
-      <c r="Z10" s="117"/>
-      <c r="AA10" s="123" t="s">
+      <c r="X10" s="111"/>
+      <c r="Y10" s="119"/>
+      <c r="Z10" s="165"/>
+      <c r="AA10" s="117" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="15" thickBot="1">
-      <c r="A11" s="109"/>
-      <c r="B11" s="91"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="90"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="111"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="107"/>
+      <c r="A11" s="92"/>
+      <c r="B11" s="125"/>
+      <c r="C11" s="137"/>
+      <c r="D11" s="105"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="104"/>
+      <c r="H11" s="103"/>
+      <c r="I11" s="104"/>
+      <c r="J11" s="106"/>
       <c r="K11" s="22" t="s">
         <v>56</v>
       </c>
@@ -10045,36 +10049,36 @@
       <c r="U11" s="31"/>
       <c r="V11" s="31"/>
       <c r="W11" s="32"/>
-      <c r="X11" s="94"/>
-      <c r="Y11" s="165"/>
-      <c r="Z11" s="118"/>
-      <c r="AA11" s="124"/>
+      <c r="X11" s="111"/>
+      <c r="Y11" s="120"/>
+      <c r="Z11" s="166"/>
+      <c r="AA11" s="118"/>
     </row>
     <row r="12" spans="1:27" ht="14.45">
-      <c r="A12" s="109" t="s">
+      <c r="A12" s="92" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="93" t="s">
+      <c r="B12" s="123" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="93" t="s">
+      <c r="C12" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="90" t="s">
+      <c r="D12" s="105" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="108">
+      <c r="E12" s="104">
         <v>84</v>
       </c>
-      <c r="F12" s="108"/>
-      <c r="G12" s="108"/>
-      <c r="H12" s="111" t="s">
+      <c r="F12" s="104"/>
+      <c r="G12" s="104"/>
+      <c r="H12" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="108" t="s">
+      <c r="I12" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="107" t="s">
+      <c r="J12" s="106" t="s">
         <v>53</v>
       </c>
       <c r="K12" s="22" t="s">
@@ -10116,24 +10120,24 @@
       <c r="W12" s="25">
         <v>0.79</v>
       </c>
-      <c r="X12" s="94"/>
-      <c r="Y12" s="95"/>
-      <c r="Z12" s="96"/>
-      <c r="AA12" s="123" t="s">
+      <c r="X12" s="111"/>
+      <c r="Y12" s="130"/>
+      <c r="Z12" s="131"/>
+      <c r="AA12" s="117" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="14.45">
-      <c r="A13" s="109"/>
-      <c r="B13" s="93"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="90"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="108"/>
-      <c r="G13" s="108"/>
-      <c r="H13" s="111"/>
-      <c r="I13" s="108"/>
-      <c r="J13" s="107"/>
+      <c r="A13" s="92"/>
+      <c r="B13" s="123"/>
+      <c r="C13" s="123"/>
+      <c r="D13" s="105"/>
+      <c r="E13" s="104"/>
+      <c r="F13" s="104"/>
+      <c r="G13" s="104"/>
+      <c r="H13" s="103"/>
+      <c r="I13" s="104"/>
+      <c r="J13" s="106"/>
       <c r="K13" s="22" t="s">
         <v>56</v>
       </c>
@@ -10167,34 +10171,34 @@
       <c r="U13" s="19"/>
       <c r="V13" s="19"/>
       <c r="W13" s="28"/>
-      <c r="X13" s="94"/>
-      <c r="Y13" s="96"/>
-      <c r="Z13" s="96"/>
-      <c r="AA13" s="124"/>
+      <c r="X13" s="111"/>
+      <c r="Y13" s="131"/>
+      <c r="Z13" s="131"/>
+      <c r="AA13" s="118"/>
     </row>
     <row r="14" spans="1:27" ht="14.45">
-      <c r="A14" s="109"/>
-      <c r="B14" s="93" t="s">
+      <c r="A14" s="92"/>
+      <c r="B14" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="122" t="s">
+      <c r="C14" s="124" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="90" t="s">
+      <c r="D14" s="105" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="108">
+      <c r="E14" s="104">
         <v>54.6</v>
       </c>
-      <c r="F14" s="108"/>
-      <c r="G14" s="108"/>
-      <c r="H14" s="111" t="s">
+      <c r="F14" s="104"/>
+      <c r="G14" s="104"/>
+      <c r="H14" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="108" t="s">
+      <c r="I14" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J14" s="107" t="s">
+      <c r="J14" s="106" t="s">
         <v>53</v>
       </c>
       <c r="K14" s="22" t="s">
@@ -10230,26 +10234,26 @@
       <c r="U14" s="37"/>
       <c r="V14" s="37"/>
       <c r="W14" s="37"/>
-      <c r="X14" s="152" t="s">
+      <c r="X14" s="129" t="s">
         <v>71</v>
       </c>
-      <c r="Y14" s="97" t="s">
+      <c r="Y14" s="96" t="s">
         <v>72</v>
       </c>
-      <c r="Z14" s="154"/>
-      <c r="AA14" s="151"/>
+      <c r="Z14" s="100"/>
+      <c r="AA14" s="127"/>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1">
-      <c r="A15" s="109"/>
-      <c r="B15" s="93"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="90"/>
-      <c r="E15" s="108"/>
-      <c r="F15" s="108"/>
-      <c r="G15" s="108"/>
-      <c r="H15" s="111"/>
-      <c r="I15" s="108"/>
-      <c r="J15" s="107"/>
+      <c r="A15" s="92"/>
+      <c r="B15" s="123"/>
+      <c r="C15" s="124"/>
+      <c r="D15" s="105"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="104"/>
+      <c r="G15" s="104"/>
+      <c r="H15" s="103"/>
+      <c r="I15" s="104"/>
+      <c r="J15" s="106"/>
       <c r="K15" s="22" t="s">
         <v>56</v>
       </c>
@@ -10283,36 +10287,36 @@
       <c r="U15" s="31"/>
       <c r="V15" s="31"/>
       <c r="W15" s="32"/>
-      <c r="X15" s="94"/>
-      <c r="Y15" s="113"/>
-      <c r="Z15" s="113"/>
-      <c r="AA15" s="131"/>
+      <c r="X15" s="111"/>
+      <c r="Y15" s="101"/>
+      <c r="Z15" s="101"/>
+      <c r="AA15" s="128"/>
     </row>
     <row r="16" spans="1:27" ht="14.45">
-      <c r="A16" s="109" t="s">
+      <c r="A16" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="93" t="s">
+      <c r="B16" s="123" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="93" t="s">
+      <c r="C16" s="123" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="90" t="s">
+      <c r="D16" s="105" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="108" t="s">
+      <c r="E16" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="F16" s="108"/>
-      <c r="G16" s="108"/>
-      <c r="H16" s="111" t="s">
+      <c r="F16" s="104"/>
+      <c r="G16" s="104"/>
+      <c r="H16" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I16" s="108" t="s">
+      <c r="I16" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="107" t="s">
+      <c r="J16" s="106" t="s">
         <v>53</v>
       </c>
       <c r="K16" s="22" t="s">
@@ -10348,24 +10352,24 @@
       <c r="U16" s="24"/>
       <c r="V16" s="24"/>
       <c r="W16" s="25"/>
-      <c r="X16" s="94"/>
-      <c r="Y16" s="95"/>
-      <c r="Z16" s="115"/>
-      <c r="AA16" s="123" t="s">
+      <c r="X16" s="111"/>
+      <c r="Y16" s="130"/>
+      <c r="Z16" s="116"/>
+      <c r="AA16" s="117" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="14.45">
-      <c r="A17" s="109"/>
-      <c r="B17" s="93"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="90"/>
-      <c r="E17" s="108"/>
-      <c r="F17" s="108"/>
-      <c r="G17" s="108"/>
-      <c r="H17" s="111"/>
-      <c r="I17" s="108"/>
-      <c r="J17" s="107"/>
+      <c r="A17" s="92"/>
+      <c r="B17" s="123"/>
+      <c r="C17" s="123"/>
+      <c r="D17" s="105"/>
+      <c r="E17" s="104"/>
+      <c r="F17" s="104"/>
+      <c r="G17" s="104"/>
+      <c r="H17" s="103"/>
+      <c r="I17" s="104"/>
+      <c r="J17" s="106"/>
       <c r="K17" s="22" t="s">
         <v>56</v>
       </c>
@@ -10399,34 +10403,34 @@
       <c r="U17" s="19"/>
       <c r="V17" s="19"/>
       <c r="W17" s="28"/>
-      <c r="X17" s="94"/>
-      <c r="Y17" s="96"/>
-      <c r="Z17" s="115"/>
-      <c r="AA17" s="124"/>
+      <c r="X17" s="111"/>
+      <c r="Y17" s="131"/>
+      <c r="Z17" s="116"/>
+      <c r="AA17" s="118"/>
     </row>
     <row r="18" spans="1:27" ht="14.45">
-      <c r="A18" s="109"/>
-      <c r="B18" s="93" t="s">
+      <c r="A18" s="92"/>
+      <c r="B18" s="123" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="93" t="s">
+      <c r="C18" s="123" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="93" t="s">
+      <c r="D18" s="123" t="s">
         <v>79</v>
       </c>
-      <c r="E18" s="108" t="s">
+      <c r="E18" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="F18" s="108"/>
-      <c r="G18" s="108"/>
-      <c r="H18" s="111" t="s">
+      <c r="F18" s="104"/>
+      <c r="G18" s="104"/>
+      <c r="H18" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I18" s="108" t="s">
+      <c r="I18" s="104" t="s">
         <v>80</v>
       </c>
-      <c r="J18" s="107" t="s">
+      <c r="J18" s="106" t="s">
         <v>53</v>
       </c>
       <c r="K18" s="22" t="s">
@@ -10462,26 +10466,26 @@
       <c r="U18" s="47"/>
       <c r="V18" s="47"/>
       <c r="W18" s="47"/>
-      <c r="X18" s="158" t="s">
+      <c r="X18" s="135" t="s">
         <v>81</v>
       </c>
-      <c r="Y18" s="158"/>
-      <c r="Z18" s="155">
+      <c r="Y18" s="135"/>
+      <c r="Z18" s="132">
         <v>46108</v>
       </c>
-      <c r="AA18" s="157"/>
+      <c r="AA18" s="134"/>
     </row>
     <row r="19" spans="1:27" ht="14.45">
-      <c r="A19" s="109"/>
-      <c r="B19" s="93"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="93"/>
-      <c r="E19" s="108"/>
-      <c r="F19" s="108"/>
-      <c r="G19" s="108"/>
-      <c r="H19" s="111"/>
-      <c r="I19" s="108"/>
-      <c r="J19" s="107"/>
+      <c r="A19" s="92"/>
+      <c r="B19" s="123"/>
+      <c r="C19" s="123"/>
+      <c r="D19" s="123"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="104"/>
+      <c r="G19" s="104"/>
+      <c r="H19" s="103"/>
+      <c r="I19" s="104"/>
+      <c r="J19" s="106"/>
       <c r="K19" s="22" t="s">
         <v>56</v>
       </c>
@@ -10515,34 +10519,34 @@
       <c r="U19" s="46"/>
       <c r="V19" s="46"/>
       <c r="W19" s="48"/>
-      <c r="X19" s="158"/>
-      <c r="Y19" s="158"/>
-      <c r="Z19" s="156"/>
-      <c r="AA19" s="157"/>
+      <c r="X19" s="135"/>
+      <c r="Y19" s="135"/>
+      <c r="Z19" s="133"/>
+      <c r="AA19" s="134"/>
     </row>
     <row r="20" spans="1:27" ht="14.45">
-      <c r="A20" s="109"/>
-      <c r="B20" s="93" t="s">
+      <c r="A20" s="92"/>
+      <c r="B20" s="123" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="93" t="s">
+      <c r="C20" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="90" t="s">
+      <c r="D20" s="105" t="s">
         <v>83</v>
       </c>
-      <c r="E20" s="108" t="s">
+      <c r="E20" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="F20" s="108"/>
-      <c r="G20" s="108"/>
-      <c r="H20" s="111" t="s">
+      <c r="F20" s="104"/>
+      <c r="G20" s="104"/>
+      <c r="H20" s="103" t="s">
         <v>52</v>
       </c>
-      <c r="I20" s="108" t="s">
+      <c r="I20" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="107" t="s">
+      <c r="J20" s="106" t="s">
         <v>53</v>
       </c>
       <c r="K20" s="22" t="s">
@@ -10578,28 +10582,28 @@
       <c r="U20" s="18"/>
       <c r="V20" s="18"/>
       <c r="W20" s="27"/>
-      <c r="X20" s="99" t="s">
+      <c r="X20" s="167" t="s">
         <v>84</v>
       </c>
-      <c r="Y20" s="101" t="s">
+      <c r="Y20" s="169" t="s">
         <v>85</v>
       </c>
-      <c r="Z20" s="153"/>
-      <c r="AA20" s="125" t="s">
+      <c r="Z20" s="95"/>
+      <c r="AA20" s="153" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="15" thickBot="1">
-      <c r="A21" s="109"/>
-      <c r="B21" s="93"/>
-      <c r="C21" s="93"/>
-      <c r="D21" s="90"/>
-      <c r="E21" s="108"/>
-      <c r="F21" s="108"/>
-      <c r="G21" s="108"/>
-      <c r="H21" s="111"/>
-      <c r="I21" s="108"/>
-      <c r="J21" s="107"/>
+      <c r="A21" s="92"/>
+      <c r="B21" s="123"/>
+      <c r="C21" s="123"/>
+      <c r="D21" s="105"/>
+      <c r="E21" s="104"/>
+      <c r="F21" s="104"/>
+      <c r="G21" s="104"/>
+      <c r="H21" s="103"/>
+      <c r="I21" s="104"/>
+      <c r="J21" s="106"/>
       <c r="K21" s="22" t="s">
         <v>56</v>
       </c>
@@ -10633,36 +10637,36 @@
       <c r="U21" s="29"/>
       <c r="V21" s="29"/>
       <c r="W21" s="30"/>
-      <c r="X21" s="100"/>
-      <c r="Y21" s="102"/>
-      <c r="Z21" s="119"/>
-      <c r="AA21" s="125"/>
+      <c r="X21" s="168"/>
+      <c r="Y21" s="170"/>
+      <c r="Z21" s="94"/>
+      <c r="AA21" s="153"/>
     </row>
     <row r="22" spans="1:27" ht="14.45">
-      <c r="A22" s="109" t="s">
+      <c r="A22" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="93" t="s">
+      <c r="B22" s="123" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="122" t="s">
+      <c r="C22" s="124" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="93" t="s">
+      <c r="D22" s="123" t="s">
         <v>89</v>
       </c>
-      <c r="E22" s="108">
+      <c r="E22" s="104">
         <v>90</v>
       </c>
-      <c r="F22" s="108"/>
-      <c r="G22" s="108"/>
-      <c r="H22" s="111" t="s">
+      <c r="F22" s="104"/>
+      <c r="G22" s="104"/>
+      <c r="H22" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="108" t="s">
+      <c r="I22" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J22" s="107" t="s">
+      <c r="J22" s="106" t="s">
         <v>53</v>
       </c>
       <c r="K22" s="22" t="s">
@@ -10704,24 +10708,24 @@
       <c r="W22" s="27">
         <v>0.9</v>
       </c>
-      <c r="X22" s="105"/>
-      <c r="Y22" s="95"/>
-      <c r="Z22" s="114">
+      <c r="X22" s="171"/>
+      <c r="Y22" s="130"/>
+      <c r="Z22" s="115">
         <v>46257</v>
       </c>
-      <c r="AA22" s="162"/>
+      <c r="AA22" s="113"/>
     </row>
     <row r="23" spans="1:27" ht="15" thickBot="1">
-      <c r="A23" s="169"/>
-      <c r="B23" s="93"/>
-      <c r="C23" s="122"/>
-      <c r="D23" s="93"/>
-      <c r="E23" s="108"/>
-      <c r="F23" s="108"/>
-      <c r="G23" s="108"/>
-      <c r="H23" s="111"/>
-      <c r="I23" s="108"/>
-      <c r="J23" s="107"/>
+      <c r="A23" s="93"/>
+      <c r="B23" s="123"/>
+      <c r="C23" s="124"/>
+      <c r="D23" s="123"/>
+      <c r="E23" s="104"/>
+      <c r="F23" s="104"/>
+      <c r="G23" s="104"/>
+      <c r="H23" s="103"/>
+      <c r="I23" s="104"/>
+      <c r="J23" s="106"/>
       <c r="K23" s="22" t="s">
         <v>56</v>
       </c>
@@ -10755,40 +10759,40 @@
       <c r="U23" s="29"/>
       <c r="V23" s="29"/>
       <c r="W23" s="30"/>
-      <c r="X23" s="106"/>
-      <c r="Y23" s="96"/>
-      <c r="Z23" s="115"/>
-      <c r="AA23" s="163"/>
+      <c r="X23" s="110"/>
+      <c r="Y23" s="131"/>
+      <c r="Z23" s="116"/>
+      <c r="AA23" s="114"/>
     </row>
     <row r="24" spans="1:27" ht="14.45">
-      <c r="A24" s="143" t="s">
+      <c r="A24" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="93" t="s">
+      <c r="B24" s="123" t="s">
         <v>90</v>
       </c>
-      <c r="C24" s="122" t="s">
+      <c r="C24" s="124" t="s">
         <v>91</v>
       </c>
-      <c r="D24" s="90" t="s">
+      <c r="D24" s="105" t="s">
         <v>92</v>
       </c>
-      <c r="E24" s="108" t="s">
+      <c r="E24" s="104" t="s">
         <v>93</v>
       </c>
-      <c r="F24" s="108" t="s">
+      <c r="F24" s="104" t="s">
         <v>93</v>
       </c>
-      <c r="G24" s="108" t="s">
+      <c r="G24" s="104" t="s">
         <v>93</v>
       </c>
-      <c r="H24" s="111" t="s">
+      <c r="H24" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="108" t="s">
+      <c r="I24" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J24" s="120" t="s">
+      <c r="J24" s="102" t="s">
         <v>34</v>
       </c>
       <c r="K24" s="22" t="s">
@@ -10820,24 +10824,24 @@
       <c r="U24" s="21"/>
       <c r="V24" s="21"/>
       <c r="W24" s="38"/>
-      <c r="X24" s="137"/>
-      <c r="Y24" s="154"/>
-      <c r="Z24" s="119"/>
-      <c r="AA24" s="123" t="s">
+      <c r="X24" s="109"/>
+      <c r="Y24" s="100"/>
+      <c r="Z24" s="94"/>
+      <c r="AA24" s="117" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="15" thickBot="1">
-      <c r="A25" s="168"/>
-      <c r="B25" s="93"/>
-      <c r="C25" s="122"/>
-      <c r="D25" s="90"/>
-      <c r="E25" s="108"/>
-      <c r="F25" s="108"/>
-      <c r="G25" s="108"/>
-      <c r="H25" s="111"/>
-      <c r="I25" s="108"/>
-      <c r="J25" s="120"/>
+      <c r="A25" s="91"/>
+      <c r="B25" s="123"/>
+      <c r="C25" s="124"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="104"/>
+      <c r="F25" s="104"/>
+      <c r="G25" s="104"/>
+      <c r="H25" s="103"/>
+      <c r="I25" s="104"/>
+      <c r="J25" s="102"/>
       <c r="K25" s="22" t="s">
         <v>56</v>
       </c>
@@ -10871,34 +10875,34 @@
       <c r="U25" s="21"/>
       <c r="V25" s="21"/>
       <c r="W25" s="55"/>
-      <c r="X25" s="106"/>
-      <c r="Y25" s="113"/>
-      <c r="Z25" s="153"/>
-      <c r="AA25" s="124"/>
+      <c r="X25" s="110"/>
+      <c r="Y25" s="101"/>
+      <c r="Z25" s="95"/>
+      <c r="AA25" s="118"/>
     </row>
     <row r="26" spans="1:27" ht="14.45">
-      <c r="A26" s="168"/>
-      <c r="B26" s="91" t="s">
+      <c r="A26" s="91"/>
+      <c r="B26" s="125" t="s">
         <v>96</v>
       </c>
-      <c r="C26" s="161" t="s">
+      <c r="C26" s="126" t="s">
         <v>91</v>
       </c>
-      <c r="D26" s="90" t="s">
+      <c r="D26" s="105" t="s">
         <v>97</v>
       </c>
-      <c r="E26" s="108">
+      <c r="E26" s="104">
         <v>34</v>
       </c>
-      <c r="F26" s="159"/>
-      <c r="G26" s="159"/>
-      <c r="H26" s="111" t="s">
+      <c r="F26" s="112"/>
+      <c r="G26" s="112"/>
+      <c r="H26" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I26" s="108" t="s">
+      <c r="I26" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J26" s="107" t="s">
+      <c r="J26" s="106" t="s">
         <v>53</v>
       </c>
       <c r="K26" s="22" t="s">
@@ -10934,24 +10938,24 @@
       <c r="U26" s="24"/>
       <c r="V26" s="24"/>
       <c r="W26" s="25"/>
-      <c r="X26" s="94"/>
-      <c r="Y26" s="96"/>
-      <c r="Z26" s="115"/>
-      <c r="AA26" s="123" t="s">
+      <c r="X26" s="111"/>
+      <c r="Y26" s="131"/>
+      <c r="Z26" s="116"/>
+      <c r="AA26" s="117" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:27" ht="15" thickBot="1">
-      <c r="A27" s="168"/>
-      <c r="B27" s="91"/>
-      <c r="C27" s="161"/>
-      <c r="D27" s="90"/>
-      <c r="E27" s="108"/>
-      <c r="F27" s="159"/>
-      <c r="G27" s="159"/>
-      <c r="H27" s="111"/>
-      <c r="I27" s="108"/>
-      <c r="J27" s="107"/>
+      <c r="A27" s="91"/>
+      <c r="B27" s="125"/>
+      <c r="C27" s="126"/>
+      <c r="D27" s="105"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="112"/>
+      <c r="H27" s="103"/>
+      <c r="I27" s="104"/>
+      <c r="J27" s="106"/>
       <c r="K27" s="22" t="s">
         <v>56</v>
       </c>
@@ -10985,34 +10989,34 @@
       <c r="U27" s="19"/>
       <c r="V27" s="19"/>
       <c r="W27" s="28"/>
-      <c r="X27" s="94"/>
-      <c r="Y27" s="96"/>
-      <c r="Z27" s="115"/>
-      <c r="AA27" s="124"/>
+      <c r="X27" s="111"/>
+      <c r="Y27" s="131"/>
+      <c r="Z27" s="116"/>
+      <c r="AA27" s="118"/>
     </row>
     <row r="28" spans="1:27" ht="14.45">
-      <c r="A28" s="168"/>
-      <c r="B28" s="90" t="s">
+      <c r="A28" s="91"/>
+      <c r="B28" s="105" t="s">
         <v>99</v>
       </c>
-      <c r="C28" s="93" t="s">
+      <c r="C28" s="123" t="s">
         <v>74</v>
       </c>
-      <c r="D28" s="90" t="s">
+      <c r="D28" s="105" t="s">
         <v>100</v>
       </c>
-      <c r="E28" s="108" t="s">
+      <c r="E28" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="108"/>
-      <c r="G28" s="108"/>
-      <c r="H28" s="111" t="s">
+      <c r="F28" s="104"/>
+      <c r="G28" s="104"/>
+      <c r="H28" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I28" s="108" t="s">
+      <c r="I28" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J28" s="107" t="s">
+      <c r="J28" s="106" t="s">
         <v>53</v>
       </c>
       <c r="K28" s="22" t="s">
@@ -11048,26 +11052,26 @@
       <c r="U28" s="24"/>
       <c r="V28" s="24"/>
       <c r="W28" s="25"/>
-      <c r="X28" s="103" t="s">
+      <c r="X28" s="159" t="s">
         <v>101</v>
       </c>
-      <c r="Y28" s="97"/>
-      <c r="Z28" s="119"/>
-      <c r="AA28" s="128" t="s">
+      <c r="Y28" s="96"/>
+      <c r="Z28" s="94"/>
+      <c r="AA28" s="154" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:27" ht="15" thickBot="1">
-      <c r="A29" s="168"/>
-      <c r="B29" s="90"/>
-      <c r="C29" s="93"/>
-      <c r="D29" s="90"/>
-      <c r="E29" s="108"/>
-      <c r="F29" s="108"/>
-      <c r="G29" s="108"/>
-      <c r="H29" s="111"/>
-      <c r="I29" s="108"/>
-      <c r="J29" s="107"/>
+      <c r="A29" s="91"/>
+      <c r="B29" s="105"/>
+      <c r="C29" s="123"/>
+      <c r="D29" s="105"/>
+      <c r="E29" s="104"/>
+      <c r="F29" s="104"/>
+      <c r="G29" s="104"/>
+      <c r="H29" s="103"/>
+      <c r="I29" s="104"/>
+      <c r="J29" s="106"/>
       <c r="K29" s="22" t="s">
         <v>56</v>
       </c>
@@ -11101,32 +11105,32 @@
       <c r="U29" s="19"/>
       <c r="V29" s="19"/>
       <c r="W29" s="28"/>
-      <c r="X29" s="104"/>
-      <c r="Y29" s="98"/>
-      <c r="Z29" s="153"/>
-      <c r="AA29" s="129"/>
+      <c r="X29" s="160"/>
+      <c r="Y29" s="97"/>
+      <c r="Z29" s="95"/>
+      <c r="AA29" s="155"/>
     </row>
     <row r="30" spans="1:27" ht="14.45">
-      <c r="A30" s="168"/>
-      <c r="B30" s="90"/>
-      <c r="C30" s="93" t="s">
+      <c r="A30" s="91"/>
+      <c r="B30" s="105"/>
+      <c r="C30" s="123" t="s">
         <v>74</v>
       </c>
-      <c r="D30" s="90" t="s">
+      <c r="D30" s="105" t="s">
         <v>103</v>
       </c>
-      <c r="E30" s="108" t="s">
+      <c r="E30" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="F30" s="108"/>
-      <c r="G30" s="108"/>
-      <c r="H30" s="111" t="s">
+      <c r="F30" s="104"/>
+      <c r="G30" s="104"/>
+      <c r="H30" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I30" s="108" t="s">
+      <c r="I30" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J30" s="107" t="s">
+      <c r="J30" s="106" t="s">
         <v>53</v>
       </c>
       <c r="K30" s="22" t="s">
@@ -11162,22 +11166,22 @@
       <c r="U30" s="24"/>
       <c r="V30" s="24"/>
       <c r="W30" s="25"/>
-      <c r="X30" s="103"/>
-      <c r="Y30" s="154"/>
-      <c r="Z30" s="119"/>
-      <c r="AA30" s="166"/>
+      <c r="X30" s="159"/>
+      <c r="Y30" s="100"/>
+      <c r="Z30" s="94"/>
+      <c r="AA30" s="107"/>
     </row>
     <row r="31" spans="1:27" ht="14.45">
-      <c r="A31" s="168"/>
-      <c r="B31" s="90"/>
-      <c r="C31" s="93"/>
-      <c r="D31" s="90"/>
-      <c r="E31" s="108"/>
-      <c r="F31" s="108"/>
-      <c r="G31" s="108"/>
-      <c r="H31" s="111"/>
-      <c r="I31" s="108"/>
-      <c r="J31" s="107"/>
+      <c r="A31" s="91"/>
+      <c r="B31" s="105"/>
+      <c r="C31" s="123"/>
+      <c r="D31" s="105"/>
+      <c r="E31" s="104"/>
+      <c r="F31" s="104"/>
+      <c r="G31" s="104"/>
+      <c r="H31" s="103"/>
+      <c r="I31" s="104"/>
+      <c r="J31" s="106"/>
       <c r="K31" s="22" t="s">
         <v>56</v>
       </c>
@@ -11211,34 +11215,34 @@
       <c r="U31" s="44"/>
       <c r="V31" s="44"/>
       <c r="W31" s="45"/>
-      <c r="X31" s="104"/>
-      <c r="Y31" s="113"/>
-      <c r="Z31" s="153"/>
-      <c r="AA31" s="167"/>
+      <c r="X31" s="160"/>
+      <c r="Y31" s="101"/>
+      <c r="Z31" s="95"/>
+      <c r="AA31" s="108"/>
     </row>
     <row r="32" spans="1:27" ht="14.45">
-      <c r="A32" s="168"/>
-      <c r="B32" s="93" t="s">
+      <c r="A32" s="91"/>
+      <c r="B32" s="123" t="s">
         <v>104</v>
       </c>
-      <c r="C32" s="122" t="s">
+      <c r="C32" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="90" t="s">
+      <c r="D32" s="105" t="s">
         <v>105</v>
       </c>
-      <c r="E32" s="108" t="s">
+      <c r="E32" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="F32" s="108"/>
-      <c r="G32" s="108"/>
-      <c r="H32" s="111" t="s">
+      <c r="F32" s="104"/>
+      <c r="G32" s="104"/>
+      <c r="H32" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I32" s="108" t="s">
+      <c r="I32" s="104" t="s">
         <v>80</v>
       </c>
-      <c r="J32" s="107" t="s">
+      <c r="J32" s="106" t="s">
         <v>53</v>
       </c>
       <c r="K32" s="22" t="s">
@@ -11274,28 +11278,28 @@
       <c r="U32" s="8"/>
       <c r="V32" s="8"/>
       <c r="W32" s="33"/>
-      <c r="X32" s="170" t="s">
+      <c r="X32" s="98" t="s">
         <v>106</v>
       </c>
-      <c r="Y32" s="97" t="s">
+      <c r="Y32" s="96" t="s">
         <v>107</v>
       </c>
-      <c r="Z32" s="119"/>
-      <c r="AA32" s="123" t="s">
+      <c r="Z32" s="94"/>
+      <c r="AA32" s="117" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:29" ht="15" thickBot="1">
-      <c r="A33" s="168"/>
-      <c r="B33" s="93"/>
-      <c r="C33" s="122"/>
-      <c r="D33" s="90"/>
-      <c r="E33" s="108"/>
-      <c r="F33" s="108"/>
-      <c r="G33" s="108"/>
-      <c r="H33" s="111"/>
-      <c r="I33" s="108"/>
-      <c r="J33" s="107"/>
+      <c r="A33" s="91"/>
+      <c r="B33" s="123"/>
+      <c r="C33" s="124"/>
+      <c r="D33" s="105"/>
+      <c r="E33" s="104"/>
+      <c r="F33" s="104"/>
+      <c r="G33" s="104"/>
+      <c r="H33" s="103"/>
+      <c r="I33" s="104"/>
+      <c r="J33" s="106"/>
       <c r="K33" s="22" t="s">
         <v>56</v>
       </c>
@@ -11329,36 +11333,36 @@
       <c r="U33" s="31"/>
       <c r="V33" s="31"/>
       <c r="W33" s="32"/>
-      <c r="X33" s="171"/>
-      <c r="Y33" s="98"/>
-      <c r="Z33" s="153"/>
-      <c r="AA33" s="124"/>
+      <c r="X33" s="99"/>
+      <c r="Y33" s="97"/>
+      <c r="Z33" s="95"/>
+      <c r="AA33" s="118"/>
     </row>
     <row r="34" spans="1:29" ht="14.45">
-      <c r="A34" s="109" t="s">
+      <c r="A34" s="92" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="148" t="s">
+      <c r="B34" s="144" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="93" t="s">
+      <c r="C34" s="123" t="s">
         <v>88</v>
       </c>
-      <c r="D34" s="90" t="s">
+      <c r="D34" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="E34" s="108">
+      <c r="E34" s="104">
         <v>90</v>
       </c>
-      <c r="F34" s="108"/>
-      <c r="G34" s="108"/>
-      <c r="H34" s="111" t="s">
+      <c r="F34" s="104"/>
+      <c r="G34" s="104"/>
+      <c r="H34" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I34" s="108" t="s">
+      <c r="I34" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J34" s="120" t="s">
+      <c r="J34" s="102" t="s">
         <v>34</v>
       </c>
       <c r="K34" s="22" t="s">
@@ -11384,26 +11388,26 @@
       <c r="W34" s="25">
         <v>0.9</v>
       </c>
-      <c r="X34" s="94"/>
-      <c r="Y34" s="96" t="s">
+      <c r="X34" s="111"/>
+      <c r="Y34" s="131" t="s">
         <v>109</v>
       </c>
-      <c r="Z34" s="115"/>
-      <c r="AA34" s="123" t="s">
+      <c r="Z34" s="116"/>
+      <c r="AA34" s="117" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:29" ht="14.45">
-      <c r="A35" s="109"/>
-      <c r="B35" s="148"/>
-      <c r="C35" s="93"/>
-      <c r="D35" s="90"/>
-      <c r="E35" s="108"/>
-      <c r="F35" s="108"/>
-      <c r="G35" s="108"/>
-      <c r="H35" s="111"/>
-      <c r="I35" s="108"/>
-      <c r="J35" s="120"/>
+      <c r="A35" s="92"/>
+      <c r="B35" s="144"/>
+      <c r="C35" s="123"/>
+      <c r="D35" s="105"/>
+      <c r="E35" s="104"/>
+      <c r="F35" s="104"/>
+      <c r="G35" s="104"/>
+      <c r="H35" s="103"/>
+      <c r="I35" s="104"/>
+      <c r="J35" s="102"/>
       <c r="K35" s="22" t="s">
         <v>56</v>
       </c>
@@ -11437,34 +11441,34 @@
       <c r="U35" s="19"/>
       <c r="V35" s="19"/>
       <c r="W35" s="28"/>
-      <c r="X35" s="94"/>
-      <c r="Y35" s="96"/>
-      <c r="Z35" s="115"/>
-      <c r="AA35" s="124"/>
+      <c r="X35" s="111"/>
+      <c r="Y35" s="131"/>
+      <c r="Z35" s="116"/>
+      <c r="AA35" s="118"/>
     </row>
     <row r="36" spans="1:29" ht="14.45">
-      <c r="A36" s="109"/>
-      <c r="B36" s="148" t="s">
+      <c r="A36" s="92"/>
+      <c r="B36" s="144" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="93" t="s">
+      <c r="C36" s="123" t="s">
         <v>111</v>
       </c>
-      <c r="D36" s="90" t="s">
+      <c r="D36" s="105" t="s">
         <v>37</v>
       </c>
-      <c r="E36" s="108">
+      <c r="E36" s="104">
         <v>83</v>
       </c>
-      <c r="F36" s="108"/>
-      <c r="G36" s="108"/>
-      <c r="H36" s="111" t="s">
+      <c r="F36" s="104"/>
+      <c r="G36" s="104"/>
+      <c r="H36" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I36" s="108" t="s">
+      <c r="I36" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J36" s="121" t="s">
+      <c r="J36" s="161" t="s">
         <v>38</v>
       </c>
       <c r="K36" s="22" t="s">
@@ -11486,28 +11490,28 @@
       <c r="U36" s="18"/>
       <c r="V36" s="18"/>
       <c r="W36" s="27"/>
-      <c r="X36" s="94" t="s">
+      <c r="X36" s="111" t="s">
         <v>112</v>
       </c>
-      <c r="Y36" s="95" t="s">
+      <c r="Y36" s="130" t="s">
         <v>113</v>
       </c>
-      <c r="Z36" s="115"/>
-      <c r="AA36" s="123" t="s">
+      <c r="Z36" s="116"/>
+      <c r="AA36" s="117" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:29" ht="14.45">
-      <c r="A37" s="109"/>
-      <c r="B37" s="148"/>
-      <c r="C37" s="93"/>
-      <c r="D37" s="90"/>
-      <c r="E37" s="108"/>
-      <c r="F37" s="108"/>
-      <c r="G37" s="108"/>
-      <c r="H37" s="111"/>
-      <c r="I37" s="108"/>
-      <c r="J37" s="121"/>
+      <c r="A37" s="92"/>
+      <c r="B37" s="144"/>
+      <c r="C37" s="123"/>
+      <c r="D37" s="105"/>
+      <c r="E37" s="104"/>
+      <c r="F37" s="104"/>
+      <c r="G37" s="104"/>
+      <c r="H37" s="103"/>
+      <c r="I37" s="104"/>
+      <c r="J37" s="161"/>
       <c r="K37" s="22" t="s">
         <v>56</v>
       </c>
@@ -11539,45 +11543,45 @@
       <c r="U37" s="56"/>
       <c r="V37" s="56"/>
       <c r="W37" s="57"/>
-      <c r="X37" s="137"/>
-      <c r="Y37" s="97"/>
-      <c r="Z37" s="119"/>
-      <c r="AA37" s="125"/>
+      <c r="X37" s="109"/>
+      <c r="Y37" s="96"/>
+      <c r="Z37" s="94"/>
+      <c r="AA37" s="153"/>
     </row>
     <row r="38" spans="1:29" s="5" customFormat="1" ht="20.45" customHeight="1">
-      <c r="A38" s="138"/>
-      <c r="B38" s="138"/>
-      <c r="C38" s="138"/>
-      <c r="D38" s="138"/>
-      <c r="E38" s="138"/>
-      <c r="F38" s="138"/>
-      <c r="G38" s="138"/>
-      <c r="H38" s="138"/>
-      <c r="I38" s="138"/>
-      <c r="J38" s="138"/>
-      <c r="K38" s="138"/>
-      <c r="L38" s="138"/>
-      <c r="M38" s="138"/>
-      <c r="N38" s="138"/>
-      <c r="O38" s="138"/>
-      <c r="P38" s="139"/>
-      <c r="Q38" s="139"/>
-      <c r="R38" s="139"/>
-      <c r="S38" s="139"/>
-      <c r="T38" s="139"/>
-      <c r="U38" s="139"/>
-      <c r="V38" s="139"/>
-      <c r="W38" s="139"/>
-      <c r="X38" s="139"/>
-      <c r="Y38" s="139"/>
-      <c r="Z38" s="139"/>
-      <c r="AA38" s="139"/>
+      <c r="A38" s="147"/>
+      <c r="B38" s="147"/>
+      <c r="C38" s="147"/>
+      <c r="D38" s="147"/>
+      <c r="E38" s="147"/>
+      <c r="F38" s="147"/>
+      <c r="G38" s="147"/>
+      <c r="H38" s="147"/>
+      <c r="I38" s="147"/>
+      <c r="J38" s="147"/>
+      <c r="K38" s="147"/>
+      <c r="L38" s="147"/>
+      <c r="M38" s="147"/>
+      <c r="N38" s="147"/>
+      <c r="O38" s="147"/>
+      <c r="P38" s="148"/>
+      <c r="Q38" s="148"/>
+      <c r="R38" s="148"/>
+      <c r="S38" s="148"/>
+      <c r="T38" s="148"/>
+      <c r="U38" s="148"/>
+      <c r="V38" s="148"/>
+      <c r="W38" s="148"/>
+      <c r="X38" s="148"/>
+      <c r="Y38" s="148"/>
+      <c r="Z38" s="148"/>
+      <c r="AA38" s="148"/>
     </row>
     <row r="39" spans="1:29" s="5" customFormat="1" ht="20.45" customHeight="1">
-      <c r="A39" s="141" t="s">
+      <c r="A39" s="149" t="s">
         <v>116</v>
       </c>
-      <c r="B39" s="141"/>
+      <c r="B39" s="149"/>
       <c r="C39" s="58"/>
       <c r="D39"/>
       <c r="E39"/>
@@ -11688,34 +11692,34 @@
       </c>
     </row>
     <row r="41" spans="1:29" ht="20.45" customHeight="1">
-      <c r="A41" s="142" t="s">
+      <c r="A41" s="150" t="s">
         <v>48</v>
       </c>
-      <c r="B41" s="145" t="s">
+      <c r="B41" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="C41" s="146" t="s">
+      <c r="C41" s="152" t="s">
         <v>50</v>
       </c>
-      <c r="D41" s="147" t="s">
+      <c r="D41" s="143" t="s">
         <v>124</v>
       </c>
-      <c r="E41" s="140" t="s">
+      <c r="E41" s="121" t="s">
         <v>93</v>
       </c>
-      <c r="F41" s="140" t="s">
+      <c r="F41" s="121" t="s">
         <v>93</v>
       </c>
-      <c r="G41" s="140" t="s">
+      <c r="G41" s="121" t="s">
         <v>93</v>
       </c>
-      <c r="H41" s="160" t="s">
+      <c r="H41" s="122" t="s">
         <v>52</v>
       </c>
-      <c r="I41" s="140" t="s">
+      <c r="I41" s="121" t="s">
         <v>33</v>
       </c>
-      <c r="J41" s="149" t="s">
+      <c r="J41" s="138" t="s">
         <v>53</v>
       </c>
       <c r="K41" s="61" t="s">
@@ -11757,25 +11761,25 @@
       <c r="W41" s="63">
         <v>3.32E-2</v>
       </c>
-      <c r="X41" s="136"/>
-      <c r="Y41" s="131"/>
-      <c r="Z41" s="131"/>
-      <c r="AA41" s="124" t="s">
+      <c r="X41" s="158"/>
+      <c r="Y41" s="128"/>
+      <c r="Z41" s="128"/>
+      <c r="AA41" s="118" t="s">
         <v>123</v>
       </c>
       <c r="AC41" s="12"/>
     </row>
     <row r="42" spans="1:29" ht="20.45" customHeight="1">
-      <c r="A42" s="143"/>
-      <c r="B42" s="91"/>
-      <c r="C42" s="92"/>
-      <c r="D42" s="90"/>
-      <c r="E42" s="108"/>
-      <c r="F42" s="108"/>
-      <c r="G42" s="108"/>
-      <c r="H42" s="111"/>
-      <c r="I42" s="108"/>
-      <c r="J42" s="127"/>
+      <c r="A42" s="90"/>
+      <c r="B42" s="125"/>
+      <c r="C42" s="137"/>
+      <c r="D42" s="105"/>
+      <c r="E42" s="104"/>
+      <c r="F42" s="104"/>
+      <c r="G42" s="104"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="104"/>
+      <c r="J42" s="139"/>
       <c r="K42" s="22" t="s">
         <v>56</v>
       </c>
@@ -11809,40 +11813,40 @@
       <c r="U42" s="55"/>
       <c r="V42" s="55"/>
       <c r="W42" s="59"/>
-      <c r="X42" s="136"/>
-      <c r="Y42" s="131"/>
-      <c r="Z42" s="131"/>
-      <c r="AA42" s="126"/>
+      <c r="X42" s="158"/>
+      <c r="Y42" s="128"/>
+      <c r="Z42" s="128"/>
+      <c r="AA42" s="145"/>
     </row>
     <row r="43" spans="1:29" ht="20.45" customHeight="1">
-      <c r="A43" s="144" t="s">
+      <c r="A43" s="136" t="s">
         <v>26</v>
       </c>
-      <c r="B43" s="91" t="s">
+      <c r="B43" s="125" t="s">
         <v>125</v>
       </c>
-      <c r="C43" s="92" t="s">
+      <c r="C43" s="137" t="s">
         <v>91</v>
       </c>
-      <c r="D43" s="90" t="s">
+      <c r="D43" s="105" t="s">
         <v>126</v>
       </c>
-      <c r="E43" s="108" t="s">
+      <c r="E43" s="104" t="s">
         <v>93</v>
       </c>
-      <c r="F43" s="108" t="s">
+      <c r="F43" s="104" t="s">
         <v>93</v>
       </c>
-      <c r="G43" s="108" t="s">
+      <c r="G43" s="104" t="s">
         <v>93</v>
       </c>
-      <c r="H43" s="111" t="s">
+      <c r="H43" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I43" s="108" t="s">
+      <c r="I43" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J43" s="120" t="s">
+      <c r="J43" s="102" t="s">
         <v>34</v>
       </c>
       <c r="K43" s="22" t="s">
@@ -11864,28 +11868,28 @@
       <c r="U43" s="35"/>
       <c r="V43" s="35"/>
       <c r="W43" s="38"/>
-      <c r="X43" s="130" t="s">
+      <c r="X43" s="146" t="s">
         <v>127</v>
       </c>
-      <c r="Y43" s="132" t="s">
+      <c r="Y43" s="141" t="s">
         <v>128</v>
       </c>
-      <c r="Z43" s="133"/>
-      <c r="AA43" s="134" t="s">
+      <c r="Z43" s="140"/>
+      <c r="AA43" s="156" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="44" spans="1:29" ht="20.45" customHeight="1">
-      <c r="A44" s="144"/>
-      <c r="B44" s="91"/>
-      <c r="C44" s="92"/>
-      <c r="D44" s="90"/>
-      <c r="E44" s="108"/>
-      <c r="F44" s="108"/>
-      <c r="G44" s="108"/>
-      <c r="H44" s="111"/>
-      <c r="I44" s="159"/>
-      <c r="J44" s="120"/>
+      <c r="A44" s="136"/>
+      <c r="B44" s="125"/>
+      <c r="C44" s="137"/>
+      <c r="D44" s="105"/>
+      <c r="E44" s="104"/>
+      <c r="F44" s="104"/>
+      <c r="G44" s="104"/>
+      <c r="H44" s="103"/>
+      <c r="I44" s="112"/>
+      <c r="J44" s="102"/>
       <c r="K44" s="22" t="s">
         <v>56</v>
       </c>
@@ -11921,38 +11925,38 @@
         <v>94</v>
       </c>
       <c r="W44" s="55"/>
-      <c r="X44" s="130"/>
-      <c r="Y44" s="132"/>
-      <c r="Z44" s="133"/>
-      <c r="AA44" s="134"/>
+      <c r="X44" s="146"/>
+      <c r="Y44" s="141"/>
+      <c r="Z44" s="140"/>
+      <c r="AA44" s="156"/>
     </row>
     <row r="45" spans="1:29" ht="20.45" customHeight="1">
-      <c r="A45" s="144"/>
-      <c r="B45" s="91" t="s">
+      <c r="A45" s="136"/>
+      <c r="B45" s="125" t="s">
         <v>130</v>
       </c>
-      <c r="C45" s="92" t="s">
+      <c r="C45" s="137" t="s">
         <v>91</v>
       </c>
-      <c r="D45" s="90" t="s">
+      <c r="D45" s="105" t="s">
         <v>131</v>
       </c>
-      <c r="E45" s="108" t="s">
+      <c r="E45" s="104" t="s">
         <v>93</v>
       </c>
-      <c r="F45" s="108" t="s">
+      <c r="F45" s="104" t="s">
         <v>93</v>
       </c>
-      <c r="G45" s="108" t="s">
+      <c r="G45" s="104" t="s">
         <v>93</v>
       </c>
-      <c r="H45" s="111" t="s">
+      <c r="H45" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I45" s="108" t="s">
+      <c r="I45" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J45" s="127" t="s">
+      <c r="J45" s="139" t="s">
         <v>53</v>
       </c>
       <c r="K45" s="22" t="s">
@@ -11988,28 +11992,28 @@
       <c r="U45" s="35"/>
       <c r="V45" s="35"/>
       <c r="W45" s="38"/>
-      <c r="X45" s="130"/>
-      <c r="Y45" s="132" t="s">
+      <c r="X45" s="146"/>
+      <c r="Y45" s="141" t="s">
         <v>132</v>
       </c>
-      <c r="Z45" s="135">
+      <c r="Z45" s="157">
         <v>46188</v>
       </c>
-      <c r="AA45" s="126" t="s">
+      <c r="AA45" s="145" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="46" spans="1:29" ht="20.45" customHeight="1">
-      <c r="A46" s="144"/>
-      <c r="B46" s="91"/>
-      <c r="C46" s="92"/>
-      <c r="D46" s="90"/>
-      <c r="E46" s="108"/>
-      <c r="F46" s="108"/>
-      <c r="G46" s="108"/>
-      <c r="H46" s="111"/>
-      <c r="I46" s="108"/>
-      <c r="J46" s="127"/>
+      <c r="A46" s="136"/>
+      <c r="B46" s="125"/>
+      <c r="C46" s="137"/>
+      <c r="D46" s="105"/>
+      <c r="E46" s="104"/>
+      <c r="F46" s="104"/>
+      <c r="G46" s="104"/>
+      <c r="H46" s="103"/>
+      <c r="I46" s="104"/>
+      <c r="J46" s="139"/>
       <c r="K46" s="22" t="s">
         <v>56</v>
       </c>
@@ -12043,38 +12047,38 @@
       <c r="U46" s="19"/>
       <c r="V46" s="19"/>
       <c r="W46" s="28"/>
-      <c r="X46" s="130"/>
-      <c r="Y46" s="133"/>
-      <c r="Z46" s="133"/>
-      <c r="AA46" s="126"/>
+      <c r="X46" s="146"/>
+      <c r="Y46" s="140"/>
+      <c r="Z46" s="140"/>
+      <c r="AA46" s="145"/>
     </row>
     <row r="47" spans="1:29" ht="20.45" customHeight="1">
-      <c r="A47" s="144"/>
-      <c r="B47" s="91" t="s">
+      <c r="A47" s="136"/>
+      <c r="B47" s="125" t="s">
         <v>133</v>
       </c>
-      <c r="C47" s="92" t="s">
+      <c r="C47" s="137" t="s">
         <v>88</v>
       </c>
-      <c r="D47" s="90" t="s">
+      <c r="D47" s="105" t="s">
         <v>134</v>
       </c>
-      <c r="E47" s="108" t="s">
+      <c r="E47" s="104" t="s">
         <v>93</v>
       </c>
-      <c r="F47" s="108" t="s">
+      <c r="F47" s="104" t="s">
         <v>93</v>
       </c>
-      <c r="G47" s="108" t="s">
+      <c r="G47" s="104" t="s">
         <v>93</v>
       </c>
-      <c r="H47" s="111" t="s">
+      <c r="H47" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I47" s="108" t="s">
+      <c r="I47" s="104" t="s">
         <v>80</v>
       </c>
-      <c r="J47" s="127" t="s">
+      <c r="J47" s="139" t="s">
         <v>53</v>
       </c>
       <c r="K47" s="22" t="s">
@@ -12116,24 +12120,24 @@
       <c r="W47" s="39">
         <v>67</v>
       </c>
-      <c r="X47" s="130"/>
-      <c r="Y47" s="133"/>
-      <c r="Z47" s="133"/>
-      <c r="AA47" s="90" t="s">
+      <c r="X47" s="146"/>
+      <c r="Y47" s="140"/>
+      <c r="Z47" s="140"/>
+      <c r="AA47" s="105" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="48" spans="1:29" ht="20.45" customHeight="1">
-      <c r="A48" s="144"/>
-      <c r="B48" s="91"/>
-      <c r="C48" s="92"/>
-      <c r="D48" s="90"/>
-      <c r="E48" s="108"/>
-      <c r="F48" s="108"/>
-      <c r="G48" s="108"/>
-      <c r="H48" s="111"/>
-      <c r="I48" s="108"/>
-      <c r="J48" s="127"/>
+      <c r="A48" s="136"/>
+      <c r="B48" s="125"/>
+      <c r="C48" s="137"/>
+      <c r="D48" s="105"/>
+      <c r="E48" s="104"/>
+      <c r="F48" s="104"/>
+      <c r="G48" s="104"/>
+      <c r="H48" s="103"/>
+      <c r="I48" s="104"/>
+      <c r="J48" s="139"/>
       <c r="K48" s="22" t="s">
         <v>56</v>
       </c>
@@ -12168,40 +12172,40 @@
       <c r="U48" s="9"/>
       <c r="V48" s="9"/>
       <c r="W48" s="26"/>
-      <c r="X48" s="130"/>
-      <c r="Y48" s="133"/>
-      <c r="Z48" s="133"/>
-      <c r="AA48" s="90"/>
+      <c r="X48" s="146"/>
+      <c r="Y48" s="140"/>
+      <c r="Z48" s="140"/>
+      <c r="AA48" s="105"/>
     </row>
     <row r="49" spans="1:27" ht="20.45" customHeight="1">
-      <c r="A49" s="143" t="s">
+      <c r="A49" s="90" t="s">
         <v>136</v>
       </c>
-      <c r="B49" s="150" t="s">
+      <c r="B49" s="142" t="s">
         <v>137</v>
       </c>
-      <c r="C49" s="92" t="s">
+      <c r="C49" s="137" t="s">
         <v>69</v>
       </c>
-      <c r="D49" s="90" t="s">
+      <c r="D49" s="105" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="108">
+      <c r="E49" s="104">
         <v>74</v>
       </c>
-      <c r="F49" s="108" t="s">
+      <c r="F49" s="104" t="s">
         <v>93</v>
       </c>
-      <c r="G49" s="108" t="s">
+      <c r="G49" s="104" t="s">
         <v>93</v>
       </c>
-      <c r="H49" s="111" t="s">
+      <c r="H49" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I49" s="108" t="s">
+      <c r="I49" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J49" s="107" t="s">
+      <c r="J49" s="106" t="s">
         <v>53</v>
       </c>
       <c r="K49" s="22" t="s">
@@ -12243,24 +12247,24 @@
       <c r="W49" s="40">
         <v>0.73999999999999966</v>
       </c>
-      <c r="X49" s="130"/>
-      <c r="Y49" s="132"/>
-      <c r="Z49" s="133"/>
-      <c r="AA49" s="126" t="s">
+      <c r="X49" s="146"/>
+      <c r="Y49" s="141"/>
+      <c r="Z49" s="140"/>
+      <c r="AA49" s="145" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="50" spans="1:27" ht="20.45" customHeight="1">
-      <c r="A50" s="143"/>
-      <c r="B50" s="150"/>
-      <c r="C50" s="92"/>
-      <c r="D50" s="90"/>
-      <c r="E50" s="108"/>
-      <c r="F50" s="108"/>
-      <c r="G50" s="108"/>
-      <c r="H50" s="111"/>
-      <c r="I50" s="108"/>
-      <c r="J50" s="107"/>
+      <c r="A50" s="90"/>
+      <c r="B50" s="142"/>
+      <c r="C50" s="137"/>
+      <c r="D50" s="105"/>
+      <c r="E50" s="104"/>
+      <c r="F50" s="104"/>
+      <c r="G50" s="104"/>
+      <c r="H50" s="103"/>
+      <c r="I50" s="104"/>
+      <c r="J50" s="106"/>
       <c r="K50" s="22" t="s">
         <v>56</v>
       </c>
@@ -12294,40 +12298,40 @@
       <c r="U50" s="17"/>
       <c r="V50" s="17"/>
       <c r="W50" s="74"/>
-      <c r="X50" s="130"/>
-      <c r="Y50" s="132"/>
-      <c r="Z50" s="133"/>
-      <c r="AA50" s="126"/>
+      <c r="X50" s="146"/>
+      <c r="Y50" s="141"/>
+      <c r="Z50" s="140"/>
+      <c r="AA50" s="145"/>
     </row>
     <row r="51" spans="1:27" ht="20.45" customHeight="1">
-      <c r="A51" s="144" t="s">
+      <c r="A51" s="136" t="s">
         <v>25</v>
       </c>
-      <c r="B51" s="91" t="s">
+      <c r="B51" s="125" t="s">
         <v>140</v>
       </c>
-      <c r="C51" s="92" t="s">
+      <c r="C51" s="137" t="s">
         <v>74</v>
       </c>
-      <c r="D51" s="90" t="s">
+      <c r="D51" s="105" t="s">
         <v>141</v>
       </c>
-      <c r="E51" s="108">
+      <c r="E51" s="104">
         <v>33.1</v>
       </c>
-      <c r="F51" s="108" t="s">
+      <c r="F51" s="104" t="s">
         <v>93</v>
       </c>
-      <c r="G51" s="108" t="s">
+      <c r="G51" s="104" t="s">
         <v>93</v>
       </c>
-      <c r="H51" s="111" t="s">
+      <c r="H51" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I51" s="108" t="s">
+      <c r="I51" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J51" s="107" t="s">
+      <c r="J51" s="106" t="s">
         <v>53</v>
       </c>
       <c r="K51" s="22" t="s">
@@ -12363,24 +12367,24 @@
       <c r="U51" s="35"/>
       <c r="V51" s="35"/>
       <c r="W51" s="38"/>
-      <c r="X51" s="130"/>
-      <c r="Y51" s="133"/>
-      <c r="Z51" s="133"/>
-      <c r="AA51" s="93" t="s">
+      <c r="X51" s="146"/>
+      <c r="Y51" s="140"/>
+      <c r="Z51" s="140"/>
+      <c r="AA51" s="123" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="52" spans="1:27" ht="20.45" customHeight="1" thickBot="1">
-      <c r="A52" s="144"/>
-      <c r="B52" s="91"/>
-      <c r="C52" s="92"/>
-      <c r="D52" s="90"/>
-      <c r="E52" s="108"/>
-      <c r="F52" s="108"/>
-      <c r="G52" s="108"/>
-      <c r="H52" s="111"/>
-      <c r="I52" s="108"/>
-      <c r="J52" s="107"/>
+      <c r="A52" s="136"/>
+      <c r="B52" s="125"/>
+      <c r="C52" s="137"/>
+      <c r="D52" s="105"/>
+      <c r="E52" s="104"/>
+      <c r="F52" s="104"/>
+      <c r="G52" s="104"/>
+      <c r="H52" s="103"/>
+      <c r="I52" s="104"/>
+      <c r="J52" s="106"/>
       <c r="K52" s="22" t="s">
         <v>56</v>
       </c>
@@ -12414,35 +12418,237 @@
       <c r="U52" s="29"/>
       <c r="V52" s="29"/>
       <c r="W52" s="30"/>
-      <c r="X52" s="130"/>
-      <c r="Y52" s="133"/>
-      <c r="Z52" s="133"/>
-      <c r="AA52" s="93"/>
+      <c r="X52" s="146"/>
+      <c r="Y52" s="140"/>
+      <c r="Z52" s="140"/>
+      <c r="AA52" s="123"/>
     </row>
   </sheetData>
   <mergeCells count="270">
-    <mergeCell ref="A24:A33"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="Z32:Z33"/>
-    <mergeCell ref="Y32:Y33"/>
-    <mergeCell ref="X32:X33"/>
-    <mergeCell ref="Z24:Z25"/>
-    <mergeCell ref="Y24:Y25"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="Y30:Y31"/>
-    <mergeCell ref="Z28:Z29"/>
-    <mergeCell ref="Z30:Z31"/>
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="X16:X17"/>
+    <mergeCell ref="Y16:Y17"/>
+    <mergeCell ref="Y28:Y29"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="X20:X21"/>
+    <mergeCell ref="Y20:Y21"/>
+    <mergeCell ref="X28:X29"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="Y26:Y27"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="A4:AA4"/>
+    <mergeCell ref="Z6:Z7"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="X6:X7"/>
+    <mergeCell ref="A6:A11"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="Z10:Z11"/>
+    <mergeCell ref="Y6:Y7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="Z36:Z37"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="X34:X35"/>
+    <mergeCell ref="Y34:Y35"/>
+    <mergeCell ref="Z34:Z35"/>
+    <mergeCell ref="Y36:Y37"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="AA32:AA33"/>
+    <mergeCell ref="AA16:AA17"/>
+    <mergeCell ref="AA20:AA21"/>
+    <mergeCell ref="AA41:AA42"/>
+    <mergeCell ref="AA45:AA46"/>
+    <mergeCell ref="AA47:AA48"/>
+    <mergeCell ref="AA24:AA25"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="AA28:AA29"/>
+    <mergeCell ref="AA26:AA27"/>
+    <mergeCell ref="AA34:AA35"/>
+    <mergeCell ref="AA36:AA37"/>
+    <mergeCell ref="X47:X48"/>
+    <mergeCell ref="Y41:Y42"/>
+    <mergeCell ref="Z41:Z42"/>
+    <mergeCell ref="X45:X46"/>
+    <mergeCell ref="Y45:Y46"/>
+    <mergeCell ref="AA43:AA44"/>
+    <mergeCell ref="Z43:Z44"/>
+    <mergeCell ref="Z45:Z46"/>
+    <mergeCell ref="X41:X42"/>
+    <mergeCell ref="X36:X37"/>
+    <mergeCell ref="X30:X31"/>
+    <mergeCell ref="AA51:AA52"/>
+    <mergeCell ref="AA49:AA50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="J51:J52"/>
+    <mergeCell ref="X51:X52"/>
+    <mergeCell ref="Z51:Z52"/>
+    <mergeCell ref="X49:X50"/>
+    <mergeCell ref="A38:AA38"/>
+    <mergeCell ref="Z49:Z50"/>
+    <mergeCell ref="Y47:Y48"/>
+    <mergeCell ref="Z47:Z48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="X43:X44"/>
+    <mergeCell ref="Y43:Y44"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A48"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J45:J46"/>
+    <mergeCell ref="Y51:Y52"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="Y49:Y50"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="F51:F52"/>
+    <mergeCell ref="G51:G52"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="AA12:AA13"/>
+    <mergeCell ref="AA14:AA15"/>
+    <mergeCell ref="X14:X15"/>
+    <mergeCell ref="Y14:Y15"/>
+    <mergeCell ref="Z20:Z21"/>
+    <mergeCell ref="X12:X13"/>
+    <mergeCell ref="Y12:Y13"/>
+    <mergeCell ref="Z12:Z13"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="Z14:Z15"/>
+    <mergeCell ref="Z16:Z17"/>
+    <mergeCell ref="Z18:Z19"/>
+    <mergeCell ref="AA18:AA19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="X18:X19"/>
+    <mergeCell ref="Y18:Y19"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="E28:G29"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="E26:G27"/>
+    <mergeCell ref="E22:G23"/>
+    <mergeCell ref="AA22:AA23"/>
+    <mergeCell ref="Z22:Z23"/>
+    <mergeCell ref="Z26:Z27"/>
+    <mergeCell ref="AA6:AA7"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AA10:AA11"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="E6:G7"/>
+    <mergeCell ref="E8:G9"/>
+    <mergeCell ref="E10:G11"/>
+    <mergeCell ref="E12:G13"/>
+    <mergeCell ref="E14:G15"/>
+    <mergeCell ref="E16:G17"/>
+    <mergeCell ref="E18:G19"/>
+    <mergeCell ref="E20:G21"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="X10:X11"/>
+    <mergeCell ref="Y10:Y11"/>
     <mergeCell ref="AA30:AA31"/>
     <mergeCell ref="X24:X25"/>
     <mergeCell ref="E30:G31"/>
@@ -12467,230 +12673,28 @@
     <mergeCell ref="I36:I37"/>
     <mergeCell ref="J26:J27"/>
     <mergeCell ref="X26:X27"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="E26:G27"/>
-    <mergeCell ref="E22:G23"/>
-    <mergeCell ref="AA22:AA23"/>
-    <mergeCell ref="Z22:Z23"/>
-    <mergeCell ref="Z26:Z27"/>
-    <mergeCell ref="AA6:AA7"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AA10:AA11"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="E6:G7"/>
-    <mergeCell ref="E8:G9"/>
-    <mergeCell ref="E10:G11"/>
-    <mergeCell ref="E12:G13"/>
-    <mergeCell ref="E14:G15"/>
-    <mergeCell ref="E16:G17"/>
-    <mergeCell ref="E18:G19"/>
-    <mergeCell ref="E20:G21"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="X10:X11"/>
-    <mergeCell ref="Y10:Y11"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="E28:G29"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="I32:I33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="AA12:AA13"/>
-    <mergeCell ref="AA14:AA15"/>
-    <mergeCell ref="X14:X15"/>
-    <mergeCell ref="Y14:Y15"/>
-    <mergeCell ref="Z20:Z21"/>
-    <mergeCell ref="X12:X13"/>
-    <mergeCell ref="Y12:Y13"/>
-    <mergeCell ref="Z12:Z13"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="Z14:Z15"/>
-    <mergeCell ref="Z16:Z17"/>
-    <mergeCell ref="Z18:Z19"/>
-    <mergeCell ref="AA18:AA19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="X18:X19"/>
-    <mergeCell ref="Y18:Y19"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="F51:F52"/>
-    <mergeCell ref="G51:G52"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="J45:J46"/>
-    <mergeCell ref="Y51:Y52"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="Y49:Y50"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="AA51:AA52"/>
-    <mergeCell ref="AA49:AA50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="J51:J52"/>
-    <mergeCell ref="X51:X52"/>
-    <mergeCell ref="Z51:Z52"/>
-    <mergeCell ref="X49:X50"/>
-    <mergeCell ref="A38:AA38"/>
-    <mergeCell ref="Z49:Z50"/>
-    <mergeCell ref="Y47:Y48"/>
-    <mergeCell ref="Z47:Z48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="X43:X44"/>
-    <mergeCell ref="Y43:Y44"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A48"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="AA32:AA33"/>
-    <mergeCell ref="AA16:AA17"/>
-    <mergeCell ref="AA20:AA21"/>
-    <mergeCell ref="AA41:AA42"/>
-    <mergeCell ref="AA45:AA46"/>
-    <mergeCell ref="AA47:AA48"/>
-    <mergeCell ref="AA24:AA25"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="AA28:AA29"/>
-    <mergeCell ref="AA26:AA27"/>
-    <mergeCell ref="AA34:AA35"/>
-    <mergeCell ref="AA36:AA37"/>
-    <mergeCell ref="X47:X48"/>
-    <mergeCell ref="Y41:Y42"/>
-    <mergeCell ref="Z41:Z42"/>
-    <mergeCell ref="X45:X46"/>
-    <mergeCell ref="Y45:Y46"/>
-    <mergeCell ref="AA43:AA44"/>
-    <mergeCell ref="Z43:Z44"/>
-    <mergeCell ref="Z45:Z46"/>
-    <mergeCell ref="X41:X42"/>
-    <mergeCell ref="X36:X37"/>
-    <mergeCell ref="X30:X31"/>
-    <mergeCell ref="Z36:Z37"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="X34:X35"/>
-    <mergeCell ref="Y34:Y35"/>
-    <mergeCell ref="Z34:Z35"/>
-    <mergeCell ref="Y36:Y37"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A16:A21"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="A4:AA4"/>
-    <mergeCell ref="Z6:Z7"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="X6:X7"/>
-    <mergeCell ref="A6:A11"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="Z10:Z11"/>
-    <mergeCell ref="Y6:Y7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="X16:X17"/>
-    <mergeCell ref="Y16:Y17"/>
-    <mergeCell ref="Y28:Y29"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="X20:X21"/>
-    <mergeCell ref="Y20:Y21"/>
-    <mergeCell ref="X28:X29"/>
-    <mergeCell ref="X22:X23"/>
-    <mergeCell ref="Y22:Y23"/>
-    <mergeCell ref="Y26:Y27"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="A24:A33"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="Z32:Z33"/>
+    <mergeCell ref="Y32:Y33"/>
+    <mergeCell ref="X32:X33"/>
+    <mergeCell ref="Z24:Z25"/>
+    <mergeCell ref="Y24:Y25"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="Y30:Y31"/>
+    <mergeCell ref="Z28:Z29"/>
+    <mergeCell ref="Z30:Z31"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="B28:B31"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B6 H6:J6 C6:C12 B8 H8:J8 B10 H10:J10 B12 H12:J12 H14:J14 H16:J16 H20:J20 C22 H22:J22 H24:J24 D26:E26 H26:J26 C26:C27 H28:J28 H30:J30 H32:J32 H34:J34 H36:J36 D41:J41 C41:C43 D45:J45 C45:C52 D47:J47 D49:J49 D51:J51">
@@ -13009,6 +13013,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -13146,12 +13155,13 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -13160,26 +13170,20 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{497B9C89-7047-44E4-9E7C-8AF16D1DE759}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D35B5AFA-8D8A-4152-8465-0651392DA3FD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/GlobalMoSMT-2023/Shared Documents/General/2026/Goals Alignment 2026/Strategic Execution 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3344" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A27AE65D-DBDE-4CC8-A71E-1E2190A0DEC8}"/>
+  <xr:revisionPtr revIDLastSave="3351" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E9AEA8D-0DA6-49E7-94E7-3A95162BDB91}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Mastersheet" sheetId="5" r:id="rId1"/>
     <sheet name="AOP Critical" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -498,9 +498,6 @@
     <t>Q2</t>
   </si>
   <si>
-    <t>Q3</t>
-  </si>
-  <si>
     <t xml:space="preserve">If reported Red then
 state Cause  </t>
   </si>
@@ -584,13 +581,6 @@
     <t>Increase contract penetration %</t>
   </si>
   <si>
-    <t>-0.8% delta Vs AOP. Excluding GRC 0.7% YoY improvement.  LATAM renewals improved ITM Sep. Expected turnaround is Q4 2026 (Dec)</t>
-  </si>
-  <si>
-    <t>1) Funnel focus actions driven across regions for renewals.
-2) Contract Funnel tracked 90 days before expiry for timely renewals.</t>
-  </si>
-  <si>
     <t>Adjusted EBITA %</t>
   </si>
   <si>
@@ -615,13 +605,200 @@
     <t>Mn</t>
   </si>
   <si>
+    <t>Inventory MAT sales</t>
+  </si>
+  <si>
+    <t>Inventory as a % MAT sales</t>
+  </si>
+  <si>
+    <t>Inventory as a % MAT sales KPI</t>
+  </si>
+  <si>
+    <t>NPI Schedule Adherence</t>
+  </si>
+  <si>
+    <t>Shivaraj G</t>
+  </si>
+  <si>
+    <t>Dhruv  Schedule Adherence</t>
+  </si>
+  <si>
+    <t>Implied Market Share Gain</t>
+  </si>
+  <si>
+    <t>Sarika P</t>
+  </si>
+  <si>
+    <t>Implied Market Share Gain (ITQ)</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>QTR</t>
+  </si>
+  <si>
+    <t>Win Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Win Rate </t>
+  </si>
+  <si>
+    <t>(Philips OIT) / (Philips OIT + lost SFDC + not pursuing SFDC)</t>
+  </si>
+  <si>
+    <t>Implied Market Share Gain KPI</t>
+  </si>
+  <si>
+    <t>Order Intake Growth</t>
+  </si>
+  <si>
+    <t>OIT Growth % (EQ)</t>
+  </si>
+  <si>
+    <t>OIT (Equipment  + Service)</t>
+  </si>
+  <si>
+    <t>OIT Growth % (CS)</t>
+  </si>
+  <si>
+    <t>Comparable Sales</t>
+  </si>
+  <si>
+    <t>Monthly Sales recognized (EQ)</t>
+  </si>
+  <si>
+    <t>CSG % KPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impact Index KPI </t>
+  </si>
+  <si>
+    <t>Lakshmi M</t>
+  </si>
+  <si>
+    <t>EES scores are out! It is a balanced story. We are better than H1 2025 but slightly worse than H2 2025</t>
+  </si>
+  <si>
+    <t>CS has hit it out of the park.Quality dipped from 100% but still highest, Marketing is holding but at low scores. R&amp;D has dropped some big numbers.</t>
+  </si>
+  <si>
+    <t>Employee Engagement KPI</t>
+  </si>
+  <si>
+    <t>HY</t>
+  </si>
+  <si>
+    <t>MoS Value Levers 2026 - 2028:</t>
+  </si>
+  <si>
+    <t>Value Levers</t>
+  </si>
+  <si>
+    <t>AOP
+ 2026</t>
+  </si>
+  <si>
+    <t>AOP
+ 2027</t>
+  </si>
+  <si>
+    <t>AOP
+ 2028</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
+  <si>
+    <t>Cost Of Non-Quality as % of Sales</t>
+  </si>
+  <si>
+    <t>Cost of FCO, Warranty, Obsolescence, Scrap and Rework.</t>
+  </si>
+  <si>
+    <t>Competitive Roadmap</t>
+  </si>
+  <si>
+    <t>Roadmap MS% delivery (NPI OIT)</t>
+  </si>
+  <si>
+    <t>Zenition 10 &amp; 30 OIT below Q2 AOP due NPIs and price pressure from GE &amp; Siemens</t>
+  </si>
+  <si>
+    <t>Focus on Philips IB opportunity through mapping and targeted promotions to improve win rate</t>
+  </si>
+  <si>
+    <t>(MS% delivered by roadmap)
+/ (MS% ambition) 
+over 5 year horizon</t>
+  </si>
+  <si>
+    <t>Vitality index</t>
+  </si>
+  <si>
+    <t>% of sales from MoS Innovation &lt; 3 years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Improve Z10 &amp; Z30 competitiveness (sales training to counter competition) and bundling service at POS address price gap
+</t>
+  </si>
+  <si>
+    <t>I2M Value Creation</t>
+  </si>
+  <si>
+    <t>Development progress (per year, per quarter, %) X Incremental IGM</t>
+  </si>
+  <si>
+    <t>Development progress 
+(per year, per quarter, %) X Incremental IGM,( from business cases, M€ )</t>
+  </si>
+  <si>
+    <t>Cusotomer Focus</t>
+  </si>
+  <si>
+    <t>Services - Time To System Up (TTSU)</t>
+  </si>
+  <si>
+    <t>% of system down cases back up &lt;48hrs</t>
+  </si>
+  <si>
+    <t>Time To System Up &lt; 48h</t>
+  </si>
+  <si>
+    <t>Profitability - Margin Expansion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Driving profitability via margin expansion  </t>
+  </si>
+  <si>
+    <t>Focus on optimizing FCP, pricing, and product mix to drive margin expansion</t>
+  </si>
+  <si>
     <t>YTD Sept Productivity no's on track.Good Realization from E&amp;E savings of Pune and also a gap reduction of R&amp;D Budget YTD.</t>
   </si>
   <si>
-    <t>Inventory MAT sales</t>
-  </si>
-  <si>
-    <t>Inventory as a % MAT sales</t>
+    <t>EQ OIT YTD Sep lower by 0.2M, which is mainly coming by NAR -4.4M, EU -3.7M however Growth supported by over-drive +7.9M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current OOH does not support FY revnue plan. 
+OOH is 117 M agaist AOP of 141M .B&amp;B  24 M B&amp;B required to meet FY AOP.
+</t>
+  </si>
+  <si>
+    <t>Growth</t>
+  </si>
+  <si>
+    <t>Drive B&amp;B OIT 
+NAR : 5 M , EU: 8.5M , Growth : 7.6</t>
+  </si>
+  <si>
+    <t>1. NAR :AOP accelator program launched to improve OIT to rev conversion.
+2. EU : Demo  liquidation plan aligned toward Q4 to maximise OIT in Q3.
+3. Growth:  Namibia tender conversion in Q4
+4. UIEP : COE team to analyse the difference and accurate capturing in AOP 2027</t>
   </si>
   <si>
     <t xml:space="preserve">Market inventory : 7.7 M above AOP .
@@ -632,191 +809,14 @@
 </t>
   </si>
   <si>
-    <t>1. NAR :AOP accelator program launched to improve OIT to rev conversion.
-2. EU : Demo  liquidation plan aligned toward Q4 to maximise OIT in Q3.
-3. Growth:  Namibia tender conversion in Q4
-4. UIEP : COE team to analyse the difference and accurate capturing in AOP 2027</t>
-  </si>
-  <si>
-    <t>Inventory as a % MAT sales KPI</t>
-  </si>
-  <si>
-    <t>NPI Schedule Adherence</t>
-  </si>
-  <si>
-    <t>Shivaraj G</t>
-  </si>
-  <si>
-    <t>Dhruv  Schedule Adherence</t>
-  </si>
-  <si>
-    <t>Implied Market Share Gain</t>
-  </si>
-  <si>
-    <t>Sarika P</t>
-  </si>
-  <si>
-    <t>Implied Market Share Gain (ITQ)</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>QTR</t>
-  </si>
-  <si>
-    <t>Win Rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Win Rate </t>
-  </si>
-  <si>
-    <t>(Philips OIT) / (Philips OIT + lost SFDC + not pursuing SFDC)</t>
-  </si>
-  <si>
-    <t>Implied Market Share Gain KPI</t>
-  </si>
-  <si>
-    <t>Order Intake Growth</t>
-  </si>
-  <si>
-    <t>OIT Growth % (EQ)</t>
-  </si>
-  <si>
-    <t>EQ OIT YTD Sep lower by 0.2M, which is mainly coming by NAR -4.4M, EU -3.7M however Growth supported by over-drive +7.9M</t>
-  </si>
-  <si>
-    <t>OIT (Equipment  + Service)</t>
-  </si>
-  <si>
-    <t>OIT Growth % (CS)</t>
-  </si>
-  <si>
-    <t>Comparable Sales</t>
-  </si>
-  <si>
-    <t>Monthly Sales recognized (EQ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current OOH does not support FY revnue plan. 
-OOH is 117 M agaist AOP of 141M .B&amp;B  24 M B&amp;B required to meet FY AOP.
-</t>
-  </si>
-  <si>
-    <t>Drive B&amp;B OIT 
-NAR : 5 M , EU: 8.5M , Growth : 7.6</t>
-  </si>
-  <si>
-    <t>CSG % KPI</t>
-  </si>
-  <si>
-    <t>Growth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Impact Index KPI </t>
-  </si>
-  <si>
-    <t>Lakshmi M</t>
-  </si>
-  <si>
-    <t>EES scores are out! It is a balanced story. We are better than H1 2025 but slightly worse than H2 2025</t>
-  </si>
-  <si>
-    <t>CS has hit it out of the park.Quality dipped from 100% but still highest, Marketing is holding but at low scores. R&amp;D has dropped some big numbers.</t>
-  </si>
-  <si>
-    <t>Employee Engagement KPI</t>
-  </si>
-  <si>
-    <t>HY</t>
-  </si>
-  <si>
-    <t>MoS Value Levers 2026 - 2028:</t>
-  </si>
-  <si>
-    <t>Value Levers</t>
-  </si>
-  <si>
-    <t>AOP
- 2026</t>
-  </si>
-  <si>
-    <t>AOP
- 2027</t>
-  </si>
-  <si>
-    <t>AOP
- 2028</t>
-  </si>
-  <si>
-    <t>Mar</t>
-  </si>
-  <si>
-    <t>June</t>
-  </si>
-  <si>
-    <t>Cost Of Non-Quality as % of Sales</t>
-  </si>
-  <si>
-    <t>Cost of FCO, Warranty, Obsolescence, Scrap and Rework.</t>
-  </si>
-  <si>
-    <t>Competitive Roadmap</t>
-  </si>
-  <si>
-    <t>Roadmap MS% delivery (NPI OIT)</t>
-  </si>
-  <si>
-    <t>Zenition 10 &amp; 30 OIT below Q2 AOP due NPIs and price pressure from GE &amp; Siemens</t>
-  </si>
-  <si>
-    <t>Focus on Philips IB opportunity through mapping and targeted promotions to improve win rate</t>
-  </si>
-  <si>
-    <t>(MS% delivered by roadmap)
-/ (MS% ambition) 
-over 5 year horizon</t>
-  </si>
-  <si>
-    <t>Vitality index</t>
-  </si>
-  <si>
-    <t>% of sales from MoS Innovation &lt; 3 years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Improve Z10 &amp; Z30 competitiveness (sales training to counter competition) and bundling service at POS address price gap
-</t>
-  </si>
-  <si>
-    <t>I2M Value Creation</t>
-  </si>
-  <si>
-    <t>Development progress (per year, per quarter, %) X Incremental IGM</t>
-  </si>
-  <si>
-    <t>Development progress 
-(per year, per quarter, %) X Incremental IGM,( from business cases, M€ )</t>
-  </si>
-  <si>
-    <t>Cusotomer Focus</t>
-  </si>
-  <si>
-    <t>Services - Time To System Up (TTSU)</t>
-  </si>
-  <si>
-    <t>% of system down cases back up &lt;48hrs</t>
-  </si>
-  <si>
-    <t>Time To System Up &lt; 48h</t>
-  </si>
-  <si>
-    <t>Profitability - Margin Expansion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Driving profitability via margin expansion  </t>
-  </si>
-  <si>
-    <t>Focus on optimizing FCP, pricing, and product mix to drive margin expansion</t>
+    <t>1) Funnel focus actions driven across regions for renewals.
+2) Contract Funnel tracked 90 days before expiry for timely renewals.</t>
+  </si>
+  <si>
+    <t>-0.8% delta Vs AOP. Excluding GRC 0.7% YoY improvement.  LATAM renewals improved ITM Sep. Expected turnaround is Q4 2026 (Dec)</t>
+  </si>
+  <si>
+    <t>Q3</t>
   </si>
 </sst>
 </file>
@@ -830,7 +830,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1068,7 +1068,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -1310,6 +1310,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1318,7 +1331,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1556,260 +1569,269 @@
     <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4628,6 +4650,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BD41CE00-E924-4733-B76A-3C4E09FA89B8}" name="Customer_Focus" displayName="Customer_Focus" ref="A14:V20" totalsRowShown="0">
   <autoFilter ref="A14:V20" xr:uid="{BD41CE00-E924-4733-B76A-3C4E09FA89B8}"/>
@@ -5184,29 +5210,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247AD843-49A7-417E-9F24-86908363EFA2}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:V59"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.5703125" customWidth="1"/>
-    <col min="5" max="6" width="10.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" customWidth="1"/>
+    <col min="3" max="3" width="55.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.54296875" customWidth="1"/>
+    <col min="5" max="6" width="10.453125" customWidth="1"/>
+    <col min="7" max="7" width="13.81640625" customWidth="1"/>
+    <col min="9" max="9" width="11.54296875" customWidth="1"/>
+    <col min="10" max="10" width="13.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="15.95">
+    <row r="1" spans="1:22" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -5274,7 +5300,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5" t="str">
         <f>IF('AOP Critical'!B6="","",'AOP Critical'!B6)</f>
         <v>Complaint Closure</v>
@@ -5360,7 +5386,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" t="str">
         <f>IF('AOP Critical'!B6="","",'AOP Critical'!B6)</f>
         <v>Complaint Closure</v>
@@ -5441,12 +5467,12 @@
         <f>IF('AOP Critical'!V7="","",'AOP Critical'!V7)</f>
         <v/>
       </c>
-      <c r="V6" s="67" t="str">
+      <c r="V6" s="67">
         <f>IF('AOP Critical'!W7="","",'AOP Critical'!W7)</f>
-        <v/>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" t="str">
         <f>IF('AOP Critical'!B8="","",'AOP Critical'!B8)</f>
         <v>% of CAPA investgation</v>
@@ -5532,7 +5558,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" t="str">
         <f>IF('AOP Critical'!B8="","",'AOP Critical'!B8)</f>
         <v>% of CAPA investgation</v>
@@ -5618,7 +5644,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
         <f>IF('AOP Critical'!B10="","",'AOP Critical'!B10)</f>
         <v xml:space="preserve"># of Corrections &amp; Removals </v>
@@ -5704,7 +5730,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
         <f>IF('AOP Critical'!B10="","",'AOP Critical'!B10)</f>
         <v xml:space="preserve"># of Corrections &amp; Removals </v>
@@ -5790,7 +5816,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11" t="str">
         <f>IF('AOP Critical'!B41="","",'AOP Critical'!B41)</f>
         <v>Cost Of Non-Quality as % of Sales</v>
@@ -5876,7 +5902,7 @@
         <v>3.32E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
         <f>IF('AOP Critical'!B41="","",'AOP Critical'!B41)</f>
         <v>Cost Of Non-Quality as % of Sales</v>
@@ -5962,12 +5988,12 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -6035,7 +6061,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15" t="str">
         <f>IF('AOP Critical'!B12="","",'AOP Critical'!B12)</f>
         <v>Ontime In Full</v>
@@ -6125,7 +6151,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" t="str">
         <f>IF('AOP Critical'!B12="","",'AOP Critical'!B12)</f>
         <v>Ontime In Full</v>
@@ -6215,7 +6241,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" t="str">
         <f>IF('AOP Critical'!B14="","",'AOP Critical'!B14)</f>
         <v>Contract Penetration</v>
@@ -6305,7 +6331,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A18" t="str">
         <f>IF('AOP Critical'!B14="","",'AOP Critical'!B14)</f>
         <v>Contract Penetration</v>
@@ -6395,7 +6421,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19" t="str">
         <f>IF('AOP Critical'!B49="","",'AOP Critical'!B49)</f>
         <v>Services - Time To System Up (TTSU)</v>
@@ -6485,7 +6511,7 @@
         <v>0.73999999999999966</v>
       </c>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A20" t="str">
         <f>IF('AOP Critical'!B49="","",'AOP Critical'!B49)</f>
         <v>Services - Time To System Up (TTSU)</v>
@@ -6575,12 +6601,12 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>2</v>
       </c>
@@ -6648,7 +6674,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:22">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A23" t="str">
         <f>IF('AOP Critical'!B16="","",'AOP Critical'!B16)</f>
         <v>Adjusted EBITA %</v>
@@ -6738,7 +6764,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A24" t="str">
         <f>IF('AOP Critical'!B16="","",'AOP Critical'!B16)</f>
         <v>Adjusted EBITA %</v>
@@ -6828,7 +6854,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A25" t="str">
         <f>IF('AOP Critical'!B18="","",'AOP Critical'!B18)</f>
         <v>Productivity</v>
@@ -6918,7 +6944,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A26" t="str">
         <f>IF('AOP Critical'!B18="","",'AOP Critical'!B18)</f>
         <v>Productivity</v>
@@ -7008,7 +7034,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A27" t="str">
         <f>IF('AOP Critical'!B20="","",'AOP Critical'!B20)</f>
         <v>Inventory MAT sales</v>
@@ -7098,7 +7124,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A28" t="str">
         <f>IF('AOP Critical'!B20="","",'AOP Critical'!B20)</f>
         <v>Inventory MAT sales</v>
@@ -7188,7 +7214,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A29" t="str">
         <f>IF('AOP Critical'!B51="","",'AOP Critical'!B51)</f>
         <v>Profitability - Margin Expansion</v>
@@ -7278,7 +7304,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:22">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A30" t="str">
         <f>IF('AOP Critical'!B51="","",'AOP Critical'!B51)</f>
         <v>Profitability - Margin Expansion</v>
@@ -7368,12 +7394,12 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>2</v>
       </c>
@@ -7441,7 +7467,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:22">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A33" t="str">
         <f>IF('AOP Critical'!B26="","",'AOP Critical'!B26)</f>
         <v xml:space="preserve">Win Rate </v>
@@ -7531,7 +7557,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:22">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A34" t="str">
         <f>IF('AOP Critical'!B26="","",'AOP Critical'!B26)</f>
         <v xml:space="preserve">Win Rate </v>
@@ -7621,7 +7647,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:22">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A35" t="str">
         <f>IF('AOP Critical'!B22="","",'AOP Critical'!B22)</f>
         <v>NPI Schedule Adherence</v>
@@ -7711,7 +7737,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A36" t="str">
         <f>IF('AOP Critical'!B22="","",'AOP Critical'!B22)</f>
         <v>NPI Schedule Adherence</v>
@@ -7801,7 +7827,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:22">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A37" t="str">
         <f>IF('AOP Critical'!B43="","",'AOP Critical'!B43)</f>
         <v>Competitive Roadmap</v>
@@ -7891,7 +7917,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:22">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A38" t="str">
         <f>IF('AOP Critical'!B43="","",'AOP Critical'!B43)</f>
         <v>Competitive Roadmap</v>
@@ -7981,7 +8007,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:22">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A39" t="str">
         <f>IF('AOP Critical'!B45="","",'AOP Critical'!B45)</f>
         <v>Vitality index</v>
@@ -8071,7 +8097,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:22">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A40" t="str">
         <f>IF('AOP Critical'!B45="","",'AOP Critical'!B45)</f>
         <v>Vitality index</v>
@@ -8161,7 +8187,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:22">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A41" t="str">
         <f>IF('AOP Critical'!B47="","",'AOP Critical'!B47)</f>
         <v>I2M Value Creation</v>
@@ -8251,7 +8277,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:22">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A42" t="str">
         <f>IF('AOP Critical'!B47="","",'AOP Critical'!B47)</f>
         <v>I2M Value Creation</v>
@@ -8341,12 +8367,12 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:22">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="1:22">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>2</v>
       </c>
@@ -8414,7 +8440,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="1:22">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A45" t="str">
         <f>IF('AOP Critical'!D28="","",'AOP Critical'!D28)</f>
         <v>OIT Growth % (EQ)</v>
@@ -8504,7 +8530,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:22">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A46" t="str">
         <f>IF('AOP Critical'!D28="","",'AOP Critical'!D28)</f>
         <v>OIT Growth % (EQ)</v>
@@ -8594,7 +8620,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:22">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A47" t="str">
         <f>IF('AOP Critical'!D30="","",'AOP Critical'!D30)</f>
         <v>OIT Growth % (CS)</v>
@@ -8681,7 +8707,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:22">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A48" t="str">
         <f>IF('AOP Critical'!D30="","",'AOP Critical'!D30)</f>
         <v>OIT Growth % (CS)</v>
@@ -8767,7 +8793,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:22">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A49" t="str">
         <f>IF('AOP Critical'!B32="","",'AOP Critical'!B32)</f>
         <v>Comparable Sales</v>
@@ -8857,7 +8883,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:22">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A50" t="str">
         <f>IF('AOP Critical'!B32="","",'AOP Critical'!B32)</f>
         <v>Comparable Sales</v>
@@ -8947,7 +8973,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:22">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A51" t="str">
         <f>IF('AOP Critical'!B24="","",'AOP Critical'!B24)</f>
         <v>Implied Market Share Gain</v>
@@ -9037,7 +9063,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:22">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A52" t="str">
         <f>IF('AOP Critical'!B24="","",'AOP Critical'!B24)</f>
         <v>Implied Market Share Gain</v>
@@ -9127,12 +9153,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:22">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A54" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:22">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>2</v>
       </c>
@@ -9200,7 +9226,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:22">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>29</v>
       </c>
@@ -9275,7 +9301,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="57" spans="1:22">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>29</v>
       </c>
@@ -9350,7 +9376,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:22">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>35</v>
       </c>
@@ -9425,7 +9451,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:22">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>35</v>
       </c>
@@ -9521,35 +9547,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{632542D1-52E6-4116-B536-B17D5839DF19}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AC52"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.45" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="20.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.5703125" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="1" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="26.85546875" customWidth="1"/>
-    <col min="5" max="5" width="5.140625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="1.85546875" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="2.7109375" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" customWidth="1"/>
-    <col min="12" max="12" width="5.5703125" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="6.85546875" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="6.28515625" customWidth="1"/>
-    <col min="15" max="15" width="7.28515625" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="6.140625" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="6.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.54296875" customWidth="1"/>
+    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" style="1" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="26.81640625" customWidth="1"/>
+    <col min="5" max="5" width="5.1796875" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="4.54296875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="1.81640625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="2.7265625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="5.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.7265625" customWidth="1"/>
+    <col min="12" max="12" width="5.54296875" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="6.81640625" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="6.26953125" customWidth="1"/>
+    <col min="15" max="15" width="7.26953125" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="6.1796875" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="6.1796875" customWidth="1"/>
     <col min="23" max="23" width="6" customWidth="1"/>
-    <col min="24" max="24" width="58.85546875" style="20" customWidth="1"/>
-    <col min="25" max="25" width="68.140625" customWidth="1"/>
-    <col min="26" max="26" width="17.7109375" customWidth="1"/>
+    <col min="24" max="24" width="58.81640625" style="20" customWidth="1"/>
+    <col min="25" max="25" width="68.1796875" customWidth="1"/>
+    <col min="26" max="26" width="17.7265625" customWidth="1"/>
     <col min="27" max="27" width="57" style="13" customWidth="1"/>
-    <col min="28" max="46" width="8.5703125" customWidth="1"/>
+    <col min="28" max="46" width="8.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="20.45" customHeight="1">
+    <row r="1" spans="1:27" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
         <v>39</v>
       </c>
@@ -9560,7 +9586,7 @@
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
     </row>
-    <row r="2" spans="1:27" ht="20.45" customHeight="1">
+    <row r="2" spans="1:27" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="6"/>
       <c r="C2" s="7"/>
       <c r="E2" s="6"/>
@@ -9569,11 +9595,11 @@
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
     </row>
-    <row r="3" spans="1:27" s="5" customFormat="1" ht="20.45" customHeight="1">
-      <c r="A3" s="162" t="s">
+    <row r="3" spans="1:27" s="5" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="105" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="162"/>
+      <c r="B3" s="105"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -9590,42 +9616,42 @@
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
       <c r="V3" s="2"/>
-      <c r="X3" s="89"/>
+      <c r="X3" s="171"/>
       <c r="AA3" s="14"/>
     </row>
-    <row r="4" spans="1:27" s="5" customFormat="1" ht="20.45" customHeight="1">
-      <c r="A4" s="163" t="str">
+    <row r="4" spans="1:27" s="5" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="107" t="str">
         <f ca="1">"Current Month-Year " &amp; ":" &amp; TEXT(TODAY(),"YYYY-MM")</f>
         <v>Current Month-Year :2026-10</v>
       </c>
-      <c r="B4" s="163"/>
-      <c r="C4" s="163"/>
-      <c r="D4" s="163"/>
-      <c r="E4" s="163"/>
-      <c r="F4" s="163"/>
-      <c r="G4" s="163"/>
-      <c r="H4" s="163"/>
-      <c r="I4" s="163"/>
-      <c r="J4" s="163"/>
-      <c r="K4" s="163"/>
-      <c r="L4" s="163"/>
-      <c r="M4" s="163"/>
-      <c r="N4" s="163"/>
-      <c r="O4" s="163"/>
-      <c r="P4" s="163"/>
-      <c r="Q4" s="163"/>
-      <c r="R4" s="163"/>
-      <c r="S4" s="163"/>
-      <c r="T4" s="163"/>
-      <c r="U4" s="163"/>
-      <c r="V4" s="163"/>
-      <c r="W4" s="163"/>
-      <c r="X4" s="163"/>
-      <c r="Y4" s="163"/>
-      <c r="Z4" s="163"/>
-      <c r="AA4" s="163"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="107"/>
+      <c r="K4" s="107"/>
+      <c r="L4" s="107"/>
+      <c r="M4" s="107"/>
+      <c r="N4" s="107"/>
+      <c r="O4" s="107"/>
+      <c r="P4" s="107"/>
+      <c r="Q4" s="107"/>
+      <c r="R4" s="107"/>
+      <c r="S4" s="107"/>
+      <c r="T4" s="107"/>
+      <c r="U4" s="107"/>
+      <c r="V4" s="107"/>
+      <c r="W4" s="107"/>
+      <c r="X4" s="107"/>
+      <c r="Y4" s="107"/>
+      <c r="Z4" s="107"/>
+      <c r="AA4" s="107"/>
     </row>
-    <row r="5" spans="1:27" ht="20.45" customHeight="1">
+    <row r="5" spans="1:27" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="85" t="s">
         <v>0</v>
       </c>
@@ -9638,11 +9664,11 @@
       <c r="D5" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="164" t="s">
+      <c r="E5" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="164"/>
-      <c r="G5" s="164"/>
+      <c r="F5" s="111"/>
+      <c r="G5" s="111"/>
       <c r="H5" s="86" t="s">
         <v>8</v>
       </c>
@@ -9680,7 +9706,7 @@
         <v>19</v>
       </c>
       <c r="T5" s="34" t="s">
-        <v>43</v>
+        <v>142</v>
       </c>
       <c r="U5" s="34" t="s">
         <v>21</v>
@@ -9692,47 +9718,47 @@
         <v>23</v>
       </c>
       <c r="X5" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y5" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="Y5" s="11" t="s">
+      <c r="Z5" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="Z5" s="11" t="s">
+      <c r="AA5" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="AA5" s="15" t="s">
+    </row>
+    <row r="6" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="104" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="6" spans="1:27" ht="14.45">
-      <c r="A6" s="92" t="s">
+      <c r="B6" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="125" t="s">
+      <c r="C6" s="89" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="137" t="s">
+      <c r="D6" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="105" t="s">
+      <c r="E6" s="103">
+        <v>10</v>
+      </c>
+      <c r="F6" s="103"/>
+      <c r="G6" s="103"/>
+      <c r="H6" s="106" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="104">
-        <v>10</v>
-      </c>
-      <c r="F6" s="104"/>
-      <c r="G6" s="104"/>
-      <c r="H6" s="103" t="s">
+      <c r="I6" s="103" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="102" t="s">
         <v>52</v>
       </c>
-      <c r="I6" s="104" t="s">
-        <v>33</v>
-      </c>
-      <c r="J6" s="106" t="s">
+      <c r="K6" s="22" t="s">
         <v>53</v>
-      </c>
-      <c r="K6" s="22" t="s">
-        <v>54</v>
       </c>
       <c r="L6" s="35">
         <v>0.08</v>
@@ -9770,26 +9796,26 @@
       <c r="W6" s="27">
         <v>0.05</v>
       </c>
-      <c r="X6" s="110"/>
-      <c r="Y6" s="101"/>
-      <c r="Z6" s="101"/>
-      <c r="AA6" s="117" t="s">
+      <c r="X6" s="101"/>
+      <c r="Y6" s="108"/>
+      <c r="Z6" s="108"/>
+      <c r="AA6" s="118" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="104"/>
+      <c r="B7" s="88"/>
+      <c r="C7" s="89"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="103"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="106"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="102"/>
+      <c r="K7" s="22" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="14.45">
-      <c r="A7" s="92"/>
-      <c r="B7" s="125"/>
-      <c r="C7" s="137"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="104"/>
-      <c r="F7" s="104"/>
-      <c r="G7" s="104"/>
-      <c r="H7" s="103"/>
-      <c r="I7" s="104"/>
-      <c r="J7" s="106"/>
-      <c r="K7" s="22" t="s">
-        <v>56</v>
       </c>
       <c r="L7" s="17">
         <v>3.7999999999999999E-2</v>
@@ -9820,39 +9846,41 @@
       </c>
       <c r="U7" s="50"/>
       <c r="V7" s="50"/>
-      <c r="W7" s="50"/>
-      <c r="X7" s="111"/>
-      <c r="Y7" s="131"/>
-      <c r="Z7" s="131"/>
-      <c r="AA7" s="118"/>
+      <c r="W7" s="50">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="X7" s="91"/>
+      <c r="Y7" s="93"/>
+      <c r="Z7" s="93"/>
+      <c r="AA7" s="119"/>
     </row>
-    <row r="8" spans="1:27" ht="14.45">
-      <c r="A8" s="92"/>
-      <c r="B8" s="125" t="s">
+    <row r="8" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="104"/>
+      <c r="B8" s="88" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="89" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="87" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="137" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="105" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" s="104">
+      <c r="E8" s="103">
         <v>90</v>
       </c>
-      <c r="F8" s="104"/>
-      <c r="G8" s="104"/>
-      <c r="H8" s="103" t="s">
+      <c r="F8" s="103"/>
+      <c r="G8" s="103"/>
+      <c r="H8" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="104" t="s">
+      <c r="I8" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="106" t="s">
+      <c r="J8" s="102" t="s">
+        <v>52</v>
+      </c>
+      <c r="K8" s="22" t="s">
         <v>53</v>
-      </c>
-      <c r="K8" s="22" t="s">
-        <v>54</v>
       </c>
       <c r="L8" s="35">
         <v>0.9</v>
@@ -9884,26 +9912,26 @@
       <c r="U8" s="18"/>
       <c r="V8" s="18"/>
       <c r="W8" s="27"/>
-      <c r="X8" s="111"/>
-      <c r="Y8" s="130"/>
-      <c r="Z8" s="115"/>
-      <c r="AA8" s="117" t="s">
-        <v>59</v>
+      <c r="X8" s="91"/>
+      <c r="Y8" s="92"/>
+      <c r="Z8" s="109"/>
+      <c r="AA8" s="118" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="14.45">
-      <c r="A9" s="92"/>
-      <c r="B9" s="125"/>
-      <c r="C9" s="137"/>
-      <c r="D9" s="105"/>
-      <c r="E9" s="104"/>
-      <c r="F9" s="104"/>
-      <c r="G9" s="104"/>
-      <c r="H9" s="103"/>
-      <c r="I9" s="104"/>
-      <c r="J9" s="106"/>
+    <row r="9" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="104"/>
+      <c r="B9" s="88"/>
+      <c r="C9" s="89"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="103"/>
+      <c r="F9" s="103"/>
+      <c r="G9" s="103"/>
+      <c r="H9" s="106"/>
+      <c r="I9" s="103"/>
+      <c r="J9" s="102"/>
       <c r="K9" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L9" s="19">
         <v>1</v>
@@ -9935,38 +9963,38 @@
       <c r="U9" s="52"/>
       <c r="V9" s="52"/>
       <c r="W9" s="52"/>
-      <c r="X9" s="111"/>
-      <c r="Y9" s="131"/>
-      <c r="Z9" s="116"/>
-      <c r="AA9" s="118"/>
+      <c r="X9" s="91"/>
+      <c r="Y9" s="93"/>
+      <c r="Z9" s="110"/>
+      <c r="AA9" s="119"/>
     </row>
-    <row r="10" spans="1:27" ht="14.45">
-      <c r="A10" s="92"/>
-      <c r="B10" s="125" t="s">
+    <row r="10" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="104"/>
+      <c r="B10" s="88" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="89" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="87" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="137" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="105" t="s">
+      <c r="E10" s="103">
+        <v>1</v>
+      </c>
+      <c r="F10" s="103"/>
+      <c r="G10" s="103"/>
+      <c r="H10" s="106" t="s">
+        <v>51</v>
+      </c>
+      <c r="I10" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="E10" s="104">
-        <v>1</v>
-      </c>
-      <c r="F10" s="104"/>
-      <c r="G10" s="104"/>
-      <c r="H10" s="103" t="s">
+      <c r="J10" s="102" t="s">
         <v>52</v>
       </c>
-      <c r="I10" s="104" t="s">
-        <v>62</v>
-      </c>
-      <c r="J10" s="106" t="s">
+      <c r="K10" s="22" t="s">
         <v>53</v>
-      </c>
-      <c r="K10" s="22" t="s">
-        <v>54</v>
       </c>
       <c r="L10" s="36">
         <v>1</v>
@@ -9998,26 +10026,26 @@
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
       <c r="W10" s="33"/>
-      <c r="X10" s="111"/>
-      <c r="Y10" s="119"/>
-      <c r="Z10" s="165"/>
-      <c r="AA10" s="117" t="s">
-        <v>63</v>
+      <c r="X10" s="91"/>
+      <c r="Y10" s="158"/>
+      <c r="Z10" s="112"/>
+      <c r="AA10" s="118" t="s">
+        <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="15" thickBot="1">
-      <c r="A11" s="92"/>
-      <c r="B11" s="125"/>
-      <c r="C11" s="137"/>
-      <c r="D11" s="105"/>
-      <c r="E11" s="104"/>
-      <c r="F11" s="104"/>
-      <c r="G11" s="104"/>
-      <c r="H11" s="103"/>
-      <c r="I11" s="104"/>
-      <c r="J11" s="106"/>
+    <row r="11" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="104"/>
+      <c r="B11" s="88"/>
+      <c r="C11" s="89"/>
+      <c r="D11" s="87"/>
+      <c r="E11" s="103"/>
+      <c r="F11" s="103"/>
+      <c r="G11" s="103"/>
+      <c r="H11" s="106"/>
+      <c r="I11" s="103"/>
+      <c r="J11" s="102"/>
       <c r="K11" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L11" s="9">
         <v>2</v>
@@ -10049,40 +10077,40 @@
       <c r="U11" s="31"/>
       <c r="V11" s="31"/>
       <c r="W11" s="32"/>
-      <c r="X11" s="111"/>
-      <c r="Y11" s="120"/>
-      <c r="Z11" s="166"/>
-      <c r="AA11" s="118"/>
+      <c r="X11" s="91"/>
+      <c r="Y11" s="159"/>
+      <c r="Z11" s="113"/>
+      <c r="AA11" s="119"/>
     </row>
-    <row r="12" spans="1:27" ht="14.45">
-      <c r="A12" s="92" t="s">
+    <row r="12" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="104" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="123" t="s">
+      <c r="B12" s="90" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="90" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="123" t="s">
+      <c r="D12" s="87" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="105" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12" s="104">
+      <c r="E12" s="103">
         <v>84</v>
       </c>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="103" t="s">
+      <c r="F12" s="103"/>
+      <c r="G12" s="103"/>
+      <c r="H12" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="104" t="s">
+      <c r="I12" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="106" t="s">
+      <c r="J12" s="102" t="s">
+        <v>52</v>
+      </c>
+      <c r="K12" s="22" t="s">
         <v>53</v>
-      </c>
-      <c r="K12" s="22" t="s">
-        <v>54</v>
       </c>
       <c r="L12" s="35">
         <v>0.69</v>
@@ -10120,26 +10148,26 @@
       <c r="W12" s="25">
         <v>0.79</v>
       </c>
-      <c r="X12" s="111"/>
-      <c r="Y12" s="130"/>
-      <c r="Z12" s="131"/>
-      <c r="AA12" s="117" t="s">
-        <v>67</v>
+      <c r="X12" s="91"/>
+      <c r="Y12" s="92"/>
+      <c r="Z12" s="93"/>
+      <c r="AA12" s="118" t="s">
+        <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="14.45">
-      <c r="A13" s="92"/>
-      <c r="B13" s="123"/>
-      <c r="C13" s="123"/>
-      <c r="D13" s="105"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="104"/>
-      <c r="G13" s="104"/>
-      <c r="H13" s="103"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="106"/>
+    <row r="13" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="104"/>
+      <c r="B13" s="90"/>
+      <c r="C13" s="90"/>
+      <c r="D13" s="87"/>
+      <c r="E13" s="103"/>
+      <c r="F13" s="103"/>
+      <c r="G13" s="103"/>
+      <c r="H13" s="106"/>
+      <c r="I13" s="103"/>
+      <c r="J13" s="102"/>
       <c r="K13" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L13" s="19">
         <v>0.83</v>
@@ -10171,38 +10199,38 @@
       <c r="U13" s="19"/>
       <c r="V13" s="19"/>
       <c r="W13" s="28"/>
-      <c r="X13" s="111"/>
-      <c r="Y13" s="131"/>
-      <c r="Z13" s="131"/>
-      <c r="AA13" s="118"/>
+      <c r="X13" s="91"/>
+      <c r="Y13" s="93"/>
+      <c r="Z13" s="93"/>
+      <c r="AA13" s="119"/>
     </row>
-    <row r="14" spans="1:27" ht="14.45">
-      <c r="A14" s="92"/>
-      <c r="B14" s="123" t="s">
+    <row r="14" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="104"/>
+      <c r="B14" s="90" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="124" t="s">
+      <c r="D14" s="87" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="105" t="s">
-        <v>70</v>
-      </c>
-      <c r="E14" s="104">
+      <c r="E14" s="103">
         <v>54.6</v>
       </c>
-      <c r="F14" s="104"/>
-      <c r="G14" s="104"/>
-      <c r="H14" s="103" t="s">
+      <c r="F14" s="103"/>
+      <c r="G14" s="103"/>
+      <c r="H14" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="104" t="s">
+      <c r="I14" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="J14" s="106" t="s">
+      <c r="J14" s="102" t="s">
+        <v>52</v>
+      </c>
+      <c r="K14" s="22" t="s">
         <v>53</v>
-      </c>
-      <c r="K14" s="22" t="s">
-        <v>54</v>
       </c>
       <c r="L14" s="37">
         <v>0.54249999999999998</v>
@@ -10234,28 +10262,28 @@
       <c r="U14" s="37"/>
       <c r="V14" s="37"/>
       <c r="W14" s="37"/>
-      <c r="X14" s="129" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y14" s="96" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z14" s="100"/>
-      <c r="AA14" s="127"/>
+      <c r="X14" s="170" t="s">
+        <v>141</v>
+      </c>
+      <c r="Y14" s="94" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z14" s="147"/>
+      <c r="AA14" s="146"/>
     </row>
-    <row r="15" spans="1:27" ht="15" thickBot="1">
-      <c r="A15" s="92"/>
-      <c r="B15" s="123"/>
-      <c r="C15" s="124"/>
-      <c r="D15" s="105"/>
-      <c r="E15" s="104"/>
-      <c r="F15" s="104"/>
-      <c r="G15" s="104"/>
-      <c r="H15" s="103"/>
-      <c r="I15" s="104"/>
-      <c r="J15" s="106"/>
+    <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="104"/>
+      <c r="B15" s="90"/>
+      <c r="C15" s="117"/>
+      <c r="D15" s="87"/>
+      <c r="E15" s="103"/>
+      <c r="F15" s="103"/>
+      <c r="G15" s="103"/>
+      <c r="H15" s="106"/>
+      <c r="I15" s="103"/>
+      <c r="J15" s="102"/>
       <c r="K15" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L15" s="17">
         <v>0.51780000000000004</v>
@@ -10287,40 +10315,40 @@
       <c r="U15" s="31"/>
       <c r="V15" s="31"/>
       <c r="W15" s="32"/>
-      <c r="X15" s="111"/>
-      <c r="Y15" s="101"/>
-      <c r="Z15" s="101"/>
-      <c r="AA15" s="128"/>
+      <c r="X15" s="91"/>
+      <c r="Y15" s="108"/>
+      <c r="Z15" s="108"/>
+      <c r="AA15" s="126"/>
     </row>
-    <row r="16" spans="1:27" ht="14.45">
-      <c r="A16" s="92" t="s">
+    <row r="16" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="104" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="123" t="s">
+      <c r="B16" s="90" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="90" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="87" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="103" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="123" t="s">
-        <v>74</v>
-      </c>
-      <c r="D16" s="105" t="s">
-        <v>75</v>
-      </c>
-      <c r="E16" s="104" t="s">
-        <v>76</v>
-      </c>
-      <c r="F16" s="104"/>
-      <c r="G16" s="104"/>
-      <c r="H16" s="103" t="s">
+      <c r="F16" s="103"/>
+      <c r="G16" s="103"/>
+      <c r="H16" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="I16" s="104" t="s">
+      <c r="I16" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="106" t="s">
+      <c r="J16" s="102" t="s">
+        <v>52</v>
+      </c>
+      <c r="K16" s="22" t="s">
         <v>53</v>
-      </c>
-      <c r="K16" s="22" t="s">
-        <v>54</v>
       </c>
       <c r="L16" s="37">
         <v>0.11774014693384624</v>
@@ -10352,26 +10380,26 @@
       <c r="U16" s="24"/>
       <c r="V16" s="24"/>
       <c r="W16" s="25"/>
-      <c r="X16" s="111"/>
-      <c r="Y16" s="130"/>
-      <c r="Z16" s="116"/>
-      <c r="AA16" s="117" t="s">
-        <v>77</v>
+      <c r="X16" s="91"/>
+      <c r="Y16" s="92"/>
+      <c r="Z16" s="110"/>
+      <c r="AA16" s="118" t="s">
+        <v>74</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="14.45">
-      <c r="A17" s="92"/>
-      <c r="B17" s="123"/>
-      <c r="C17" s="123"/>
-      <c r="D17" s="105"/>
-      <c r="E17" s="104"/>
-      <c r="F17" s="104"/>
-      <c r="G17" s="104"/>
-      <c r="H17" s="103"/>
-      <c r="I17" s="104"/>
-      <c r="J17" s="106"/>
+    <row r="17" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="104"/>
+      <c r="B17" s="90"/>
+      <c r="C17" s="90"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="103"/>
+      <c r="F17" s="103"/>
+      <c r="G17" s="103"/>
+      <c r="H17" s="106"/>
+      <c r="I17" s="103"/>
+      <c r="J17" s="102"/>
       <c r="K17" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L17" s="17">
         <v>-4.253311543933095E-2</v>
@@ -10403,38 +10431,38 @@
       <c r="U17" s="19"/>
       <c r="V17" s="19"/>
       <c r="W17" s="28"/>
-      <c r="X17" s="111"/>
-      <c r="Y17" s="131"/>
-      <c r="Z17" s="116"/>
-      <c r="AA17" s="118"/>
+      <c r="X17" s="91"/>
+      <c r="Y17" s="93"/>
+      <c r="Z17" s="110"/>
+      <c r="AA17" s="119"/>
     </row>
-    <row r="18" spans="1:27" ht="14.45">
-      <c r="A18" s="92"/>
-      <c r="B18" s="123" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" s="123" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" s="123" t="s">
-        <v>79</v>
-      </c>
-      <c r="E18" s="104" t="s">
+    <row r="18" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="104"/>
+      <c r="B18" s="90" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="90" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="90" t="s">
         <v>76</v>
       </c>
-      <c r="F18" s="104"/>
-      <c r="G18" s="104"/>
-      <c r="H18" s="103" t="s">
+      <c r="E18" s="103" t="s">
+        <v>73</v>
+      </c>
+      <c r="F18" s="103"/>
+      <c r="G18" s="103"/>
+      <c r="H18" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="I18" s="104" t="s">
-        <v>80</v>
-      </c>
-      <c r="J18" s="106" t="s">
+      <c r="I18" s="103" t="s">
+        <v>77</v>
+      </c>
+      <c r="J18" s="102" t="s">
+        <v>52</v>
+      </c>
+      <c r="K18" s="22" t="s">
         <v>53</v>
-      </c>
-      <c r="K18" s="22" t="s">
-        <v>54</v>
       </c>
       <c r="L18" s="47">
         <v>0.224</v>
@@ -10466,91 +10494,91 @@
       <c r="U18" s="47"/>
       <c r="V18" s="47"/>
       <c r="W18" s="47"/>
-      <c r="X18" s="135" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y18" s="135"/>
-      <c r="Z18" s="132">
+      <c r="X18" s="152" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y18" s="152"/>
+      <c r="Z18" s="149">
         <v>46108</v>
       </c>
-      <c r="AA18" s="134"/>
+      <c r="AA18" s="151"/>
     </row>
-    <row r="19" spans="1:27" ht="14.45">
-      <c r="A19" s="92"/>
-      <c r="B19" s="123"/>
-      <c r="C19" s="123"/>
-      <c r="D19" s="123"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="104"/>
-      <c r="G19" s="104"/>
-      <c r="H19" s="103"/>
-      <c r="I19" s="104"/>
-      <c r="J19" s="106"/>
+    <row r="19" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="104"/>
+      <c r="B19" s="90"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="90"/>
+      <c r="E19" s="103"/>
+      <c r="F19" s="103"/>
+      <c r="G19" s="103"/>
+      <c r="H19" s="106"/>
+      <c r="I19" s="103"/>
+      <c r="J19" s="102"/>
       <c r="K19" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="L19" s="87">
+        <v>55</v>
+      </c>
+      <c r="L19" s="168">
         <v>0.2598381666666667</v>
       </c>
-      <c r="M19" s="87">
+      <c r="M19" s="168">
         <v>0.3838381666666667</v>
       </c>
-      <c r="N19" s="87">
+      <c r="N19" s="168">
         <v>1.1128381666666667</v>
       </c>
-      <c r="O19" s="87">
+      <c r="O19" s="168">
         <v>1.3223861666666668</v>
       </c>
-      <c r="P19" s="87">
+      <c r="P19" s="168">
         <v>1.6513861666666667</v>
       </c>
-      <c r="Q19" s="87">
+      <c r="Q19" s="168">
         <v>2.1303861666666668</v>
       </c>
-      <c r="R19" s="88">
+      <c r="R19" s="169">
         <v>2.6433861666666667</v>
       </c>
-      <c r="S19" s="88">
+      <c r="S19" s="169">
         <v>3.3972231666666666</v>
       </c>
-      <c r="T19" s="88">
+      <c r="T19" s="169">
         <v>4.5205241666666662</v>
       </c>
       <c r="U19" s="46"/>
       <c r="V19" s="46"/>
       <c r="W19" s="48"/>
-      <c r="X19" s="135"/>
-      <c r="Y19" s="135"/>
-      <c r="Z19" s="133"/>
-      <c r="AA19" s="134"/>
+      <c r="X19" s="152"/>
+      <c r="Y19" s="152"/>
+      <c r="Z19" s="150"/>
+      <c r="AA19" s="151"/>
     </row>
-    <row r="20" spans="1:27" ht="14.45">
-      <c r="A20" s="92"/>
-      <c r="B20" s="123" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" s="123" t="s">
-        <v>65</v>
-      </c>
-      <c r="D20" s="105" t="s">
-        <v>83</v>
-      </c>
-      <c r="E20" s="104" t="s">
-        <v>76</v>
-      </c>
-      <c r="F20" s="104"/>
-      <c r="G20" s="104"/>
-      <c r="H20" s="103" t="s">
+    <row r="20" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="104"/>
+      <c r="B20" s="90" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="90" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="87" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" s="103" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" s="103"/>
+      <c r="G20" s="103"/>
+      <c r="H20" s="106" t="s">
+        <v>51</v>
+      </c>
+      <c r="I20" s="103" t="s">
+        <v>33</v>
+      </c>
+      <c r="J20" s="102" t="s">
         <v>52</v>
       </c>
-      <c r="I20" s="104" t="s">
-        <v>33</v>
-      </c>
-      <c r="J20" s="106" t="s">
+      <c r="K20" s="22" t="s">
         <v>53</v>
-      </c>
-      <c r="K20" s="22" t="s">
-        <v>54</v>
       </c>
       <c r="L20" s="35">
         <v>0.28399999999999997</v>
@@ -10582,30 +10610,30 @@
       <c r="U20" s="18"/>
       <c r="V20" s="18"/>
       <c r="W20" s="27"/>
-      <c r="X20" s="167" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y20" s="169" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z20" s="95"/>
-      <c r="AA20" s="153" t="s">
-        <v>86</v>
+      <c r="X20" s="166" t="s">
+        <v>139</v>
+      </c>
+      <c r="Y20" s="96" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z20" s="148"/>
+      <c r="AA20" s="120" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="15" thickBot="1">
-      <c r="A21" s="92"/>
-      <c r="B21" s="123"/>
-      <c r="C21" s="123"/>
-      <c r="D21" s="105"/>
-      <c r="E21" s="104"/>
-      <c r="F21" s="104"/>
-      <c r="G21" s="104"/>
-      <c r="H21" s="103"/>
-      <c r="I21" s="104"/>
-      <c r="J21" s="106"/>
+    <row r="21" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="104"/>
+      <c r="B21" s="90"/>
+      <c r="C21" s="90"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="103"/>
+      <c r="F21" s="103"/>
+      <c r="G21" s="103"/>
+      <c r="H21" s="106"/>
+      <c r="I21" s="103"/>
+      <c r="J21" s="102"/>
       <c r="K21" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L21" s="19">
         <v>0.27400000000000002</v>
@@ -10637,40 +10665,40 @@
       <c r="U21" s="29"/>
       <c r="V21" s="29"/>
       <c r="W21" s="30"/>
-      <c r="X21" s="168"/>
-      <c r="Y21" s="170"/>
-      <c r="Z21" s="94"/>
-      <c r="AA21" s="153"/>
+      <c r="X21" s="167"/>
+      <c r="Y21" s="97"/>
+      <c r="Z21" s="114"/>
+      <c r="AA21" s="120"/>
     </row>
-    <row r="22" spans="1:27" ht="14.45">
-      <c r="A22" s="92" t="s">
+    <row r="22" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="104" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="123" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" s="124" t="s">
-        <v>88</v>
-      </c>
-      <c r="D22" s="123" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" s="104">
+      <c r="B22" s="90" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" s="117" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" s="90" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" s="103">
         <v>90</v>
       </c>
-      <c r="F22" s="104"/>
-      <c r="G22" s="104"/>
-      <c r="H22" s="103" t="s">
+      <c r="F22" s="103"/>
+      <c r="G22" s="103"/>
+      <c r="H22" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="104" t="s">
+      <c r="I22" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="J22" s="106" t="s">
+      <c r="J22" s="102" t="s">
+        <v>52</v>
+      </c>
+      <c r="K22" s="22" t="s">
         <v>53</v>
-      </c>
-      <c r="K22" s="22" t="s">
-        <v>54</v>
       </c>
       <c r="L22" s="35">
         <v>0.9</v>
@@ -10708,26 +10736,26 @@
       <c r="W22" s="27">
         <v>0.9</v>
       </c>
-      <c r="X22" s="171"/>
-      <c r="Y22" s="130"/>
-      <c r="Z22" s="115">
+      <c r="X22" s="100"/>
+      <c r="Y22" s="92"/>
+      <c r="Z22" s="109">
         <v>46257</v>
       </c>
-      <c r="AA22" s="113"/>
+      <c r="AA22" s="156"/>
     </row>
-    <row r="23" spans="1:27" ht="15" thickBot="1">
-      <c r="A23" s="93"/>
-      <c r="B23" s="123"/>
-      <c r="C23" s="124"/>
-      <c r="D23" s="123"/>
-      <c r="E23" s="104"/>
-      <c r="F23" s="104"/>
-      <c r="G23" s="104"/>
-      <c r="H23" s="103"/>
-      <c r="I23" s="104"/>
-      <c r="J23" s="106"/>
+    <row r="23" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="163"/>
+      <c r="B23" s="90"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="90"/>
+      <c r="E23" s="103"/>
+      <c r="F23" s="103"/>
+      <c r="G23" s="103"/>
+      <c r="H23" s="106"/>
+      <c r="I23" s="103"/>
+      <c r="J23" s="102"/>
       <c r="K23" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L23" s="54">
         <v>0.81</v>
@@ -10759,154 +10787,154 @@
       <c r="U23" s="29"/>
       <c r="V23" s="29"/>
       <c r="W23" s="30"/>
-      <c r="X23" s="110"/>
-      <c r="Y23" s="131"/>
-      <c r="Z23" s="116"/>
-      <c r="AA23" s="114"/>
+      <c r="X23" s="101"/>
+      <c r="Y23" s="93"/>
+      <c r="Z23" s="110"/>
+      <c r="AA23" s="157"/>
     </row>
-    <row r="24" spans="1:27" ht="14.45">
-      <c r="A24" s="90" t="s">
+    <row r="24" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="138" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="123" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" s="124" t="s">
-        <v>91</v>
-      </c>
-      <c r="D24" s="105" t="s">
-        <v>92</v>
-      </c>
-      <c r="E24" s="104" t="s">
-        <v>93</v>
-      </c>
-      <c r="F24" s="104" t="s">
-        <v>93</v>
-      </c>
-      <c r="G24" s="104" t="s">
-        <v>93</v>
-      </c>
-      <c r="H24" s="103" t="s">
+      <c r="B24" s="90" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="117" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" s="87" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="F24" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="G24" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="H24" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="104" t="s">
+      <c r="I24" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="J24" s="102" t="s">
+      <c r="J24" s="115" t="s">
         <v>34</v>
       </c>
       <c r="K24" s="22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L24" s="35"/>
-      <c r="M24" s="35"/>
+      <c r="M24" s="172"/>
       <c r="N24" s="37">
         <v>0.104</v>
       </c>
       <c r="O24" s="21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="P24" s="21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="Q24" s="37">
         <v>0.11799999999999999</v>
       </c>
       <c r="R24" s="21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="S24" s="21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="T24" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="U24" s="21"/>
+        <v>88</v>
+      </c>
+      <c r="U24" s="174"/>
       <c r="V24" s="21"/>
       <c r="W24" s="38"/>
-      <c r="X24" s="109"/>
-      <c r="Y24" s="100"/>
-      <c r="Z24" s="94"/>
-      <c r="AA24" s="117" t="s">
-        <v>95</v>
+      <c r="X24" s="132"/>
+      <c r="Y24" s="147"/>
+      <c r="Z24" s="114"/>
+      <c r="AA24" s="118" t="s">
+        <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="15" thickBot="1">
-      <c r="A25" s="91"/>
-      <c r="B25" s="123"/>
-      <c r="C25" s="124"/>
-      <c r="D25" s="105"/>
-      <c r="E25" s="104"/>
-      <c r="F25" s="104"/>
-      <c r="G25" s="104"/>
-      <c r="H25" s="103"/>
-      <c r="I25" s="104"/>
-      <c r="J25" s="102"/>
+    <row r="25" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="162"/>
+      <c r="B25" s="90"/>
+      <c r="C25" s="117"/>
+      <c r="D25" s="87"/>
+      <c r="E25" s="103"/>
+      <c r="F25" s="103"/>
+      <c r="G25" s="103"/>
+      <c r="H25" s="106"/>
+      <c r="I25" s="103"/>
+      <c r="J25" s="115"/>
       <c r="K25" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L25" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="M25" s="21" t="s">
-        <v>94</v>
+        <v>88</v>
+      </c>
+      <c r="M25" s="173" t="s">
+        <v>88</v>
       </c>
       <c r="N25" s="50">
         <v>0.115</v>
       </c>
       <c r="O25" s="21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="P25" s="21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="Q25" s="17">
         <v>0.12</v>
       </c>
       <c r="R25" s="21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="S25" s="21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="T25" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="U25" s="21"/>
+        <v>88</v>
+      </c>
+      <c r="U25" s="174"/>
       <c r="V25" s="21"/>
       <c r="W25" s="55"/>
-      <c r="X25" s="110"/>
-      <c r="Y25" s="101"/>
-      <c r="Z25" s="95"/>
-      <c r="AA25" s="118"/>
+      <c r="X25" s="101"/>
+      <c r="Y25" s="108"/>
+      <c r="Z25" s="148"/>
+      <c r="AA25" s="119"/>
     </row>
-    <row r="26" spans="1:27" ht="14.45">
-      <c r="A26" s="91"/>
-      <c r="B26" s="125" t="s">
-        <v>96</v>
-      </c>
-      <c r="C26" s="126" t="s">
+    <row r="26" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="162"/>
+      <c r="B26" s="88" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="155" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="87" t="s">
         <v>91</v>
       </c>
-      <c r="D26" s="105" t="s">
-        <v>97</v>
-      </c>
-      <c r="E26" s="104">
+      <c r="E26" s="103">
         <v>34</v>
       </c>
-      <c r="F26" s="112"/>
-      <c r="G26" s="112"/>
-      <c r="H26" s="103" t="s">
+      <c r="F26" s="153"/>
+      <c r="G26" s="153"/>
+      <c r="H26" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="I26" s="104" t="s">
+      <c r="I26" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="J26" s="106" t="s">
+      <c r="J26" s="102" t="s">
+        <v>52</v>
+      </c>
+      <c r="K26" s="22" t="s">
         <v>53</v>
-      </c>
-      <c r="K26" s="22" t="s">
-        <v>54</v>
       </c>
       <c r="L26" s="35">
         <v>0.34</v>
@@ -10938,26 +10966,26 @@
       <c r="U26" s="24"/>
       <c r="V26" s="24"/>
       <c r="W26" s="25"/>
-      <c r="X26" s="111"/>
-      <c r="Y26" s="131"/>
-      <c r="Z26" s="116"/>
-      <c r="AA26" s="117" t="s">
-        <v>98</v>
+      <c r="X26" s="91"/>
+      <c r="Y26" s="93"/>
+      <c r="Z26" s="110"/>
+      <c r="AA26" s="118" t="s">
+        <v>92</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="15" thickBot="1">
-      <c r="A27" s="91"/>
-      <c r="B27" s="125"/>
-      <c r="C27" s="126"/>
-      <c r="D27" s="105"/>
-      <c r="E27" s="104"/>
-      <c r="F27" s="112"/>
-      <c r="G27" s="112"/>
-      <c r="H27" s="103"/>
-      <c r="I27" s="104"/>
-      <c r="J27" s="106"/>
+    <row r="27" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="162"/>
+      <c r="B27" s="88"/>
+      <c r="C27" s="155"/>
+      <c r="D27" s="87"/>
+      <c r="E27" s="103"/>
+      <c r="F27" s="153"/>
+      <c r="G27" s="153"/>
+      <c r="H27" s="106"/>
+      <c r="I27" s="103"/>
+      <c r="J27" s="102"/>
       <c r="K27" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L27" s="78">
         <v>0.318</v>
@@ -10989,38 +11017,38 @@
       <c r="U27" s="19"/>
       <c r="V27" s="19"/>
       <c r="W27" s="28"/>
-      <c r="X27" s="111"/>
-      <c r="Y27" s="131"/>
-      <c r="Z27" s="116"/>
-      <c r="AA27" s="118"/>
+      <c r="X27" s="91"/>
+      <c r="Y27" s="93"/>
+      <c r="Z27" s="110"/>
+      <c r="AA27" s="119"/>
     </row>
-    <row r="28" spans="1:27" ht="14.45">
-      <c r="A28" s="91"/>
-      <c r="B28" s="105" t="s">
-        <v>99</v>
-      </c>
-      <c r="C28" s="123" t="s">
-        <v>74</v>
-      </c>
-      <c r="D28" s="105" t="s">
-        <v>100</v>
-      </c>
-      <c r="E28" s="104" t="s">
-        <v>76</v>
-      </c>
-      <c r="F28" s="104"/>
-      <c r="G28" s="104"/>
-      <c r="H28" s="103" t="s">
+    <row r="28" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="162"/>
+      <c r="B28" s="87" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" s="90" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" s="87" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28" s="103" t="s">
+        <v>73</v>
+      </c>
+      <c r="F28" s="103"/>
+      <c r="G28" s="103"/>
+      <c r="H28" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="I28" s="104" t="s">
+      <c r="I28" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="J28" s="106" t="s">
+      <c r="J28" s="102" t="s">
+        <v>52</v>
+      </c>
+      <c r="K28" s="22" t="s">
         <v>53</v>
-      </c>
-      <c r="K28" s="22" t="s">
-        <v>54</v>
       </c>
       <c r="L28" s="37" vm="1">
         <v>3.6951550944796852E-2</v>
@@ -11052,28 +11080,28 @@
       <c r="U28" s="24"/>
       <c r="V28" s="24"/>
       <c r="W28" s="25"/>
-      <c r="X28" s="159" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y28" s="96"/>
-      <c r="Z28" s="94"/>
-      <c r="AA28" s="154" t="s">
-        <v>102</v>
+      <c r="X28" s="98" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y28" s="94"/>
+      <c r="Z28" s="114"/>
+      <c r="AA28" s="123" t="s">
+        <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="15" thickBot="1">
-      <c r="A29" s="91"/>
-      <c r="B29" s="105"/>
-      <c r="C29" s="123"/>
-      <c r="D29" s="105"/>
-      <c r="E29" s="104"/>
-      <c r="F29" s="104"/>
-      <c r="G29" s="104"/>
-      <c r="H29" s="103"/>
-      <c r="I29" s="104"/>
-      <c r="J29" s="106"/>
+    <row r="29" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="162"/>
+      <c r="B29" s="87"/>
+      <c r="C29" s="90"/>
+      <c r="D29" s="87"/>
+      <c r="E29" s="103"/>
+      <c r="F29" s="103"/>
+      <c r="G29" s="103"/>
+      <c r="H29" s="106"/>
+      <c r="I29" s="103"/>
+      <c r="J29" s="102"/>
       <c r="K29" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L29" s="17" vm="2">
         <v>-0.21537837470975407</v>
@@ -11105,36 +11133,36 @@
       <c r="U29" s="19"/>
       <c r="V29" s="19"/>
       <c r="W29" s="28"/>
-      <c r="X29" s="160"/>
-      <c r="Y29" s="97"/>
-      <c r="Z29" s="95"/>
-      <c r="AA29" s="155"/>
+      <c r="X29" s="99"/>
+      <c r="Y29" s="95"/>
+      <c r="Z29" s="148"/>
+      <c r="AA29" s="124"/>
     </row>
-    <row r="30" spans="1:27" ht="14.45">
-      <c r="A30" s="91"/>
-      <c r="B30" s="105"/>
-      <c r="C30" s="123" t="s">
-        <v>74</v>
-      </c>
-      <c r="D30" s="105" t="s">
-        <v>103</v>
-      </c>
-      <c r="E30" s="104" t="s">
-        <v>76</v>
-      </c>
-      <c r="F30" s="104"/>
-      <c r="G30" s="104"/>
-      <c r="H30" s="103" t="s">
+    <row r="30" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="162"/>
+      <c r="B30" s="87"/>
+      <c r="C30" s="90" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" s="87" t="s">
+        <v>96</v>
+      </c>
+      <c r="E30" s="103" t="s">
+        <v>73</v>
+      </c>
+      <c r="F30" s="103"/>
+      <c r="G30" s="103"/>
+      <c r="H30" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="I30" s="104" t="s">
+      <c r="I30" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="J30" s="106" t="s">
+      <c r="J30" s="102" t="s">
+        <v>52</v>
+      </c>
+      <c r="K30" s="22" t="s">
         <v>53</v>
-      </c>
-      <c r="K30" s="22" t="s">
-        <v>54</v>
       </c>
       <c r="L30" s="37">
         <v>0.35899999999999999</v>
@@ -11166,24 +11194,24 @@
       <c r="U30" s="24"/>
       <c r="V30" s="24"/>
       <c r="W30" s="25"/>
-      <c r="X30" s="159"/>
-      <c r="Y30" s="100"/>
-      <c r="Z30" s="94"/>
-      <c r="AA30" s="107"/>
+      <c r="X30" s="98"/>
+      <c r="Y30" s="147"/>
+      <c r="Z30" s="114"/>
+      <c r="AA30" s="160"/>
     </row>
-    <row r="31" spans="1:27" ht="14.45">
-      <c r="A31" s="91"/>
-      <c r="B31" s="105"/>
-      <c r="C31" s="123"/>
-      <c r="D31" s="105"/>
-      <c r="E31" s="104"/>
-      <c r="F31" s="104"/>
-      <c r="G31" s="104"/>
-      <c r="H31" s="103"/>
-      <c r="I31" s="104"/>
-      <c r="J31" s="106"/>
+    <row r="31" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="162"/>
+      <c r="B31" s="87"/>
+      <c r="C31" s="90"/>
+      <c r="D31" s="87"/>
+      <c r="E31" s="103"/>
+      <c r="F31" s="103"/>
+      <c r="G31" s="103"/>
+      <c r="H31" s="106"/>
+      <c r="I31" s="103"/>
+      <c r="J31" s="102"/>
       <c r="K31" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L31" s="17">
         <v>0.32500000000000001</v>
@@ -11215,38 +11243,38 @@
       <c r="U31" s="44"/>
       <c r="V31" s="44"/>
       <c r="W31" s="45"/>
-      <c r="X31" s="160"/>
-      <c r="Y31" s="101"/>
-      <c r="Z31" s="95"/>
-      <c r="AA31" s="108"/>
+      <c r="X31" s="99"/>
+      <c r="Y31" s="108"/>
+      <c r="Z31" s="148"/>
+      <c r="AA31" s="161"/>
     </row>
-    <row r="32" spans="1:27" ht="14.45">
-      <c r="A32" s="91"/>
-      <c r="B32" s="123" t="s">
-        <v>104</v>
-      </c>
-      <c r="C32" s="124" t="s">
-        <v>65</v>
-      </c>
-      <c r="D32" s="105" t="s">
-        <v>105</v>
-      </c>
-      <c r="E32" s="104" t="s">
-        <v>76</v>
-      </c>
-      <c r="F32" s="104"/>
-      <c r="G32" s="104"/>
-      <c r="H32" s="103" t="s">
+    <row r="32" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="162"/>
+      <c r="B32" s="90" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" s="117" t="s">
+        <v>64</v>
+      </c>
+      <c r="D32" s="87" t="s">
+        <v>98</v>
+      </c>
+      <c r="E32" s="103" t="s">
+        <v>73</v>
+      </c>
+      <c r="F32" s="103"/>
+      <c r="G32" s="103"/>
+      <c r="H32" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="I32" s="104" t="s">
-        <v>80</v>
-      </c>
-      <c r="J32" s="106" t="s">
+      <c r="I32" s="103" t="s">
+        <v>77</v>
+      </c>
+      <c r="J32" s="102" t="s">
+        <v>52</v>
+      </c>
+      <c r="K32" s="22" t="s">
         <v>53</v>
-      </c>
-      <c r="K32" s="22" t="s">
-        <v>54</v>
       </c>
       <c r="L32" s="41">
         <v>8.6903037999999988</v>
@@ -11278,30 +11306,30 @@
       <c r="U32" s="8"/>
       <c r="V32" s="8"/>
       <c r="W32" s="33"/>
-      <c r="X32" s="98" t="s">
-        <v>106</v>
-      </c>
-      <c r="Y32" s="96" t="s">
-        <v>107</v>
-      </c>
-      <c r="Z32" s="94"/>
-      <c r="AA32" s="117" t="s">
-        <v>108</v>
+      <c r="X32" s="164" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y32" s="94" t="s">
+        <v>137</v>
+      </c>
+      <c r="Z32" s="114"/>
+      <c r="AA32" s="118" t="s">
+        <v>99</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="15" thickBot="1">
-      <c r="A33" s="91"/>
-      <c r="B33" s="123"/>
-      <c r="C33" s="124"/>
-      <c r="D33" s="105"/>
-      <c r="E33" s="104"/>
-      <c r="F33" s="104"/>
-      <c r="G33" s="104"/>
-      <c r="H33" s="103"/>
-      <c r="I33" s="104"/>
-      <c r="J33" s="106"/>
+    <row r="33" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="162"/>
+      <c r="B33" s="90"/>
+      <c r="C33" s="117"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="103"/>
+      <c r="F33" s="103"/>
+      <c r="G33" s="103"/>
+      <c r="H33" s="106"/>
+      <c r="I33" s="103"/>
+      <c r="J33" s="102"/>
       <c r="K33" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L33" s="42">
         <v>4.05</v>
@@ -11333,40 +11361,40 @@
       <c r="U33" s="31"/>
       <c r="V33" s="31"/>
       <c r="W33" s="32"/>
-      <c r="X33" s="99"/>
-      <c r="Y33" s="97"/>
-      <c r="Z33" s="95"/>
-      <c r="AA33" s="118"/>
+      <c r="X33" s="165"/>
+      <c r="Y33" s="95"/>
+      <c r="Z33" s="148"/>
+      <c r="AA33" s="119"/>
     </row>
-    <row r="34" spans="1:29" ht="14.45">
-      <c r="A34" s="92" t="s">
+    <row r="34" spans="1:29" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="104" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="144" t="s">
+      <c r="B34" s="143" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="123" t="s">
-        <v>88</v>
-      </c>
-      <c r="D34" s="105" t="s">
+      <c r="C34" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="D34" s="87" t="s">
         <v>31</v>
       </c>
-      <c r="E34" s="104">
+      <c r="E34" s="103">
         <v>90</v>
       </c>
-      <c r="F34" s="104"/>
-      <c r="G34" s="104"/>
-      <c r="H34" s="103" t="s">
+      <c r="F34" s="103"/>
+      <c r="G34" s="103"/>
+      <c r="H34" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="I34" s="104" t="s">
+      <c r="I34" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="J34" s="102" t="s">
+      <c r="J34" s="115" t="s">
         <v>34</v>
       </c>
       <c r="K34" s="22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L34" s="35"/>
       <c r="M34" s="35"/>
@@ -11388,52 +11416,52 @@
       <c r="W34" s="25">
         <v>0.9</v>
       </c>
-      <c r="X34" s="111"/>
-      <c r="Y34" s="131" t="s">
-        <v>109</v>
-      </c>
-      <c r="Z34" s="116"/>
-      <c r="AA34" s="117" t="s">
-        <v>110</v>
+      <c r="X34" s="91"/>
+      <c r="Y34" s="93" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z34" s="110"/>
+      <c r="AA34" s="118" t="s">
+        <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="14.45">
-      <c r="A35" s="92"/>
-      <c r="B35" s="144"/>
-      <c r="C35" s="123"/>
-      <c r="D35" s="105"/>
-      <c r="E35" s="104"/>
-      <c r="F35" s="104"/>
-      <c r="G35" s="104"/>
-      <c r="H35" s="103"/>
-      <c r="I35" s="104"/>
-      <c r="J35" s="102"/>
+    <row r="35" spans="1:29" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="104"/>
+      <c r="B35" s="143"/>
+      <c r="C35" s="90"/>
+      <c r="D35" s="87"/>
+      <c r="E35" s="103"/>
+      <c r="F35" s="103"/>
+      <c r="G35" s="103"/>
+      <c r="H35" s="106"/>
+      <c r="I35" s="103"/>
+      <c r="J35" s="115"/>
       <c r="K35" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L35" s="21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="M35" s="21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="N35" s="19">
         <v>1</v>
       </c>
       <c r="O35" s="21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="P35" s="21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="Q35" s="19">
         <v>0.96199999999999997</v>
       </c>
       <c r="R35" s="21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="S35" s="21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="T35" s="19">
         <v>0.91300000000000003</v>
@@ -11441,38 +11469,38 @@
       <c r="U35" s="19"/>
       <c r="V35" s="19"/>
       <c r="W35" s="28"/>
-      <c r="X35" s="111"/>
-      <c r="Y35" s="131"/>
-      <c r="Z35" s="116"/>
-      <c r="AA35" s="118"/>
+      <c r="X35" s="91"/>
+      <c r="Y35" s="93"/>
+      <c r="Z35" s="110"/>
+      <c r="AA35" s="119"/>
     </row>
-    <row r="36" spans="1:29" ht="14.45">
-      <c r="A36" s="92"/>
-      <c r="B36" s="144" t="s">
+    <row r="36" spans="1:29" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="104"/>
+      <c r="B36" s="143" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="123" t="s">
-        <v>111</v>
-      </c>
-      <c r="D36" s="105" t="s">
+      <c r="C36" s="90" t="s">
+        <v>101</v>
+      </c>
+      <c r="D36" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="E36" s="104">
+      <c r="E36" s="103">
         <v>83</v>
       </c>
-      <c r="F36" s="104"/>
-      <c r="G36" s="104"/>
-      <c r="H36" s="103" t="s">
+      <c r="F36" s="103"/>
+      <c r="G36" s="103"/>
+      <c r="H36" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="I36" s="104" t="s">
+      <c r="I36" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="J36" s="161" t="s">
+      <c r="J36" s="116" t="s">
         <v>38</v>
       </c>
       <c r="K36" s="22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L36" s="35"/>
       <c r="M36" s="35"/>
@@ -11490,98 +11518,98 @@
       <c r="U36" s="18"/>
       <c r="V36" s="18"/>
       <c r="W36" s="27"/>
-      <c r="X36" s="111" t="s">
-        <v>112</v>
-      </c>
-      <c r="Y36" s="130" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z36" s="116"/>
-      <c r="AA36" s="117" t="s">
-        <v>114</v>
+      <c r="X36" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y36" s="92" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z36" s="110"/>
+      <c r="AA36" s="118" t="s">
+        <v>104</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="14.45">
-      <c r="A37" s="92"/>
-      <c r="B37" s="144"/>
-      <c r="C37" s="123"/>
-      <c r="D37" s="105"/>
-      <c r="E37" s="104"/>
-      <c r="F37" s="104"/>
-      <c r="G37" s="104"/>
-      <c r="H37" s="103"/>
-      <c r="I37" s="104"/>
-      <c r="J37" s="161"/>
+    <row r="37" spans="1:29" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A37" s="104"/>
+      <c r="B37" s="143"/>
+      <c r="C37" s="90"/>
+      <c r="D37" s="87"/>
+      <c r="E37" s="103"/>
+      <c r="F37" s="103"/>
+      <c r="G37" s="103"/>
+      <c r="H37" s="106"/>
+      <c r="I37" s="103"/>
+      <c r="J37" s="116"/>
       <c r="K37" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L37" s="21" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="M37" s="21" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="N37" s="21" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="O37" s="19">
         <v>0.79</v>
       </c>
       <c r="P37" s="21" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="Q37" s="19">
         <v>0.79</v>
       </c>
       <c r="R37" s="21" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="S37" s="56"/>
       <c r="T37" s="21" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="U37" s="56"/>
       <c r="V37" s="56"/>
       <c r="W37" s="57"/>
-      <c r="X37" s="109"/>
-      <c r="Y37" s="96"/>
-      <c r="Z37" s="94"/>
-      <c r="AA37" s="153"/>
+      <c r="X37" s="132"/>
+      <c r="Y37" s="94"/>
+      <c r="Z37" s="114"/>
+      <c r="AA37" s="120"/>
     </row>
-    <row r="38" spans="1:29" s="5" customFormat="1" ht="20.45" customHeight="1">
-      <c r="A38" s="147"/>
-      <c r="B38" s="147"/>
-      <c r="C38" s="147"/>
-      <c r="D38" s="147"/>
-      <c r="E38" s="147"/>
-      <c r="F38" s="147"/>
-      <c r="G38" s="147"/>
-      <c r="H38" s="147"/>
-      <c r="I38" s="147"/>
-      <c r="J38" s="147"/>
-      <c r="K38" s="147"/>
-      <c r="L38" s="147"/>
-      <c r="M38" s="147"/>
-      <c r="N38" s="147"/>
-      <c r="O38" s="147"/>
-      <c r="P38" s="148"/>
-      <c r="Q38" s="148"/>
-      <c r="R38" s="148"/>
-      <c r="S38" s="148"/>
-      <c r="T38" s="148"/>
-      <c r="U38" s="148"/>
-      <c r="V38" s="148"/>
-      <c r="W38" s="148"/>
-      <c r="X38" s="148"/>
-      <c r="Y38" s="148"/>
-      <c r="Z38" s="148"/>
-      <c r="AA38" s="148"/>
+    <row r="38" spans="1:29" s="5" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="133"/>
+      <c r="B38" s="133"/>
+      <c r="C38" s="133"/>
+      <c r="D38" s="133"/>
+      <c r="E38" s="133"/>
+      <c r="F38" s="133"/>
+      <c r="G38" s="133"/>
+      <c r="H38" s="133"/>
+      <c r="I38" s="133"/>
+      <c r="J38" s="133"/>
+      <c r="K38" s="133"/>
+      <c r="L38" s="133"/>
+      <c r="M38" s="133"/>
+      <c r="N38" s="133"/>
+      <c r="O38" s="133"/>
+      <c r="P38" s="134"/>
+      <c r="Q38" s="134"/>
+      <c r="R38" s="134"/>
+      <c r="S38" s="134"/>
+      <c r="T38" s="134"/>
+      <c r="U38" s="134"/>
+      <c r="V38" s="134"/>
+      <c r="W38" s="134"/>
+      <c r="X38" s="134"/>
+      <c r="Y38" s="134"/>
+      <c r="Z38" s="134"/>
+      <c r="AA38" s="134"/>
     </row>
-    <row r="39" spans="1:29" s="5" customFormat="1" ht="20.45" customHeight="1">
-      <c r="A39" s="149" t="s">
-        <v>116</v>
-      </c>
-      <c r="B39" s="149"/>
+    <row r="39" spans="1:29" s="5" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="136" t="s">
+        <v>106</v>
+      </c>
+      <c r="B39" s="136"/>
       <c r="C39" s="58"/>
       <c r="D39"/>
       <c r="E39"/>
@@ -11608,12 +11636,12 @@
       <c r="Z39"/>
       <c r="AA39" s="13"/>
     </row>
-    <row r="40" spans="1:29" ht="20.45" customHeight="1">
+    <row r="40" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="43" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>3</v>
@@ -11622,13 +11650,13 @@
         <v>4</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="H40" s="10" t="s">
         <v>8</v>
@@ -11649,7 +11677,7 @@
         <v>13</v>
       </c>
       <c r="N40" s="10" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="O40" s="10" t="s">
         <v>15</v>
@@ -11658,7 +11686,7 @@
         <v>16</v>
       </c>
       <c r="Q40" s="10" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="R40" s="10" t="s">
         <v>18</v>
@@ -11679,51 +11707,51 @@
         <v>23</v>
       </c>
       <c r="X40" s="60" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y40" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="Y40" s="10" t="s">
+      <c r="Z40" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="Z40" s="10" t="s">
+      <c r="AA40" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="AA40" s="16" t="s">
+    </row>
+    <row r="41" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="137" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="41" spans="1:29" ht="20.45" customHeight="1">
-      <c r="A41" s="150" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="151" t="s">
-        <v>123</v>
-      </c>
-      <c r="C41" s="152" t="s">
-        <v>50</v>
-      </c>
-      <c r="D41" s="143" t="s">
-        <v>124</v>
-      </c>
-      <c r="E41" s="121" t="s">
-        <v>93</v>
-      </c>
-      <c r="F41" s="121" t="s">
-        <v>93</v>
-      </c>
-      <c r="G41" s="121" t="s">
-        <v>93</v>
-      </c>
-      <c r="H41" s="122" t="s">
+      <c r="B41" s="140" t="s">
+        <v>113</v>
+      </c>
+      <c r="C41" s="141" t="s">
+        <v>49</v>
+      </c>
+      <c r="D41" s="142" t="s">
+        <v>114</v>
+      </c>
+      <c r="E41" s="135" t="s">
+        <v>87</v>
+      </c>
+      <c r="F41" s="135" t="s">
+        <v>87</v>
+      </c>
+      <c r="G41" s="135" t="s">
+        <v>87</v>
+      </c>
+      <c r="H41" s="154" t="s">
+        <v>51</v>
+      </c>
+      <c r="I41" s="135" t="s">
+        <v>33</v>
+      </c>
+      <c r="J41" s="144" t="s">
         <v>52</v>
       </c>
-      <c r="I41" s="121" t="s">
-        <v>33</v>
-      </c>
-      <c r="J41" s="138" t="s">
+      <c r="K41" s="61" t="s">
         <v>53</v>
-      </c>
-      <c r="K41" s="61" t="s">
-        <v>54</v>
       </c>
       <c r="L41" s="76">
         <v>1.9099999999999999E-2</v>
@@ -11761,27 +11789,27 @@
       <c r="W41" s="63">
         <v>3.32E-2</v>
       </c>
-      <c r="X41" s="158"/>
-      <c r="Y41" s="128"/>
-      <c r="Z41" s="128"/>
-      <c r="AA41" s="118" t="s">
-        <v>123</v>
+      <c r="X41" s="131"/>
+      <c r="Y41" s="126"/>
+      <c r="Z41" s="126"/>
+      <c r="AA41" s="119" t="s">
+        <v>113</v>
       </c>
       <c r="AC41" s="12"/>
     </row>
-    <row r="42" spans="1:29" ht="20.45" customHeight="1">
-      <c r="A42" s="90"/>
-      <c r="B42" s="125"/>
-      <c r="C42" s="137"/>
-      <c r="D42" s="105"/>
-      <c r="E42" s="104"/>
-      <c r="F42" s="104"/>
-      <c r="G42" s="104"/>
-      <c r="H42" s="103"/>
-      <c r="I42" s="104"/>
-      <c r="J42" s="139"/>
+    <row r="42" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="138"/>
+      <c r="B42" s="88"/>
+      <c r="C42" s="89"/>
+      <c r="D42" s="87"/>
+      <c r="E42" s="103"/>
+      <c r="F42" s="103"/>
+      <c r="G42" s="103"/>
+      <c r="H42" s="106"/>
+      <c r="I42" s="103"/>
+      <c r="J42" s="122"/>
       <c r="K42" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L42" s="55">
         <v>9.1999999999999998E-3</v>
@@ -11813,44 +11841,44 @@
       <c r="U42" s="55"/>
       <c r="V42" s="55"/>
       <c r="W42" s="59"/>
-      <c r="X42" s="158"/>
-      <c r="Y42" s="128"/>
-      <c r="Z42" s="128"/>
-      <c r="AA42" s="145"/>
+      <c r="X42" s="131"/>
+      <c r="Y42" s="126"/>
+      <c r="Z42" s="126"/>
+      <c r="AA42" s="121"/>
     </row>
-    <row r="43" spans="1:29" ht="20.45" customHeight="1">
-      <c r="A43" s="136" t="s">
+    <row r="43" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="139" t="s">
         <v>26</v>
       </c>
-      <c r="B43" s="125" t="s">
-        <v>125</v>
-      </c>
-      <c r="C43" s="137" t="s">
-        <v>91</v>
-      </c>
-      <c r="D43" s="105" t="s">
-        <v>126</v>
-      </c>
-      <c r="E43" s="104" t="s">
-        <v>93</v>
-      </c>
-      <c r="F43" s="104" t="s">
-        <v>93</v>
-      </c>
-      <c r="G43" s="104" t="s">
-        <v>93</v>
-      </c>
-      <c r="H43" s="103" t="s">
+      <c r="B43" s="88" t="s">
+        <v>115</v>
+      </c>
+      <c r="C43" s="89" t="s">
+        <v>85</v>
+      </c>
+      <c r="D43" s="87" t="s">
+        <v>116</v>
+      </c>
+      <c r="E43" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="F43" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="G43" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="H43" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="I43" s="104" t="s">
+      <c r="I43" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="J43" s="102" t="s">
+      <c r="J43" s="115" t="s">
         <v>34</v>
       </c>
       <c r="K43" s="22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L43" s="35"/>
       <c r="M43" s="35"/>
@@ -11868,99 +11896,99 @@
       <c r="U43" s="35"/>
       <c r="V43" s="35"/>
       <c r="W43" s="38"/>
-      <c r="X43" s="146" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y43" s="141" t="s">
-        <v>128</v>
-      </c>
-      <c r="Z43" s="140"/>
-      <c r="AA43" s="156" t="s">
-        <v>129</v>
+      <c r="X43" s="125" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y43" s="127" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z43" s="128"/>
+      <c r="AA43" s="129" t="s">
+        <v>119</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="20.45" customHeight="1">
-      <c r="A44" s="136"/>
-      <c r="B44" s="125"/>
-      <c r="C44" s="137"/>
-      <c r="D44" s="105"/>
-      <c r="E44" s="104"/>
-      <c r="F44" s="104"/>
-      <c r="G44" s="104"/>
-      <c r="H44" s="103"/>
-      <c r="I44" s="112"/>
-      <c r="J44" s="102"/>
+    <row r="44" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="139"/>
+      <c r="B44" s="88"/>
+      <c r="C44" s="89"/>
+      <c r="D44" s="87"/>
+      <c r="E44" s="103"/>
+      <c r="F44" s="103"/>
+      <c r="G44" s="103"/>
+      <c r="H44" s="106"/>
+      <c r="I44" s="153"/>
+      <c r="J44" s="115"/>
       <c r="K44" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L44" s="21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="M44" s="21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="N44" s="17">
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="O44" s="21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="P44" s="21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="Q44" s="17">
         <v>0.04</v>
       </c>
       <c r="R44" s="21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="S44" s="21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="T44" s="55"/>
       <c r="U44" s="21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="V44" s="21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="W44" s="55"/>
-      <c r="X44" s="146"/>
-      <c r="Y44" s="141"/>
-      <c r="Z44" s="140"/>
-      <c r="AA44" s="156"/>
+      <c r="X44" s="125"/>
+      <c r="Y44" s="127"/>
+      <c r="Z44" s="128"/>
+      <c r="AA44" s="129"/>
     </row>
-    <row r="45" spans="1:29" ht="20.45" customHeight="1">
-      <c r="A45" s="136"/>
-      <c r="B45" s="125" t="s">
-        <v>130</v>
-      </c>
-      <c r="C45" s="137" t="s">
-        <v>91</v>
-      </c>
-      <c r="D45" s="105" t="s">
-        <v>131</v>
-      </c>
-      <c r="E45" s="104" t="s">
-        <v>93</v>
-      </c>
-      <c r="F45" s="104" t="s">
-        <v>93</v>
-      </c>
-      <c r="G45" s="104" t="s">
-        <v>93</v>
-      </c>
-      <c r="H45" s="103" t="s">
+    <row r="45" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="139"/>
+      <c r="B45" s="88" t="s">
+        <v>120</v>
+      </c>
+      <c r="C45" s="89" t="s">
+        <v>85</v>
+      </c>
+      <c r="D45" s="87" t="s">
+        <v>121</v>
+      </c>
+      <c r="E45" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="F45" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="G45" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="H45" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="I45" s="104" t="s">
+      <c r="I45" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="J45" s="139" t="s">
+      <c r="J45" s="122" t="s">
+        <v>52</v>
+      </c>
+      <c r="K45" s="22" t="s">
         <v>53</v>
-      </c>
-      <c r="K45" s="22" t="s">
-        <v>54</v>
       </c>
       <c r="L45" s="35">
         <v>0.4</v>
@@ -11992,30 +12020,30 @@
       <c r="U45" s="35"/>
       <c r="V45" s="35"/>
       <c r="W45" s="38"/>
-      <c r="X45" s="146"/>
-      <c r="Y45" s="141" t="s">
-        <v>132</v>
-      </c>
-      <c r="Z45" s="157">
+      <c r="X45" s="125"/>
+      <c r="Y45" s="127" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z45" s="130">
         <v>46188</v>
       </c>
-      <c r="AA45" s="145" t="s">
-        <v>130</v>
+      <c r="AA45" s="121" t="s">
+        <v>120</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="20.45" customHeight="1">
-      <c r="A46" s="136"/>
-      <c r="B46" s="125"/>
-      <c r="C46" s="137"/>
-      <c r="D46" s="105"/>
-      <c r="E46" s="104"/>
-      <c r="F46" s="104"/>
-      <c r="G46" s="104"/>
-      <c r="H46" s="103"/>
-      <c r="I46" s="104"/>
-      <c r="J46" s="139"/>
+    <row r="46" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="139"/>
+      <c r="B46" s="88"/>
+      <c r="C46" s="89"/>
+      <c r="D46" s="87"/>
+      <c r="E46" s="103"/>
+      <c r="F46" s="103"/>
+      <c r="G46" s="103"/>
+      <c r="H46" s="106"/>
+      <c r="I46" s="103"/>
+      <c r="J46" s="122"/>
       <c r="K46" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L46" s="19">
         <v>0.66</v>
@@ -12047,42 +12075,42 @@
       <c r="U46" s="19"/>
       <c r="V46" s="19"/>
       <c r="W46" s="28"/>
-      <c r="X46" s="146"/>
-      <c r="Y46" s="140"/>
-      <c r="Z46" s="140"/>
-      <c r="AA46" s="145"/>
+      <c r="X46" s="125"/>
+      <c r="Y46" s="128"/>
+      <c r="Z46" s="128"/>
+      <c r="AA46" s="121"/>
     </row>
-    <row r="47" spans="1:29" ht="20.45" customHeight="1">
-      <c r="A47" s="136"/>
-      <c r="B47" s="125" t="s">
-        <v>133</v>
-      </c>
-      <c r="C47" s="137" t="s">
-        <v>88</v>
-      </c>
-      <c r="D47" s="105" t="s">
-        <v>134</v>
-      </c>
-      <c r="E47" s="104" t="s">
-        <v>93</v>
-      </c>
-      <c r="F47" s="104" t="s">
-        <v>93</v>
-      </c>
-      <c r="G47" s="104" t="s">
-        <v>93</v>
-      </c>
-      <c r="H47" s="103" t="s">
+    <row r="47" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="139"/>
+      <c r="B47" s="88" t="s">
+        <v>123</v>
+      </c>
+      <c r="C47" s="89" t="s">
+        <v>82</v>
+      </c>
+      <c r="D47" s="87" t="s">
+        <v>124</v>
+      </c>
+      <c r="E47" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="F47" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="G47" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="H47" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="I47" s="104" t="s">
-        <v>80</v>
-      </c>
-      <c r="J47" s="139" t="s">
+      <c r="I47" s="103" t="s">
+        <v>77</v>
+      </c>
+      <c r="J47" s="122" t="s">
+        <v>52</v>
+      </c>
+      <c r="K47" s="22" t="s">
         <v>53</v>
-      </c>
-      <c r="K47" s="22" t="s">
-        <v>54</v>
       </c>
       <c r="L47" s="36">
         <v>5.5</v>
@@ -12120,26 +12148,26 @@
       <c r="W47" s="39">
         <v>67</v>
       </c>
-      <c r="X47" s="146"/>
-      <c r="Y47" s="140"/>
-      <c r="Z47" s="140"/>
-      <c r="AA47" s="105" t="s">
-        <v>135</v>
+      <c r="X47" s="125"/>
+      <c r="Y47" s="128"/>
+      <c r="Z47" s="128"/>
+      <c r="AA47" s="87" t="s">
+        <v>125</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="20.45" customHeight="1">
-      <c r="A48" s="136"/>
-      <c r="B48" s="125"/>
-      <c r="C48" s="137"/>
-      <c r="D48" s="105"/>
-      <c r="E48" s="104"/>
-      <c r="F48" s="104"/>
-      <c r="G48" s="104"/>
-      <c r="H48" s="103"/>
-      <c r="I48" s="104"/>
-      <c r="J48" s="139"/>
+    <row r="48" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="139"/>
+      <c r="B48" s="88"/>
+      <c r="C48" s="89"/>
+      <c r="D48" s="87"/>
+      <c r="E48" s="103"/>
+      <c r="F48" s="103"/>
+      <c r="G48" s="103"/>
+      <c r="H48" s="106"/>
+      <c r="I48" s="103"/>
+      <c r="J48" s="122"/>
       <c r="K48" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L48" s="9">
         <v>9</v>
@@ -12172,44 +12200,44 @@
       <c r="U48" s="9"/>
       <c r="V48" s="9"/>
       <c r="W48" s="26"/>
-      <c r="X48" s="146"/>
-      <c r="Y48" s="140"/>
-      <c r="Z48" s="140"/>
-      <c r="AA48" s="105"/>
+      <c r="X48" s="125"/>
+      <c r="Y48" s="128"/>
+      <c r="Z48" s="128"/>
+      <c r="AA48" s="87"/>
     </row>
-    <row r="49" spans="1:27" ht="20.45" customHeight="1">
-      <c r="A49" s="90" t="s">
-        <v>136</v>
-      </c>
-      <c r="B49" s="142" t="s">
-        <v>137</v>
-      </c>
-      <c r="C49" s="137" t="s">
-        <v>69</v>
-      </c>
-      <c r="D49" s="105" t="s">
-        <v>138</v>
-      </c>
-      <c r="E49" s="104">
+    <row r="49" spans="1:27" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="138" t="s">
+        <v>126</v>
+      </c>
+      <c r="B49" s="145" t="s">
+        <v>127</v>
+      </c>
+      <c r="C49" s="89" t="s">
+        <v>68</v>
+      </c>
+      <c r="D49" s="87" t="s">
+        <v>128</v>
+      </c>
+      <c r="E49" s="103">
         <v>74</v>
       </c>
-      <c r="F49" s="104" t="s">
-        <v>93</v>
-      </c>
-      <c r="G49" s="104" t="s">
-        <v>93</v>
-      </c>
-      <c r="H49" s="103" t="s">
+      <c r="F49" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="G49" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="H49" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="I49" s="104" t="s">
+      <c r="I49" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="J49" s="106" t="s">
+      <c r="J49" s="102" t="s">
+        <v>52</v>
+      </c>
+      <c r="K49" s="22" t="s">
         <v>53</v>
-      </c>
-      <c r="K49" s="22" t="s">
-        <v>54</v>
       </c>
       <c r="L49" s="37">
         <v>0.73199999999999998</v>
@@ -12247,26 +12275,26 @@
       <c r="W49" s="40">
         <v>0.73999999999999966</v>
       </c>
-      <c r="X49" s="146"/>
-      <c r="Y49" s="141"/>
-      <c r="Z49" s="140"/>
-      <c r="AA49" s="145" t="s">
-        <v>139</v>
+      <c r="X49" s="125"/>
+      <c r="Y49" s="127"/>
+      <c r="Z49" s="128"/>
+      <c r="AA49" s="121" t="s">
+        <v>129</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="20.45" customHeight="1">
-      <c r="A50" s="90"/>
-      <c r="B50" s="142"/>
-      <c r="C50" s="137"/>
-      <c r="D50" s="105"/>
-      <c r="E50" s="104"/>
-      <c r="F50" s="104"/>
-      <c r="G50" s="104"/>
-      <c r="H50" s="103"/>
-      <c r="I50" s="104"/>
-      <c r="J50" s="106"/>
+    <row r="50" spans="1:27" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="138"/>
+      <c r="B50" s="145"/>
+      <c r="C50" s="89"/>
+      <c r="D50" s="87"/>
+      <c r="E50" s="103"/>
+      <c r="F50" s="103"/>
+      <c r="G50" s="103"/>
+      <c r="H50" s="106"/>
+      <c r="I50" s="103"/>
+      <c r="J50" s="102"/>
       <c r="K50" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L50" s="17">
         <v>0.69299999999999995</v>
@@ -12298,44 +12326,44 @@
       <c r="U50" s="17"/>
       <c r="V50" s="17"/>
       <c r="W50" s="74"/>
-      <c r="X50" s="146"/>
-      <c r="Y50" s="141"/>
-      <c r="Z50" s="140"/>
-      <c r="AA50" s="145"/>
+      <c r="X50" s="125"/>
+      <c r="Y50" s="127"/>
+      <c r="Z50" s="128"/>
+      <c r="AA50" s="121"/>
     </row>
-    <row r="51" spans="1:27" ht="20.45" customHeight="1">
-      <c r="A51" s="136" t="s">
+    <row r="51" spans="1:27" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="139" t="s">
         <v>25</v>
       </c>
-      <c r="B51" s="125" t="s">
-        <v>140</v>
-      </c>
-      <c r="C51" s="137" t="s">
-        <v>74</v>
-      </c>
-      <c r="D51" s="105" t="s">
-        <v>141</v>
-      </c>
-      <c r="E51" s="104">
+      <c r="B51" s="88" t="s">
+        <v>130</v>
+      </c>
+      <c r="C51" s="89" t="s">
+        <v>71</v>
+      </c>
+      <c r="D51" s="87" t="s">
+        <v>131</v>
+      </c>
+      <c r="E51" s="103">
         <v>33.1</v>
       </c>
-      <c r="F51" s="104" t="s">
-        <v>93</v>
-      </c>
-      <c r="G51" s="104" t="s">
-        <v>93</v>
-      </c>
-      <c r="H51" s="103" t="s">
+      <c r="F51" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="G51" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="H51" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="I51" s="104" t="s">
+      <c r="I51" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="J51" s="106" t="s">
+      <c r="J51" s="102" t="s">
+        <v>52</v>
+      </c>
+      <c r="K51" s="22" t="s">
         <v>53</v>
-      </c>
-      <c r="K51" s="22" t="s">
-        <v>54</v>
       </c>
       <c r="L51" s="37">
         <v>0.34700072985878605</v>
@@ -12367,26 +12395,26 @@
       <c r="U51" s="35"/>
       <c r="V51" s="35"/>
       <c r="W51" s="38"/>
-      <c r="X51" s="146"/>
-      <c r="Y51" s="140"/>
-      <c r="Z51" s="140"/>
-      <c r="AA51" s="123" t="s">
-        <v>142</v>
+      <c r="X51" s="125"/>
+      <c r="Y51" s="128"/>
+      <c r="Z51" s="128"/>
+      <c r="AA51" s="90" t="s">
+        <v>132</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="20.45" customHeight="1" thickBot="1">
-      <c r="A52" s="136"/>
-      <c r="B52" s="125"/>
-      <c r="C52" s="137"/>
-      <c r="D52" s="105"/>
-      <c r="E52" s="104"/>
-      <c r="F52" s="104"/>
-      <c r="G52" s="104"/>
-      <c r="H52" s="103"/>
-      <c r="I52" s="104"/>
-      <c r="J52" s="106"/>
+    <row r="52" spans="1:27" ht="20.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="139"/>
+      <c r="B52" s="88"/>
+      <c r="C52" s="89"/>
+      <c r="D52" s="87"/>
+      <c r="E52" s="103"/>
+      <c r="F52" s="103"/>
+      <c r="G52" s="103"/>
+      <c r="H52" s="106"/>
+      <c r="I52" s="103"/>
+      <c r="J52" s="102"/>
       <c r="K52" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L52" s="17">
         <v>0.36591770011686803</v>
@@ -12418,34 +12446,238 @@
       <c r="U52" s="29"/>
       <c r="V52" s="29"/>
       <c r="W52" s="30"/>
-      <c r="X52" s="146"/>
-      <c r="Y52" s="140"/>
-      <c r="Z52" s="140"/>
-      <c r="AA52" s="123"/>
+      <c r="X52" s="125"/>
+      <c r="Y52" s="128"/>
+      <c r="Z52" s="128"/>
+      <c r="AA52" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="270">
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="X16:X17"/>
-    <mergeCell ref="Y16:Y17"/>
-    <mergeCell ref="Y28:Y29"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="X20:X21"/>
-    <mergeCell ref="Y20:Y21"/>
-    <mergeCell ref="X28:X29"/>
-    <mergeCell ref="X22:X23"/>
-    <mergeCell ref="Y22:Y23"/>
-    <mergeCell ref="Y26:Y27"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="A24:A33"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="Z32:Z33"/>
+    <mergeCell ref="Y32:Y33"/>
+    <mergeCell ref="X32:X33"/>
+    <mergeCell ref="Z24:Z25"/>
+    <mergeCell ref="Y24:Y25"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="Y30:Y31"/>
+    <mergeCell ref="Z28:Z29"/>
+    <mergeCell ref="Z30:Z31"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="AA30:AA31"/>
+    <mergeCell ref="X24:X25"/>
+    <mergeCell ref="E30:G31"/>
+    <mergeCell ref="E32:G33"/>
+    <mergeCell ref="E34:G35"/>
+    <mergeCell ref="E36:G37"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="I34:I35"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="X26:X27"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="E26:G27"/>
+    <mergeCell ref="E22:G23"/>
+    <mergeCell ref="AA22:AA23"/>
+    <mergeCell ref="Z22:Z23"/>
+    <mergeCell ref="Z26:Z27"/>
+    <mergeCell ref="AA6:AA7"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AA10:AA11"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="E6:G7"/>
+    <mergeCell ref="E8:G9"/>
+    <mergeCell ref="E10:G11"/>
+    <mergeCell ref="E12:G13"/>
+    <mergeCell ref="E14:G15"/>
+    <mergeCell ref="E16:G17"/>
+    <mergeCell ref="E18:G19"/>
+    <mergeCell ref="E20:G21"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="X10:X11"/>
+    <mergeCell ref="Y10:Y11"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="E28:G29"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="AA12:AA13"/>
+    <mergeCell ref="AA14:AA15"/>
+    <mergeCell ref="X14:X15"/>
+    <mergeCell ref="Y14:Y15"/>
+    <mergeCell ref="Z20:Z21"/>
+    <mergeCell ref="X12:X13"/>
+    <mergeCell ref="Y12:Y13"/>
+    <mergeCell ref="Z12:Z13"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="Z14:Z15"/>
+    <mergeCell ref="Z16:Z17"/>
+    <mergeCell ref="Z18:Z19"/>
+    <mergeCell ref="AA18:AA19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="X18:X19"/>
+    <mergeCell ref="Y18:Y19"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="F51:F52"/>
+    <mergeCell ref="G51:G52"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J45:J46"/>
+    <mergeCell ref="Y51:Y52"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="Y49:Y50"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="AA51:AA52"/>
+    <mergeCell ref="AA49:AA50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="J51:J52"/>
+    <mergeCell ref="X51:X52"/>
+    <mergeCell ref="Z51:Z52"/>
+    <mergeCell ref="X49:X50"/>
+    <mergeCell ref="A38:AA38"/>
+    <mergeCell ref="Z49:Z50"/>
+    <mergeCell ref="Y47:Y48"/>
+    <mergeCell ref="Z47:Z48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="X43:X44"/>
+    <mergeCell ref="Y43:Y44"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A48"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="AA32:AA33"/>
+    <mergeCell ref="AA16:AA17"/>
+    <mergeCell ref="AA20:AA21"/>
+    <mergeCell ref="AA41:AA42"/>
+    <mergeCell ref="AA45:AA46"/>
+    <mergeCell ref="AA47:AA48"/>
+    <mergeCell ref="AA24:AA25"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="AA28:AA29"/>
+    <mergeCell ref="AA26:AA27"/>
+    <mergeCell ref="AA34:AA35"/>
+    <mergeCell ref="AA36:AA37"/>
+    <mergeCell ref="X47:X48"/>
+    <mergeCell ref="Y41:Y42"/>
+    <mergeCell ref="Z41:Z42"/>
+    <mergeCell ref="X45:X46"/>
+    <mergeCell ref="Y45:Y46"/>
+    <mergeCell ref="AA43:AA44"/>
+    <mergeCell ref="Z43:Z44"/>
+    <mergeCell ref="Z45:Z46"/>
+    <mergeCell ref="X41:X42"/>
+    <mergeCell ref="X36:X37"/>
+    <mergeCell ref="X30:X31"/>
+    <mergeCell ref="Z36:Z37"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="X34:X35"/>
+    <mergeCell ref="Y34:Y35"/>
+    <mergeCell ref="Z34:Z35"/>
+    <mergeCell ref="Y36:Y37"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="C18:C19"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A3:B3"/>
@@ -12470,231 +12702,27 @@
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="J8:J9"/>
-    <mergeCell ref="Z36:Z37"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="X34:X35"/>
-    <mergeCell ref="Y34:Y35"/>
-    <mergeCell ref="Z34:Z35"/>
-    <mergeCell ref="Y36:Y37"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="AA32:AA33"/>
-    <mergeCell ref="AA16:AA17"/>
-    <mergeCell ref="AA20:AA21"/>
-    <mergeCell ref="AA41:AA42"/>
-    <mergeCell ref="AA45:AA46"/>
-    <mergeCell ref="AA47:AA48"/>
-    <mergeCell ref="AA24:AA25"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="AA28:AA29"/>
-    <mergeCell ref="AA26:AA27"/>
-    <mergeCell ref="AA34:AA35"/>
-    <mergeCell ref="AA36:AA37"/>
-    <mergeCell ref="X47:X48"/>
-    <mergeCell ref="Y41:Y42"/>
-    <mergeCell ref="Z41:Z42"/>
-    <mergeCell ref="X45:X46"/>
-    <mergeCell ref="Y45:Y46"/>
-    <mergeCell ref="AA43:AA44"/>
-    <mergeCell ref="Z43:Z44"/>
-    <mergeCell ref="Z45:Z46"/>
-    <mergeCell ref="X41:X42"/>
-    <mergeCell ref="X36:X37"/>
-    <mergeCell ref="X30:X31"/>
-    <mergeCell ref="AA51:AA52"/>
-    <mergeCell ref="AA49:AA50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="J51:J52"/>
-    <mergeCell ref="X51:X52"/>
-    <mergeCell ref="Z51:Z52"/>
-    <mergeCell ref="X49:X50"/>
-    <mergeCell ref="A38:AA38"/>
-    <mergeCell ref="Z49:Z50"/>
-    <mergeCell ref="Y47:Y48"/>
-    <mergeCell ref="Z47:Z48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="X43:X44"/>
-    <mergeCell ref="Y43:Y44"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A48"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="J45:J46"/>
-    <mergeCell ref="Y51:Y52"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="Y49:Y50"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="F51:F52"/>
-    <mergeCell ref="G51:G52"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="AA12:AA13"/>
-    <mergeCell ref="AA14:AA15"/>
-    <mergeCell ref="X14:X15"/>
-    <mergeCell ref="Y14:Y15"/>
-    <mergeCell ref="Z20:Z21"/>
-    <mergeCell ref="X12:X13"/>
-    <mergeCell ref="Y12:Y13"/>
-    <mergeCell ref="Z12:Z13"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="Z14:Z15"/>
-    <mergeCell ref="Z16:Z17"/>
-    <mergeCell ref="Z18:Z19"/>
-    <mergeCell ref="AA18:AA19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="X18:X19"/>
-    <mergeCell ref="Y18:Y19"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="E28:G29"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="I32:I33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="E26:G27"/>
-    <mergeCell ref="E22:G23"/>
-    <mergeCell ref="AA22:AA23"/>
-    <mergeCell ref="Z22:Z23"/>
-    <mergeCell ref="Z26:Z27"/>
-    <mergeCell ref="AA6:AA7"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AA10:AA11"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="E6:G7"/>
-    <mergeCell ref="E8:G9"/>
-    <mergeCell ref="E10:G11"/>
-    <mergeCell ref="E12:G13"/>
-    <mergeCell ref="E14:G15"/>
-    <mergeCell ref="E16:G17"/>
-    <mergeCell ref="E18:G19"/>
-    <mergeCell ref="E20:G21"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="X10:X11"/>
-    <mergeCell ref="Y10:Y11"/>
-    <mergeCell ref="AA30:AA31"/>
-    <mergeCell ref="X24:X25"/>
-    <mergeCell ref="E30:G31"/>
-    <mergeCell ref="E32:G33"/>
-    <mergeCell ref="E34:G35"/>
-    <mergeCell ref="E36:G37"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="H32:H33"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="I34:I35"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="X26:X27"/>
-    <mergeCell ref="A24:A33"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="Z32:Z33"/>
-    <mergeCell ref="Y32:Y33"/>
-    <mergeCell ref="X32:X33"/>
-    <mergeCell ref="Z24:Z25"/>
-    <mergeCell ref="Y24:Y25"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="Y30:Y31"/>
-    <mergeCell ref="Z28:Z29"/>
-    <mergeCell ref="Z30:Z31"/>
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="X16:X17"/>
+    <mergeCell ref="Y16:Y17"/>
+    <mergeCell ref="Y28:Y29"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="X20:X21"/>
+    <mergeCell ref="Y20:Y21"/>
+    <mergeCell ref="X28:X29"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="Y26:Y27"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="I12:I13"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B6 H6:J6 C6:C12 B8 H8:J8 B10 H10:J10 B12 H12:J12 H14:J14 H16:J16 H20:J20 C22 H22:J22 H24:J24 D26:E26 H26:J26 C26:C27 H28:J28 H30:J30 H32:J32 H34:J34 H36:J36 D41:J41 C41:C43 D45:J45 C45:C52 D47:J47 D49:J49 D51:J51">
@@ -13013,11 +13041,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -13155,13 +13178,12 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -13170,20 +13192,47 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB3DE2B1-3B6B-45A6-B5D6-4DFC8B688F1E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D35B5AFA-8D8A-4152-8465-0651392DA3FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="68108f69-118e-4385-83b3-00743b1bf54c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f5a961e1-edc1-4f62-8655-e8a46ef79e5c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -13199,7 +13199,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB3DE2B1-3B6B-45A6-B5D6-4DFC8B688F1E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0063A4B1-C40C-4501-B159-F510C79726E6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -13199,7 +13199,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0063A4B1-C40C-4501-B159-F510C79726E6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2856A1C-26B9-44C6-B5C4-875582D9F1BC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/GlobalMoSMT-2023/Shared Documents/General/2026/Goals Alignment 2026/Strategic Execution 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3351" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E9AEA8D-0DA6-49E7-94E7-3A95162BDB91}"/>
+  <xr:revisionPtr revIDLastSave="3352" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00BD3D4C-BD44-4126-BA34-012A5B3B89E0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
   </bookViews>
@@ -9551,7 +9551,7 @@
   <cols>
     <col min="1" max="1" width="25.54296875" customWidth="1"/>
     <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" style="1" customWidth="1"/>
     <col min="4" max="4" width="26.81640625" customWidth="1"/>
     <col min="5" max="5" width="5.1796875" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="4.54296875" hidden="1" customWidth="1"/>
@@ -13199,7 +13199,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2856A1C-26B9-44C6-B5C4-875582D9F1BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{027D36C5-224F-4894-BFD9-BC0879E806E0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/GlobalMoSMT-2023/Shared Documents/General/2026/Goals Alignment 2026/Strategic Execution 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3352" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00BD3D4C-BD44-4126-BA34-012A5B3B89E0}"/>
+  <xr:revisionPtr revIDLastSave="3353" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D338CB53-6341-484E-8B13-EB11B21BA77E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
+    <workbookView minimized="1" xWindow="3990" yWindow="0" windowWidth="9600" windowHeight="6000" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
   </bookViews>
   <sheets>
     <sheet name="Mastersheet" sheetId="5" r:id="rId1"/>
     <sheet name="AOP Critical" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028" calcCompleted="0" concurrentManualCount="14"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -5467,9 +5467,9 @@
         <f>IF('AOP Critical'!V7="","",'AOP Critical'!V7)</f>
         <v/>
       </c>
-      <c r="V6" s="67">
+      <c r="V6" s="67" t="str">
         <f>IF('AOP Critical'!W7="","",'AOP Critical'!W7)</f>
-        <v>7.0000000000000007E-2</v>
+        <v/>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.35">
@@ -9846,9 +9846,7 @@
       </c>
       <c r="U7" s="50"/>
       <c r="V7" s="50"/>
-      <c r="W7" s="50">
-        <v>7.0000000000000007E-2</v>
-      </c>
+      <c r="W7" s="50"/>
       <c r="X7" s="91"/>
       <c r="Y7" s="93"/>
       <c r="Z7" s="93"/>
@@ -13199,7 +13197,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{027D36C5-224F-4894-BFD9-BC0879E806E0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A1696FE-4AD6-4A32-8C72-2012B091FFE3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -13197,7 +13197,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A1696FE-4AD6-4A32-8C72-2012B091FFE3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33952598-C185-4A1C-875B-66EF559BDEC2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -13197,7 +13197,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33952598-C185-4A1C-875B-66EF559BDEC2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9107C667-8A83-4B78-837A-E58DD64D8D1A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -13197,7 +13197,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9107C667-8A83-4B78-837A-E58DD64D8D1A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BB2F6CD-52A6-4BF5-A736-C72821FD6679}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -13197,7 +13197,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BB2F6CD-52A6-4BF5-A736-C72821FD6679}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{510C4433-6A59-4A7C-B4FA-A71CD713FA82}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="3353" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D338CB53-6341-484E-8B13-EB11B21BA77E}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3990" yWindow="0" windowWidth="9600" windowHeight="6000" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
   </bookViews>
   <sheets>
     <sheet name="Mastersheet" sheetId="5" r:id="rId1"/>
@@ -13197,7 +13197,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{510C4433-6A59-4A7C-B4FA-A71CD713FA82}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DE396ED-5583-4DCD-8412-54E8129D456C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -13197,7 +13197,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DE396ED-5583-4DCD-8412-54E8129D456C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C4FB08B-4783-49A4-96F7-DD5BC89D40EE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -13197,7 +13197,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C4FB08B-4783-49A4-96F7-DD5BC89D40EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BFA13AF-4636-436E-8E36-82C3463B090E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -13197,7 +13197,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BFA13AF-4636-436E-8E36-82C3463B090E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09AC71C5-5BCB-43D4-A11E-192FA0775BEF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -13197,7 +13197,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09AC71C5-5BCB-43D4-A11E-192FA0775BEF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D5053A2-5186-45F5-BDA6-6E4EE17EFE0C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -13197,7 +13197,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D5053A2-5186-45F5-BDA6-6E4EE17EFE0C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48CB18A1-BAD4-4852-9500-CA631FA5ACCA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -13197,7 +13197,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48CB18A1-BAD4-4852-9500-CA631FA5ACCA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAD404F6-EFAF-438A-9E52-765E116BC393}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="3353" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D338CB53-6341-484E-8B13-EB11B21BA77E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
+    <workbookView minimized="1" xWindow="3990" yWindow="0" windowWidth="9600" windowHeight="6000" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
   </bookViews>
   <sheets>
     <sheet name="Mastersheet" sheetId="5" r:id="rId1"/>
@@ -13197,7 +13197,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAD404F6-EFAF-438A-9E52-765E116BC393}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3BBE96C-9DE5-4C2D-A888-81B3BE40A604}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -13197,7 +13197,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3BBE96C-9DE5-4C2D-A888-81B3BE40A604}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72C3C3D7-3D63-4ADE-B70B-70859ED83E92}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="3353" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D338CB53-6341-484E-8B13-EB11B21BA77E}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3990" yWindow="0" windowWidth="9600" windowHeight="6000" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
   </bookViews>
   <sheets>
     <sheet name="Mastersheet" sheetId="5" r:id="rId1"/>
@@ -13197,7 +13197,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72C3C3D7-3D63-4ADE-B70B-70859ED83E92}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B478CF5F-B1ED-4007-8A88-6493DB0977B7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -13197,7 +13197,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B478CF5F-B1ED-4007-8A88-6493DB0977B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37472E4F-5BD2-4B5E-BFDC-80710EA14686}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -13197,7 +13197,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37472E4F-5BD2-4B5E-BFDC-80710EA14686}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD1715EE-E406-4670-A361-62C1F7B5386F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -13197,7 +13197,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD1715EE-E406-4670-A361-62C1F7B5386F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{751A5037-890E-408B-84FB-FE44BDEA8A16}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -13197,7 +13197,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{751A5037-890E-408B-84FB-FE44BDEA8A16}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB0CFCEE-1D8F-46CB-B485-78E1C32C3331}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
